--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -961,7 +961,7 @@
         <v>78.93103851222787</v>
       </c>
       <c r="J6" t="n">
-        <v>47.80188401830082</v>
+        <v>47.45383708182479</v>
       </c>
       <c r="K6" t="n">
         <v>0.9725210130735034</v>
@@ -979,13 +979,13 @@
         <v>0.3354735513319747</v>
       </c>
       <c r="P6" t="n">
-        <v>102.7255412489931</v>
+        <v>103.0021862935916</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.725541248993103</v>
+        <v>3.00218629359158</v>
       </c>
       <c r="R6" t="n">
-        <v>-61.31193457658048</v>
+        <v>-47.70052328027374</v>
       </c>
       <c r="S6" t="n">
         <v>16.61777908527611</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 48); RSI ipercomprato (79) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 47); RSI ipercomprato (79) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -3441,52 +3441,52 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6.01800012588501</v>
+        <v>6.013999938964844</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.666662770938176</v>
+        <v>-1.732025303535689</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7994734944494986</v>
+        <v>-0.8654124509633543</v>
       </c>
       <c r="G33" t="n">
-        <v>10.98201895266073</v>
+        <v>10.90824879458472</v>
       </c>
       <c r="H33" t="n">
-        <v>1.81019040815924</v>
+        <v>1.742516798406624</v>
       </c>
       <c r="I33" t="n">
-        <v>59.03181131715577</v>
+        <v>58.79787118060198</v>
       </c>
       <c r="J33" t="n">
         <v>41.18504839863726</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7118642458761441</v>
+        <v>0.7082016218621492</v>
       </c>
       <c r="L33" t="n">
-        <v>5.88746229504312</v>
+        <v>5.887081324860246</v>
       </c>
       <c r="M33" t="n">
-        <v>5.784862869287112</v>
+        <v>5.784705999211812</v>
       </c>
       <c r="N33" t="n">
-        <v>5.390784341683061</v>
+        <v>5.390744538828134</v>
       </c>
       <c r="O33" t="n">
-        <v>0.03098514955627635</v>
+        <v>0.0307298669721969</v>
       </c>
       <c r="P33" t="n">
-        <v>78.39406953611015</v>
+        <v>77.73178703382069</v>
       </c>
       <c r="Q33" t="n">
-        <v>-21.60593046388986</v>
+        <v>-22.2682129661793</v>
       </c>
       <c r="R33" t="n">
-        <v>73.33510330531644</v>
+        <v>72.99061488786609</v>
       </c>
       <c r="S33" t="n">
-        <v>8.844281744277115</v>
+        <v>8.771932548022443</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3629,52 +3629,52 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>106.0599975585938</v>
+        <v>105.9499969482422</v>
       </c>
       <c r="E35" t="n">
-        <v>4.072214451334921</v>
+        <v>3.964275479302048</v>
       </c>
       <c r="F35" t="n">
-        <v>6.710934912874134</v>
+        <v>6.600259179875767</v>
       </c>
       <c r="G35" t="n">
-        <v>1.50253586651532</v>
+        <v>1.397262048350467</v>
       </c>
       <c r="H35" t="n">
-        <v>60.98968120872406</v>
+        <v>60.82271002636588</v>
       </c>
       <c r="I35" t="n">
-        <v>56.51326607877485</v>
+        <v>56.43550392523061</v>
       </c>
       <c r="J35" t="n">
         <v>24.05054899031809</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6182810600634471</v>
+        <v>0.6149626116446049</v>
       </c>
       <c r="L35" t="n">
-        <v>99.63768896358509</v>
+        <v>99.62721271498017</v>
       </c>
       <c r="M35" t="n">
-        <v>93.18843065247158</v>
+        <v>93.18411690304602</v>
       </c>
       <c r="N35" t="n">
-        <v>77.33811325798219</v>
+        <v>77.33701872454586</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.5038585561817581</v>
+        <v>-0.5108785381529128</v>
       </c>
       <c r="P35" t="n">
-        <v>77.47186901226412</v>
+        <v>77.04534475306825</v>
       </c>
       <c r="Q35" t="n">
-        <v>-22.52813098773587</v>
+        <v>-22.95465524693175</v>
       </c>
       <c r="R35" t="n">
-        <v>25.66839044128133</v>
+        <v>25.36188607292824</v>
       </c>
       <c r="S35" t="n">
-        <v>3.756599776984637</v>
+        <v>3.6489881461512</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5489,52 +5489,52 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>96.70999908447266</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E55" t="n">
-        <v>4.033993155047666</v>
+        <v>3.894151013590852</v>
       </c>
       <c r="F55" t="n">
-        <v>2.133273409002578</v>
+        <v>1.995986208594691</v>
       </c>
       <c r="G55" t="n">
-        <v>4.721170202913805</v>
+        <v>4.580404360395263</v>
       </c>
       <c r="H55" t="n">
-        <v>58.35925915792821</v>
+        <v>58.14639317779462</v>
       </c>
       <c r="I55" t="n">
-        <v>53.22447969302775</v>
+        <v>53.11916667753718</v>
       </c>
       <c r="J55" t="n">
         <v>18.80673059102289</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4647176078372875</v>
+        <v>0.4606976379621026</v>
       </c>
       <c r="L55" t="n">
-        <v>94.30710332505542</v>
+        <v>94.2947226342537</v>
       </c>
       <c r="M55" t="n">
-        <v>87.78469935494213</v>
+        <v>87.77960142343555</v>
       </c>
       <c r="N55" t="n">
-        <v>72.76344358789842</v>
+        <v>72.76215008288928</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.401693885748485</v>
+        <v>-1.409990006764334</v>
       </c>
       <c r="P55" t="n">
-        <v>43.56623053367276</v>
+        <v>43.21555005218325</v>
       </c>
       <c r="Q55" t="n">
-        <v>-56.43376946632724</v>
+        <v>-56.78444994781675</v>
       </c>
       <c r="R55" t="n">
-        <v>-18.83886155609971</v>
+        <v>-19.2241759980246</v>
       </c>
       <c r="S55" t="n">
-        <v>7.074844343710307</v>
+        <v>6.930914700378588</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="W55" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="X55" t="n">
         <v>79.2</v>
@@ -5581,52 +5581,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>159.7149963378906</v>
+        <v>159.7010040283203</v>
       </c>
       <c r="E56" t="n">
-        <v>0.214587939550781</v>
+        <v>0.2058083410781064</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5704906950205313</v>
+        <v>0.5616799166233255</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6281543391333466</v>
+        <v>0.6193385089402703</v>
       </c>
       <c r="H56" t="n">
-        <v>3.485251563982383</v>
+        <v>3.476185429248368</v>
       </c>
       <c r="I56" t="n">
-        <v>56.78175520470175</v>
+        <v>56.68743323980835</v>
       </c>
       <c r="J56" t="n">
         <v>18.64026120965874</v>
       </c>
       <c r="K56" t="n">
-        <v>0.732774483182578</v>
+        <v>0.7262490148743661</v>
       </c>
       <c r="L56" t="n">
-        <v>159.0811536534126</v>
+        <v>159.0798210525012</v>
       </c>
       <c r="M56" t="n">
-        <v>158.249579179845</v>
+        <v>158.2490304618226</v>
       </c>
       <c r="N56" t="n">
-        <v>154.6487800300269</v>
+        <v>154.648640803066</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.05930838884831624</v>
+        <v>-0.0602013453565261</v>
       </c>
       <c r="P56" t="n">
-        <v>87.51547786110247</v>
+        <v>86.93319278906296</v>
       </c>
       <c r="Q56" t="n">
-        <v>-12.48452213889753</v>
+        <v>-13.06680721093705</v>
       </c>
       <c r="R56" t="n">
-        <v>58.79576300121095</v>
+        <v>58.16167285539258</v>
       </c>
       <c r="S56" t="n">
-        <v>0.2076705608885732</v>
+        <v>0.1988915684335346</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5769,52 +5769,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.346549272537231</v>
+        <v>1.346545696258545</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.327078859386265</v>
+        <v>-0.3273435791041224</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7971585856231478</v>
+        <v>-0.7974220568637724</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3663976824076043</v>
+        <v>0.3661311208964957</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.549738645187337</v>
+        <v>-1.550000117662609</v>
       </c>
       <c r="I58" t="n">
-        <v>52.78177662781864</v>
+        <v>52.77925200733311</v>
       </c>
       <c r="J58" t="n">
         <v>35.816263122645</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6448622869739232</v>
+        <v>0.644800549526221</v>
       </c>
       <c r="L58" t="n">
-        <v>1.343773615922409</v>
+        <v>1.343773275324439</v>
       </c>
       <c r="M58" t="n">
-        <v>1.342366712529883</v>
+        <v>1.342366572283661</v>
       </c>
       <c r="N58" t="n">
-        <v>1.337413551362701</v>
+        <v>1.337413515777838</v>
       </c>
       <c r="O58" t="n">
-        <v>0.001537653116546977</v>
+        <v>0.001537424886796145</v>
       </c>
       <c r="P58" t="n">
-        <v>67.49310011528922</v>
+        <v>67.48436608400974</v>
       </c>
       <c r="Q58" t="n">
-        <v>-32.50689988471079</v>
+        <v>-32.51563391599026</v>
       </c>
       <c r="R58" t="n">
-        <v>46.71053091154222</v>
+        <v>46.70444653115718</v>
       </c>
       <c r="S58" t="n">
-        <v>0.7622865563744474</v>
+        <v>0.7620189434283997</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6225,52 +6225,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>77911.09375</v>
+        <v>77984</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3733967153037088</v>
+        <v>-0.2801699141368408</v>
       </c>
       <c r="F63" t="n">
-        <v>2.885239846878473</v>
+        <v>2.981515956692249</v>
       </c>
       <c r="G63" t="n">
-        <v>16.47893412283046</v>
+        <v>16.58793069677333</v>
       </c>
       <c r="H63" t="n">
-        <v>14.56600312429133</v>
+        <v>14.67320964987398</v>
       </c>
       <c r="I63" t="n">
-        <v>64.26124329399308</v>
+        <v>64.53223810986381</v>
       </c>
       <c r="J63" t="n">
         <v>45.68130131762761</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8575238302100211</v>
+        <v>0.8625119937210681</v>
       </c>
       <c r="L63" t="n">
-        <v>74092.08413614359</v>
+        <v>74099.02758852454</v>
       </c>
       <c r="M63" t="n">
-        <v>72565.60000066027</v>
+        <v>72568.45906928772</v>
       </c>
       <c r="N63" t="n">
-        <v>82605.48188146936</v>
+        <v>82606.20731679273</v>
       </c>
       <c r="O63" t="n">
-        <v>411.3826159723376</v>
+        <v>416.0353225250419</v>
       </c>
       <c r="P63" t="n">
-        <v>82.56041991369646</v>
+        <v>83.37707434338166</v>
       </c>
       <c r="Q63" t="n">
-        <v>-17.43958008630354</v>
+        <v>-16.62292565661834</v>
       </c>
       <c r="R63" t="n">
-        <v>84.31034526659771</v>
+        <v>84.71425120825873</v>
       </c>
       <c r="S63" t="n">
-        <v>16.40491779034434</v>
+        <v>16.51384510260727</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>59.8</v>
       </c>
       <c r="X63" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 46); RSI in forza (64) — momentum positivo; segnale candlestick: Bearish Harami; in zona Fib Fib 38.2 — livello strutturale; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 46); RSI in forza (65) — momentum positivo; segnale candlestick: Bearish Harami; in zona Fib Fib 38.2 — livello strutturale; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -7437,52 +7437,52 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4707.7998046875</v>
+        <v>4705.39990234375</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5219270007923882</v>
+        <v>-0.5726380909931272</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.621601104188675</v>
+        <v>-1.671751611831196</v>
       </c>
       <c r="G76" t="n">
-        <v>7.012479569391705</v>
+        <v>6.957927653171025</v>
       </c>
       <c r="H76" t="n">
-        <v>-5.393681525872474</v>
+        <v>-5.441909134279599</v>
       </c>
       <c r="I76" t="n">
-        <v>46.74070501610692</v>
+        <v>46.61769538470455</v>
       </c>
       <c r="J76" t="n">
         <v>31.15818978795262</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5109924759529426</v>
+        <v>0.5063080781855865</v>
       </c>
       <c r="L76" t="n">
-        <v>4751.248224830999</v>
+        <v>4751.019662703022</v>
       </c>
       <c r="M76" t="n">
-        <v>4772.998417555489</v>
+        <v>4772.904303738087</v>
       </c>
       <c r="N76" t="n">
-        <v>4293.531430050952</v>
+        <v>4293.50755042564</v>
       </c>
       <c r="O76" t="n">
-        <v>9.89798768025846</v>
+        <v>9.74483151928996</v>
       </c>
       <c r="P76" t="n">
-        <v>37.42254517531542</v>
+        <v>36.54890096802978</v>
       </c>
       <c r="Q76" t="n">
-        <v>-62.57745482468458</v>
+        <v>-63.45109903197022</v>
       </c>
       <c r="R76" t="n">
-        <v>9.329168852335787</v>
+        <v>9.001301241289806</v>
       </c>
       <c r="S76" t="n">
-        <v>3.472680266881589</v>
+        <v>3.419932839593098</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7515,83 +7515,83 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MOO</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Agribusiness</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>83.12999725341797</v>
+        <v>2326.219970703125</v>
       </c>
       <c r="E77" t="n">
-        <v>0.02406045351890373</v>
+        <v>-2.098750603264932</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.7995295631743837</v>
+        <v>-1.058253967660594</v>
       </c>
       <c r="G77" t="n">
-        <v>1.119083054605063</v>
+        <v>13.09609836023544</v>
       </c>
       <c r="H77" t="n">
-        <v>4.76370365719625</v>
+        <v>18.14086233482954</v>
       </c>
       <c r="I77" t="n">
-        <v>45.35554130370132</v>
+        <v>55.3902225703355</v>
       </c>
       <c r="J77" t="n">
-        <v>27.39858677518637</v>
+        <v>47.76939751961269</v>
       </c>
       <c r="K77" t="n">
-        <v>0.2448120791372954</v>
+        <v>0.6387888171610275</v>
       </c>
       <c r="L77" t="n">
-        <v>83.8359717804021</v>
+        <v>2276.814307480008</v>
       </c>
       <c r="M77" t="n">
-        <v>83.00361606280865</v>
+        <v>2226.010301975022</v>
       </c>
       <c r="N77" t="n">
-        <v>77.86687997661033</v>
+        <v>2636.91315048008</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.2484960445130959</v>
+        <v>0.1741131713582789</v>
       </c>
       <c r="P77" t="n">
-        <v>12.88658172093755</v>
+        <v>51.9641954860109</v>
       </c>
       <c r="Q77" t="n">
-        <v>-87.11341827906246</v>
+        <v>-48.0358045139891</v>
       </c>
       <c r="R77" t="n">
-        <v>-69.47277854259958</v>
+        <v>36.9860126584938</v>
       </c>
       <c r="S77" t="n">
-        <v>0.2290750017109655</v>
+        <v>13.28706906206951</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W77" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="X77" t="n">
-        <v>68.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7600,94 +7600,90 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); pattern: Double Top; sul supporto dei 20g (82.41); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 48); pattern: Bull Flag / Consolidation; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>MOO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Agribusiness</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.434100031852722</v>
+        <v>83.12999725341797</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2847545803815077</v>
+        <v>0.02406045351890373</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.04063151511596308</v>
+        <v>-0.7995295631743837</v>
       </c>
       <c r="G78" t="n">
-        <v>8.751786072333157</v>
+        <v>1.119083054605063</v>
       </c>
       <c r="H78" t="n">
-        <v>0.3278264975613787</v>
+        <v>4.76370365719625</v>
       </c>
       <c r="I78" t="n">
-        <v>56.39184229456626</v>
+        <v>45.35554130370132</v>
       </c>
       <c r="J78" t="n">
-        <v>30.7101634397846</v>
+        <v>27.39858677518637</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7561663730868244</v>
+        <v>0.2448120791372954</v>
       </c>
       <c r="L78" t="n">
-        <v>1.399948418551437</v>
+        <v>83.8359717804021</v>
       </c>
       <c r="M78" t="n">
-        <v>1.413700475473443</v>
+        <v>83.00361606280865</v>
       </c>
       <c r="N78" t="n">
-        <v>1.77906755991494</v>
+        <v>77.86687997661033</v>
       </c>
       <c r="O78" t="n">
-        <v>0.007611267121834756</v>
+        <v>-0.2484960445130959</v>
       </c>
       <c r="P78" t="n">
-        <v>60.35566877337805</v>
+        <v>12.88658172093755</v>
       </c>
       <c r="Q78" t="n">
-        <v>-39.64433122662195</v>
+        <v>-87.11341827906246</v>
       </c>
       <c r="R78" t="n">
-        <v>69.39581010006799</v>
+        <v>-69.47277854259958</v>
       </c>
       <c r="S78" t="n">
-        <v>8.816483882770454</v>
+        <v>0.2290750017109655</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W78" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="X78" t="n">
-        <v>74.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7696,19 +7692,19 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); pattern: Double Bottom; candela di inversione bullish (engulfing); penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 27); pattern: Double Top; sul supporto dei 20g (82.41); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7717,69 +7713,73 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2323.330078125</v>
+        <v>1.435400009155273</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.220374567285532</v>
+        <v>0.375660306516945</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.181170553850486</v>
+        <v>0.04997925632361788</v>
       </c>
       <c r="G79" t="n">
-        <v>12.95559764259808</v>
+        <v>8.8503669595557</v>
       </c>
       <c r="H79" t="n">
-        <v>17.99409444291282</v>
+        <v>0.4187712673572763</v>
       </c>
       <c r="I79" t="n">
-        <v>55.17761372403093</v>
+        <v>56.5667712227112</v>
       </c>
       <c r="J79" t="n">
-        <v>47.76939751961269</v>
+        <v>30.7101634397846</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6320539476778102</v>
+        <v>0.7620851862799014</v>
       </c>
       <c r="L79" t="n">
-        <v>2276.539079615424</v>
+        <v>1.400072225913585</v>
       </c>
       <c r="M79" t="n">
-        <v>2225.896972854311</v>
+        <v>1.413751454975504</v>
       </c>
       <c r="N79" t="n">
-        <v>2636.884395330049</v>
+        <v>1.779080495012478</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.01031302166212811</v>
+        <v>0.007694228636299694</v>
       </c>
       <c r="P79" t="n">
-        <v>50.96235634056606</v>
+        <v>61.05894492454533</v>
       </c>
       <c r="Q79" t="n">
-        <v>-49.03764365943393</v>
+        <v>-38.94105507545466</v>
       </c>
       <c r="R79" t="n">
-        <v>36.48777288306212</v>
+        <v>69.98816633533384</v>
       </c>
       <c r="S79" t="n">
-        <v>13.14633109910677</v>
+        <v>8.915123417007331</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Hammer, Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W79" t="n">
-        <v>55.5</v>
+        <v>55.8</v>
       </c>
       <c r="X79" t="n">
-        <v>71.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 48); pattern: Bull Flag / Consolidation; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 31); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -7809,52 +7809,52 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>75.38500213623047</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.219795974197204</v>
+        <v>-3.226221305045418</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.097652286517983</v>
+        <v>-4.104019335641129</v>
       </c>
       <c r="G80" t="n">
-        <v>8.821491292507977</v>
+        <v>8.814266529014358</v>
       </c>
       <c r="H80" t="n">
-        <v>-25.30592037973936</v>
+        <v>-25.31087939154135</v>
       </c>
       <c r="I80" t="n">
-        <v>47.00724217260541</v>
+        <v>46.99941491692338</v>
       </c>
       <c r="J80" t="n">
         <v>18.16319029254958</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5005638333885781</v>
+        <v>0.5002428789336565</v>
       </c>
       <c r="L80" t="n">
-        <v>76.8906407644827</v>
+        <v>76.89016410897675</v>
       </c>
       <c r="M80" t="n">
-        <v>77.42828247064199</v>
+        <v>77.42808620072778</v>
       </c>
       <c r="N80" t="n">
-        <v>64.40165318834158</v>
+        <v>64.4016033885126</v>
       </c>
       <c r="O80" t="n">
-        <v>0.4048877372575233</v>
+        <v>0.4045683373287473</v>
       </c>
       <c r="P80" t="n">
-        <v>41.97195142401469</v>
+        <v>41.9329422104666</v>
       </c>
       <c r="Q80" t="n">
-        <v>-58.02804857598531</v>
+        <v>-58.0670577895334</v>
       </c>
       <c r="R80" t="n">
-        <v>11.95675161877016</v>
+        <v>11.93355213659001</v>
       </c>
       <c r="S80" t="n">
-        <v>4.179049588375805</v>
+        <v>4.172133041052972</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7887,87 +7887,83 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.168770432472229</v>
+        <v>2016.099975585938</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.4815365156224827</v>
+        <v>-2.726050342958308</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.028512925787006</v>
+        <v>-3.724756145019592</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6287941621823778</v>
+        <v>6.559195326952305</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.589526230645721</v>
+        <v>-25.93586189861954</v>
       </c>
       <c r="I81" t="n">
-        <v>50.98401094051396</v>
+        <v>47.51155736778559</v>
       </c>
       <c r="J81" t="n">
-        <v>41.33755530898934</v>
+        <v>30.40702094970498</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5745656053357326</v>
+        <v>0.5145222109116466</v>
       </c>
       <c r="L81" t="n">
-        <v>1.16880349740695</v>
+        <v>2043.503056443961</v>
       </c>
       <c r="M81" t="n">
-        <v>1.167190537267485</v>
+        <v>2060.031791023349</v>
       </c>
       <c r="N81" t="n">
-        <v>1.15967937969669</v>
+        <v>1817.275614522447</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0009417033320426259</v>
+        <v>6.820965907734315</v>
       </c>
       <c r="P81" t="n">
-        <v>52.51440762495844</v>
+        <v>42.83604650813351</v>
       </c>
       <c r="Q81" t="n">
-        <v>-47.48559237504156</v>
+        <v>-57.16395349186649</v>
       </c>
       <c r="R81" t="n">
-        <v>24.53844918135707</v>
+        <v>22.14542942260731</v>
       </c>
       <c r="S81" t="n">
-        <v>1.091623991620949</v>
+        <v>4.72158875542934</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
+          <t>Double Bottom, Outside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W81" t="n">
         <v>54.8</v>
       </c>
       <c r="X81" t="n">
-        <v>59.4</v>
+        <v>72</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -7976,90 +7972,94 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 41); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; vicino alla resistenza dei 20g (1.1851); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 30); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>2015.5</v>
+        <v>1.168770432472229</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.75499830965078</v>
+        <v>-0.4815365156224827</v>
       </c>
       <c r="F82" t="n">
-        <v>-3.753406904675682</v>
+        <v>-1.028512925787006</v>
       </c>
       <c r="G82" t="n">
-        <v>6.527484143763207</v>
+        <v>0.6287941621823778</v>
       </c>
       <c r="H82" t="n">
-        <v>-25.95790280690407</v>
+        <v>-1.589526230645721</v>
       </c>
       <c r="I82" t="n">
-        <v>47.46821138903463</v>
+        <v>50.98401094051396</v>
       </c>
       <c r="J82" t="n">
-        <v>30.40702094970498</v>
+        <v>41.33755530898934</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5128536387270496</v>
+        <v>0.5745656053357326</v>
       </c>
       <c r="L82" t="n">
-        <v>2043.445915911967</v>
+        <v>1.16880349740695</v>
       </c>
       <c r="M82" t="n">
-        <v>2060.008262568999</v>
+        <v>1.167190537267485</v>
       </c>
       <c r="N82" t="n">
-        <v>1817.269644616119</v>
+        <v>1.15967937969669</v>
       </c>
       <c r="O82" t="n">
-        <v>6.782676867492372</v>
+        <v>0.0009417033320426259</v>
       </c>
       <c r="P82" t="n">
-        <v>42.54063751844428</v>
+        <v>52.51440762495844</v>
       </c>
       <c r="Q82" t="n">
-        <v>-57.45936248155572</v>
+        <v>-47.48559237504156</v>
       </c>
       <c r="R82" t="n">
-        <v>22.0212466877602</v>
+        <v>24.53844918135707</v>
       </c>
       <c r="S82" t="n">
-        <v>4.690424429585049</v>
+        <v>1.091623991620949</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr"/>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Double Bottom, Outside Bar, Bull Flag / Consolidation</t>
+          <t>Double Top, Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W82" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="X82" t="n">
-        <v>72</v>
+        <v>59.4</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 30); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 41); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; vicino alla resistenza dei 20g (1.1851); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -8181,52 +8181,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>9.303000450134277</v>
+        <v>9.314999580383301</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0458851605401156</v>
+        <v>0.1749256366053276</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1090486241308586</v>
+        <v>0.2381705692479752</v>
       </c>
       <c r="G84" t="n">
-        <v>7.817611681864256</v>
+        <v>7.956676231268922</v>
       </c>
       <c r="H84" t="n">
-        <v>4.044041731514847</v>
+        <v>4.178239081613144</v>
       </c>
       <c r="I84" t="n">
-        <v>53.06597795965542</v>
+        <v>53.26431337140535</v>
       </c>
       <c r="J84" t="n">
         <v>26.41326136077118</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6491870264439139</v>
+        <v>0.6594259756724083</v>
       </c>
       <c r="L84" t="n">
-        <v>9.179171137195546</v>
+        <v>9.180313911504976</v>
       </c>
       <c r="M84" t="n">
-        <v>9.201294496441804</v>
+        <v>9.201765050569216</v>
       </c>
       <c r="N84" t="n">
-        <v>11.81198042146294</v>
+        <v>11.81209981579378</v>
       </c>
       <c r="O84" t="n">
-        <v>0.01666474093828908</v>
+        <v>0.0174304973986254</v>
       </c>
       <c r="P84" t="n">
-        <v>52.03218307718846</v>
+        <v>53.06568863406741</v>
       </c>
       <c r="Q84" t="n">
-        <v>-47.96781692281154</v>
+        <v>-46.93431136593259</v>
       </c>
       <c r="R84" t="n">
-        <v>38.18011957763543</v>
+        <v>39.14659534144751</v>
       </c>
       <c r="S84" t="n">
-        <v>7.447383853234779</v>
+        <v>7.585970877999793</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="W84" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="X84" t="n">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -8369,52 +8369,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>98.81300354003906</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2261965822416112</v>
+        <v>0.2332927938706097</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6037490449663618</v>
+        <v>0.6108719880514757</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.6205338059368404</v>
+        <v>-0.6134975444828661</v>
       </c>
       <c r="H86" t="n">
-        <v>1.242833078772643</v>
+        <v>1.250001270262935</v>
       </c>
       <c r="I86" t="n">
-        <v>49.80674195193146</v>
+        <v>49.89771666757966</v>
       </c>
       <c r="J86" t="n">
         <v>37.35734105194766</v>
       </c>
       <c r="K86" t="n">
-        <v>0.4266765311414699</v>
+        <v>0.4286594030126377</v>
       </c>
       <c r="L86" t="n">
-        <v>98.77302471010404</v>
+        <v>98.77369101055976</v>
       </c>
       <c r="M86" t="n">
-        <v>98.79402266057278</v>
+        <v>98.79429701958396</v>
       </c>
       <c r="N86" t="n">
-        <v>99.1224161837786</v>
+        <v>99.12248579725905</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.06317170270958383</v>
+        <v>-0.06272522445550166</v>
       </c>
       <c r="P86" t="n">
-        <v>44.47385932104218</v>
+        <v>44.73687229673141</v>
       </c>
       <c r="Q86" t="n">
-        <v>-55.52614067895782</v>
+        <v>-55.26312770326859</v>
       </c>
       <c r="R86" t="n">
-        <v>-26.49982892843805</v>
+        <v>-26.30246620878067</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.7901555684124983</v>
+        <v>-0.7831313165125642</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8933,52 +8933,52 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>85.69999694824219</v>
+        <v>85.80000305175781</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.398856817422334</v>
+        <v>-1.283795948308986</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.5831789358869632</v>
+        <v>-0.4671662258219134</v>
       </c>
       <c r="G92" t="n">
-        <v>8.547900637273331</v>
+        <v>8.674568699981556</v>
       </c>
       <c r="H92" t="n">
-        <v>1.25821070443195</v>
+        <v>1.376372191737829</v>
       </c>
       <c r="I92" t="n">
-        <v>50.76734116801742</v>
+        <v>50.95389330333007</v>
       </c>
       <c r="J92" t="n">
         <v>15.81676323019232</v>
       </c>
       <c r="K92" t="n">
-        <v>0.6092820323663177</v>
+        <v>0.6188843788153817</v>
       </c>
       <c r="L92" t="n">
-        <v>85.29063754602709</v>
+        <v>85.30016193683811</v>
       </c>
       <c r="M92" t="n">
-        <v>87.07432884841138</v>
+        <v>87.07825065639238</v>
       </c>
       <c r="N92" t="n">
-        <v>116.3570699380338</v>
+        <v>116.3580650236409</v>
       </c>
       <c r="O92" t="n">
-        <v>0.2773005186784711</v>
+        <v>0.2836826745723509</v>
       </c>
       <c r="P92" t="n">
-        <v>46.34986838507331</v>
+        <v>47.42947317789923</v>
       </c>
       <c r="Q92" t="n">
-        <v>-53.65013161492668</v>
+        <v>-52.57052682210077</v>
       </c>
       <c r="R92" t="n">
-        <v>33.5103569288838</v>
+        <v>34.3603816282762</v>
       </c>
       <c r="S92" t="n">
-        <v>6.633753766114614</v>
+        <v>6.758188148811684</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="W92" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="X92" t="n">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -9199,83 +9199,83 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>187.6000061035156</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="E95" t="n">
-        <v>0.6869894423466416</v>
+        <v>-0.09023166942870864</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.2923134790380755</v>
+        <v>-0.01952915044725057</v>
       </c>
       <c r="G95" t="n">
-        <v>-9.279939941805715</v>
+        <v>6.718560891973957</v>
       </c>
       <c r="H95" t="n">
-        <v>12.52399515950797</v>
+        <v>1.871045861993892</v>
       </c>
       <c r="I95" t="n">
-        <v>44.20878712036655</v>
+        <v>50.54403862889385</v>
       </c>
       <c r="J95" t="n">
-        <v>27.94193093460997</v>
+        <v>11.57160422805518</v>
       </c>
       <c r="K95" t="n">
-        <v>0.3222581729498758</v>
+        <v>0.529455557156444</v>
       </c>
       <c r="L95" t="n">
-        <v>190.8660994586552</v>
+        <v>9.31713541006458</v>
       </c>
       <c r="M95" t="n">
-        <v>188.9591777509368</v>
+        <v>9.423815906362012</v>
       </c>
       <c r="N95" t="n">
-        <v>170.3927978675914</v>
+        <v>13.03827820831332</v>
       </c>
       <c r="O95" t="n">
-        <v>-1.23392995107507</v>
+        <v>-0.0003513998630566839</v>
       </c>
       <c r="P95" t="n">
-        <v>36.68156404918918</v>
+        <v>37.07700890177019</v>
       </c>
       <c r="Q95" t="n">
-        <v>-63.31843595081082</v>
+        <v>-62.92299109822981</v>
       </c>
       <c r="R95" t="n">
-        <v>-50.63032932581163</v>
+        <v>2.712060330658014</v>
       </c>
       <c r="S95" t="n">
-        <v>-8.554710365638229</v>
+        <v>4.803359802860063</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="n">
         <v>45.2</v>
       </c>
       <c r="X95" t="n">
-        <v>62</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -9284,19 +9284,19 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 12); doji — indecisione del mercato; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9305,52 +9305,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>150.5299987792969</v>
+        <v>187.6000061035156</v>
       </c>
       <c r="E96" t="n">
-        <v>0.688962394178505</v>
+        <v>0.6869894423466416</v>
       </c>
       <c r="F96" t="n">
-        <v>-0.9540709231507405</v>
+        <v>-0.2923134790380755</v>
       </c>
       <c r="G96" t="n">
-        <v>-8.979323778614145</v>
+        <v>-9.279939941805715</v>
       </c>
       <c r="H96" t="n">
-        <v>11.52848589898878</v>
+        <v>12.52399515950797</v>
       </c>
       <c r="I96" t="n">
-        <v>44.12610205291566</v>
+        <v>44.20878712036655</v>
       </c>
       <c r="J96" t="n">
-        <v>26.04755064752774</v>
+        <v>27.94193093460997</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3124551651628892</v>
+        <v>0.3222581729498758</v>
       </c>
       <c r="L96" t="n">
-        <v>153.4241665617511</v>
+        <v>190.8660994586552</v>
       </c>
       <c r="M96" t="n">
-        <v>151.6238484346959</v>
+        <v>188.9591777509368</v>
       </c>
       <c r="N96" t="n">
-        <v>132.8130545886702</v>
+        <v>170.3927978675914</v>
       </c>
       <c r="O96" t="n">
-        <v>-1.160041869642174</v>
+        <v>-1.23392995107507</v>
       </c>
       <c r="P96" t="n">
-        <v>35.26986424269706</v>
+        <v>36.68156404918918</v>
       </c>
       <c r="Q96" t="n">
-        <v>-64.73013575730293</v>
+        <v>-63.31843595081082</v>
       </c>
       <c r="R96" t="n">
-        <v>-51.5400708518328</v>
+        <v>-50.63032932581163</v>
       </c>
       <c r="S96" t="n">
-        <v>-7.797376060187256</v>
+        <v>-8.554710365638229</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="W96" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="X96" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9376,90 +9376,90 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 28); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Investment Grade Corp ETF</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>109.5199966430664</v>
+        <v>150.5299987792969</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.2731770648256027</v>
+        <v>0.688962394178505</v>
       </c>
       <c r="F97" t="n">
-        <v>0.08224101036247156</v>
+        <v>-0.9540709231507405</v>
       </c>
       <c r="G97" t="n">
-        <v>1.089164062268932</v>
+        <v>-8.979323778614145</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.190905574193868</v>
+        <v>11.52848589898878</v>
       </c>
       <c r="I97" t="n">
-        <v>50.24992371487744</v>
+        <v>44.12610205291566</v>
       </c>
       <c r="J97" t="n">
-        <v>17.0003976352271</v>
+        <v>26.04755064752774</v>
       </c>
       <c r="K97" t="n">
-        <v>0.6021058773104883</v>
+        <v>0.3124551651628892</v>
       </c>
       <c r="L97" t="n">
-        <v>109.4932316896937</v>
+        <v>153.4241665617511</v>
       </c>
       <c r="M97" t="n">
-        <v>109.6907843285293</v>
+        <v>151.6238484346959</v>
       </c>
       <c r="N97" t="n">
-        <v>109.9777522424339</v>
+        <v>132.8130545886702</v>
       </c>
       <c r="O97" t="n">
-        <v>0.08848631271169924</v>
+        <v>-1.160041869642174</v>
       </c>
       <c r="P97" t="n">
-        <v>61.88105723544564</v>
+        <v>35.26986424269706</v>
       </c>
       <c r="Q97" t="n">
-        <v>-38.11894276455436</v>
+        <v>-64.73013575730293</v>
       </c>
       <c r="R97" t="n">
-        <v>31.02979111052034</v>
+        <v>-51.5400708518328</v>
       </c>
       <c r="S97" t="n">
-        <v>0.7265642065138689</v>
+        <v>-7.797376060187256</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U97" t="inlineStr"/>
       <c r="V97" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W97" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="X97" t="n">
-        <v>63.3</v>
+        <v>62.2</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -9468,94 +9468,90 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; vicino alla resistenza dei 20g (110.29); in zona Fib Fib 50.0 — livello strutturale; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 26); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Investment Grade Corp ETF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>230.6499938964844</v>
+        <v>109.5199966430664</v>
       </c>
       <c r="E98" t="n">
-        <v>2.012378447652763</v>
+        <v>-0.2731770648256027</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.658565490322472</v>
+        <v>0.08224101036247156</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.963705653962688</v>
+        <v>1.089164062268932</v>
       </c>
       <c r="H98" t="n">
-        <v>4.774232095927844</v>
+        <v>-1.190905574193868</v>
       </c>
       <c r="I98" t="n">
-        <v>39.50218861531254</v>
+        <v>50.24992371487744</v>
       </c>
       <c r="J98" t="n">
-        <v>21.94832483422106</v>
+        <v>17.0003976352271</v>
       </c>
       <c r="K98" t="n">
-        <v>0.1830365576793783</v>
+        <v>0.6021058773104883</v>
       </c>
       <c r="L98" t="n">
-        <v>235.551725476233</v>
+        <v>109.4932316896937</v>
       </c>
       <c r="M98" t="n">
-        <v>235.3816498815415</v>
+        <v>109.6907843285293</v>
       </c>
       <c r="N98" t="n">
-        <v>209.7595009673515</v>
+        <v>109.9777522424339</v>
       </c>
       <c r="O98" t="n">
-        <v>-1.381654913750403</v>
+        <v>0.08848631271169924</v>
       </c>
       <c r="P98" t="n">
-        <v>33.64346588255514</v>
+        <v>61.88105723544564</v>
       </c>
       <c r="Q98" t="n">
-        <v>-66.35653411744487</v>
+        <v>-38.11894276455436</v>
       </c>
       <c r="R98" t="n">
-        <v>-140.626121860965</v>
+        <v>31.02979111052034</v>
       </c>
       <c r="S98" t="n">
-        <v>-3.867794382771061</v>
+        <v>0.7265642065138689</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W98" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="X98" t="n">
-        <v>59.8</v>
+        <v>63.3</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -9564,73 +9560,73 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); pattern: Double Top; morning star — inversione rialzista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>pattern: Double Bottom; vicino alla resistenza dei 20g (110.29); in zona Fib Fib 50.0 — livello strutturale; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LDO</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>54.34000015258789</v>
+        <v>230.6499938964844</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.9659172400473537</v>
+        <v>2.012378447652763</v>
       </c>
       <c r="F99" t="n">
-        <v>-6.278025902702589</v>
+        <v>-1.658565490322472</v>
       </c>
       <c r="G99" t="n">
-        <v>-8.209460384659373</v>
+        <v>-1.963705653962688</v>
       </c>
       <c r="H99" t="n">
-        <v>-6.407166952659448</v>
+        <v>4.774232095927844</v>
       </c>
       <c r="I99" t="n">
-        <v>39.45246008795751</v>
+        <v>39.50218861531254</v>
       </c>
       <c r="J99" t="n">
-        <v>19.2964111757685</v>
+        <v>21.94832483422106</v>
       </c>
       <c r="K99" t="n">
-        <v>0.094814790298544</v>
+        <v>0.1830365576793783</v>
       </c>
       <c r="L99" t="n">
-        <v>57.56497321641366</v>
+        <v>235.551725476233</v>
       </c>
       <c r="M99" t="n">
-        <v>57.76129324325107</v>
+        <v>235.3816498815415</v>
       </c>
       <c r="N99" t="n">
-        <v>52.50326284586755</v>
+        <v>209.7595009673515</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.4391945908027174</v>
+        <v>-1.381654913750403</v>
       </c>
       <c r="P99" t="n">
-        <v>4.982621691258863</v>
+        <v>33.64346588255514</v>
       </c>
       <c r="Q99" t="n">
-        <v>-95.01737830874114</v>
+        <v>-66.35653411744487</v>
       </c>
       <c r="R99" t="n">
-        <v>-98.86139584850996</v>
+        <v>-140.626121860965</v>
       </c>
       <c r="S99" t="n">
-        <v>-6.278025902702589</v>
+        <v>-3.867794382771061</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9639,15 +9635,19 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr"/>
+          <t>Morning Star</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W99" t="n">
-        <v>44.3</v>
+        <v>44.8</v>
       </c>
       <c r="X99" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -9656,90 +9656,90 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>doji — indecisione del mercato; sul supporto dei 20g (53.91)</t>
+          <t>trend in sviluppo (ADX 22); pattern: Double Top; morning star — inversione rialzista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>LDO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>179.3000030517578</v>
+        <v>54.34000015258789</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.8899455960205471</v>
+        <v>-0.9659172400473537</v>
       </c>
       <c r="F100" t="n">
-        <v>-8.450345946382242</v>
+        <v>-6.278025902702589</v>
       </c>
       <c r="G100" t="n">
-        <v>-7.577318014557832</v>
+        <v>-8.209460384659373</v>
       </c>
       <c r="H100" t="n">
-        <v>-8.487720229511886</v>
+        <v>-6.407166952659448</v>
       </c>
       <c r="I100" t="n">
-        <v>27.64288435788757</v>
+        <v>39.45246008795751</v>
       </c>
       <c r="J100" t="n">
-        <v>21.06988903846733</v>
+        <v>19.2964111757685</v>
       </c>
       <c r="K100" t="n">
-        <v>-0.05566820986037459</v>
+        <v>0.094814790298544</v>
       </c>
       <c r="L100" t="n">
-        <v>194.226741049741</v>
+        <v>57.56497321641366</v>
       </c>
       <c r="M100" t="n">
-        <v>196.1814754143191</v>
+        <v>57.76129324325107</v>
       </c>
       <c r="N100" t="n">
-        <v>178.8841909119897</v>
+        <v>52.50326284586755</v>
       </c>
       <c r="O100" t="n">
-        <v>-1.995593554491845</v>
+        <v>-0.4391945908027174</v>
       </c>
       <c r="P100" t="n">
-        <v>6.460886619970172</v>
+        <v>4.982621691258863</v>
       </c>
       <c r="Q100" t="n">
-        <v>-93.53911338002983</v>
+        <v>-95.01737830874114</v>
       </c>
       <c r="R100" t="n">
-        <v>-176.5601222213973</v>
+        <v>-98.86139584850996</v>
       </c>
       <c r="S100" t="n">
-        <v>-8.051280486278046</v>
+        <v>-6.278025902702589</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Breakdown 20d, Breakdown 50d</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="n">
-        <v>43.1</v>
+        <v>44.3</v>
       </c>
       <c r="X100" t="n">
-        <v>68.2</v>
+        <v>59.4</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
@@ -9748,19 +9748,19 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); RSI ipervenduto (28) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (177.50)</t>
+          <t>doji — indecisione del mercato; sul supporto dei 20g (53.91)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9769,69 +9769,69 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>302.5299987792969</v>
+        <v>179.3000030517578</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8198058436477362</v>
+        <v>-0.8899455960205471</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.443182433900203</v>
+        <v>-8.450345946382242</v>
       </c>
       <c r="G101" t="n">
-        <v>-1.724921264865598</v>
+        <v>-7.577318014557832</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.172999586322755</v>
+        <v>-8.487720229511886</v>
       </c>
       <c r="I101" t="n">
-        <v>40.81446424836196</v>
+        <v>27.64288435788757</v>
       </c>
       <c r="J101" t="n">
-        <v>20.87217957537462</v>
+        <v>21.06988903846733</v>
       </c>
       <c r="K101" t="n">
-        <v>0.1728255629706962</v>
+        <v>-0.05566820986037459</v>
       </c>
       <c r="L101" t="n">
-        <v>307.4153209894906</v>
+        <v>194.226741049741</v>
       </c>
       <c r="M101" t="n">
-        <v>312.4247814923716</v>
+        <v>196.1814754143191</v>
       </c>
       <c r="N101" t="n">
-        <v>310.3781219386761</v>
+        <v>178.8841909119897</v>
       </c>
       <c r="O101" t="n">
-        <v>0.07638849832604055</v>
+        <v>-1.995593554491845</v>
       </c>
       <c r="P101" t="n">
-        <v>21.24317497514899</v>
+        <v>6.460886619970172</v>
       </c>
       <c r="Q101" t="n">
-        <v>-78.75682502485101</v>
+        <v>-93.53911338002983</v>
       </c>
       <c r="R101" t="n">
-        <v>-33.3039563944481</v>
+        <v>-176.5601222213973</v>
       </c>
       <c r="S101" t="n">
-        <v>-2.941935536930185</v>
+        <v>-8.051280486278046</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Breakdown 20d, Breakdown 50d</t>
+        </is>
+      </c>
       <c r="W101" t="n">
         <v>43.1</v>
       </c>
       <c r="X101" t="n">
-        <v>59.7</v>
+        <v>68.2</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
@@ -9840,19 +9840,19 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); doji — indecisione del mercato; sul supporto dei 20g (299.83)</t>
+          <t>trend in sviluppo (ADX 21); RSI ipervenduto (28) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (177.50)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9861,69 +9861,69 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>308.8800048828125</v>
+        <v>302.5299987792969</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.7741988486474671</v>
+        <v>0.8198058436477362</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.973976864557647</v>
+        <v>-1.443182433900203</v>
       </c>
       <c r="G102" t="n">
-        <v>1.685539555104043</v>
+        <v>-1.724921264865598</v>
       </c>
       <c r="H102" t="n">
-        <v>-5.303816353372937</v>
+        <v>-2.172999586322755</v>
       </c>
       <c r="I102" t="n">
-        <v>48.95993286983835</v>
+        <v>40.81446424836196</v>
       </c>
       <c r="J102" t="n">
-        <v>15.62706146248983</v>
+        <v>20.87217957537462</v>
       </c>
       <c r="K102" t="n">
-        <v>0.5714749142062491</v>
+        <v>0.1728255629706962</v>
       </c>
       <c r="L102" t="n">
-        <v>309.5130785116543</v>
+        <v>307.4153209894906</v>
       </c>
       <c r="M102" t="n">
-        <v>312.7618791710622</v>
+        <v>312.4247814923716</v>
       </c>
       <c r="N102" t="n">
-        <v>326.5906329961865</v>
+        <v>310.3781219386761</v>
       </c>
       <c r="O102" t="n">
-        <v>0.7808680927458985</v>
+        <v>0.07638849832604055</v>
       </c>
       <c r="P102" t="n">
-        <v>47.14718842837614</v>
+        <v>21.24317497514899</v>
       </c>
       <c r="Q102" t="n">
-        <v>-52.85281157162386</v>
+        <v>-78.75682502485101</v>
       </c>
       <c r="R102" t="n">
-        <v>18.3839268670761</v>
+        <v>-33.3039563944481</v>
       </c>
       <c r="S102" t="n">
-        <v>1.302023932642937</v>
+        <v>-2.941935536930185</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom, Outside Bar, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="X102" t="n">
-        <v>68.2</v>
+        <v>59.7</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -9932,94 +9932,90 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); doji — indecisione del mercato; sul supporto dei 20g (299.83)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INW</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INWIT</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7.320000171661377</v>
+        <v>308.8800048828125</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2739723343007316</v>
+        <v>-0.7741988486474671</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2053435136926574</v>
+        <v>-1.973976864557647</v>
       </c>
       <c r="G103" t="n">
-        <v>16.74641457621991</v>
+        <v>1.685539555104043</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.745760384252514</v>
+        <v>-5.303816353372937</v>
       </c>
       <c r="I103" t="n">
-        <v>48.11671242845422</v>
+        <v>48.95993286983835</v>
       </c>
       <c r="J103" t="n">
-        <v>44.60634783270435</v>
+        <v>15.62706146248983</v>
       </c>
       <c r="K103" t="n">
-        <v>0.6363630110577875</v>
+        <v>0.5714749142062491</v>
       </c>
       <c r="L103" t="n">
-        <v>7.327354718066685</v>
+        <v>309.5130785116543</v>
       </c>
       <c r="M103" t="n">
-        <v>7.568177391960353</v>
+        <v>312.7618791710622</v>
       </c>
       <c r="N103" t="n">
-        <v>8.495977468405496</v>
+        <v>326.5906329961865</v>
       </c>
       <c r="O103" t="n">
-        <v>0.04967103892824293</v>
+        <v>0.7808680927458985</v>
       </c>
       <c r="P103" t="n">
-        <v>58.0645459003392</v>
+        <v>47.14718842837614</v>
       </c>
       <c r="Q103" t="n">
-        <v>-41.9354540996608</v>
+        <v>-52.85281157162386</v>
       </c>
       <c r="R103" t="n">
-        <v>22.97394122710711</v>
+        <v>18.3839268670761</v>
       </c>
       <c r="S103" t="n">
-        <v>6.240933432631723</v>
+        <v>1.302023932642937</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Double Top, Double Bottom, Outside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W103" t="n">
-        <v>40.7</v>
+        <v>42.1</v>
       </c>
       <c r="X103" t="n">
-        <v>73.8</v>
+        <v>68.2</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -10028,186 +10024,186 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 45); morning star — inversione rialzista a 3 candele; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>INW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>US Treasury 1-3Y ETF</t>
+          <t>INWIT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>82.48000335693359</v>
+        <v>7.320000171661377</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.0484649633540335</v>
+        <v>0.2739723343007316</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>0.2053435136926574</v>
       </c>
       <c r="G104" t="n">
-        <v>0.206543315979113</v>
+        <v>16.74641457621991</v>
       </c>
       <c r="H104" t="n">
-        <v>-0.4345642164066299</v>
+        <v>-0.745760384252514</v>
       </c>
       <c r="I104" t="n">
-        <v>48.26342516328437</v>
+        <v>48.11671242845422</v>
       </c>
       <c r="J104" t="n">
-        <v>17.17347188972481</v>
+        <v>44.60634783270435</v>
       </c>
       <c r="K104" t="n">
-        <v>0.5746040174060476</v>
+        <v>0.6363630110577875</v>
       </c>
       <c r="L104" t="n">
-        <v>82.49721848542269</v>
+        <v>7.327354718066685</v>
       </c>
       <c r="M104" t="n">
-        <v>82.585823161402</v>
+        <v>7.568177391960353</v>
       </c>
       <c r="N104" t="n">
-        <v>82.68602732838687</v>
+        <v>8.495977468405496</v>
       </c>
       <c r="O104" t="n">
-        <v>0.02209075636245684</v>
+        <v>0.04967103892824293</v>
       </c>
       <c r="P104" t="n">
-        <v>56.09787867510234</v>
+        <v>58.0645459003392</v>
       </c>
       <c r="Q104" t="n">
-        <v>-43.90212132489766</v>
+        <v>-41.9354540996608</v>
       </c>
       <c r="R104" t="n">
-        <v>22.37407971358872</v>
+        <v>22.97394122710711</v>
       </c>
       <c r="S104" t="n">
-        <v>0.09708959899661362</v>
+        <v>6.240933432631723</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Volatility Squeeze</t>
+          <t>Outside Bar</t>
         </is>
       </c>
       <c r="W104" t="n">
-        <v>40</v>
+        <v>40.7</v>
       </c>
       <c r="X104" t="n">
-        <v>67.2</v>
+        <v>73.8</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; sul supporto dei 20g (82.22); vicino alla resistenza dei 20g (82.66); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 45); morning star — inversione rialzista a 3 candele; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>US Treasury 1-3Y ETF</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>373.7200012207031</v>
+        <v>82.48000335693359</v>
       </c>
       <c r="E105" t="n">
-        <v>-3.558619957523779</v>
+        <v>-0.0484649633540335</v>
       </c>
       <c r="F105" t="n">
-        <v>-3.903315226027437</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>-2.430618381919014</v>
+        <v>0.206543315979113</v>
       </c>
       <c r="H105" t="n">
-        <v>-16.77726734678927</v>
+        <v>-0.4345642164066299</v>
       </c>
       <c r="I105" t="n">
-        <v>47.73190737000726</v>
+        <v>48.26342516328437</v>
       </c>
       <c r="J105" t="n">
-        <v>26.17587599041789</v>
+        <v>17.17347188972481</v>
       </c>
       <c r="K105" t="n">
-        <v>0.5659772861386169</v>
+        <v>0.5746040174060476</v>
       </c>
       <c r="L105" t="n">
-        <v>377.1781098891953</v>
+        <v>82.49721848542269</v>
       </c>
       <c r="M105" t="n">
-        <v>387.7482162577223</v>
+        <v>82.585823161402</v>
       </c>
       <c r="N105" t="n">
-        <v>390.4194970942265</v>
+        <v>82.68602732838687</v>
       </c>
       <c r="O105" t="n">
-        <v>3.900508826547031</v>
+        <v>0.02209075636245684</v>
       </c>
       <c r="P105" t="n">
-        <v>50.63854339159377</v>
+        <v>56.09787867510234</v>
       </c>
       <c r="Q105" t="n">
-        <v>-49.36145660840623</v>
+        <v>-43.90212132489766</v>
       </c>
       <c r="R105" t="n">
-        <v>20.10099100759111</v>
+        <v>22.37407971358872</v>
       </c>
       <c r="S105" t="n">
-        <v>-3.168806995598095</v>
+        <v>0.09708959899661362</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>Double Top, Bull Flag / Consolidation</t>
+          <t>Double Top, Double Bottom, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W105" t="n">
-        <v>38.4</v>
+        <v>40</v>
       </c>
       <c r="X105" t="n">
-        <v>64.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -10216,73 +10212,73 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 26); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; sul supporto dei 20g (82.22); vicino alla resistenza dei 20g (82.66); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>9.310000419616699</v>
+        <v>373.7200012207031</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.4111381279045423</v>
+        <v>-3.558619957523779</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.3406627027833786</v>
+        <v>-3.903315226027437</v>
       </c>
       <c r="G106" t="n">
-        <v>6.375784845129662</v>
+        <v>-2.430618381919014</v>
       </c>
       <c r="H106" t="n">
-        <v>1.543839853061546</v>
+        <v>-16.77726734678927</v>
       </c>
       <c r="I106" t="n">
-        <v>50.04988026413901</v>
+        <v>47.73190737000726</v>
       </c>
       <c r="J106" t="n">
-        <v>11.57160422805518</v>
+        <v>26.17587599041789</v>
       </c>
       <c r="K106" t="n">
-        <v>0.5001353499908346</v>
+        <v>0.5659772861386169</v>
       </c>
       <c r="L106" t="n">
-        <v>9.314278292638752</v>
+        <v>377.1781098891953</v>
       </c>
       <c r="M106" t="n">
-        <v>9.422639446245496</v>
+        <v>387.7482162577223</v>
       </c>
       <c r="N106" t="n">
-        <v>13.03797970350764</v>
+        <v>390.4194970942265</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.002265912736433531</v>
+        <v>3.900508826547031</v>
       </c>
       <c r="P106" t="n">
-        <v>34.17160337155239</v>
+        <v>50.63854339159377</v>
       </c>
       <c r="Q106" t="n">
-        <v>-65.82839662844761</v>
+        <v>-49.36145660840623</v>
       </c>
       <c r="R106" t="n">
-        <v>-0.2488754698333332</v>
+        <v>20.10099100759111</v>
       </c>
       <c r="S106" t="n">
-        <v>4.466735310654002</v>
+        <v>-3.168806995598095</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10291,15 +10287,19 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Double Top, Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W106" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="X106" t="n">
-        <v>76.5</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 12); evening star — inversione ribassista a 3 candele; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 26); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -10781,52 +10781,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.2483000010251999</v>
+        <v>0.2486999928951263</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.1046006856236792</v>
+        <v>0.05632298495155119</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.4841497932597361</v>
+        <v>-0.3238375465937526</v>
       </c>
       <c r="G112" t="n">
-        <v>3.73583012882428</v>
+        <v>3.902940432893076</v>
       </c>
       <c r="H112" t="n">
-        <v>-12.84875782605517</v>
+        <v>-12.7083639952874</v>
       </c>
       <c r="I112" t="n">
-        <v>48.18191375044643</v>
+        <v>48.41913427871974</v>
       </c>
       <c r="J112" t="n">
         <v>12.32075114472588</v>
       </c>
       <c r="K112" t="n">
-        <v>0.4492248482387216</v>
+        <v>0.4640095905513412</v>
       </c>
       <c r="L112" t="n">
-        <v>0.2497987895283943</v>
+        <v>0.2498368839921969</v>
       </c>
       <c r="M112" t="n">
-        <v>0.2593392360756277</v>
+        <v>0.2593549220313111</v>
       </c>
       <c r="N112" t="n">
-        <v>0.3851530281591867</v>
+        <v>0.3851570081777929</v>
       </c>
       <c r="O112" t="n">
-        <v>0.0005905926343626683</v>
+        <v>0.0006161191810473972</v>
       </c>
       <c r="P112" t="n">
-        <v>39.6230673792034</v>
+        <v>40.88794415938682</v>
       </c>
       <c r="Q112" t="n">
-        <v>-60.3769326207966</v>
+        <v>-59.11205584061318</v>
       </c>
       <c r="R112" t="n">
-        <v>-24.49076662004261</v>
+        <v>-22.63480916647228</v>
       </c>
       <c r="S112" t="n">
-        <v>0.8660745984199192</v>
+        <v>1.028561950913609</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Doji, Evening Star</t>
+          <t>Doji, Bullish Harami</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -10844,10 +10844,10 @@
         </is>
       </c>
       <c r="W112" t="n">
-        <v>33.4</v>
+        <v>34.2</v>
       </c>
       <c r="X112" t="n">
-        <v>74.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -10965,52 +10965,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.230000019073486</v>
+        <v>1.235000014305115</v>
       </c>
       <c r="E114" t="n">
-        <v>-3.248257402318655</v>
+        <v>-2.854958016840148</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.447014826767758</v>
+        <v>-3.054523397516162</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.5141682143651183</v>
+        <v>-0.109754655967409</v>
       </c>
       <c r="H114" t="n">
-        <v>-8.301472546043954</v>
+        <v>-7.928714665631476</v>
       </c>
       <c r="I114" t="n">
-        <v>43.5587514385575</v>
+        <v>44.01954532160602</v>
       </c>
       <c r="J114" t="n">
         <v>19.33722230750936</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3182559602199019</v>
+        <v>0.3438322437868248</v>
       </c>
       <c r="L114" t="n">
-        <v>1.273451647000312</v>
+        <v>1.273927837022372</v>
       </c>
       <c r="M114" t="n">
-        <v>1.345682272945614</v>
+        <v>1.345878351189991</v>
       </c>
       <c r="N114" t="n">
-        <v>2.031442211470432</v>
+        <v>2.031491962666767</v>
       </c>
       <c r="O114" t="n">
-        <v>0.006576834550873645</v>
+        <v>0.006895922565655421</v>
       </c>
       <c r="P114" t="n">
-        <v>39.65237575697144</v>
+        <v>42.08390194357455</v>
       </c>
       <c r="Q114" t="n">
-        <v>-60.34762424302856</v>
+        <v>-57.91609805642546</v>
       </c>
       <c r="R114" t="n">
-        <v>-31.79832883357597</v>
+        <v>-29.53099523011899</v>
       </c>
       <c r="S114" t="n">
-        <v>-0.5963359716729122</v>
+        <v>-0.1922564282250905</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11020,10 +11020,10 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="n">
-        <v>32.1</v>
+        <v>32.3</v>
       </c>
       <c r="X114" t="n">
-        <v>73.7</v>
+        <v>73.5</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -11145,52 +11145,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.734999895095825</v>
+        <v>2.733999967575073</v>
       </c>
       <c r="E116" t="n">
-        <v>0.4775904481910453</v>
+        <v>0.440855416468322</v>
       </c>
       <c r="F116" t="n">
-        <v>3.32451145584578</v>
+        <v>3.286735577770528</v>
       </c>
       <c r="G116" t="n">
-        <v>-7.067624110720194</v>
+        <v>-7.101600580111356</v>
       </c>
       <c r="H116" t="n">
-        <v>-48.1516616938503</v>
+        <v>-48.17061766546497</v>
       </c>
       <c r="I116" t="n">
-        <v>44.00617385824521</v>
+        <v>43.93364990113606</v>
       </c>
       <c r="J116" t="n">
         <v>29.08539706069566</v>
       </c>
       <c r="K116" t="n">
-        <v>0.4526188859419134</v>
+        <v>0.4508471323165879</v>
       </c>
       <c r="L116" t="n">
-        <v>2.766172723519229</v>
+        <v>2.766077492326777</v>
       </c>
       <c r="M116" t="n">
-        <v>3.015011208281834</v>
+        <v>3.014971995437883</v>
       </c>
       <c r="N116" t="n">
-        <v>3.408362893671473</v>
+        <v>3.408352944143903</v>
       </c>
       <c r="O116" t="n">
-        <v>0.02038028958849897</v>
+        <v>0.0203164765501376</v>
       </c>
       <c r="P116" t="n">
-        <v>53.21095967516735</v>
+        <v>52.90517135155668</v>
       </c>
       <c r="Q116" t="n">
-        <v>-46.78904032483265</v>
+        <v>-47.09482864844332</v>
       </c>
       <c r="R116" t="n">
-        <v>3.042341702172461</v>
+        <v>2.917776303930737</v>
       </c>
       <c r="S116" t="n">
-        <v>-7.350949010163077</v>
+        <v>-7.384821894773575</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11479,52 +11479,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.70999908447266</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E2" t="n">
-        <v>15.33691215787032</v>
+        <v>15.1818766709489</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.637510796733976</v>
+        <v>-1.769729321776159</v>
       </c>
       <c r="G2" t="n">
-        <v>65.17506463647888</v>
+        <v>64.9530368736917</v>
       </c>
       <c r="H2" t="n">
-        <v>36.71190557669499</v>
+        <v>36.52813789597169</v>
       </c>
       <c r="I2" t="n">
-        <v>62.67917002467193</v>
+        <v>62.61906557397396</v>
       </c>
       <c r="J2" t="n">
         <v>58.66713718370163</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7808399710965243</v>
+        <v>0.7793214075796742</v>
       </c>
       <c r="L2" t="n">
-        <v>81.18182258686821</v>
+        <v>81.16944189606649</v>
       </c>
       <c r="M2" t="n">
-        <v>72.76889101837904</v>
+        <v>72.76379308687245</v>
       </c>
       <c r="N2" t="n">
-        <v>71.92808008071189</v>
+        <v>71.92678657570275</v>
       </c>
       <c r="O2" t="n">
-        <v>2.378448136307071</v>
+        <v>2.370152015291222</v>
       </c>
       <c r="P2" t="n">
-        <v>62.53701332564452</v>
+        <v>62.32313170690499</v>
       </c>
       <c r="Q2" t="n">
-        <v>-37.46298667435548</v>
+        <v>-37.67686829309501</v>
       </c>
       <c r="R2" t="n">
-        <v>97.69142073235309</v>
+        <v>97.49616069605565</v>
       </c>
       <c r="S2" t="n">
-        <v>60.96870195913397</v>
+        <v>60.75232837481965</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -11575,52 +11575,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>106.0599975585938</v>
+        <v>105.9499969482422</v>
       </c>
       <c r="E3" t="n">
-        <v>17.34897187616678</v>
+        <v>17.22726285459739</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.463949326513329</v>
+        <v>-5.561997822776632</v>
       </c>
       <c r="G3" t="n">
-        <v>67.81644980736685</v>
+        <v>67.64239821081044</v>
       </c>
       <c r="H3" t="n">
-        <v>41.90527239766848</v>
+        <v>41.7580946969786</v>
       </c>
       <c r="I3" t="n">
-        <v>66.92510803836461</v>
+        <v>66.87637536738788</v>
       </c>
       <c r="J3" t="n">
         <v>60.96010584971138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8255860717932053</v>
+        <v>0.8243832754371067</v>
       </c>
       <c r="L3" t="n">
-        <v>86.29170793777584</v>
+        <v>86.28123168917092</v>
       </c>
       <c r="M3" t="n">
-        <v>77.20347209682322</v>
+        <v>77.19915834739766</v>
       </c>
       <c r="N3" t="n">
-        <v>76.06154695216154</v>
+        <v>76.06045241872519</v>
       </c>
       <c r="O3" t="n">
-        <v>2.461758127164718</v>
+        <v>2.454738145193563</v>
       </c>
       <c r="P3" t="n">
-        <v>76.23797077686571</v>
+        <v>76.04203097623696</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.7620292231343</v>
+        <v>-23.95796902376303</v>
       </c>
       <c r="R3" t="n">
-        <v>109.7387281865493</v>
+        <v>109.5817564546903</v>
       </c>
       <c r="S3" t="n">
-        <v>66.36862362132352</v>
+        <v>66.19607364430146</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -13343,52 +13343,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.01800012588501</v>
+        <v>6.013999938964844</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.400831736519326</v>
+        <v>-1.466370967987651</v>
       </c>
       <c r="F22" t="n">
-        <v>12.6438912409681</v>
+        <v>12.56901643024142</v>
       </c>
       <c r="G22" t="n">
-        <v>16.05438159587935</v>
+        <v>15.97723981961201</v>
       </c>
       <c r="H22" t="n">
-        <v>29.23870510828652</v>
+        <v>29.15279966346447</v>
       </c>
       <c r="I22" t="n">
-        <v>61.08871866526456</v>
+        <v>60.97566942831919</v>
       </c>
       <c r="J22" t="n">
         <v>48.57643889583426</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8022045847174878</v>
+        <v>0.7983255124047095</v>
       </c>
       <c r="L22" t="n">
-        <v>5.668024367467906</v>
+        <v>5.667643397285032</v>
       </c>
       <c r="M22" t="n">
-        <v>5.312570787877227</v>
+        <v>5.312413917801926</v>
       </c>
       <c r="N22" t="n">
-        <v>4.525446576881701</v>
+        <v>4.525406774026774</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.005266870820254899</v>
+        <v>-0.005522153404334346</v>
       </c>
       <c r="P22" t="n">
-        <v>60.48388213198548</v>
+        <v>60.16128635307183</v>
       </c>
       <c r="Q22" t="n">
-        <v>-39.51611786801453</v>
+        <v>-39.83871364692817</v>
       </c>
       <c r="R22" t="n">
-        <v>46.0907518753779</v>
+        <v>45.90320740113416</v>
       </c>
       <c r="S22" t="n">
-        <v>11.81717131194542</v>
+        <v>11.7428460250103</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -13406,10 +13406,10 @@
         </is>
       </c>
       <c r="W22" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -14371,52 +14371,52 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4707.7998046875</v>
+        <v>4705.39990234375</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.083833373624711</v>
+        <v>-3.133238476875344</v>
       </c>
       <c r="F33" t="n">
-        <v>3.00629934534371</v>
+        <v>2.953789665774553</v>
       </c>
       <c r="G33" t="n">
-        <v>11.60420128166455</v>
+        <v>11.54730863640774</v>
       </c>
       <c r="H33" t="n">
-        <v>63.26118897394733</v>
+        <v>63.17796306666217</v>
       </c>
       <c r="I33" t="n">
-        <v>54.65991825216081</v>
+        <v>54.59289472123281</v>
       </c>
       <c r="J33" t="n">
         <v>44.58204990747586</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4728127551916955</v>
+        <v>0.4708166594523198</v>
       </c>
       <c r="L33" t="n">
-        <v>4654.22246181327</v>
+        <v>4653.993899685292</v>
       </c>
       <c r="M33" t="n">
-        <v>4170.108574965235</v>
+        <v>4170.014461147833</v>
       </c>
       <c r="N33" t="n">
-        <v>2980.304398391343</v>
+        <v>2980.280518766032</v>
       </c>
       <c r="O33" t="n">
-        <v>-63.83830200858552</v>
+        <v>-63.99145816955479</v>
       </c>
       <c r="P33" t="n">
-        <v>40.86440287958975</v>
+        <v>40.70283685611913</v>
       </c>
       <c r="Q33" t="n">
-        <v>-59.13559712041025</v>
+        <v>-59.29716314388087</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.21602128494787</v>
+        <v>-0.3348037936943221</v>
       </c>
       <c r="S33" t="n">
-        <v>11.74725044068632</v>
+        <v>11.6902848730398</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -14747,52 +14747,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>75.38500213623047</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.772390940343565</v>
+        <v>-7.778514020032368</v>
       </c>
       <c r="F37" t="n">
-        <v>8.686564983939338</v>
+        <v>8.67934917833313</v>
       </c>
       <c r="G37" t="n">
-        <v>33.55242758995416</v>
+        <v>33.5435609158085</v>
       </c>
       <c r="H37" t="n">
-        <v>129.8253259111819</v>
+        <v>129.8100675867018</v>
       </c>
       <c r="I37" t="n">
-        <v>53.58236936841062</v>
+        <v>53.57872393323125</v>
       </c>
       <c r="J37" t="n">
         <v>55.22104530237728</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4267971270097556</v>
+        <v>0.4266666749979549</v>
       </c>
       <c r="L37" t="n">
-        <v>73.75160043505718</v>
+        <v>73.75112377955124</v>
       </c>
       <c r="M37" t="n">
-        <v>61.11608456116711</v>
+        <v>61.11588829125289</v>
       </c>
       <c r="N37" t="n">
-        <v>39.02589425579421</v>
+        <v>39.02584445596523</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.883937030390622</v>
+        <v>-1.884256430319398</v>
       </c>
       <c r="P37" t="n">
-        <v>23.74190548966018</v>
+        <v>23.73359311202937</v>
       </c>
       <c r="Q37" t="n">
-        <v>-76.25809451033982</v>
+        <v>-76.26640688797063</v>
       </c>
       <c r="R37" t="n">
-        <v>-8.326563312321927</v>
+        <v>-8.333236036402434</v>
       </c>
       <c r="S37" t="n">
-        <v>29.03529662499655</v>
+        <v>29.02672984752115</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>80.95135377215732</v>
       </c>
       <c r="J45" t="n">
-        <v>24.30623998972093</v>
+        <v>24.67093203662111</v>
       </c>
       <c r="K45" t="n">
         <v>1.140966420531304</v>
@@ -15529,7 +15529,7 @@
         <v>2.285124380319148</v>
       </c>
       <c r="R45" t="n">
-        <v>205.2800019976372</v>
+        <v>214.7842957419916</v>
       </c>
       <c r="S45" t="n">
         <v>27.97360497235619</v>
@@ -15562,7 +15562,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 24); RSI ipercomprato (81) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 25); RSI ipercomprato (81) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -16051,52 +16051,52 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>159.7149963378906</v>
+        <v>159.7010040283203</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3266365085262013</v>
+        <v>0.3178470937037936</v>
       </c>
       <c r="F51" t="n">
-        <v>1.134090076173178</v>
+        <v>1.125229921967841</v>
       </c>
       <c r="G51" t="n">
-        <v>2.195362180962968</v>
+        <v>2.186409050843241</v>
       </c>
       <c r="H51" t="n">
-        <v>4.396393201192028</v>
+        <v>4.387247243171877</v>
       </c>
       <c r="I51" t="n">
-        <v>59.784326543186</v>
+        <v>59.7555905300759</v>
       </c>
       <c r="J51" t="n">
         <v>13.25914642780409</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8045566283363256</v>
+        <v>0.8030894705474647</v>
       </c>
       <c r="L51" t="n">
-        <v>157.0495311116209</v>
+        <v>157.0481985107095</v>
       </c>
       <c r="M51" t="n">
-        <v>154.0790115365088</v>
+        <v>154.0784628184865</v>
       </c>
       <c r="N51" t="n">
-        <v>144.835268437029</v>
+        <v>144.8351292100681</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05249483776898334</v>
+        <v>0.05160188126077347</v>
       </c>
       <c r="P51" t="n">
-        <v>93.51180334914277</v>
+        <v>93.3358659114979</v>
       </c>
       <c r="Q51" t="n">
-        <v>-6.48819665085724</v>
+        <v>-6.664134088502095</v>
       </c>
       <c r="R51" t="n">
-        <v>53.54258942272985</v>
+        <v>53.44014287650015</v>
       </c>
       <c r="S51" t="n">
-        <v>2.947620951933949</v>
+        <v>2.938601917936423</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -16243,52 +16243,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2015.5</v>
+        <v>2016.099975585938</v>
       </c>
       <c r="E53" t="n">
-        <v>-5.130618969169221</v>
+        <v>-5.102378179056832</v>
       </c>
       <c r="F53" t="n">
-        <v>2.278495126881941</v>
+        <v>2.308941467761416</v>
       </c>
       <c r="G53" t="n">
-        <v>20.13471172793271</v>
+        <v>20.17047352106614</v>
       </c>
       <c r="H53" t="n">
-        <v>99.59398141854821</v>
+        <v>99.6533967080303</v>
       </c>
       <c r="I53" t="n">
-        <v>51.90206403826052</v>
+        <v>51.91982895110198</v>
       </c>
       <c r="J53" t="n">
         <v>33.03065630583864</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3645319278655966</v>
+        <v>0.3651829960451154</v>
       </c>
       <c r="L53" t="n">
-        <v>2013.273618803018</v>
+        <v>2013.330759335012</v>
       </c>
       <c r="M53" t="n">
-        <v>1755.081562684274</v>
+        <v>1755.105091138624</v>
       </c>
       <c r="N53" t="n">
-        <v>1271.739879154689</v>
+        <v>1271.745849061017</v>
       </c>
       <c r="O53" t="n">
-        <v>-45.50277957447435</v>
+        <v>-45.46449053423203</v>
       </c>
       <c r="P53" t="n">
-        <v>18.73968524133157</v>
+        <v>18.79794095963702</v>
       </c>
       <c r="Q53" t="n">
-        <v>-81.26031475866843</v>
+        <v>-81.20205904036297</v>
       </c>
       <c r="R53" t="n">
-        <v>-19.51402611893307</v>
+        <v>-19.47398560321286</v>
       </c>
       <c r="S53" t="n">
-        <v>21.78247734138974</v>
+        <v>21.81872964265483</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -17179,52 +17179,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.346549272537231</v>
+        <v>1.346545696258545</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4482601562274202</v>
+        <v>-0.4485245541018035</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2963783136563203</v>
+        <v>0.2961119381085231</v>
       </c>
       <c r="G63" t="n">
-        <v>1.694089121560438</v>
+        <v>1.69381903385486</v>
       </c>
       <c r="H63" t="n">
-        <v>7.179934456667647</v>
+        <v>7.179649799193122</v>
       </c>
       <c r="I63" t="n">
-        <v>51.95418442082336</v>
+        <v>51.95293536506068</v>
       </c>
       <c r="J63" t="n">
         <v>20.56534698593375</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5218361000680223</v>
+        <v>0.5217646219276939</v>
       </c>
       <c r="L63" t="n">
-        <v>1.3423036326153</v>
+        <v>1.34230329201733</v>
       </c>
       <c r="M63" t="n">
-        <v>1.334202667393638</v>
+        <v>1.334202527147415</v>
       </c>
       <c r="N63" t="n">
-        <v>1.302902309923197</v>
+        <v>1.302902274338335</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.0005799779045127778</v>
+        <v>-0.0005802061342636096</v>
       </c>
       <c r="P63" t="n">
-        <v>44.38638801900851</v>
+        <v>44.38117163469313</v>
       </c>
       <c r="Q63" t="n">
-        <v>-55.61361198099149</v>
+        <v>-55.61882836530687</v>
       </c>
       <c r="R63" t="n">
-        <v>18.6922083117287</v>
+        <v>18.68529636084946</v>
       </c>
       <c r="S63" t="n">
-        <v>1.078717143770902</v>
+        <v>1.078448690421929</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -19323,52 +19323,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>98.81300354003906</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7268145535252568</v>
+        <v>0.7339462098901794</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.8399377551664977</v>
+        <v>-0.8329170279431808</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.6505082951831609</v>
+        <v>-0.6434741559819268</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.278780310592314</v>
+        <v>-7.272215466072107</v>
       </c>
       <c r="I86" t="n">
-        <v>49.8764783564711</v>
+        <v>49.91194831290031</v>
       </c>
       <c r="J86" t="n">
         <v>18.97345570552778</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5622874883129366</v>
+        <v>0.5639221123514799</v>
       </c>
       <c r="L86" t="n">
-        <v>98.79074324719255</v>
+        <v>98.79140954764827</v>
       </c>
       <c r="M86" t="n">
-        <v>99.39020879353023</v>
+        <v>99.39048315254142</v>
       </c>
       <c r="N86" t="n">
-        <v>100.9677698348068</v>
+        <v>100.9678394482873</v>
       </c>
       <c r="O86" t="n">
-        <v>0.07504621953511736</v>
+        <v>0.07549269778921093</v>
       </c>
       <c r="P86" t="n">
-        <v>64.10614608877084</v>
+        <v>64.24359520112237</v>
       </c>
       <c r="Q86" t="n">
-        <v>-35.89385391122916</v>
+        <v>-35.75640479887763</v>
       </c>
       <c r="R86" t="n">
-        <v>7.149287929424712</v>
+        <v>7.349173803316109</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.1788002096676955</v>
+        <v>-0.1717326726072499</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -20069,66 +20069,66 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BRK</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>470.5499877929688</v>
+        <v>77984</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.849171666172488</v>
+        <v>5.588752152219478</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.160355677567771</v>
+        <v>14.9440010907181</v>
       </c>
       <c r="G94" t="n">
-        <v>-8.419456602864505</v>
+        <v>-13.72908555502317</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.884945185252118</v>
+        <v>-18.91450516165026</v>
       </c>
       <c r="I94" t="n">
-        <v>40.92931508789494</v>
+        <v>46.62357884333346</v>
       </c>
       <c r="J94" t="n">
-        <v>23.25404823888321</v>
+        <v>53.35674088539724</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1023017801845535</v>
+        <v>0.5236082038757068</v>
       </c>
       <c r="L94" t="n">
-        <v>486.5504695275415</v>
+        <v>77846.54053635502</v>
       </c>
       <c r="M94" t="n">
-        <v>486.9210142016596</v>
+        <v>86258.88351617246</v>
       </c>
       <c r="N94" t="n">
-        <v>419.8693474616322</v>
+        <v>68560.76792809997</v>
       </c>
       <c r="O94" t="n">
-        <v>-2.733220831329563</v>
+        <v>1154.2846467864</v>
       </c>
       <c r="P94" t="n">
-        <v>13.59097816077666</v>
+        <v>53.3241934103233</v>
       </c>
       <c r="Q94" t="n">
-        <v>-86.40902183922334</v>
+        <v>-46.6758065896767</v>
       </c>
       <c r="R94" t="n">
-        <v>-148.0222835032215</v>
+        <v>-2.0967491168449</v>
       </c>
       <c r="S94" t="n">
-        <v>-6.699847085354637</v>
+        <v>-13.7398955851932</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -20138,14 +20138,14 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Inside Bar</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W94" t="n">
         <v>42.8</v>
       </c>
       <c r="X94" t="n">
-        <v>59.8</v>
+        <v>69.5</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -20154,73 +20154,73 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); pattern: Double Bottom; sul supporto dei 20g (464.01); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 53); pattern: Bear Flag / Consolidation; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>BRK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>77911.09375</v>
+        <v>470.5499877929688</v>
       </c>
       <c r="E95" t="n">
-        <v>5.490038570438616</v>
+        <v>-0.849171666172488</v>
       </c>
       <c r="F95" t="n">
-        <v>14.83654140566066</v>
+        <v>-2.160355677567771</v>
       </c>
       <c r="G95" t="n">
-        <v>-13.8097391359661</v>
+        <v>-8.419456602864505</v>
       </c>
       <c r="H95" t="n">
-        <v>-18.9903109597378</v>
+        <v>-1.884945185252118</v>
       </c>
       <c r="I95" t="n">
-        <v>46.54668387363936</v>
+        <v>40.92931508789494</v>
       </c>
       <c r="J95" t="n">
-        <v>53.35674088539724</v>
+        <v>23.25404823888321</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5218913290355296</v>
+        <v>0.1023017801845535</v>
       </c>
       <c r="L95" t="n">
-        <v>77839.59708397408</v>
+        <v>486.5504695275415</v>
       </c>
       <c r="M95" t="n">
-        <v>86256.024447545</v>
+        <v>486.9210142016596</v>
       </c>
       <c r="N95" t="n">
-        <v>68560.0424927766</v>
+        <v>419.8693474616322</v>
       </c>
       <c r="O95" t="n">
-        <v>1149.631940233685</v>
+        <v>-2.733220831329563</v>
       </c>
       <c r="P95" t="n">
-        <v>53.10712411562638</v>
+        <v>13.59097816077666</v>
       </c>
       <c r="Q95" t="n">
-        <v>-46.89287588437362</v>
+        <v>-86.40902183922334</v>
       </c>
       <c r="R95" t="n">
-        <v>-2.199633874902784</v>
+        <v>-148.0222835032215</v>
       </c>
       <c r="S95" t="n">
-        <v>-13.82053905997638</v>
+        <v>-6.699847085354637</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -20230,14 +20230,14 @@
       <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W95" t="n">
-        <v>42.7</v>
+        <v>42.8</v>
       </c>
       <c r="X95" t="n">
-        <v>69.5</v>
+        <v>59.8</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 53); pattern: Bear Flag / Consolidation; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 23); pattern: Double Bottom; sul supporto dei 20g (464.01); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -20827,52 +20827,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2323.330078125</v>
+        <v>2326.219970703125</v>
       </c>
       <c r="E102" t="n">
-        <v>2.579038708217007</v>
+        <v>2.706632460574965</v>
       </c>
       <c r="F102" t="n">
-        <v>13.16489889866988</v>
+        <v>13.30565995733764</v>
       </c>
       <c r="G102" t="n">
-        <v>-22.35151451655978</v>
+        <v>-22.25493083092078</v>
       </c>
       <c r="H102" t="n">
-        <v>-12.76550924920126</v>
+        <v>-12.65700193474307</v>
       </c>
       <c r="I102" t="n">
-        <v>43.66372952162997</v>
+        <v>43.73988527897399</v>
       </c>
       <c r="J102" t="n">
         <v>39.58791687396969</v>
       </c>
       <c r="K102" t="n">
-        <v>0.444628688971607</v>
+        <v>0.4460328214542326</v>
       </c>
       <c r="L102" t="n">
-        <v>2443.346519179529</v>
+        <v>2443.621747044112</v>
       </c>
       <c r="M102" t="n">
-        <v>2780.764717215747</v>
+        <v>2780.878046336457</v>
       </c>
       <c r="N102" t="n">
-        <v>2567.436228137884</v>
+        <v>2567.464983287915</v>
       </c>
       <c r="O102" t="n">
-        <v>31.72268098232922</v>
+        <v>31.90710717534927</v>
       </c>
       <c r="P102" t="n">
-        <v>37.46364016153739</v>
+        <v>37.65202618019774</v>
       </c>
       <c r="Q102" t="n">
-        <v>-62.53635983846261</v>
+        <v>-62.34797381980226</v>
       </c>
       <c r="R102" t="n">
-        <v>-12.45861179979048</v>
+        <v>-12.37194609444037</v>
       </c>
       <c r="S102" t="n">
-        <v>-24.10646640123543</v>
+        <v>-24.01206562644249</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -21015,52 +21015,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.434100031852722</v>
+        <v>1.435400009155273</v>
       </c>
       <c r="E104" t="n">
-        <v>2.828450533827231</v>
+        <v>2.921662059370389</v>
       </c>
       <c r="F104" t="n">
-        <v>3.553873075371339</v>
+        <v>3.647742179059565</v>
       </c>
       <c r="G104" t="n">
-        <v>-33.6361935282217</v>
+        <v>-33.57603632843922</v>
       </c>
       <c r="H104" t="n">
-        <v>-47.42697678337486</v>
+        <v>-47.37932059803902</v>
       </c>
       <c r="I104" t="n">
-        <v>37.74899937920223</v>
+        <v>37.81141542673841</v>
       </c>
       <c r="J104" t="n">
         <v>43.71256524006639</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3566572400133978</v>
+        <v>0.3577127208031831</v>
       </c>
       <c r="L104" t="n">
-        <v>1.615967087055542</v>
+        <v>1.61609089441769</v>
       </c>
       <c r="M104" t="n">
-        <v>1.890347190726482</v>
+        <v>1.890398170228543</v>
       </c>
       <c r="N104" t="n">
-        <v>1.41988454676092</v>
+        <v>1.419897481858458</v>
       </c>
       <c r="O104" t="n">
-        <v>0.014202725486543</v>
+        <v>0.01428568700100774</v>
       </c>
       <c r="P104" t="n">
-        <v>33.69833445217897</v>
+        <v>33.84404717110214</v>
       </c>
       <c r="Q104" t="n">
-        <v>-66.30166554782103</v>
+        <v>-66.15595282889785</v>
       </c>
       <c r="R104" t="n">
-        <v>-26.88190022907698</v>
+        <v>-26.82574834271536</v>
       </c>
       <c r="S104" t="n">
-        <v>-29.81863844657249</v>
+        <v>-29.75502072461781</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -21107,52 +21107,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>85.69999694824219</v>
+        <v>85.80000305175781</v>
       </c>
       <c r="E105" t="n">
-        <v>2.53532548519313</v>
+        <v>2.654977279121118</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.4973418850094502</v>
+        <v>-0.3812290089082127</v>
       </c>
       <c r="G105" t="n">
-        <v>-35.83639960408092</v>
+        <v>-35.76152501958118</v>
       </c>
       <c r="H105" t="n">
-        <v>-54.53253129188121</v>
+        <v>-54.47947382928919</v>
       </c>
       <c r="I105" t="n">
-        <v>35.01740161300347</v>
+        <v>35.08578039780929</v>
       </c>
       <c r="J105" t="n">
         <v>61.92755203820978</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3275049720156248</v>
+        <v>0.3285306669973538</v>
       </c>
       <c r="L105" t="n">
-        <v>102.8207468417937</v>
+        <v>102.8302712326047</v>
       </c>
       <c r="M105" t="n">
-        <v>130.4863071333156</v>
+        <v>130.4902289412966</v>
       </c>
       <c r="N105" t="n">
-        <v>117.4801725087594</v>
+        <v>117.4811675943665</v>
       </c>
       <c r="O105" t="n">
-        <v>1.094002689307541</v>
+        <v>1.100384845201418</v>
       </c>
       <c r="P105" t="n">
-        <v>24.5407612063953</v>
+        <v>24.68505801484667</v>
       </c>
       <c r="Q105" t="n">
-        <v>-75.45923879360471</v>
+        <v>-75.31494198515333</v>
       </c>
       <c r="R105" t="n">
-        <v>-26.90814901623196</v>
+        <v>-26.85735045976111</v>
       </c>
       <c r="S105" t="n">
-        <v>-35.12174819484702</v>
+        <v>-35.04603966045982</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -21199,52 +21199,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2.734999895095825</v>
+        <v>2.733999967575073</v>
       </c>
       <c r="E106" t="n">
-        <v>2.281221755222584</v>
+        <v>2.243827308271218</v>
       </c>
       <c r="F106" t="n">
-        <v>-11.63166818050266</v>
+        <v>-11.6639760160926</v>
       </c>
       <c r="G106" t="n">
-        <v>-43.60824847680021</v>
+        <v>-43.62886553948915</v>
       </c>
       <c r="H106" t="n">
-        <v>-26.57718214450253</v>
+        <v>-26.60402583702205</v>
       </c>
       <c r="I106" t="n">
-        <v>42.56578488929212</v>
+        <v>42.55224658085536</v>
       </c>
       <c r="J106" t="n">
         <v>43.25348725498805</v>
       </c>
       <c r="K106" t="n">
-        <v>0.26046365795588</v>
+        <v>0.2601368875560531</v>
       </c>
       <c r="L106" t="n">
-        <v>3.235813531222279</v>
+        <v>3.235718300029827</v>
       </c>
       <c r="M106" t="n">
-        <v>3.38779194328342</v>
+        <v>3.387752730439469</v>
       </c>
       <c r="N106" t="n">
-        <v>3.368107611220307</v>
+        <v>3.368097661692737</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.1034161222593963</v>
+        <v>-0.1034799352977576</v>
       </c>
       <c r="P106" t="n">
-        <v>3.304211646516614</v>
+        <v>3.285223277458601</v>
       </c>
       <c r="Q106" t="n">
-        <v>-96.69578835348338</v>
+        <v>-96.7147767225414</v>
       </c>
       <c r="R106" t="n">
-        <v>-61.64847131069026</v>
+        <v>-61.67444581267559</v>
       </c>
       <c r="S106" t="n">
-        <v>-48.28890381277691</v>
+        <v>-48.30780960809287</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -21483,52 +21483,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9.303000450134277</v>
+        <v>9.314999580383301</v>
       </c>
       <c r="E109" t="n">
-        <v>2.561163281203438</v>
+        <v>2.693447995505971</v>
       </c>
       <c r="F109" t="n">
-        <v>7.112952747510248</v>
+        <v>7.251108418711616</v>
       </c>
       <c r="G109" t="n">
-        <v>-28.3364577626089</v>
+        <v>-28.24402519937061</v>
       </c>
       <c r="H109" t="n">
-        <v>-50.26541858732602</v>
+        <v>-50.2012702812553</v>
       </c>
       <c r="I109" t="n">
-        <v>38.49711176537373</v>
+        <v>38.57186304487637</v>
       </c>
       <c r="J109" t="n">
         <v>47.34271749339238</v>
       </c>
       <c r="K109" t="n">
-        <v>0.380383486781987</v>
+        <v>0.3818054954106573</v>
       </c>
       <c r="L109" t="n">
-        <v>10.53692363900762</v>
+        <v>10.53806641331705</v>
       </c>
       <c r="M109" t="n">
-        <v>13.16004193015339</v>
+        <v>13.1605124842808</v>
       </c>
       <c r="N109" t="n">
-        <v>13.65449355709497</v>
+        <v>13.65461295142581</v>
       </c>
       <c r="O109" t="n">
-        <v>0.1991093041808538</v>
+        <v>0.1998750606411903</v>
       </c>
       <c r="P109" t="n">
-        <v>33.00073484689685</v>
+        <v>33.2003859731358</v>
       </c>
       <c r="Q109" t="n">
-        <v>-66.99926515310315</v>
+        <v>-66.79961402686421</v>
       </c>
       <c r="R109" t="n">
-        <v>-19.25993697985381</v>
+        <v>-19.19494561000423</v>
       </c>
       <c r="S109" t="n">
-        <v>-31.81076071147913</v>
+        <v>-31.7228093490998</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -21951,52 +21951,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>9.310000419616699</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="E114" t="n">
-        <v>3.327273423917276</v>
+        <v>3.660226213567785</v>
       </c>
       <c r="F114" t="n">
-        <v>3.232212978341242</v>
+        <v>3.564859453506797</v>
       </c>
       <c r="G114" t="n">
-        <v>-32.41173865747382</v>
+        <v>-32.19394814180525</v>
       </c>
       <c r="H114" t="n">
-        <v>-62.5159884796937</v>
+        <v>-62.39520327178665</v>
       </c>
       <c r="I114" t="n">
-        <v>36.46958618521637</v>
+        <v>36.62214930427147</v>
       </c>
       <c r="J114" t="n">
         <v>61.5386935822199</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3508934183627638</v>
+        <v>0.3545466615960448</v>
       </c>
       <c r="L114" t="n">
-        <v>11.133494744846</v>
+        <v>11.13635186227183</v>
       </c>
       <c r="M114" t="n">
-        <v>16.01068570164248</v>
+        <v>16.011862161759</v>
       </c>
       <c r="N114" t="n">
-        <v>22.95331476526543</v>
+        <v>22.95361327007111</v>
       </c>
       <c r="O114" t="n">
-        <v>0.3750430130260471</v>
+        <v>0.3769575258994227</v>
       </c>
       <c r="P114" t="n">
-        <v>30.39438597401035</v>
+        <v>30.96081961725529</v>
       </c>
       <c r="Q114" t="n">
-        <v>-69.60561402598965</v>
+        <v>-69.0391803827447</v>
       </c>
       <c r="R114" t="n">
-        <v>-17.03048802862964</v>
+        <v>-16.90539003683725</v>
       </c>
       <c r="S114" t="n">
-        <v>-30.81064979174609</v>
+        <v>-30.58770006702596</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 62); RSI scarico (36) — zona di interesse long; morning star — inversione rialzista a 3 candele; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 62); RSI scarico (37) — zona di interesse long; morning star — inversione rialzista a 3 candele; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -22047,52 +22047,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.2483000010251999</v>
+        <v>0.2486999928951263</v>
       </c>
       <c r="E115" t="n">
-        <v>2.381621221086161</v>
+        <v>2.546550000583703</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.9158212695542955</v>
+        <v>-0.756204411854422</v>
       </c>
       <c r="G115" t="n">
-        <v>-40.29599524464189</v>
+        <v>-40.19981676536041</v>
       </c>
       <c r="H115" t="n">
-        <v>-67.83699664031187</v>
+        <v>-67.78518455894587</v>
       </c>
       <c r="I115" t="n">
-        <v>32.2892580624947</v>
+        <v>32.36501927002818</v>
       </c>
       <c r="J115" t="n">
         <v>50.19357591898496</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2839904987808711</v>
+        <v>0.2855050224448236</v>
       </c>
       <c r="L115" t="n">
-        <v>0.3222178104505755</v>
+        <v>0.322255904914378</v>
       </c>
       <c r="M115" t="n">
-        <v>0.4623710542783812</v>
+        <v>0.4623867402340646</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5560524564196643</v>
+        <v>0.5560564364382705</v>
       </c>
       <c r="O115" t="n">
-        <v>0.009837327424130904</v>
+        <v>0.009862853970815683</v>
       </c>
       <c r="P115" t="n">
-        <v>14.76302035684176</v>
+        <v>15.0306790981786</v>
       </c>
       <c r="Q115" t="n">
-        <v>-85.23697964315824</v>
+        <v>-84.9693209018214</v>
       </c>
       <c r="R115" t="n">
-        <v>-22.8094810418478</v>
+        <v>-22.75983354964038</v>
       </c>
       <c r="S115" t="n">
-        <v>-40.42863375684692</v>
+        <v>-40.33266894782843</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="W115" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="X115" t="n">
         <v>79.2</v>
@@ -22139,52 +22139,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.230000019073486</v>
+        <v>1.235000014305115</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.8326777755084835</v>
+        <v>-0.429558970169519</v>
       </c>
       <c r="F116" t="n">
-        <v>-12.85915132416999</v>
+        <v>-12.50492057530593</v>
       </c>
       <c r="G116" t="n">
-        <v>-44.55908408362421</v>
+        <v>-44.33371472515233</v>
       </c>
       <c r="H116" t="n">
-        <v>-74.79924367357211</v>
+        <v>-74.69680167396915</v>
       </c>
       <c r="I116" t="n">
-        <v>30.59380890559606</v>
+        <v>30.67419795812202</v>
       </c>
       <c r="J116" t="n">
         <v>39.87769041366358</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2401777756846827</v>
+        <v>0.2436789550201171</v>
       </c>
       <c r="L116" t="n">
-        <v>1.672339946934674</v>
+        <v>1.672816136956734</v>
       </c>
       <c r="M116" t="n">
-        <v>2.654394828812003</v>
+        <v>2.65459090705638</v>
       </c>
       <c r="N116" t="n">
-        <v>5.831664316145875</v>
+        <v>5.831714067342209</v>
       </c>
       <c r="O116" t="n">
-        <v>0.05234437647509971</v>
+        <v>0.05266346448988146</v>
       </c>
       <c r="P116" t="n">
-        <v>10.63193925245528</v>
+        <v>11.16524766424063</v>
       </c>
       <c r="Q116" t="n">
-        <v>-89.36806074754472</v>
+        <v>-88.83475233575938</v>
       </c>
       <c r="R116" t="n">
-        <v>-27.66186380720245</v>
+        <v>-27.53372905026585</v>
       </c>
       <c r="S116" t="n">
-        <v>-41.19140492973681</v>
+        <v>-40.9523458318747</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>20.4</v>
       </c>
       <c r="X116" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -22473,52 +22473,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4707.7998046875</v>
+        <v>4705.39990234375</v>
       </c>
       <c r="E2" t="n">
-        <v>1.29528586294696</v>
+        <v>1.24364840935105</v>
       </c>
       <c r="F2" t="n">
-        <v>11.60420128166455</v>
+        <v>11.54730863640774</v>
       </c>
       <c r="G2" t="n">
-        <v>94.01606448330931</v>
+        <v>93.91716061585618</v>
       </c>
       <c r="H2" t="n">
-        <v>172.4263567616366</v>
+        <v>172.2874815589483</v>
       </c>
       <c r="I2" t="n">
-        <v>75.58290710567346</v>
+        <v>75.55999689067148</v>
       </c>
       <c r="J2" t="n">
         <v>92.43498481484269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8431108421660874</v>
+        <v>0.842485120892047</v>
       </c>
       <c r="L2" t="n">
-        <v>3760.14560552968</v>
+        <v>3759.917043401704</v>
       </c>
       <c r="M2" t="n">
-        <v>2937.137621540489</v>
+        <v>2937.043507723088</v>
       </c>
       <c r="N2" t="n">
-        <v>2266.503115546979</v>
+        <v>2266.462439236068</v>
       </c>
       <c r="O2" t="n">
-        <v>115.4067001055394</v>
+        <v>115.2535439445708</v>
       </c>
       <c r="P2" t="n">
-        <v>67.7390812358385</v>
+        <v>67.65094027485992</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32.26091876416151</v>
+        <v>-32.34905972514008</v>
       </c>
       <c r="R2" t="n">
-        <v>86.33692615822352</v>
+        <v>86.28335217775647</v>
       </c>
       <c r="S2" t="n">
-        <v>88.78016330538479</v>
+        <v>88.6839285513243</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -22527,7 +22527,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
+          <t>Doji, Bullish Harami</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -22548,7 +22548,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 92); RSI ipercomprato (76) — attenzione estensione; segnale candlestick: Bullish Harami; favorito dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 92); RSI ipercomprato (76) — attenzione estensione; doji — indecisione del mercato; favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -22569,52 +22569,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2015.5</v>
+        <v>2016.099975585938</v>
       </c>
       <c r="E3" t="n">
-        <v>3.358974358974365</v>
+        <v>3.389742337740387</v>
       </c>
       <c r="F3" t="n">
-        <v>20.13471172793271</v>
+        <v>20.17047352106614</v>
       </c>
       <c r="G3" t="n">
-        <v>105.2026038434997</v>
+        <v>105.2636887120072</v>
       </c>
       <c r="H3" t="n">
-        <v>70.29995775242924</v>
+        <v>70.35065277447718</v>
       </c>
       <c r="I3" t="n">
-        <v>67.16567699358563</v>
+        <v>67.17668997064877</v>
       </c>
       <c r="J3" t="n">
         <v>68.41678221756783</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8214808421887022</v>
+        <v>0.8217532606044605</v>
       </c>
       <c r="L3" t="n">
-        <v>1555.078034899715</v>
+        <v>1555.135175431709</v>
       </c>
       <c r="M3" t="n">
-        <v>1260.718648218328</v>
+        <v>1260.742176672679</v>
       </c>
       <c r="N3" t="n">
-        <v>1105.75877605238</v>
+        <v>1105.768945130108</v>
       </c>
       <c r="O3" t="n">
-        <v>84.53252239421522</v>
+        <v>84.57081143445734</v>
       </c>
       <c r="P3" t="n">
-        <v>57.47243539435058</v>
+        <v>57.5029235093824</v>
       </c>
       <c r="Q3" t="n">
-        <v>-42.52756460564942</v>
+        <v>-42.4970764906176</v>
       </c>
       <c r="R3" t="n">
-        <v>116.2780250397983</v>
+        <v>116.3113828962836</v>
       </c>
       <c r="S3" t="n">
-        <v>117.2343205990366</v>
+        <v>117.2989870782165</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -22665,52 +22665,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75.38500213623047</v>
+        <v>75.37999725341797</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9305123471771815</v>
+        <v>0.9238114733668867</v>
       </c>
       <c r="F4" t="n">
-        <v>33.55242758995416</v>
+        <v>33.5435609158085</v>
       </c>
       <c r="G4" t="n">
-        <v>161.9535841823547</v>
+        <v>161.9361928319004</v>
       </c>
       <c r="H4" t="n">
-        <v>185.5276150152446</v>
+        <v>185.508658562205</v>
       </c>
       <c r="I4" t="n">
-        <v>70.88619465469031</v>
+        <v>70.88414066502712</v>
       </c>
       <c r="J4" t="n">
         <v>61.80579865011009</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8534263859355894</v>
+        <v>0.8533736320181183</v>
       </c>
       <c r="L4" t="n">
-        <v>52.94187068550083</v>
+        <v>52.94139402999487</v>
       </c>
       <c r="M4" t="n">
-        <v>38.67430899733741</v>
+        <v>38.67411272742319</v>
       </c>
       <c r="N4" t="n">
-        <v>29.25810938195093</v>
+        <v>29.25802455342868</v>
       </c>
       <c r="O4" t="n">
-        <v>4.115381706555002</v>
+        <v>4.115062306626227</v>
       </c>
       <c r="P4" t="n">
-        <v>50.6237239004353</v>
+        <v>50.6183417274925</v>
       </c>
       <c r="Q4" t="n">
-        <v>-49.37627609956471</v>
+        <v>-49.3816582725075</v>
       </c>
       <c r="R4" t="n">
-        <v>128.3211221900949</v>
+        <v>128.3147728610845</v>
       </c>
       <c r="S4" t="n">
-        <v>162.3820952075701</v>
+        <v>162.3646754078567</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -23957,52 +23957,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.01800012588501</v>
+        <v>6.013999938964844</v>
       </c>
       <c r="E18" t="n">
-        <v>7.704698401249299</v>
+        <v>7.633106690253499</v>
       </c>
       <c r="F18" t="n">
-        <v>16.05438159587935</v>
+        <v>15.97723981961201</v>
       </c>
       <c r="G18" t="n">
-        <v>44.66346987076795</v>
+        <v>44.56731152781381</v>
       </c>
       <c r="H18" t="n">
-        <v>46.97765369569462</v>
+        <v>46.87995710620116</v>
       </c>
       <c r="I18" t="n">
-        <v>65.82447745215703</v>
+        <v>65.78920953257676</v>
       </c>
       <c r="J18" t="n">
         <v>53.34789996467301</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9360846187053881</v>
+        <v>0.9348535121808438</v>
       </c>
       <c r="L18" t="n">
-        <v>5.057523783822462</v>
+        <v>5.057142813639588</v>
       </c>
       <c r="M18" t="n">
-        <v>4.482147052144998</v>
+        <v>4.481990182069698</v>
       </c>
       <c r="N18" t="n">
-        <v>3.807786889787433</v>
+        <v>3.807719090009125</v>
       </c>
       <c r="O18" t="n">
-        <v>0.115119328943193</v>
+        <v>0.1148640463591136</v>
       </c>
       <c r="P18" t="n">
-        <v>79.6638411996783</v>
+        <v>79.49782390490726</v>
       </c>
       <c r="Q18" t="n">
-        <v>-20.33615880032171</v>
+        <v>-20.50217609509274</v>
       </c>
       <c r="R18" t="n">
-        <v>124.1469612738254</v>
+        <v>124.0050188627805</v>
       </c>
       <c r="S18" t="n">
-        <v>45.18697596084989</v>
+        <v>45.09046964146333</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -27519,66 +27519,66 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>159.7149963378906</v>
+        <v>187.6000061035156</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.07883276342343093</v>
+        <v>-9.328172238915034</v>
       </c>
       <c r="F57" t="n">
-        <v>2.195362180962968</v>
+        <v>24.13154240879054</v>
       </c>
       <c r="G57" t="n">
-        <v>4.614526923062701</v>
+        <v>16.90658981518865</v>
       </c>
       <c r="H57" t="n">
-        <v>50.13771480913998</v>
+        <v>87.60000610351561</v>
       </c>
       <c r="I57" t="n">
-        <v>61.42260476249023</v>
+        <v>59.73765559503357</v>
       </c>
       <c r="J57" t="n">
-        <v>19.38458414734579</v>
+        <v>19.62628180651337</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8816228299328864</v>
+        <v>0.8930101795376867</v>
       </c>
       <c r="L57" t="n">
-        <v>152.233533383736</v>
+        <v>164.9002285910118</v>
       </c>
       <c r="M57" t="n">
-        <v>144.0931453920352</v>
+        <v>153.4169062027084</v>
       </c>
       <c r="N57" t="n">
-        <v>129.4372572931536</v>
+        <v>135.7044086107842</v>
       </c>
       <c r="O57" t="n">
-        <v>0.5630333747530045</v>
+        <v>4.859897286472398</v>
       </c>
       <c r="P57" t="n">
-        <v>97.46297086809054</v>
+        <v>67.20697204912196</v>
       </c>
       <c r="Q57" t="n">
-        <v>-2.53702913190946</v>
+        <v>-32.79302795087804</v>
       </c>
       <c r="R57" t="n">
-        <v>123.7936844466849</v>
+        <v>209.7963547107595</v>
       </c>
       <c r="S57" t="n">
-        <v>10.23189799895972</v>
+        <v>26.79960119846729</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -27586,16 +27586,12 @@
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar</t>
-        </is>
-      </c>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
         <v>73.2</v>
       </c>
       <c r="X57" t="n">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -27604,73 +27600,73 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (61) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (160.23)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>187.6000061035156</v>
+        <v>159.7010040283203</v>
       </c>
       <c r="E58" t="n">
-        <v>-9.328172238915034</v>
+        <v>-0.08758665589851944</v>
       </c>
       <c r="F58" t="n">
-        <v>24.13154240879054</v>
+        <v>2.186409050843241</v>
       </c>
       <c r="G58" t="n">
-        <v>16.90658981518865</v>
+        <v>4.60536185478595</v>
       </c>
       <c r="H58" t="n">
-        <v>87.60000610351561</v>
+        <v>50.12456154594018</v>
       </c>
       <c r="I58" t="n">
-        <v>59.73765559503357</v>
+        <v>61.40295346179372</v>
       </c>
       <c r="J58" t="n">
-        <v>19.62628180651337</v>
+        <v>19.38458414734579</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8930101795376867</v>
+        <v>0.8810905071628335</v>
       </c>
       <c r="L58" t="n">
-        <v>164.9002285910118</v>
+        <v>152.2322007828246</v>
       </c>
       <c r="M58" t="n">
-        <v>153.4169062027084</v>
+        <v>144.0925966740128</v>
       </c>
       <c r="N58" t="n">
-        <v>135.7044086107842</v>
+        <v>129.4370545060583</v>
       </c>
       <c r="O58" t="n">
-        <v>4.859897286472398</v>
+        <v>0.5621404182447947</v>
       </c>
       <c r="P58" t="n">
-        <v>67.20697204912196</v>
+        <v>97.39417541864319</v>
       </c>
       <c r="Q58" t="n">
-        <v>-32.79302795087804</v>
+        <v>-2.605824581356808</v>
       </c>
       <c r="R58" t="n">
-        <v>209.7963547107595</v>
+        <v>123.7304995275291</v>
       </c>
       <c r="S58" t="n">
-        <v>26.79960119846729</v>
+        <v>10.22224080410206</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -27678,12 +27674,16 @@
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Double Top, Inside Bar</t>
+        </is>
+      </c>
       <c r="W58" t="n">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="X58" t="n">
-        <v>73.7</v>
+        <v>75.7</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (61) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (160.23)</t>
         </is>
       </c>
     </row>
@@ -27713,52 +27713,52 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>106.0599975585938</v>
+        <v>105.9499969482422</v>
       </c>
       <c r="E59" t="n">
-        <v>-10.38445380142081</v>
+        <v>-10.47739897401887</v>
       </c>
       <c r="F59" t="n">
-        <v>67.81644980736685</v>
+        <v>67.64239821081044</v>
       </c>
       <c r="G59" t="n">
-        <v>31.39246277834719</v>
+        <v>31.25618848611717</v>
       </c>
       <c r="H59" t="n">
-        <v>60.38107056342268</v>
+        <v>60.21473060437197</v>
       </c>
       <c r="I59" t="n">
-        <v>64.8432971786099</v>
+        <v>64.77322890740928</v>
       </c>
       <c r="J59" t="n">
         <v>16.10599589638658</v>
       </c>
       <c r="K59" t="n">
-        <v>1.074719608900185</v>
+        <v>1.073400729188607</v>
       </c>
       <c r="L59" t="n">
-        <v>78.43599922129768</v>
+        <v>78.42552297269276</v>
       </c>
       <c r="M59" t="n">
-        <v>77.17608553808111</v>
+        <v>77.17177178865555</v>
       </c>
       <c r="N59" t="n">
-        <v>71.44345986659947</v>
+        <v>71.44159544947487</v>
       </c>
       <c r="O59" t="n">
-        <v>4.772340703086263</v>
+        <v>4.765320721115108</v>
       </c>
       <c r="P59" t="n">
-        <v>78.1347262740657</v>
+        <v>77.95442696821428</v>
       </c>
       <c r="Q59" t="n">
-        <v>-21.8652737259343</v>
+        <v>-22.04557303178573</v>
       </c>
       <c r="R59" t="n">
-        <v>188.3614806432875</v>
+        <v>188.1633284875432</v>
       </c>
       <c r="S59" t="n">
-        <v>34.59390031867245</v>
+        <v>34.45430564089138</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -27897,52 +27897,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>96.70999908447266</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.606429567434089</v>
+        <v>-4.734657281914112</v>
       </c>
       <c r="F61" t="n">
-        <v>65.17506463647888</v>
+        <v>64.9530368736917</v>
       </c>
       <c r="G61" t="n">
-        <v>24.13039986995462</v>
+        <v>23.96354420661546</v>
       </c>
       <c r="H61" t="n">
-        <v>57.25203103166285</v>
+        <v>57.04065338382875</v>
       </c>
       <c r="I61" t="n">
-        <v>65.73252829037003</v>
+        <v>65.6297415939008</v>
       </c>
       <c r="J61" t="n">
         <v>13.82316078082327</v>
       </c>
       <c r="K61" t="n">
-        <v>1.113800747309128</v>
+        <v>1.111981457028275</v>
       </c>
       <c r="L61" t="n">
-        <v>72.53673697699735</v>
+        <v>72.52435628619564</v>
       </c>
       <c r="M61" t="n">
-        <v>71.99809085212949</v>
+        <v>71.99299292062291</v>
       </c>
       <c r="N61" t="n">
-        <v>66.87896844300572</v>
+        <v>66.87676509972745</v>
       </c>
       <c r="O61" t="n">
-        <v>3.853608491664677</v>
+        <v>3.845312370648817</v>
       </c>
       <c r="P61" t="n">
-        <v>64.69766988250556</v>
+        <v>64.49612376509533</v>
       </c>
       <c r="Q61" t="n">
-        <v>-35.30233011749444</v>
+        <v>-35.50387623490467</v>
       </c>
       <c r="R61" t="n">
-        <v>202.4285597727185</v>
+        <v>202.1864011256831</v>
       </c>
       <c r="S61" t="n">
-        <v>31.48877644018171</v>
+        <v>31.31202967196405</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -29557,52 +29557,52 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.434100031852722</v>
+        <v>1.435400009155273</v>
       </c>
       <c r="E79" t="n">
-        <v>7.001712279573247</v>
+        <v>7.098706766853091</v>
       </c>
       <c r="F79" t="n">
-        <v>-33.6361935282217</v>
+        <v>-33.57603632843922</v>
       </c>
       <c r="G79" t="n">
-        <v>129.8462002000581</v>
+        <v>130.0545502709745</v>
       </c>
       <c r="H79" t="n">
-        <v>245.6054190925393</v>
+        <v>245.9187021205569</v>
       </c>
       <c r="I79" t="n">
-        <v>46.37675810680397</v>
+        <v>46.39784993687425</v>
       </c>
       <c r="J79" t="n">
         <v>49.98060633402685</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2985933270585924</v>
+        <v>0.2990179805502031</v>
       </c>
       <c r="L79" t="n">
-        <v>1.762795120945075</v>
+        <v>1.762918928307223</v>
       </c>
       <c r="M79" t="n">
-        <v>1.36047997216944</v>
+        <v>1.360531971261543</v>
       </c>
       <c r="N79" t="n">
-        <v>1.075401657529712</v>
+        <v>1.075428187678744</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.174229638917196</v>
+        <v>-0.1741466774027312</v>
       </c>
       <c r="P79" t="n">
-        <v>11.94556486946683</v>
+        <v>11.99721788925251</v>
       </c>
       <c r="Q79" t="n">
-        <v>-88.05443513053318</v>
+        <v>-88.00278211074749</v>
       </c>
       <c r="R79" t="n">
-        <v>-45.57846063992977</v>
+        <v>-45.54876878457257</v>
       </c>
       <c r="S79" t="n">
-        <v>153.2345116741584</v>
+        <v>153.4640626887928</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>2.285124380319148</v>
       </c>
       <c r="R81" t="n">
-        <v>63.23428322243683</v>
+        <v>66.93150196375541</v>
       </c>
       <c r="S81" t="n">
         <v>13.927498342446</v>
@@ -30105,52 +30105,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1.346549272537231</v>
+        <v>1.346545696258545</v>
       </c>
       <c r="E85" t="n">
-        <v>2.221943492873302</v>
+        <v>2.221672003247743</v>
       </c>
       <c r="F85" t="n">
-        <v>1.694089121560438</v>
+        <v>1.69381903385486</v>
       </c>
       <c r="G85" t="n">
-        <v>4.896181728221904</v>
+        <v>4.895903136129753</v>
       </c>
       <c r="H85" t="n">
-        <v>-3.873885297198765</v>
+        <v>-3.874140597010101</v>
       </c>
       <c r="I85" t="n">
-        <v>54.87178945388087</v>
+        <v>54.87132244777467</v>
       </c>
       <c r="J85" t="n">
         <v>21.65217664783298</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6622373366048333</v>
+        <v>0.6622163110508387</v>
       </c>
       <c r="L85" t="n">
-        <v>1.323291033377612</v>
+        <v>1.323290692779642</v>
       </c>
       <c r="M85" t="n">
-        <v>1.304221548080412</v>
+        <v>1.304221407834189</v>
       </c>
       <c r="N85" t="n">
-        <v>1.345124479476919</v>
+        <v>1.345124427646793</v>
       </c>
       <c r="O85" t="n">
-        <v>-6.277214397854697e-05</v>
+        <v>-6.300037372937786e-05</v>
       </c>
       <c r="P85" t="n">
-        <v>69.79487068098477</v>
+        <v>69.79203753353738</v>
       </c>
       <c r="Q85" t="n">
-        <v>-30.20512931901524</v>
+        <v>-30.20796246646262</v>
       </c>
       <c r="R85" t="n">
-        <v>41.33145409864407</v>
+        <v>41.32949905361538</v>
       </c>
       <c r="S85" t="n">
-        <v>2.273107136887842</v>
+        <v>2.27283551137758</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -30193,52 +30193,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>77911.09375</v>
+        <v>77984</v>
       </c>
       <c r="E86" t="n">
-        <v>14.18336717860502</v>
+        <v>14.2902156479652</v>
       </c>
       <c r="F86" t="n">
-        <v>-13.8097391359661</v>
+        <v>-13.72908555502317</v>
       </c>
       <c r="G86" t="n">
-        <v>20.56948006979344</v>
+        <v>20.68230442167</v>
       </c>
       <c r="H86" t="n">
-        <v>72.60731879110733</v>
+        <v>72.76883818109296</v>
       </c>
       <c r="I86" t="n">
-        <v>49.3552187098741</v>
+        <v>49.38967118925057</v>
       </c>
       <c r="J86" t="n">
         <v>33.80484147146453</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3043212743786471</v>
+        <v>0.3053373688496108</v>
       </c>
       <c r="L86" t="n">
-        <v>83078.44473721365</v>
+        <v>83085.3881895946</v>
       </c>
       <c r="M86" t="n">
-        <v>66672.43023353454</v>
+        <v>66675.34648353454</v>
       </c>
       <c r="N86" t="n">
-        <v>49322.39815138273</v>
+        <v>49323.88603403579</v>
       </c>
       <c r="O86" t="n">
-        <v>-5645.000911208092</v>
+        <v>-5640.348204655376</v>
       </c>
       <c r="P86" t="n">
-        <v>26.97496589910862</v>
+        <v>27.08522298645239</v>
       </c>
       <c r="Q86" t="n">
-        <v>-73.02503410089138</v>
+        <v>-72.91477701354761</v>
       </c>
       <c r="R86" t="n">
-        <v>-43.14041960906816</v>
+        <v>-43.08210346123076</v>
       </c>
       <c r="S86" t="n">
-        <v>32.12010841866222</v>
+        <v>32.24374141097146</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -31011,52 +31011,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2.734999895095825</v>
+        <v>2.733999967575073</v>
       </c>
       <c r="E95" t="n">
-        <v>-5.166441213411654</v>
+        <v>-5.201112763305171</v>
       </c>
       <c r="F95" t="n">
-        <v>-43.60824847680021</v>
+        <v>-43.62886553948915</v>
       </c>
       <c r="G95" t="n">
-        <v>34.33201754226749</v>
+        <v>34.28290518891804</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.299170499489954</v>
+        <v>-1.335255939900959</v>
       </c>
       <c r="I95" t="n">
-        <v>45.50954276425621</v>
+        <v>45.5033998361591</v>
       </c>
       <c r="J95" t="n">
         <v>44.68840827516345</v>
       </c>
       <c r="K95" t="n">
-        <v>0.198716686838536</v>
+        <v>0.1983421285558312</v>
       </c>
       <c r="L95" t="n">
-        <v>3.353021746302509</v>
+        <v>3.352926515110056</v>
       </c>
       <c r="M95" t="n">
-        <v>3.386315210192477</v>
+        <v>3.386275997348526</v>
       </c>
       <c r="N95" t="n">
-        <v>3.324885814568322</v>
+        <v>3.324868866644241</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.06361104954838773</v>
+        <v>-0.06367486258674909</v>
       </c>
       <c r="P95" t="n">
-        <v>3.304211646516614</v>
+        <v>3.285223277458601</v>
       </c>
       <c r="Q95" t="n">
-        <v>-96.69578835348338</v>
+        <v>-96.7147767225414</v>
       </c>
       <c r="R95" t="n">
-        <v>-71.1150450990519</v>
+        <v>-71.14281498761611</v>
       </c>
       <c r="S95" t="n">
-        <v>28.58485072497965</v>
+        <v>28.5378395601082</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -31099,52 +31099,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2323.330078125</v>
+        <v>2326.219970703125</v>
       </c>
       <c r="E96" t="n">
-        <v>10.387274624357</v>
+        <v>10.52458071300104</v>
       </c>
       <c r="F96" t="n">
-        <v>-22.35151451655978</v>
+        <v>-22.25493083092078</v>
       </c>
       <c r="G96" t="n">
-        <v>-28.09911791774581</v>
+        <v>-28.00968343426603</v>
       </c>
       <c r="H96" t="n">
-        <v>64.07131108035129</v>
+        <v>64.27539248429757</v>
       </c>
       <c r="I96" t="n">
-        <v>46.1184318378932</v>
+        <v>46.14582702507994</v>
       </c>
       <c r="J96" t="n">
         <v>14.24892668051552</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3289153805441318</v>
+        <v>0.3297677937600152</v>
       </c>
       <c r="L96" t="n">
-        <v>2760.429993343727</v>
+        <v>2760.705221208311</v>
       </c>
       <c r="M96" t="n">
-        <v>2511.233687249764</v>
+        <v>2511.34928295289</v>
       </c>
       <c r="N96" t="n">
-        <v>2059.789011552135</v>
+        <v>2059.847988951689</v>
       </c>
       <c r="O96" t="n">
-        <v>-154.6735629882777</v>
+        <v>-154.4891367952573</v>
       </c>
       <c r="P96" t="n">
-        <v>26.25590684838496</v>
+        <v>26.33692581053185</v>
       </c>
       <c r="Q96" t="n">
-        <v>-73.74409315161505</v>
+        <v>-73.66307418946815</v>
       </c>
       <c r="R96" t="n">
-        <v>-69.49386261243762</v>
+        <v>-69.39449605650846</v>
       </c>
       <c r="S96" t="n">
-        <v>-7.562035077501294</v>
+        <v>-7.447055380349477</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -31187,52 +31187,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>98.81300354003906</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.147454536753556</v>
+        <v>-1.140455582322553</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.6505082951831609</v>
+        <v>-0.6434741559819268</v>
       </c>
       <c r="G97" t="n">
-        <v>-5.078765621112247</v>
+        <v>-5.07204501122972</v>
       </c>
       <c r="H97" t="n">
-        <v>8.669309588042061</v>
+        <v>8.677003588659771</v>
       </c>
       <c r="I97" t="n">
-        <v>45.42829557259474</v>
+        <v>45.44217860270738</v>
       </c>
       <c r="J97" t="n">
         <v>28.5699342843782</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3543106164992945</v>
+        <v>0.3547321343339674</v>
       </c>
       <c r="L97" t="n">
-        <v>100.2891393977673</v>
+        <v>100.289805698223</v>
       </c>
       <c r="M97" t="n">
-        <v>100.9217348664977</v>
+        <v>100.9220092255089</v>
       </c>
       <c r="N97" t="n">
-        <v>99.52911701405448</v>
+        <v>99.52923559294915</v>
       </c>
       <c r="O97" t="n">
-        <v>-0.1958940797135926</v>
+        <v>-0.1954476014595103</v>
       </c>
       <c r="P97" t="n">
-        <v>27.16904230409091</v>
+        <v>27.22729507665608</v>
       </c>
       <c r="Q97" t="n">
-        <v>-72.83095769590909</v>
+        <v>-72.77270492334392</v>
       </c>
       <c r="R97" t="n">
-        <v>-42.1014622281302</v>
+        <v>-42.06031618104782</v>
       </c>
       <c r="S97" t="n">
-        <v>-2.838734999837211</v>
+        <v>-2.831855791385796</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31739,52 +31739,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>85.69999694824219</v>
+        <v>85.80000305175781</v>
       </c>
       <c r="E103" t="n">
-        <v>3.12073978259293</v>
+        <v>3.241074715434689</v>
       </c>
       <c r="F103" t="n">
-        <v>-35.83639960408092</v>
+        <v>-35.76152501958118</v>
       </c>
       <c r="G103" t="n">
-        <v>-50.12400985045555</v>
+        <v>-50.06580794133701</v>
       </c>
       <c r="H103" t="n">
-        <v>554.7358957003498</v>
+        <v>555.4999282335172</v>
       </c>
       <c r="I103" t="n">
-        <v>42.30637624569914</v>
+        <v>42.32490960945398</v>
       </c>
       <c r="J103" t="n">
         <v>32.80032248447666</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1242763039694392</v>
+        <v>0.1247279232522633</v>
       </c>
       <c r="L103" t="n">
-        <v>132.3881409674547</v>
+        <v>132.3976653582657</v>
       </c>
       <c r="M103" t="n">
-        <v>123.8063733856322</v>
+        <v>123.8117791209574</v>
       </c>
       <c r="N103" t="n">
-        <v>96.99097920538084</v>
+        <v>96.99375715270072</v>
       </c>
       <c r="O103" t="n">
-        <v>-14.86797723183383</v>
+        <v>-14.86159507593995</v>
       </c>
       <c r="P103" t="n">
-        <v>9.217621686427963</v>
+        <v>9.2718202249198</v>
       </c>
       <c r="Q103" t="n">
-        <v>-90.78237831357204</v>
+        <v>-90.72817977508021</v>
       </c>
       <c r="R103" t="n">
-        <v>-97.84850112969475</v>
+        <v>-97.80925477426443</v>
       </c>
       <c r="S103" t="n">
-        <v>-49.11832768810356</v>
+        <v>-49.05895221588102</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -32015,52 +32015,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.2483000010251999</v>
+        <v>0.2486999928951263</v>
       </c>
       <c r="E106" t="n">
-        <v>2.788917834221283</v>
+        <v>2.954502736687936</v>
       </c>
       <c r="F106" t="n">
-        <v>-40.29599524464189</v>
+        <v>-40.19981676536041</v>
       </c>
       <c r="G106" t="n">
-        <v>-36.13239482203873</v>
+        <v>-36.02950910831589</v>
       </c>
       <c r="H106" t="n">
-        <v>-81.01767539789775</v>
+        <v>-80.98709635850267</v>
       </c>
       <c r="I106" t="n">
-        <v>39.46643675433538</v>
+        <v>39.48447979299285</v>
       </c>
       <c r="J106" t="n">
         <v>29.80750264091312</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1696314086699909</v>
+        <v>0.1699735180971987</v>
       </c>
       <c r="L106" t="n">
-        <v>0.4871546972512193</v>
+        <v>0.4871927917150218</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5335737986629716</v>
+        <v>0.5335897983377687</v>
       </c>
       <c r="N106" t="n">
-        <v>0.509066188269392</v>
+        <v>0.5090743513687783</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.05472486279218118</v>
+        <v>-0.05469933624549636</v>
       </c>
       <c r="P106" t="n">
-        <v>2.429655677232493</v>
+        <v>2.473706187543452</v>
       </c>
       <c r="Q106" t="n">
-        <v>-97.57034432276751</v>
+        <v>-97.52629381245654</v>
       </c>
       <c r="R106" t="n">
-        <v>-102.6346439038306</v>
+        <v>-102.6004514988219</v>
       </c>
       <c r="S106" t="n">
-        <v>-28.10234042020729</v>
+        <v>-27.98651891726765</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -32295,52 +32295,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9.303000450134277</v>
+        <v>9.314999580383301</v>
       </c>
       <c r="E109" t="n">
-        <v>5.986360381328693</v>
+        <v>6.123062959131675</v>
       </c>
       <c r="F109" t="n">
-        <v>-28.3364577626089</v>
+        <v>-28.24402519937061</v>
       </c>
       <c r="G109" t="n">
-        <v>-27.48373645863325</v>
+        <v>-27.39020404443318</v>
       </c>
       <c r="H109" t="n">
-        <v>-62.28034024824771</v>
+        <v>-62.23168894346318</v>
       </c>
       <c r="I109" t="n">
-        <v>42.88719745556876</v>
+        <v>42.90803890594356</v>
       </c>
       <c r="J109" t="n">
         <v>21.68509511411116</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2073094782429802</v>
+        <v>0.2078592886038513</v>
       </c>
       <c r="L109" t="n">
-        <v>13.47329715109226</v>
+        <v>13.47443992540169</v>
       </c>
       <c r="M109" t="n">
-        <v>13.21556484238318</v>
+        <v>13.21604480759314</v>
       </c>
       <c r="N109" t="n">
-        <v>11.0984359065269</v>
+        <v>11.09868078673606</v>
       </c>
       <c r="O109" t="n">
-        <v>-1.125336647359776</v>
+        <v>-1.124570890899439</v>
       </c>
       <c r="P109" t="n">
-        <v>9.714916766581833</v>
+        <v>9.77369103578415</v>
       </c>
       <c r="Q109" t="n">
-        <v>-90.28508323341816</v>
+        <v>-90.22630896421585</v>
       </c>
       <c r="R109" t="n">
-        <v>-106.2228648792432</v>
+        <v>-106.160358301531</v>
       </c>
       <c r="S109" t="n">
-        <v>-15.61578511750413</v>
+        <v>-15.50694526623636</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -32354,10 +32354,10 @@
         </is>
       </c>
       <c r="W109" t="n">
-        <v>32</v>
+        <v>32.1</v>
       </c>
       <c r="X109" t="n">
-        <v>74.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -32931,52 +32931,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>9.310000419616699</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="E116" t="n">
-        <v>4.497442113583183</v>
+        <v>4.834165552711567</v>
       </c>
       <c r="F116" t="n">
-        <v>-32.41173865747382</v>
+        <v>-32.19394814180525</v>
       </c>
       <c r="G116" t="n">
-        <v>-63.80120526156148</v>
+        <v>-63.68456142406562</v>
       </c>
       <c r="H116" t="n">
-        <v>-60.92047719224981</v>
+        <v>-60.79455074799275</v>
       </c>
       <c r="I116" t="n">
-        <v>40.68666411211211</v>
+        <v>40.71438699126962</v>
       </c>
       <c r="J116" t="n">
         <v>16.45586195882462</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1924427150963454</v>
+        <v>0.19311202191815</v>
       </c>
       <c r="L116" t="n">
-        <v>18.59309355994176</v>
+        <v>18.59595067736759</v>
       </c>
       <c r="M116" t="n">
-        <v>21.46091936522137</v>
+        <v>21.46263363567687</v>
       </c>
       <c r="N116" t="n">
-        <v>22.21327883963408</v>
+        <v>22.21416118472147</v>
       </c>
       <c r="O116" t="n">
-        <v>-1.568196175536024</v>
+        <v>-1.566281662662646</v>
       </c>
       <c r="P116" t="n">
-        <v>5.706352643586037</v>
+        <v>5.812696957312615</v>
       </c>
       <c r="Q116" t="n">
-        <v>-94.29364735641396</v>
+        <v>-94.18730304268739</v>
       </c>
       <c r="R116" t="n">
-        <v>-91.9349517016791</v>
+        <v>-91.87074309551444</v>
       </c>
       <c r="S116" t="n">
-        <v>-79.26173838813718</v>
+        <v>-79.19491322351831</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -33027,52 +33027,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1.230000019073486</v>
+        <v>1.235000014305115</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.727364074918925</v>
+        <v>-1.327882202231567</v>
       </c>
       <c r="F117" t="n">
-        <v>-44.55908408362421</v>
+        <v>-44.33371472515233</v>
       </c>
       <c r="G117" t="n">
-        <v>-77.16017452320979</v>
+        <v>-77.06732979418189</v>
       </c>
       <c r="H117" t="n">
-        <v>-96.34007622752524</v>
+        <v>-96.32519850303197</v>
       </c>
       <c r="I117" t="n">
-        <v>35.29148180259233</v>
+        <v>35.30708939798467</v>
       </c>
       <c r="J117" t="n">
         <v>25.5772157418073</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1810428785075822</v>
+        <v>0.1815952279135867</v>
       </c>
       <c r="L117" t="n">
-        <v>3.424748279537659</v>
+        <v>3.425224469559719</v>
       </c>
       <c r="M117" t="n">
-        <v>4.826665382615241</v>
+        <v>4.826951096628476</v>
       </c>
       <c r="N117" t="n">
-        <v>6.781479987174726</v>
+        <v>6.781627045858009</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.1109138429750545</v>
+        <v>-0.1105947549602722</v>
       </c>
       <c r="P117" t="n">
-        <v>2.353200751296955</v>
+        <v>2.471239589319516</v>
       </c>
       <c r="Q117" t="n">
-        <v>-97.64679924870305</v>
+        <v>-97.52876041068049</v>
       </c>
       <c r="R117" t="n">
-        <v>-86.49167534191116</v>
+        <v>-86.44297523452234</v>
       </c>
       <c r="S117" t="n">
-        <v>-86.28344752906084</v>
+        <v>-86.22768923972298</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -33356,7 +33356,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/04/2026 20:34:44</t>
+          <t>23/04/2026 20:39:48</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33396,13 +33396,13 @@
         <v>19.30999946594238</v>
       </c>
       <c r="N2" t="n">
-        <v>98.81300354003906</v>
+        <v>98.81999969482422</v>
       </c>
       <c r="O2" t="n">
-        <v>4707.7998046875</v>
+        <v>4705.39990234375</v>
       </c>
       <c r="P2" t="n">
-        <v>96.70999908447266</v>
+        <v>96.58000183105469</v>
       </c>
       <c r="Q2" t="n">
         <v>2.787751808934846</v>
@@ -33419,7 +33419,7 @@
         <v>2.30287058551863</v>
       </c>
       <c r="U2" t="n">
-        <v>2.847419890756203</v>
+        <v>2.831622076043044</v>
       </c>
       <c r="V2" t="n">
         <v>0.008443311100047646</v>
@@ -33443,10 +33443,10 @@
         <v>-0.09933745989944809</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6622868534921994</v>
+        <v>0.6619492385047592</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7.959541084248278</v>
+        <v>-8.006460690483831</v>
       </c>
       <c r="AE2" t="n">
         <v>1.215636666136732</v>
@@ -33470,7 +33470,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.219339758087572</v>
+        <v>1.216706788968712</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33569,10 +33569,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.89221284026223</v>
+        <v>79.89203854716712</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1991367894725578</v>
+        <v>0.1991298177487536</v>
       </c>
       <c r="D2" t="n">
         <v>69.82758620689656</v>
@@ -33581,7 +33581,7 @@
         <v>35.18017681969694</v>
       </c>
       <c r="F2" t="n">
-        <v>18.20188259772918</v>
+        <v>18.20188259772922</v>
       </c>
     </row>
   </sheetData>
@@ -33754,33 +33754,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>FTSEMIB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.947</v>
+        <v>0.946</v>
       </c>
       <c r="D8" t="n">
         <v>0.945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FTSEMIB</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -33790,7 +33790,7 @@
         <v>0.945</v>
       </c>
       <c r="E9" t="n">
-        <v>0.903</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -33943,7 +33943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -33952,19 +33952,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.918</v>
+        <v>0.951</v>
       </c>
       <c r="D17" t="n">
         <v>0.9370000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.926</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -33973,13 +33973,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.951</v>
+        <v>0.918</v>
       </c>
       <c r="D18" t="n">
         <v>0.9360000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>0.952</v>
+        <v>0.926</v>
       </c>
     </row>
     <row r="19">
@@ -34140,7 +34140,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.826</v>
+        <v>-0.825</v>
       </c>
       <c r="D4" t="n">
         <v>-0.8090000000000001</v>
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.909</v>
+        <v>-0.91</v>
       </c>
       <c r="D9" t="n">
         <v>-0.739</v>
@@ -34287,7 +34287,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.834</v>
+        <v>-0.835</v>
       </c>
       <c r="D11" t="n">
         <v>-0.737</v>
@@ -34398,7 +34398,7 @@
         <v>-0.713</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.576</v>
+        <v>-0.575</v>
       </c>
     </row>
     <row r="17">
@@ -34434,10 +34434,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.706</v>
+        <v>-0.707</v>
       </c>
       <c r="E18" t="n">
         <v>-0.653</v>
@@ -34482,7 +34482,7 @@
         <v>-0.702</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.611</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="21">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -961,7 +961,7 @@
         <v>78.93103851222787</v>
       </c>
       <c r="J6" t="n">
-        <v>47.45383708182479</v>
+        <v>47.80188401830082</v>
       </c>
       <c r="K6" t="n">
         <v>0.9725210130735034</v>
@@ -979,13 +979,13 @@
         <v>0.3354735513319747</v>
       </c>
       <c r="P6" t="n">
-        <v>103.0021862935916</v>
+        <v>102.7255412489931</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.00218629359158</v>
+        <v>2.725541248993103</v>
       </c>
       <c r="R6" t="n">
-        <v>-47.70052328027374</v>
+        <v>-61.31193457658048</v>
       </c>
       <c r="S6" t="n">
         <v>16.61777908527611</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 47); RSI ipercomprato (79) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 48); RSI ipercomprato (79) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>72.59999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -3441,52 +3441,52 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6.013999938964844</v>
+        <v>6.021999835968018</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.732025303535689</v>
+        <v>-1.601308029797643</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8654124509633543</v>
+        <v>-0.7335423981045031</v>
       </c>
       <c r="G33" t="n">
-        <v>10.90824879458472</v>
+        <v>11.05578031705954</v>
       </c>
       <c r="H33" t="n">
-        <v>1.742516798406624</v>
+        <v>1.877855950965879</v>
       </c>
       <c r="I33" t="n">
-        <v>58.79787118060198</v>
+        <v>59.26759223190381</v>
       </c>
       <c r="J33" t="n">
         <v>41.18504839863726</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7082016218621492</v>
+        <v>0.7155185804306334</v>
       </c>
       <c r="L33" t="n">
-        <v>5.887081324860246</v>
+        <v>5.88784321981293</v>
       </c>
       <c r="M33" t="n">
-        <v>5.784705999211812</v>
+        <v>5.785019720662916</v>
       </c>
       <c r="N33" t="n">
-        <v>5.390744538828134</v>
+        <v>5.390824139793339</v>
       </c>
       <c r="O33" t="n">
-        <v>0.0307298669721969</v>
+        <v>0.0312404017097225</v>
       </c>
       <c r="P33" t="n">
-        <v>77.73178703382069</v>
+        <v>79.0562730918622</v>
       </c>
       <c r="Q33" t="n">
-        <v>-22.2682129661793</v>
+        <v>-20.94372690813781</v>
       </c>
       <c r="R33" t="n">
-        <v>72.99061488786609</v>
+        <v>73.67936242612009</v>
       </c>
       <c r="S33" t="n">
-        <v>8.771932548022443</v>
+        <v>8.916622316238509</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="W33" t="n">
-        <v>70.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="X33" t="n">
-        <v>77.09999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3523,66 +3523,66 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>273.4299926757812</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E34" t="n">
-        <v>0.09517122497622044</v>
+        <v>4.317528935699877</v>
       </c>
       <c r="F34" t="n">
-        <v>3.807896359799701</v>
+        <v>6.962469274012317</v>
       </c>
       <c r="G34" t="n">
-        <v>8.659193029321388</v>
+        <v>1.741793216607279</v>
       </c>
       <c r="H34" t="n">
-        <v>10.23625224838607</v>
+        <v>61.36915906303897</v>
       </c>
       <c r="I34" t="n">
-        <v>62.94078408540657</v>
+        <v>56.68896901546076</v>
       </c>
       <c r="J34" t="n">
-        <v>12.76518184945696</v>
+        <v>24.05054899031809</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9085562672060516</v>
+        <v>0.6258097700542922</v>
       </c>
       <c r="L34" t="n">
-        <v>263.3237552564631</v>
+        <v>99.66149848739461</v>
       </c>
       <c r="M34" t="n">
-        <v>261.302373643884</v>
+        <v>93.1982345740402</v>
       </c>
       <c r="N34" t="n">
-        <v>252.9600203919621</v>
+        <v>77.34060082017123</v>
       </c>
       <c r="O34" t="n">
-        <v>1.812859936747026</v>
+        <v>-0.4879041402273356</v>
       </c>
       <c r="P34" t="n">
-        <v>92.21816775741412</v>
+        <v>78.44123694993444</v>
       </c>
       <c r="Q34" t="n">
-        <v>-7.781832242585886</v>
+        <v>-21.55876305006557</v>
       </c>
       <c r="R34" t="n">
-        <v>131.0299973669376</v>
+        <v>26.36445346781798</v>
       </c>
       <c r="S34" t="n">
-        <v>8.237668419295252</v>
+        <v>4.001170308206037</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3590,16 +3590,12 @@
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
         <v>70.5</v>
       </c>
       <c r="X34" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3608,73 +3604,73 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); RSI in forza (63) — momentum positivo; pattern: Double Bottom; vicino alla resistenza dei 20g (275.77); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>105.9499969482422</v>
+        <v>273.4299926757812</v>
       </c>
       <c r="E35" t="n">
-        <v>3.964275479302048</v>
+        <v>0.09517122497622044</v>
       </c>
       <c r="F35" t="n">
-        <v>6.600259179875767</v>
+        <v>3.807896359799701</v>
       </c>
       <c r="G35" t="n">
-        <v>1.397262048350467</v>
+        <v>8.659193029321388</v>
       </c>
       <c r="H35" t="n">
-        <v>60.82271002636588</v>
+        <v>10.23625224838607</v>
       </c>
       <c r="I35" t="n">
-        <v>56.43550392523061</v>
+        <v>62.94078408540657</v>
       </c>
       <c r="J35" t="n">
-        <v>24.05054899031809</v>
+        <v>12.76518184945696</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6149626116446049</v>
+        <v>0.9085562672060516</v>
       </c>
       <c r="L35" t="n">
-        <v>99.62721271498017</v>
+        <v>263.3237552564631</v>
       </c>
       <c r="M35" t="n">
-        <v>93.18411690304602</v>
+        <v>261.302373643884</v>
       </c>
       <c r="N35" t="n">
-        <v>77.33701872454586</v>
+        <v>252.9600203919621</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.5108785381529128</v>
+        <v>1.812859936747026</v>
       </c>
       <c r="P35" t="n">
-        <v>77.04534475306825</v>
+        <v>92.21816775741412</v>
       </c>
       <c r="Q35" t="n">
-        <v>-22.95465524693175</v>
+        <v>-7.781832242585886</v>
       </c>
       <c r="R35" t="n">
-        <v>25.36188607292824</v>
+        <v>131.0299973669376</v>
       </c>
       <c r="S35" t="n">
-        <v>3.6489881461512</v>
+        <v>8.237668419295252</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3682,12 +3678,16 @@
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W35" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="X35" t="n">
-        <v>77.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); favorito dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); RSI in forza (63) — momentum positivo; pattern: Double Bottom; vicino alla resistenza dei 20g (275.77); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5489,52 +5489,52 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>96.58000183105469</v>
+        <v>96.87999725341797</v>
       </c>
       <c r="E55" t="n">
-        <v>3.894151013590852</v>
+        <v>4.21686554168661</v>
       </c>
       <c r="F55" t="n">
-        <v>1.995986208594691</v>
+        <v>2.312804684282144</v>
       </c>
       <c r="G55" t="n">
-        <v>4.580404360395263</v>
+        <v>4.905250518836013</v>
       </c>
       <c r="H55" t="n">
-        <v>58.14639317779462</v>
+        <v>58.63762524568787</v>
       </c>
       <c r="I55" t="n">
-        <v>53.11916667753718</v>
+        <v>53.3614862947192</v>
       </c>
       <c r="J55" t="n">
         <v>18.80673059102289</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4606976379621026</v>
+        <v>0.4699768105232864</v>
       </c>
       <c r="L55" t="n">
-        <v>94.2947226342537</v>
+        <v>94.32329362685974</v>
       </c>
       <c r="M55" t="n">
-        <v>87.77960142343555</v>
+        <v>87.79136594980274</v>
       </c>
       <c r="N55" t="n">
-        <v>72.76215008288928</v>
+        <v>72.76513511196752</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.409990006764334</v>
+        <v>-1.390844999753115</v>
       </c>
       <c r="P55" t="n">
-        <v>43.21555005218325</v>
+        <v>44.0248174512471</v>
       </c>
       <c r="Q55" t="n">
-        <v>-56.78444994781675</v>
+        <v>-55.9751825487529</v>
       </c>
       <c r="R55" t="n">
-        <v>-19.2241759980246</v>
+        <v>-18.33464252584803</v>
       </c>
       <c r="S55" t="n">
-        <v>6.930914700378588</v>
+        <v>7.263061980468177</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="W55" t="n">
-        <v>64.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="X55" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5581,52 +5581,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>159.7010040283203</v>
+        <v>159.7039947509766</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2058083410781064</v>
+        <v>0.2076848964768452</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5616799166233255</v>
+        <v>0.5635631364334204</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6193385089402703</v>
+        <v>0.621222808523525</v>
       </c>
       <c r="H56" t="n">
-        <v>3.476185429248368</v>
+        <v>3.478123229038843</v>
       </c>
       <c r="I56" t="n">
-        <v>56.68743323980835</v>
+        <v>56.70762823848671</v>
       </c>
       <c r="J56" t="n">
         <v>18.64026120965874</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7262490148743661</v>
+        <v>0.7276460572565669</v>
       </c>
       <c r="L56" t="n">
-        <v>159.0798210525012</v>
+        <v>159.0801058832303</v>
       </c>
       <c r="M56" t="n">
-        <v>158.2490304618226</v>
+        <v>158.249147745064</v>
       </c>
       <c r="N56" t="n">
-        <v>154.648640803066</v>
+        <v>154.6486705615004</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.0602013453565261</v>
+        <v>-0.06001048442347756</v>
       </c>
       <c r="P56" t="n">
-        <v>86.93319278906296</v>
+        <v>87.05765066705612</v>
       </c>
       <c r="Q56" t="n">
-        <v>-13.06680721093705</v>
+        <v>-12.94234933294387</v>
       </c>
       <c r="R56" t="n">
-        <v>58.16167285539258</v>
+        <v>58.29725658334412</v>
       </c>
       <c r="S56" t="n">
-        <v>0.1988915684335346</v>
+        <v>0.2007679943017981</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5769,52 +5769,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.346545696258545</v>
+        <v>1.346590995788574</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.3273435791041224</v>
+        <v>-0.3239904626780032</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.7974220568637724</v>
+        <v>-0.7940847544825713</v>
       </c>
       <c r="G58" t="n">
-        <v>0.3661311208964957</v>
+        <v>0.3695075667039083</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.550000117662609</v>
+        <v>-1.546688132975838</v>
       </c>
       <c r="I58" t="n">
-        <v>52.77925200733311</v>
+        <v>52.81124838933329</v>
       </c>
       <c r="J58" t="n">
         <v>35.816263122645</v>
       </c>
       <c r="K58" t="n">
-        <v>0.644800549526221</v>
+        <v>0.6455824464971287</v>
       </c>
       <c r="L58" t="n">
-        <v>1.343773275324439</v>
+        <v>1.343777589565394</v>
       </c>
       <c r="M58" t="n">
-        <v>1.342366572283661</v>
+        <v>1.342368348735819</v>
       </c>
       <c r="N58" t="n">
-        <v>1.337413515777838</v>
+        <v>1.33741396651943</v>
       </c>
       <c r="O58" t="n">
-        <v>0.001537424886796145</v>
+        <v>0.001540315796974589</v>
       </c>
       <c r="P58" t="n">
-        <v>67.48436608400974</v>
+        <v>67.59499714688312</v>
       </c>
       <c r="Q58" t="n">
-        <v>-32.51563391599026</v>
+        <v>-32.40500285311688</v>
       </c>
       <c r="R58" t="n">
-        <v>46.70444653115718</v>
+        <v>46.78151109764871</v>
       </c>
       <c r="S58" t="n">
-        <v>0.7620189434283997</v>
+        <v>0.7654087074116189</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6225,52 +6225,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>77984</v>
+        <v>77989.5390625</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2801699141368408</v>
+        <v>-0.2730869949311709</v>
       </c>
       <c r="F63" t="n">
-        <v>2.981515956692249</v>
+        <v>2.988830547547172</v>
       </c>
       <c r="G63" t="n">
-        <v>16.58793069677333</v>
+        <v>16.59621172666248</v>
       </c>
       <c r="H63" t="n">
-        <v>14.67320964987398</v>
+        <v>14.68135468058957</v>
       </c>
       <c r="I63" t="n">
-        <v>64.53223810986381</v>
+        <v>64.55292043013765</v>
       </c>
       <c r="J63" t="n">
         <v>45.68130131762761</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8625119937210681</v>
+        <v>0.8628898686701251</v>
       </c>
       <c r="L63" t="n">
-        <v>74099.02758852454</v>
+        <v>74099.55511828644</v>
       </c>
       <c r="M63" t="n">
-        <v>72568.45906928772</v>
+        <v>72568.67628742498</v>
       </c>
       <c r="N63" t="n">
-        <v>82606.20731679273</v>
+        <v>82606.26243184248</v>
       </c>
       <c r="O63" t="n">
-        <v>416.0353225250419</v>
+        <v>416.3888125535489</v>
       </c>
       <c r="P63" t="n">
-        <v>83.37707434338166</v>
+        <v>83.43911977744153</v>
       </c>
       <c r="Q63" t="n">
-        <v>-16.62292565661834</v>
+        <v>-16.56088022255846</v>
       </c>
       <c r="R63" t="n">
-        <v>84.71425120825873</v>
+        <v>84.74492734134724</v>
       </c>
       <c r="S63" t="n">
-        <v>16.51384510260727</v>
+        <v>16.52212087033062</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7437,52 +7437,52 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4705.39990234375</v>
+        <v>4705.2001953125</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5726380909931272</v>
+        <v>-0.5768579965662934</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.671751611831196</v>
+        <v>-1.675924868723522</v>
       </c>
       <c r="G76" t="n">
-        <v>6.957927653171025</v>
+        <v>6.953388134608596</v>
       </c>
       <c r="H76" t="n">
-        <v>-5.441909134279599</v>
+        <v>-5.445922377786927</v>
       </c>
       <c r="I76" t="n">
-        <v>46.61769538470455</v>
+        <v>46.60748835581663</v>
       </c>
       <c r="J76" t="n">
         <v>31.15818978795262</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5063080781855865</v>
+        <v>0.5059182473123295</v>
       </c>
       <c r="L76" t="n">
-        <v>4751.019662703022</v>
+        <v>4751.00064298576</v>
       </c>
       <c r="M76" t="n">
-        <v>4772.904303738087</v>
+        <v>4772.896472089803</v>
       </c>
       <c r="N76" t="n">
-        <v>4293.50755042564</v>
+        <v>4293.505563291002</v>
       </c>
       <c r="O76" t="n">
-        <v>9.74483151928996</v>
+        <v>9.732086683107422</v>
       </c>
       <c r="P76" t="n">
-        <v>36.54890096802978</v>
+        <v>36.47620097194029</v>
       </c>
       <c r="Q76" t="n">
-        <v>-63.45109903197022</v>
+        <v>-63.52379902805971</v>
       </c>
       <c r="R76" t="n">
-        <v>9.001301241289806</v>
+        <v>8.974010534457566</v>
       </c>
       <c r="S76" t="n">
-        <v>3.419932839593098</v>
+        <v>3.415543480943861</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7529,69 +7529,73 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2326.219970703125</v>
+        <v>2328.590087890625</v>
       </c>
       <c r="E77" t="n">
-        <v>-2.098750603264932</v>
+        <v>-1.999001896437869</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.058253967660594</v>
+        <v>-0.9574451293796526</v>
       </c>
       <c r="G77" t="n">
-        <v>13.09609836023544</v>
+        <v>13.21132865227088</v>
       </c>
       <c r="H77" t="n">
-        <v>18.14086233482954</v>
+        <v>18.26123258867154</v>
       </c>
       <c r="I77" t="n">
-        <v>55.3902225703355</v>
+        <v>55.56581842199144</v>
       </c>
       <c r="J77" t="n">
         <v>47.76939751961269</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6387888171610275</v>
+        <v>0.6442997088515746</v>
       </c>
       <c r="L77" t="n">
-        <v>2276.814307480008</v>
+        <v>2277.040032926436</v>
       </c>
       <c r="M77" t="n">
-        <v>2226.010301975022</v>
+        <v>2226.103247747081</v>
       </c>
       <c r="N77" t="n">
-        <v>2636.91315048008</v>
+        <v>2636.936733735677</v>
       </c>
       <c r="O77" t="n">
-        <v>0.1741131713582789</v>
+        <v>0.3253685132383737</v>
       </c>
       <c r="P77" t="n">
-        <v>51.9641954860109</v>
+        <v>52.78584408143022</v>
       </c>
       <c r="Q77" t="n">
-        <v>-48.0358045139891</v>
+        <v>-47.21415591856978</v>
       </c>
       <c r="R77" t="n">
-        <v>36.9860126584938</v>
+        <v>37.3943534897409</v>
       </c>
       <c r="S77" t="n">
-        <v>13.28706906206951</v>
+        <v>13.40249392854265</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bearish Harami</t>
+        </is>
+      </c>
       <c r="V77" t="inlineStr">
         <is>
           <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W77" t="n">
-        <v>56</v>
+        <v>56.2</v>
       </c>
       <c r="X77" t="n">
-        <v>71.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7600,90 +7604,94 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 48); pattern: Bull Flag / Consolidation; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 48); pattern: Bull Flag / Consolidation; segnale candlestick: Bearish Harami; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MOO</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Agribusiness</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>83.12999725341797</v>
+        <v>1.437199950218201</v>
       </c>
       <c r="E78" t="n">
-        <v>0.02406045351890373</v>
+        <v>0.5015278497465525</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.7995295631743837</v>
+        <v>0.1754384069853732</v>
       </c>
       <c r="G78" t="n">
-        <v>1.119083054605063</v>
+        <v>8.986861486485886</v>
       </c>
       <c r="H78" t="n">
-        <v>4.76370365719625</v>
+        <v>0.5446928702135923</v>
       </c>
       <c r="I78" t="n">
-        <v>45.35554130370132</v>
+        <v>56.80667278161111</v>
       </c>
       <c r="J78" t="n">
-        <v>27.39858677518637</v>
+        <v>30.7101634397846</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2448120791372954</v>
+        <v>0.7702375177853598</v>
       </c>
       <c r="L78" t="n">
-        <v>83.8359717804021</v>
+        <v>1.400243648871959</v>
       </c>
       <c r="M78" t="n">
-        <v>83.00361606280865</v>
+        <v>1.413822040899541</v>
       </c>
       <c r="N78" t="n">
-        <v>77.86687997661033</v>
+        <v>1.7790984048738</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.2484960445130959</v>
+        <v>0.007809096669945139</v>
       </c>
       <c r="P78" t="n">
-        <v>12.88658172093755</v>
+        <v>62.03269702050819</v>
       </c>
       <c r="Q78" t="n">
-        <v>-87.11341827906246</v>
+        <v>-37.96730297949181</v>
       </c>
       <c r="R78" t="n">
-        <v>-69.47277854259958</v>
+        <v>70.80742335627504</v>
       </c>
       <c r="S78" t="n">
-        <v>0.2290750017109655</v>
+        <v>9.051699146254698</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Hammer, Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W78" t="n">
         <v>55.9</v>
       </c>
       <c r="X78" t="n">
-        <v>68.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7692,94 +7700,90 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); pattern: Double Top; sul supporto dei 20g (82.41); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
+          <t>trend molto direzionale (ADX 31); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; penalizzato dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>MOO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Agribusiness</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.435400009155273</v>
+        <v>83.12999725341797</v>
       </c>
       <c r="E79" t="n">
-        <v>0.375660306516945</v>
+        <v>0.02406045351890373</v>
       </c>
       <c r="F79" t="n">
-        <v>0.04997925632361788</v>
+        <v>-0.7995295631743837</v>
       </c>
       <c r="G79" t="n">
-        <v>8.8503669595557</v>
+        <v>1.119083054605063</v>
       </c>
       <c r="H79" t="n">
-        <v>0.4187712673572763</v>
+        <v>4.76370365719625</v>
       </c>
       <c r="I79" t="n">
-        <v>56.5667712227112</v>
+        <v>45.35554130370132</v>
       </c>
       <c r="J79" t="n">
-        <v>30.7101634397846</v>
+        <v>27.39858677518637</v>
       </c>
       <c r="K79" t="n">
-        <v>0.7620851862799014</v>
+        <v>0.2448120791372954</v>
       </c>
       <c r="L79" t="n">
-        <v>1.400072225913585</v>
+        <v>83.8359717804021</v>
       </c>
       <c r="M79" t="n">
-        <v>1.413751454975504</v>
+        <v>83.00361606280865</v>
       </c>
       <c r="N79" t="n">
-        <v>1.779080495012478</v>
+        <v>77.86687997661033</v>
       </c>
       <c r="O79" t="n">
-        <v>0.007694228636299694</v>
+        <v>-0.2484960445130959</v>
       </c>
       <c r="P79" t="n">
-        <v>61.05894492454533</v>
+        <v>12.88658172093755</v>
       </c>
       <c r="Q79" t="n">
-        <v>-38.94105507545466</v>
+        <v>-87.11341827906246</v>
       </c>
       <c r="R79" t="n">
-        <v>69.98816633533384</v>
+        <v>-69.47277854259958</v>
       </c>
       <c r="S79" t="n">
-        <v>8.915123417007331</v>
+        <v>0.2290750017109655</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Hammer, Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
       <c r="V79" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W79" t="n">
-        <v>55.8</v>
+        <v>55.9</v>
       </c>
       <c r="X79" t="n">
-        <v>74.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -7788,7 +7792,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; penalizzato dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 27); pattern: Double Top; sul supporto dei 20g (82.41); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -7809,52 +7813,52 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>75.37999725341797</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.226221305045418</v>
+        <v>-3.200539571075867</v>
       </c>
       <c r="F80" t="n">
-        <v>-4.104019335641129</v>
+        <v>-4.078570550883686</v>
       </c>
       <c r="G80" t="n">
-        <v>8.814266529014358</v>
+        <v>8.843143556270894</v>
       </c>
       <c r="H80" t="n">
-        <v>-25.31087939154135</v>
+        <v>-25.29105846327179</v>
       </c>
       <c r="I80" t="n">
-        <v>46.99941491692338</v>
+        <v>47.03071569861722</v>
       </c>
       <c r="J80" t="n">
         <v>18.16319029254958</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5002428789336565</v>
+        <v>0.5015257169580563</v>
       </c>
       <c r="L80" t="n">
-        <v>76.89016410897675</v>
+        <v>76.89206927778255</v>
       </c>
       <c r="M80" t="n">
-        <v>77.42808620072778</v>
+        <v>77.42887068200076</v>
       </c>
       <c r="N80" t="n">
-        <v>64.4016033885126</v>
+        <v>64.40180243599978</v>
       </c>
       <c r="O80" t="n">
-        <v>0.4045683373287473</v>
+        <v>0.4058449632635741</v>
       </c>
       <c r="P80" t="n">
-        <v>41.9329422104666</v>
+        <v>42.08886013412985</v>
       </c>
       <c r="Q80" t="n">
-        <v>-58.0670577895334</v>
+        <v>-57.91113986587015</v>
       </c>
       <c r="R80" t="n">
-        <v>11.93355213659001</v>
+        <v>12.02627445643852</v>
       </c>
       <c r="S80" t="n">
-        <v>4.172133041052972</v>
+        <v>4.199778143309807</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -7901,52 +7905,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2016.099975585938</v>
+        <v>2016.300048828125</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.726050342958308</v>
+        <v>-2.716397094248457</v>
       </c>
       <c r="F81" t="n">
-        <v>-3.724756145019592</v>
+        <v>-3.715202005634788</v>
       </c>
       <c r="G81" t="n">
-        <v>6.559195326952305</v>
+        <v>6.569770022628174</v>
       </c>
       <c r="H81" t="n">
-        <v>-25.93586189861954</v>
+        <v>-25.9285119395802</v>
       </c>
       <c r="I81" t="n">
-        <v>47.51155736778559</v>
+        <v>47.52602951297266</v>
       </c>
       <c r="J81" t="n">
         <v>30.40702094970498</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5145222109116466</v>
+        <v>0.5150786046652086</v>
       </c>
       <c r="L81" t="n">
-        <v>2043.503056443961</v>
+        <v>2043.522111038455</v>
       </c>
       <c r="M81" t="n">
-        <v>2060.031791023349</v>
+        <v>2060.039637032847</v>
       </c>
       <c r="N81" t="n">
-        <v>1817.275614522447</v>
+        <v>1817.277605300976</v>
       </c>
       <c r="O81" t="n">
-        <v>6.820965907734315</v>
+        <v>6.833734114643047</v>
       </c>
       <c r="P81" t="n">
-        <v>42.83604650813351</v>
+        <v>42.93455624040221</v>
       </c>
       <c r="Q81" t="n">
-        <v>-57.16395349186649</v>
+        <v>-57.06544375959778</v>
       </c>
       <c r="R81" t="n">
-        <v>22.14542942260731</v>
+        <v>22.18683528233412</v>
       </c>
       <c r="S81" t="n">
-        <v>4.72158875542934</v>
+        <v>4.731981091148341</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8151,7 +8155,7 @@
         <v>53.4</v>
       </c>
       <c r="X83" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -8369,52 +8373,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>98.81999969482422</v>
+        <v>98.81400299072266</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2332927938706097</v>
+        <v>0.2272103267600301</v>
       </c>
       <c r="F86" t="n">
-        <v>0.6108719880514757</v>
+        <v>0.6047666082642289</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.6134975444828661</v>
+        <v>-0.6195286257291266</v>
       </c>
       <c r="H86" t="n">
-        <v>1.250001270262935</v>
+        <v>1.243857106128399</v>
       </c>
       <c r="I86" t="n">
-        <v>49.89771666757966</v>
+        <v>49.8197585619892</v>
       </c>
       <c r="J86" t="n">
         <v>37.35734105194766</v>
       </c>
       <c r="K86" t="n">
-        <v>0.4286594030126377</v>
+        <v>0.426959751883883</v>
       </c>
       <c r="L86" t="n">
-        <v>98.77369101055976</v>
+        <v>98.77311989588343</v>
       </c>
       <c r="M86" t="n">
-        <v>98.79429701958396</v>
+        <v>98.79406185471723</v>
       </c>
       <c r="N86" t="n">
-        <v>99.12248579725905</v>
+        <v>99.12242612856151</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.06272522445550166</v>
+        <v>-0.06310792010186431</v>
       </c>
       <c r="P86" t="n">
-        <v>44.73687229673141</v>
+        <v>44.5114326032835</v>
       </c>
       <c r="Q86" t="n">
-        <v>-55.26312770326859</v>
+        <v>-55.4885673967165</v>
       </c>
       <c r="R86" t="n">
-        <v>-26.30246620878067</v>
+        <v>-26.47163790349653</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.7831313165125642</v>
+        <v>-0.7891521038553617</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8461,52 +8465,52 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1471.5</v>
+        <v>1471</v>
       </c>
       <c r="E87" t="n">
-        <v>-4.886560453684019</v>
+        <v>-4.918878985639951</v>
       </c>
       <c r="F87" t="n">
-        <v>-6.30372492836676</v>
+        <v>-6.335561922954469</v>
       </c>
       <c r="G87" t="n">
-        <v>4.272962791562684</v>
+        <v>4.237531951334494</v>
       </c>
       <c r="H87" t="n">
-        <v>-26.7910447761194</v>
+        <v>-26.81592039800995</v>
       </c>
       <c r="I87" t="n">
-        <v>42.32451898523097</v>
+        <v>42.28140598501045</v>
       </c>
       <c r="J87" t="n">
         <v>26.61423539958696</v>
       </c>
       <c r="K87" t="n">
-        <v>0.3693962627629984</v>
+        <v>0.3677576028937318</v>
       </c>
       <c r="L87" t="n">
-        <v>1533.80297315175</v>
+        <v>1533.755354104131</v>
       </c>
       <c r="M87" t="n">
-        <v>1573.657016385984</v>
+        <v>1573.637408542847</v>
       </c>
       <c r="N87" t="n">
-        <v>1478.459116642471</v>
+        <v>1478.454141518093</v>
       </c>
       <c r="O87" t="n">
-        <v>4.550685762144898</v>
+        <v>4.518776930235985</v>
       </c>
       <c r="P87" t="n">
-        <v>19.87870292911121</v>
+        <v>19.5417757608212</v>
       </c>
       <c r="Q87" t="n">
-        <v>-80.12129707088879</v>
+        <v>-80.4582242391788</v>
       </c>
       <c r="R87" t="n">
-        <v>-7.684417237020885</v>
+        <v>-7.821142471942546</v>
       </c>
       <c r="S87" t="n">
-        <v>3.919491525423724</v>
+        <v>3.884180790960445</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8523,7 +8527,7 @@
         <v>49.2</v>
       </c>
       <c r="X87" t="n">
-        <v>65.8</v>
+        <v>65.7</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -8933,52 +8937,52 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>85.80000305175781</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.283795948308986</v>
+        <v>-1.226274291664209</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.4671662258219134</v>
+        <v>-0.409168721316544</v>
       </c>
       <c r="G92" t="n">
-        <v>8.674568699981556</v>
+        <v>8.737893067919234</v>
       </c>
       <c r="H92" t="n">
-        <v>1.376372191737829</v>
+        <v>1.435443920934931</v>
       </c>
       <c r="I92" t="n">
-        <v>50.95389330333007</v>
+        <v>51.04767011564712</v>
       </c>
       <c r="J92" t="n">
         <v>15.81676323019232</v>
       </c>
       <c r="K92" t="n">
-        <v>0.6188843788153817</v>
+        <v>0.6236739263497695</v>
       </c>
       <c r="L92" t="n">
-        <v>85.30016193683811</v>
+        <v>85.30492340563461</v>
       </c>
       <c r="M92" t="n">
-        <v>87.07825065639238</v>
+        <v>87.08021126119094</v>
       </c>
       <c r="N92" t="n">
-        <v>116.3580650236409</v>
+        <v>116.3585624905301</v>
       </c>
       <c r="O92" t="n">
-        <v>0.2836826745723509</v>
+        <v>0.2868732656291466</v>
       </c>
       <c r="P92" t="n">
-        <v>47.42947317789923</v>
+        <v>47.96919321203016</v>
       </c>
       <c r="Q92" t="n">
-        <v>-52.57052682210077</v>
+        <v>-52.03080678796984</v>
       </c>
       <c r="R92" t="n">
-        <v>34.3603816282762</v>
+        <v>34.78491244331131</v>
       </c>
       <c r="S92" t="n">
-        <v>6.758188148811684</v>
+        <v>6.820395847149618</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10391,7 +10395,7 @@
         <v>38.2</v>
       </c>
       <c r="X107" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -10781,52 +10785,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.2486999928951263</v>
+        <v>0.2489999979734421</v>
       </c>
       <c r="E112" t="n">
-        <v>0.05632298495155119</v>
+        <v>0.1770202341297544</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.3238375465937526</v>
+        <v>-0.2035988824307999</v>
       </c>
       <c r="G112" t="n">
-        <v>3.902940432893076</v>
+        <v>4.028277830047511</v>
       </c>
       <c r="H112" t="n">
-        <v>-12.7083639952874</v>
+        <v>-12.60306469957352</v>
       </c>
       <c r="I112" t="n">
-        <v>48.41913427871974</v>
+        <v>48.60404082188705</v>
       </c>
       <c r="J112" t="n">
         <v>12.32075114472588</v>
       </c>
       <c r="K112" t="n">
-        <v>0.4640095905513412</v>
+        <v>0.4751127949939141</v>
       </c>
       <c r="L112" t="n">
-        <v>0.2498368839921969</v>
+        <v>0.2498654559044174</v>
       </c>
       <c r="M112" t="n">
-        <v>0.2593549220313111</v>
+        <v>0.2593666869363431</v>
       </c>
       <c r="N112" t="n">
-        <v>0.3851570081777929</v>
+        <v>0.3851599933029503</v>
       </c>
       <c r="O112" t="n">
-        <v>0.0006161191810473972</v>
+        <v>0.0006352648042789507</v>
       </c>
       <c r="P112" t="n">
-        <v>40.88794415938682</v>
+        <v>41.83663708549169</v>
       </c>
       <c r="Q112" t="n">
-        <v>-59.11205584061318</v>
+        <v>-58.16336291450831</v>
       </c>
       <c r="R112" t="n">
-        <v>-22.63480916647228</v>
+        <v>-21.23933115512089</v>
       </c>
       <c r="S112" t="n">
-        <v>1.028561950913609</v>
+        <v>1.150432005220314</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10965,52 +10969,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.235000014305115</v>
+        <v>1.235999941825867</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.854958016840148</v>
+        <v>-2.776303765942656</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.054523397516162</v>
+        <v>-2.976030726306123</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.109754655967409</v>
+        <v>-0.0288777294757403</v>
       </c>
       <c r="H114" t="n">
-        <v>-7.928714665631476</v>
+        <v>-7.854168421898322</v>
       </c>
       <c r="I114" t="n">
-        <v>44.01954532160602</v>
+        <v>44.11286979025736</v>
       </c>
       <c r="J114" t="n">
         <v>19.33722230750936</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3438322437868248</v>
+        <v>0.3489821652008541</v>
       </c>
       <c r="L114" t="n">
-        <v>1.273927837022372</v>
+        <v>1.274023068214824</v>
       </c>
       <c r="M114" t="n">
-        <v>1.345878351189991</v>
+        <v>1.345917564033942</v>
       </c>
       <c r="N114" t="n">
-        <v>2.031491962666767</v>
+        <v>2.031501912194336</v>
       </c>
       <c r="O114" t="n">
-        <v>0.006895922565655421</v>
+        <v>0.00695973560401696</v>
       </c>
       <c r="P114" t="n">
-        <v>42.08390194357455</v>
+        <v>42.57017239760088</v>
       </c>
       <c r="Q114" t="n">
-        <v>-57.91609805642546</v>
+        <v>-57.42982760239912</v>
       </c>
       <c r="R114" t="n">
-        <v>-29.53099523011899</v>
+        <v>-29.07661274092767</v>
       </c>
       <c r="S114" t="n">
-        <v>-0.1922564282250905</v>
+        <v>-0.1114462999452726</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11020,7 +11024,7 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="X114" t="n">
         <v>73.5</v>
@@ -11479,52 +11483,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.58000183105469</v>
+        <v>96.87999725341797</v>
       </c>
       <c r="E2" t="n">
-        <v>15.1818766709489</v>
+        <v>15.53965297127389</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.769729321776159</v>
+        <v>-1.4646078578884</v>
       </c>
       <c r="G2" t="n">
-        <v>64.9530368736917</v>
+        <v>65.46541164102284</v>
       </c>
       <c r="H2" t="n">
-        <v>36.52813789597169</v>
+        <v>36.95221964805346</v>
       </c>
       <c r="I2" t="n">
-        <v>62.61906557397396</v>
+        <v>62.75747793408465</v>
       </c>
       <c r="J2" t="n">
         <v>58.66713718370163</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7793214075796742</v>
+        <v>0.7828230138208827</v>
       </c>
       <c r="L2" t="n">
-        <v>81.16944189606649</v>
+        <v>81.19801288867252</v>
       </c>
       <c r="M2" t="n">
-        <v>72.76379308687245</v>
+        <v>72.77555761323964</v>
       </c>
       <c r="N2" t="n">
-        <v>71.92678657570275</v>
+        <v>71.929771604781</v>
       </c>
       <c r="O2" t="n">
-        <v>2.370152015291222</v>
+        <v>2.38929702230244</v>
       </c>
       <c r="P2" t="n">
-        <v>62.32313170690499</v>
+        <v>62.81670756995196</v>
       </c>
       <c r="Q2" t="n">
-        <v>-37.67686829309501</v>
+        <v>-37.18329243004804</v>
       </c>
       <c r="R2" t="n">
-        <v>97.49616069605565</v>
+        <v>97.94667034221942</v>
       </c>
       <c r="S2" t="n">
-        <v>60.75232837481965</v>
+        <v>61.25165496140477</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -11575,52 +11579,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>105.9499969482422</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E3" t="n">
-        <v>17.22726285459739</v>
+        <v>17.62558175401288</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.561997822776632</v>
+        <v>-5.241113071446335</v>
       </c>
       <c r="G3" t="n">
-        <v>67.64239821081044</v>
+        <v>68.21201942284476</v>
       </c>
       <c r="H3" t="n">
-        <v>41.7580946969786</v>
+        <v>42.23976531597933</v>
       </c>
       <c r="I3" t="n">
-        <v>66.87637536738788</v>
+        <v>67.03533199099815</v>
       </c>
       <c r="J3" t="n">
         <v>60.96010584971138</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8243832754371067</v>
+        <v>0.8283145443903709</v>
       </c>
       <c r="L3" t="n">
-        <v>86.28123168917092</v>
+        <v>86.31551746158536</v>
       </c>
       <c r="M3" t="n">
-        <v>77.19915834739766</v>
+        <v>77.21327601839184</v>
       </c>
       <c r="N3" t="n">
-        <v>76.06045241872519</v>
+        <v>76.06403451435058</v>
       </c>
       <c r="O3" t="n">
-        <v>2.454738145193563</v>
+        <v>2.477712543119129</v>
       </c>
       <c r="P3" t="n">
-        <v>76.04203097623696</v>
+        <v>76.68328603466863</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.95796902376303</v>
+        <v>-23.31671396533137</v>
       </c>
       <c r="R3" t="n">
-        <v>109.5817564546903</v>
+        <v>110.0953304243817</v>
       </c>
       <c r="S3" t="n">
-        <v>66.19607364430146</v>
+        <v>66.76078048406863</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -13343,52 +13347,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.013999938964844</v>
+        <v>6.021999835968018</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.466370967987651</v>
+        <v>-1.335300317571131</v>
       </c>
       <c r="F22" t="n">
-        <v>12.56901643024142</v>
+        <v>12.71875712633885</v>
       </c>
       <c r="G22" t="n">
-        <v>15.97723981961201</v>
+        <v>16.13151417656005</v>
       </c>
       <c r="H22" t="n">
-        <v>29.15279966346447</v>
+        <v>29.32460031286008</v>
       </c>
       <c r="I22" t="n">
-        <v>60.97566942831919</v>
+        <v>61.20217431761125</v>
       </c>
       <c r="J22" t="n">
         <v>48.57643889583426</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7983255124047095</v>
+        <v>0.8060700836818788</v>
       </c>
       <c r="L22" t="n">
-        <v>5.667643397285032</v>
+        <v>5.668405292237716</v>
       </c>
       <c r="M22" t="n">
-        <v>5.312413917801926</v>
+        <v>5.312727639253031</v>
       </c>
       <c r="N22" t="n">
-        <v>4.525406774026774</v>
+        <v>4.52548637499198</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.005522153404334346</v>
+        <v>-0.005011618666808743</v>
       </c>
       <c r="P22" t="n">
-        <v>60.16128635307183</v>
+        <v>60.80643945628248</v>
       </c>
       <c r="Q22" t="n">
-        <v>-39.83871364692817</v>
+        <v>-39.19356054371752</v>
       </c>
       <c r="R22" t="n">
-        <v>45.90320740113416</v>
+        <v>46.27821937082219</v>
       </c>
       <c r="S22" t="n">
-        <v>11.7428460250103</v>
+        <v>11.89148773902991</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -13406,10 +13410,10 @@
         </is>
       </c>
       <c r="W22" t="n">
-        <v>74.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="X22" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -14371,52 +14375,52 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4705.39990234375</v>
+        <v>4705.2001953125</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.133238476875344</v>
+        <v>-3.137349705202819</v>
       </c>
       <c r="F33" t="n">
-        <v>2.953789665774553</v>
+        <v>2.949420091218347</v>
       </c>
       <c r="G33" t="n">
-        <v>11.54730863640774</v>
+        <v>11.54257433490009</v>
       </c>
       <c r="H33" t="n">
-        <v>63.17796306666217</v>
+        <v>63.17103745199694</v>
       </c>
       <c r="I33" t="n">
-        <v>54.59289472123281</v>
+        <v>54.5873247888562</v>
       </c>
       <c r="J33" t="n">
         <v>44.58204990747586</v>
       </c>
       <c r="K33" t="n">
-        <v>0.4708166594523198</v>
+        <v>0.4706505686999741</v>
       </c>
       <c r="L33" t="n">
-        <v>4653.993899685292</v>
+        <v>4653.974879968031</v>
       </c>
       <c r="M33" t="n">
-        <v>4170.014461147833</v>
+        <v>4170.006629499549</v>
       </c>
       <c r="N33" t="n">
-        <v>2980.280518766032</v>
+        <v>2980.278531631393</v>
       </c>
       <c r="O33" t="n">
-        <v>-63.99145816955479</v>
+        <v>-64.00420300573728</v>
       </c>
       <c r="P33" t="n">
-        <v>40.70283685611913</v>
+        <v>40.68939219618027</v>
       </c>
       <c r="Q33" t="n">
-        <v>-59.29716314388087</v>
+        <v>-59.31060780381973</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.3348037936943221</v>
+        <v>-0.3446872844725172</v>
       </c>
       <c r="S33" t="n">
-        <v>11.6902848730398</v>
+        <v>11.68554450332109</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -14747,52 +14751,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>75.37999725341797</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.778514020032368</v>
+        <v>-7.754040369203041</v>
       </c>
       <c r="F37" t="n">
-        <v>8.67934917833313</v>
+        <v>8.70819040135058</v>
       </c>
       <c r="G37" t="n">
-        <v>33.5435609158085</v>
+        <v>33.57900057984804</v>
       </c>
       <c r="H37" t="n">
-        <v>129.8100675867018</v>
+        <v>129.8710543653403</v>
       </c>
       <c r="I37" t="n">
-        <v>53.57872393323125</v>
+        <v>53.59329753150701</v>
       </c>
       <c r="J37" t="n">
         <v>55.22104530237728</v>
       </c>
       <c r="K37" t="n">
-        <v>0.4266666749979549</v>
+        <v>0.427188105239013</v>
       </c>
       <c r="L37" t="n">
-        <v>73.75112377955124</v>
+        <v>73.75302894835704</v>
       </c>
       <c r="M37" t="n">
-        <v>61.11588829125289</v>
+        <v>61.11667277252587</v>
       </c>
       <c r="N37" t="n">
-        <v>39.02584445596523</v>
+        <v>39.0260435034524</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.884256430319398</v>
+        <v>-1.882979804384571</v>
       </c>
       <c r="P37" t="n">
-        <v>23.73359311202937</v>
+        <v>23.76681727993788</v>
       </c>
       <c r="Q37" t="n">
-        <v>-76.26640688797063</v>
+        <v>-76.23318272006212</v>
       </c>
       <c r="R37" t="n">
-        <v>-8.333236036402434</v>
+        <v>-8.306565081214526</v>
       </c>
       <c r="S37" t="n">
-        <v>29.02672984752115</v>
+        <v>29.06097083919878</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -15505,7 +15509,7 @@
         <v>80.95135377215732</v>
       </c>
       <c r="J45" t="n">
-        <v>24.67093203662111</v>
+        <v>24.30623998972093</v>
       </c>
       <c r="K45" t="n">
         <v>1.140966420531304</v>
@@ -15529,7 +15533,7 @@
         <v>2.285124380319148</v>
       </c>
       <c r="R45" t="n">
-        <v>214.7842957419916</v>
+        <v>205.2800019976372</v>
       </c>
       <c r="S45" t="n">
         <v>27.97360497235619</v>
@@ -15562,7 +15566,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); RSI ipercomprato (81) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
+          <t>trend in sviluppo (ADX 24); RSI ipercomprato (81) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (79.09); favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
@@ -16051,52 +16055,52 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>159.7010040283203</v>
+        <v>159.7039947509766</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3178470937037936</v>
+        <v>0.3197257472536297</v>
       </c>
       <c r="F51" t="n">
-        <v>1.125229921967841</v>
+        <v>1.127123695385768</v>
       </c>
       <c r="G51" t="n">
-        <v>2.186409050843241</v>
+        <v>2.188322696975686</v>
       </c>
       <c r="H51" t="n">
-        <v>4.387247243171877</v>
+        <v>4.38920210442808</v>
       </c>
       <c r="I51" t="n">
-        <v>59.7555905300759</v>
+        <v>59.76173602887761</v>
       </c>
       <c r="J51" t="n">
         <v>13.25914642780409</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8030894705474647</v>
+        <v>0.8034032206386739</v>
       </c>
       <c r="L51" t="n">
-        <v>157.0481985107095</v>
+        <v>157.0484833414386</v>
       </c>
       <c r="M51" t="n">
-        <v>154.0784628184865</v>
+        <v>154.0785801017279</v>
       </c>
       <c r="N51" t="n">
-        <v>144.8351292100681</v>
+        <v>144.8351589685025</v>
       </c>
       <c r="O51" t="n">
-        <v>0.05160188126077347</v>
+        <v>0.05179274219382202</v>
       </c>
       <c r="P51" t="n">
-        <v>93.3358659114979</v>
+        <v>93.37347086000214</v>
       </c>
       <c r="Q51" t="n">
-        <v>-6.664134088502095</v>
+        <v>-6.626529139997851</v>
       </c>
       <c r="R51" t="n">
-        <v>53.44014287650015</v>
+        <v>53.46204122637735</v>
       </c>
       <c r="S51" t="n">
-        <v>2.938601917936423</v>
+        <v>2.940529650393908</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -16243,52 +16247,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2016.099975585938</v>
+        <v>2016.300048828125</v>
       </c>
       <c r="E53" t="n">
-        <v>-5.102378179056832</v>
+        <v>-5.092960751794539</v>
       </c>
       <c r="F53" t="n">
-        <v>2.308941467761416</v>
+        <v>2.319094377771869</v>
       </c>
       <c r="G53" t="n">
-        <v>20.17047352106614</v>
+        <v>20.18239896947826</v>
       </c>
       <c r="H53" t="n">
-        <v>99.6533967080303</v>
+        <v>99.67320986356667</v>
       </c>
       <c r="I53" t="n">
-        <v>51.91982895110198</v>
+        <v>51.92575570247612</v>
       </c>
       <c r="J53" t="n">
         <v>33.03065630583864</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3651829960451154</v>
+        <v>0.3654001414664626</v>
       </c>
       <c r="L53" t="n">
-        <v>2013.330759335012</v>
+        <v>2013.349813929506</v>
       </c>
       <c r="M53" t="n">
-        <v>1755.105091138624</v>
+        <v>1755.112937148122</v>
       </c>
       <c r="N53" t="n">
-        <v>1271.745849061017</v>
+        <v>1271.747839839546</v>
       </c>
       <c r="O53" t="n">
-        <v>-45.46449053423203</v>
+        <v>-45.4517223273233</v>
       </c>
       <c r="P53" t="n">
-        <v>18.79794095963702</v>
+        <v>18.81736743416452</v>
       </c>
       <c r="Q53" t="n">
-        <v>-81.20205904036297</v>
+        <v>-81.18263256583548</v>
       </c>
       <c r="R53" t="n">
-        <v>-19.47398560321286</v>
+        <v>-19.46063279094261</v>
       </c>
       <c r="S53" t="n">
-        <v>21.81872964265483</v>
+        <v>21.83081866030967</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -17179,52 +17183,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.346545696258545</v>
+        <v>1.346590995788574</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.4485245541018035</v>
+        <v>-0.4451755143596303</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2961119381085231</v>
+        <v>0.2994860283805467</v>
       </c>
       <c r="G63" t="n">
-        <v>1.69381903385486</v>
+        <v>1.697240144792223</v>
       </c>
       <c r="H63" t="n">
-        <v>7.179649799193122</v>
+        <v>7.183255460536886</v>
       </c>
       <c r="I63" t="n">
-        <v>51.95293536506068</v>
+        <v>51.96876117704838</v>
       </c>
       <c r="J63" t="n">
         <v>20.56534698593375</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5217646219276939</v>
+        <v>0.5226699895199916</v>
       </c>
       <c r="L63" t="n">
-        <v>1.34230329201733</v>
+        <v>1.342307606258285</v>
       </c>
       <c r="M63" t="n">
-        <v>1.334202527147415</v>
+        <v>1.334204303599573</v>
       </c>
       <c r="N63" t="n">
-        <v>1.302902274338335</v>
+        <v>1.302902725079927</v>
       </c>
       <c r="O63" t="n">
-        <v>-0.0005802061342636096</v>
+        <v>-0.0005773152240851659</v>
       </c>
       <c r="P63" t="n">
-        <v>44.38117163469313</v>
+        <v>44.44724583602122</v>
       </c>
       <c r="Q63" t="n">
-        <v>-55.61882836530687</v>
+        <v>-55.55275416397878</v>
       </c>
       <c r="R63" t="n">
-        <v>18.68529636084946</v>
+        <v>18.77284236865096</v>
       </c>
       <c r="S63" t="n">
-        <v>1.078448690421929</v>
+        <v>1.081849099509036</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -18863,52 +18867,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1471.5</v>
+        <v>1471</v>
       </c>
       <c r="E81" t="n">
-        <v>-7.476108060163533</v>
+        <v>-7.507546691471667</v>
       </c>
       <c r="F81" t="n">
-        <v>3.277649464588728</v>
+        <v>3.242556821209663</v>
       </c>
       <c r="G81" t="n">
-        <v>0.1974686410372239</v>
+        <v>0.1634226102383618</v>
       </c>
       <c r="H81" t="n">
-        <v>46.4179104477612</v>
+        <v>46.3681592039801</v>
       </c>
       <c r="I81" t="n">
-        <v>47.0777340603082</v>
+        <v>47.05986811946588</v>
       </c>
       <c r="J81" t="n">
         <v>27.29489222299879</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2190025275188947</v>
+        <v>0.2183696702775351</v>
       </c>
       <c r="L81" t="n">
-        <v>1566.843185047831</v>
+        <v>1566.795566000211</v>
       </c>
       <c r="M81" t="n">
-        <v>1439.721111738184</v>
+        <v>1439.701503895046</v>
       </c>
       <c r="N81" t="n">
-        <v>1368.793142748639</v>
+        <v>1368.78816762426</v>
       </c>
       <c r="O81" t="n">
-        <v>-43.22375899754395</v>
+        <v>-43.25566782945285</v>
       </c>
       <c r="P81" t="n">
-        <v>15.71324815222404</v>
+        <v>15.65290539475448</v>
       </c>
       <c r="Q81" t="n">
-        <v>-84.28675184777596</v>
+        <v>-84.34709460524552</v>
       </c>
       <c r="R81" t="n">
-        <v>-49.72420026568962</v>
+        <v>-49.76995730431268</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.06112635147643708</v>
+        <v>-0.09508451445588983</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -19323,52 +19327,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>98.81999969482422</v>
+        <v>98.81400299072266</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7339462098901794</v>
+        <v>0.7278333615773791</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.8329170279431808</v>
+        <v>-0.8389347941345937</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.6434741559819268</v>
+        <v>-0.6495034181544179</v>
       </c>
       <c r="H86" t="n">
-        <v>-7.272215466072107</v>
+        <v>-7.277842475660856</v>
       </c>
       <c r="I86" t="n">
-        <v>49.91194831290031</v>
+        <v>49.88154856848116</v>
       </c>
       <c r="J86" t="n">
         <v>18.97345570552778</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5639221123514799</v>
+        <v>0.5625210334990803</v>
       </c>
       <c r="L86" t="n">
-        <v>98.79140954764827</v>
+        <v>98.79083843297194</v>
       </c>
       <c r="M86" t="n">
-        <v>99.39048315254142</v>
+        <v>99.39024798767468</v>
       </c>
       <c r="N86" t="n">
-        <v>100.9678394482873</v>
+        <v>100.9677797795898</v>
       </c>
       <c r="O86" t="n">
-        <v>0.07549269778921093</v>
+        <v>0.07511000214284827</v>
       </c>
       <c r="P86" t="n">
-        <v>64.24359520112237</v>
+        <v>64.12578167624964</v>
       </c>
       <c r="Q86" t="n">
-        <v>-35.75640479887763</v>
+        <v>-35.87421832375037</v>
       </c>
       <c r="R86" t="n">
-        <v>7.349173803316109</v>
+        <v>7.177846743800149</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.1717326726072499</v>
+        <v>-0.1777905615162001</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -20083,52 +20087,52 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>77984</v>
+        <v>77989.5390625</v>
       </c>
       <c r="E94" t="n">
-        <v>5.588752152219478</v>
+        <v>5.59625193034663</v>
       </c>
       <c r="F94" t="n">
-        <v>14.9440010907181</v>
+        <v>14.95216535526009</v>
       </c>
       <c r="G94" t="n">
-        <v>-13.72908555502317</v>
+        <v>-13.72295788797553</v>
       </c>
       <c r="H94" t="n">
-        <v>-18.91450516165026</v>
+        <v>-18.90874580558038</v>
       </c>
       <c r="I94" t="n">
-        <v>46.62357884333346</v>
+        <v>46.62941190772215</v>
       </c>
       <c r="J94" t="n">
         <v>53.35674088539724</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5236082038757068</v>
+        <v>0.5237386362831515</v>
       </c>
       <c r="L94" t="n">
-        <v>77846.54053635502</v>
+        <v>77847.06806611693</v>
       </c>
       <c r="M94" t="n">
-        <v>86258.88351617246</v>
+        <v>86259.10073430972</v>
       </c>
       <c r="N94" t="n">
-        <v>68560.76792809997</v>
+        <v>68560.82304314972</v>
       </c>
       <c r="O94" t="n">
-        <v>1154.2846467864</v>
+        <v>1154.638136814884</v>
       </c>
       <c r="P94" t="n">
-        <v>53.3241934103233</v>
+        <v>53.34068528022687</v>
       </c>
       <c r="Q94" t="n">
-        <v>-46.6758065896767</v>
+        <v>-46.65931471977312</v>
       </c>
       <c r="R94" t="n">
-        <v>-2.0967491168449</v>
+        <v>-2.088931782954198</v>
       </c>
       <c r="S94" t="n">
-        <v>-13.7398955851932</v>
+        <v>-13.73376868596246</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -20827,52 +20831,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2326.219970703125</v>
+        <v>2328.590087890625</v>
       </c>
       <c r="E102" t="n">
-        <v>2.706632460574965</v>
+        <v>2.811277231031251</v>
       </c>
       <c r="F102" t="n">
-        <v>13.30565995733764</v>
+        <v>13.42110376552776</v>
       </c>
       <c r="G102" t="n">
-        <v>-22.25493083092078</v>
+        <v>-22.1757186639711</v>
       </c>
       <c r="H102" t="n">
-        <v>-12.65700193474307</v>
+        <v>-12.56801072001299</v>
       </c>
       <c r="I102" t="n">
-        <v>43.73988527897399</v>
+        <v>43.80219017260816</v>
       </c>
       <c r="J102" t="n">
         <v>39.58791687396969</v>
       </c>
       <c r="K102" t="n">
-        <v>0.4460328214542326</v>
+        <v>0.4471846191091856</v>
       </c>
       <c r="L102" t="n">
-        <v>2443.621747044112</v>
+        <v>2443.847472490541</v>
       </c>
       <c r="M102" t="n">
-        <v>2780.878046336457</v>
+        <v>2780.970992108516</v>
       </c>
       <c r="N102" t="n">
-        <v>2567.464983287915</v>
+        <v>2567.488566543513</v>
       </c>
       <c r="O102" t="n">
-        <v>31.90710717534927</v>
+        <v>32.05836251722974</v>
       </c>
       <c r="P102" t="n">
-        <v>37.65202618019774</v>
+        <v>37.80652913442218</v>
       </c>
       <c r="Q102" t="n">
-        <v>-62.34797381980226</v>
+        <v>-62.19347086557782</v>
       </c>
       <c r="R102" t="n">
-        <v>-12.37194609444037</v>
+        <v>-12.30085957334968</v>
       </c>
       <c r="S102" t="n">
-        <v>-24.01206562644249</v>
+        <v>-23.93464375251414</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -21015,52 +21019,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.435400009155273</v>
+        <v>1.437199950218201</v>
       </c>
       <c r="E104" t="n">
-        <v>2.921662059370389</v>
+        <v>3.050722199138955</v>
       </c>
       <c r="F104" t="n">
-        <v>3.647742179059565</v>
+        <v>3.777712797728827</v>
       </c>
       <c r="G104" t="n">
-        <v>-33.57603632843922</v>
+        <v>-33.49274301715857</v>
       </c>
       <c r="H104" t="n">
-        <v>-47.37932059803902</v>
+        <v>-47.31333611914073</v>
       </c>
       <c r="I104" t="n">
-        <v>37.81141542673841</v>
+        <v>37.89762998686645</v>
       </c>
       <c r="J104" t="n">
         <v>43.71256524006639</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3577127208031831</v>
+        <v>0.3591748416719711</v>
       </c>
       <c r="L104" t="n">
-        <v>1.61609089441769</v>
+        <v>1.616262317376064</v>
       </c>
       <c r="M104" t="n">
-        <v>1.890398170228543</v>
+        <v>1.890468756152579</v>
       </c>
       <c r="N104" t="n">
-        <v>1.419897481858458</v>
+        <v>1.41991539171978</v>
       </c>
       <c r="O104" t="n">
-        <v>0.01428568700100774</v>
+        <v>0.01440055503465321</v>
       </c>
       <c r="P104" t="n">
-        <v>33.84404717110214</v>
+        <v>34.04580015991653</v>
       </c>
       <c r="Q104" t="n">
-        <v>-66.15595282889785</v>
+        <v>-65.95419984008346</v>
       </c>
       <c r="R104" t="n">
-        <v>-26.82574834271536</v>
+        <v>-26.74799279635965</v>
       </c>
       <c r="S104" t="n">
-        <v>-29.75502072461781</v>
+        <v>-29.66693599432953</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -21074,7 +21078,7 @@
         </is>
       </c>
       <c r="W104" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="X104" t="n">
         <v>71.59999999999999</v>
@@ -21107,52 +21111,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>85.80000305175781</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="E105" t="n">
-        <v>2.654977279121118</v>
+        <v>2.714794047934843</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.3812290089082127</v>
+        <v>-0.3231814290263535</v>
       </c>
       <c r="G105" t="n">
-        <v>-35.76152501958118</v>
+        <v>-35.72409343946011</v>
       </c>
       <c r="H105" t="n">
-        <v>-54.47947382928919</v>
+        <v>-54.45294914570928</v>
       </c>
       <c r="I105" t="n">
-        <v>35.08578039780929</v>
+        <v>35.11991064863901</v>
       </c>
       <c r="J105" t="n">
         <v>61.92755203820978</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3285306669973538</v>
+        <v>0.3290436211629845</v>
       </c>
       <c r="L105" t="n">
-        <v>102.8302712326047</v>
+        <v>102.8350327014012</v>
       </c>
       <c r="M105" t="n">
-        <v>130.4902289412966</v>
+        <v>130.4921895460952</v>
       </c>
       <c r="N105" t="n">
-        <v>117.4811675943665</v>
+        <v>117.4816650612557</v>
       </c>
       <c r="O105" t="n">
-        <v>1.100384845201418</v>
+        <v>1.103575436258215</v>
       </c>
       <c r="P105" t="n">
-        <v>24.68505801484667</v>
+        <v>24.75719541077144</v>
       </c>
       <c r="Q105" t="n">
-        <v>-75.31494198515333</v>
+        <v>-75.24280458922856</v>
       </c>
       <c r="R105" t="n">
-        <v>-26.85735045976111</v>
+        <v>-26.83195357575975</v>
       </c>
       <c r="S105" t="n">
-        <v>-35.04603966045982</v>
+        <v>-35.00819116901648</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -22047,52 +22051,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.2486999928951263</v>
+        <v>0.2489999979734421</v>
       </c>
       <c r="E115" t="n">
-        <v>2.546550000583703</v>
+        <v>2.670251193357376</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.756204411854422</v>
+        <v>-0.6364873088453904</v>
       </c>
       <c r="G115" t="n">
-        <v>-40.19981676536041</v>
+        <v>-40.12768021864902</v>
       </c>
       <c r="H115" t="n">
-        <v>-67.78518455894587</v>
+        <v>-67.74632405027911</v>
       </c>
       <c r="I115" t="n">
-        <v>32.36501927002818</v>
+        <v>32.42173112074623</v>
       </c>
       <c r="J115" t="n">
         <v>50.19357591898496</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2855050224448236</v>
+        <v>0.2866418539301916</v>
       </c>
       <c r="L115" t="n">
-        <v>0.322255904914378</v>
+        <v>0.3222844768265986</v>
       </c>
       <c r="M115" t="n">
-        <v>0.4623867402340646</v>
+        <v>0.4623985051390966</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5560564364382705</v>
+        <v>0.5560594215634279</v>
       </c>
       <c r="O115" t="n">
-        <v>0.009862853970815683</v>
+        <v>0.00988199959404723</v>
       </c>
       <c r="P115" t="n">
-        <v>15.0306790981786</v>
+        <v>15.23143063263207</v>
       </c>
       <c r="Q115" t="n">
-        <v>-84.9693209018214</v>
+        <v>-84.76856936736793</v>
       </c>
       <c r="R115" t="n">
-        <v>-22.75983354964038</v>
+        <v>-22.72259407452991</v>
       </c>
       <c r="S115" t="n">
-        <v>-40.33266894782843</v>
+        <v>-40.26069265978428</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -22139,52 +22143,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.235000014305115</v>
+        <v>1.235999941825867</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.429558970169519</v>
+        <v>-0.3489409757679862</v>
       </c>
       <c r="F116" t="n">
-        <v>-12.50492057530593</v>
+        <v>-12.43407949284947</v>
       </c>
       <c r="G116" t="n">
-        <v>-44.33371472515233</v>
+        <v>-44.28864407739557</v>
       </c>
       <c r="H116" t="n">
-        <v>-74.69680167396915</v>
+        <v>-74.67631473949452</v>
       </c>
       <c r="I116" t="n">
-        <v>30.67419795812202</v>
+        <v>30.69032533681819</v>
       </c>
       <c r="J116" t="n">
         <v>39.87769041366358</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2436789550201171</v>
+        <v>0.24438021102285</v>
       </c>
       <c r="L116" t="n">
-        <v>1.672816136956734</v>
+        <v>1.672911368149187</v>
       </c>
       <c r="M116" t="n">
-        <v>2.65459090705638</v>
+        <v>2.654630119900331</v>
       </c>
       <c r="N116" t="n">
-        <v>5.831714067342209</v>
+        <v>5.831724016869779</v>
       </c>
       <c r="O116" t="n">
-        <v>0.05266346448988146</v>
+        <v>0.05272727752824302</v>
       </c>
       <c r="P116" t="n">
-        <v>11.16524766424063</v>
+        <v>11.2719017175524</v>
       </c>
       <c r="Q116" t="n">
-        <v>-88.83475233575938</v>
+        <v>-88.7280982824476</v>
       </c>
       <c r="R116" t="n">
-        <v>-27.53372905026585</v>
+        <v>-27.50810091411096</v>
       </c>
       <c r="S116" t="n">
-        <v>-40.9523458318747</v>
+        <v>-40.90453743207338</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22473,52 +22477,52 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4705.39990234375</v>
+        <v>4705.2001953125</v>
       </c>
       <c r="E2" t="n">
-        <v>1.24364840935105</v>
+        <v>1.239351416773093</v>
       </c>
       <c r="F2" t="n">
-        <v>11.54730863640774</v>
+        <v>11.54257433490009</v>
       </c>
       <c r="G2" t="n">
-        <v>93.91716061585618</v>
+        <v>93.90893036523799</v>
       </c>
       <c r="H2" t="n">
-        <v>172.2874815589483</v>
+        <v>172.2759251076972</v>
       </c>
       <c r="I2" t="n">
-        <v>75.55999689067148</v>
+        <v>75.55808848735455</v>
       </c>
       <c r="J2" t="n">
         <v>92.43498481484269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.842485120892047</v>
+        <v>0.8424330337628082</v>
       </c>
       <c r="L2" t="n">
-        <v>3759.917043401704</v>
+        <v>3759.898023684442</v>
       </c>
       <c r="M2" t="n">
-        <v>2937.043507723088</v>
+        <v>2937.035676074803</v>
       </c>
       <c r="N2" t="n">
-        <v>2266.462439236068</v>
+        <v>2266.459054371132</v>
       </c>
       <c r="O2" t="n">
-        <v>115.2535439445708</v>
+        <v>115.2407991083879</v>
       </c>
       <c r="P2" t="n">
-        <v>67.65094027485992</v>
+        <v>67.6436056557266</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32.34905972514008</v>
+        <v>-32.35639434427339</v>
       </c>
       <c r="R2" t="n">
-        <v>86.28335217775647</v>
+        <v>86.27889383030303</v>
       </c>
       <c r="S2" t="n">
-        <v>88.6839285513243</v>
+        <v>88.67592041004033</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -22569,52 +22573,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2016.099975585938</v>
+        <v>2016.300048828125</v>
       </c>
       <c r="E3" t="n">
-        <v>3.389742337740387</v>
+        <v>3.400002504006405</v>
       </c>
       <c r="F3" t="n">
-        <v>20.17047352106614</v>
+        <v>20.18239896947826</v>
       </c>
       <c r="G3" t="n">
-        <v>105.2636887120072</v>
+        <v>105.2840586203458</v>
       </c>
       <c r="H3" t="n">
-        <v>70.35065277447718</v>
+        <v>70.36755799139205</v>
       </c>
       <c r="I3" t="n">
-        <v>67.17668997064877</v>
+        <v>67.18036081442389</v>
       </c>
       <c r="J3" t="n">
         <v>68.41678221756783</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8217532606044605</v>
+        <v>0.8218440881550911</v>
       </c>
       <c r="L3" t="n">
-        <v>1555.135175431709</v>
+        <v>1555.154230026203</v>
       </c>
       <c r="M3" t="n">
-        <v>1260.742176672679</v>
+        <v>1260.750022682176</v>
       </c>
       <c r="N3" t="n">
-        <v>1105.768945130108</v>
+        <v>1105.77233620201</v>
       </c>
       <c r="O3" t="n">
-        <v>84.57081143445734</v>
+        <v>84.58357964136624</v>
       </c>
       <c r="P3" t="n">
-        <v>57.5029235093824</v>
+        <v>57.51309034977653</v>
       </c>
       <c r="Q3" t="n">
-        <v>-42.4970764906176</v>
+        <v>-42.48690965022347</v>
       </c>
       <c r="R3" t="n">
-        <v>116.3113828962836</v>
+        <v>116.3225062998556</v>
       </c>
       <c r="S3" t="n">
-        <v>117.2989870782165</v>
+        <v>117.320551342586</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -22665,52 +22669,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>75.37999725341797</v>
+        <v>75.40000152587891</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9238114733668867</v>
+        <v>0.9505945391147241</v>
       </c>
       <c r="F4" t="n">
-        <v>33.5435609158085</v>
+        <v>33.57900057984804</v>
       </c>
       <c r="G4" t="n">
-        <v>161.9361928319004</v>
+        <v>162.0057052113076</v>
       </c>
       <c r="H4" t="n">
-        <v>185.508658562205</v>
+        <v>185.5844265802992</v>
       </c>
       <c r="I4" t="n">
-        <v>70.88414066502712</v>
+        <v>70.89234862618019</v>
       </c>
       <c r="J4" t="n">
         <v>61.80579865011009</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8533736320181183</v>
+        <v>0.8535844692367101</v>
       </c>
       <c r="L4" t="n">
-        <v>52.94139402999487</v>
+        <v>52.94329919880068</v>
       </c>
       <c r="M4" t="n">
-        <v>38.67411272742319</v>
+        <v>38.67489720869617</v>
       </c>
       <c r="N4" t="n">
-        <v>29.25802455342868</v>
+        <v>29.25836360889413</v>
       </c>
       <c r="O4" t="n">
-        <v>4.115062306626227</v>
+        <v>4.116338932561058</v>
       </c>
       <c r="P4" t="n">
-        <v>50.6183417274925</v>
+        <v>50.63985401019983</v>
       </c>
       <c r="Q4" t="n">
-        <v>-49.3816582725075</v>
+        <v>-49.36014598980017</v>
       </c>
       <c r="R4" t="n">
-        <v>128.3147728610845</v>
+        <v>128.3401504186747</v>
       </c>
       <c r="S4" t="n">
-        <v>162.3646754078567</v>
+        <v>162.4343014975651</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -23957,52 +23961,52 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.013999938964844</v>
+        <v>6.021999835968018</v>
       </c>
       <c r="E18" t="n">
-        <v>7.633106690253499</v>
+        <v>7.776281578246902</v>
       </c>
       <c r="F18" t="n">
-        <v>15.97723981961201</v>
+        <v>16.13151417656005</v>
       </c>
       <c r="G18" t="n">
-        <v>44.56731152781381</v>
+        <v>44.75961675128999</v>
       </c>
       <c r="H18" t="n">
-        <v>46.87995710620116</v>
+        <v>47.07533863939128</v>
       </c>
       <c r="I18" t="n">
-        <v>65.78920953257676</v>
+        <v>65.85966854010542</v>
       </c>
       <c r="J18" t="n">
         <v>53.34789996467301</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9348535121808438</v>
+        <v>0.93731346849797</v>
       </c>
       <c r="L18" t="n">
-        <v>5.057142813639588</v>
+        <v>5.057904708592272</v>
       </c>
       <c r="M18" t="n">
-        <v>4.481990182069698</v>
+        <v>4.482303903520802</v>
       </c>
       <c r="N18" t="n">
-        <v>3.807719090009125</v>
+        <v>3.807854681483755</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1148640463591136</v>
+        <v>0.1153745810966392</v>
       </c>
       <c r="P18" t="n">
-        <v>79.49782390490726</v>
+        <v>79.82983870457035</v>
       </c>
       <c r="Q18" t="n">
-        <v>-20.50217609509274</v>
+        <v>-20.17016129542965</v>
       </c>
       <c r="R18" t="n">
-        <v>124.0050188627805</v>
+        <v>124.2888534542797</v>
       </c>
       <c r="S18" t="n">
-        <v>45.09046964146333</v>
+        <v>45.28347077632426</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -27427,66 +27431,66 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>255.0800018310547</v>
+        <v>106.3099975585938</v>
       </c>
       <c r="E56" t="n">
-        <v>22.47563095901051</v>
+        <v>-10.17321594487394</v>
       </c>
       <c r="F56" t="n">
-        <v>9.373124301489376</v>
+        <v>68.21201942284476</v>
       </c>
       <c r="G56" t="n">
-        <v>36.42101169087022</v>
+        <v>31.70217536038302</v>
       </c>
       <c r="H56" t="n">
-        <v>64.94392206425452</v>
+        <v>60.75911382727157</v>
       </c>
       <c r="I56" t="n">
-        <v>62.92456550332555</v>
+        <v>65.00310752322562</v>
       </c>
       <c r="J56" t="n">
-        <v>13.65055413465318</v>
+        <v>16.10599589638658</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9549815854662987</v>
+        <v>1.077703114924796</v>
       </c>
       <c r="L56" t="n">
-        <v>214.6639378795472</v>
+        <v>78.4598087451072</v>
       </c>
       <c r="M56" t="n">
-        <v>183.4627893815327</v>
+        <v>77.18588945964973</v>
       </c>
       <c r="N56" t="n">
-        <v>127.480833899757</v>
+        <v>71.44769715473507</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.126357538556324</v>
+        <v>4.788295119040685</v>
       </c>
       <c r="P56" t="n">
-        <v>96.1913493744069</v>
+        <v>78.54449515006372</v>
       </c>
       <c r="Q56" t="n">
-        <v>-3.808650625593097</v>
+        <v>-21.45550484993628</v>
       </c>
       <c r="R56" t="n">
-        <v>52.41063678735669</v>
+        <v>188.8115690294602</v>
       </c>
       <c r="S56" t="n">
-        <v>42.90196181011468</v>
+        <v>34.91115918963441</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -27495,15 +27499,19 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W56" t="n">
-        <v>73.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="X56" t="n">
-        <v>76.5</v>
+        <v>84.3</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -27512,19 +27520,19 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 14); RSI in forza (63) — momentum positivo; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (258.79)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); RSI in forza (65) — momentum positivo; doji — indecisione del mercato; favorito dal quadrante macro (Stagflazione)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -27533,65 +27541,69 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>187.6000061035156</v>
+        <v>255.0800018310547</v>
       </c>
       <c r="E57" t="n">
-        <v>-9.328172238915034</v>
+        <v>22.47563095901051</v>
       </c>
       <c r="F57" t="n">
-        <v>24.13154240879054</v>
+        <v>9.373124301489376</v>
       </c>
       <c r="G57" t="n">
-        <v>16.90658981518865</v>
+        <v>36.42101169087022</v>
       </c>
       <c r="H57" t="n">
-        <v>87.60000610351561</v>
+        <v>64.94392206425452</v>
       </c>
       <c r="I57" t="n">
-        <v>59.73765559503357</v>
+        <v>62.92456550332555</v>
       </c>
       <c r="J57" t="n">
-        <v>19.62628180651337</v>
+        <v>13.65055413465318</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8930101795376867</v>
+        <v>0.9549815854662987</v>
       </c>
       <c r="L57" t="n">
-        <v>164.9002285910118</v>
+        <v>214.6639378795472</v>
       </c>
       <c r="M57" t="n">
-        <v>153.4169062027084</v>
+        <v>183.4627893815327</v>
       </c>
       <c r="N57" t="n">
-        <v>135.7044086107842</v>
+        <v>127.480833899757</v>
       </c>
       <c r="O57" t="n">
-        <v>4.859897286472398</v>
+        <v>-1.126357538556324</v>
       </c>
       <c r="P57" t="n">
-        <v>67.20697204912196</v>
+        <v>96.1913493744069</v>
       </c>
       <c r="Q57" t="n">
-        <v>-32.79302795087804</v>
+        <v>-3.808650625593097</v>
       </c>
       <c r="R57" t="n">
-        <v>209.7963547107595</v>
+        <v>52.41063678735669</v>
       </c>
       <c r="S57" t="n">
-        <v>26.79960119846729</v>
+        <v>42.90196181011468</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="X57" t="n">
-        <v>73.7</v>
+        <v>76.5</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -27600,73 +27612,73 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 14); RSI in forza (63) — momentum positivo; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (258.79)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>159.7010040283203</v>
+        <v>187.6000061035156</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.08758665589851944</v>
+        <v>-9.328172238915034</v>
       </c>
       <c r="F58" t="n">
-        <v>2.186409050843241</v>
+        <v>24.13154240879054</v>
       </c>
       <c r="G58" t="n">
-        <v>4.60536185478595</v>
+        <v>16.90658981518865</v>
       </c>
       <c r="H58" t="n">
-        <v>50.12456154594018</v>
+        <v>87.60000610351561</v>
       </c>
       <c r="I58" t="n">
-        <v>61.40295346179372</v>
+        <v>59.73765559503357</v>
       </c>
       <c r="J58" t="n">
-        <v>19.38458414734579</v>
+        <v>19.62628180651337</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8810905071628335</v>
+        <v>0.8930101795376867</v>
       </c>
       <c r="L58" t="n">
-        <v>152.2322007828246</v>
+        <v>164.9002285910118</v>
       </c>
       <c r="M58" t="n">
-        <v>144.0925966740128</v>
+        <v>153.4169062027084</v>
       </c>
       <c r="N58" t="n">
-        <v>129.4370545060583</v>
+        <v>135.7044086107842</v>
       </c>
       <c r="O58" t="n">
-        <v>0.5621404182447947</v>
+        <v>4.859897286472398</v>
       </c>
       <c r="P58" t="n">
-        <v>97.39417541864319</v>
+        <v>67.20697204912196</v>
       </c>
       <c r="Q58" t="n">
-        <v>-2.605824581356808</v>
+        <v>-32.79302795087804</v>
       </c>
       <c r="R58" t="n">
-        <v>123.7304995275291</v>
+        <v>209.7963547107595</v>
       </c>
       <c r="S58" t="n">
-        <v>10.22224080410206</v>
+        <v>26.79960119846729</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -27674,16 +27686,12 @@
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar</t>
-        </is>
-      </c>
+      <c r="V58" t="inlineStr"/>
       <c r="W58" t="n">
-        <v>73.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="X58" t="n">
-        <v>75.7</v>
+        <v>73.7</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -27692,94 +27700,90 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (61) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (160.23)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>105.9499969482422</v>
+        <v>159.7039947509766</v>
       </c>
       <c r="E59" t="n">
-        <v>-10.47739897401887</v>
+        <v>-0.08571559491147296</v>
       </c>
       <c r="F59" t="n">
-        <v>67.64239821081044</v>
+        <v>2.188322696975686</v>
       </c>
       <c r="G59" t="n">
-        <v>31.25618848611717</v>
+        <v>4.607320800677162</v>
       </c>
       <c r="H59" t="n">
-        <v>60.21473060437197</v>
+        <v>50.12737293044089</v>
       </c>
       <c r="I59" t="n">
-        <v>64.77322890740928</v>
+        <v>61.40715268314162</v>
       </c>
       <c r="J59" t="n">
-        <v>16.10599589638658</v>
+        <v>19.38458414734579</v>
       </c>
       <c r="K59" t="n">
-        <v>1.073400729188607</v>
+        <v>0.8812043137949481</v>
       </c>
       <c r="L59" t="n">
-        <v>78.42552297269276</v>
+        <v>152.2324856135537</v>
       </c>
       <c r="M59" t="n">
-        <v>77.17177178865555</v>
+        <v>144.0927139572542</v>
       </c>
       <c r="N59" t="n">
-        <v>71.44159544947487</v>
+        <v>129.437097849865</v>
       </c>
       <c r="O59" t="n">
-        <v>4.765320721115108</v>
+        <v>0.5623312791778434</v>
       </c>
       <c r="P59" t="n">
-        <v>77.95442696821428</v>
+        <v>97.40887978951743</v>
       </c>
       <c r="Q59" t="n">
-        <v>-22.04557303178573</v>
+        <v>-2.591120210482566</v>
       </c>
       <c r="R59" t="n">
-        <v>188.1633284875432</v>
+        <v>123.7440052557841</v>
       </c>
       <c r="S59" t="n">
-        <v>34.45430564089138</v>
+        <v>10.22430493735409</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W59" t="n">
-        <v>72.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="X59" t="n">
-        <v>83.3</v>
+        <v>75.7</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -27788,7 +27792,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); RSI in forza (65) — momentum positivo; doji — indecisione del mercato; favorito dal quadrante macro (Stagflazione)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (61) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (160.23)</t>
         </is>
       </c>
     </row>
@@ -27897,52 +27901,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>96.58000183105469</v>
+        <v>96.87999725341797</v>
       </c>
       <c r="E61" t="n">
-        <v>-4.734657281914112</v>
+        <v>-4.438745434911995</v>
       </c>
       <c r="F61" t="n">
-        <v>64.9530368736917</v>
+        <v>65.46541164102284</v>
       </c>
       <c r="G61" t="n">
-        <v>23.96354420661546</v>
+        <v>24.34859799722282</v>
       </c>
       <c r="H61" t="n">
-        <v>57.04065338382875</v>
+        <v>57.52845081856582</v>
       </c>
       <c r="I61" t="n">
-        <v>65.6297415939008</v>
+        <v>65.86742985864549</v>
       </c>
       <c r="J61" t="n">
         <v>13.82316078082327</v>
       </c>
       <c r="K61" t="n">
-        <v>1.111981457028275</v>
+        <v>1.116167662605136</v>
       </c>
       <c r="L61" t="n">
-        <v>72.52435628619564</v>
+        <v>72.55292727880166</v>
       </c>
       <c r="M61" t="n">
-        <v>71.99299292062291</v>
+        <v>72.0047574469901</v>
       </c>
       <c r="N61" t="n">
-        <v>66.87676509972745</v>
+        <v>66.88184976790309</v>
       </c>
       <c r="O61" t="n">
-        <v>3.845312370648817</v>
+        <v>3.864457377660046</v>
       </c>
       <c r="P61" t="n">
-        <v>64.49612376509533</v>
+        <v>64.96123291954615</v>
       </c>
       <c r="Q61" t="n">
-        <v>-35.50387623490467</v>
+        <v>-35.03876708045385</v>
       </c>
       <c r="R61" t="n">
-        <v>202.1864011256831</v>
+        <v>202.7450756476517</v>
       </c>
       <c r="S61" t="n">
-        <v>31.31202967196405</v>
+        <v>31.71990922317518</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -28687,7 +28691,7 @@
         <v>68.3</v>
       </c>
       <c r="X69" t="n">
-        <v>87.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -29365,52 +29369,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1471.5</v>
+        <v>1471</v>
       </c>
       <c r="E77" t="n">
-        <v>0.02039483673759168</v>
+        <v>-0.01359102627183084</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1974686410372239</v>
+        <v>0.1634226102383618</v>
       </c>
       <c r="G77" t="n">
-        <v>59.49490992187157</v>
+        <v>59.4407152531927</v>
       </c>
       <c r="H77" t="n">
-        <v>-36.30146150407359</v>
+        <v>-36.32310558783027</v>
       </c>
       <c r="I77" t="n">
-        <v>55.23745339744062</v>
+        <v>55.22166244806256</v>
       </c>
       <c r="J77" t="n">
         <v>50.9561631164703</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7182811051501908</v>
+        <v>0.7178797939688665</v>
       </c>
       <c r="L77" t="n">
-        <v>1336.111355483811</v>
+        <v>1336.063736436192</v>
       </c>
       <c r="M77" t="n">
-        <v>1369.827698929935</v>
+        <v>1369.808091086798</v>
       </c>
       <c r="N77" t="n">
-        <v>1349.486304279362</v>
+        <v>1349.477829703091</v>
       </c>
       <c r="O77" t="n">
-        <v>66.95836992945976</v>
+        <v>66.92646109755086</v>
       </c>
       <c r="P77" t="n">
-        <v>45.99861270427996</v>
+        <v>45.95995191186397</v>
       </c>
       <c r="Q77" t="n">
-        <v>-54.00138729572004</v>
+        <v>-54.04004808813603</v>
       </c>
       <c r="R77" t="n">
-        <v>77.83665196299293</v>
+        <v>77.79281506144999</v>
       </c>
       <c r="S77" t="n">
-        <v>53.10582014143696</v>
+        <v>53.05379641729784</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -29557,52 +29561,52 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.435400009155273</v>
+        <v>1.437199950218201</v>
       </c>
       <c r="E79" t="n">
-        <v>7.098706766853091</v>
+        <v>7.233004773587481</v>
       </c>
       <c r="F79" t="n">
-        <v>-33.57603632843922</v>
+        <v>-33.49274301715857</v>
       </c>
       <c r="G79" t="n">
-        <v>130.0545502709745</v>
+        <v>130.3430305754923</v>
       </c>
       <c r="H79" t="n">
-        <v>245.9187021205569</v>
+        <v>246.352471991262</v>
       </c>
       <c r="I79" t="n">
-        <v>46.39784993687425</v>
+        <v>46.42702618655936</v>
       </c>
       <c r="J79" t="n">
         <v>49.98060633402685</v>
       </c>
       <c r="K79" t="n">
-        <v>0.2990179805502031</v>
+        <v>0.2996061183408909</v>
       </c>
       <c r="L79" t="n">
-        <v>1.762918928307223</v>
+        <v>1.763090351265597</v>
       </c>
       <c r="M79" t="n">
-        <v>1.360531971261543</v>
+        <v>1.36060396890406</v>
       </c>
       <c r="N79" t="n">
-        <v>1.075428187678744</v>
+        <v>1.075464921169824</v>
       </c>
       <c r="O79" t="n">
-        <v>-0.1741466774027312</v>
+        <v>-0.1740318093690857</v>
       </c>
       <c r="P79" t="n">
-        <v>11.99721788925251</v>
+        <v>12.06873636203969</v>
       </c>
       <c r="Q79" t="n">
-        <v>-88.00278211074749</v>
+        <v>-87.93126363796031</v>
       </c>
       <c r="R79" t="n">
-        <v>-45.54876878457257</v>
+        <v>-45.50765535274312</v>
       </c>
       <c r="S79" t="n">
-        <v>153.4640626887928</v>
+        <v>153.7818976975012</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -29615,7 +29619,7 @@
         <v>61.3</v>
       </c>
       <c r="X79" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -29779,7 +29783,7 @@
         <v>2.285124380319148</v>
       </c>
       <c r="R81" t="n">
-        <v>66.93150196375541</v>
+        <v>63.23428322243683</v>
       </c>
       <c r="S81" t="n">
         <v>13.927498342446</v>
@@ -30105,52 +30109,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1.346545696258545</v>
+        <v>1.346590995788574</v>
       </c>
       <c r="E85" t="n">
-        <v>2.221672003247743</v>
+        <v>2.225110871838254</v>
       </c>
       <c r="F85" t="n">
-        <v>1.69381903385486</v>
+        <v>1.697240144792223</v>
       </c>
       <c r="G85" t="n">
-        <v>4.895903136129753</v>
+        <v>4.899431969296919</v>
       </c>
       <c r="H85" t="n">
-        <v>-3.874140597010101</v>
+        <v>-3.870906799399876</v>
       </c>
       <c r="I85" t="n">
-        <v>54.87132244777467</v>
+        <v>54.87723714436931</v>
       </c>
       <c r="J85" t="n">
         <v>21.65217664783298</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6622163110508387</v>
+        <v>0.6624826202997071</v>
       </c>
       <c r="L85" t="n">
-        <v>1.323290692779642</v>
+        <v>1.323295007020597</v>
       </c>
       <c r="M85" t="n">
-        <v>1.304221407834189</v>
+        <v>1.304223184286347</v>
       </c>
       <c r="N85" t="n">
-        <v>1.345124427646793</v>
+        <v>1.345125084161721</v>
       </c>
       <c r="O85" t="n">
-        <v>-6.300037372937786e-05</v>
+        <v>-6.010946355093638e-05</v>
       </c>
       <c r="P85" t="n">
-        <v>69.79203753353738</v>
+        <v>69.82792406787088</v>
       </c>
       <c r="Q85" t="n">
-        <v>-30.20796246646262</v>
+        <v>-30.17207593212912</v>
       </c>
       <c r="R85" t="n">
-        <v>41.32949905361538</v>
+        <v>41.35426252014096</v>
       </c>
       <c r="S85" t="n">
-        <v>2.27283551137758</v>
+        <v>2.276276101174335</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -30193,52 +30197,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>77984</v>
+        <v>77989.5390625</v>
       </c>
       <c r="E86" t="n">
-        <v>14.2902156479652</v>
+        <v>14.29833347530944</v>
       </c>
       <c r="F86" t="n">
-        <v>-13.72908555502317</v>
+        <v>-13.72295788797553</v>
       </c>
       <c r="G86" t="n">
-        <v>20.68230442167</v>
+        <v>20.69087626752091</v>
       </c>
       <c r="H86" t="n">
-        <v>72.76883818109296</v>
+        <v>72.78110963924769</v>
       </c>
       <c r="I86" t="n">
-        <v>49.38967118925057</v>
+        <v>49.39228680533802</v>
       </c>
       <c r="J86" t="n">
         <v>33.80484147146453</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3053373688496108</v>
+        <v>0.3054145894168231</v>
       </c>
       <c r="L86" t="n">
-        <v>83085.3881895946</v>
+        <v>83085.9157193565</v>
       </c>
       <c r="M86" t="n">
-        <v>66675.34648353454</v>
+        <v>66675.56804603455</v>
       </c>
       <c r="N86" t="n">
-        <v>49323.88603403579</v>
+        <v>49323.99907612763</v>
       </c>
       <c r="O86" t="n">
-        <v>-5640.348204655376</v>
+        <v>-5639.994714626881</v>
       </c>
       <c r="P86" t="n">
-        <v>27.08522298645239</v>
+        <v>27.09359978402276</v>
       </c>
       <c r="Q86" t="n">
-        <v>-72.91477701354761</v>
+        <v>-72.90640021597723</v>
       </c>
       <c r="R86" t="n">
-        <v>-43.08210346123076</v>
+        <v>-43.0776726682994</v>
       </c>
       <c r="S86" t="n">
-        <v>32.24374141097146</v>
+        <v>32.25313444478493</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -31099,52 +31103,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2326.219970703125</v>
+        <v>2328.590087890625</v>
       </c>
       <c r="E96" t="n">
-        <v>10.52458071300104</v>
+        <v>10.63719096125282</v>
       </c>
       <c r="F96" t="n">
-        <v>-22.25493083092078</v>
+        <v>-22.1757186639711</v>
       </c>
       <c r="G96" t="n">
-        <v>-28.00968343426603</v>
+        <v>-27.9363346156784</v>
       </c>
       <c r="H96" t="n">
-        <v>64.27539248429757</v>
+        <v>64.4427678555496</v>
       </c>
       <c r="I96" t="n">
-        <v>46.14582702507994</v>
+        <v>46.16827413685184</v>
       </c>
       <c r="J96" t="n">
         <v>14.24892668051552</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3297677937600152</v>
+        <v>0.3304671442883174</v>
       </c>
       <c r="L96" t="n">
-        <v>2760.705221208311</v>
+        <v>2760.930946654739</v>
       </c>
       <c r="M96" t="n">
-        <v>2511.34928295289</v>
+        <v>2511.444087640389</v>
       </c>
       <c r="N96" t="n">
-        <v>2059.847988951689</v>
+        <v>2059.89635869021</v>
       </c>
       <c r="O96" t="n">
-        <v>-154.4891367952573</v>
+        <v>-154.3378814533772</v>
       </c>
       <c r="P96" t="n">
-        <v>26.33692581053185</v>
+        <v>26.40337272144864</v>
       </c>
       <c r="Q96" t="n">
-        <v>-73.66307418946815</v>
+        <v>-73.59662727855137</v>
       </c>
       <c r="R96" t="n">
-        <v>-69.39449605650846</v>
+        <v>-69.31298988267595</v>
       </c>
       <c r="S96" t="n">
-        <v>-7.447055380349477</v>
+        <v>-7.352755904135078</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -31154,7 +31158,7 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="X96" t="n">
         <v>64.2</v>
@@ -31187,52 +31191,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>98.81999969482422</v>
+        <v>98.81400299072266</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.140455582322553</v>
+        <v>-1.146454686120557</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.6434741559819268</v>
+        <v>-0.6495034181544179</v>
       </c>
       <c r="G97" t="n">
-        <v>-5.07204501122972</v>
+        <v>-5.077805533986169</v>
       </c>
       <c r="H97" t="n">
-        <v>8.677003588659771</v>
+        <v>8.670408730987456</v>
       </c>
       <c r="I97" t="n">
-        <v>45.44217860270738</v>
+        <v>45.43027834323288</v>
       </c>
       <c r="J97" t="n">
         <v>28.5699342843782</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3547321343339674</v>
+        <v>0.3543708290425597</v>
       </c>
       <c r="L97" t="n">
-        <v>100.289805698223</v>
+        <v>100.2892345835467</v>
       </c>
       <c r="M97" t="n">
-        <v>100.9220092255089</v>
+        <v>100.9217740606422</v>
       </c>
       <c r="N97" t="n">
-        <v>99.52923559294915</v>
+        <v>99.52913395389658</v>
       </c>
       <c r="O97" t="n">
-        <v>-0.1954476014595103</v>
+        <v>-0.1958302971058732</v>
       </c>
       <c r="P97" t="n">
-        <v>27.22729507665608</v>
+        <v>27.17736412874308</v>
       </c>
       <c r="Q97" t="n">
-        <v>-72.77270492334392</v>
+        <v>-72.82263587125692</v>
       </c>
       <c r="R97" t="n">
-        <v>-42.06031618104782</v>
+        <v>-42.09558438194849</v>
       </c>
       <c r="S97" t="n">
-        <v>-2.831855791385796</v>
+        <v>-2.837752255772719</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31739,52 +31743,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>85.80000305175781</v>
+        <v>85.84999847412109</v>
       </c>
       <c r="E103" t="n">
-        <v>3.241074715434689</v>
+        <v>3.30123300158911</v>
       </c>
       <c r="F103" t="n">
-        <v>-35.76152501958118</v>
+        <v>-35.72409343946011</v>
       </c>
       <c r="G103" t="n">
-        <v>-50.06580794133701</v>
+        <v>-50.03671142696003</v>
       </c>
       <c r="H103" t="n">
-        <v>555.4999282335172</v>
+        <v>555.8818862126021</v>
       </c>
       <c r="I103" t="n">
-        <v>42.32490960945398</v>
+        <v>42.33417041384887</v>
       </c>
       <c r="J103" t="n">
         <v>32.80032248447666</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1247279232522633</v>
+        <v>0.1249537856907138</v>
       </c>
       <c r="L103" t="n">
-        <v>132.3976653582657</v>
+        <v>132.4024268270622</v>
       </c>
       <c r="M103" t="n">
-        <v>123.8117791209574</v>
+        <v>123.8144815762203</v>
       </c>
       <c r="N103" t="n">
-        <v>96.99375715270072</v>
+        <v>96.99514591443304</v>
       </c>
       <c r="O103" t="n">
-        <v>-14.86159507593995</v>
+        <v>-14.85840448488314</v>
       </c>
       <c r="P103" t="n">
-        <v>9.2718202249198</v>
+        <v>9.298915359397753</v>
       </c>
       <c r="Q103" t="n">
-        <v>-90.72817977508021</v>
+        <v>-90.70108464060225</v>
       </c>
       <c r="R103" t="n">
-        <v>-97.80925477426443</v>
+        <v>-97.78963365577775</v>
       </c>
       <c r="S103" t="n">
-        <v>-49.05895221588102</v>
+        <v>-49.02926900948232</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -32015,52 +32019,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.2486999928951263</v>
+        <v>0.2489999979734421</v>
       </c>
       <c r="E106" t="n">
-        <v>2.954502736687936</v>
+        <v>3.07869604002069</v>
       </c>
       <c r="F106" t="n">
-        <v>-40.19981676536041</v>
+        <v>-40.12768021864902</v>
       </c>
       <c r="G106" t="n">
-        <v>-36.02950910831589</v>
+        <v>-35.95234194837171</v>
       </c>
       <c r="H106" t="n">
-        <v>-80.98709635850267</v>
+        <v>-80.96416122457052</v>
       </c>
       <c r="I106" t="n">
-        <v>39.48447979299285</v>
+        <v>39.49800551865223</v>
       </c>
       <c r="J106" t="n">
         <v>29.80750264091312</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1699735180971987</v>
+        <v>0.1702301843703743</v>
       </c>
       <c r="L106" t="n">
-        <v>0.4871927917150218</v>
+        <v>0.4872213636272424</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5335897983377687</v>
+        <v>0.5336017985409013</v>
       </c>
       <c r="N106" t="n">
-        <v>0.5090743513687783</v>
+        <v>0.509080473921397</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.05469933624549636</v>
+        <v>-0.05468019062226485</v>
       </c>
       <c r="P106" t="n">
-        <v>2.473706187543452</v>
+        <v>2.506745301058727</v>
       </c>
       <c r="Q106" t="n">
-        <v>-97.52629381245654</v>
+        <v>-97.49325469894127</v>
       </c>
       <c r="R106" t="n">
-        <v>-102.6004514988219</v>
+        <v>-102.5748049927999</v>
       </c>
       <c r="S106" t="n">
-        <v>-27.98651891726765</v>
+        <v>-27.89964955398172</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -32354,7 +32358,7 @@
         </is>
       </c>
       <c r="W109" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="X109" t="n">
         <v>74.8</v>
@@ -33027,52 +33031,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1.235000014305115</v>
+        <v>1.235999941825867</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.327882202231567</v>
+        <v>-1.247991542333571</v>
       </c>
       <c r="F117" t="n">
-        <v>-44.33371472515233</v>
+        <v>-44.28864407739557</v>
       </c>
       <c r="G117" t="n">
-        <v>-77.06732979418189</v>
+        <v>-77.04876217653209</v>
       </c>
       <c r="H117" t="n">
-        <v>-96.32519850303197</v>
+        <v>-96.32222317096108</v>
       </c>
       <c r="I117" t="n">
-        <v>35.30708939798467</v>
+        <v>35.31021235038629</v>
       </c>
       <c r="J117" t="n">
         <v>25.5772157418073</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1815952279135867</v>
+        <v>0.181705723977823</v>
       </c>
       <c r="L117" t="n">
-        <v>3.425224469559719</v>
+        <v>3.425319700752172</v>
       </c>
       <c r="M117" t="n">
-        <v>4.826951096628476</v>
+        <v>4.827008235343948</v>
       </c>
       <c r="N117" t="n">
-        <v>6.781627045858009</v>
+        <v>6.781656455490972</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.1105947549602722</v>
+        <v>-0.1105309419219112</v>
       </c>
       <c r="P117" t="n">
-        <v>2.471239589319516</v>
+        <v>2.494845668363295</v>
       </c>
       <c r="Q117" t="n">
-        <v>-97.52876041068049</v>
+        <v>-97.5051543316367</v>
       </c>
       <c r="R117" t="n">
-        <v>-86.44297523452234</v>
+        <v>-86.43323545322041</v>
       </c>
       <c r="S117" t="n">
-        <v>-86.22768923972298</v>
+        <v>-86.21653837948489</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -33356,7 +33360,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23/04/2026 20:39:48</t>
+          <t>23/04/2026 20:47:08</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33396,13 +33400,13 @@
         <v>19.30999946594238</v>
       </c>
       <c r="N2" t="n">
-        <v>98.81999969482422</v>
+        <v>98.81400299072266</v>
       </c>
       <c r="O2" t="n">
-        <v>4705.39990234375</v>
+        <v>4705.2001953125</v>
       </c>
       <c r="P2" t="n">
-        <v>96.58000183105469</v>
+        <v>96.87999725341797</v>
       </c>
       <c r="Q2" t="n">
         <v>2.787751808934846</v>
@@ -33419,7 +33423,7 @@
         <v>2.30287058551863</v>
       </c>
       <c r="U2" t="n">
-        <v>2.831622076043044</v>
+        <v>2.866040961520563</v>
       </c>
       <c r="V2" t="n">
         <v>0.008443311100047646</v>
@@ -33443,10 +33447,10 @@
         <v>-0.09933745989944809</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.6619492385047592</v>
+        <v>0.6619211439920709</v>
       </c>
       <c r="AD2" t="n">
-        <v>-8.006460690483831</v>
+        <v>-8.010365089049509</v>
       </c>
       <c r="AE2" t="n">
         <v>1.215636666136732</v>
@@ -33470,7 +33474,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.216706788968712</v>
+        <v>1.222443269881632</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33569,10 +33573,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79.89203854716712</v>
+        <v>79.89254221614779</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1991298177487536</v>
+        <v>0.1991499645079799</v>
       </c>
       <c r="D2" t="n">
         <v>69.82758620689656</v>
@@ -33754,22 +33758,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>DAX</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>CAC40</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>FTSEMIB</t>
-        </is>
-      </c>
       <c r="C8" t="n">
-        <v>0.946</v>
+        <v>0.944</v>
       </c>
       <c r="D8" t="n">
         <v>0.945</v>
       </c>
       <c r="E8" t="n">
-        <v>0.903</v>
+        <v>0.895</v>
       </c>
     </row>
     <row r="9">
@@ -33784,7 +33788,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.946</v>
+        <v>0.947</v>
       </c>
       <c r="D9" t="n">
         <v>0.945</v>
@@ -33796,22 +33800,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>FTSEMIB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.944</v>
+        <v>0.946</v>
       </c>
       <c r="D10" t="n">
         <v>0.945</v>
       </c>
       <c r="E10" t="n">
-        <v>0.895</v>
+        <v>0.903</v>
       </c>
     </row>
     <row r="11">
@@ -33868,7 +33872,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.918</v>
+        <v>0.919</v>
       </c>
       <c r="D13" t="n">
         <v>0.9409999999999999</v>
@@ -33955,7 +33959,7 @@
         <v>0.951</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="E17" t="n">
         <v>0.952</v>
@@ -34036,7 +34040,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.876</v>
+        <v>0.877</v>
       </c>
       <c r="D21" t="n">
         <v>0.9340000000000001</v>
@@ -34104,7 +34108,7 @@
         <v>-0.853</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6929999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -34161,7 +34165,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.87</v>
+        <v>-0.871</v>
       </c>
       <c r="D5" t="n">
         <v>-0.803</v>
@@ -34182,7 +34186,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>-0.797</v>
@@ -34203,13 +34207,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.878</v>
+        <v>-0.877</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.764</v>
+        <v>-0.763</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.718</v>
+        <v>-0.717</v>
       </c>
     </row>
     <row r="8">
@@ -34224,7 +34228,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.83</v>
+        <v>-0.831</v>
       </c>
       <c r="D8" t="n">
         <v>-0.742</v>
@@ -34245,13 +34249,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.91</v>
+        <v>-0.909</v>
       </c>
       <c r="D9" t="n">
         <v>-0.739</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.614</v>
+        <v>-0.613</v>
       </c>
     </row>
     <row r="10">
@@ -34287,13 +34291,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.835</v>
+        <v>-0.832</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.737</v>
+        <v>-0.735</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.679</v>
+        <v>-0.677</v>
       </c>
     </row>
     <row r="12">
@@ -34341,43 +34345,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.834</v>
+        <v>-0.884</v>
       </c>
       <c r="D14" t="n">
         <v>-0.716</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5</v>
+        <v>-0.442</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>CVX</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ISP</t>
-        </is>
-      </c>
       <c r="C15" t="n">
-        <v>-0.884</v>
+        <v>-0.834</v>
       </c>
       <c r="D15" t="n">
         <v>-0.716</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.442</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="16">
@@ -34398,7 +34402,7 @@
         <v>-0.713</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.575</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="17">
@@ -34425,43 +34429,43 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>PST</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-0.859</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.707</v>
+        <v>-0.706</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.653</v>
+        <v>-0.482</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PST</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.859</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.706</v>
+        <v>-0.705</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.482</v>
+        <v>-0.652</v>
       </c>
     </row>
     <row r="20">
@@ -34476,13 +34480,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.842</v>
+        <v>-0.843</v>
       </c>
       <c r="D20" t="n">
         <v>-0.702</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.61</v>
+        <v>-0.611</v>
       </c>
     </row>
     <row r="21">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -4029,52 +4029,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>158.8950042724609</v>
+        <v>158.8699951171875</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.07735042226556521</v>
+        <v>-0.09307766976502929</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03211335254562631</v>
+        <v>0.01636887608069681</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5333369502995455</v>
+        <v>-0.5489924281550596</v>
       </c>
       <c r="H40" t="n">
-        <v>1.725356835385705</v>
+        <v>1.709345852183364</v>
       </c>
       <c r="I40" t="n">
-        <v>54.76459884869266</v>
+        <v>54.50652682675082</v>
       </c>
       <c r="J40" t="n">
         <v>33.09448640353283</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6742329447990199</v>
+        <v>0.6689404375208198</v>
       </c>
       <c r="L40" t="n">
-        <v>158.4361842426812</v>
+        <v>158.4338024183694</v>
       </c>
       <c r="M40" t="n">
-        <v>158.2621354345381</v>
+        <v>158.2611546833509</v>
       </c>
       <c r="N40" t="n">
-        <v>155.3618645600413</v>
+        <v>155.3616157127251</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1802107081245447</v>
+        <v>0.1786146822609305</v>
       </c>
       <c r="P40" t="n">
-        <v>90.09624728478336</v>
+        <v>89.51068937921573</v>
       </c>
       <c r="Q40" t="n">
-        <v>-9.903752715216646</v>
+        <v>-10.48931062078427</v>
       </c>
       <c r="R40" t="n">
-        <v>52.12432931203905</v>
+        <v>51.65910227229956</v>
       </c>
       <c r="S40" t="n">
-        <v>-0.4267557393770272</v>
+        <v>-0.442427992499117</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4091,7 +4091,7 @@
         <v>65</v>
       </c>
       <c r="X40" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4391,87 +4391,79 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Russell 2000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.350894927978516</v>
+        <v>2869.22998046875</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5687233738171482</v>
+        <v>0.9066461425231154</v>
       </c>
       <c r="F44" t="n">
-        <v>1.506247194658594</v>
+        <v>2.718287699614663</v>
       </c>
       <c r="G44" t="n">
-        <v>0.316109025346889</v>
+        <v>3.391945497461468</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3620407930712166</v>
+        <v>8.177711519867925</v>
       </c>
       <c r="I44" t="n">
-        <v>52.47966055424565</v>
+        <v>60.71352792032251</v>
       </c>
       <c r="J44" t="n">
-        <v>17.35609375318657</v>
+        <v>13.05303816711215</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5045191463318871</v>
+        <v>0.7840385659005626</v>
       </c>
       <c r="L44" t="n">
-        <v>1.347630609003021</v>
+        <v>2805.192564353292</v>
       </c>
       <c r="M44" t="n">
-        <v>1.346658048343221</v>
+        <v>2732.449646245859</v>
       </c>
       <c r="N44" t="n">
-        <v>1.339997511575461</v>
+        <v>2549.071487220237</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.001181149147536233</v>
+        <v>-7.660916487861996</v>
       </c>
       <c r="P44" t="n">
-        <v>58.80177666888293</v>
+        <v>88.30298942258695</v>
       </c>
       <c r="Q44" t="n">
-        <v>-41.19822333111707</v>
+        <v>-11.69701057741305</v>
       </c>
       <c r="R44" t="n">
-        <v>-20.37251384402821</v>
+        <v>52.38472041406454</v>
       </c>
       <c r="S44" t="n">
-        <v>-0.04553116309100602</v>
+        <v>2.9504836910208</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom, Volatility Squeeze</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="n">
-        <v>64.09999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="X44" t="n">
-        <v>71</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4480,73 +4472,73 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Bottom; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3658); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); RSI in forza (61) — momentum positivo; vicino alla resistenza dei 20g (2,889)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>ENEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Russell 2000</t>
+          <t>Enel</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2869.22998046875</v>
+        <v>9.798999786376953</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9066461425231154</v>
+        <v>1.041450119922227</v>
       </c>
       <c r="F45" t="n">
-        <v>2.718287699614663</v>
+        <v>1.903074121895165</v>
       </c>
       <c r="G45" t="n">
-        <v>3.391945497461468</v>
+        <v>-0.8599761195469902</v>
       </c>
       <c r="H45" t="n">
-        <v>8.177711519867925</v>
+        <v>1.020618340809198</v>
       </c>
       <c r="I45" t="n">
-        <v>60.71352792032251</v>
+        <v>53.39541032032729</v>
       </c>
       <c r="J45" t="n">
-        <v>13.05303816711215</v>
+        <v>15.43450372025413</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7840385659005626</v>
+        <v>0.660015299924777</v>
       </c>
       <c r="L45" t="n">
-        <v>2805.192564353292</v>
+        <v>9.705887222038715</v>
       </c>
       <c r="M45" t="n">
-        <v>2732.449646245859</v>
+        <v>9.647664188668227</v>
       </c>
       <c r="N45" t="n">
-        <v>2549.071487220237</v>
+        <v>9.022449951291634</v>
       </c>
       <c r="O45" t="n">
-        <v>-7.660916487861996</v>
+        <v>-4.945930047958735e-05</v>
       </c>
       <c r="P45" t="n">
-        <v>88.30298942258695</v>
+        <v>79.2421200152085</v>
       </c>
       <c r="Q45" t="n">
-        <v>-11.69701057741305</v>
+        <v>-20.7578799847915</v>
       </c>
       <c r="R45" t="n">
-        <v>52.38472041406454</v>
+        <v>64.58943997632123</v>
       </c>
       <c r="S45" t="n">
-        <v>2.9504836910208</v>
+        <v>-0.2240129577741112</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4554,12 +4546,16 @@
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W45" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="X45" t="n">
-        <v>65.40000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -4568,19 +4564,19 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); RSI in forza (61) — momentum positivo; vicino alla resistenza dei 20g (2,889)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENEL</t>
+          <t>TRN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Enel</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4589,52 +4585,52 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9.798999786376953</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="E46" t="n">
-        <v>1.041450119922227</v>
+        <v>1.105533793569857</v>
       </c>
       <c r="F46" t="n">
-        <v>1.903074121895165</v>
+        <v>2.402280663894762</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.8599761195469902</v>
+        <v>-1.613691498261938</v>
       </c>
       <c r="H46" t="n">
-        <v>1.020618340809198</v>
+        <v>0.6402573813874657</v>
       </c>
       <c r="I46" t="n">
-        <v>53.39541032032729</v>
+        <v>52.3494035573238</v>
       </c>
       <c r="J46" t="n">
-        <v>15.43450372025413</v>
+        <v>21.29316607990519</v>
       </c>
       <c r="K46" t="n">
-        <v>0.660015299924777</v>
+        <v>0.5637879203323768</v>
       </c>
       <c r="L46" t="n">
-        <v>9.705887222038715</v>
+        <v>9.994018438594653</v>
       </c>
       <c r="M46" t="n">
-        <v>9.647664188668227</v>
+        <v>9.948721105623312</v>
       </c>
       <c r="N46" t="n">
-        <v>9.022449951291634</v>
+        <v>9.382881526154984</v>
       </c>
       <c r="O46" t="n">
-        <v>-4.945930047958735e-05</v>
+        <v>0.0004422470774380835</v>
       </c>
       <c r="P46" t="n">
-        <v>79.2421200152085</v>
+        <v>66.28414822031093</v>
       </c>
       <c r="Q46" t="n">
-        <v>-20.7578799847915</v>
+        <v>-33.71585177968907</v>
       </c>
       <c r="R46" t="n">
-        <v>64.58943997632123</v>
+        <v>11.95326061216765</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.2240129577741112</v>
+        <v>-1.372543061434861</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4644,14 +4640,14 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="X46" t="n">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -4660,90 +4656,94 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TRN</t>
+          <t>CORN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Terna</t>
+          <t>Corn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.0600004196167</v>
+        <v>463.25</v>
       </c>
       <c r="E47" t="n">
-        <v>1.105533793569857</v>
+        <v>0.2163331530557144</v>
       </c>
       <c r="F47" t="n">
-        <v>2.402280663894762</v>
+        <v>1.645639056500281</v>
       </c>
       <c r="G47" t="n">
-        <v>-1.613691498261938</v>
+        <v>1.701427003293077</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6402573813874657</v>
+        <v>8.299240210403269</v>
       </c>
       <c r="I47" t="n">
-        <v>52.3494035573238</v>
+        <v>51.7640141169116</v>
       </c>
       <c r="J47" t="n">
-        <v>21.29316607990519</v>
+        <v>11.22848488519097</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5637879203323768</v>
+        <v>0.4883582615914524</v>
       </c>
       <c r="L47" t="n">
-        <v>9.994018438594653</v>
+        <v>462.2647392166729</v>
       </c>
       <c r="M47" t="n">
-        <v>9.948721105623312</v>
+        <v>456.3128458033316</v>
       </c>
       <c r="N47" t="n">
-        <v>9.382881526154984</v>
+        <v>441.4133927049047</v>
       </c>
       <c r="O47" t="n">
-        <v>0.0004422470774380835</v>
+        <v>-0.1415570983329268</v>
       </c>
       <c r="P47" t="n">
-        <v>66.28414822031093</v>
+        <v>47.14285714285714</v>
       </c>
       <c r="Q47" t="n">
-        <v>-33.71585177968907</v>
+        <v>-52.85714285714285</v>
       </c>
       <c r="R47" t="n">
-        <v>11.95326061216765</v>
+        <v>1.262493424513223</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.372543061434861</v>
+        <v>1.813186813186807</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Doji, Bullish Harami</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W47" t="n">
-        <v>62.8</v>
+        <v>62.7</v>
       </c>
       <c r="X47" t="n">
-        <v>68.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4752,94 +4752,86 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 11); doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CORN</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Reply</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>463.25</v>
+        <v>105.1999969482422</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2163331530557144</v>
+        <v>0.2859822859862193</v>
       </c>
       <c r="F48" t="n">
-        <v>1.645639056500281</v>
+        <v>6.316321569235805</v>
       </c>
       <c r="G48" t="n">
-        <v>1.701427003293077</v>
+        <v>14.47224722691438</v>
       </c>
       <c r="H48" t="n">
-        <v>8.299240210403269</v>
+        <v>18.73589024831612</v>
       </c>
       <c r="I48" t="n">
-        <v>51.7640141169116</v>
+        <v>69.55211064436919</v>
       </c>
       <c r="J48" t="n">
-        <v>11.22848488519097</v>
+        <v>32.07940746259378</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4883582615914524</v>
+        <v>0.909898994734777</v>
       </c>
       <c r="L48" t="n">
-        <v>462.2647392166729</v>
+        <v>98.19438952999867</v>
       </c>
       <c r="M48" t="n">
-        <v>456.3128458033316</v>
+        <v>94.79156085791348</v>
       </c>
       <c r="N48" t="n">
-        <v>441.4133927049047</v>
+        <v>107.1947574065142</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.1415570983329268</v>
+        <v>0.7070076473361731</v>
       </c>
       <c r="P48" t="n">
-        <v>47.14285714285714</v>
+        <v>95.49836372824642</v>
       </c>
       <c r="Q48" t="n">
-        <v>-52.85714285714285</v>
+        <v>-4.501636271753583</v>
       </c>
       <c r="R48" t="n">
-        <v>1.262493424513223</v>
+        <v>96.61357603196706</v>
       </c>
       <c r="S48" t="n">
-        <v>1.813186813186807</v>
+        <v>14.72191979201454</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Doji, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="n">
-        <v>62.7</v>
+        <v>62.5</v>
       </c>
       <c r="X48" t="n">
-        <v>79.09999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4848,86 +4840,94 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 11); doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 32); RSI in forza (70) — momentum positivo; vicino alla resistenza dei 20g (105.90); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Reply</t>
+          <t>Consumer Discr.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>105.1999969482422</v>
+        <v>119.1800003051758</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2859822859862193</v>
+        <v>0.4043836303912363</v>
       </c>
       <c r="F49" t="n">
-        <v>6.316321569235805</v>
+        <v>2.274093841619185</v>
       </c>
       <c r="G49" t="n">
-        <v>14.47224722691438</v>
+        <v>1.223035899042912</v>
       </c>
       <c r="H49" t="n">
-        <v>18.73589024831612</v>
+        <v>2.090116914558826</v>
       </c>
       <c r="I49" t="n">
-        <v>69.55211064436919</v>
+        <v>56.85244701294989</v>
       </c>
       <c r="J49" t="n">
-        <v>32.07940746259378</v>
+        <v>11.16115529921645</v>
       </c>
       <c r="K49" t="n">
-        <v>0.909898994734777</v>
+        <v>0.6940333808920923</v>
       </c>
       <c r="L49" t="n">
-        <v>98.19438952999867</v>
+        <v>117.7311802929923</v>
       </c>
       <c r="M49" t="n">
-        <v>94.79156085791348</v>
+        <v>116.6755825004548</v>
       </c>
       <c r="N49" t="n">
-        <v>107.1947574065142</v>
+        <v>115.3126143279716</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7070076473361731</v>
+        <v>-0.2132384445311677</v>
       </c>
       <c r="P49" t="n">
-        <v>95.49836372824642</v>
+        <v>71.86151713751295</v>
       </c>
       <c r="Q49" t="n">
-        <v>-4.501636271753583</v>
+        <v>-28.13848286248705</v>
       </c>
       <c r="R49" t="n">
-        <v>96.61357603196706</v>
+        <v>47.6573141326727</v>
       </c>
       <c r="S49" t="n">
-        <v>14.72191979201454</v>
+        <v>0.412838363544088</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W49" t="n">
-        <v>62.5</v>
+        <v>62.1</v>
       </c>
       <c r="X49" t="n">
-        <v>65.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -4936,73 +4936,73 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); RSI in forza (70) — momentum positivo; vicino alla resistenza dei 20g (105.90); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 11); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Consumer Discr.</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>119.1800003051758</v>
+        <v>1.350566625595093</v>
       </c>
       <c r="E50" t="n">
-        <v>0.4043836303912363</v>
+        <v>0.5442825746864388</v>
       </c>
       <c r="F50" t="n">
-        <v>2.274093841619185</v>
+        <v>1.481578553007701</v>
       </c>
       <c r="G50" t="n">
-        <v>1.223035899042912</v>
+        <v>0.291729618032055</v>
       </c>
       <c r="H50" t="n">
-        <v>2.090116914558826</v>
+        <v>-0.3862553924523615</v>
       </c>
       <c r="I50" t="n">
-        <v>56.85244701294989</v>
+        <v>52.26164993432197</v>
       </c>
       <c r="J50" t="n">
-        <v>11.16115529921645</v>
+        <v>17.3531454319541</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6940333808920923</v>
+        <v>0.4951059598080276</v>
       </c>
       <c r="L50" t="n">
-        <v>117.7311802929923</v>
+        <v>1.347599342109362</v>
       </c>
       <c r="M50" t="n">
-        <v>116.6755825004548</v>
+        <v>1.346645173739949</v>
       </c>
       <c r="N50" t="n">
-        <v>115.3126143279716</v>
+        <v>1.339994244885078</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.2132384445311677</v>
+        <v>-0.001202100638672023</v>
       </c>
       <c r="P50" t="n">
-        <v>71.86151713751295</v>
+        <v>57.8579213248247</v>
       </c>
       <c r="Q50" t="n">
-        <v>-28.13848286248705</v>
+        <v>-42.14207867517531</v>
       </c>
       <c r="R50" t="n">
-        <v>47.6573141326727</v>
+        <v>-21.22557768927481</v>
       </c>
       <c r="S50" t="n">
-        <v>0.412838363544088</v>
+        <v>-0.0698226824929038</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5011,19 +5011,19 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Top, Double Bottom, Bear Flag / Consolidation, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W50" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="X50" t="n">
-        <v>73.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 11); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); pattern: Double Bottom; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3658); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7815,52 +7815,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.164686679840088</v>
+        <v>1.164279937744141</v>
       </c>
       <c r="E81" t="n">
-        <v>0.221284690365553</v>
+        <v>0.1862845344445807</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2795276051215323</v>
+        <v>0.2445071090991124</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.3167893886727002</v>
+        <v>-0.3516016336451933</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.424417718885496</v>
+        <v>-1.458843148179279</v>
       </c>
       <c r="I81" t="n">
-        <v>45.97636157265175</v>
+        <v>45.47396795439307</v>
       </c>
       <c r="J81" t="n">
         <v>19.3248038386208</v>
       </c>
       <c r="K81" t="n">
-        <v>0.2706413241467881</v>
+        <v>0.253203559866135</v>
       </c>
       <c r="L81" t="n">
-        <v>1.167658239412543</v>
+        <v>1.167619502070071</v>
       </c>
       <c r="M81" t="n">
-        <v>1.168134211724731</v>
+        <v>1.168118261054302</v>
       </c>
       <c r="N81" t="n">
-        <v>1.161599668433297</v>
+        <v>1.161595621248262</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.001326394412732029</v>
+        <v>-0.001352351743071416</v>
       </c>
       <c r="P81" t="n">
-        <v>31.72148789077786</v>
+        <v>29.86705943736684</v>
       </c>
       <c r="Q81" t="n">
-        <v>-68.27851210922213</v>
+        <v>-70.13294056263315</v>
       </c>
       <c r="R81" t="n">
-        <v>-86.51548647974066</v>
+        <v>-88.5001014380455</v>
       </c>
       <c r="S81" t="n">
-        <v>-0.5089672885590257</v>
+        <v>-0.5437124194800469</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8575,52 +8575,52 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>77280.0390625</v>
+        <v>77285.0234375</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3882952639364445</v>
+        <v>0.3947700653894159</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.2294597005727428</v>
+        <v>-0.2230247428160248</v>
       </c>
       <c r="G89" t="n">
-        <v>-3.191699879388987</v>
+        <v>-3.185455978935936</v>
       </c>
       <c r="H89" t="n">
-        <v>9.589315029459522</v>
+        <v>9.59638327436112</v>
       </c>
       <c r="I89" t="n">
-        <v>48.13401400670391</v>
+        <v>48.15496005944417</v>
       </c>
       <c r="J89" t="n">
         <v>33.22754798923612</v>
       </c>
       <c r="K89" t="n">
-        <v>0.3056469469887519</v>
+        <v>0.3062188210197999</v>
       </c>
       <c r="L89" t="n">
-        <v>77818.98841951831</v>
+        <v>77819.46312189927</v>
       </c>
       <c r="M89" t="n">
-        <v>76758.54317835714</v>
+        <v>76758.73864404341</v>
       </c>
       <c r="N89" t="n">
-        <v>81480.77293940274</v>
+        <v>81480.82253517388</v>
       </c>
       <c r="O89" t="n">
-        <v>-431.8786144465865</v>
+        <v>-431.5605232784949</v>
       </c>
       <c r="P89" t="n">
-        <v>39.02607920830003</v>
+        <v>39.09038769550838</v>
       </c>
       <c r="Q89" t="n">
-        <v>-60.97392079169997</v>
+        <v>-60.90961230449162</v>
       </c>
       <c r="R89" t="n">
-        <v>-49.03983820589977</v>
+        <v>-48.99259730479742</v>
       </c>
       <c r="S89" t="n">
-        <v>-4.506546839104619</v>
+        <v>-4.500387743090006</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9511,52 +9511,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>9.522000312805176</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="E99" t="n">
-        <v>0.9863231834294384</v>
+        <v>0.8590553496234499</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.038533610087977</v>
+        <v>-1.16324962172879</v>
       </c>
       <c r="G99" t="n">
-        <v>1.804546880625435</v>
+        <v>1.676247881863357</v>
       </c>
       <c r="H99" t="n">
-        <v>2.979211579252872</v>
+        <v>2.849432211397929</v>
       </c>
       <c r="I99" t="n">
-        <v>46.96294386571149</v>
+        <v>46.71233904314905</v>
       </c>
       <c r="J99" t="n">
         <v>33.95525235157974</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2626297268640682</v>
+        <v>0.2562582788649342</v>
       </c>
       <c r="L99" t="n">
-        <v>9.684625529443531</v>
+        <v>9.683482664307975</v>
       </c>
       <c r="M99" t="n">
-        <v>9.576462542802576</v>
+        <v>9.575991951276171</v>
       </c>
       <c r="N99" t="n">
-        <v>11.23381568018078</v>
+        <v>11.23369627636065</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.08543877241022103</v>
+        <v>-0.08620458973182538</v>
       </c>
       <c r="P99" t="n">
-        <v>25.09668574659035</v>
+        <v>24.38532965868136</v>
       </c>
       <c r="Q99" t="n">
-        <v>-74.90331425340965</v>
+        <v>-75.61467034131863</v>
       </c>
       <c r="R99" t="n">
-        <v>-54.38307640790317</v>
+        <v>-54.84115439304429</v>
       </c>
       <c r="S99" t="n">
-        <v>-2.498344544016473</v>
+        <v>-2.621220831529603</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>42.7</v>
       </c>
       <c r="X99" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -9773,83 +9773,87 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Investment Grade Corp ETF</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>108.370002746582</v>
+        <v>1.274999976158142</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1848983831213014</v>
+        <v>2.439258229041319</v>
       </c>
       <c r="F102" t="n">
-        <v>0.4728371345674942</v>
+        <v>2.210711378848695</v>
       </c>
       <c r="G102" t="n">
-        <v>-1.050030982225358</v>
+        <v>3.815947498544747</v>
       </c>
       <c r="H102" t="n">
-        <v>-2.963823020727863</v>
+        <v>-8.952116473461336</v>
       </c>
       <c r="I102" t="n">
-        <v>47.21595294956771</v>
+        <v>49.33693405077627</v>
       </c>
       <c r="J102" t="n">
-        <v>43.30556513127745</v>
+        <v>30.82866162063231</v>
       </c>
       <c r="K102" t="n">
-        <v>0.429645604460562</v>
+        <v>0.3646429768895229</v>
       </c>
       <c r="L102" t="n">
-        <v>108.4786422370491</v>
+        <v>1.278174685256816</v>
       </c>
       <c r="M102" t="n">
-        <v>109.0014902217753</v>
+        <v>1.297624518634279</v>
       </c>
       <c r="N102" t="n">
-        <v>109.7084384992036</v>
+        <v>1.824826219117784</v>
       </c>
       <c r="O102" t="n">
-        <v>-0.03662095116250719</v>
+        <v>-0.004172028199852181</v>
       </c>
       <c r="P102" t="n">
-        <v>58.53670639535785</v>
+        <v>30.78156134683335</v>
       </c>
       <c r="Q102" t="n">
-        <v>-41.46329360464215</v>
+        <v>-69.21843865316664</v>
       </c>
       <c r="R102" t="n">
-        <v>-20.25480368336319</v>
+        <v>-41.024776187779</v>
       </c>
       <c r="S102" t="n">
-        <v>-1.122258891116212</v>
+        <v>-0.3369012908570279</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Piercing Pattern</t>
+        </is>
+      </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Volatility Squeeze</t>
+          <t>Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W102" t="n">
-        <v>34.6</v>
+        <v>35.5</v>
       </c>
       <c r="X102" t="n">
-        <v>72.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -9858,19 +9862,19 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); pattern: Double Bottom; sul supporto dei 20g (106.93); vicino alla resistenza dei 20g (109.59); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 31); pattern: Double Bottom; segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>US Treasury 7-10Y ETF</t>
+          <t>Investment Grade Corp ETF</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9879,73 +9883,69 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>93.87999725341797</v>
+        <v>108.370002746582</v>
       </c>
       <c r="E103" t="n">
-        <v>0.08528166210828303</v>
+        <v>0.1848983831213014</v>
       </c>
       <c r="F103" t="n">
-        <v>0.3956743757191461</v>
+        <v>0.4728371345674942</v>
       </c>
       <c r="G103" t="n">
-        <v>-1.56234187926293</v>
+        <v>-1.050030982225358</v>
       </c>
       <c r="H103" t="n">
-        <v>-3.633751777934024</v>
+        <v>-2.963823020727863</v>
       </c>
       <c r="I103" t="n">
-        <v>41.03512958474433</v>
+        <v>47.21595294956771</v>
       </c>
       <c r="J103" t="n">
-        <v>54.92695620059033</v>
+        <v>43.30556513127745</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2977724724528542</v>
+        <v>0.429645604460562</v>
       </c>
       <c r="L103" t="n">
-        <v>94.29429839161831</v>
+        <v>108.4786422370491</v>
       </c>
       <c r="M103" t="n">
-        <v>94.94138304997593</v>
+        <v>109.0014902217753</v>
       </c>
       <c r="N103" t="n">
-        <v>95.62757604437337</v>
+        <v>109.7084384992036</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.04903808341769722</v>
+        <v>-0.03662095116250719</v>
       </c>
       <c r="P103" t="n">
-        <v>41.70398678029772</v>
+        <v>58.53670639535785</v>
       </c>
       <c r="Q103" t="n">
-        <v>-58.29601321970228</v>
+        <v>-41.46329360464215</v>
       </c>
       <c r="R103" t="n">
-        <v>-54.48834508917206</v>
+        <v>-20.25480368336319</v>
       </c>
       <c r="S103" t="n">
-        <v>-1.758058129025875</v>
+        <v>-1.122258891116212</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Double Bottom, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W103" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="X103" t="n">
-        <v>78.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -9954,19 +9954,19 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 55); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (92.95); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); pattern: Double Bottom; sul supporto dei 20g (106.93); vicino alla resistenza dei 20g (109.59); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>US Treasury 1-3Y ETF</t>
+          <t>US Treasury 7-10Y ETF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9975,59 +9975,63 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>82.12000274658203</v>
+        <v>93.87999725341797</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.0243445863343017</v>
+        <v>0.08528166210828303</v>
       </c>
       <c r="F104" t="n">
-        <v>0.07312355565869399</v>
+        <v>0.3956743757191461</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.4364701693738482</v>
+        <v>-1.56234187926293</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.131705802602045</v>
+        <v>-3.633751777934024</v>
       </c>
       <c r="I104" t="n">
-        <v>41.74395104577886</v>
+        <v>41.03512958474433</v>
       </c>
       <c r="J104" t="n">
-        <v>41.39994093847094</v>
+        <v>54.92695620059033</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3038935138985066</v>
+        <v>0.2977724724528542</v>
       </c>
       <c r="L104" t="n">
-        <v>82.22047382019801</v>
+        <v>94.29429839161831</v>
       </c>
       <c r="M104" t="n">
-        <v>82.37757725562591</v>
+        <v>94.94138304997593</v>
       </c>
       <c r="N104" t="n">
-        <v>82.60192690722243</v>
+        <v>95.62757604437337</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.002411052595110319</v>
+        <v>-0.04903808341769722</v>
       </c>
       <c r="P104" t="n">
-        <v>33.3340397575552</v>
+        <v>41.70398678029772</v>
       </c>
       <c r="Q104" t="n">
-        <v>-66.6659602424448</v>
+        <v>-58.29601321970228</v>
       </c>
       <c r="R104" t="n">
-        <v>-46.24522131188951</v>
+        <v>-54.48834508917206</v>
       </c>
       <c r="S104" t="n">
-        <v>-0.5449884339413402</v>
+        <v>-1.758058129025875</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
       <c r="V104" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom</t>
@@ -10037,7 +10041,7 @@
         <v>34.4</v>
       </c>
       <c r="X104" t="n">
-        <v>65.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -10046,94 +10050,90 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); pattern: Double Bottom; sul supporto dei 20g (82.00); vicino alla resistenza dei 20g (82.58); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 55); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (92.95); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>US Treasury 1-3Y ETF</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.269999980926514</v>
+        <v>82.12000274658203</v>
       </c>
       <c r="E105" t="n">
-        <v>2.037536023351483</v>
+        <v>-0.0243445863343017</v>
       </c>
       <c r="F105" t="n">
-        <v>1.809885434478486</v>
+        <v>0.07312355565869399</v>
       </c>
       <c r="G105" t="n">
-        <v>3.408826516453578</v>
+        <v>-0.4364701693738482</v>
       </c>
       <c r="H105" t="n">
-        <v>-9.309166663261569</v>
+        <v>-1.131705802602045</v>
       </c>
       <c r="I105" t="n">
-        <v>48.71655226240159</v>
+        <v>41.74395104577886</v>
       </c>
       <c r="J105" t="n">
-        <v>30.82866162063231</v>
+        <v>41.39994093847094</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3407497842262626</v>
+        <v>0.3038935138985066</v>
       </c>
       <c r="L105" t="n">
-        <v>1.277698495234756</v>
+        <v>82.22047382019801</v>
       </c>
       <c r="M105" t="n">
-        <v>1.297428440389901</v>
+        <v>82.37757725562591</v>
       </c>
       <c r="N105" t="n">
-        <v>1.82477646792145</v>
+        <v>82.60192690722243</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.004491116214634135</v>
+        <v>-0.002411052595110319</v>
       </c>
       <c r="P105" t="n">
-        <v>28.5908287261075</v>
+        <v>33.3340397575552</v>
       </c>
       <c r="Q105" t="n">
-        <v>-71.4091712738925</v>
+        <v>-66.6659602424448</v>
       </c>
       <c r="R105" t="n">
-        <v>-42.85262776591595</v>
+        <v>-46.24522131188951</v>
       </c>
       <c r="S105" t="n">
-        <v>-0.7277366066478219</v>
+        <v>-0.5449884339413402</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Piercing Pattern</t>
-        </is>
-      </c>
+      <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr">
         <is>
-          <t>Double Bottom, Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W105" t="n">
-        <v>33.9</v>
+        <v>34.4</v>
       </c>
       <c r="X105" t="n">
-        <v>72.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 31); pattern: Double Bottom; segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); pattern: Double Bottom; sul supporto dei 20g (82.00); vicino alla resistenza dei 20g (82.58); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -10163,52 +10163,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>85.47000122070312</v>
+        <v>85.45999908447266</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2584248505975717</v>
+        <v>0.2466920974761866</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.6647195183339449</v>
+        <v>-0.6763442403847075</v>
       </c>
       <c r="G106" t="n">
-        <v>1.641270693258989</v>
+        <v>1.629376112451775</v>
       </c>
       <c r="H106" t="n">
-        <v>-5.89328524529461</v>
+        <v>-5.904298093869964</v>
       </c>
       <c r="I106" t="n">
-        <v>45.89684092880506</v>
+        <v>45.87111063962005</v>
       </c>
       <c r="J106" t="n">
         <v>33.81356000471499</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2911283122018055</v>
+        <v>0.2905740818640971</v>
       </c>
       <c r="L106" t="n">
-        <v>86.99136726910295</v>
+        <v>86.99041468470006</v>
       </c>
       <c r="M106" t="n">
-        <v>87.31123429969377</v>
+        <v>87.31084205905728</v>
       </c>
       <c r="N106" t="n">
-        <v>108.4240793334279</v>
+        <v>108.4239798096843</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.5802308630423202</v>
+        <v>-0.5808691760097393</v>
       </c>
       <c r="P106" t="n">
-        <v>23.7235036286556</v>
+        <v>23.66070273765898</v>
       </c>
       <c r="Q106" t="n">
-        <v>-76.27649637134439</v>
+        <v>-76.33929726234102</v>
       </c>
       <c r="R106" t="n">
-        <v>-52.91165458240093</v>
+        <v>-52.95918126491046</v>
       </c>
       <c r="S106" t="n">
-        <v>-0.9837786344722987</v>
+        <v>-0.9953660185951452</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10625,12 +10625,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -10639,52 +10639,52 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.2449000030755997</v>
+        <v>1.354699969291687</v>
       </c>
       <c r="E111" t="n">
-        <v>1.144433362738217</v>
+        <v>0.3456896477125104</v>
       </c>
       <c r="F111" t="n">
-        <v>-1.646978661024112</v>
+        <v>-0.7813306928680652</v>
       </c>
       <c r="G111" t="n">
-        <v>-1.998443420320284</v>
+        <v>-2.676729985908566</v>
       </c>
       <c r="H111" t="n">
-        <v>-7.997702820063235</v>
+        <v>-4.290164675990615</v>
       </c>
       <c r="I111" t="n">
-        <v>42.12299840716615</v>
+        <v>42.84330468884762</v>
       </c>
       <c r="J111" t="n">
-        <v>39.60642768256695</v>
+        <v>29.15747068783356</v>
       </c>
       <c r="K111" t="n">
-        <v>0.2186157589000814</v>
+        <v>0.222002380719466</v>
       </c>
       <c r="L111" t="n">
-        <v>0.252881542207471</v>
+        <v>1.386957893098051</v>
       </c>
       <c r="M111" t="n">
-        <v>0.2563511815175361</v>
+        <v>1.401426176742333</v>
       </c>
       <c r="N111" t="n">
-        <v>0.34970750158664</v>
+        <v>1.675479009360618</v>
       </c>
       <c r="O111" t="n">
-        <v>-0.002375827773522811</v>
+        <v>-0.008537763384974322</v>
       </c>
       <c r="P111" t="n">
-        <v>17.9614334974369</v>
+        <v>19.69306552877554</v>
       </c>
       <c r="Q111" t="n">
-        <v>-82.0385665025631</v>
+        <v>-80.30693447122445</v>
       </c>
       <c r="R111" t="n">
-        <v>-74.36623753576522</v>
+        <v>-93.85040447631768</v>
       </c>
       <c r="S111" t="n">
-        <v>-6.575927717166152</v>
+        <v>-4.136084019094088</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -10693,19 +10693,19 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
+          <t>Piercing Pattern</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W111" t="n">
-        <v>32.1</v>
+        <v>32.8</v>
       </c>
       <c r="X111" t="n">
-        <v>77.3</v>
+        <v>67.3</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -10714,19 +10714,19 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 40); pattern: Double Bottom; segnale candlestick: Bullish Harami</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29); pattern: Double Top; segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10735,69 +10735,73 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.353500008583069</v>
+        <v>0.2445999979972839</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2568058449621269</v>
+        <v>1.020530368572792</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.8692162080586985</v>
+        <v>-1.767462146115295</v>
       </c>
       <c r="G112" t="n">
-        <v>-2.762936601910937</v>
+        <v>-2.118496357386501</v>
       </c>
       <c r="H112" t="n">
-        <v>-4.374942150280492</v>
+        <v>-8.110406601296649</v>
       </c>
       <c r="I112" t="n">
-        <v>42.59431678630272</v>
+        <v>41.83634411301754</v>
       </c>
       <c r="J112" t="n">
-        <v>29.15747068783356</v>
+        <v>39.60642768256695</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2160186219301444</v>
+        <v>0.2134253030126457</v>
       </c>
       <c r="L112" t="n">
-        <v>1.386843611125802</v>
+        <v>0.2528529702952504</v>
       </c>
       <c r="M112" t="n">
-        <v>1.401379119459643</v>
+        <v>0.2563394166125041</v>
       </c>
       <c r="N112" t="n">
-        <v>1.67546706945307</v>
+        <v>0.3497045164614827</v>
       </c>
       <c r="O112" t="n">
-        <v>-0.008614342074071284</v>
+        <v>-0.002394973396754409</v>
       </c>
       <c r="P112" t="n">
-        <v>19.19291944994862</v>
+        <v>17.29113584372839</v>
       </c>
       <c r="Q112" t="n">
-        <v>-80.80708055005138</v>
+        <v>-82.70886415627162</v>
       </c>
       <c r="R112" t="n">
-        <v>-94.48457017813621</v>
+        <v>-74.79669465470181</v>
       </c>
       <c r="S112" t="n">
-        <v>-4.22099797433061</v>
+        <v>-6.690373187847232</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W112" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="X112" t="n">
-        <v>70.8</v>
+        <v>77.3</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -10806,7 +10810,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29); pattern: Double Top; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 40); pattern: Double Bottom; segnale candlestick: Bullish Harami</t>
         </is>
       </c>
     </row>
@@ -11103,52 +11107,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2114.89990234375</v>
+        <v>2110.68994140625</v>
       </c>
       <c r="E116" t="n">
-        <v>0.8058176855378241</v>
+        <v>0.6051516614585806</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.568104861684704</v>
+        <v>-0.7660359287815499</v>
       </c>
       <c r="G116" t="n">
-        <v>-9.866065845219385</v>
+        <v>-10.04548821008606</v>
       </c>
       <c r="H116" t="n">
-        <v>-1.892858983223222</v>
+        <v>-2.088152968963497</v>
       </c>
       <c r="I116" t="n">
-        <v>39.6988657298682</v>
+        <v>39.1242087568104</v>
       </c>
       <c r="J116" t="n">
         <v>47.20569154547086</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2612677387593735</v>
+        <v>0.2518557187328582</v>
       </c>
       <c r="L116" t="n">
-        <v>2182.200074694491</v>
+        <v>2181.799126033777</v>
       </c>
       <c r="M116" t="n">
-        <v>2221.417480681568</v>
+        <v>2221.252384174215</v>
       </c>
       <c r="N116" t="n">
-        <v>2528.748418638445</v>
+        <v>2528.706528479863</v>
       </c>
       <c r="O116" t="n">
-        <v>-12.33511493915154</v>
+        <v>-12.60378481094645</v>
       </c>
       <c r="P116" t="n">
-        <v>31.70367705553691</v>
+        <v>30.42459801618134</v>
       </c>
       <c r="Q116" t="n">
-        <v>-68.29632294446309</v>
+        <v>-69.57540198381865</v>
       </c>
       <c r="R116" t="n">
-        <v>-77.54968253549303</v>
+        <v>-78.52059058609963</v>
       </c>
       <c r="S116" t="n">
-        <v>-10.43048144819512</v>
+        <v>-10.60878027636939</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11162,10 +11166,10 @@
       </c>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="X116" t="n">
-        <v>78</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -16689,52 +16693,52 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>158.8950042724609</v>
+        <v>158.8699951171875</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.07735042226556521</v>
+        <v>-0.09307766976502929</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.5333369502995455</v>
+        <v>-0.5489924281550596</v>
       </c>
       <c r="G59" t="n">
-        <v>1.380710533384377</v>
+        <v>1.364753795517948</v>
       </c>
       <c r="H59" t="n">
-        <v>6.930880853266563</v>
+        <v>6.914050550671269</v>
       </c>
       <c r="I59" t="n">
-        <v>56.462210134142</v>
+        <v>56.38290723045462</v>
       </c>
       <c r="J59" t="n">
         <v>10.58957675968701</v>
       </c>
       <c r="K59" t="n">
-        <v>0.6529190656177376</v>
+        <v>0.6500713545183054</v>
       </c>
       <c r="L59" t="n">
-        <v>157.4805174086109</v>
+        <v>157.4781355842991</v>
       </c>
       <c r="M59" t="n">
-        <v>154.8032819016445</v>
+        <v>154.8023011504573</v>
       </c>
       <c r="N59" t="n">
-        <v>145.5023379046181</v>
+        <v>145.5020890573019</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.213138660418962</v>
+        <v>-0.2147346862825763</v>
       </c>
       <c r="P59" t="n">
-        <v>73.05812763053122</v>
+        <v>72.68524627459902</v>
       </c>
       <c r="Q59" t="n">
-        <v>-26.94187236946878</v>
+        <v>-27.31475372540098</v>
       </c>
       <c r="R59" t="n">
-        <v>47.11970561662537</v>
+        <v>46.84461525717781</v>
       </c>
       <c r="S59" t="n">
-        <v>1.2844207846332</v>
+        <v>1.268479202216688</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -17061,52 +17065,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.350894927978516</v>
+        <v>1.350566625595093</v>
       </c>
       <c r="E63" t="n">
-        <v>0.5687233738171482</v>
+        <v>0.5442825746864388</v>
       </c>
       <c r="F63" t="n">
-        <v>0.316109025346889</v>
+        <v>0.291729618032055</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2620745999095675</v>
+        <v>0.2377083243567224</v>
       </c>
       <c r="H63" t="n">
-        <v>4.171568230457412</v>
+        <v>4.146251846905558</v>
       </c>
       <c r="I63" t="n">
-        <v>52.72294075196015</v>
+        <v>52.61350507125866</v>
       </c>
       <c r="J63" t="n">
-        <v>11.10477856791236</v>
+        <v>11.10344450471869</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5789555779293744</v>
+        <v>0.5726803758139501</v>
       </c>
       <c r="L63" t="n">
-        <v>1.3450438271134</v>
+        <v>1.34501256021974</v>
       </c>
       <c r="M63" t="n">
-        <v>1.336993760279298</v>
+        <v>1.336980885676026</v>
       </c>
       <c r="N63" t="n">
-        <v>1.305115883664347</v>
+        <v>1.305112616973965</v>
       </c>
       <c r="O63" t="n">
-        <v>-1.565877062598533e-05</v>
+        <v>-3.66102617617753e-05</v>
       </c>
       <c r="P63" t="n">
-        <v>70.02066596740009</v>
+        <v>69.35964303801721</v>
       </c>
       <c r="Q63" t="n">
-        <v>-29.9793340325999</v>
+        <v>-30.64035696198278</v>
       </c>
       <c r="R63" t="n">
-        <v>7.702090583851151</v>
+        <v>7.079978873523908</v>
       </c>
       <c r="S63" t="n">
-        <v>0.5279342434799439</v>
+        <v>0.5035033571621605</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -17116,7 +17120,7 @@
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Double Bottom, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W63" t="n">
@@ -18163,66 +18167,66 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.164686679840088</v>
+        <v>328.8800048828125</v>
       </c>
       <c r="E75" t="n">
-        <v>0.221284690365553</v>
+        <v>0.9608610538181184</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.3167893886727002</v>
+        <v>3.741094025660674</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.881667313583856</v>
+        <v>-7.3577451034331</v>
       </c>
       <c r="H75" t="n">
-        <v>7.278125961458004</v>
+        <v>-0.8800431035513534</v>
       </c>
       <c r="I75" t="n">
-        <v>49.24280346298583</v>
+        <v>52.95237519130382</v>
       </c>
       <c r="J75" t="n">
-        <v>17.2833888244175</v>
+        <v>27.77548190956076</v>
       </c>
       <c r="K75" t="n">
-        <v>0.3988124283578505</v>
+        <v>0.7044218044939171</v>
       </c>
       <c r="L75" t="n">
-        <v>1.167225823633194</v>
+        <v>320.8600168106299</v>
       </c>
       <c r="M75" t="n">
-        <v>1.157431950395351</v>
+        <v>325.8391032128765</v>
       </c>
       <c r="N75" t="n">
-        <v>1.12207996859848</v>
+        <v>288.6760504158779</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.001017683830873413</v>
+        <v>2.692434862859466</v>
       </c>
       <c r="P75" t="n">
-        <v>53.09168151670184</v>
+        <v>72.75939467436808</v>
       </c>
       <c r="Q75" t="n">
-        <v>-46.90831848329816</v>
+        <v>-27.24060532563191</v>
       </c>
       <c r="R75" t="n">
-        <v>-39.48952992513703</v>
+        <v>46.97949264557219</v>
       </c>
       <c r="S75" t="n">
-        <v>-0.09434188000276844</v>
+        <v>-5.079659878044196</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -18232,14 +18236,14 @@
       <c r="U75" t="inlineStr"/>
       <c r="V75" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Inside Bar</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W75" t="n">
-        <v>54.1</v>
+        <v>54</v>
       </c>
       <c r="X75" t="n">
-        <v>56.1</v>
+        <v>61.2</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -18248,73 +18252,73 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 28); pattern: Double Top</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>328.8800048828125</v>
+        <v>1.164279937744141</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9608610538181184</v>
+        <v>0.1862845344445807</v>
       </c>
       <c r="F76" t="n">
-        <v>3.741094025660674</v>
+        <v>-0.3516016336451933</v>
       </c>
       <c r="G76" t="n">
-        <v>-7.3577451034331</v>
+        <v>-0.9162822869337783</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.8800431035513534</v>
+        <v>7.24066135354402</v>
       </c>
       <c r="I76" t="n">
-        <v>52.95237519130382</v>
+        <v>49.04392101428784</v>
       </c>
       <c r="J76" t="n">
-        <v>27.77548190956076</v>
+        <v>17.2833888244175</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7044218044939171</v>
+        <v>0.3906069218412305</v>
       </c>
       <c r="L76" t="n">
-        <v>320.8600168106299</v>
+        <v>1.167187086290723</v>
       </c>
       <c r="M76" t="n">
-        <v>325.8391032128765</v>
+        <v>1.157415999724921</v>
       </c>
       <c r="N76" t="n">
-        <v>288.6760504158779</v>
+        <v>1.122075921413446</v>
       </c>
       <c r="O76" t="n">
-        <v>2.692434862859466</v>
+        <v>-0.001043641161212978</v>
       </c>
       <c r="P76" t="n">
-        <v>72.75939467436808</v>
+        <v>52.1577032675552</v>
       </c>
       <c r="Q76" t="n">
-        <v>-27.24060532563191</v>
+        <v>-47.84229673244479</v>
       </c>
       <c r="R76" t="n">
-        <v>46.97949264557219</v>
+        <v>-40.39525437265983</v>
       </c>
       <c r="S76" t="n">
-        <v>-5.079659878044196</v>
+        <v>-0.129231810044983</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -18324,14 +18328,14 @@
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W76" t="n">
         <v>54</v>
       </c>
       <c r="X76" t="n">
-        <v>61.2</v>
+        <v>56</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -18340,7 +18344,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); pattern: Double Top</t>
+          <t>pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -19097,52 +19101,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>77280.0390625</v>
+        <v>77285.0234375</v>
       </c>
       <c r="E85" t="n">
-        <v>0.3882952639364445</v>
+        <v>0.3947700653894159</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.751262519038976</v>
+        <v>-1.744925713871393</v>
       </c>
       <c r="G85" t="n">
-        <v>-15.46101432818101</v>
+        <v>-15.45556176873849</v>
       </c>
       <c r="H85" t="n">
-        <v>-10.19626943720177</v>
+        <v>-10.19047731448866</v>
       </c>
       <c r="I85" t="n">
-        <v>46.20191620734643</v>
+        <v>46.20812259641718</v>
       </c>
       <c r="J85" t="n">
         <v>39.73448181746351</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5991465500754584</v>
+        <v>0.5993048604406241</v>
       </c>
       <c r="L85" t="n">
-        <v>78071.2954903991</v>
+        <v>78071.77019278007</v>
       </c>
       <c r="M85" t="n">
-        <v>84857.90640135838</v>
+        <v>84858.10186704465</v>
       </c>
       <c r="N85" t="n">
-        <v>69068.5217720073</v>
+        <v>69068.57136777844</v>
       </c>
       <c r="O85" t="n">
-        <v>1951.015329729778</v>
+        <v>1951.33342089787</v>
       </c>
       <c r="P85" t="n">
-        <v>72.76463515138414</v>
+        <v>72.78926269833764</v>
       </c>
       <c r="Q85" t="n">
-        <v>-27.23536484861586</v>
+        <v>-27.21073730166236</v>
       </c>
       <c r="R85" t="n">
-        <v>14.6027042580682</v>
+        <v>14.61166226488456</v>
       </c>
       <c r="S85" t="n">
-        <v>-14.91555718410121</v>
+        <v>-14.91006944399645</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -20291,87 +20295,87 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>US Treasury 1-3Y ETF</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2114.89990234375</v>
+        <v>82.12000274658203</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8058176855378241</v>
+        <v>0.07312355565869399</v>
       </c>
       <c r="F98" t="n">
-        <v>-10.75351236966088</v>
+        <v>-0.6292311797034489</v>
       </c>
       <c r="G98" t="n">
-        <v>-32.66173572702857</v>
+        <v>-0.8092742620318671</v>
       </c>
       <c r="H98" t="n">
-        <v>5.465553884297414</v>
+        <v>-0.3639837770298748</v>
       </c>
       <c r="I98" t="n">
-        <v>39.86694005758697</v>
+        <v>37.6045789973985</v>
       </c>
       <c r="J98" t="n">
-        <v>31.27410151462559</v>
+        <v>20.53341526844853</v>
       </c>
       <c r="K98" t="n">
-        <v>0.4173885881260038</v>
+        <v>0.1251952687362177</v>
       </c>
       <c r="L98" t="n">
-        <v>2347.365763671929</v>
+        <v>82.51472921149627</v>
       </c>
       <c r="M98" t="n">
-        <v>2677.111177215168</v>
+        <v>82.60273548624369</v>
       </c>
       <c r="N98" t="n">
-        <v>2548.92842992531</v>
+        <v>82.65215982067235</v>
       </c>
       <c r="O98" t="n">
-        <v>41.20518235627196</v>
+        <v>-0.06232869820654374</v>
       </c>
       <c r="P98" t="n">
-        <v>47.04108693551448</v>
+        <v>10.00025431379779</v>
       </c>
       <c r="Q98" t="n">
-        <v>-52.95891306448552</v>
+        <v>-89.9997456862022</v>
       </c>
       <c r="R98" t="n">
-        <v>-16.86844598964621</v>
+        <v>-136.8409919792621</v>
       </c>
       <c r="S98" t="n">
-        <v>-32.19051904218206</v>
+        <v>-0.89307006796846</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bearish</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>Piercing Pattern</t>
+          <t>Doji, Bullish Harami</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Inside Bar, Bull Flag / Consolidation</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W98" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="X98" t="n">
-        <v>73.8</v>
+        <v>70.3</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -20380,94 +20384,94 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); pattern: Bull Flag / Consolidation; segnale candlestick: Piercing Pattern</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (82.00); vicino alla resistenza dei 20g (83.20)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>US Treasury 1-3Y ETF</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>82.12000274658203</v>
+        <v>1360.300048828125</v>
       </c>
       <c r="E99" t="n">
-        <v>0.07312355565869399</v>
+        <v>0.1693703113494038</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.6292311797034489</v>
+        <v>-9.40392615197303</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.8092742620318671</v>
+        <v>-18.44723927888939</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.3639837770298748</v>
+        <v>43.00883424842219</v>
       </c>
       <c r="I99" t="n">
-        <v>37.6045789973985</v>
+        <v>42.60350580589397</v>
       </c>
       <c r="J99" t="n">
-        <v>20.53341526844853</v>
+        <v>26.53773457615651</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1251952687362177</v>
+        <v>0.1727757723383724</v>
       </c>
       <c r="L99" t="n">
-        <v>82.51472921149627</v>
+        <v>1511.980699505505</v>
       </c>
       <c r="M99" t="n">
-        <v>82.60273548624369</v>
+        <v>1438.697354415907</v>
       </c>
       <c r="N99" t="n">
-        <v>82.65215982067235</v>
+        <v>1372.713817705288</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.06232869820654374</v>
+        <v>-40.40031411387112</v>
       </c>
       <c r="P99" t="n">
-        <v>10.00025431379779</v>
+        <v>3.794687807644279</v>
       </c>
       <c r="Q99" t="n">
-        <v>-89.9997456862022</v>
+        <v>-96.20531219235572</v>
       </c>
       <c r="R99" t="n">
-        <v>-136.8409919792621</v>
+        <v>-80.71923537662148</v>
       </c>
       <c r="S99" t="n">
-        <v>-0.89307006796846</v>
+        <v>-26.58931198984754</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>Doji, Bullish Harami</t>
+          <t>Doji, Shooting Star</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W99" t="n">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="X99" t="n">
-        <v>70.3</v>
+        <v>76.2</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -20476,94 +20480,90 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (82.00); vicino alla resistenza dei 20g (83.20)</t>
+          <t>trend in sviluppo (ADX 27); pattern: Double Top; doji — indecisione del mercato; sul supporto dei 20g (1,341)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1360.300048828125</v>
+        <v>2110.68994140625</v>
       </c>
       <c r="E100" t="n">
-        <v>0.1693703113494038</v>
+        <v>0.6051516614585806</v>
       </c>
       <c r="F100" t="n">
-        <v>-9.40392615197303</v>
+        <v>-10.93116816619121</v>
       </c>
       <c r="G100" t="n">
-        <v>-18.44723927888939</v>
+        <v>-32.79578058743737</v>
       </c>
       <c r="H100" t="n">
-        <v>43.00883424842219</v>
+        <v>5.255612098583273</v>
       </c>
       <c r="I100" t="n">
-        <v>42.60350580589397</v>
+        <v>39.72844952803676</v>
       </c>
       <c r="J100" t="n">
-        <v>26.53773457615651</v>
+        <v>31.27410151462559</v>
       </c>
       <c r="K100" t="n">
-        <v>0.1727757723383724</v>
+        <v>0.4143139330364269</v>
       </c>
       <c r="L100" t="n">
-        <v>1511.980699505505</v>
+        <v>2346.964815011214</v>
       </c>
       <c r="M100" t="n">
-        <v>1438.697354415907</v>
+        <v>2676.946080707815</v>
       </c>
       <c r="N100" t="n">
-        <v>1372.713817705288</v>
+        <v>2548.886539766728</v>
       </c>
       <c r="O100" t="n">
-        <v>-40.40031411387112</v>
+        <v>40.93651248447742</v>
       </c>
       <c r="P100" t="n">
-        <v>3.794687807644279</v>
+        <v>46.40386075403251</v>
       </c>
       <c r="Q100" t="n">
-        <v>-96.20531219235572</v>
+        <v>-53.59613924596749</v>
       </c>
       <c r="R100" t="n">
-        <v>-80.71923537662148</v>
+        <v>-17.02875336350607</v>
       </c>
       <c r="S100" t="n">
-        <v>-26.58931198984754</v>
+        <v>-32.32550191570162</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Doji, Shooting Star</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr"/>
       <c r="V100" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W100" t="n">
-        <v>38.5</v>
+        <v>37.8</v>
       </c>
       <c r="X100" t="n">
-        <v>76.2</v>
+        <v>71.3</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); pattern: Double Top; doji — indecisione del mercato; sul supporto dei 20g (1,341)</t>
+          <t>trend molto direzionale (ADX 31); pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -20685,52 +20685,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>85.47000122070312</v>
+        <v>85.45999908447266</v>
       </c>
       <c r="E102" t="n">
-        <v>0.2584248505975717</v>
+        <v>0.2466920974761866</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.725163697470622</v>
+        <v>-1.736664320925463</v>
       </c>
       <c r="G102" t="n">
-        <v>-36.16859700213498</v>
+        <v>-36.1760668790444</v>
       </c>
       <c r="H102" t="n">
-        <v>-35.54265469079563</v>
+        <v>-35.55019781867242</v>
       </c>
       <c r="I102" t="n">
-        <v>38.48843930563677</v>
+        <v>38.48150442873197</v>
       </c>
       <c r="J102" t="n">
         <v>49.21776064464172</v>
       </c>
       <c r="K102" t="n">
-        <v>0.4129867792723947</v>
+        <v>0.4128212473515054</v>
       </c>
       <c r="L102" t="n">
-        <v>96.69322535421418</v>
+        <v>96.69227276981128</v>
       </c>
       <c r="M102" t="n">
-        <v>122.6755980011857</v>
+        <v>122.6752057605492</v>
       </c>
       <c r="N102" t="n">
-        <v>116.0167511260987</v>
+        <v>116.0166516023551</v>
       </c>
       <c r="O102" t="n">
-        <v>3.067930719815742</v>
+        <v>3.067292406848324</v>
       </c>
       <c r="P102" t="n">
-        <v>42.46980265396393</v>
+        <v>42.42483591083208</v>
       </c>
       <c r="Q102" t="n">
-        <v>-57.53019734603607</v>
+        <v>-57.57516408916792</v>
       </c>
       <c r="R102" t="n">
-        <v>-13.38881077023896</v>
+        <v>-13.39556583800539</v>
       </c>
       <c r="S102" t="n">
-        <v>-38.72699306809812</v>
+        <v>-38.73416354842841</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -21249,52 +21249,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1.353500008583069</v>
+        <v>1.354699969291687</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2568058449621269</v>
+        <v>0.3456896477125104</v>
       </c>
       <c r="F108" t="n">
-        <v>-5.453778903200379</v>
+        <v>-5.369957883809873</v>
       </c>
       <c r="G108" t="n">
-        <v>-35.23988148547663</v>
+        <v>-35.18246767150538</v>
       </c>
       <c r="H108" t="n">
-        <v>-44.42603559911418</v>
+        <v>-44.37676587375007</v>
       </c>
       <c r="I108" t="n">
-        <v>36.84207667020258</v>
+        <v>36.91052007889797</v>
       </c>
       <c r="J108" t="n">
         <v>35.86970734861186</v>
       </c>
       <c r="K108" t="n">
-        <v>0.3594781022771072</v>
+        <v>0.3610998231863631</v>
       </c>
       <c r="L108" t="n">
-        <v>1.526472412542831</v>
+        <v>1.52658669451508</v>
       </c>
       <c r="M108" t="n">
-        <v>1.799815676842058</v>
+        <v>1.799862734124749</v>
       </c>
       <c r="N108" t="n">
-        <v>1.416174154987639</v>
+        <v>1.416186094895188</v>
       </c>
       <c r="O108" t="n">
-        <v>0.03372847929233208</v>
+        <v>0.03380505798142905</v>
       </c>
       <c r="P108" t="n">
-        <v>24.52398351704119</v>
+        <v>24.88886182327508</v>
       </c>
       <c r="Q108" t="n">
-        <v>-75.47601648295881</v>
+        <v>-75.11113817672492</v>
       </c>
       <c r="R108" t="n">
-        <v>-20.74973653892273</v>
+        <v>-20.68467407429605</v>
       </c>
       <c r="S108" t="n">
-        <v>-34.6471481151133</v>
+        <v>-34.58920880668279</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>32.4</v>
       </c>
       <c r="X108" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21529,52 +21529,52 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>9.522000312805176</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9863231834294384</v>
+        <v>0.8590553496234499</v>
       </c>
       <c r="F111" t="n">
-        <v>0.2940956959148089</v>
+        <v>0.1677002405662265</v>
       </c>
       <c r="G111" t="n">
-        <v>-28.93371905200555</v>
+        <v>-29.02328020591023</v>
       </c>
       <c r="H111" t="n">
-        <v>-34.0384812813282</v>
+        <v>-34.12160916773151</v>
       </c>
       <c r="I111" t="n">
-        <v>42.46136072720428</v>
+        <v>42.38996238298512</v>
       </c>
       <c r="J111" t="n">
         <v>45.80678007727939</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5176955316408393</v>
+        <v>0.5152884432440258</v>
       </c>
       <c r="L111" t="n">
-        <v>10.20190474299847</v>
+        <v>10.20076187786291</v>
       </c>
       <c r="M111" t="n">
-        <v>12.53264962158528</v>
+        <v>12.53217903005887</v>
       </c>
       <c r="N111" t="n">
-        <v>13.46313319260038</v>
+        <v>13.46301378878025</v>
       </c>
       <c r="O111" t="n">
-        <v>0.3763527669167934</v>
+        <v>0.3755869495951889</v>
       </c>
       <c r="P111" t="n">
-        <v>52.02165528038958</v>
+        <v>51.58943588894541</v>
       </c>
       <c r="Q111" t="n">
-        <v>-47.97834471961042</v>
+        <v>-48.41056411105459</v>
       </c>
       <c r="R111" t="n">
-        <v>-1.422273755328402</v>
+        <v>-1.518817741909937</v>
       </c>
       <c r="S111" t="n">
-        <v>-27.72222835121503</v>
+        <v>-27.81331628411617</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -21809,52 +21809,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.2449000030755997</v>
+        <v>0.2445999979972839</v>
       </c>
       <c r="E114" t="n">
-        <v>1.144433362738217</v>
+        <v>1.020530368572792</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.94378946848739</v>
+        <v>-3.062684346706512</v>
       </c>
       <c r="G114" t="n">
-        <v>-38.78892359573226</v>
+        <v>-38.86390780781814</v>
       </c>
       <c r="H114" t="n">
-        <v>-65.48312317087421</v>
+        <v>-65.52540670785376</v>
       </c>
       <c r="I114" t="n">
-        <v>35.30738174329389</v>
+        <v>35.24593531685518</v>
       </c>
       <c r="J114" t="n">
         <v>40.22919263312446</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3338180019543226</v>
+        <v>0.3318148056178002</v>
       </c>
       <c r="L114" t="n">
-        <v>0.2952553840945915</v>
+        <v>0.295226812182371</v>
       </c>
       <c r="M114" t="n">
-        <v>0.4246822695263598</v>
+        <v>0.4246705046213279</v>
       </c>
       <c r="N114" t="n">
-        <v>0.5393885910192036</v>
+        <v>0.5393856058940462</v>
       </c>
       <c r="O114" t="n">
-        <v>0.01457182661862066</v>
+        <v>0.01455268099538912</v>
       </c>
       <c r="P114" t="n">
-        <v>13.14928894410395</v>
+        <v>12.76318196794313</v>
       </c>
       <c r="Q114" t="n">
-        <v>-86.85071105589604</v>
+        <v>-87.23681803205687</v>
       </c>
       <c r="R114" t="n">
-        <v>-17.31949942349831</v>
+        <v>-17.37609666265417</v>
       </c>
       <c r="S114" t="n">
-        <v>-37.25098010498182</v>
+        <v>-37.32784831401174</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -21997,52 +21997,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1.269999980926514</v>
+        <v>1.274999976158142</v>
       </c>
       <c r="E116" t="n">
-        <v>2.037536023351483</v>
+        <v>2.439258229041319</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6101564814476435</v>
+        <v>1.006259087916694</v>
       </c>
       <c r="G116" t="n">
-        <v>-40.65004371499583</v>
+        <v>-40.41638268910677</v>
       </c>
       <c r="H116" t="n">
-        <v>-71.75229380177693</v>
+        <v>-71.6410824644409</v>
       </c>
       <c r="I116" t="n">
-        <v>35.316982553975</v>
+        <v>35.51284228660265</v>
       </c>
       <c r="J116" t="n">
         <v>26.05081721968851</v>
       </c>
       <c r="K116" t="n">
-        <v>0.3604430717943172</v>
+        <v>0.3658438471609581</v>
       </c>
       <c r="L116" t="n">
-        <v>1.516041285527757</v>
+        <v>1.516517475549817</v>
       </c>
       <c r="M116" t="n">
-        <v>2.404628382659237</v>
+        <v>2.404824460903614</v>
       </c>
       <c r="N116" t="n">
-        <v>5.609546708089879</v>
+        <v>5.609596459286213</v>
       </c>
       <c r="O116" t="n">
-        <v>0.07741920880592407</v>
+        <v>0.07773829682070599</v>
       </c>
       <c r="P116" t="n">
-        <v>20.34976070118206</v>
+        <v>21.18693730646416</v>
       </c>
       <c r="Q116" t="n">
-        <v>-79.65023929881794</v>
+        <v>-78.81306269353584</v>
       </c>
       <c r="R116" t="n">
-        <v>-17.85597427842953</v>
+        <v>-17.66994034680465</v>
       </c>
       <c r="S116" t="n">
-        <v>-38.5334950049203</v>
+        <v>-38.29150111791564</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 26); RSI scarico (35) — zona di interesse long; candela di inversione bullish (engulfing)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 26); RSI scarico (36) — zona di interesse long; candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -27737,66 +27737,66 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>149.8899993896484</v>
+        <v>158.8699951171875</v>
       </c>
       <c r="E61" t="n">
-        <v>2.671411569107041</v>
+        <v>-0.82031324792321</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.171836928496508</v>
+        <v>1.57084182301237</v>
       </c>
       <c r="G61" t="n">
-        <v>-4.650125763679602</v>
+        <v>9.64869610492789</v>
       </c>
       <c r="H61" t="n">
-        <v>28.39643835231478</v>
+        <v>44.0279177531836</v>
       </c>
       <c r="I61" t="n">
-        <v>54.0276924129715</v>
+        <v>59.9651498619826</v>
       </c>
       <c r="J61" t="n">
-        <v>27.39184541707561</v>
+        <v>20.2697483957454</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6450712695305483</v>
+        <v>0.8116156674265609</v>
       </c>
       <c r="L61" t="n">
-        <v>146.240990662911</v>
+        <v>152.9059987033013</v>
       </c>
       <c r="M61" t="n">
-        <v>138.3316249810972</v>
+        <v>144.7234797231319</v>
       </c>
       <c r="N61" t="n">
-        <v>114.368931294505</v>
+        <v>131.0044180674282</v>
       </c>
       <c r="O61" t="n">
-        <v>0.2031153142987767</v>
+        <v>0.5506131007248407</v>
       </c>
       <c r="P61" t="n">
-        <v>67.80987474158408</v>
+        <v>91.19653557256028</v>
       </c>
       <c r="Q61" t="n">
-        <v>-32.19012525841592</v>
+        <v>-8.803464427439721</v>
       </c>
       <c r="R61" t="n">
-        <v>30.26995588985354</v>
+        <v>88.06232718544621</v>
       </c>
       <c r="S61" t="n">
-        <v>-2.681473034831583</v>
+        <v>11.26674031226747</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -27810,10 +27810,10 @@
         </is>
       </c>
       <c r="W61" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="X61" t="n">
-        <v>78.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -27822,73 +27822,73 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Double Top</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); pattern: Double Top; vicino alla resistenza dei 20g (160.70)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>158.8950042724609</v>
+        <v>149.8899993896484</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8047004811189806</v>
+        <v>2.671411569107041</v>
       </c>
       <c r="F62" t="n">
-        <v>1.586831003049349</v>
+        <v>-3.171836928496508</v>
       </c>
       <c r="G62" t="n">
-        <v>9.66595689268328</v>
+        <v>-4.650125763679602</v>
       </c>
       <c r="H62" t="n">
-        <v>44.05059048352607</v>
+        <v>28.39643835231478</v>
       </c>
       <c r="I62" t="n">
-        <v>60.00078455776788</v>
+        <v>54.0276924129715</v>
       </c>
       <c r="J62" t="n">
-        <v>20.2697483957454</v>
+        <v>27.39184541707561</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8126358937882379</v>
+        <v>0.6450712695305483</v>
       </c>
       <c r="L62" t="n">
-        <v>152.908380527613</v>
+        <v>146.240990662911</v>
       </c>
       <c r="M62" t="n">
-        <v>144.7244604743191</v>
+        <v>138.3316249810972</v>
       </c>
       <c r="N62" t="n">
-        <v>131.0047805189539</v>
+        <v>114.368931294505</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5522091265884548</v>
+        <v>0.2031153142987767</v>
       </c>
       <c r="P62" t="n">
-        <v>91.31671413194272</v>
+        <v>67.80987474158408</v>
       </c>
       <c r="Q62" t="n">
-        <v>-8.683285868057286</v>
+        <v>-32.19012525841592</v>
       </c>
       <c r="R62" t="n">
-        <v>88.17474475766802</v>
+        <v>30.26995588985354</v>
       </c>
       <c r="S62" t="n">
-        <v>11.28425581091896</v>
+        <v>-2.681473034831583</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -27902,10 +27902,10 @@
         </is>
       </c>
       <c r="W62" t="n">
-        <v>72.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="X62" t="n">
-        <v>75.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); RSI in forza (60) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (160.70)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Double Top</t>
         </is>
       </c>
     </row>
@@ -29407,52 +29407,52 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.350894927978516</v>
+        <v>1.350566625595093</v>
       </c>
       <c r="E79" t="n">
-        <v>0.150887468067995</v>
+        <v>0.1265482138619767</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3100263571973905</v>
+        <v>0.2856484281281269</v>
       </c>
       <c r="G79" t="n">
-        <v>2.603168348602014</v>
+        <v>2.578233126759111</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.729146838774576</v>
+        <v>-1.753029196051692</v>
       </c>
       <c r="I79" t="n">
-        <v>55.45318337127343</v>
+        <v>55.40814945772713</v>
       </c>
       <c r="J79" t="n">
         <v>23.83028542371799</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6828863114468039</v>
+        <v>0.6809902891045472</v>
       </c>
       <c r="L79" t="n">
-        <v>1.32611903230066</v>
+        <v>1.326087765407</v>
       </c>
       <c r="M79" t="n">
-        <v>1.306032675596496</v>
+        <v>1.306019800993224</v>
       </c>
       <c r="N79" t="n">
-        <v>1.341609903293911</v>
+        <v>1.341605145288354</v>
       </c>
       <c r="O79" t="n">
-        <v>-3.076365077849322e-05</v>
+        <v>-5.17151419142832e-05</v>
       </c>
       <c r="P79" t="n">
-        <v>69.94364951333671</v>
+        <v>69.6515560816207</v>
       </c>
       <c r="Q79" t="n">
-        <v>-30.05635048666329</v>
+        <v>-30.3484439183793</v>
       </c>
       <c r="R79" t="n">
-        <v>55.22876401991392</v>
+        <v>55.04226008028867</v>
       </c>
       <c r="S79" t="n">
-        <v>0.9388669392780935</v>
+        <v>0.9143361856940535</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>59.6</v>
       </c>
       <c r="X79" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
@@ -29577,83 +29577,83 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.164686679840088</v>
+        <v>1.354699969291687</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3237862453742135</v>
+        <v>-0.9309436436792606</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.8548819540785235</v>
+        <v>-26.37392020064773</v>
       </c>
       <c r="G81" t="n">
-        <v>5.11181383371353</v>
+        <v>139.213986171788</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.6545547132576157</v>
+        <v>136.0643270553444</v>
       </c>
       <c r="I81" t="n">
-        <v>56.37064729976593</v>
+        <v>45.19711114308426</v>
       </c>
       <c r="J81" t="n">
-        <v>41.82770114805145</v>
+        <v>45.48102698280077</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6580899121841214</v>
+        <v>0.2368726141490748</v>
       </c>
       <c r="L81" t="n">
-        <v>1.142772183562191</v>
+        <v>1.718164585505744</v>
       </c>
       <c r="M81" t="n">
-        <v>1.122062054858426</v>
+        <v>1.350795886610891</v>
       </c>
       <c r="N81" t="n">
-        <v>1.136432611356771</v>
+        <v>1.028834358201207</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0014224996347682</v>
+        <v>-0.180545891312973</v>
       </c>
       <c r="P81" t="n">
-        <v>69.71841783481484</v>
+        <v>8.790699784975654</v>
       </c>
       <c r="Q81" t="n">
-        <v>-30.28158216518516</v>
+        <v>-91.20930021502434</v>
       </c>
       <c r="R81" t="n">
-        <v>52.24325987634691</v>
+        <v>-47.18197333971845</v>
       </c>
       <c r="S81" t="n">
-        <v>4.270900925514831</v>
+        <v>121.5401048022284</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Double Bottom, Inside Bar</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Doji, Bearish Harami</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="X81" t="n">
-        <v>64.7</v>
+        <v>67.2</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -29662,90 +29662,90 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 45); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.353500008583069</v>
+        <v>1.164279937744141</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.018696635310035</v>
+        <v>-0.3585960468430516</v>
       </c>
       <c r="F82" t="n">
-        <v>-26.43913641448953</v>
+        <v>-0.8895062816465793</v>
       </c>
       <c r="G82" t="n">
-        <v>139.0020961659823</v>
+        <v>5.075105764318066</v>
       </c>
       <c r="H82" t="n">
-        <v>135.8552269419659</v>
+        <v>-0.6892490008614582</v>
       </c>
       <c r="I82" t="n">
-        <v>45.1791473268999</v>
+        <v>56.28272325487121</v>
       </c>
       <c r="J82" t="n">
-        <v>45.48102698280077</v>
+        <v>41.82770114805145</v>
       </c>
       <c r="K82" t="n">
-        <v>0.2364573959916733</v>
+        <v>0.6562995380571306</v>
       </c>
       <c r="L82" t="n">
-        <v>1.718050303533494</v>
+        <v>1.14273344621972</v>
       </c>
       <c r="M82" t="n">
-        <v>1.350747888182546</v>
+        <v>1.122046104187997</v>
       </c>
       <c r="N82" t="n">
-        <v>1.028809869207153</v>
+        <v>1.136426716543786</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.1806224700020699</v>
+        <v>0.001396542304428636</v>
       </c>
       <c r="P82" t="n">
-        <v>8.74302080311754</v>
+        <v>69.39145134025597</v>
       </c>
       <c r="Q82" t="n">
-        <v>-91.25697919688245</v>
+        <v>-30.60854865974402</v>
       </c>
       <c r="R82" t="n">
-        <v>-47.20841509210625</v>
+        <v>52.06970894581277</v>
       </c>
       <c r="S82" t="n">
-        <v>121.3438698962183</v>
+        <v>4.234486527099479</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Doji, Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Double Bottom, Inside Bar</t>
+        </is>
+      </c>
       <c r="W82" t="n">
-        <v>57.9</v>
+        <v>58.4</v>
       </c>
       <c r="X82" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 45); doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 42); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -29775,52 +29775,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>77280.0390625</v>
+        <v>77285.0234375</v>
       </c>
       <c r="E83" t="n">
-        <v>1.278720190421723</v>
+        <v>1.28525242212183</v>
       </c>
       <c r="F83" t="n">
-        <v>-11.68886531983827</v>
+        <v>-11.68316946593782</v>
       </c>
       <c r="G83" t="n">
-        <v>31.04997822644417</v>
+        <v>31.05843063204783</v>
       </c>
       <c r="H83" t="n">
-        <v>31.16356247780232</v>
+        <v>31.17202220931457</v>
       </c>
       <c r="I83" t="n">
-        <v>49.1190652137216</v>
+        <v>49.12162884487427</v>
       </c>
       <c r="J83" t="n">
         <v>31.03302765789525</v>
       </c>
       <c r="K83" t="n">
-        <v>0.2732652757903316</v>
+        <v>0.2733377595944074</v>
       </c>
       <c r="L83" t="n">
-        <v>82387.59308946253</v>
+        <v>82388.0677918435</v>
       </c>
       <c r="M83" t="n">
-        <v>66974.85716823765</v>
+        <v>66975.05654323765</v>
       </c>
       <c r="N83" t="n">
-        <v>49416.1563367731</v>
+        <v>49416.25805871188</v>
       </c>
       <c r="O83" t="n">
-        <v>-5353.431344097797</v>
+        <v>-5353.113252929705</v>
       </c>
       <c r="P83" t="n">
-        <v>26.02061353839355</v>
+        <v>26.02815147471217</v>
       </c>
       <c r="Q83" t="n">
-        <v>-73.97938646160644</v>
+        <v>-73.97184852528783</v>
       </c>
       <c r="R83" t="n">
-        <v>-35.78319332003179</v>
+        <v>-35.77915925383775</v>
       </c>
       <c r="S83" t="n">
-        <v>22.02850024475165</v>
+        <v>22.03637078691605</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -31249,52 +31249,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2114.89990234375</v>
+        <v>2110.68994140625</v>
       </c>
       <c r="E99" t="n">
-        <v>-6.264874986541836</v>
+        <v>-6.451465952072177</v>
       </c>
       <c r="F99" t="n">
-        <v>-28.72015157427155</v>
+        <v>-28.86204262886504</v>
       </c>
       <c r="G99" t="n">
-        <v>-15.85481338698987</v>
+        <v>-16.0223144343571</v>
       </c>
       <c r="H99" t="n">
-        <v>10.24508594278846</v>
+        <v>10.02562992746778</v>
       </c>
       <c r="I99" t="n">
-        <v>44.33932040315945</v>
+        <v>44.30447300811836</v>
       </c>
       <c r="J99" t="n">
         <v>14.47629393105002</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2765368439606921</v>
+        <v>0.27534679589133</v>
       </c>
       <c r="L99" t="n">
-        <v>2693.148071618368</v>
+        <v>2692.747122957654</v>
       </c>
       <c r="M99" t="n">
-        <v>2484.742920642468</v>
+        <v>2484.574522204968</v>
       </c>
       <c r="N99" t="n">
-        <v>2000.001133808427</v>
+        <v>1999.915216238274</v>
       </c>
       <c r="O99" t="n">
-        <v>-162.8299649263068</v>
+        <v>-163.0986347981017</v>
       </c>
       <c r="P99" t="n">
-        <v>20.41250746056169</v>
+        <v>20.29448000569467</v>
       </c>
       <c r="Q99" t="n">
-        <v>-79.58749253943832</v>
+        <v>-79.70551999430533</v>
       </c>
       <c r="R99" t="n">
-        <v>-73.66017898700912</v>
+        <v>-73.79749367957039</v>
       </c>
       <c r="S99" t="n">
-        <v>-18.75340280965978</v>
+        <v>-18.91513386846643</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -31308,7 +31308,7 @@
       </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="X99" t="n">
         <v>68.59999999999999</v>
@@ -31521,52 +31521,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>85.47000122070312</v>
+        <v>85.45999908447266</v>
       </c>
       <c r="E102" t="n">
-        <v>2.94643767879148</v>
+        <v>2.934390360675199</v>
       </c>
       <c r="F102" t="n">
-        <v>-31.34083023563736</v>
+        <v>-31.34886508248006</v>
       </c>
       <c r="G102" t="n">
-        <v>-36.863916323551</v>
+        <v>-36.87130483064087</v>
       </c>
       <c r="H102" t="n">
-        <v>339.0906527200441</v>
+        <v>339.0392680884388</v>
       </c>
       <c r="I102" t="n">
-        <v>42.302713467815</v>
+        <v>42.30071721794506</v>
       </c>
       <c r="J102" t="n">
         <v>29.49738868005443</v>
       </c>
       <c r="K102" t="n">
-        <v>0.1621458091610761</v>
+        <v>0.1621020282624433</v>
       </c>
       <c r="L102" t="n">
-        <v>127.6891410765633</v>
+        <v>127.6881884921604</v>
       </c>
       <c r="M102" t="n">
-        <v>120.8995017381257</v>
+        <v>120.898975309903</v>
       </c>
       <c r="N102" t="n">
-        <v>95.96541847646438</v>
+        <v>95.96514444533477</v>
       </c>
       <c r="O102" t="n">
-        <v>-14.27559203839011</v>
+        <v>-14.27623035135753</v>
       </c>
       <c r="P102" t="n">
-        <v>9.092974971339855</v>
+        <v>9.08755429053708</v>
       </c>
       <c r="Q102" t="n">
-        <v>-90.90702502866014</v>
+        <v>-90.91244570946292</v>
       </c>
       <c r="R102" t="n">
-        <v>-88.16250759283028</v>
+        <v>-88.16644636380137</v>
       </c>
       <c r="S102" t="n">
-        <v>-64.04952667948332</v>
+        <v>-64.05373378755125</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -31709,52 +31709,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.2449000030755997</v>
+        <v>0.2445999979972839</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.5199426664229345</v>
+        <v>-0.6418067824556339</v>
       </c>
       <c r="F104" t="n">
-        <v>-26.41889422221968</v>
+        <v>-26.5090318503299</v>
       </c>
       <c r="G104" t="n">
-        <v>-29.08684261168147</v>
+        <v>-29.1737119749674</v>
       </c>
       <c r="H104" t="n">
-        <v>-79.47646107464027</v>
+        <v>-79.50160262558063</v>
       </c>
       <c r="I104" t="n">
-        <v>39.46836317351504</v>
+        <v>39.45885746681632</v>
       </c>
       <c r="J104" t="n">
         <v>29.35481237847949</v>
       </c>
       <c r="K104" t="n">
-        <v>0.18192593769646</v>
+        <v>0.1816746665159332</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4638923498235749</v>
+        <v>0.4638637779113544</v>
       </c>
       <c r="M104" t="n">
-        <v>0.5191923782946398</v>
+        <v>0.5191803780915072</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4832887574659289</v>
+        <v>0.4832826349133102</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.05145215950060671</v>
+        <v>-0.05147130512383827</v>
       </c>
       <c r="P104" t="n">
-        <v>2.361603607116411</v>
+        <v>2.323639141351004</v>
       </c>
       <c r="Q104" t="n">
-        <v>-97.63839639288359</v>
+        <v>-97.67636085864899</v>
       </c>
       <c r="R104" t="n">
-        <v>-93.13043518745593</v>
+        <v>-93.15469516509968</v>
       </c>
       <c r="S104" t="n">
-        <v>-34.38081131461959</v>
+        <v>-34.46119551059077</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -31989,52 +31989,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9.522000312805176</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="E107" t="n">
-        <v>4.58721660248862</v>
+        <v>4.455410749169042</v>
       </c>
       <c r="F107" t="n">
-        <v>-21.87402509207121</v>
+        <v>-21.97248321270655</v>
       </c>
       <c r="G107" t="n">
-        <v>-13.62931509958734</v>
+        <v>-13.73816360129632</v>
       </c>
       <c r="H107" t="n">
-        <v>-67.55832572860332</v>
+        <v>-67.59921029078369</v>
       </c>
       <c r="I107" t="n">
-        <v>43.33029148375309</v>
+        <v>43.30817055137159</v>
       </c>
       <c r="J107" t="n">
         <v>20.59975096251946</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2318996396189867</v>
+        <v>0.231356072336629</v>
       </c>
       <c r="L107" t="n">
-        <v>13.07984807937861</v>
+        <v>13.07870521424305</v>
       </c>
       <c r="M107" t="n">
-        <v>13.0534943421771</v>
+        <v>13.05301433882017</v>
       </c>
       <c r="N107" t="n">
-        <v>11.01278071666322</v>
+        <v>11.01253581699132</v>
       </c>
       <c r="O107" t="n">
-        <v>-1.047401408744292</v>
+        <v>-1.048167226065896</v>
       </c>
       <c r="P107" t="n">
-        <v>10.78762425593816</v>
+        <v>10.72884531543803</v>
       </c>
       <c r="Q107" t="n">
-        <v>-89.21237574406183</v>
+        <v>-89.27115468456198</v>
       </c>
       <c r="R107" t="n">
-        <v>-87.61985275922098</v>
+        <v>-87.67916729697477</v>
       </c>
       <c r="S107" t="n">
-        <v>-19.64944947886832</v>
+        <v>-19.75071111695538</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
       </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="X107" t="n">
         <v>72.40000000000001</v>
@@ -32725,52 +32725,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.269999980926514</v>
+        <v>1.274999976158142</v>
       </c>
       <c r="E115" t="n">
-        <v>5.532298819103709</v>
+        <v>5.947779920523377</v>
       </c>
       <c r="F115" t="n">
-        <v>-29.01851696018273</v>
+        <v>-28.7390625648574</v>
       </c>
       <c r="G115" t="n">
-        <v>-70.17718007839933</v>
+        <v>-70.05976751175274</v>
       </c>
       <c r="H115" t="n">
-        <v>-96.57007164029457</v>
+        <v>-96.55656799801039</v>
       </c>
       <c r="I115" t="n">
-        <v>35.61591898777293</v>
+        <v>35.64629111726357</v>
       </c>
       <c r="J115" t="n">
         <v>27.37097468108967</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2164274905644594</v>
+        <v>0.2169723299704548</v>
       </c>
       <c r="L115" t="n">
-        <v>3.217244074585384</v>
+        <v>3.217720264607444</v>
       </c>
       <c r="M115" t="n">
-        <v>4.711733946345683</v>
+        <v>4.712011723858551</v>
       </c>
       <c r="N115" t="n">
-        <v>6.653257679810903</v>
+        <v>6.653402607208921</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.07990825982799898</v>
+        <v>-0.07958917181321712</v>
       </c>
       <c r="P115" t="n">
-        <v>3.297511455477438</v>
+        <v>3.415550293499998</v>
       </c>
       <c r="Q115" t="n">
-        <v>-96.70248854452257</v>
+        <v>-96.5844497065</v>
       </c>
       <c r="R115" t="n">
-        <v>-77.97623812689596</v>
+        <v>-77.9281665786247</v>
       </c>
       <c r="S115" t="n">
-        <v>-80.85888486805202</v>
+        <v>-80.78352621779601</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25/05/2026 19:41:12</t>
+          <t>25/05/2026 21:07:48</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33451,10 +33451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.77885939877726</v>
+        <v>76.77884174568915</v>
       </c>
       <c r="C2" t="n">
-        <v>0.173569170076488</v>
+        <v>0.1735684639529637</v>
       </c>
       <c r="D2" t="n">
         <v>68.10344827586206</v>
@@ -33603,7 +33603,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.962</v>
+        <v>0.961</v>
       </c>
       <c r="D6" t="n">
         <v>0.954</v>
@@ -33657,43 +33657,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>MSCIWORLD</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.907</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.9340000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MSCIWORLD</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="C10" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="D10" t="n">
-        <v>0.9340000000000001</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.925</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -33792,7 +33792,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.893</v>
+        <v>0.894</v>
       </c>
       <c r="D15" t="n">
         <v>0.923</v>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -4085,52 +4085,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>100.8079986572266</v>
+        <v>100.7320022583008</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.04164582799206507</v>
+        <v>-0.117001703129016</v>
       </c>
       <c r="F40" t="n">
-        <v>1.060650282933895</v>
+        <v>0.9844634168428845</v>
       </c>
       <c r="G40" t="n">
-        <v>1.713245925152029</v>
+        <v>1.636567085017049</v>
       </c>
       <c r="H40" t="n">
-        <v>1.877717803221612</v>
+        <v>1.800914972226542</v>
       </c>
       <c r="I40" t="n">
-        <v>69.97438433056571</v>
+        <v>68.38306128596909</v>
       </c>
       <c r="J40" t="n">
         <v>54.89484458347739</v>
       </c>
       <c r="K40" t="n">
-        <v>1.028452434297158</v>
+        <v>1.002514493583477</v>
       </c>
       <c r="L40" t="n">
-        <v>99.75645881330041</v>
+        <v>99.74922106102176</v>
       </c>
       <c r="M40" t="n">
-        <v>99.2911207272344</v>
+        <v>99.28814047629614</v>
       </c>
       <c r="N40" t="n">
-        <v>99.14626280223131</v>
+        <v>99.14550661915742</v>
       </c>
       <c r="O40" t="n">
-        <v>0.09124420361337948</v>
+        <v>0.08639429097538293</v>
       </c>
       <c r="P40" t="n">
-        <v>84.64126713586741</v>
+        <v>80.98230946678618</v>
       </c>
       <c r="Q40" t="n">
-        <v>-15.35873286413259</v>
+        <v>-19.01769053321383</v>
       </c>
       <c r="R40" t="n">
-        <v>143.834680109404</v>
+        <v>141.3230548029026</v>
       </c>
       <c r="S40" t="n">
-        <v>1.631208968641884</v>
+        <v>1.554591973929464</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Doji, Bearish Harami</t>
+          <t>Shooting Star, Bearish Harami</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="W40" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="X40" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 55); RSI in forza (70) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (101.13); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 55); RSI in forza (68) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (101.13); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -4277,52 +4277,52 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>161.2989959716797</v>
+        <v>161.2680053710938</v>
       </c>
       <c r="E42" t="n">
-        <v>0.435236514071824</v>
+        <v>0.4159397522983665</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7300262619255538</v>
+        <v>0.7106728617875646</v>
       </c>
       <c r="G42" t="n">
-        <v>1.517418229186074</v>
+        <v>1.497913546333551</v>
       </c>
       <c r="H42" t="n">
-        <v>1.626150540346938</v>
+        <v>1.606624966604153</v>
       </c>
       <c r="I42" t="n">
-        <v>70.71846385736271</v>
+        <v>70.48981637109725</v>
       </c>
       <c r="J42" t="n">
         <v>50.61984995168159</v>
       </c>
       <c r="K42" t="n">
-        <v>1.063462818408888</v>
+        <v>1.054574012824137</v>
       </c>
       <c r="L42" t="n">
-        <v>159.9806764397499</v>
+        <v>159.9777249539798</v>
       </c>
       <c r="M42" t="n">
-        <v>159.2439885190913</v>
+        <v>159.2427732014213</v>
       </c>
       <c r="N42" t="n">
-        <v>156.1692369504374</v>
+        <v>156.1689285862524</v>
       </c>
       <c r="O42" t="n">
-        <v>0.06715944821361042</v>
+        <v>0.06518170048389926</v>
       </c>
       <c r="P42" t="n">
-        <v>91.78206725758039</v>
+        <v>90.19036199343256</v>
       </c>
       <c r="Q42" t="n">
-        <v>-8.217932742419611</v>
+        <v>-9.80963800656745</v>
       </c>
       <c r="R42" t="n">
-        <v>84.23820917868589</v>
+        <v>83.63754853570602</v>
       </c>
       <c r="S42" t="n">
-        <v>1.434422847439754</v>
+        <v>1.414934110605448</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (71) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (161.46); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (70) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (161.46); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5217,52 +5217,52 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.204999923706055</v>
+        <v>3.197999954223633</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.8660722549139299</v>
+        <v>-1.082588475009738</v>
       </c>
       <c r="F52" t="n">
-        <v>2.724360296947292</v>
+        <v>2.500002292486414</v>
       </c>
       <c r="G52" t="n">
-        <v>6.691077851207283</v>
+        <v>6.458056226625919</v>
       </c>
       <c r="H52" t="n">
-        <v>10.86128978759469</v>
+        <v>10.61916009531134</v>
       </c>
       <c r="I52" t="n">
-        <v>55.78046016365939</v>
+        <v>55.37537833192449</v>
       </c>
       <c r="J52" t="n">
         <v>19.22499663949089</v>
       </c>
       <c r="K52" t="n">
-        <v>0.6007227003865492</v>
+        <v>0.5861227670944709</v>
       </c>
       <c r="L52" t="n">
-        <v>3.135272284223814</v>
+        <v>3.134605620463583</v>
       </c>
       <c r="M52" t="n">
-        <v>3.057596086125304</v>
+        <v>3.05732157751815</v>
       </c>
       <c r="N52" t="n">
-        <v>3.276538269390067</v>
+        <v>3.27646861795243</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.009400017267039568</v>
+        <v>-0.00984673896620275</v>
       </c>
       <c r="P52" t="n">
-        <v>52.36768265753725</v>
+        <v>50.41783025791048</v>
       </c>
       <c r="Q52" t="n">
-        <v>-47.63231734246275</v>
+        <v>-49.58216974208952</v>
       </c>
       <c r="R52" t="n">
-        <v>27.56640611576669</v>
+        <v>26.48760651622542</v>
       </c>
       <c r="S52" t="n">
-        <v>6.196157826785331</v>
+        <v>5.964217146088413</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5271,15 +5271,15 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>Bearish Harami</t>
+          <t>Shooting Star, Bearish Harami</t>
         </is>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="X52" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>segnale candlestick: Bearish Harami</t>
+          <t>shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
@@ -5309,52 +5309,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.33549976348877</v>
+        <v>6.336999893188477</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.6118132491839789</v>
+        <v>-0.5882799564192687</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.477338722929178</v>
+        <v>-1.454010370661263</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7153580523546754</v>
+        <v>0.7392055948487464</v>
       </c>
       <c r="H53" t="n">
-        <v>16.47210097113661</v>
+        <v>16.49967942025297</v>
       </c>
       <c r="I53" t="n">
-        <v>49.87604903809291</v>
+        <v>49.9452355486542</v>
       </c>
       <c r="J53" t="n">
         <v>11.64027060034949</v>
       </c>
       <c r="K53" t="n">
-        <v>0.3570105075544036</v>
+        <v>0.3603034397173553</v>
       </c>
       <c r="L53" t="n">
-        <v>6.368606834033723</v>
+        <v>6.368749703528932</v>
       </c>
       <c r="M53" t="n">
-        <v>6.224503688287667</v>
+        <v>6.224562516903342</v>
       </c>
       <c r="N53" t="n">
-        <v>5.689552628562685</v>
+        <v>5.689567555226365</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.01547588379291957</v>
+        <v>-0.01538014902006088</v>
       </c>
       <c r="P53" t="n">
-        <v>21.43734171904784</v>
+        <v>21.80912100080241</v>
       </c>
       <c r="Q53" t="n">
-        <v>-78.56265828095216</v>
+        <v>-78.19087899919759</v>
       </c>
       <c r="R53" t="n">
-        <v>-38.33145904733797</v>
+        <v>-38.07189805478079</v>
       </c>
       <c r="S53" t="n">
-        <v>1.254591567671715</v>
+        <v>1.278566790734259</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>Evening Star</t>
+          <t>Hammer, Evening Star</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="W53" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
       <c r="X53" t="n">
-        <v>73.2</v>
+        <v>69.7</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Top; evening star — inversione ribassista a 3 candele; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Top; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -6069,52 +6069,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10356.900390625</v>
+        <v>10363.26953125</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.411548447394583</v>
+        <v>-0.3503049451264006</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.096286205165509</v>
+        <v>-1.03546379327244</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.7227496858230764</v>
+        <v>-0.6616975617062204</v>
       </c>
       <c r="H61" t="n">
-        <v>2.91549054131266</v>
+        <v>2.978780059124553</v>
       </c>
       <c r="I61" t="n">
-        <v>48.22300298411007</v>
+        <v>48.58817229134002</v>
       </c>
       <c r="J61" t="n">
         <v>19.83219191664904</v>
       </c>
       <c r="K61" t="n">
-        <v>0.3837957847798039</v>
+        <v>0.4022709636521399</v>
       </c>
       <c r="L61" t="n">
-        <v>10388.7335556457</v>
+        <v>10389.34014046713</v>
       </c>
       <c r="M61" t="n">
-        <v>10372.8179011629</v>
+        <v>10373.06767138349</v>
       </c>
       <c r="N61" t="n">
-        <v>10006.02969605115</v>
+        <v>10006.09307058473</v>
       </c>
       <c r="O61" t="n">
-        <v>5.440741219229083</v>
+        <v>5.847204894443118</v>
       </c>
       <c r="P61" t="n">
-        <v>51.81938559322033</v>
+        <v>53.25873940677967</v>
       </c>
       <c r="Q61" t="n">
-        <v>-48.18061440677966</v>
+        <v>-46.74126059322034</v>
       </c>
       <c r="R61" t="n">
-        <v>-18.7824880925278</v>
+        <v>-16.89802709443956</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.8292201788193565</v>
+        <v>-0.7682335304256216</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>51.7</v>
       </c>
       <c r="X61" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -7159,83 +7159,87 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.322016835212708</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.6094525278675156</v>
+        <v>2.365184552677113</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.443639553926812</v>
+        <v>-6.804478770149447</v>
       </c>
       <c r="G73" t="n">
-        <v>-1.591711253317096</v>
+        <v>-9.037416742912507</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.462152086137047</v>
+        <v>-8.382732342228072</v>
       </c>
       <c r="I73" t="n">
-        <v>33.19418968021928</v>
+        <v>37.73954267031441</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6844322067588</v>
+        <v>12.49419890522083</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.1895902017423606</v>
+        <v>0.09838005211627279</v>
       </c>
       <c r="L73" t="n">
-        <v>1.339374966913617</v>
+        <v>22.68470318951033</v>
       </c>
       <c r="M73" t="n">
-        <v>1.342732453577015</v>
+        <v>22.72577484181309</v>
       </c>
       <c r="N73" t="n">
-        <v>1.339991917180515</v>
+        <v>19.66609361543729</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.001261943942482292</v>
+        <v>-0.2151530795502726</v>
       </c>
       <c r="P73" t="n">
-        <v>17.67889513913547</v>
+        <v>18.33330790201823</v>
       </c>
       <c r="Q73" t="n">
-        <v>-82.32110486086452</v>
+        <v>-81.66669209798177</v>
       </c>
       <c r="R73" t="n">
-        <v>-258.3373097351454</v>
+        <v>-146.1213850174805</v>
       </c>
       <c r="S73" t="n">
-        <v>-1.581135110938514</v>
+        <v>-7.104531793196733</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="X73" t="n">
-        <v>57.3</v>
+        <v>58.3</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -7244,94 +7248,90 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 29); RSI scarico (33) — zona di interesse long; pattern: Double Bottom; sul supporto dei 20g (1.3164); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 12); RSI scarico (38) — zona di interesse long; pattern: Double Top; segnale candlestick: Bullish Harami; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>21.63999938964844</v>
+        <v>1.323451638221741</v>
       </c>
       <c r="E74" t="n">
-        <v>2.365184552677113</v>
+        <v>-0.5015826030798087</v>
       </c>
       <c r="F74" t="n">
-        <v>-6.804478770149447</v>
+        <v>-1.336674983763353</v>
       </c>
       <c r="G74" t="n">
-        <v>-9.037416742912507</v>
+        <v>-1.484907387400503</v>
       </c>
       <c r="H74" t="n">
-        <v>-8.382732342228072</v>
+        <v>-1.355207607878772</v>
       </c>
       <c r="I74" t="n">
-        <v>37.73954267031441</v>
+        <v>34.00810467124548</v>
       </c>
       <c r="J74" t="n">
-        <v>12.49419890522083</v>
+        <v>28.6844322067588</v>
       </c>
       <c r="K74" t="n">
-        <v>0.09838005211627279</v>
+        <v>-0.1591493014751707</v>
       </c>
       <c r="L74" t="n">
-        <v>22.68470318951033</v>
+        <v>1.339511614819239</v>
       </c>
       <c r="M74" t="n">
-        <v>22.72577484181309</v>
+        <v>1.342788720361683</v>
       </c>
       <c r="N74" t="n">
-        <v>19.66609361543729</v>
+        <v>1.340006193827371</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.2151530795502726</v>
+        <v>-0.001170378166407305</v>
       </c>
       <c r="P74" t="n">
-        <v>18.33330790201823</v>
+        <v>22.17757760376759</v>
       </c>
       <c r="Q74" t="n">
-        <v>-81.66669209798177</v>
+        <v>-77.82242239623241</v>
       </c>
       <c r="R74" t="n">
-        <v>-146.1213850174805</v>
+        <v>-253.5079585172091</v>
       </c>
       <c r="S74" t="n">
-        <v>-7.104531793196733</v>
+        <v>-1.474319766589482</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
+      <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W74" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="X74" t="n">
-        <v>58.3</v>
+        <v>57.8</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 12); RSI scarico (38) — zona di interesse long; pattern: Double Top; segnale candlestick: Bullish Harami; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 29); RSI scarico (34) — zona di interesse long; pattern: Double Bottom; sul supporto dei 20g (1.3164); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7925,52 +7925,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.146657466888428</v>
+        <v>1.147842049598694</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.3543227678095562</v>
+        <v>-0.251381349111679</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.9448428059617209</v>
+        <v>-0.8425114385193111</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.365673093458075</v>
+        <v>-1.26377647509891</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.27508790073132</v>
+        <v>-1.173097701109904</v>
       </c>
       <c r="I81" t="n">
-        <v>32.40442646541879</v>
+        <v>33.385186109595</v>
       </c>
       <c r="J81" t="n">
         <v>34.4828225717103</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.06477689524356042</v>
+        <v>-0.02631480536629894</v>
       </c>
       <c r="L81" t="n">
-        <v>1.15835150583127</v>
+        <v>1.158464323232248</v>
       </c>
       <c r="M81" t="n">
-        <v>1.16266431563824</v>
+        <v>1.162710769862172</v>
       </c>
       <c r="N81" t="n">
-        <v>1.161057910581459</v>
+        <v>1.161069697474099</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.0006194816833962821</v>
+        <v>-0.0005438843822282865</v>
       </c>
       <c r="P81" t="n">
-        <v>19.11445647501893</v>
+        <v>24.19919356489347</v>
       </c>
       <c r="Q81" t="n">
-        <v>-80.88554352498107</v>
+        <v>-75.80080643510654</v>
       </c>
       <c r="R81" t="n">
-        <v>-169.6950812060314</v>
+        <v>-164.6270700286243</v>
       </c>
       <c r="S81" t="n">
-        <v>-1.330129020504434</v>
+        <v>-1.228195682466116</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="W81" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="X81" t="n">
-        <v>59.3</v>
+        <v>65.7</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 34); RSI scarico (32) — zona di interesse long; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (1.1422); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 34); RSI scarico (33) — zona di interesse long; pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (1.1422); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -9133,52 +9133,52 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>4169.5</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.292585317439443</v>
+        <v>-1.212097112492871</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.079478054567018</v>
+        <v>-0.9988160772538501</v>
       </c>
       <c r="G94" t="n">
-        <v>-7.984459653568465</v>
+        <v>-7.909428150681963</v>
       </c>
       <c r="H94" t="n">
-        <v>-5.326856621199372</v>
+        <v>-5.2496580501324</v>
       </c>
       <c r="I94" t="n">
-        <v>36.31599385850778</v>
+        <v>36.45891281876063</v>
       </c>
       <c r="J94" t="n">
         <v>46.49607209561968</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1694884564785909</v>
+        <v>0.1746113816223894</v>
       </c>
       <c r="L94" t="n">
-        <v>4346.091022392866</v>
+        <v>4346.41482261608</v>
       </c>
       <c r="M94" t="n">
-        <v>4492.062912576666</v>
+        <v>4492.196242080343</v>
       </c>
       <c r="N94" t="n">
-        <v>4352.462316939226</v>
+        <v>4352.496146813293</v>
       </c>
       <c r="O94" t="n">
-        <v>-2.431804860159929</v>
+        <v>-2.214831035373237</v>
       </c>
       <c r="P94" t="n">
-        <v>27.78335005015045</v>
+        <v>28.46537659854564</v>
       </c>
       <c r="Q94" t="n">
-        <v>-72.21664994984955</v>
+        <v>-71.53462340145437</v>
       </c>
       <c r="R94" t="n">
-        <v>-83.38472659474722</v>
+        <v>-82.92600078757205</v>
       </c>
       <c r="S94" t="n">
-        <v>-8.15674304195424</v>
+        <v>-8.081852022745872</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9313,52 +9313,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>76.38999938964844</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.2741502462870193</v>
+        <v>-0.07832579606906753</v>
       </c>
       <c r="F96" t="n">
-        <v>-10.00235407456691</v>
+        <v>-9.825632195758338</v>
       </c>
       <c r="G96" t="n">
-        <v>-22.25727892439981</v>
+        <v>-22.10462115662271</v>
       </c>
       <c r="H96" t="n">
-        <v>-13.32122799233857</v>
+        <v>-13.1510231465951</v>
       </c>
       <c r="I96" t="n">
-        <v>31.07945536912395</v>
+        <v>31.21755122904698</v>
       </c>
       <c r="J96" t="n">
         <v>26.17776911416089</v>
       </c>
       <c r="K96" t="n">
-        <v>0.08835696630110716</v>
+        <v>0.09286387371986823</v>
       </c>
       <c r="L96" t="n">
-        <v>86.38554117860377</v>
+        <v>86.39982703821128</v>
       </c>
       <c r="M96" t="n">
-        <v>90.17974221304128</v>
+        <v>90.18562462582084</v>
       </c>
       <c r="N96" t="n">
-        <v>79.54720280273885</v>
+        <v>79.54869535523515</v>
       </c>
       <c r="O96" t="n">
-        <v>-1.478569047663887</v>
+        <v>-1.468996300713211</v>
       </c>
       <c r="P96" t="n">
-        <v>11.99828257168602</v>
+        <v>12.63876736078308</v>
       </c>
       <c r="Q96" t="n">
-        <v>-88.00171742831398</v>
+        <v>-87.36123263921692</v>
       </c>
       <c r="R96" t="n">
-        <v>-96.40702351721433</v>
+        <v>-96.04221087117665</v>
       </c>
       <c r="S96" t="n">
-        <v>-20.71613845415241</v>
+        <v>-20.56045446011561</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="W96" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="X96" t="n">
         <v>77.2</v>
@@ -9593,52 +9593,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>64.68499755859375</v>
+        <v>64.91000366210938</v>
       </c>
       <c r="E99" t="n">
-        <v>-2.369632118192</v>
+        <v>-2.030025880408903</v>
       </c>
       <c r="F99" t="n">
-        <v>-4.677350899412724</v>
+        <v>-4.345772037846219</v>
       </c>
       <c r="G99" t="n">
-        <v>-14.72096699015142</v>
+        <v>-14.42432474460221</v>
       </c>
       <c r="H99" t="n">
-        <v>-6.320157880471688</v>
+        <v>-5.994293506214266</v>
       </c>
       <c r="I99" t="n">
-        <v>35.86623489587059</v>
+        <v>36.18466872636674</v>
       </c>
       <c r="J99" t="n">
         <v>55.46353599302523</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1522461236769023</v>
+        <v>0.1631564355310234</v>
       </c>
       <c r="L99" t="n">
-        <v>70.28919115383169</v>
+        <v>70.31062030654746</v>
       </c>
       <c r="M99" t="n">
-        <v>73.52294259303346</v>
+        <v>73.53176636179877</v>
       </c>
       <c r="N99" t="n">
-        <v>67.51922681599038</v>
+        <v>67.52146568269204</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.2487513514789037</v>
+        <v>-0.2343919876078182</v>
       </c>
       <c r="P99" t="n">
-        <v>10.4972202693772</v>
+        <v>12.27311662524293</v>
       </c>
       <c r="Q99" t="n">
-        <v>-89.50277973062281</v>
+        <v>-87.72688337475707</v>
       </c>
       <c r="R99" t="n">
-        <v>-84.37944039284645</v>
+        <v>-83.46231305980453</v>
       </c>
       <c r="S99" t="n">
-        <v>-15.34928636297922</v>
+        <v>-15.05482971995268</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9652,10 +9652,10 @@
       </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="X99" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -9781,52 +9781,52 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1666.400024414062</v>
+        <v>1668.199951171875</v>
       </c>
       <c r="E101" t="n">
-        <v>-2.275388685716762</v>
+        <v>-2.16983351275446</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.504091269629849</v>
+        <v>-2.398783124928672</v>
       </c>
       <c r="G101" t="n">
-        <v>-14.53482497266284</v>
+        <v>-14.44251157063506</v>
       </c>
       <c r="H101" t="n">
-        <v>-10.42305108448541</v>
+        <v>-10.32629643681735</v>
       </c>
       <c r="I101" t="n">
-        <v>33.85936712311913</v>
+        <v>33.9677576391427</v>
       </c>
       <c r="J101" t="n">
         <v>44.17038424803421</v>
       </c>
       <c r="K101" t="n">
-        <v>0.138557649293901</v>
+        <v>0.1422263661608618</v>
       </c>
       <c r="L101" t="n">
-        <v>1804.611083343608</v>
+        <v>1804.78250493959</v>
       </c>
       <c r="M101" t="n">
-        <v>1902.343746865287</v>
+        <v>1902.414332228338</v>
       </c>
       <c r="N101" t="n">
-        <v>1844.361048963209</v>
+        <v>1844.378958682192</v>
       </c>
       <c r="O101" t="n">
-        <v>-4.943012436518245</v>
+        <v>-4.828145315791687</v>
       </c>
       <c r="P101" t="n">
-        <v>6.680448616767769</v>
+        <v>7.300258054264957</v>
       </c>
       <c r="Q101" t="n">
-        <v>-93.31955138323224</v>
+        <v>-92.69974194573504</v>
       </c>
       <c r="R101" t="n">
-        <v>-81.77463277306228</v>
+        <v>-81.47114340762118</v>
       </c>
       <c r="S101" t="n">
-        <v>-14.76650579392251</v>
+        <v>-14.67444263703597</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -9961,52 +9961,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>80.36000061035156</v>
+        <v>80.58999633789062</v>
       </c>
       <c r="E103" t="n">
-        <v>0.6387002454305124</v>
+        <v>0.9267349754669807</v>
       </c>
       <c r="F103" t="n">
-        <v>-7.981221887739132</v>
+        <v>-7.717857954707275</v>
       </c>
       <c r="G103" t="n">
-        <v>-23.48123864117733</v>
+        <v>-23.26223679877512</v>
       </c>
       <c r="H103" t="n">
-        <v>-19.59175640658427</v>
+        <v>-19.36162260438239</v>
       </c>
       <c r="I103" t="n">
-        <v>31.24063308907475</v>
+        <v>31.70606281233002</v>
       </c>
       <c r="J103" t="n">
-        <v>39.1908685696358</v>
+        <v>39.14168323036948</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1288009769403078</v>
+        <v>0.1355662511892576</v>
       </c>
       <c r="L103" t="n">
-        <v>89.88772012848185</v>
+        <v>89.90962448348556</v>
       </c>
       <c r="M103" t="n">
-        <v>94.67069624254998</v>
+        <v>94.67971568284563</v>
       </c>
       <c r="N103" t="n">
-        <v>84.2348588808222</v>
+        <v>84.23714739552408</v>
       </c>
       <c r="O103" t="n">
-        <v>-1.299905878339058</v>
+        <v>-1.285228088319463</v>
       </c>
       <c r="P103" t="n">
-        <v>16.85994240861571</v>
+        <v>17.88579319506955</v>
       </c>
       <c r="Q103" t="n">
-        <v>-83.14005759138429</v>
+        <v>-82.11420680493045</v>
       </c>
       <c r="R103" t="n">
-        <v>-80.83983785183487</v>
+        <v>-80.09549586003624</v>
       </c>
       <c r="S103" t="n">
-        <v>-21.66114332625828</v>
+        <v>-21.43693224862752</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 39); RSI scarico (31) — zona di interesse long; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 39); RSI scarico (32) — zona di interesse long; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -10145,52 +10145,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1262</v>
+        <v>1264.5</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.9807767752059604</v>
+        <v>-0.7846214201647661</v>
       </c>
       <c r="F105" t="n">
-        <v>-1.112674480110731</v>
+        <v>-0.9167804121236189</v>
       </c>
       <c r="G105" t="n">
-        <v>-8.138014620358502</v>
+        <v>-7.95603762871896</v>
       </c>
       <c r="H105" t="n">
-        <v>-10.57890198133958</v>
+        <v>-10.40176034501101</v>
       </c>
       <c r="I105" t="n">
-        <v>39.75239994250958</v>
+        <v>39.99490402532096</v>
       </c>
       <c r="J105" t="n">
         <v>38.41853496439487</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3024746414706263</v>
+        <v>0.3115637403392147</v>
       </c>
       <c r="L105" t="n">
-        <v>1320.251843810881</v>
+        <v>1320.489939048977</v>
       </c>
       <c r="M105" t="n">
-        <v>1398.717401397884</v>
+        <v>1398.81544061357</v>
       </c>
       <c r="N105" t="n">
-        <v>1446.788860774967</v>
+        <v>1446.813736396858</v>
       </c>
       <c r="O105" t="n">
-        <v>7.402433980963551</v>
+        <v>7.561978140507755</v>
       </c>
       <c r="P105" t="n">
-        <v>32.92024979693311</v>
+        <v>34.26723273273767</v>
       </c>
       <c r="Q105" t="n">
-        <v>-67.07975020306688</v>
+        <v>-65.73276726726233</v>
       </c>
       <c r="R105" t="n">
-        <v>-38.83941495427035</v>
+        <v>-38.21546121040969</v>
       </c>
       <c r="S105" t="n">
-        <v>-8.775482309643689</v>
+        <v>-8.594768130383867</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="W105" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="X105" t="n">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -10407,66 +10407,66 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>63151.6484375</v>
+        <v>577.219970703125</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4057076183661579</v>
+        <v>1.698430762715764</v>
       </c>
       <c r="F108" t="n">
-        <v>-1.970893639097937</v>
+        <v>1.546360702391247</v>
       </c>
       <c r="G108" t="n">
-        <v>-14.1221006261873</v>
+        <v>-4.21334117681853</v>
       </c>
       <c r="H108" t="n">
-        <v>-18.11978841681321</v>
+        <v>-2.769262403581962</v>
       </c>
       <c r="I108" t="n">
-        <v>36.11451831252166</v>
+        <v>42.82363147477857</v>
       </c>
       <c r="J108" t="n">
-        <v>53.64910087311483</v>
+        <v>11.39436231198384</v>
       </c>
       <c r="K108" t="n">
-        <v>0.3799184149065462</v>
+        <v>0.2596992972285576</v>
       </c>
       <c r="L108" t="n">
-        <v>65942.01516927309</v>
+        <v>594.3614138944586</v>
       </c>
       <c r="M108" t="n">
-        <v>69901.39190841814</v>
+        <v>609.5017259745606</v>
       </c>
       <c r="N108" t="n">
-        <v>78238.90361411794</v>
+        <v>637.4971458358525</v>
       </c>
       <c r="O108" t="n">
-        <v>454.3515567366921</v>
+        <v>-1.593866142056221</v>
       </c>
       <c r="P108" t="n">
-        <v>49.66978444922561</v>
+        <v>23.66782699441756</v>
       </c>
       <c r="Q108" t="n">
-        <v>-50.33021555077439</v>
+        <v>-76.33217300558243</v>
       </c>
       <c r="R108" t="n">
-        <v>-24.36782691353545</v>
+        <v>-99.3157407670116</v>
       </c>
       <c r="S108" t="n">
-        <v>-13.93011241968026</v>
+        <v>-4.601201032592261</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10475,19 +10475,15 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Inside Bar, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+          <t>Hammer, Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="X108" t="n">
-        <v>76.8</v>
+        <v>73.5</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -10496,73 +10492,73 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 54); RSI scarico (36) — zona di interesse long; pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 11); hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>577.219970703125</v>
+        <v>69.18000030517578</v>
       </c>
       <c r="E109" t="n">
-        <v>1.698430762715764</v>
+        <v>-0.6412717656335443</v>
       </c>
       <c r="F109" t="n">
-        <v>1.546360702391247</v>
+        <v>-2.790908644545065</v>
       </c>
       <c r="G109" t="n">
-        <v>-4.21334117681853</v>
+        <v>-15.56462835882673</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.769262403581962</v>
+        <v>-19.74730505873121</v>
       </c>
       <c r="I109" t="n">
-        <v>42.82363147477857</v>
+        <v>41.4509384019511</v>
       </c>
       <c r="J109" t="n">
-        <v>11.39436231198384</v>
+        <v>48.88619086340117</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2596992972285576</v>
+        <v>0.4700093363625951</v>
       </c>
       <c r="L109" t="n">
-        <v>594.3614138944586</v>
+        <v>71.72523136923382</v>
       </c>
       <c r="M109" t="n">
-        <v>609.5017259745606</v>
+        <v>77.17467736206044</v>
       </c>
       <c r="N109" t="n">
-        <v>637.4971458358525</v>
+        <v>100.3760559780021</v>
       </c>
       <c r="O109" t="n">
-        <v>-1.593866142056221</v>
+        <v>0.9331811878456584</v>
       </c>
       <c r="P109" t="n">
-        <v>23.66782699441756</v>
+        <v>56.46252084386892</v>
       </c>
       <c r="Q109" t="n">
-        <v>-76.33217300558243</v>
+        <v>-43.53747915613108</v>
       </c>
       <c r="R109" t="n">
-        <v>-99.3157407670116</v>
+        <v>-8.131153414414376</v>
       </c>
       <c r="S109" t="n">
-        <v>-4.601201032592261</v>
+        <v>-16.19349776827119</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10571,15 +10567,19 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Hammer, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr"/>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W109" t="n">
-        <v>34.2</v>
+        <v>33.9</v>
       </c>
       <c r="X109" t="n">
-        <v>73.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -10588,19 +10588,19 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 11); hammer — segnale di rimbalzo da supporto</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 49); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10609,73 +10609,69 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>69.20999908447266</v>
+        <v>63074.69921875</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.5981864729713182</v>
+        <v>0.2833649566869489</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.748755506870038</v>
+        <v>-2.090340452219486</v>
       </c>
       <c r="G110" t="n">
-        <v>-15.52801433645697</v>
+        <v>-14.22674139849027</v>
       </c>
       <c r="H110" t="n">
-        <v>-19.71250478592257</v>
+        <v>-18.21955807395283</v>
       </c>
       <c r="I110" t="n">
-        <v>41.49968142842607</v>
+        <v>35.80078524003233</v>
       </c>
       <c r="J110" t="n">
-        <v>48.88619086340117</v>
+        <v>53.64910087311483</v>
       </c>
       <c r="K110" t="n">
-        <v>0.4713328811669406</v>
+        <v>0.375177318112401</v>
       </c>
       <c r="L110" t="n">
-        <v>71.72808839583352</v>
+        <v>65934.68667224929</v>
       </c>
       <c r="M110" t="n">
-        <v>77.17585378477796</v>
+        <v>69898.37429199657</v>
       </c>
       <c r="N110" t="n">
-        <v>100.3763544733185</v>
+        <v>78238.13795024979</v>
       </c>
       <c r="O110" t="n">
-        <v>0.9350956398577601</v>
+        <v>449.4408373634697</v>
       </c>
       <c r="P110" t="n">
-        <v>56.65576126256959</v>
+        <v>48.72437116026337</v>
       </c>
       <c r="Q110" t="n">
-        <v>-43.3442387374304</v>
+        <v>-51.27562883973663</v>
       </c>
       <c r="R110" t="n">
-        <v>-8.050387184986535</v>
+        <v>-24.47455434660233</v>
       </c>
       <c r="S110" t="n">
-        <v>-16.15715644486845</v>
+        <v>-14.03498712637554</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W110" t="n">
         <v>33.9</v>
       </c>
       <c r="X110" t="n">
-        <v>76.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -10684,7 +10680,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 49); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 54); RSI scarico (36) — zona di interesse long; pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -10787,12 +10783,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -10801,52 +10797,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7.89799976348877</v>
+        <v>1702.2900390625</v>
       </c>
       <c r="E112" t="n">
-        <v>-1.295500187715648</v>
+        <v>-0.4237067262246708</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.9955611110241125</v>
+        <v>1.313846425227894</v>
       </c>
       <c r="G112" t="n">
-        <v>-12.13083483872967</v>
+        <v>-15.20571241220897</v>
       </c>
       <c r="H112" t="n">
-        <v>-17.9438596359119</v>
+        <v>-29.68857615075968</v>
       </c>
       <c r="I112" t="n">
-        <v>39.95966173475026</v>
+        <v>38.33548944044239</v>
       </c>
       <c r="J112" t="n">
-        <v>41.16426805910175</v>
+        <v>50.99003675562322</v>
       </c>
       <c r="K112" t="n">
-        <v>0.3906322811943439</v>
+        <v>0.4120888047036948</v>
       </c>
       <c r="L112" t="n">
-        <v>8.233618333773268</v>
+        <v>1778.407849772546</v>
       </c>
       <c r="M112" t="n">
-        <v>8.719096722895459</v>
+        <v>1940.993186786887</v>
       </c>
       <c r="N112" t="n">
-        <v>10.59921345208019</v>
+        <v>2370.684475954701</v>
       </c>
       <c r="O112" t="n">
-        <v>0.06583238401375413</v>
+        <v>21.26608974243412</v>
       </c>
       <c r="P112" t="n">
-        <v>56.44997171450819</v>
+        <v>57.37032910233274</v>
       </c>
       <c r="Q112" t="n">
-        <v>-43.55002828549181</v>
+        <v>-42.62967089766725</v>
       </c>
       <c r="R112" t="n">
-        <v>-20.15343132461668</v>
+        <v>-18.45262320752426</v>
       </c>
       <c r="S112" t="n">
-        <v>-12.39276470590102</v>
+        <v>-15.39223575984848</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10856,14 +10852,14 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W112" t="n">
-        <v>32.7</v>
+        <v>32.9</v>
       </c>
       <c r="X112" t="n">
-        <v>71.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -10872,19 +10868,19 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); pattern: Bull Flag / Consolidation</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10893,73 +10889,69 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1705.510009765625</v>
+        <v>7.89799976348877</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.2353529558860257</v>
+        <v>-1.295500187715648</v>
       </c>
       <c r="F113" t="n">
-        <v>1.505486868292349</v>
+        <v>-0.9955611110241125</v>
       </c>
       <c r="G113" t="n">
-        <v>-15.04531957928409</v>
+        <v>-12.13083483872967</v>
       </c>
       <c r="H113" t="n">
-        <v>-29.55557841259854</v>
+        <v>-17.9438596359119</v>
       </c>
       <c r="I113" t="n">
-        <v>38.5550390457171</v>
+        <v>39.95966173475026</v>
       </c>
       <c r="J113" t="n">
-        <v>50.99003675562322</v>
+        <v>41.16426805910175</v>
       </c>
       <c r="K113" t="n">
-        <v>0.4177527599892419</v>
+        <v>0.3906322811943439</v>
       </c>
       <c r="L113" t="n">
-        <v>1778.714513649034</v>
+        <v>8.233618333773268</v>
       </c>
       <c r="M113" t="n">
-        <v>1941.119460147793</v>
+        <v>8.719096722895459</v>
       </c>
       <c r="N113" t="n">
-        <v>2370.716515464185</v>
+        <v>10.59921345208019</v>
       </c>
       <c r="O113" t="n">
-        <v>21.47158075026894</v>
+        <v>0.06583238401375413</v>
       </c>
       <c r="P113" t="n">
-        <v>58.31387144602211</v>
+        <v>56.44997171450819</v>
       </c>
       <c r="Q113" t="n">
-        <v>-41.68612855397789</v>
+        <v>-43.55002828549181</v>
       </c>
       <c r="R113" t="n">
-        <v>-18.09430601541072</v>
+        <v>-20.15343132461668</v>
       </c>
       <c r="S113" t="n">
-        <v>-15.2321957455979</v>
+        <v>-12.39276470590102</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W113" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="X113" t="n">
-        <v>69.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -10968,7 +10960,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -10989,52 +10981,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.135599970817566</v>
+        <v>1.13289999961853</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.8575015278145526</v>
+        <v>-1.093220000299733</v>
       </c>
       <c r="F114" t="n">
-        <v>-4.235776889666754</v>
+        <v>-4.463463267740342</v>
       </c>
       <c r="G114" t="n">
-        <v>-14.50900104767072</v>
+        <v>-14.71226209106604</v>
       </c>
       <c r="H114" t="n">
-        <v>-20.84662616754326</v>
+        <v>-21.03481904808753</v>
       </c>
       <c r="I114" t="n">
-        <v>39.32454653614948</v>
+        <v>39.05790865877866</v>
       </c>
       <c r="J114" t="n">
         <v>38.6536907671133</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3455060974820164</v>
+        <v>0.3354272937458474</v>
       </c>
       <c r="L114" t="n">
-        <v>1.193441932489831</v>
+        <v>1.193184792375637</v>
       </c>
       <c r="M114" t="n">
-        <v>1.267618900299055</v>
+        <v>1.267513019075564</v>
       </c>
       <c r="N114" t="n">
-        <v>1.570253835367946</v>
+        <v>1.570226969982881</v>
       </c>
       <c r="O114" t="n">
-        <v>0.007739533974303735</v>
+        <v>0.00756722812000641</v>
       </c>
       <c r="P114" t="n">
-        <v>34.49814273716492</v>
+        <v>33.34740697046416</v>
       </c>
       <c r="Q114" t="n">
-        <v>-65.50185726283507</v>
+        <v>-66.65259302953584</v>
       </c>
       <c r="R114" t="n">
-        <v>-28.79425594063143</v>
+        <v>-29.38201820817617</v>
       </c>
       <c r="S114" t="n">
-        <v>-15.14849342995813</v>
+        <v>-15.35023403388661</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11044,10 +11036,10 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="X114" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -11077,52 +11069,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.9670000076293945</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.5692354469082672</v>
+        <v>-1.289006117569591</v>
       </c>
       <c r="F115" t="n">
-        <v>-1.319785690841935</v>
+        <v>-2.034123193460458</v>
       </c>
       <c r="G115" t="n">
-        <v>-20.2639929753381</v>
+        <v>-20.84119500641926</v>
       </c>
       <c r="H115" t="n">
-        <v>-27.63422193119716</v>
+        <v>-28.1580715148509</v>
       </c>
       <c r="I115" t="n">
-        <v>35.64683146739102</v>
+        <v>34.92020483575737</v>
       </c>
       <c r="J115" t="n">
         <v>68.11421132733075</v>
       </c>
       <c r="K115" t="n">
-        <v>0.3567606281541437</v>
+        <v>0.3372021782981767</v>
       </c>
       <c r="L115" t="n">
-        <v>1.027422232483812</v>
+        <v>1.026755563046949</v>
       </c>
       <c r="M115" t="n">
-        <v>1.130153009725567</v>
+        <v>1.129878498780976</v>
       </c>
       <c r="N115" t="n">
-        <v>1.657889025550977</v>
+        <v>1.65781937352026</v>
       </c>
       <c r="O115" t="n">
-        <v>0.008561369522260998</v>
+        <v>0.008114644019268646</v>
       </c>
       <c r="P115" t="n">
-        <v>49.06562938105979</v>
+        <v>44.44984206076799</v>
       </c>
       <c r="Q115" t="n">
-        <v>-50.93437061894021</v>
+        <v>-55.55015793923201</v>
       </c>
       <c r="R115" t="n">
-        <v>-26.76578024339038</v>
+        <v>-27.87480425155955</v>
       </c>
       <c r="S115" t="n">
-        <v>-18.88284949577929</v>
+        <v>-19.47004950457921</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11139,7 +11131,7 @@
         <v>31.4</v>
       </c>
       <c r="X115" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -11148,7 +11140,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 68); RSI scarico (36) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 68); RSI scarico (35) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -11257,52 +11249,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.110000133514404</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="E117" t="n">
-        <v>-3.123191630501165</v>
+        <v>-4.708735228924176</v>
       </c>
       <c r="F117" t="n">
-        <v>-9.015908158149987</v>
+        <v>-10.5050080449666</v>
       </c>
       <c r="G117" t="n">
-        <v>-31.44728648162811</v>
+        <v>-32.56926105844337</v>
       </c>
       <c r="H117" t="n">
-        <v>-37.2770792192666</v>
+        <v>-38.30363993273449</v>
       </c>
       <c r="I117" t="n">
-        <v>24.05561813034186</v>
+        <v>23.21436317430548</v>
       </c>
       <c r="J117" t="n">
         <v>87.65845511487178</v>
       </c>
       <c r="K117" t="n">
-        <v>0.2110588566108486</v>
+        <v>0.1874165908091151</v>
       </c>
       <c r="L117" t="n">
-        <v>7.147753601478728</v>
+        <v>7.138229801037531</v>
       </c>
       <c r="M117" t="n">
-        <v>8.067294563118262</v>
+        <v>8.06337299823071</v>
       </c>
       <c r="N117" t="n">
-        <v>11.06021539255637</v>
+        <v>11.05922036862967</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.003384821496392521</v>
+        <v>-0.009766581792032936</v>
       </c>
       <c r="P117" t="n">
-        <v>7.759816604745685</v>
+        <v>1.979376578516438</v>
       </c>
       <c r="Q117" t="n">
-        <v>-92.24018339525432</v>
+        <v>-98.02062342148356</v>
       </c>
       <c r="R117" t="n">
-        <v>-60.55873166523297</v>
+        <v>-62.27258194550118</v>
       </c>
       <c r="S117" t="n">
-        <v>-30.69314112148865</v>
+        <v>-31.82745849084812</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11316,10 +11308,10 @@
         </is>
       </c>
       <c r="W117" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="X117" t="n">
-        <v>78</v>
+        <v>78.2</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -11328,7 +11320,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 88); RSI ipervenduto (24) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 88); RSI ipervenduto (23) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (5.9758)</t>
         </is>
       </c>
     </row>
@@ -13427,52 +13419,52 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.33549976348877</v>
+        <v>6.336999893188477</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.477338722929178</v>
+        <v>-1.454010370661263</v>
       </c>
       <c r="F23" t="n">
-        <v>1.343671631549626</v>
+        <v>1.367667947131213</v>
       </c>
       <c r="G23" t="n">
-        <v>7.181526048370213</v>
+        <v>7.206904660395685</v>
       </c>
       <c r="H23" t="n">
-        <v>40.55462057039983</v>
+        <v>40.58790131676871</v>
       </c>
       <c r="I23" t="n">
-        <v>62.79023942317739</v>
+        <v>62.84083761219825</v>
       </c>
       <c r="J23" t="n">
         <v>30.16637292709833</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7853670863195811</v>
+        <v>0.7864128069532585</v>
       </c>
       <c r="L23" t="n">
-        <v>6.012258635435896</v>
+        <v>6.012401504931105</v>
       </c>
       <c r="M23" t="n">
-        <v>5.577590250272977</v>
+        <v>5.577649078888652</v>
       </c>
       <c r="N23" t="n">
-        <v>4.660483929099303</v>
+        <v>4.660498855762982</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02022759858199924</v>
+        <v>0.02032333335485792</v>
       </c>
       <c r="P23" t="n">
-        <v>77.10361986384052</v>
+        <v>77.21197159159595</v>
       </c>
       <c r="Q23" t="n">
-        <v>-22.89638013615948</v>
+        <v>-22.78802840840405</v>
       </c>
       <c r="R23" t="n">
-        <v>82.34546487543636</v>
+        <v>82.43795787728635</v>
       </c>
       <c r="S23" t="n">
-        <v>7.435983376600697</v>
+        <v>7.461422239436621</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -15343,52 +15335,52 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>161.2989959716797</v>
+        <v>161.2680053710938</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7300262619255538</v>
+        <v>0.7106728617875646</v>
       </c>
       <c r="F44" t="n">
-        <v>1.84174471707963</v>
+        <v>1.822177720927609</v>
       </c>
       <c r="G44" t="n">
-        <v>1.765281459813028</v>
+        <v>1.745729154653053</v>
       </c>
       <c r="H44" t="n">
-        <v>12.21034364785354</v>
+        <v>12.18878451835832</v>
       </c>
       <c r="I44" t="n">
-        <v>62.48505753853679</v>
+        <v>62.41341794467198</v>
       </c>
       <c r="J44" t="n">
         <v>10.55074253768085</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8819650358143774</v>
+        <v>0.8787774632657759</v>
       </c>
       <c r="L44" t="n">
-        <v>158.2945767736688</v>
+        <v>158.2916252878987</v>
       </c>
       <c r="M44" t="n">
-        <v>155.4595185308705</v>
+        <v>155.4583032132004</v>
       </c>
       <c r="N44" t="n">
-        <v>145.9547094158332</v>
+        <v>145.9544010516483</v>
       </c>
       <c r="O44" t="n">
-        <v>0.01595319735743317</v>
+        <v>0.01397544962772201</v>
       </c>
       <c r="P44" t="n">
-        <v>97.50462261165065</v>
+        <v>97.02130089929727</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2.495377388349353</v>
+        <v>-2.978699100702732</v>
       </c>
       <c r="R44" t="n">
-        <v>107.2508253388059</v>
+        <v>106.9010277658738</v>
       </c>
       <c r="S44" t="n">
-        <v>5.312671075080022</v>
+        <v>5.292437205016132</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -16551,52 +16543,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10356.900390625</v>
+        <v>10363.26953125</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.096286205165509</v>
+        <v>-1.03546379327244</v>
       </c>
       <c r="F57" t="n">
-        <v>1.58404764709883</v>
+        <v>1.646518372925909</v>
       </c>
       <c r="G57" t="n">
-        <v>2.10481684423427</v>
+        <v>2.167607825362117</v>
       </c>
       <c r="H57" t="n">
-        <v>30.04319500557977</v>
+        <v>30.12316713672671</v>
       </c>
       <c r="I57" t="n">
-        <v>53.99713704636876</v>
+        <v>54.17227097374229</v>
       </c>
       <c r="J57" t="n">
         <v>11.25529383656284</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4641491691358075</v>
+        <v>0.4707611816683155</v>
       </c>
       <c r="L57" t="n">
-        <v>10297.55233242487</v>
+        <v>10298.1589172463</v>
       </c>
       <c r="M57" t="n">
-        <v>9892.201357073658</v>
+        <v>9892.451127294247</v>
       </c>
       <c r="N57" t="n">
-        <v>8674.258836466037</v>
+        <v>8674.322210999619</v>
       </c>
       <c r="O57" t="n">
-        <v>-38.10691064598512</v>
+        <v>-37.70044697077108</v>
       </c>
       <c r="P57" t="n">
-        <v>67.46610252462523</v>
+        <v>68.09212357628684</v>
       </c>
       <c r="Q57" t="n">
-        <v>-32.53389747537478</v>
+        <v>-31.90787642371316</v>
       </c>
       <c r="R57" t="n">
-        <v>10.6791951331159</v>
+        <v>11.19203204359047</v>
       </c>
       <c r="S57" t="n">
-        <v>1.304840716241995</v>
+        <v>1.367139739326073</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -16606,10 +16598,10 @@
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
-        <v>57.8</v>
+        <v>58.7</v>
       </c>
       <c r="X57" t="n">
-        <v>62.5</v>
+        <v>62.6</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -17103,52 +17095,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>76.38999938964844</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="E63" t="n">
-        <v>-10.00235407456691</v>
+        <v>-9.825632195758338</v>
       </c>
       <c r="F63" t="n">
-        <v>-27.5374684912948</v>
+        <v>-27.39517905050149</v>
       </c>
       <c r="G63" t="n">
-        <v>25.08596654884643</v>
+        <v>25.33158882922713</v>
       </c>
       <c r="H63" t="n">
-        <v>24.21138112137957</v>
+        <v>24.45528604150788</v>
       </c>
       <c r="I63" t="n">
-        <v>45.6995916105143</v>
+        <v>45.77637542273652</v>
       </c>
       <c r="J63" t="n">
         <v>52.52314145766847</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2881928588401096</v>
+        <v>0.290564970864077</v>
       </c>
       <c r="L63" t="n">
-        <v>86.21918221254873</v>
+        <v>86.23346807215624</v>
       </c>
       <c r="M63" t="n">
-        <v>77.86018556297647</v>
+        <v>77.86606797575602</v>
       </c>
       <c r="N63" t="n">
-        <v>73.4203124213599</v>
+        <v>73.4218049738562</v>
       </c>
       <c r="O63" t="n">
-        <v>-2.551978816888904</v>
+        <v>-2.542406069938228</v>
       </c>
       <c r="P63" t="n">
-        <v>6.379109763010717</v>
+        <v>6.719635396306818</v>
       </c>
       <c r="Q63" t="n">
-        <v>-93.62089023698928</v>
+        <v>-93.28036460369319</v>
       </c>
       <c r="R63" t="n">
-        <v>-44.13650544367948</v>
+        <v>-43.95705085572996</v>
       </c>
       <c r="S63" t="n">
-        <v>17.14461043112925</v>
+        <v>17.37463884392618</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -17170,7 +17162,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 53); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 53); in zona Fib Fib 61.8 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -17191,52 +17183,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>80.36000061035156</v>
+        <v>80.58999633789062</v>
       </c>
       <c r="E64" t="n">
-        <v>-7.981221887739132</v>
+        <v>-7.717857954707275</v>
       </c>
       <c r="F64" t="n">
-        <v>-26.4506690104628</v>
+        <v>-26.24016587753013</v>
       </c>
       <c r="G64" t="n">
-        <v>21.97936241744811</v>
+        <v>22.32847555820059</v>
       </c>
       <c r="H64" t="n">
-        <v>24.0889406416396</v>
+        <v>24.44409153718039</v>
       </c>
       <c r="I64" t="n">
-        <v>44.62973559158226</v>
+        <v>44.75972669367627</v>
       </c>
       <c r="J64" t="n">
         <v>56.32460508659494</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2759430095883689</v>
+        <v>0.2794316211210656</v>
       </c>
       <c r="L64" t="n">
-        <v>90.96581479641272</v>
+        <v>90.98771915141643</v>
       </c>
       <c r="M64" t="n">
-        <v>82.34954894589245</v>
+        <v>82.3585683861881</v>
       </c>
       <c r="N64" t="n">
-        <v>77.60564553768903</v>
+        <v>77.6079340523909</v>
       </c>
       <c r="O64" t="n">
-        <v>-2.914929148959811</v>
+        <v>-2.900251358940215</v>
       </c>
       <c r="P64" t="n">
-        <v>7.633277535421916</v>
+        <v>8.097727743681906</v>
       </c>
       <c r="Q64" t="n">
-        <v>-92.36672246457809</v>
+        <v>-91.9022722563181</v>
       </c>
       <c r="R64" t="n">
-        <v>-49.23830792968396</v>
+        <v>-48.97758911944656</v>
       </c>
       <c r="S64" t="n">
-        <v>13.6794424034157</v>
+        <v>14.00480061475498</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -17911,52 +17903,52 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>100.8079986572266</v>
+        <v>100.7320022583008</v>
       </c>
       <c r="E72" t="n">
-        <v>1.060650282933895</v>
+        <v>0.9844634168428845</v>
       </c>
       <c r="F72" t="n">
-        <v>1.549312044091411</v>
+        <v>1.472756789235263</v>
       </c>
       <c r="G72" t="n">
-        <v>3.286885484896884</v>
+        <v>3.209020320845757</v>
       </c>
       <c r="H72" t="n">
-        <v>1.030266476755037</v>
+        <v>0.9541025161862837</v>
       </c>
       <c r="I72" t="n">
-        <v>59.87801750964287</v>
+        <v>59.55159642071497</v>
       </c>
       <c r="J72" t="n">
         <v>20.63682955986187</v>
       </c>
       <c r="K72" t="n">
-        <v>0.931251734930842</v>
+        <v>0.9172980262394728</v>
       </c>
       <c r="L72" t="n">
-        <v>99.1450376240598</v>
+        <v>99.13779987178116</v>
       </c>
       <c r="M72" t="n">
-        <v>99.36963947267994</v>
+        <v>99.36665922174167</v>
       </c>
       <c r="N72" t="n">
-        <v>100.8446823669737</v>
+        <v>100.8439261838998</v>
       </c>
       <c r="O72" t="n">
-        <v>0.2079569003428886</v>
+        <v>0.2031069877049034</v>
       </c>
       <c r="P72" t="n">
-        <v>90.87789265619307</v>
+        <v>88.70470526377797</v>
       </c>
       <c r="Q72" t="n">
-        <v>-9.122107343806929</v>
+        <v>-11.29529473622204</v>
       </c>
       <c r="R72" t="n">
-        <v>128.2564379236176</v>
+        <v>126.4696485300107</v>
       </c>
       <c r="S72" t="n">
-        <v>3.936489202546145</v>
+        <v>3.858134319981321</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -17977,7 +17969,7 @@
         <v>52.7</v>
       </c>
       <c r="X72" t="n">
-        <v>62.5</v>
+        <v>62.4</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -18383,52 +18375,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.322016835212708</v>
+        <v>1.323451638221741</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.443639553926812</v>
+        <v>-1.336674983763353</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.278391780149513</v>
+        <v>-1.17124786431001</v>
       </c>
       <c r="G77" t="n">
-        <v>-2.082175568454825</v>
+        <v>-1.975904010188512</v>
       </c>
       <c r="H77" t="n">
-        <v>1.755638506508483</v>
+        <v>1.866075297044323</v>
       </c>
       <c r="I77" t="n">
-        <v>41.94683664603708</v>
+        <v>42.41224320794789</v>
       </c>
       <c r="J77" t="n">
         <v>8.297192574645349</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.010431462091273</v>
+        <v>0.01499094487622545</v>
       </c>
       <c r="L77" t="n">
-        <v>1.341897703176631</v>
+        <v>1.342034351082253</v>
       </c>
       <c r="M77" t="n">
-        <v>1.336554073833898</v>
+        <v>1.336610340618566</v>
       </c>
       <c r="N77" t="n">
-        <v>1.3059055398142</v>
+        <v>1.305919816461056</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.002142946291352375</v>
+        <v>-0.002051380515277388</v>
       </c>
       <c r="P77" t="n">
-        <v>11.87585058097531</v>
+        <v>14.76476560568566</v>
       </c>
       <c r="Q77" t="n">
-        <v>-88.12414941902469</v>
+        <v>-85.23523439431433</v>
       </c>
       <c r="R77" t="n">
-        <v>-116.4241595380007</v>
+        <v>-113.3770114250307</v>
       </c>
       <c r="S77" t="n">
-        <v>-4.246319789985487</v>
+        <v>-4.142397007134369</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -18446,7 +18438,7 @@
         </is>
       </c>
       <c r="W77" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="X77" t="n">
         <v>59.3</v>
@@ -18479,52 +18471,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.146657466888428</v>
+        <v>1.147842049598694</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.9448428059617209</v>
+        <v>-0.8425114385193111</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.67642148074868</v>
+        <v>-1.574845888657128</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.450407596707749</v>
+        <v>-2.349631590017609</v>
       </c>
       <c r="H78" t="n">
-        <v>1.854145155546649</v>
+        <v>1.959368086373225</v>
       </c>
       <c r="I78" t="n">
-        <v>40.85980193034013</v>
+        <v>41.34120983078301</v>
       </c>
       <c r="J78" t="n">
         <v>16.06760456933839</v>
       </c>
       <c r="K78" t="n">
-        <v>0.05193040378651651</v>
+        <v>0.07362123640878293</v>
       </c>
       <c r="L78" t="n">
-        <v>1.164014455448796</v>
+        <v>1.164127272849773</v>
       </c>
       <c r="M78" t="n">
-        <v>1.157175083750769</v>
+        <v>1.157221537974701</v>
       </c>
       <c r="N78" t="n">
-        <v>1.123000644976642</v>
+        <v>1.123012431869281</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.002370934133502138</v>
+        <v>-0.002295336832334143</v>
       </c>
       <c r="P78" t="n">
-        <v>11.69224704983863</v>
+        <v>14.41233552046294</v>
       </c>
       <c r="Q78" t="n">
-        <v>-88.30775295016137</v>
+        <v>-85.58766447953707</v>
       </c>
       <c r="R78" t="n">
-        <v>-114.0721841084851</v>
+        <v>-111.6252015021066</v>
       </c>
       <c r="S78" t="n">
-        <v>-4.171542508942894</v>
+        <v>-4.07254456302325</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -18671,52 +18663,52 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4169.5</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.079478054567018</v>
+        <v>-0.9988160772538501</v>
       </c>
       <c r="F80" t="n">
-        <v>-8.479297187072021</v>
+        <v>-8.404669185634129</v>
       </c>
       <c r="G80" t="n">
-        <v>-16.21116843475064</v>
+        <v>-16.14284517181294</v>
       </c>
       <c r="H80" t="n">
-        <v>29.3991702309971</v>
+        <v>29.50468517095337</v>
       </c>
       <c r="I80" t="n">
-        <v>39.82355454843363</v>
+        <v>39.90297797361786</v>
       </c>
       <c r="J80" t="n">
         <v>27.48598700046218</v>
       </c>
       <c r="K80" t="n">
-        <v>0.04921203176827421</v>
+        <v>0.05141874981654557</v>
       </c>
       <c r="L80" t="n">
-        <v>4527.620037778568</v>
+        <v>4527.943838001782</v>
       </c>
       <c r="M80" t="n">
-        <v>4246.522910306941</v>
+        <v>4246.656239810617</v>
       </c>
       <c r="N80" t="n">
-        <v>3094.516847497213</v>
+        <v>3094.55067737128</v>
       </c>
       <c r="O80" t="n">
-        <v>-105.3364759458003</v>
+        <v>-105.1195021210136</v>
       </c>
       <c r="P80" t="n">
-        <v>14.03810929362547</v>
+        <v>14.38271724084003</v>
       </c>
       <c r="Q80" t="n">
-        <v>-85.96189070637453</v>
+        <v>-85.61728275915998</v>
       </c>
       <c r="R80" t="n">
-        <v>-95.34824650747115</v>
+        <v>-95.14706506487747</v>
       </c>
       <c r="S80" t="n">
-        <v>-11.54882185922265</v>
+        <v>-11.47669681596367</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -18729,7 +18721,7 @@
         <v>49.1</v>
       </c>
       <c r="X80" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
@@ -18759,52 +18751,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>64.68499755859375</v>
+        <v>64.91000366210938</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.677350899412724</v>
+        <v>-4.345772037846219</v>
       </c>
       <c r="F81" t="n">
-        <v>-16.16879647865899</v>
+        <v>-15.87719049320191</v>
       </c>
       <c r="G81" t="n">
-        <v>-35.90785672265865</v>
+        <v>-35.68491285670679</v>
       </c>
       <c r="H81" t="n">
-        <v>103.2585431377911</v>
+        <v>103.9655759046436</v>
       </c>
       <c r="I81" t="n">
-        <v>43.56705825643876</v>
+        <v>43.74111444647041</v>
       </c>
       <c r="J81" t="n">
         <v>18.56245965147523</v>
       </c>
       <c r="K81" t="n">
-        <v>0.05058480161717118</v>
+        <v>0.05738279986620563</v>
       </c>
       <c r="L81" t="n">
-        <v>72.96420576973871</v>
+        <v>72.98563492245448</v>
       </c>
       <c r="M81" t="n">
-        <v>64.36947761842755</v>
+        <v>64.37830138719286</v>
       </c>
       <c r="N81" t="n">
-        <v>41.67654869255071</v>
+        <v>41.67878755925236</v>
       </c>
       <c r="O81" t="n">
-        <v>-2.578596458522864</v>
+        <v>-2.564237094651779</v>
       </c>
       <c r="P81" t="n">
-        <v>12.93257559030168</v>
+        <v>13.74200828617338</v>
       </c>
       <c r="Q81" t="n">
-        <v>-87.06742440969832</v>
+        <v>-86.25799171382663</v>
       </c>
       <c r="R81" t="n">
-        <v>-88.69295019298963</v>
+        <v>-88.11386755566063</v>
       </c>
       <c r="S81" t="n">
-        <v>-17.37770238579126</v>
+        <v>-17.09030156718813</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -19515,52 +19507,52 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1666.400024414062</v>
+        <v>1668.199951171875</v>
       </c>
       <c r="E89" t="n">
-        <v>-2.504091269629849</v>
+        <v>-2.398783124928672</v>
       </c>
       <c r="F89" t="n">
-        <v>-15.89360604923599</v>
+        <v>-15.80276030586274</v>
       </c>
       <c r="G89" t="n">
-        <v>-38.7825588835309</v>
+        <v>-38.71643615867731</v>
       </c>
       <c r="H89" t="n">
-        <v>78.35813402400682</v>
+        <v>78.55078379188964</v>
       </c>
       <c r="I89" t="n">
-        <v>40.11689551145322</v>
+        <v>40.1710639961839</v>
       </c>
       <c r="J89" t="n">
         <v>14.68560438856163</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.01458742152350535</v>
+        <v>-0.01254035088734602</v>
       </c>
       <c r="L89" t="n">
-        <v>1924.266278479479</v>
+        <v>1924.437700075461</v>
       </c>
       <c r="M89" t="n">
-        <v>1786.340542996473</v>
+        <v>1786.411128359524</v>
       </c>
       <c r="N89" t="n">
-        <v>1319.20161022038</v>
+        <v>1319.219519939363</v>
       </c>
       <c r="O89" t="n">
-        <v>-63.60021478903309</v>
+        <v>-63.48534766830653</v>
       </c>
       <c r="P89" t="n">
-        <v>3.523432795715612</v>
+        <v>3.850335527021742</v>
       </c>
       <c r="Q89" t="n">
-        <v>-96.47656720428439</v>
+        <v>-96.14966447297826</v>
       </c>
       <c r="R89" t="n">
-        <v>-115.0313556031713</v>
+        <v>-114.8263965855805</v>
       </c>
       <c r="S89" t="n">
-        <v>-20.75328201829104</v>
+        <v>-20.6676853511797</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -19879,52 +19871,52 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3.204999923706055</v>
+        <v>3.197999954223633</v>
       </c>
       <c r="E93" t="n">
-        <v>2.724360296947292</v>
+        <v>2.500002292486414</v>
       </c>
       <c r="F93" t="n">
-        <v>8.277023054109733</v>
+        <v>8.040537601670227</v>
       </c>
       <c r="G93" t="n">
-        <v>-39.24170870592545</v>
+        <v>-39.37440954679499</v>
       </c>
       <c r="H93" t="n">
-        <v>-9.129572759578487</v>
+        <v>-9.328040850898144</v>
       </c>
       <c r="I93" t="n">
-        <v>50.16615831091163</v>
+        <v>50.05983166202966</v>
       </c>
       <c r="J93" t="n">
         <v>34.50375736356138</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7109513868427686</v>
+        <v>0.7044121241449058</v>
       </c>
       <c r="L93" t="n">
-        <v>3.133655631728571</v>
+        <v>3.13298896796834</v>
       </c>
       <c r="M93" t="n">
-        <v>3.288074672895228</v>
+        <v>3.287800164288074</v>
       </c>
       <c r="N93" t="n">
-        <v>3.341680105117906</v>
+        <v>3.34161045368027</v>
       </c>
       <c r="O93" t="n">
-        <v>0.05837966778919401</v>
+        <v>0.05793294609003083</v>
       </c>
       <c r="P93" t="n">
-        <v>79.0799548440891</v>
+        <v>78.31325489978975</v>
       </c>
       <c r="Q93" t="n">
-        <v>-20.92004515591089</v>
+        <v>-21.68674510021024</v>
       </c>
       <c r="R93" t="n">
-        <v>18.89858352993632</v>
+        <v>18.66032894720463</v>
       </c>
       <c r="S93" t="n">
-        <v>-26.38953017194173</v>
+        <v>-26.55030117183222</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -19945,7 +19937,7 @@
         <v>44</v>
       </c>
       <c r="X93" t="n">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -20063,52 +20055,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1262</v>
+        <v>1264.5</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.112674480110731</v>
+        <v>-0.9167804121236189</v>
       </c>
       <c r="F95" t="n">
-        <v>-11.30789385433595</v>
+        <v>-11.13219633819953</v>
       </c>
       <c r="G95" t="n">
-        <v>-37.21393034825871</v>
+        <v>-37.08955223880596</v>
       </c>
       <c r="H95" t="n">
-        <v>40.7225710501838</v>
+        <v>41.00134001026736</v>
       </c>
       <c r="I95" t="n">
-        <v>39.40209807080943</v>
+        <v>39.50071006296046</v>
       </c>
       <c r="J95" t="n">
         <v>31.55879434703814</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1353500132122973</v>
+        <v>0.1385264987570213</v>
       </c>
       <c r="L95" t="n">
-        <v>1447.255220395934</v>
+        <v>1447.493315634029</v>
       </c>
       <c r="M95" t="n">
-        <v>1418.733969964431</v>
+        <v>1418.832009180117</v>
       </c>
       <c r="N95" t="n">
-        <v>1369.708208679064</v>
+        <v>1369.733084300954</v>
       </c>
       <c r="O95" t="n">
-        <v>-42.78878722949317</v>
+        <v>-42.62924306994915</v>
       </c>
       <c r="P95" t="n">
-        <v>14.79060256522015</v>
+        <v>15.39578294472853</v>
       </c>
       <c r="Q95" t="n">
-        <v>-85.20939743477985</v>
+        <v>-84.60421705527146</v>
       </c>
       <c r="R95" t="n">
-        <v>-87.89682138281798</v>
+        <v>-87.60015592305483</v>
       </c>
       <c r="S95" t="n">
-        <v>-25.25025389438485</v>
+        <v>-25.10217595043553</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -20247,52 +20239,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>63151.6484375</v>
+        <v>63074.69921875</v>
       </c>
       <c r="E97" t="n">
-        <v>-3.893980345338699</v>
+        <v>-4.011083909736035</v>
       </c>
       <c r="F97" t="n">
-        <v>-18.4396521950403</v>
+        <v>-18.53903210355973</v>
       </c>
       <c r="G97" t="n">
-        <v>-27.05321712977352</v>
+        <v>-27.142101554663</v>
       </c>
       <c r="H97" t="n">
-        <v>-24.53645680316911</v>
+        <v>-24.62840785807862</v>
       </c>
       <c r="I97" t="n">
-        <v>35.47426958842848</v>
+        <v>35.42066016239342</v>
       </c>
       <c r="J97" t="n">
         <v>29.63618508237403</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1533163819542119</v>
+        <v>0.1503990096608305</v>
       </c>
       <c r="L97" t="n">
-        <v>74167.95056028626</v>
+        <v>74160.62206326246</v>
       </c>
       <c r="M97" t="n">
-        <v>82373.9525321376</v>
+        <v>82370.93491571603</v>
       </c>
       <c r="N97" t="n">
-        <v>68849.66678890552</v>
+        <v>68848.90112503737</v>
       </c>
       <c r="O97" t="n">
-        <v>20.06723234942729</v>
+        <v>15.15651297619843</v>
       </c>
       <c r="P97" t="n">
-        <v>17.06996773668411</v>
+        <v>16.74505844788067</v>
       </c>
       <c r="Q97" t="n">
-        <v>-82.93003226331589</v>
+        <v>-83.25494155211933</v>
       </c>
       <c r="R97" t="n">
-        <v>-42.83743234752379</v>
+        <v>-42.98366168572247</v>
       </c>
       <c r="S97" t="n">
-        <v>-17.95764401923569</v>
+        <v>-18.05761124658965</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -20431,52 +20423,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>69.20999908447266</v>
+        <v>69.18000030517578</v>
       </c>
       <c r="E99" t="n">
-        <v>-2.748755506870038</v>
+        <v>-2.790908644545065</v>
       </c>
       <c r="F99" t="n">
-        <v>-18.74180889660312</v>
+        <v>-18.77702991341022</v>
       </c>
       <c r="G99" t="n">
-        <v>-41.72911181518566</v>
+        <v>-41.75436908345921</v>
       </c>
       <c r="H99" t="n">
-        <v>-46.17392206246096</v>
+        <v>-46.19725274666592</v>
       </c>
       <c r="I99" t="n">
-        <v>33.88490520977793</v>
+        <v>33.87403433914288</v>
       </c>
       <c r="J99" t="n">
         <v>40.75210913078011</v>
       </c>
       <c r="K99" t="n">
-        <v>0.02054178674136967</v>
+        <v>0.01973735972814835</v>
       </c>
       <c r="L99" t="n">
-        <v>89.28377786288574</v>
+        <v>89.28092083628604</v>
       </c>
       <c r="M99" t="n">
-        <v>116.4874056886386</v>
+        <v>116.4862292659211</v>
       </c>
       <c r="N99" t="n">
-        <v>114.5937573814386</v>
+        <v>114.5934588861222</v>
       </c>
       <c r="O99" t="n">
-        <v>1.220456336614308</v>
+        <v>1.218541884602196</v>
       </c>
       <c r="P99" t="n">
-        <v>23.23599791346356</v>
+        <v>23.15674500315641</v>
       </c>
       <c r="Q99" t="n">
-        <v>-76.76400208653644</v>
+        <v>-76.84325499684358</v>
       </c>
       <c r="R99" t="n">
-        <v>-29.85957720986314</v>
+        <v>-29.88217953124724</v>
       </c>
       <c r="S99" t="n">
-        <v>-31.37368481573046</v>
+        <v>-31.40343059972706</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -20601,66 +20593,66 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1705.510009765625</v>
+        <v>278.6099853515625</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.107684354055827</v>
+        <v>-2.176894161082155</v>
       </c>
       <c r="F101" t="n">
-        <v>-19.8404903822046</v>
+        <v>0.8032022090048274</v>
       </c>
       <c r="G101" t="n">
-        <v>-39.43291344775972</v>
+        <v>-9.90784628890461</v>
       </c>
       <c r="H101" t="n">
-        <v>6.815631438717751</v>
+        <v>-10.09680837727723</v>
       </c>
       <c r="I101" t="n">
-        <v>32.67289597582811</v>
+        <v>36.38517283300568</v>
       </c>
       <c r="J101" t="n">
-        <v>28.48067893451241</v>
+        <v>33.09778727265918</v>
       </c>
       <c r="K101" t="n">
-        <v>0.0696959556479385</v>
+        <v>0.2163633292060131</v>
       </c>
       <c r="L101" t="n">
-        <v>2173.246966830176</v>
+        <v>294.918187375925</v>
       </c>
       <c r="M101" t="n">
-        <v>2563.411696602589</v>
+        <v>301.2806953192116</v>
       </c>
       <c r="N101" t="n">
-        <v>2518.609859220364</v>
+        <v>284.4536564567983</v>
       </c>
       <c r="O101" t="n">
-        <v>-10.03802797677537</v>
+        <v>-2.811390514550959</v>
       </c>
       <c r="P101" t="n">
-        <v>20.76686855932917</v>
+        <v>11.5279349887979</v>
       </c>
       <c r="Q101" t="n">
-        <v>-79.23313144067083</v>
+        <v>-88.4720650112021</v>
       </c>
       <c r="R101" t="n">
-        <v>-42.53409208399877</v>
+        <v>-78.26880543074529</v>
       </c>
       <c r="S101" t="n">
-        <v>-24.79998027898773</v>
+        <v>-11.55238560267857</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -20669,7 +20661,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>Doji, Bearish Harami</t>
+          <t>Bearish Harami</t>
         </is>
       </c>
       <c r="V101" t="inlineStr"/>
@@ -20677,7 +20669,7 @@
         <v>39.5</v>
       </c>
       <c r="X101" t="n">
-        <v>75.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
@@ -20686,90 +20678,94 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); RSI scarico (33) — zona di interesse long; doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 33); RSI scarico (36) — zona di interesse long; segnale candlestick: Bearish Harami</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>NEXI</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Nexi</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>278.6099853515625</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.176894161082155</v>
+        <v>2.503683022813319</v>
       </c>
       <c r="F102" t="n">
-        <v>0.8032022090048274</v>
+        <v>-5.869624183447009</v>
       </c>
       <c r="G102" t="n">
-        <v>-9.90784628890461</v>
+        <v>-6.249996788542756</v>
       </c>
       <c r="H102" t="n">
-        <v>-10.09680837727723</v>
+        <v>-22.99181283587791</v>
       </c>
       <c r="I102" t="n">
-        <v>36.38517283300568</v>
+        <v>46.23591235409716</v>
       </c>
       <c r="J102" t="n">
-        <v>33.09778727265918</v>
+        <v>24.07881149398846</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2163633292060131</v>
+        <v>0.5498737647113203</v>
       </c>
       <c r="L102" t="n">
-        <v>294.918187375925</v>
+        <v>3.575989751655031</v>
       </c>
       <c r="M102" t="n">
-        <v>301.2806953192116</v>
+        <v>3.995828835583944</v>
       </c>
       <c r="N102" t="n">
-        <v>284.4536564567983</v>
+        <v>6.118809807401441</v>
       </c>
       <c r="O102" t="n">
-        <v>-2.811390514550959</v>
+        <v>0.04129626934034622</v>
       </c>
       <c r="P102" t="n">
-        <v>11.5279349887979</v>
+        <v>47.13010492089536</v>
       </c>
       <c r="Q102" t="n">
-        <v>-88.4720650112021</v>
+        <v>-52.86989507910464</v>
       </c>
       <c r="R102" t="n">
-        <v>-78.26880543074529</v>
+        <v>14.06188572754478</v>
       </c>
       <c r="S102" t="n">
-        <v>-11.55238560267857</v>
+        <v>-3.467406361682235</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bearish</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W102" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="X102" t="n">
-        <v>70.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -20778,94 +20774,90 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 33); RSI scarico (36) — zona di interesse long; segnale candlestick: Bearish Harami</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 24); pattern: Bull Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NEXI</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Nexi</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>3.480000019073486</v>
+        <v>275.1000061035156</v>
       </c>
       <c r="E103" t="n">
-        <v>2.503683022813319</v>
+        <v>6.959561837841566</v>
       </c>
       <c r="F103" t="n">
-        <v>-5.869624183447009</v>
+        <v>-3.338018199670956</v>
       </c>
       <c r="G103" t="n">
-        <v>-6.249996788542756</v>
+        <v>-21.60159279322467</v>
       </c>
       <c r="H103" t="n">
-        <v>-22.99181283587791</v>
+        <v>-23.09197743490934</v>
       </c>
       <c r="I103" t="n">
-        <v>46.23591235409716</v>
+        <v>41.64773405802849</v>
       </c>
       <c r="J103" t="n">
-        <v>24.07881149398846</v>
+        <v>12.93267592899167</v>
       </c>
       <c r="K103" t="n">
-        <v>0.5498737647113203</v>
+        <v>0.3123059634501504</v>
       </c>
       <c r="L103" t="n">
-        <v>3.575989751655031</v>
+        <v>292.6120040713739</v>
       </c>
       <c r="M103" t="n">
-        <v>3.995828835583944</v>
+        <v>316.5481923082561</v>
       </c>
       <c r="N103" t="n">
-        <v>6.118809807401441</v>
+        <v>274.1383963038507</v>
       </c>
       <c r="O103" t="n">
-        <v>0.04129626934034622</v>
+        <v>-1.32625413351585</v>
       </c>
       <c r="P103" t="n">
-        <v>47.13010492089536</v>
+        <v>42.18751024454792</v>
       </c>
       <c r="Q103" t="n">
-        <v>-52.86989507910464</v>
+        <v>-57.81248975545208</v>
       </c>
       <c r="R103" t="n">
-        <v>14.06188572754478</v>
+        <v>-25.97862784162916</v>
       </c>
       <c r="S103" t="n">
-        <v>-3.467406361682235</v>
+        <v>-17.20090109751222</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W103" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="X103" t="n">
-        <v>69.3</v>
+        <v>74.5</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -20874,90 +20866,94 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 24); pattern: Bull Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 13); pattern: Bear Flag / Consolidation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>US Treasury 7-10Y ETF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>275.1000061035156</v>
+        <v>94.36000061035156</v>
       </c>
       <c r="E104" t="n">
-        <v>6.959561837841566</v>
+        <v>0.1911237041755331</v>
       </c>
       <c r="F104" t="n">
-        <v>-3.338018199670956</v>
+        <v>0.9089920379669936</v>
       </c>
       <c r="G104" t="n">
-        <v>-21.60159279322467</v>
+        <v>-1.657109315749439</v>
       </c>
       <c r="H104" t="n">
-        <v>-23.09197743490934</v>
+        <v>0.9089920379669936</v>
       </c>
       <c r="I104" t="n">
-        <v>41.64773405802849</v>
+        <v>44.41699164986338</v>
       </c>
       <c r="J104" t="n">
-        <v>12.93267592899167</v>
+        <v>34.43607688912962</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3123059634501504</v>
+        <v>0.3093326681572698</v>
       </c>
       <c r="L104" t="n">
-        <v>292.6120040713739</v>
+        <v>94.98287325280597</v>
       </c>
       <c r="M104" t="n">
-        <v>316.5481923082561</v>
+        <v>95.38234178051606</v>
       </c>
       <c r="N104" t="n">
-        <v>274.1383963038507</v>
+        <v>97.44879453357419</v>
       </c>
       <c r="O104" t="n">
-        <v>-1.32625413351585</v>
+        <v>-0.1199814128939863</v>
       </c>
       <c r="P104" t="n">
-        <v>42.18751024454792</v>
+        <v>42.34242903292322</v>
       </c>
       <c r="Q104" t="n">
-        <v>-57.81248975545208</v>
+        <v>-57.65757096707677</v>
       </c>
       <c r="R104" t="n">
-        <v>-25.97862784162916</v>
+        <v>-65.4925005923772</v>
       </c>
       <c r="S104" t="n">
-        <v>-17.20090109751222</v>
+        <v>-1.646864489105726</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr"/>
+          <t>Trend Bearish</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W104" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="X104" t="n">
-        <v>74.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20966,94 +20962,90 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 13); pattern: Bear Flag / Consolidation</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 34); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US Treasury 7-10Y ETF</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>94.36000061035156</v>
+        <v>1702.2900390625</v>
       </c>
       <c r="E105" t="n">
-        <v>0.1911237041755331</v>
+        <v>-1.294391179181931</v>
       </c>
       <c r="F105" t="n">
-        <v>0.9089920379669936</v>
+        <v>-19.99183002317313</v>
       </c>
       <c r="G105" t="n">
-        <v>-1.657109315749439</v>
+        <v>-39.54726296383125</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9089920379669936</v>
+        <v>6.613965542945177</v>
       </c>
       <c r="I105" t="n">
-        <v>44.41699164986338</v>
+        <v>32.61634461920802</v>
       </c>
       <c r="J105" t="n">
-        <v>34.43607688912962</v>
+        <v>28.48067893451241</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3093326681572698</v>
+        <v>0.06654307770343193</v>
       </c>
       <c r="L105" t="n">
-        <v>94.98287325280597</v>
+        <v>2172.940302953688</v>
       </c>
       <c r="M105" t="n">
-        <v>95.38234178051606</v>
+        <v>2563.285423241682</v>
       </c>
       <c r="N105" t="n">
-        <v>97.44879453357419</v>
+        <v>2518.57781971088</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.1199814128939863</v>
+        <v>-10.24351898460986</v>
       </c>
       <c r="P105" t="n">
-        <v>42.34242903292322</v>
+        <v>20.43085211340179</v>
       </c>
       <c r="Q105" t="n">
-        <v>-57.65757096707677</v>
+        <v>-79.5691478865982</v>
       </c>
       <c r="R105" t="n">
-        <v>-65.4925005923772</v>
+        <v>-42.66146425061854</v>
       </c>
       <c r="S105" t="n">
-        <v>-1.646864489105726</v>
+        <v>-24.94195649665259</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+          <t>Bearish Harami</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr"/>
       <c r="W105" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="X105" t="n">
-        <v>75.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -21062,7 +21054,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 34); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>trend in sviluppo (ADX 28); RSI scarico (33) — zona di interesse long; segnale candlestick: Bearish Harami</t>
         </is>
       </c>
     </row>
@@ -21083,52 +21075,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.135599970817566</v>
+        <v>1.13289999961853</v>
       </c>
       <c r="E106" t="n">
-        <v>-4.235776889666754</v>
+        <v>-4.463463267740342</v>
       </c>
       <c r="F106" t="n">
-        <v>-18.94031822090644</v>
+        <v>-19.13304348669609</v>
       </c>
       <c r="G106" t="n">
-        <v>-38.0477997093884</v>
+        <v>-38.19509555369977</v>
       </c>
       <c r="H106" t="n">
-        <v>-46.43899041905892</v>
+        <v>-46.56633559955915</v>
       </c>
       <c r="I106" t="n">
-        <v>31.20895801920994</v>
+        <v>31.13452181864753</v>
       </c>
       <c r="J106" t="n">
         <v>27.33735214824244</v>
       </c>
       <c r="K106" t="n">
-        <v>-0.06352124522745831</v>
+        <v>-0.06828720843691453</v>
       </c>
       <c r="L106" t="n">
-        <v>1.429341854114031</v>
+        <v>1.429084713999837</v>
       </c>
       <c r="M106" t="n">
-        <v>1.726507791820456</v>
+        <v>1.726401910596965</v>
       </c>
       <c r="N106" t="n">
-        <v>1.403911717106033</v>
+        <v>1.403884851720968</v>
       </c>
       <c r="O106" t="n">
-        <v>0.01098798092502998</v>
+        <v>0.01081567507073247</v>
       </c>
       <c r="P106" t="n">
-        <v>14.79605278210873</v>
+        <v>14.30250890433869</v>
       </c>
       <c r="Q106" t="n">
-        <v>-85.20394721789127</v>
+        <v>-85.69749109566131</v>
       </c>
       <c r="R106" t="n">
-        <v>-34.68370389461433</v>
+        <v>-34.8417272856151</v>
       </c>
       <c r="S106" t="n">
-        <v>-28.63884755456979</v>
+        <v>-28.80851386425977</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -21137,12 +21129,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>Shooting Star, Bearish Engulfing, Dark Cloud Cover</t>
+          <t>Bearish Engulfing, Dark Cloud Cover</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="X106" t="n">
         <v>73.8</v>
@@ -21154,7 +21146,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); RSI scarico (31) — zona di interesse long; shooting star — rifiuto di resistenza; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 27); RSI scarico (31) — zona di interesse long; candela di inversione bearish (engulfing); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -21819,52 +21811,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.9670000076293945</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.767356435091706</v>
+        <v>-3.471215098790492</v>
       </c>
       <c r="F114" t="n">
-        <v>-22.54972483987742</v>
+        <v>-23.11038065646967</v>
       </c>
       <c r="G114" t="n">
-        <v>-46.91637227874541</v>
+        <v>-47.3006400503732</v>
       </c>
       <c r="H114" t="n">
-        <v>-73.62073449869573</v>
+        <v>-73.81169171105115</v>
       </c>
       <c r="I114" t="n">
-        <v>29.5788181741691</v>
+        <v>29.44836493776469</v>
       </c>
       <c r="J114" t="n">
         <v>26.52166259263409</v>
       </c>
       <c r="K114" t="n">
-        <v>0.01874725168663853</v>
+        <v>0.01023870914419332</v>
       </c>
       <c r="L114" t="n">
-        <v>1.370389693587353</v>
+        <v>1.36972302415049</v>
       </c>
       <c r="M114" t="n">
-        <v>2.240299399317426</v>
+        <v>2.240024888372835</v>
       </c>
       <c r="N114" t="n">
-        <v>5.47183606203936</v>
+        <v>5.471766410008643</v>
       </c>
       <c r="O114" t="n">
-        <v>0.04416178867426185</v>
+        <v>0.04371506317126939</v>
       </c>
       <c r="P114" t="n">
-        <v>9.799611577139522</v>
+        <v>8.877725453754625</v>
       </c>
       <c r="Q114" t="n">
-        <v>-90.20038842286047</v>
+        <v>-91.12227454624538</v>
       </c>
       <c r="R114" t="n">
-        <v>-41.36453671462964</v>
+        <v>-41.66484553178141</v>
       </c>
       <c r="S114" t="n">
-        <v>-35.39891871538858</v>
+        <v>-35.86656033325871</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -21890,7 +21882,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 27); RSI scarico (30) — zona di interesse long; candela di inversione bearish (engulfing)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 27); RSI scarico (29) — zona di interesse long; candela di inversione bearish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -21999,52 +21991,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.110000133514404</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="E116" t="n">
-        <v>-9.825747264919615</v>
+        <v>-11.30159284213311</v>
       </c>
       <c r="F116" t="n">
-        <v>-33.44226655341698</v>
+        <v>-34.53159009707947</v>
       </c>
       <c r="G116" t="n">
-        <v>-46.79956176148037</v>
+        <v>-47.67027184887979</v>
       </c>
       <c r="H116" t="n">
-        <v>-68.80523525591025</v>
+        <v>-69.31578737232242</v>
       </c>
       <c r="I116" t="n">
-        <v>29.33695684762591</v>
+        <v>29.08252556054356</v>
       </c>
       <c r="J116" t="n">
         <v>40.64460376582078</v>
       </c>
       <c r="K116" t="n">
-        <v>-0.147345135007135</v>
+        <v>-0.1615493201299669</v>
       </c>
       <c r="L116" t="n">
-        <v>9.415063305466276</v>
+        <v>9.405539505025079</v>
       </c>
       <c r="M116" t="n">
-        <v>13.86990033937829</v>
+        <v>13.86597877449073</v>
       </c>
       <c r="N116" t="n">
-        <v>21.82541288845978</v>
+        <v>21.82441786453309</v>
       </c>
       <c r="O116" t="n">
-        <v>0.1220335519101132</v>
+        <v>0.1156517916144741</v>
       </c>
       <c r="P116" t="n">
-        <v>2.956657975731054</v>
+        <v>0.7541852914754125</v>
       </c>
       <c r="Q116" t="n">
-        <v>-97.04334202426895</v>
+        <v>-99.24581470852459</v>
       </c>
       <c r="R116" t="n">
-        <v>-62.31780318117666</v>
+        <v>-63.07386301606874</v>
       </c>
       <c r="S116" t="n">
-        <v>-38.38205762472566</v>
+        <v>-39.39053360288219</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22070,7 +22062,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); RSI scarico (29) — zona di interesse long; breakdown minimi 50g — rottura supporto importante</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); RSI scarico (29) — zona di interesse long; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (5.9758)</t>
         </is>
       </c>
     </row>
@@ -22501,52 +22493,52 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4169.5</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.573621313452474</v>
+        <v>-8.499070225989481</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.54882185922265</v>
+        <v>-11.47669681596367</v>
       </c>
       <c r="G4" t="n">
-        <v>58.16925934288657</v>
+        <v>58.29823404861845</v>
       </c>
       <c r="H4" t="n">
-        <v>135.9248506084037</v>
+        <v>136.1172289397462</v>
       </c>
       <c r="I4" t="n">
-        <v>61.57674502575817</v>
+        <v>61.65659627417211</v>
       </c>
       <c r="J4" t="n">
         <v>87.90305422329666</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6340610385398573</v>
+        <v>0.6350786732612603</v>
       </c>
       <c r="L4" t="n">
-        <v>3860.838248575097</v>
+        <v>3861.162048798311</v>
       </c>
       <c r="M4" t="n">
-        <v>3043.151363535156</v>
+        <v>3043.284693038832</v>
       </c>
       <c r="N4" t="n">
-        <v>2333.882875299472</v>
+        <v>2333.940500762926</v>
       </c>
       <c r="O4" t="n">
-        <v>19.80608803119082</v>
+        <v>20.02306185597752</v>
       </c>
       <c r="P4" t="n">
-        <v>42.43864444628728</v>
+        <v>42.57678446229351</v>
       </c>
       <c r="Q4" t="n">
-        <v>-57.56135555371272</v>
+        <v>-57.42321553770649</v>
       </c>
       <c r="R4" t="n">
-        <v>37.35095332574027</v>
+        <v>37.42845663294439</v>
       </c>
       <c r="S4" t="n">
-        <v>52.26600174018063</v>
+        <v>52.39016279934599</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -22593,52 +22585,52 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1666.400024414062</v>
+        <v>1668.199951171875</v>
       </c>
       <c r="E5" t="n">
-        <v>-13.30766482445613</v>
+        <v>-13.21402593133707</v>
       </c>
       <c r="F5" t="n">
-        <v>-20.75328201829104</v>
+        <v>-20.6676853511797</v>
       </c>
       <c r="G5" t="n">
-        <v>70.21450709030262</v>
+        <v>70.39836069171348</v>
       </c>
       <c r="H5" t="n">
-        <v>38.52036778171759</v>
+        <v>38.66998762858478</v>
       </c>
       <c r="I5" t="n">
-        <v>55.196813650888</v>
+        <v>55.25149501522444</v>
       </c>
       <c r="J5" t="n">
         <v>70.91188215878482</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5982942423897384</v>
+        <v>0.5992059368580401</v>
       </c>
       <c r="L5" t="n">
-        <v>1594.468744574802</v>
+        <v>1594.640166170784</v>
       </c>
       <c r="M5" t="n">
-        <v>1300.438166759076</v>
+        <v>1300.508752122127</v>
       </c>
       <c r="N5" t="n">
-        <v>1131.819778108748</v>
+        <v>1131.850285341931</v>
       </c>
       <c r="O5" t="n">
-        <v>24.41749964984379</v>
+        <v>24.53236677057035</v>
       </c>
       <c r="P5" t="n">
-        <v>37.41094838504363</v>
+        <v>37.50593634486073</v>
       </c>
       <c r="Q5" t="n">
-        <v>-62.58905161495637</v>
+        <v>-62.49406365513927</v>
       </c>
       <c r="R5" t="n">
-        <v>44.11097221509235</v>
+        <v>44.20682834357888</v>
       </c>
       <c r="S5" t="n">
-        <v>68.05164032294222</v>
+        <v>68.23315774953844</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -22863,79 +22855,87 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>FTSE 100</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>173.6399993896484</v>
+        <v>10363.26953125</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8479537553567118</v>
+        <v>-0.4422033595071539</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7017379604848495</v>
+        <v>1.367139739326073</v>
       </c>
       <c r="G8" t="n">
-        <v>19.25823633976878</v>
+        <v>25.81364005402453</v>
       </c>
       <c r="H8" t="n">
-        <v>12.28660118662148</v>
+        <v>48.68819509392854</v>
       </c>
       <c r="I8" t="n">
-        <v>66.19446789324152</v>
+        <v>68.3416987607217</v>
       </c>
       <c r="J8" t="n">
-        <v>29.03598171486176</v>
+        <v>23.23692819656796</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7980265199491641</v>
+        <v>0.7904913379379708</v>
       </c>
       <c r="L8" t="n">
-        <v>155.998135704909</v>
+        <v>9556.722143592344</v>
       </c>
       <c r="M8" t="n">
-        <v>143.99881482463</v>
+        <v>8662.946166041535</v>
       </c>
       <c r="N8" t="n">
-        <v>126.3944411069018</v>
+        <v>7750.474458296037</v>
       </c>
       <c r="O8" t="n">
-        <v>2.517589548448935</v>
+        <v>67.52649631752195</v>
       </c>
       <c r="P8" t="n">
-        <v>90.53478457521518</v>
+        <v>76.82515512912944</v>
       </c>
       <c r="Q8" t="n">
-        <v>-9.465215424784809</v>
+        <v>-23.17484487087057</v>
       </c>
       <c r="R8" t="n">
-        <v>101.2117229537083</v>
+        <v>77.04199988055157</v>
       </c>
       <c r="S8" t="n">
-        <v>23.7721916740673</v>
+        <v>27.78226417014134</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Doji, Bearish Engulfing</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W8" t="n">
         <v>71</v>
       </c>
       <c r="X8" t="n">
-        <v>77.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -22944,73 +22944,73 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 29); RSI in forza (66) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 23); RSI in forza (68) — momentum positivo; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.63999938964844</v>
+        <v>173.6399993896484</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.950294140579458</v>
+        <v>0.8479537553567118</v>
       </c>
       <c r="F9" t="n">
-        <v>25.62405433939534</v>
+        <v>0.7017379604848495</v>
       </c>
       <c r="G9" t="n">
-        <v>58.16400479639208</v>
+        <v>19.25823633976878</v>
       </c>
       <c r="H9" t="n">
-        <v>117.9254655044581</v>
+        <v>12.28660118662148</v>
       </c>
       <c r="I9" t="n">
-        <v>66.75676230900071</v>
+        <v>66.19446789324152</v>
       </c>
       <c r="J9" t="n">
-        <v>37.51910523510585</v>
+        <v>29.03598171486176</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8306682100940692</v>
+        <v>0.7980265199491641</v>
       </c>
       <c r="L9" t="n">
-        <v>17.8894013076482</v>
+        <v>155.998135704909</v>
       </c>
       <c r="M9" t="n">
-        <v>15.57977426313369</v>
+        <v>143.99881482463</v>
       </c>
       <c r="N9" t="n">
-        <v>14.86010837629611</v>
+        <v>126.3944411069018</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8226479729349681</v>
+        <v>2.517589548448935</v>
       </c>
       <c r="P9" t="n">
-        <v>73.24189108347331</v>
+        <v>90.53478457521518</v>
       </c>
       <c r="Q9" t="n">
-        <v>-26.75810891652669</v>
+        <v>-9.465215424784809</v>
       </c>
       <c r="R9" t="n">
-        <v>158.6804264422274</v>
+        <v>101.2117229537083</v>
       </c>
       <c r="S9" t="n">
-        <v>54.4390469600202</v>
+        <v>23.7721916740673</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>71</v>
       </c>
       <c r="X9" t="n">
-        <v>72.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -23032,94 +23032,86 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 38); RSI in forza (67) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 29); RSI in forza (66) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FTSE 100</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10356.900390625</v>
+        <v>21.63999938964844</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5033903821167973</v>
+        <v>-3.950294140579458</v>
       </c>
       <c r="F10" t="n">
-        <v>1.304840716241995</v>
+        <v>25.62405433939534</v>
       </c>
       <c r="G10" t="n">
-        <v>25.73631650631298</v>
+        <v>58.16400479639208</v>
       </c>
       <c r="H10" t="n">
-        <v>48.59681312022082</v>
+        <v>117.9254655044581</v>
       </c>
       <c r="I10" t="n">
-        <v>68.20516364800061</v>
+        <v>66.75676230900071</v>
       </c>
       <c r="J10" t="n">
-        <v>23.23692819656796</v>
+        <v>37.51910523510585</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7887969497086954</v>
+        <v>0.8306682100940692</v>
       </c>
       <c r="L10" t="n">
-        <v>9556.115558770915</v>
+        <v>17.8894013076482</v>
       </c>
       <c r="M10" t="n">
-        <v>8662.696395820945</v>
+        <v>15.57977426313369</v>
       </c>
       <c r="N10" t="n">
-        <v>7750.384752090052</v>
+        <v>14.86010837629611</v>
       </c>
       <c r="O10" t="n">
-        <v>67.12003264230793</v>
+        <v>0.8226479729349681</v>
       </c>
       <c r="P10" t="n">
-        <v>76.56693980795779</v>
+        <v>73.24189108347331</v>
       </c>
       <c r="Q10" t="n">
-        <v>-23.4330601920422</v>
+        <v>-26.75810891652669</v>
       </c>
       <c r="R10" t="n">
-        <v>76.89764924735215</v>
+        <v>158.6804264422274</v>
       </c>
       <c r="S10" t="n">
-        <v>27.70373072976074</v>
+        <v>54.4390469600202</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Doji, Bearish Engulfing</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Outside Bar</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="n">
-        <v>70.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="X10" t="n">
-        <v>77.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -23128,7 +23120,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 23); RSI in forza (68) — momentum positivo; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 38); RSI in forza (67) — momentum positivo</t>
         </is>
       </c>
     </row>
@@ -23149,52 +23141,52 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>64.68499755859375</v>
+        <v>64.91000366210938</v>
       </c>
       <c r="E11" t="n">
-        <v>-14.45593544234064</v>
+        <v>-14.15837128725857</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.37770238579126</v>
+        <v>-17.09030156718813</v>
       </c>
       <c r="G11" t="n">
-        <v>107.5632090780101</v>
+        <v>108.2852155813812</v>
       </c>
       <c r="H11" t="n">
-        <v>150.2030555646137</v>
+        <v>151.0733843385972</v>
       </c>
       <c r="I11" t="n">
-        <v>60.04769050114141</v>
+        <v>60.22976471773609</v>
       </c>
       <c r="J11" t="n">
         <v>64.4098855493549</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6702072596066355</v>
+        <v>0.6727567254014117</v>
       </c>
       <c r="L11" t="n">
-        <v>55.86973562163587</v>
+        <v>55.89116477435164</v>
       </c>
       <c r="M11" t="n">
-        <v>41.01897292004769</v>
+        <v>41.02779668881301</v>
       </c>
       <c r="N11" t="n">
-        <v>30.60205246248024</v>
+        <v>30.60586612525169</v>
       </c>
       <c r="O11" t="n">
-        <v>1.913263734614123</v>
+        <v>1.92762309848521</v>
       </c>
       <c r="P11" t="n">
-        <v>36.82418877666007</v>
+        <v>37.07526961637701</v>
       </c>
       <c r="Q11" t="n">
-        <v>-63.17581122333993</v>
+        <v>-62.92473038362299</v>
       </c>
       <c r="R11" t="n">
-        <v>66.97480623431558</v>
+        <v>67.24467875592971</v>
       </c>
       <c r="S11" t="n">
-        <v>98.09817719784648</v>
+        <v>98.78725968446882</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -25349,52 +25341,52 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.33549976348877</v>
+        <v>6.336999893188477</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3773908028274819</v>
+        <v>-0.3538020031434774</v>
       </c>
       <c r="F35" t="n">
-        <v>7.435983376600697</v>
+        <v>7.461422239436621</v>
       </c>
       <c r="G35" t="n">
-        <v>40.91414650546543</v>
+        <v>40.94751238095642</v>
       </c>
       <c r="H35" t="n">
-        <v>41.44897597652075</v>
+        <v>41.48246848978361</v>
       </c>
       <c r="I35" t="n">
-        <v>68.39025396458651</v>
+        <v>68.41804461674975</v>
       </c>
       <c r="J35" t="n">
         <v>57.80266600735187</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9173462229880904</v>
+        <v>0.9177491211651808</v>
       </c>
       <c r="L35" t="n">
-        <v>5.284250901524063</v>
+        <v>5.284393771019273</v>
       </c>
       <c r="M35" t="n">
-        <v>4.621152933965009</v>
+        <v>4.621211762580684</v>
       </c>
       <c r="N35" t="n">
-        <v>3.875233751095698</v>
+        <v>3.875259177022811</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1258241507793538</v>
+        <v>0.1259198855522125</v>
       </c>
       <c r="P35" t="n">
-        <v>86.38899142901074</v>
+        <v>86.45340232219083</v>
       </c>
       <c r="Q35" t="n">
-        <v>-13.61100857098926</v>
+        <v>-13.54659767780918</v>
       </c>
       <c r="R35" t="n">
-        <v>139.3461740320645</v>
+        <v>139.3910826575821</v>
       </c>
       <c r="S35" t="n">
-        <v>46.8760836894274</v>
+        <v>46.910861241877</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -25897,52 +25889,52 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>161.2989959716797</v>
+        <v>161.2680053710938</v>
       </c>
       <c r="E41" t="n">
-        <v>1.27393209316915</v>
+        <v>1.254474191646815</v>
       </c>
       <c r="F41" t="n">
-        <v>5.312671075080022</v>
+        <v>5.292437205016132</v>
       </c>
       <c r="G41" t="n">
-        <v>12.96792376793321</v>
+        <v>12.94621908351516</v>
       </c>
       <c r="H41" t="n">
-        <v>48.11117770337037</v>
+        <v>48.08272089666264</v>
       </c>
       <c r="I41" t="n">
-        <v>62.5028318169111</v>
+        <v>62.4742998115506</v>
       </c>
       <c r="J41" t="n">
         <v>23.75431164910174</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8777162048885921</v>
+        <v>0.8765903030690091</v>
       </c>
       <c r="L41" t="n">
-        <v>153.7398011553171</v>
+        <v>153.736849669547</v>
       </c>
       <c r="M41" t="n">
-        <v>145.3947941586966</v>
+        <v>145.3935788410265</v>
       </c>
       <c r="N41" t="n">
-        <v>131.6618475412502</v>
+        <v>131.6613984021112</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6361617841876974</v>
+        <v>0.6341840364579863</v>
       </c>
       <c r="P41" t="n">
-        <v>99.17216660877254</v>
+        <v>99.01182619130326</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.8278333912274608</v>
+        <v>-0.9881738086967505</v>
       </c>
       <c r="R41" t="n">
-        <v>118.058679361306</v>
+        <v>117.9300613300662</v>
       </c>
       <c r="S41" t="n">
-        <v>5.283805578216838</v>
+        <v>5.263577254121032</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -25968,7 +25960,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (63) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (161.46)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (161.46)</t>
         </is>
       </c>
     </row>
@@ -28013,52 +28005,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>76.38999938964844</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="E64" t="n">
-        <v>-12.55723574182674</v>
+        <v>-12.38553069966683</v>
       </c>
       <c r="F64" t="n">
-        <v>17.14461043112925</v>
+        <v>17.37463884392618</v>
       </c>
       <c r="G64" t="n">
-        <v>12.05809218350211</v>
+        <v>12.27813256770038</v>
       </c>
       <c r="H64" t="n">
-        <v>20.14784081421166</v>
+        <v>20.38376645365641</v>
       </c>
       <c r="I64" t="n">
-        <v>51.18926311045608</v>
+        <v>51.26762836035237</v>
       </c>
       <c r="J64" t="n">
         <v>19.84339967349042</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6090913419899121</v>
+        <v>0.6117611822901408</v>
       </c>
       <c r="L64" t="n">
-        <v>74.83273915349278</v>
+        <v>74.84702501310029</v>
       </c>
       <c r="M64" t="n">
-        <v>73.02294570102598</v>
+        <v>73.02882811380553</v>
       </c>
       <c r="N64" t="n">
-        <v>67.05854295379194</v>
+        <v>67.06108535253566</v>
       </c>
       <c r="O64" t="n">
-        <v>3.040954274432328</v>
+        <v>3.050527021383003</v>
       </c>
       <c r="P64" t="n">
-        <v>33.19379624987484</v>
+        <v>33.42635674135923</v>
       </c>
       <c r="Q64" t="n">
-        <v>-66.80620375012516</v>
+        <v>-66.57364325864077</v>
       </c>
       <c r="R64" t="n">
-        <v>69.54475589629554</v>
+        <v>69.82243543639963</v>
       </c>
       <c r="S64" t="n">
-        <v>10.29453802122857</v>
+        <v>10.51111544146004</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -28068,10 +28060,10 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
-        <v>64.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -28087,83 +28079,79 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>21.10000038146973</v>
+        <v>80.58999633789062</v>
       </c>
       <c r="E65" t="n">
-        <v>-10.47942021779866</v>
+        <v>-12.44976244859379</v>
       </c>
       <c r="F65" t="n">
-        <v>16.25344807130269</v>
+        <v>14.00480061475498</v>
       </c>
       <c r="G65" t="n">
-        <v>43.63513263571632</v>
+        <v>12.28925749946557</v>
       </c>
       <c r="H65" t="n">
-        <v>-9.208259082291182</v>
+        <v>19.83642578125</v>
       </c>
       <c r="I65" t="n">
-        <v>64.79451028886521</v>
+        <v>50.4665631452711</v>
       </c>
       <c r="J65" t="n">
-        <v>46.08311684420929</v>
+        <v>21.75599156738005</v>
       </c>
       <c r="K65" t="n">
-        <v>0.8767058932592894</v>
+        <v>0.580070683960892</v>
       </c>
       <c r="L65" t="n">
-        <v>17.14950937720234</v>
+        <v>80.43401047868542</v>
       </c>
       <c r="M65" t="n">
-        <v>16.33683643934495</v>
+        <v>78.1379981665921</v>
       </c>
       <c r="N65" t="n">
-        <v>14.8715482608863</v>
+        <v>71.74279094365154</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9753885142547463</v>
+        <v>3.25997932953221</v>
       </c>
       <c r="P65" t="n">
-        <v>77.74086294528824</v>
+        <v>32.76702162869712</v>
       </c>
       <c r="Q65" t="n">
-        <v>-22.25913705471175</v>
+        <v>-67.23297837130288</v>
       </c>
       <c r="R65" t="n">
-        <v>136.4138869036161</v>
+        <v>59.99730894669381</v>
       </c>
       <c r="S65" t="n">
-        <v>61.06870051176638</v>
+        <v>10.15581233442358</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
+      <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr"/>
       <c r="W65" t="n">
-        <v>64</v>
+        <v>64.3</v>
       </c>
       <c r="X65" t="n">
-        <v>81.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -28172,19 +28160,19 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 46); RSI in forza (65) — momentum positivo; segnale candlestick: Bearish Harami</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 22); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -28193,69 +28181,69 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>83.30000305175781</v>
+        <v>21.10000038146973</v>
       </c>
       <c r="E66" t="n">
-        <v>0.4703888221231356</v>
+        <v>-10.47942021779866</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.2514657874515214</v>
+        <v>16.25344807130269</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3614494599491813</v>
+        <v>43.63513263571632</v>
       </c>
       <c r="H66" t="n">
-        <v>19.71831109463935</v>
+        <v>-9.208259082291182</v>
       </c>
       <c r="I66" t="n">
-        <v>54.27818860167661</v>
+        <v>64.79451028886521</v>
       </c>
       <c r="J66" t="n">
-        <v>17.79105977111829</v>
+        <v>46.08311684420929</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6518549730383788</v>
+        <v>0.8767058932592894</v>
       </c>
       <c r="L66" t="n">
-        <v>81.25350165423184</v>
+        <v>17.14950937720234</v>
       </c>
       <c r="M66" t="n">
-        <v>77.3038446421815</v>
+        <v>16.33683643934495</v>
       </c>
       <c r="N66" t="n">
-        <v>66.94187177391723</v>
+        <v>14.8715482608863</v>
       </c>
       <c r="O66" t="n">
-        <v>0.05234235641232687</v>
+        <v>0.9753885142547463</v>
       </c>
       <c r="P66" t="n">
-        <v>54.33913024877538</v>
+        <v>77.74086294528824</v>
       </c>
       <c r="Q66" t="n">
-        <v>-45.66086975122462</v>
+        <v>-22.25913705471175</v>
       </c>
       <c r="R66" t="n">
-        <v>50.57223495393614</v>
+        <v>136.4138869036161</v>
       </c>
       <c r="S66" t="n">
-        <v>3.969046675190535</v>
+        <v>61.06870051176638</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Bull Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bearish Harami</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="n">
-        <v>63.3</v>
+        <v>64</v>
       </c>
       <c r="X66" t="n">
-        <v>75.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -28264,19 +28252,19 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Bull Flag / Consolidation</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 46); RSI in forza (65) — momentum positivo; segnale candlestick: Bearish Harami</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -28285,73 +28273,69 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>43.86000061035156</v>
+        <v>83.30000305175781</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.2955241262899699</v>
+        <v>0.4703888221231356</v>
       </c>
       <c r="F67" t="n">
-        <v>5.865315682539851</v>
+        <v>-0.2514657874515214</v>
       </c>
       <c r="G67" t="n">
-        <v>-1.813292124011912</v>
+        <v>0.3614494599491813</v>
       </c>
       <c r="H67" t="n">
-        <v>2.548515643960036</v>
+        <v>19.71831109463935</v>
       </c>
       <c r="I67" t="n">
-        <v>55.53021061014197</v>
+        <v>54.27818860167661</v>
       </c>
       <c r="J67" t="n">
-        <v>25.39675376784596</v>
+        <v>17.79105977111829</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8069688348033327</v>
+        <v>0.6518549730383788</v>
       </c>
       <c r="L67" t="n">
-        <v>42.09827458771242</v>
+        <v>81.25350165423184</v>
       </c>
       <c r="M67" t="n">
-        <v>40.93348356576547</v>
+        <v>77.3038446421815</v>
       </c>
       <c r="N67" t="n">
-        <v>38.34974186023613</v>
+        <v>66.94187177391723</v>
       </c>
       <c r="O67" t="n">
-        <v>0.1717517700289497</v>
+        <v>0.05234235641232687</v>
       </c>
       <c r="P67" t="n">
-        <v>69.78902964452834</v>
+        <v>54.33913024877538</v>
       </c>
       <c r="Q67" t="n">
-        <v>-30.21097035547166</v>
+        <v>-45.66086975122462</v>
       </c>
       <c r="R67" t="n">
-        <v>100.6501848602426</v>
+        <v>50.57223495393614</v>
       </c>
       <c r="S67" t="n">
-        <v>1.527777397583541</v>
+        <v>3.969046675190535</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Double Top, Outside Bar</t>
+          <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>62.4</v>
+        <v>63.3</v>
       </c>
       <c r="X67" t="n">
-        <v>69.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -28360,19 +28344,19 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 25); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -28381,52 +28365,52 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>58.22000122070312</v>
+        <v>43.86000061035156</v>
       </c>
       <c r="E68" t="n">
-        <v>5.547500692088159</v>
+        <v>-0.2955241262899699</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3764500533463666</v>
+        <v>5.865315682539851</v>
       </c>
       <c r="G68" t="n">
-        <v>2.590310521062777</v>
+        <v>-1.813292124011912</v>
       </c>
       <c r="H68" t="n">
-        <v>48.29343787508722</v>
+        <v>2.548515643960036</v>
       </c>
       <c r="I68" t="n">
-        <v>54.96036335417634</v>
+        <v>55.53021061014197</v>
       </c>
       <c r="J68" t="n">
-        <v>41.22527098608453</v>
+        <v>25.39675376784596</v>
       </c>
       <c r="K68" t="n">
-        <v>0.4851239916018608</v>
+        <v>0.8069688348033327</v>
       </c>
       <c r="L68" t="n">
-        <v>56.65987174994409</v>
+        <v>42.09827458771242</v>
       </c>
       <c r="M68" t="n">
-        <v>51.29116969118049</v>
+        <v>40.93348356576547</v>
       </c>
       <c r="N68" t="n">
-        <v>40.26126554114012</v>
+        <v>38.34974186023613</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.8289982935245837</v>
+        <v>0.1717517700289497</v>
       </c>
       <c r="P68" t="n">
-        <v>61.07556912761118</v>
+        <v>69.78902964452834</v>
       </c>
       <c r="Q68" t="n">
-        <v>-38.92443087238881</v>
+        <v>-30.21097035547166</v>
       </c>
       <c r="R68" t="n">
-        <v>-13.60906962573774</v>
+        <v>100.6501848602426</v>
       </c>
       <c r="S68" t="n">
-        <v>3.908624824413631</v>
+        <v>1.527777397583541</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -28435,19 +28419,19 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
+          <t>Doji</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Double Top, Outside Bar</t>
         </is>
       </c>
       <c r="W68" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="X68" t="n">
-        <v>76.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -28456,19 +28440,19 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 41); candela di inversione bullish (engulfing)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 25); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MOO</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agribusiness</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -28477,65 +28461,73 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>76.95999908447266</v>
+        <v>58.22000122070312</v>
       </c>
       <c r="E69" t="n">
-        <v>-3.146237136678409</v>
+        <v>5.547500692088159</v>
       </c>
       <c r="F69" t="n">
-        <v>-4.171334299539675</v>
+        <v>-0.3764500533463666</v>
       </c>
       <c r="G69" t="n">
-        <v>1.920271364350112</v>
+        <v>2.590310521062777</v>
       </c>
       <c r="H69" t="n">
-        <v>-15.80790285388254</v>
+        <v>48.29343787508722</v>
       </c>
       <c r="I69" t="n">
-        <v>50.59799451635429</v>
+        <v>54.96036335417634</v>
       </c>
       <c r="J69" t="n">
-        <v>28.78427453806398</v>
+        <v>41.22527098608453</v>
       </c>
       <c r="K69" t="n">
-        <v>0.6155161779235524</v>
+        <v>0.4851239916018608</v>
       </c>
       <c r="L69" t="n">
-        <v>76.74611971683434</v>
+        <v>56.65987174994409</v>
       </c>
       <c r="M69" t="n">
-        <v>76.49973976088734</v>
+        <v>51.29116969118049</v>
       </c>
       <c r="N69" t="n">
-        <v>70.99865367353051</v>
+        <v>40.26126554114012</v>
       </c>
       <c r="O69" t="n">
-        <v>1.093667517950294</v>
+        <v>-0.8289982935245837</v>
       </c>
       <c r="P69" t="n">
-        <v>46.48828734502522</v>
+        <v>61.07556912761118</v>
       </c>
       <c r="Q69" t="n">
-        <v>-53.51171265497478</v>
+        <v>-38.92443087238881</v>
       </c>
       <c r="R69" t="n">
-        <v>54.75244601799345</v>
+        <v>-13.60906962573774</v>
       </c>
       <c r="S69" t="n">
-        <v>7.531087624188193</v>
+        <v>3.908624824413631</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W69" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="X69" t="n">
-        <v>75</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -28544,90 +28536,86 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 29); in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 41); candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BRK</t>
+          <t>MOO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Agribusiness</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>489.4599914550781</v>
+        <v>76.95999908447266</v>
       </c>
       <c r="E70" t="n">
-        <v>3.157136259040771</v>
+        <v>-3.146237136678409</v>
       </c>
       <c r="F70" t="n">
-        <v>1.85836320281072</v>
+        <v>-4.171334299539675</v>
       </c>
       <c r="G70" t="n">
-        <v>6.344236099139366</v>
+        <v>1.920271364350112</v>
       </c>
       <c r="H70" t="n">
-        <v>78.01781041076137</v>
+        <v>-15.80790285388254</v>
       </c>
       <c r="I70" t="n">
-        <v>55.29073618596212</v>
+        <v>50.59799451635429</v>
       </c>
       <c r="J70" t="n">
-        <v>27.9225645929027</v>
+        <v>28.78427453806398</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4655097947644197</v>
+        <v>0.6155161779235524</v>
       </c>
       <c r="L70" t="n">
-        <v>477.1150496609309</v>
+        <v>76.74611971683434</v>
       </c>
       <c r="M70" t="n">
-        <v>420.6824399944636</v>
+        <v>76.49973976088734</v>
       </c>
       <c r="N70" t="n">
-        <v>308.836959105891</v>
+        <v>70.99865367353051</v>
       </c>
       <c r="O70" t="n">
-        <v>-8.05254344093396</v>
+        <v>1.093667517950294</v>
       </c>
       <c r="P70" t="n">
-        <v>39.44519692407559</v>
+        <v>46.48828734502522</v>
       </c>
       <c r="Q70" t="n">
-        <v>-60.55480307592441</v>
+        <v>-53.51171265497478</v>
       </c>
       <c r="R70" t="n">
-        <v>-5.367307840513911</v>
+        <v>54.75244601799345</v>
       </c>
       <c r="S70" t="n">
-        <v>8.546965510440852</v>
+        <v>7.531087624188193</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern, Morning Star</t>
-        </is>
-      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="n">
         <v>61.9</v>
       </c>
       <c r="X70" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -28636,19 +28624,19 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 28); candela di inversione bullish (engulfing)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 29); in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BRK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -28657,52 +28645,52 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>327.239990234375</v>
+        <v>489.4599914550781</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2696423956094263</v>
+        <v>3.157136259040771</v>
       </c>
       <c r="F71" t="n">
-        <v>1.681012922297898</v>
+        <v>1.85836320281072</v>
       </c>
       <c r="G71" t="n">
-        <v>19.01799443746544</v>
+        <v>6.344236099139366</v>
       </c>
       <c r="H71" t="n">
-        <v>40.10960509291817</v>
+        <v>78.01781041076137</v>
       </c>
       <c r="I71" t="n">
-        <v>54.04487520465466</v>
+        <v>55.29073618596212</v>
       </c>
       <c r="J71" t="n">
-        <v>24.14192434343606</v>
+        <v>27.9225645929027</v>
       </c>
       <c r="K71" t="n">
-        <v>0.353345069513795</v>
+        <v>0.4655097947644197</v>
       </c>
       <c r="L71" t="n">
-        <v>322.9574567838732</v>
+        <v>477.1150496609309</v>
       </c>
       <c r="M71" t="n">
-        <v>288.1501791257111</v>
+        <v>420.6824399944636</v>
       </c>
       <c r="N71" t="n">
-        <v>209.9966615491955</v>
+        <v>308.836959105891</v>
       </c>
       <c r="O71" t="n">
-        <v>-6.032642389422016</v>
+        <v>-8.05254344093396</v>
       </c>
       <c r="P71" t="n">
-        <v>40.86005584545138</v>
+        <v>39.44519692407559</v>
       </c>
       <c r="Q71" t="n">
-        <v>-59.13994415454862</v>
+        <v>-60.55480307592441</v>
       </c>
       <c r="R71" t="n">
-        <v>-18.8819505412629</v>
+        <v>-5.367307840513911</v>
       </c>
       <c r="S71" t="n">
-        <v>12.89976999948936</v>
+        <v>8.546965510440852</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -28711,19 +28699,15 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Outside Bar</t>
-        </is>
-      </c>
+          <t>Bullish Engulfing, Piercing Pattern, Morning Star</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="n">
         <v>61.9</v>
       </c>
       <c r="X71" t="n">
-        <v>65.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -28732,90 +28716,94 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); doji — indecisione del mercato</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 28); candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TIT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Telecom Italia</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>7.896999835968018</v>
+        <v>327.239990234375</v>
       </c>
       <c r="E72" t="n">
-        <v>8.356198137089898</v>
+        <v>0.2696423956094263</v>
       </c>
       <c r="F72" t="n">
-        <v>38.54386140735899</v>
+        <v>1.681012922297898</v>
       </c>
       <c r="G72" t="n">
-        <v>216.5130339955286</v>
+        <v>19.01799443746544</v>
       </c>
       <c r="H72" t="n">
-        <v>73.06595411056497</v>
+        <v>40.10960509291817</v>
       </c>
       <c r="I72" t="n">
-        <v>82.82250011256671</v>
+        <v>54.04487520465466</v>
       </c>
       <c r="J72" t="n">
-        <v>85.0730450396585</v>
+        <v>24.14192434343606</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9975634689229886</v>
+        <v>0.353345069513795</v>
       </c>
       <c r="L72" t="n">
-        <v>5.099322118122677</v>
+        <v>322.9574567838732</v>
       </c>
       <c r="M72" t="n">
-        <v>4.173571649522978</v>
+        <v>288.1501791257111</v>
       </c>
       <c r="N72" t="n">
-        <v>5.06979526601036</v>
+        <v>209.9966615491955</v>
       </c>
       <c r="O72" t="n">
-        <v>0.3452846216606686</v>
+        <v>-6.032642389422016</v>
       </c>
       <c r="P72" t="n">
-        <v>96.59259711521068</v>
+        <v>40.86005584545138</v>
       </c>
       <c r="Q72" t="n">
-        <v>-3.407402884789323</v>
+        <v>-59.13994415454862</v>
       </c>
       <c r="R72" t="n">
-        <v>147.3867560825311</v>
+        <v>-18.8819505412629</v>
       </c>
       <c r="S72" t="n">
-        <v>239.3639951045809</v>
+        <v>12.89976999948936</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Double Bottom</t>
+          <t>Outside Bar</t>
         </is>
       </c>
       <c r="W72" t="n">
-        <v>61.3</v>
+        <v>61.9</v>
       </c>
       <c r="X72" t="n">
-        <v>76.3</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -28824,90 +28812,90 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 85); RSI ipercomprato (83) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>TIT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Telecom Italia</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>100.6500015258789</v>
+        <v>7.896999835968018</v>
       </c>
       <c r="E73" t="n">
-        <v>1.502619815189532</v>
+        <v>8.356198137089898</v>
       </c>
       <c r="F73" t="n">
-        <v>9.461669240221804</v>
+        <v>38.54386140735899</v>
       </c>
       <c r="G73" t="n">
-        <v>3.24136191542963</v>
+        <v>216.5130339955286</v>
       </c>
       <c r="H73" t="n">
-        <v>-12.08838902622629</v>
+        <v>73.06595411056497</v>
       </c>
       <c r="I73" t="n">
-        <v>54.22017936879985</v>
+        <v>82.82250011256671</v>
       </c>
       <c r="J73" t="n">
-        <v>12.54667039167992</v>
+        <v>85.0730450396585</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6863029810449618</v>
+        <v>0.9975634689229886</v>
       </c>
       <c r="L73" t="n">
-        <v>93.62929554544468</v>
+        <v>5.099322118122677</v>
       </c>
       <c r="M73" t="n">
-        <v>92.47979743231014</v>
+        <v>4.173571649522978</v>
       </c>
       <c r="N73" t="n">
-        <v>80.44244358876097</v>
+        <v>5.06979526601036</v>
       </c>
       <c r="O73" t="n">
-        <v>1.570085460171202</v>
+        <v>0.3452846216606686</v>
       </c>
       <c r="P73" t="n">
-        <v>73.35708679134186</v>
+        <v>96.59259711521068</v>
       </c>
       <c r="Q73" t="n">
-        <v>-26.64291320865814</v>
+        <v>-3.407402884789323</v>
       </c>
       <c r="R73" t="n">
-        <v>61.80007838367867</v>
+        <v>147.3867560825311</v>
       </c>
       <c r="S73" t="n">
-        <v>3.019452067331718</v>
+        <v>239.3639951045809</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Breakout 20d, Breakout 50d, Double Bottom</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>60.9</v>
+        <v>61.3</v>
       </c>
       <c r="X73" t="n">
-        <v>70.7</v>
+        <v>76.3</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -28916,95 +28904,99 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 85); RSI ipercomprato (83) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>80.36000061035156</v>
+        <v>100.6500015258789</v>
       </c>
       <c r="E74" t="n">
-        <v>-12.69962200309022</v>
+        <v>1.502619815189532</v>
       </c>
       <c r="F74" t="n">
-        <v>13.6794424034157</v>
+        <v>9.461669240221804</v>
       </c>
       <c r="G74" t="n">
-        <v>11.9687952752817</v>
+        <v>3.24136191542963</v>
       </c>
       <c r="H74" t="n">
-        <v>19.49442469940752</v>
+        <v>-12.08838902622629</v>
       </c>
       <c r="I74" t="n">
-        <v>50.36375020984314</v>
+        <v>54.22017936879985</v>
       </c>
       <c r="J74" t="n">
-        <v>21.75599156738005</v>
+        <v>12.54667039167992</v>
       </c>
       <c r="K74" t="n">
-        <v>0.5765885234041239</v>
+        <v>0.6863029810449618</v>
       </c>
       <c r="L74" t="n">
-        <v>80.41210612368171</v>
+        <v>93.62929554544468</v>
       </c>
       <c r="M74" t="n">
-        <v>78.12897872629645</v>
+        <v>92.47979743231014</v>
       </c>
       <c r="N74" t="n">
-        <v>71.73889271098137</v>
+        <v>80.44244358876097</v>
       </c>
       <c r="O74" t="n">
-        <v>3.245301539512615</v>
+        <v>1.570085460171202</v>
       </c>
       <c r="P74" t="n">
-        <v>32.42724362278014</v>
+        <v>73.35708679134186</v>
       </c>
       <c r="Q74" t="n">
-        <v>-67.57275637721986</v>
+        <v>-26.64291320865814</v>
       </c>
       <c r="R74" t="n">
-        <v>59.59049752855905</v>
+        <v>61.80007838367867</v>
       </c>
       <c r="S74" t="n">
-        <v>9.841438747728182</v>
+        <v>3.019452067331718</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W74" t="n">
-        <v>59.7</v>
+        <v>60.9</v>
       </c>
       <c r="X74" t="n">
-        <v>72</v>
+        <v>70.7</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 13); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -29305,52 +29297,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.146657466888428</v>
+        <v>1.147842049598694</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.598437418958709</v>
+        <v>-1.49678126351328</v>
       </c>
       <c r="F78" t="n">
-        <v>-4.171542508942894</v>
+        <v>-4.07254456302325</v>
       </c>
       <c r="G78" t="n">
-        <v>2.656799631160145</v>
+        <v>2.762851763942487</v>
       </c>
       <c r="H78" t="n">
-        <v>-5.446624978300274</v>
+        <v>-5.348944287699664</v>
       </c>
       <c r="I78" t="n">
-        <v>52.44471052998917</v>
+        <v>52.68486909696011</v>
       </c>
       <c r="J78" t="n">
         <v>42.06853630988682</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5592822352507971</v>
+        <v>0.5646954426769429</v>
       </c>
       <c r="L78" t="n">
-        <v>1.143193635758686</v>
+        <v>1.143306453159664</v>
       </c>
       <c r="M78" t="n">
-        <v>1.122933722924605</v>
+        <v>1.122980177148537</v>
       </c>
       <c r="N78" t="n">
-        <v>1.132646977977018</v>
+        <v>1.132664145842384</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.0007986673819169628</v>
+        <v>-0.0007230700807489693</v>
       </c>
       <c r="P78" t="n">
-        <v>41.2772663975427</v>
+        <v>42.52615412458462</v>
       </c>
       <c r="Q78" t="n">
-        <v>-58.7227336024573</v>
+        <v>-57.47384587541537</v>
       </c>
       <c r="R78" t="n">
-        <v>25.97490801028257</v>
+        <v>26.48368006085859</v>
       </c>
       <c r="S78" t="n">
-        <v>5.593391573197581</v>
+        <v>5.702477424541996</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -29367,7 +29359,7 @@
         <v>55.7</v>
       </c>
       <c r="X78" t="n">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -29655,83 +29647,83 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1262</v>
+        <v>1.13289999961853</v>
       </c>
       <c r="E82" t="n">
-        <v>-7.274063188831736</v>
+        <v>-14.90406906203746</v>
       </c>
       <c r="F82" t="n">
-        <v>-25.25025389438485</v>
+        <v>-31.15041130647065</v>
       </c>
       <c r="G82" t="n">
-        <v>26.33896978231305</v>
+        <v>85.26817032199506</v>
       </c>
       <c r="H82" t="n">
-        <v>-57.33170974628508</v>
+        <v>-28.82336327582329</v>
       </c>
       <c r="I82" t="n">
-        <v>48.00311612739703</v>
+        <v>41.8132159016381</v>
       </c>
       <c r="J82" t="n">
-        <v>54.48887442357493</v>
+        <v>41.86732703313529</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5083349055973513</v>
+        <v>0.09907019873868352</v>
       </c>
       <c r="L82" t="n">
-        <v>1335.478214257015</v>
+        <v>1.660426788570294</v>
       </c>
       <c r="M82" t="n">
-        <v>1367.820841365783</v>
+        <v>1.346903885269372</v>
       </c>
       <c r="N82" t="n">
-        <v>1358.07660488149</v>
+        <v>1.072770761916053</v>
       </c>
       <c r="O82" t="n">
-        <v>22.25821347839883</v>
+        <v>-0.1897919313801558</v>
       </c>
       <c r="P82" t="n">
-        <v>26.30083819176981</v>
+        <v>3.014502865833013</v>
       </c>
       <c r="Q82" t="n">
-        <v>-73.69916180823019</v>
+        <v>-96.98549713416699</v>
       </c>
       <c r="R82" t="n">
-        <v>4.727780261322514</v>
+        <v>-62.69887545489238</v>
       </c>
       <c r="S82" t="n">
-        <v>14.05332128332579</v>
+        <v>122.4700912814173</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="X82" t="n">
-        <v>70.09999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -29740,19 +29732,19 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 54); pattern: Double Bottom</t>
+          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SOYBEAN</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -29761,69 +29753,69 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1122.75</v>
+        <v>1264.5</v>
       </c>
       <c r="E83" t="n">
-        <v>-5.392879713503262</v>
+        <v>-7.090374724467308</v>
       </c>
       <c r="F83" t="n">
-        <v>5.496828752642702</v>
+        <v>-25.10217595043553</v>
       </c>
       <c r="G83" t="n">
-        <v>6.220435193945129</v>
+        <v>26.5892450790292</v>
       </c>
       <c r="H83" t="n">
-        <v>-28.53278166772756</v>
+        <v>-57.2471846071137</v>
       </c>
       <c r="I83" t="n">
-        <v>50.0249290525538</v>
+        <v>48.07656672616933</v>
       </c>
       <c r="J83" t="n">
-        <v>26.04242815342785</v>
+        <v>54.48887442357493</v>
       </c>
       <c r="K83" t="n">
-        <v>0.7037393311686028</v>
+        <v>0.5104507432818538</v>
       </c>
       <c r="L83" t="n">
-        <v>1111.352901346763</v>
+        <v>1335.71630949511</v>
       </c>
       <c r="M83" t="n">
-        <v>1154.896721781048</v>
+        <v>1367.918880581469</v>
       </c>
       <c r="N83" t="n">
-        <v>1138.370827415582</v>
+        <v>1358.118977762846</v>
       </c>
       <c r="O83" t="n">
-        <v>25.08133838560368</v>
+        <v>22.41775763794303</v>
       </c>
       <c r="P83" t="n">
-        <v>61.71428571428571</v>
+        <v>26.50377675806433</v>
       </c>
       <c r="Q83" t="n">
-        <v>-38.28571428571428</v>
+        <v>-73.49622324193567</v>
       </c>
       <c r="R83" t="n">
-        <v>49.73666273375309</v>
+        <v>4.957912304106544</v>
       </c>
       <c r="S83" t="n">
-        <v>14.27480916030535</v>
+        <v>14.27925892453683</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Evening Star</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W83" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="X83" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -29832,86 +29824,90 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); candela di inversione bearish (engulfing); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 54); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>SOYBEAN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.322016835212708</v>
+        <v>1122.75</v>
       </c>
       <c r="E84" t="n">
-        <v>-1.668392291109366</v>
+        <v>-5.392879713503262</v>
       </c>
       <c r="F84" t="n">
-        <v>-4.246319789985487</v>
+        <v>5.496828752642702</v>
       </c>
       <c r="G84" t="n">
-        <v>-1.218904107734364</v>
+        <v>6.220435193945129</v>
       </c>
       <c r="H84" t="n">
-        <v>-5.251053228291025</v>
+        <v>-28.53278166772756</v>
       </c>
       <c r="I84" t="n">
-        <v>50.68717229961257</v>
+        <v>50.0249290525538</v>
       </c>
       <c r="J84" t="n">
-        <v>23.15604231256256</v>
+        <v>26.04242815342785</v>
       </c>
       <c r="K84" t="n">
-        <v>0.4958417686148544</v>
+        <v>0.7037393311686028</v>
       </c>
       <c r="L84" t="n">
-        <v>1.325172771476728</v>
+        <v>1111.352901346763</v>
       </c>
       <c r="M84" t="n">
-        <v>1.306356697101294</v>
+        <v>1154.896721781048</v>
       </c>
       <c r="N84" t="n">
-        <v>1.339187327545429</v>
+        <v>1138.370827415582</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.002349147033028812</v>
+        <v>25.08133838560368</v>
       </c>
       <c r="P84" t="n">
-        <v>24.96552570797206</v>
+        <v>61.71428571428571</v>
       </c>
       <c r="Q84" t="n">
-        <v>-75.03447429202795</v>
+        <v>-38.28571428571428</v>
       </c>
       <c r="R84" t="n">
-        <v>16.42836791853043</v>
+        <v>49.73666273375309</v>
       </c>
       <c r="S84" t="n">
-        <v>2.010783823767626</v>
+        <v>14.27480916030535</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bearish Engulfing, Evening Star</t>
+        </is>
+      </c>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="X84" t="n">
-        <v>54.1</v>
+        <v>72.7</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -29920,73 +29916,73 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 26); candela di inversione bearish (engulfing); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>High Yield Corp ETF</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>80.01000213623047</v>
+        <v>1.323451638221741</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.3735467955211957</v>
+        <v>-1.561671648175134</v>
       </c>
       <c r="F85" t="n">
-        <v>-1.368343901342306</v>
+        <v>-4.142397007134369</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.3611468300199427</v>
+        <v>-1.111695629107834</v>
       </c>
       <c r="H85" t="n">
-        <v>-8.497255372510592</v>
+        <v>-5.148220896425215</v>
       </c>
       <c r="I85" t="n">
-        <v>51.57717730929279</v>
+        <v>50.9108901180927</v>
       </c>
       <c r="J85" t="n">
-        <v>20.37678662143965</v>
+        <v>23.15604231256256</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4522763442609523</v>
+        <v>0.5045241484652614</v>
       </c>
       <c r="L85" t="n">
-        <v>79.94279318690602</v>
+        <v>1.32530941938235</v>
       </c>
       <c r="M85" t="n">
-        <v>79.80299057906961</v>
+        <v>1.306412963885962</v>
       </c>
       <c r="N85" t="n">
-        <v>82.86962799062954</v>
+        <v>1.339208121791936</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.1184087141174007</v>
+        <v>-0.002257581256953824</v>
       </c>
       <c r="P85" t="n">
-        <v>57.00640966454955</v>
+        <v>26.68367303239584</v>
       </c>
       <c r="Q85" t="n">
-        <v>-42.99359033545045</v>
+        <v>-73.31632696760416</v>
       </c>
       <c r="R85" t="n">
-        <v>-3.158356752468289</v>
+        <v>17.31004032594704</v>
       </c>
       <c r="S85" t="n">
-        <v>1.099321143911736</v>
+        <v>2.121497527016825</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -29994,16 +29990,12 @@
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar, Volatility Squeeze</t>
-        </is>
-      </c>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="X85" t="n">
-        <v>59.2</v>
+        <v>54.1</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -30012,90 +30004,90 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 23)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>High Yield Corp ETF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.135599970817566</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="E86" t="n">
-        <v>-14.70126514045127</v>
+        <v>-0.3735467955211957</v>
       </c>
       <c r="F86" t="n">
-        <v>-30.98632629755497</v>
+        <v>-1.368343901342306</v>
       </c>
       <c r="G86" t="n">
-        <v>85.70970860793012</v>
+        <v>-0.3611468300199427</v>
       </c>
       <c r="H86" t="n">
-        <v>-28.65373235582663</v>
+        <v>-8.497255372510592</v>
       </c>
       <c r="I86" t="n">
-        <v>41.85061314183157</v>
+        <v>51.57717730929279</v>
       </c>
       <c r="J86" t="n">
-        <v>41.86732703313529</v>
+        <v>20.37678662143965</v>
       </c>
       <c r="K86" t="n">
-        <v>0.100019202464153</v>
+        <v>0.4522763442609523</v>
       </c>
       <c r="L86" t="n">
-        <v>1.660683928684488</v>
+        <v>79.94279318690602</v>
       </c>
       <c r="M86" t="n">
-        <v>1.347011884117333</v>
+        <v>79.80299057906961</v>
       </c>
       <c r="N86" t="n">
-        <v>1.072825863369095</v>
+        <v>82.86962799062954</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.1896196255258583</v>
+        <v>-0.1184087141174007</v>
       </c>
       <c r="P86" t="n">
-        <v>3.118525834383713</v>
+        <v>57.00640966454955</v>
       </c>
       <c r="Q86" t="n">
-        <v>-96.88147416561628</v>
+        <v>-42.99359033545045</v>
       </c>
       <c r="R86" t="n">
-        <v>-62.64289168608248</v>
+        <v>-3.158356752468289</v>
       </c>
       <c r="S86" t="n">
-        <v>123.0002906276164</v>
+        <v>1.099321143911736</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Double Top, Inside Bar, Volatility Squeeze</t>
+        </is>
+      </c>
       <c r="W86" t="n">
-        <v>49.8</v>
+        <v>50.7</v>
       </c>
       <c r="X86" t="n">
-        <v>57.3</v>
+        <v>59.2</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -30104,7 +30096,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele</t>
+          <t>trend in sviluppo (ADX 20); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -30399,52 +30391,52 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>100.8079986572266</v>
+        <v>100.7320022583008</v>
       </c>
       <c r="E90" t="n">
-        <v>1.918911055347849</v>
+        <v>1.842077169884271</v>
       </c>
       <c r="F90" t="n">
-        <v>3.936489202546145</v>
+        <v>3.858134319981321</v>
       </c>
       <c r="G90" t="n">
-        <v>0.02778316954636928</v>
+        <v>-0.04762504621695918</v>
       </c>
       <c r="H90" t="n">
-        <v>10.4382121005141</v>
+        <v>10.35495574650216</v>
       </c>
       <c r="I90" t="n">
-        <v>50.50165290696561</v>
+        <v>50.33788731551233</v>
       </c>
       <c r="J90" t="n">
         <v>29.35186553155452</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5019186868071642</v>
+        <v>0.4972387150062632</v>
       </c>
       <c r="L90" t="n">
-        <v>100.1625712583943</v>
+        <v>100.1553335061157</v>
       </c>
       <c r="M90" t="n">
-        <v>100.8141196643983</v>
+        <v>100.81113941346</v>
       </c>
       <c r="N90" t="n">
-        <v>99.51412935735857</v>
+        <v>99.51284128280051</v>
       </c>
       <c r="O90" t="n">
-        <v>0.07101529752527691</v>
+        <v>0.0661653848872803</v>
       </c>
       <c r="P90" t="n">
-        <v>81.77286712158264</v>
+        <v>80.59096361740072</v>
       </c>
       <c r="Q90" t="n">
-        <v>-18.22713287841736</v>
+        <v>-19.40903638259929</v>
       </c>
       <c r="R90" t="n">
-        <v>-10.66742693612147</v>
+        <v>-11.12605113008034</v>
       </c>
       <c r="S90" t="n">
-        <v>-3.050591072610809</v>
+        <v>-3.123678586048273</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -30583,52 +30575,52 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3.204999923706055</v>
+        <v>3.197999954223633</v>
       </c>
       <c r="E92" t="n">
-        <v>-2.583587815578514</v>
+        <v>-2.796352847906336</v>
       </c>
       <c r="F92" t="n">
-        <v>-26.38953017194173</v>
+        <v>-26.55030117183222</v>
       </c>
       <c r="G92" t="n">
-        <v>9.64761604675255</v>
+        <v>9.40813711245665</v>
       </c>
       <c r="H92" t="n">
-        <v>9.348342885125117</v>
+        <v>9.109517586725669</v>
       </c>
       <c r="I92" t="n">
-        <v>48.95233247755974</v>
+        <v>48.90293265935876</v>
       </c>
       <c r="J92" t="n">
         <v>46.22655544113106</v>
       </c>
       <c r="K92" t="n">
-        <v>0.372842998489311</v>
+        <v>0.3698394365958335</v>
       </c>
       <c r="L92" t="n">
-        <v>3.335988531331897</v>
+        <v>3.335321867571666</v>
       </c>
       <c r="M92" t="n">
-        <v>3.376433656462276</v>
+        <v>3.376159147855122</v>
       </c>
       <c r="N92" t="n">
-        <v>3.318064270317964</v>
+        <v>3.317945626767415</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.05447187513381569</v>
+        <v>-0.05491859683297887</v>
       </c>
       <c r="P92" t="n">
-        <v>13.51047660917034</v>
+        <v>13.37948915875853</v>
       </c>
       <c r="Q92" t="n">
-        <v>-86.48952339082966</v>
+        <v>-86.62051084124147</v>
       </c>
       <c r="R92" t="n">
-        <v>-31.00370703192775</v>
+        <v>-31.19870916863072</v>
       </c>
       <c r="S92" t="n">
-        <v>18.39674559962712</v>
+        <v>18.13815788488638</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -30641,7 +30633,7 @@
         <v>48.2</v>
       </c>
       <c r="X92" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -30671,52 +30663,52 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>63151.6484375</v>
+        <v>63074.69921875</v>
       </c>
       <c r="E93" t="n">
-        <v>-14.17244271729206</v>
+        <v>-14.27702214860589</v>
       </c>
       <c r="F93" t="n">
-        <v>-19.67597167705917</v>
+        <v>-19.77384515113674</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.280835254502243</v>
+        <v>-0.4023413752674454</v>
       </c>
       <c r="H93" t="n">
-        <v>9.353170935288691</v>
+        <v>9.219925940431061</v>
       </c>
       <c r="I93" t="n">
-        <v>42.53053998035447</v>
+        <v>42.49906545092831</v>
       </c>
       <c r="J93" t="n">
         <v>30.00632113396347</v>
       </c>
       <c r="K93" t="n">
-        <v>0.07601100620653532</v>
+        <v>0.07507190214311525</v>
       </c>
       <c r="L93" t="n">
-        <v>80236.86001671651</v>
+        <v>80229.53151969271</v>
       </c>
       <c r="M93" t="n">
-        <v>66719.67422705227</v>
+        <v>66716.59625830226</v>
       </c>
       <c r="N93" t="n">
-        <v>49916.88824588739</v>
+        <v>49915.317853668</v>
       </c>
       <c r="O93" t="n">
-        <v>-5946.401838018034</v>
+        <v>-5951.312557391263</v>
       </c>
       <c r="P93" t="n">
-        <v>6.025907807026599</v>
+        <v>5.911210846248604</v>
       </c>
       <c r="Q93" t="n">
-        <v>-93.9740921929734</v>
+        <v>-94.08878915375139</v>
       </c>
       <c r="R93" t="n">
-        <v>-67.79782356795725</v>
+        <v>-67.857842710247</v>
       </c>
       <c r="S93" t="n">
-        <v>-10.05984504776833</v>
+        <v>-10.16943560999535</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -31323,52 +31315,52 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>69.20999908447266</v>
+        <v>69.18000030517578</v>
       </c>
       <c r="E100" t="n">
-        <v>-15.90349052466195</v>
+        <v>-15.9399417984773</v>
       </c>
       <c r="F100" t="n">
-        <v>-34.36180216444503</v>
+        <v>-34.39025276170498</v>
       </c>
       <c r="G100" t="n">
-        <v>-54.65162281478791</v>
+        <v>-54.67127887571331</v>
       </c>
       <c r="H100" t="n">
-        <v>61.11834672538674</v>
+        <v>61.04851066429688</v>
       </c>
       <c r="I100" t="n">
-        <v>39.75493145616498</v>
+        <v>39.75067172441278</v>
       </c>
       <c r="J100" t="n">
         <v>26.98955752673374</v>
       </c>
       <c r="K100" t="n">
-        <v>0.1302190639889434</v>
+        <v>0.130098871498916</v>
       </c>
       <c r="L100" t="n">
-        <v>121.8464006104023</v>
+        <v>121.8435435838026</v>
       </c>
       <c r="M100" t="n">
-        <v>118.0208559158263</v>
+        <v>118.0192770327054</v>
       </c>
       <c r="N100" t="n">
-        <v>94.54887222487197</v>
+        <v>94.54806144705313</v>
       </c>
       <c r="O100" t="n">
-        <v>-14.26033902610246</v>
+        <v>-14.26225347811457</v>
       </c>
       <c r="P100" t="n">
-        <v>4.56198147609522</v>
+        <v>4.546421554369698</v>
       </c>
       <c r="Q100" t="n">
-        <v>-95.43801852390479</v>
+        <v>-95.4535784456303</v>
       </c>
       <c r="R100" t="n">
-        <v>-104.6216561580153</v>
+        <v>-104.63321638096</v>
       </c>
       <c r="S100" t="n">
-        <v>-63.43212478727005</v>
+        <v>-63.44797497701682</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -31963,52 +31955,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1705.510009765625</v>
+        <v>1702.2900390625</v>
       </c>
       <c r="E107" t="n">
-        <v>-14.90921258211088</v>
+        <v>-15.06986238247711</v>
       </c>
       <c r="F107" t="n">
-        <v>-30.2476082106452</v>
+        <v>-30.37929940961125</v>
       </c>
       <c r="G107" t="n">
-        <v>-34.48064155946107</v>
+        <v>-34.60434087137251</v>
       </c>
       <c r="H107" t="n">
-        <v>-38.50044405098452</v>
+        <v>-38.61655405167471</v>
       </c>
       <c r="I107" t="n">
-        <v>40.9888641495516</v>
+        <v>40.96430048693965</v>
       </c>
       <c r="J107" t="n">
         <v>13.77196504624608</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1799155442045761</v>
+        <v>0.1790922400420079</v>
       </c>
       <c r="L107" t="n">
-        <v>2589.574342233281</v>
+        <v>2589.267678356793</v>
       </c>
       <c r="M107" t="n">
-        <v>2454.13386754199</v>
+        <v>2454.005068713865</v>
       </c>
       <c r="N107" t="n">
-        <v>2027.292896568468</v>
+        <v>2027.227182880649</v>
       </c>
       <c r="O107" t="n">
-        <v>-187.5568106900707</v>
+        <v>-187.7623016979054</v>
       </c>
       <c r="P107" t="n">
-        <v>5.772879548762672</v>
+        <v>5.679471991277523</v>
       </c>
       <c r="Q107" t="n">
-        <v>-94.22712045123733</v>
+        <v>-94.32052800872248</v>
       </c>
       <c r="R107" t="n">
-        <v>-107.9845171332129</v>
+        <v>-108.0787952656213</v>
       </c>
       <c r="S107" t="n">
-        <v>-32.20802634600049</v>
+        <v>-32.33601631253424</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -32791,52 +32783,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.9670000076293945</v>
+        <v>0.9599999785423279</v>
       </c>
       <c r="E116" t="n">
-        <v>-18.48790228577584</v>
+        <v>-19.07796128313426</v>
       </c>
       <c r="F116" t="n">
-        <v>-37.37180643296382</v>
+        <v>-37.82516648795951</v>
       </c>
       <c r="G116" t="n">
-        <v>-78.20641780054343</v>
+        <v>-78.36417964966851</v>
       </c>
       <c r="H116" t="n">
-        <v>-97.35363322948024</v>
+        <v>-97.3727900487383</v>
       </c>
       <c r="I116" t="n">
-        <v>34.38153298933427</v>
+        <v>34.35750869111423</v>
       </c>
       <c r="J116" t="n">
         <v>29.28244893567739</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2098938100423975</v>
+        <v>0.2091641092566715</v>
       </c>
       <c r="L116" t="n">
-        <v>2.995725197431399</v>
+        <v>2.995058527994535</v>
       </c>
       <c r="M116" t="n">
-        <v>4.499302921954943</v>
+        <v>4.498914031450106</v>
       </c>
       <c r="N116" t="n">
-        <v>6.521046018011159</v>
+        <v>6.5208460171801</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.06455437656013019</v>
+        <v>-0.06500110206312293</v>
       </c>
       <c r="P116" t="n">
-        <v>1.66330634886554</v>
+        <v>1.506832897863237</v>
       </c>
       <c r="Q116" t="n">
-        <v>-98.33669365113445</v>
+        <v>-98.49316710213677</v>
       </c>
       <c r="R116" t="n">
-        <v>-80.25699335141778</v>
+        <v>-80.32285306468067</v>
       </c>
       <c r="S116" t="n">
-        <v>-84.69541710627007</v>
+        <v>-84.80620565288463</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -32850,10 +32842,10 @@
         </is>
       </c>
       <c r="W116" t="n">
-        <v>27.9</v>
+        <v>27.4</v>
       </c>
       <c r="X116" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -32883,52 +32875,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.110000133514404</v>
+        <v>6.010000228881836</v>
       </c>
       <c r="E117" t="n">
-        <v>-31.80741756709521</v>
+        <v>-32.92349802387528</v>
       </c>
       <c r="F117" t="n">
-        <v>-39.53927333501311</v>
+        <v>-40.52880963098645</v>
       </c>
       <c r="G117" t="n">
-        <v>-77.97320953754463</v>
+        <v>-78.33371312141936</v>
       </c>
       <c r="H117" t="n">
-        <v>-81.4389365067188</v>
+        <v>-81.74271793693943</v>
       </c>
       <c r="I117" t="n">
-        <v>38.41201602575057</v>
+        <v>38.34601001625779</v>
       </c>
       <c r="J117" t="n">
         <v>15.77413907764411</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1813274514340256</v>
+        <v>0.1792590856182565</v>
       </c>
       <c r="L117" t="n">
-        <v>16.55685880478026</v>
+        <v>16.54733500433906</v>
       </c>
       <c r="M117" t="n">
-        <v>20.04561203612195</v>
+        <v>20.04005648586459</v>
       </c>
       <c r="N117" t="n">
-        <v>21.31157718075677</v>
+        <v>21.30872004062441</v>
       </c>
       <c r="O117" t="n">
-        <v>-1.337665582523855</v>
+        <v>-1.344047342819494</v>
       </c>
       <c r="P117" t="n">
-        <v>0.4484545016053609</v>
+        <v>0.1143919221576764</v>
       </c>
       <c r="Q117" t="n">
-        <v>-99.55154549839465</v>
+        <v>-99.88560807784232</v>
       </c>
       <c r="R117" t="n">
-        <v>-84.94844645284415</v>
+        <v>-85.14114702624134</v>
       </c>
       <c r="S117" t="n">
-        <v>-82.23715517876185</v>
+        <v>-82.52787248634156</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -32958,7 +32950,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; breakdown minimi 50g — rottura supporto importante; evening star — inversione ribassista a 3 candele</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; breakdown minimi 50g — rottura supporto importante; evening star — inversione ribassista a 3 candele; sul supporto dei 20g (5.9758)</t>
         </is>
       </c>
     </row>
@@ -33216,7 +33208,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/06/2026 16:00:58</t>
+          <t>19/06/2026 18:04:56</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33256,13 +33248,13 @@
         <v>16.78000068664551</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8079986572266</v>
+        <v>100.7320022583008</v>
       </c>
       <c r="O2" t="n">
-        <v>4169.5</v>
+        <v>4172.89990234375</v>
       </c>
       <c r="P2" t="n">
-        <v>76.38999938964844</v>
+        <v>76.54000091552734</v>
       </c>
       <c r="Q2" t="n">
         <v>15.27861609718857</v>
@@ -33279,7 +33271,7 @@
         <v>4.717527417231073</v>
       </c>
       <c r="U2" t="n">
-        <v>3.677350599661958</v>
+        <v>3.692673998604442</v>
       </c>
       <c r="V2" t="n">
         <v>1.766907821710997</v>
@@ -33330,7 +33322,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.979710702455558</v>
+        <v>2.982264602279306</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33429,10 +33421,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.64513308338173</v>
+        <v>60.64576438713685</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1337955989995382</v>
+        <v>0.133820851149743</v>
       </c>
       <c r="D2" t="n">
         <v>52.58620689655172</v>
@@ -33581,10 +33573,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.978</v>
+        <v>0.977</v>
       </c>
       <c r="D6" t="n">
-        <v>0.949</v>
+        <v>0.948</v>
       </c>
       <c r="E6" t="n">
         <v>0.847</v>
@@ -33614,43 +33606,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0.9379999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HY</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.9379999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.857</v>
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -33875,7 +33867,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="D20" t="n">
         <v>0.915</v>
@@ -33887,22 +33879,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.904</v>
+        <v>0.953</v>
       </c>
       <c r="D21" t="n">
-        <v>0.913</v>
+        <v>0.911</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.908</v>
       </c>
     </row>
   </sheetData>
@@ -33991,43 +33983,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.72</v>
+        <v>-0.502</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.699</v>
+        <v>-0.698</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.638</v>
+        <v>-0.761</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.497</v>
+        <v>-0.707</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.697</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.761</v>
+        <v>-0.634</v>
       </c>
     </row>
     <row r="6">
@@ -34042,13 +34034,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.748</v>
+        <v>-0.743</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.677</v>
+        <v>-0.675</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.574</v>
+        <v>-0.572</v>
       </c>
     </row>
     <row r="7">
@@ -34105,10 +34097,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.44</v>
+        <v>-0.444</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.66</v>
+        <v>-0.661</v>
       </c>
       <c r="E9" t="n">
         <v>-0.641</v>
@@ -34126,13 +34118,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.48</v>
+        <v>-0.484</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.658</v>
+        <v>-0.659</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.738</v>
+        <v>-0.739</v>
       </c>
     </row>
     <row r="11">
@@ -34147,13 +34139,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.583</v>
+        <v>-0.595</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.653</v>
+        <v>-0.658</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.681</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -34189,10 +34181,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.525</v>
+        <v>-0.522</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.638</v>
+        <v>-0.637</v>
       </c>
       <c r="E13" t="n">
         <v>-0.764</v>
@@ -34210,7 +34202,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="D14" t="n">
         <v>-0.632</v>
@@ -34306,64 +34298,64 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>MONC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>WTI</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>US10Y</t>
-        </is>
-      </c>
       <c r="C19" t="n">
-        <v>-0.273</v>
+        <v>-0.41</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.619</v>
+        <v>-0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.506</v>
+        <v>-0.647</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MONC</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.406</v>
+        <v>-0.273</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.618</v>
+        <v>-0.619</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.646</v>
+        <v>-0.506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.488</v>
+        <v>-0.586</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.614</v>
+        <v>-0.617</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.51</v>
+        <v>-0.711</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -4071,66 +4071,66 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>100.7320022583008</v>
+        <v>100.6500015258789</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.117001703129016</v>
+        <v>0.8314985309479273</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9844634168428845</v>
+        <v>-1.593661784192268</v>
       </c>
       <c r="G40" t="n">
-        <v>1.636567085017049</v>
+        <v>-5.386346940665065</v>
       </c>
       <c r="H40" t="n">
-        <v>1.800914972226542</v>
+        <v>8.752023994630488</v>
       </c>
       <c r="I40" t="n">
-        <v>68.38306128596909</v>
+        <v>50.97020822055099</v>
       </c>
       <c r="J40" t="n">
-        <v>54.89484458347739</v>
+        <v>46.52844539746643</v>
       </c>
       <c r="K40" t="n">
-        <v>1.002514493583477</v>
+        <v>0.5990084776839427</v>
       </c>
       <c r="L40" t="n">
-        <v>99.74922106102176</v>
+        <v>100.2143638940623</v>
       </c>
       <c r="M40" t="n">
-        <v>99.28814047629614</v>
+        <v>99.93472994157919</v>
       </c>
       <c r="N40" t="n">
-        <v>99.14550661915742</v>
+        <v>95.06093793713073</v>
       </c>
       <c r="O40" t="n">
-        <v>0.08639429097538293</v>
+        <v>0.3748028453174477</v>
       </c>
       <c r="P40" t="n">
-        <v>80.98230946678618</v>
+        <v>69.75124385663119</v>
       </c>
       <c r="Q40" t="n">
-        <v>-19.01769053321383</v>
+        <v>-30.24875614336881</v>
       </c>
       <c r="R40" t="n">
-        <v>141.3230548029026</v>
+        <v>17.74701167618312</v>
       </c>
       <c r="S40" t="n">
-        <v>1.554591973929464</v>
+        <v>-5.492956313728725</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4139,19 +4139,19 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Shooting Star, Bearish Harami</t>
+          <t>Doji</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W40" t="n">
         <v>59.3</v>
       </c>
       <c r="X40" t="n">
-        <v>69.3</v>
+        <v>63.4</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -4160,73 +4160,73 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 55); RSI in forza (68) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (101.13); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 47); doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>100.6500015258789</v>
+        <v>100.8489990234375</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8314985309479273</v>
+        <v>-0.0009910269694768381</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.593661784192268</v>
+        <v>1.101753406954886</v>
       </c>
       <c r="G41" t="n">
-        <v>-5.386346940665065</v>
+        <v>1.754614471170024</v>
       </c>
       <c r="H41" t="n">
-        <v>8.752023994630488</v>
+        <v>1.919153242812754</v>
       </c>
       <c r="I41" t="n">
-        <v>50.97020822055099</v>
+        <v>70.86405761846353</v>
       </c>
       <c r="J41" t="n">
-        <v>46.52844539746643</v>
+        <v>54.89484458347739</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5990084776839427</v>
+        <v>1.041947247685287</v>
       </c>
       <c r="L41" t="n">
-        <v>100.2143638940623</v>
+        <v>99.76036361008239</v>
       </c>
       <c r="M41" t="n">
-        <v>99.93472994157919</v>
+        <v>99.29272858473286</v>
       </c>
       <c r="N41" t="n">
-        <v>95.06093793713073</v>
+        <v>99.14667076607421</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3748028453174477</v>
+        <v>0.09386075120064258</v>
       </c>
       <c r="P41" t="n">
-        <v>69.75124385663119</v>
+        <v>86.6152896751348</v>
       </c>
       <c r="Q41" t="n">
-        <v>-30.24875614336881</v>
+        <v>-13.38471032486519</v>
       </c>
       <c r="R41" t="n">
-        <v>17.74701167618312</v>
+        <v>145.1195446475313</v>
       </c>
       <c r="S41" t="n">
-        <v>-5.492956313728725</v>
+        <v>1.672544148802957</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4240,14 +4240,14 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>59.3</v>
+        <v>59.1</v>
       </c>
       <c r="X41" t="n">
-        <v>63.4</v>
+        <v>63.9</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 47); doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 55); RSI in forza (71) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (101.13); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -4277,63 +4277,59 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>161.2680053710938</v>
+        <v>161.2079925537109</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4159397522983665</v>
+        <v>0.3785718724091724</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7106728617875646</v>
+        <v>0.6731953025838733</v>
       </c>
       <c r="G42" t="n">
-        <v>1.497913546333551</v>
+        <v>1.460143030499528</v>
       </c>
       <c r="H42" t="n">
-        <v>1.606624966604153</v>
+        <v>1.56881399588511</v>
       </c>
       <c r="I42" t="n">
-        <v>70.48981637109725</v>
+        <v>70.03673550128812</v>
       </c>
       <c r="J42" t="n">
         <v>50.61984995168159</v>
       </c>
       <c r="K42" t="n">
-        <v>1.054574012824137</v>
+        <v>1.036896044185744</v>
       </c>
       <c r="L42" t="n">
-        <v>159.9777249539798</v>
+        <v>159.9720094475624</v>
       </c>
       <c r="M42" t="n">
-        <v>159.2427732014213</v>
+        <v>159.2404197576024</v>
       </c>
       <c r="N42" t="n">
-        <v>156.1689285862524</v>
+        <v>156.1683314437909</v>
       </c>
       <c r="O42" t="n">
-        <v>0.06518170048389926</v>
+        <v>0.06135182267940742</v>
       </c>
       <c r="P42" t="n">
-        <v>90.19036199343256</v>
+        <v>87.10804943612411</v>
       </c>
       <c r="Q42" t="n">
-        <v>-9.80963800656745</v>
+        <v>-12.89195056387589</v>
       </c>
       <c r="R42" t="n">
-        <v>83.63754853570602</v>
+        <v>82.47273448868609</v>
       </c>
       <c r="S42" t="n">
-        <v>1.414934110605448</v>
+        <v>1.377194473988341</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom</t>
@@ -4352,7 +4348,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (70) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (161.46); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (70) — momentum positivo; pattern: Double Bottom; vicino alla resistenza dei 20g (161.46); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7269,52 +7265,52 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.323451638221741</v>
+        <v>1.323241353034973</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.5015826030798087</v>
+        <v>-0.5173920536718279</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.336674983763353</v>
+        <v>-1.35235174529279</v>
       </c>
       <c r="G74" t="n">
-        <v>-1.484907387400503</v>
+        <v>-1.500560596064249</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.355207607878772</v>
+        <v>-1.370881424732184</v>
       </c>
       <c r="I74" t="n">
-        <v>34.00810467124548</v>
+        <v>33.88632973511928</v>
       </c>
       <c r="J74" t="n">
         <v>28.6844322067588</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.1591493014751707</v>
+        <v>-0.1637865277029999</v>
       </c>
       <c r="L74" t="n">
-        <v>1.339511614819239</v>
+        <v>1.339491587658594</v>
       </c>
       <c r="M74" t="n">
-        <v>1.342788720361683</v>
+        <v>1.342780473883771</v>
       </c>
       <c r="N74" t="n">
-        <v>1.340006193827371</v>
+        <v>1.340004101437453</v>
       </c>
       <c r="O74" t="n">
-        <v>-0.001170378166407305</v>
+        <v>-0.001183798075762277</v>
       </c>
       <c r="P74" t="n">
-        <v>22.17757760376759</v>
+        <v>21.51824926647854</v>
       </c>
       <c r="Q74" t="n">
-        <v>-77.82242239623241</v>
+        <v>-78.48175073352147</v>
       </c>
       <c r="R74" t="n">
-        <v>-253.5079585172091</v>
+        <v>-254.2184616751978</v>
       </c>
       <c r="S74" t="n">
-        <v>-1.474319766589482</v>
+        <v>-1.489974657535953</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7925,52 +7921,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.147842049598694</v>
+        <v>1.14771032333374</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.251381349111679</v>
+        <v>-0.2628284928835489</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.8425114385193111</v>
+        <v>-0.8538907442477872</v>
       </c>
       <c r="G81" t="n">
-        <v>-1.26377647509891</v>
+        <v>-1.275107436484324</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.173097701109904</v>
+        <v>-1.184439068784415</v>
       </c>
       <c r="I81" t="n">
-        <v>33.385186109595</v>
+        <v>33.27320111805405</v>
       </c>
       <c r="J81" t="n">
         <v>34.4828225717103</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.02631480536629894</v>
+        <v>-0.03073651866660484</v>
       </c>
       <c r="L81" t="n">
-        <v>1.158464323232248</v>
+        <v>1.15845177787368</v>
       </c>
       <c r="M81" t="n">
-        <v>1.162710769862172</v>
+        <v>1.162705604126292</v>
       </c>
       <c r="N81" t="n">
-        <v>1.161069697474099</v>
+        <v>1.161068386764995</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.0005438843822282865</v>
+        <v>-0.0005522908447209802</v>
       </c>
       <c r="P81" t="n">
-        <v>24.19919356489347</v>
+        <v>23.63376793499396</v>
       </c>
       <c r="Q81" t="n">
-        <v>-75.80080643510654</v>
+        <v>-76.36623206500605</v>
       </c>
       <c r="R81" t="n">
-        <v>-164.6270700286243</v>
+        <v>-163.2346178203859</v>
       </c>
       <c r="S81" t="n">
-        <v>-1.228195682466116</v>
+        <v>-1.239530727100546</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10499,12 +10495,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -10513,52 +10509,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>69.18000030517578</v>
+        <v>63000</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.6412717656335443</v>
+        <v>0.1645996021363727</v>
       </c>
       <c r="F109" t="n">
-        <v>-2.790908644545065</v>
+        <v>-2.2062946330065</v>
       </c>
       <c r="G109" t="n">
-        <v>-15.56462835882673</v>
+        <v>-14.32832246802425</v>
       </c>
       <c r="H109" t="n">
-        <v>-19.74730505873121</v>
+        <v>-18.31641046003744</v>
       </c>
       <c r="I109" t="n">
-        <v>41.4509384019511</v>
+        <v>35.49326405401149</v>
       </c>
       <c r="J109" t="n">
-        <v>48.88619086340117</v>
+        <v>53.64910087311483</v>
       </c>
       <c r="K109" t="n">
-        <v>0.4700093363625951</v>
+        <v>0.3705820744032753</v>
       </c>
       <c r="L109" t="n">
-        <v>71.72523136923382</v>
+        <v>65927.57246093976</v>
       </c>
       <c r="M109" t="n">
-        <v>77.17467736206044</v>
+        <v>69895.44491086912</v>
       </c>
       <c r="N109" t="n">
-        <v>100.3760559780021</v>
+        <v>78237.39467444133</v>
       </c>
       <c r="O109" t="n">
-        <v>0.9331811878456584</v>
+        <v>444.6737077338403</v>
       </c>
       <c r="P109" t="n">
-        <v>56.46252084386892</v>
+        <v>47.80660181538165</v>
       </c>
       <c r="Q109" t="n">
-        <v>-43.53747915613108</v>
+        <v>-52.19339818461835</v>
       </c>
       <c r="R109" t="n">
-        <v>-8.131153414414376</v>
+        <v>-24.73624144008481</v>
       </c>
       <c r="S109" t="n">
-        <v>-16.19349776827119</v>
+        <v>-14.13679529004546</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10567,19 +10563,19 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Doji</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W109" t="n">
-        <v>33.9</v>
+        <v>33.8</v>
       </c>
       <c r="X109" t="n">
-        <v>76.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -10588,19 +10584,19 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 49); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 54); RSI scarico (35) — zona di interesse long; pattern: Bull Flag / Consolidation; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10609,52 +10605,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>63074.69921875</v>
+        <v>68.83000183105469</v>
       </c>
       <c r="E110" t="n">
-        <v>0.2833649566869489</v>
+        <v>-1.143951776030117</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.090340452219486</v>
+        <v>-3.282713118309444</v>
       </c>
       <c r="G110" t="n">
-        <v>-14.22674139849027</v>
+        <v>-15.99180747281768</v>
       </c>
       <c r="H110" t="n">
-        <v>-18.21955807395283</v>
+        <v>-20.1533229923774</v>
       </c>
       <c r="I110" t="n">
-        <v>35.80078524003233</v>
+        <v>40.89059568222741</v>
       </c>
       <c r="J110" t="n">
-        <v>53.64910087311483</v>
+        <v>48.88619086340117</v>
       </c>
       <c r="K110" t="n">
-        <v>0.375177318112401</v>
+        <v>0.4545793632867004</v>
       </c>
       <c r="L110" t="n">
-        <v>65934.68667224929</v>
+        <v>71.69189818122229</v>
       </c>
       <c r="M110" t="n">
-        <v>69898.37429199657</v>
+        <v>77.16095193170274</v>
       </c>
       <c r="N110" t="n">
-        <v>78238.13795024979</v>
+        <v>100.3725734061203</v>
       </c>
       <c r="O110" t="n">
-        <v>449.4408373634697</v>
+        <v>0.9108451028875004</v>
       </c>
       <c r="P110" t="n">
-        <v>48.72437116026337</v>
+        <v>54.20796738306178</v>
       </c>
       <c r="Q110" t="n">
-        <v>-51.27562883973663</v>
+        <v>-45.79203261693822</v>
       </c>
       <c r="R110" t="n">
-        <v>-24.47455434660233</v>
+        <v>-9.072733413778497</v>
       </c>
       <c r="S110" t="n">
-        <v>-14.03498712637554</v>
+        <v>-16.61749527872418</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10664,11 +10660,11 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Inside Bar, Bull Flag / Consolidation</t>
+          <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W110" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="X110" t="n">
         <v>73.3</v>
@@ -10680,7 +10676,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 54); RSI scarico (36) — zona di interesse long; pattern: Bull Flag / Consolidation</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 49); pattern: Bull Flag / Consolidation; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -10797,69 +10793,73 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1702.2900390625</v>
+        <v>1700.180053710938</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.4237067262246708</v>
+        <v>-0.5471313573681802</v>
       </c>
       <c r="F112" t="n">
-        <v>1.313846425227894</v>
+        <v>1.18826810017032</v>
       </c>
       <c r="G112" t="n">
-        <v>-15.20571241220897</v>
+        <v>-15.31081477467415</v>
       </c>
       <c r="H112" t="n">
-        <v>-29.68857615075968</v>
+        <v>-29.77572703043651</v>
       </c>
       <c r="I112" t="n">
-        <v>38.33548944044239</v>
+        <v>38.19297380672133</v>
       </c>
       <c r="J112" t="n">
         <v>50.99003675562322</v>
       </c>
       <c r="K112" t="n">
-        <v>0.4120888047036948</v>
+        <v>0.4083813834807802</v>
       </c>
       <c r="L112" t="n">
-        <v>1778.407849772546</v>
+        <v>1778.206898786683</v>
       </c>
       <c r="M112" t="n">
-        <v>1940.993186786887</v>
+        <v>1940.910442263296</v>
       </c>
       <c r="N112" t="n">
-        <v>2370.684475954701</v>
+        <v>2370.663481075581</v>
       </c>
       <c r="O112" t="n">
-        <v>21.26608974243412</v>
+        <v>21.13143540660806</v>
       </c>
       <c r="P112" t="n">
-        <v>57.37032910233274</v>
+        <v>56.75204381115561</v>
       </c>
       <c r="Q112" t="n">
-        <v>-42.62967089766725</v>
+        <v>-43.2479561888444</v>
       </c>
       <c r="R112" t="n">
-        <v>-18.45262320752426</v>
+        <v>-18.68731576038289</v>
       </c>
       <c r="S112" t="n">
-        <v>-15.39223575984848</v>
+        <v>-15.49710692696963</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
       <c r="V112" t="inlineStr">
         <is>
           <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W112" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="X112" t="n">
-        <v>74.2</v>
+        <v>77.8</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); pattern: Bull Flag / Consolidation</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
@@ -10889,52 +10889,52 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7.89799976348877</v>
+        <v>7.863999843597412</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.295500187715648</v>
+        <v>-1.720410948291784</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.9955611110241125</v>
+        <v>-1.421763072522653</v>
       </c>
       <c r="G113" t="n">
-        <v>-12.13083483872967</v>
+        <v>-12.50910081313683</v>
       </c>
       <c r="H113" t="n">
-        <v>-17.9438596359119</v>
+        <v>-18.29710125182967</v>
       </c>
       <c r="I113" t="n">
-        <v>39.95966173475026</v>
+        <v>39.44543998498837</v>
       </c>
       <c r="J113" t="n">
         <v>41.16426805910175</v>
       </c>
       <c r="K113" t="n">
-        <v>0.3906322811943439</v>
+        <v>0.3749403494726282</v>
       </c>
       <c r="L113" t="n">
-        <v>8.233618333773268</v>
+        <v>8.230380246164568</v>
       </c>
       <c r="M113" t="n">
-        <v>8.719096722895459</v>
+        <v>8.71776339270364</v>
       </c>
       <c r="N113" t="n">
-        <v>10.59921345208019</v>
+        <v>10.59887514441958</v>
       </c>
       <c r="O113" t="n">
-        <v>0.06583238401375413</v>
+        <v>0.06366258855629925</v>
       </c>
       <c r="P113" t="n">
-        <v>56.44997171450819</v>
+        <v>54.24938205536303</v>
       </c>
       <c r="Q113" t="n">
-        <v>-43.55002828549181</v>
+        <v>-45.75061794463698</v>
       </c>
       <c r="R113" t="n">
-        <v>-20.15343132461668</v>
+        <v>-21.13096731029091</v>
       </c>
       <c r="S113" t="n">
-        <v>-12.39276470590102</v>
+        <v>-12.76990310436901</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -10948,10 +10948,10 @@
         </is>
       </c>
       <c r="W113" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="X113" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -10981,52 +10981,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.13289999961853</v>
+        <v>1.130100011825562</v>
       </c>
       <c r="E114" t="n">
-        <v>-1.093220000299733</v>
+        <v>-1.337670328426011</v>
       </c>
       <c r="F114" t="n">
-        <v>-4.463463267740342</v>
+        <v>-4.699583963938514</v>
       </c>
       <c r="G114" t="n">
-        <v>-14.71226209106604</v>
+        <v>-14.9230526507936</v>
       </c>
       <c r="H114" t="n">
-        <v>-21.03481904808753</v>
+        <v>-21.22998326629687</v>
       </c>
       <c r="I114" t="n">
-        <v>39.05790865877866</v>
+        <v>38.7851861354335</v>
       </c>
       <c r="J114" t="n">
         <v>38.6536907671133</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3354272937458474</v>
+        <v>0.3250230627019157</v>
       </c>
       <c r="L114" t="n">
-        <v>1.193184792375637</v>
+        <v>1.192918126871545</v>
       </c>
       <c r="M114" t="n">
-        <v>1.267513019075564</v>
+        <v>1.267403215632702</v>
       </c>
       <c r="N114" t="n">
-        <v>1.570226969982881</v>
+        <v>1.570199109407827</v>
       </c>
       <c r="O114" t="n">
-        <v>0.00756722812000641</v>
+        <v>0.007388539440341103</v>
       </c>
       <c r="P114" t="n">
-        <v>33.34740697046416</v>
+        <v>32.15404383353682</v>
       </c>
       <c r="Q114" t="n">
-        <v>-66.65259302953584</v>
+        <v>-67.84595616646318</v>
       </c>
       <c r="R114" t="n">
-        <v>-29.38201820817617</v>
+        <v>-29.99099412716196</v>
       </c>
       <c r="S114" t="n">
-        <v>-15.35023403388661</v>
+        <v>-15.55944783162921</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11036,10 +11036,10 @@
       <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr"/>
       <c r="W114" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="X114" t="n">
-        <v>68.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -11069,52 +11069,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.9599999785423279</v>
+        <v>0.9520000219345093</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.289006117569591</v>
+        <v>-2.111593289887193</v>
       </c>
       <c r="F115" t="n">
-        <v>-2.034123193460458</v>
+        <v>-2.850501090352953</v>
       </c>
       <c r="G115" t="n">
-        <v>-20.84119500641926</v>
+        <v>-21.50084815145055</v>
       </c>
       <c r="H115" t="n">
-        <v>-28.1580715148509</v>
+        <v>-28.75675101833993</v>
       </c>
       <c r="I115" t="n">
-        <v>34.92020483575737</v>
+        <v>34.12522933717494</v>
       </c>
       <c r="J115" t="n">
         <v>68.11421132733075</v>
       </c>
       <c r="K115" t="n">
-        <v>0.3372021782981767</v>
+        <v>0.315056782254054</v>
       </c>
       <c r="L115" t="n">
-        <v>1.026755563046949</v>
+        <v>1.025993662417633</v>
       </c>
       <c r="M115" t="n">
-        <v>1.129878498780976</v>
+        <v>1.129564774992434</v>
       </c>
       <c r="N115" t="n">
-        <v>1.65781937352026</v>
+        <v>1.657739771961973</v>
       </c>
       <c r="O115" t="n">
-        <v>0.008114644019268646</v>
+        <v>0.007604105477915041</v>
       </c>
       <c r="P115" t="n">
-        <v>44.44984206076799</v>
+        <v>39.17470708433212</v>
       </c>
       <c r="Q115" t="n">
-        <v>-55.55015793923201</v>
+        <v>-60.82529291566788</v>
       </c>
       <c r="R115" t="n">
-        <v>-27.87480425155955</v>
+        <v>-29.13994504645431</v>
       </c>
       <c r="S115" t="n">
-        <v>-19.47004950457921</v>
+        <v>-20.14112880040519</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="W115" t="n">
-        <v>31.4</v>
+        <v>30.4</v>
       </c>
       <c r="X115" t="n">
-        <v>68.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 68); RSI scarico (35) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 68); RSI scarico (34) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -11161,52 +11161,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.1615999937057495</v>
+        <v>0.1608999967575073</v>
       </c>
       <c r="E116" t="n">
-        <v>-1.118535391991604</v>
+        <v>-1.546856717234713</v>
       </c>
       <c r="F116" t="n">
-        <v>-5.910308116031427</v>
+        <v>-6.317873089701864</v>
       </c>
       <c r="G116" t="n">
-        <v>-31.06272674806697</v>
+        <v>-31.36133988405729</v>
       </c>
       <c r="H116" t="n">
-        <v>-37.57315938600514</v>
+        <v>-37.843571512368</v>
       </c>
       <c r="I116" t="n">
-        <v>30.63661413326776</v>
+        <v>30.38815939416243</v>
       </c>
       <c r="J116" t="n">
         <v>61.78776930619959</v>
       </c>
       <c r="K116" t="n">
-        <v>0.3052479494591122</v>
+        <v>0.2991171962819937</v>
       </c>
       <c r="L116" t="n">
-        <v>0.1840092609239709</v>
+        <v>0.1839425945479478</v>
       </c>
       <c r="M116" t="n">
-        <v>0.2119679625190941</v>
+        <v>0.2119405116583787</v>
       </c>
       <c r="N116" t="n">
-        <v>0.3154594704005644</v>
+        <v>0.3154525052568009</v>
       </c>
       <c r="O116" t="n">
-        <v>0.001381264188588759</v>
+        <v>0.001336592018672454</v>
       </c>
       <c r="P116" t="n">
-        <v>30.90391009804089</v>
+        <v>29.1555352425416</v>
       </c>
       <c r="Q116" t="n">
-        <v>-69.0960899019591</v>
+        <v>-70.8444647574584</v>
       </c>
       <c r="R116" t="n">
-        <v>-41.00758031600183</v>
+        <v>-41.41914915844051</v>
       </c>
       <c r="S116" t="n">
-        <v>-30.52421112716619</v>
+        <v>-30.82515693212864</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11216,10 +11216,10 @@
       <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="n">
-        <v>30.4</v>
+        <v>29.5</v>
       </c>
       <c r="X116" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 62); RSI scarico (31) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 62); RSI scarico (30) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -11249,52 +11249,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.010000228881836</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="E117" t="n">
-        <v>-4.708735228924176</v>
+        <v>-7.087054406792803</v>
       </c>
       <c r="F117" t="n">
-        <v>-10.5050080449666</v>
+        <v>-12.73866142548572</v>
       </c>
       <c r="G117" t="n">
-        <v>-32.56926105844337</v>
+        <v>-34.25222559866464</v>
       </c>
       <c r="H117" t="n">
-        <v>-38.30363993273449</v>
+        <v>-39.84348345045014</v>
       </c>
       <c r="I117" t="n">
-        <v>23.21436317430548</v>
+        <v>22.05730419553836</v>
       </c>
       <c r="J117" t="n">
-        <v>87.65845511487178</v>
+        <v>87.82946111114951</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1874165908091151</v>
+        <v>0.1528935439758038</v>
       </c>
       <c r="L117" t="n">
-        <v>7.138229801037531</v>
+        <v>7.123944077669204</v>
       </c>
       <c r="M117" t="n">
-        <v>8.06337299823071</v>
+        <v>8.057490641549634</v>
       </c>
       <c r="N117" t="n">
-        <v>11.05922036862967</v>
+        <v>11.05772783036731</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.009766581792032936</v>
+        <v>-0.01933923745080857</v>
       </c>
       <c r="P117" t="n">
-        <v>1.979376578516438</v>
+        <v>8.096158307103225</v>
       </c>
       <c r="Q117" t="n">
-        <v>-98.02062342148356</v>
+        <v>-91.90384169289678</v>
       </c>
       <c r="R117" t="n">
-        <v>-62.27258194550118</v>
+        <v>-69.56201689779014</v>
       </c>
       <c r="S117" t="n">
-        <v>-31.82745849084812</v>
+        <v>-33.52893724931324</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11308,10 +11308,10 @@
         </is>
       </c>
       <c r="W117" t="n">
-        <v>29.1</v>
+        <v>28.8</v>
       </c>
       <c r="X117" t="n">
-        <v>78.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 88); RSI ipervenduto (23) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (5.9758)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 88); RSI ipervenduto (22) — possibile rimbalzo; breakdown minimi 50g — rottura supporto importante</t>
         </is>
       </c>
     </row>
@@ -14957,79 +14957,87 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CAC 40</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8421.1396484375</v>
+        <v>161.2079925537109</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8414635871940357</v>
+        <v>0.6731953025838733</v>
       </c>
       <c r="F40" t="n">
-        <v>5.892322025745722</v>
+        <v>1.784286536355539</v>
       </c>
       <c r="G40" t="n">
-        <v>3.415057630986351</v>
+        <v>1.707866418959214</v>
       </c>
       <c r="H40" t="n">
-        <v>18.5274726936222</v>
+        <v>12.14703559846435</v>
       </c>
       <c r="I40" t="n">
-        <v>58.17831474702005</v>
+        <v>62.27390815913697</v>
       </c>
       <c r="J40" t="n">
-        <v>12.45597245375785</v>
+        <v>10.55074253768085</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7627512036313242</v>
+        <v>0.8725713537062421</v>
       </c>
       <c r="L40" t="n">
-        <v>8168.607674169102</v>
+        <v>158.2859097814813</v>
       </c>
       <c r="M40" t="n">
-        <v>8060.016401926429</v>
+        <v>155.4559497693815</v>
       </c>
       <c r="N40" t="n">
-        <v>7514.309888148564</v>
+        <v>145.9538039091867</v>
       </c>
       <c r="O40" t="n">
-        <v>24.21747481207632</v>
+        <v>0.01014557182323017</v>
       </c>
       <c r="P40" t="n">
-        <v>91.46071316595695</v>
+        <v>96.08535589945195</v>
       </c>
       <c r="Q40" t="n">
-        <v>-8.539286834043047</v>
+        <v>-3.91464410054805</v>
       </c>
       <c r="R40" t="n">
-        <v>107.0289227545307</v>
+        <v>106.2230823908045</v>
       </c>
       <c r="S40" t="n">
-        <v>3.625284974890253</v>
+        <v>5.253254629456672</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Breakout 20d, Breakout 50d, Double Top, Outside Bar</t>
+        </is>
+      </c>
       <c r="W40" t="n">
-        <v>63.9</v>
+        <v>64</v>
       </c>
       <c r="X40" t="n">
-        <v>67.2</v>
+        <v>72.8</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -15038,19 +15046,19 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 12)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 11); RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (161.46)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>CAC 40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -15059,52 +15067,52 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>24985.8203125</v>
+        <v>8421.1396484375</v>
       </c>
       <c r="E41" t="n">
-        <v>1.422834388597272</v>
+        <v>0.8414635871940357</v>
       </c>
       <c r="F41" t="n">
-        <v>4.32244404409734</v>
+        <v>5.892322025745722</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3417949600460046</v>
+        <v>3.415057630986351</v>
       </c>
       <c r="H41" t="n">
-        <v>22.63521231143362</v>
+        <v>18.5274726936222</v>
       </c>
       <c r="I41" t="n">
-        <v>56.53868801529867</v>
+        <v>58.17831474702005</v>
       </c>
       <c r="J41" t="n">
-        <v>21.13359089329466</v>
+        <v>12.45597245375785</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7125488905055738</v>
+        <v>0.7627512036313242</v>
       </c>
       <c r="L41" t="n">
-        <v>24368.42154966652</v>
+        <v>8168.607674169102</v>
       </c>
       <c r="M41" t="n">
-        <v>23856.27891995374</v>
+        <v>8060.016401926429</v>
       </c>
       <c r="N41" t="n">
-        <v>20207.63814737558</v>
+        <v>7514.309888148564</v>
       </c>
       <c r="O41" t="n">
-        <v>96.07444769695955</v>
+        <v>24.21747481207632</v>
       </c>
       <c r="P41" t="n">
-        <v>87.33872620130641</v>
+        <v>91.46071316595695</v>
       </c>
       <c r="Q41" t="n">
-        <v>-12.66127379869358</v>
+        <v>-8.539286834043047</v>
       </c>
       <c r="R41" t="n">
-        <v>78.63464912413002</v>
+        <v>107.0289227545307</v>
       </c>
       <c r="S41" t="n">
-        <v>1.821643982177146</v>
+        <v>3.625284974890253</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -15112,16 +15120,12 @@
         </is>
       </c>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="n">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
       <c r="X41" t="n">
-        <v>71.7</v>
+        <v>67.2</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -15130,73 +15134,73 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); pattern: Double Top</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 12)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6.177999973297119</v>
+        <v>24985.8203125</v>
       </c>
       <c r="E42" t="n">
-        <v>5.787668011608704</v>
+        <v>1.422834388597272</v>
       </c>
       <c r="F42" t="n">
-        <v>7.724495718734103</v>
+        <v>4.32244404409734</v>
       </c>
       <c r="G42" t="n">
-        <v>6.719639603693883</v>
+        <v>0.3417949600460046</v>
       </c>
       <c r="H42" t="n">
-        <v>49.76969632235439</v>
+        <v>22.63521231143362</v>
       </c>
       <c r="I42" t="n">
-        <v>61.72843462210307</v>
+        <v>56.53868801529867</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28433935727599</v>
+        <v>21.13359089329466</v>
       </c>
       <c r="K42" t="n">
-        <v>0.9170378079990626</v>
+        <v>0.7125488905055738</v>
       </c>
       <c r="L42" t="n">
-        <v>5.709247533545765</v>
+        <v>24368.42154966652</v>
       </c>
       <c r="M42" t="n">
-        <v>5.463772509743818</v>
+        <v>23856.27891995374</v>
       </c>
       <c r="N42" t="n">
-        <v>4.148066351409051</v>
+        <v>20207.63814737558</v>
       </c>
       <c r="O42" t="n">
-        <v>0.03811617807437445</v>
+        <v>96.07444769695955</v>
       </c>
       <c r="P42" t="n">
-        <v>97.98923666328344</v>
+        <v>87.33872620130641</v>
       </c>
       <c r="Q42" t="n">
-        <v>-2.010763336716566</v>
+        <v>-12.66127379869358</v>
       </c>
       <c r="R42" t="n">
-        <v>139.2670784545309</v>
+        <v>78.63464912413002</v>
       </c>
       <c r="S42" t="n">
-        <v>3.553467823363077</v>
+        <v>1.821643982177146</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -15206,14 +15210,14 @@
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W42" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="X42" t="n">
-        <v>75.2</v>
+        <v>71.7</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -15222,73 +15226,73 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (62) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (6.2060)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); pattern: Double Top</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Intesa Sanpaolo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>100.6500015258789</v>
+        <v>6.177999973297119</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.319486964686435</v>
+        <v>5.787668011608704</v>
       </c>
       <c r="F43" t="n">
-        <v>-5.776070199000638</v>
+        <v>7.724495718734103</v>
       </c>
       <c r="G43" t="n">
-        <v>3.103870819551857</v>
+        <v>6.719639603693883</v>
       </c>
       <c r="H43" t="n">
-        <v>17.81575695462221</v>
+        <v>49.76969632235439</v>
       </c>
       <c r="I43" t="n">
-        <v>53.88141929769053</v>
+        <v>61.72843462210307</v>
       </c>
       <c r="J43" t="n">
-        <v>31.28560648785813</v>
+        <v>19.28433935727599</v>
       </c>
       <c r="K43" t="n">
-        <v>0.603731701898174</v>
+        <v>0.9170378079990626</v>
       </c>
       <c r="L43" t="n">
-        <v>98.1659143121184</v>
+        <v>5.709247533545765</v>
       </c>
       <c r="M43" t="n">
-        <v>94.55274699429772</v>
+        <v>5.463772509743818</v>
       </c>
       <c r="N43" t="n">
-        <v>92.52161058251333</v>
+        <v>4.148066351409051</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.118297634207388</v>
+        <v>0.03811617807437445</v>
       </c>
       <c r="P43" t="n">
-        <v>64.64778282180119</v>
+        <v>97.98923666328344</v>
       </c>
       <c r="Q43" t="n">
-        <v>-35.35221717819881</v>
+        <v>-2.010763336716566</v>
       </c>
       <c r="R43" t="n">
-        <v>28.94036877973342</v>
+        <v>139.2670784545309</v>
       </c>
       <c r="S43" t="n">
-        <v>9.461669240221804</v>
+        <v>3.553467823363077</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -15298,14 +15302,14 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakout 20d, Breakout 50d</t>
         </is>
       </c>
       <c r="W43" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="X43" t="n">
-        <v>66.3</v>
+        <v>75.2</v>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
@@ -15314,94 +15318,90 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 31); in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (62) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (6.2060)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>161.2680053710938</v>
+        <v>100.6500015258789</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7106728617875646</v>
+        <v>-2.319486964686435</v>
       </c>
       <c r="F44" t="n">
-        <v>1.822177720927609</v>
+        <v>-5.776070199000638</v>
       </c>
       <c r="G44" t="n">
-        <v>1.745729154653053</v>
+        <v>3.103870819551857</v>
       </c>
       <c r="H44" t="n">
-        <v>12.18878451835832</v>
+        <v>17.81575695462221</v>
       </c>
       <c r="I44" t="n">
-        <v>62.41341794467198</v>
+        <v>53.88141929769053</v>
       </c>
       <c r="J44" t="n">
-        <v>10.55074253768085</v>
+        <v>31.28560648785813</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8787774632657759</v>
+        <v>0.603731701898174</v>
       </c>
       <c r="L44" t="n">
-        <v>158.2916252878987</v>
+        <v>98.1659143121184</v>
       </c>
       <c r="M44" t="n">
-        <v>155.4583032132004</v>
+        <v>94.55274699429772</v>
       </c>
       <c r="N44" t="n">
-        <v>145.9544010516483</v>
+        <v>92.52161058251333</v>
       </c>
       <c r="O44" t="n">
-        <v>0.01397544962772201</v>
+        <v>-0.118297634207388</v>
       </c>
       <c r="P44" t="n">
-        <v>97.02130089929727</v>
+        <v>64.64778282180119</v>
       </c>
       <c r="Q44" t="n">
-        <v>-2.978699100702732</v>
+        <v>-35.35221717819881</v>
       </c>
       <c r="R44" t="n">
-        <v>106.9010277658738</v>
+        <v>28.94036877973342</v>
       </c>
       <c r="S44" t="n">
-        <v>5.292437205016132</v>
+        <v>9.461669240221804</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Double Top, Outside Bar</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W44" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="X44" t="n">
-        <v>72.8</v>
+        <v>66.3</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 11); RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (161.46)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 31); in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -17257,87 +17257,87 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BRK</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>489.4599914550781</v>
+        <v>100.8489990234375</v>
       </c>
       <c r="E65" t="n">
-        <v>0.04292109454842041</v>
+        <v>1.101753406954886</v>
       </c>
       <c r="F65" t="n">
-        <v>1.40045143507217</v>
+        <v>1.590613915349004</v>
       </c>
       <c r="G65" t="n">
-        <v>2.190114246746178</v>
+        <v>3.328894057491083</v>
       </c>
       <c r="H65" t="n">
-        <v>-6.611206591158892</v>
+        <v>1.071357243153659</v>
       </c>
       <c r="I65" t="n">
-        <v>52.06621615619112</v>
+        <v>60.05194458306903</v>
       </c>
       <c r="J65" t="n">
-        <v>36.17625734232099</v>
+        <v>20.63682955986187</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5870532320154289</v>
+        <v>0.938670984090488</v>
       </c>
       <c r="L65" t="n">
-        <v>484.8517939037239</v>
+        <v>99.14894242084179</v>
       </c>
       <c r="M65" t="n">
-        <v>485.7797495522178</v>
+        <v>99.37124733017839</v>
       </c>
       <c r="N65" t="n">
-        <v>424.6788131191014</v>
+        <v>100.8450903308166</v>
       </c>
       <c r="O65" t="n">
-        <v>1.428531555609</v>
+        <v>0.2105734479301517</v>
       </c>
       <c r="P65" t="n">
-        <v>71.12907366609265</v>
+        <v>92.05033609026985</v>
       </c>
       <c r="Q65" t="n">
-        <v>-28.87092633390735</v>
+        <v>-7.949663909730146</v>
       </c>
       <c r="R65" t="n">
-        <v>52.78088743252142</v>
+        <v>129.2182226477905</v>
       </c>
       <c r="S65" t="n">
-        <v>1.85836320281072</v>
+        <v>3.978761980269607</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
+          <t>Bullish Engulfing, Piercing Pattern</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Breakout 20d, Breakout 50d, Double Top, Double Bottom, Outside Bar</t>
         </is>
       </c>
       <c r="W65" t="n">
-        <v>54.4</v>
+        <v>55</v>
       </c>
       <c r="X65" t="n">
-        <v>62.9</v>
+        <v>66.5</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -17346,86 +17346,94 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); RSI in forza (60) — momentum positivo; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (101.13); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>BRK</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>44.7599983215332</v>
+        <v>489.4599914550781</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5165047126461264</v>
+        <v>0.04292109454842041</v>
       </c>
       <c r="F66" t="n">
-        <v>2.028719879912244</v>
+        <v>1.40045143507217</v>
       </c>
       <c r="G66" t="n">
-        <v>5.169165595052871</v>
+        <v>2.190114246746178</v>
       </c>
       <c r="H66" t="n">
-        <v>17.29559355480104</v>
+        <v>-6.611206591158892</v>
       </c>
       <c r="I66" t="n">
-        <v>49.65595351230954</v>
+        <v>52.06621615619112</v>
       </c>
       <c r="J66" t="n">
-        <v>30.08076200644014</v>
+        <v>36.17625734232099</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3252807242240124</v>
+        <v>0.5870532320154289</v>
       </c>
       <c r="L66" t="n">
-        <v>44.99286638580877</v>
+        <v>484.8517939037239</v>
       </c>
       <c r="M66" t="n">
-        <v>43.92064432323007</v>
+        <v>485.7797495522178</v>
       </c>
       <c r="N66" t="n">
-        <v>38.85743619649333</v>
+        <v>424.6788131191014</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.2673364168594695</v>
+        <v>1.428531555609</v>
       </c>
       <c r="P66" t="n">
-        <v>36.42238898736217</v>
+        <v>71.12907366609265</v>
       </c>
       <c r="Q66" t="n">
-        <v>-63.57761101263783</v>
+        <v>-28.87092633390735</v>
       </c>
       <c r="R66" t="n">
-        <v>-33.5098963175725</v>
+        <v>52.78088743252142</v>
       </c>
       <c r="S66" t="n">
-        <v>3.491325598920691</v>
+        <v>1.85836320281072</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W66" t="n">
         <v>54.4</v>
       </c>
       <c r="X66" t="n">
-        <v>62</v>
+        <v>62.9</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -17434,90 +17442,86 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 30); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 36); pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>173.6300048828125</v>
+        <v>44.7599983215332</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.25883786416075</v>
+        <v>0.5165047126461264</v>
       </c>
       <c r="F67" t="n">
-        <v>-9.141810917180148</v>
+        <v>2.028719879912244</v>
       </c>
       <c r="G67" t="n">
-        <v>4.144675870630521</v>
+        <v>5.169165595052871</v>
       </c>
       <c r="H67" t="n">
-        <v>28.01739927152025</v>
+        <v>17.29559355480104</v>
       </c>
       <c r="I67" t="n">
-        <v>45.16086298812717</v>
+        <v>49.65595351230954</v>
       </c>
       <c r="J67" t="n">
-        <v>42.05428199623417</v>
+        <v>30.08076200644014</v>
       </c>
       <c r="K67" t="n">
-        <v>0.04521996535720588</v>
+        <v>0.3252807242240124</v>
       </c>
       <c r="L67" t="n">
-        <v>183.3215586411724</v>
+        <v>44.99286638580877</v>
       </c>
       <c r="M67" t="n">
-        <v>173.1106894397758</v>
+        <v>43.92064432323007</v>
       </c>
       <c r="N67" t="n">
-        <v>155.9825587859165</v>
+        <v>38.85743619649333</v>
       </c>
       <c r="O67" t="n">
-        <v>-2.665156653299471</v>
+        <v>-0.2673364168594695</v>
       </c>
       <c r="P67" t="n">
-        <v>3.295689249524959</v>
+        <v>36.42238898736217</v>
       </c>
       <c r="Q67" t="n">
-        <v>-96.70431075047505</v>
+        <v>-63.57761101263783</v>
       </c>
       <c r="R67" t="n">
-        <v>-53.64025833569931</v>
+        <v>-33.5098963175725</v>
       </c>
       <c r="S67" t="n">
-        <v>-1.848495831823127</v>
+        <v>3.491325598920691</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="X67" t="n">
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -17526,86 +17530,90 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele; sul supporto dei 20g (172.23); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 30); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>58.22000122070312</v>
+        <v>173.6300048828125</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.3764500533463666</v>
+        <v>-7.25883786416075</v>
       </c>
       <c r="F68" t="n">
-        <v>2.989567447196162</v>
+        <v>-9.141810917180148</v>
       </c>
       <c r="G68" t="n">
-        <v>0.587422505724855</v>
+        <v>4.144675870630521</v>
       </c>
       <c r="H68" t="n">
-        <v>3.172073198381975</v>
+        <v>28.01739927152025</v>
       </c>
       <c r="I68" t="n">
-        <v>53.19376678395456</v>
+        <v>45.16086298812717</v>
       </c>
       <c r="J68" t="n">
-        <v>20.96757464233215</v>
+        <v>42.05428199623417</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7261939050341299</v>
+        <v>0.04521996535720588</v>
       </c>
       <c r="L68" t="n">
-        <v>57.20165546607392</v>
+        <v>183.3215586411724</v>
       </c>
       <c r="M68" t="n">
-        <v>57.4213093074215</v>
+        <v>173.1106894397758</v>
       </c>
       <c r="N68" t="n">
-        <v>51.67957794853982</v>
+        <v>155.9825587859165</v>
       </c>
       <c r="O68" t="n">
-        <v>0.2438322460571044</v>
+        <v>-2.665156653299471</v>
       </c>
       <c r="P68" t="n">
-        <v>82.81253207889803</v>
+        <v>3.295689249524959</v>
       </c>
       <c r="Q68" t="n">
-        <v>-17.18746792110197</v>
+        <v>-96.70431075047505</v>
       </c>
       <c r="R68" t="n">
-        <v>70.91742569829033</v>
+        <v>-53.64025833569931</v>
       </c>
       <c r="S68" t="n">
-        <v>-0.3764500533463666</v>
+        <v>-1.848495831823127</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
         <v>54.3</v>
       </c>
       <c r="X68" t="n">
-        <v>61.9</v>
+        <v>63.2</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -17614,73 +17622,73 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele; sul supporto dei 20g (172.23); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>137.8099975585938</v>
+        <v>58.22000122070312</v>
       </c>
       <c r="E69" t="n">
-        <v>-6.258075839744615</v>
+        <v>-0.3764500533463666</v>
       </c>
       <c r="F69" t="n">
-        <v>-12.73429638014406</v>
+        <v>2.989567447196162</v>
       </c>
       <c r="G69" t="n">
-        <v>2.104168565018139</v>
+        <v>0.587422505724855</v>
       </c>
       <c r="H69" t="n">
-        <v>33.61450298052351</v>
+        <v>3.172073198381975</v>
       </c>
       <c r="I69" t="n">
-        <v>46.03610266759141</v>
+        <v>53.19376678395456</v>
       </c>
       <c r="J69" t="n">
-        <v>41.37648743744665</v>
+        <v>20.96757464233215</v>
       </c>
       <c r="K69" t="n">
-        <v>0.01420294506009345</v>
+        <v>0.7261939050341299</v>
       </c>
       <c r="L69" t="n">
-        <v>146.2464507041888</v>
+        <v>57.20165546607392</v>
       </c>
       <c r="M69" t="n">
-        <v>135.4726181887761</v>
+        <v>57.4213093074215</v>
       </c>
       <c r="N69" t="n">
-        <v>113.6762851011928</v>
+        <v>51.67957794853982</v>
       </c>
       <c r="O69" t="n">
-        <v>-2.756972580864832</v>
+        <v>0.2438322460571044</v>
       </c>
       <c r="P69" t="n">
-        <v>4.832326363547443</v>
+        <v>82.81253207889803</v>
       </c>
       <c r="Q69" t="n">
-        <v>-95.16767363645256</v>
+        <v>-17.18746792110197</v>
       </c>
       <c r="R69" t="n">
-        <v>-57.36295614060902</v>
+        <v>70.91742569829033</v>
       </c>
       <c r="S69" t="n">
-        <v>-2.538894266515157</v>
+        <v>-0.3764500533463666</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -17690,10 +17698,10 @@
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="X69" t="n">
-        <v>57.2</v>
+        <v>61.9</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -17702,73 +17710,73 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 41); sul supporto dei 20g (135.85); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>149.3999938964844</v>
+        <v>137.8099975585938</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.867176212280598</v>
+        <v>-6.258075839744615</v>
       </c>
       <c r="F70" t="n">
-        <v>2.963464929078707</v>
+        <v>-12.73429638014406</v>
       </c>
       <c r="G70" t="n">
-        <v>-5.130811563542426</v>
+        <v>2.104168565018139</v>
       </c>
       <c r="H70" t="n">
-        <v>9.154671751517739</v>
+        <v>33.61450298052351</v>
       </c>
       <c r="I70" t="n">
-        <v>50.17654645539972</v>
+        <v>46.03610266759141</v>
       </c>
       <c r="J70" t="n">
-        <v>30.91478826330792</v>
+        <v>41.37648743744665</v>
       </c>
       <c r="K70" t="n">
-        <v>0.4712692335937358</v>
+        <v>0.01420294506009345</v>
       </c>
       <c r="L70" t="n">
-        <v>149.5190296526709</v>
+        <v>146.2464507041888</v>
       </c>
       <c r="M70" t="n">
-        <v>147.8902455071544</v>
+        <v>135.4726181887761</v>
       </c>
       <c r="N70" t="n">
-        <v>139.3635613802948</v>
+        <v>113.6762851011928</v>
       </c>
       <c r="O70" t="n">
-        <v>0.1969811699000038</v>
+        <v>-2.756972580864832</v>
       </c>
       <c r="P70" t="n">
-        <v>56.33048749450499</v>
+        <v>4.832326363547443</v>
       </c>
       <c r="Q70" t="n">
-        <v>-43.66951250549501</v>
+        <v>-95.16767363645256</v>
       </c>
       <c r="R70" t="n">
-        <v>8.144612420575374</v>
+        <v>-57.36295614060902</v>
       </c>
       <c r="S70" t="n">
-        <v>-3.450957352405937</v>
+        <v>-2.538894266515157</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -17776,16 +17784,12 @@
         </is>
       </c>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Double Top, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="n">
-        <v>53</v>
+        <v>54.2</v>
       </c>
       <c r="X70" t="n">
-        <v>60.9</v>
+        <v>57.2</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -17794,73 +17798,73 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 41); sul supporto dei 20g (135.85); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>228.3899993896484</v>
+        <v>149.3999938964844</v>
       </c>
       <c r="E71" t="n">
-        <v>-5.181216415713097</v>
+        <v>-2.867176212280598</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7410315495696596</v>
+        <v>2.963464929078707</v>
       </c>
       <c r="G71" t="n">
-        <v>3.7476151643834</v>
+        <v>-5.130811563542426</v>
       </c>
       <c r="H71" t="n">
-        <v>50.52396086517226</v>
+        <v>9.154671751517739</v>
       </c>
       <c r="I71" t="n">
-        <v>52.04181422742425</v>
+        <v>50.17654645539972</v>
       </c>
       <c r="J71" t="n">
-        <v>30.67979141546127</v>
+        <v>30.91478826330792</v>
       </c>
       <c r="K71" t="n">
-        <v>0.2576895939088667</v>
+        <v>0.4712692335937358</v>
       </c>
       <c r="L71" t="n">
-        <v>228.9619277485031</v>
+        <v>149.5190296526709</v>
       </c>
       <c r="M71" t="n">
-        <v>211.9459035648006</v>
+        <v>147.8902455071544</v>
       </c>
       <c r="N71" t="n">
-        <v>178.618446149729</v>
+        <v>139.3635613802948</v>
       </c>
       <c r="O71" t="n">
-        <v>-2.22392023925164</v>
+        <v>0.1969811699000038</v>
       </c>
       <c r="P71" t="n">
-        <v>29.88077797050234</v>
+        <v>56.33048749450499</v>
       </c>
       <c r="Q71" t="n">
-        <v>-70.11922202949766</v>
+        <v>-43.66951250549501</v>
       </c>
       <c r="R71" t="n">
-        <v>-16.60866447468998</v>
+        <v>8.144612420575374</v>
       </c>
       <c r="S71" t="n">
-        <v>0.5016498964349525</v>
+        <v>-3.450957352405937</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -17868,12 +17872,16 @@
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Double Top, Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W71" t="n">
-        <v>52.8</v>
+        <v>53</v>
       </c>
       <c r="X71" t="n">
-        <v>56.1</v>
+        <v>60.9</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -17882,94 +17890,86 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31)</t>
+          <t>trend molto direzionale (ADX 31); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>100.7320022583008</v>
+        <v>228.3899993896484</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9844634168428845</v>
+        <v>-5.181216415713097</v>
       </c>
       <c r="F72" t="n">
-        <v>1.472756789235263</v>
+        <v>0.7410315495696596</v>
       </c>
       <c r="G72" t="n">
-        <v>3.209020320845757</v>
+        <v>3.7476151643834</v>
       </c>
       <c r="H72" t="n">
-        <v>0.9541025161862837</v>
+        <v>50.52396086517226</v>
       </c>
       <c r="I72" t="n">
-        <v>59.55159642071497</v>
+        <v>52.04181422742425</v>
       </c>
       <c r="J72" t="n">
-        <v>20.63682955986187</v>
+        <v>30.67979141546127</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9172980262394728</v>
+        <v>0.2576895939088667</v>
       </c>
       <c r="L72" t="n">
-        <v>99.13779987178116</v>
+        <v>228.9619277485031</v>
       </c>
       <c r="M72" t="n">
-        <v>99.36665922174167</v>
+        <v>211.9459035648006</v>
       </c>
       <c r="N72" t="n">
-        <v>100.8439261838998</v>
+        <v>178.618446149729</v>
       </c>
       <c r="O72" t="n">
-        <v>0.2031069877049034</v>
+        <v>-2.22392023925164</v>
       </c>
       <c r="P72" t="n">
-        <v>88.70470526377797</v>
+        <v>29.88077797050234</v>
       </c>
       <c r="Q72" t="n">
-        <v>-11.29529473622204</v>
+        <v>-70.11922202949766</v>
       </c>
       <c r="R72" t="n">
-        <v>126.4696485300107</v>
+        <v>-16.60866447468998</v>
       </c>
       <c r="S72" t="n">
-        <v>3.858134319981321</v>
+        <v>0.5016498964349525</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Breakout 20d, Breakout 50d, Double Top, Double Bottom, Outside Bar</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="X72" t="n">
-        <v>62.4</v>
+        <v>56.1</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (101.13); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 31)</t>
         </is>
       </c>
     </row>
@@ -18375,52 +18375,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.323451638221741</v>
+        <v>1.323241353034973</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.336674983763353</v>
+        <v>-1.35235174529279</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.17124786431001</v>
+        <v>-1.186950910798956</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.975904010188512</v>
+        <v>-1.991479203673208</v>
       </c>
       <c r="H77" t="n">
-        <v>1.866075297044323</v>
+        <v>1.849889645789315</v>
       </c>
       <c r="I77" t="n">
-        <v>42.41224320794789</v>
+        <v>42.34338823758461</v>
       </c>
       <c r="J77" t="n">
         <v>8.297192574645349</v>
       </c>
       <c r="K77" t="n">
-        <v>0.01499094487622545</v>
+        <v>0.01119641178280147</v>
       </c>
       <c r="L77" t="n">
-        <v>1.342034351082253</v>
+        <v>1.342014323921608</v>
       </c>
       <c r="M77" t="n">
-        <v>1.336610340618566</v>
+        <v>1.336602094140653</v>
       </c>
       <c r="N77" t="n">
-        <v>1.305919816461056</v>
+        <v>1.305917724071138</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.002051380515277388</v>
+        <v>-0.002064800424632361</v>
       </c>
       <c r="P77" t="n">
-        <v>14.76476560568566</v>
+        <v>14.34136529797637</v>
       </c>
       <c r="Q77" t="n">
-        <v>-85.23523439431433</v>
+        <v>-85.65863470202363</v>
       </c>
       <c r="R77" t="n">
-        <v>-113.3770114250307</v>
+        <v>-113.8245564476398</v>
       </c>
       <c r="S77" t="n">
-        <v>-4.142397007134369</v>
+        <v>-4.157627963344856</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -18471,52 +18471,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.147842049598694</v>
+        <v>1.14771032333374</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.8425114385193111</v>
+        <v>-0.8538907442477872</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.574845888657128</v>
+        <v>-1.586141151740661</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.349631590017609</v>
+        <v>-2.360837938753901</v>
       </c>
       <c r="H78" t="n">
-        <v>1.959368086373225</v>
+        <v>1.947667237166906</v>
       </c>
       <c r="I78" t="n">
-        <v>41.34120983078301</v>
+        <v>41.28711715015259</v>
       </c>
       <c r="J78" t="n">
         <v>16.06760456933839</v>
       </c>
       <c r="K78" t="n">
-        <v>0.07362123640878293</v>
+        <v>0.07117668963285732</v>
       </c>
       <c r="L78" t="n">
-        <v>1.164127272849773</v>
+        <v>1.164114727491206</v>
       </c>
       <c r="M78" t="n">
-        <v>1.157221537974701</v>
+        <v>1.157216372238821</v>
       </c>
       <c r="N78" t="n">
-        <v>1.123012431869281</v>
+        <v>1.123011121160177</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.002295336832334143</v>
+        <v>-0.002303743294827014</v>
       </c>
       <c r="P78" t="n">
-        <v>14.41233552046294</v>
+        <v>14.10986014962266</v>
       </c>
       <c r="Q78" t="n">
-        <v>-85.58766447953707</v>
+        <v>-85.89013985037734</v>
       </c>
       <c r="R78" t="n">
-        <v>-111.6252015021066</v>
+        <v>-111.8977926118311</v>
       </c>
       <c r="S78" t="n">
-        <v>-4.07254456302325</v>
+        <v>-4.083553190399836</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -20239,52 +20239,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>63074.69921875</v>
+        <v>63000</v>
       </c>
       <c r="E97" t="n">
-        <v>-4.011083909736035</v>
+        <v>-4.124763358539029</v>
       </c>
       <c r="F97" t="n">
-        <v>-18.53903210355973</v>
+        <v>-18.63550613729834</v>
       </c>
       <c r="G97" t="n">
-        <v>-27.142101554663</v>
+        <v>-27.22838699337366</v>
       </c>
       <c r="H97" t="n">
-        <v>-24.62840785807862</v>
+        <v>-24.71767025835451</v>
       </c>
       <c r="I97" t="n">
-        <v>35.42066016239342</v>
+        <v>35.36877304613689</v>
       </c>
       <c r="J97" t="n">
         <v>29.63618508237403</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1503990096608305</v>
+        <v>0.1475754040152631</v>
       </c>
       <c r="L97" t="n">
-        <v>74160.62206326246</v>
+        <v>74153.50785195293</v>
       </c>
       <c r="M97" t="n">
-        <v>82370.93491571603</v>
+        <v>82368.00553458858</v>
       </c>
       <c r="N97" t="n">
-        <v>68848.90112503737</v>
+        <v>68848.15784922891</v>
       </c>
       <c r="O97" t="n">
-        <v>15.15651297619843</v>
+        <v>10.38938334656905</v>
       </c>
       <c r="P97" t="n">
-        <v>16.74505844788067</v>
+        <v>16.42964952713402</v>
       </c>
       <c r="Q97" t="n">
-        <v>-83.25494155211933</v>
+        <v>-83.57035047286598</v>
       </c>
       <c r="R97" t="n">
-        <v>-42.98366168572247</v>
+        <v>-43.12558357244824</v>
       </c>
       <c r="S97" t="n">
-        <v>-18.05761124658965</v>
+        <v>-18.15465542592312</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -20298,7 +20298,7 @@
       </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="X97" t="n">
         <v>71.09999999999999</v>
@@ -20423,52 +20423,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>69.18000030517578</v>
+        <v>68.83000183105469</v>
       </c>
       <c r="E99" t="n">
-        <v>-2.790908644545065</v>
+        <v>-3.282713118309444</v>
       </c>
       <c r="F99" t="n">
-        <v>-18.77702991341022</v>
+        <v>-19.18795670538023</v>
       </c>
       <c r="G99" t="n">
-        <v>-41.75436908345921</v>
+        <v>-42.0490479191788</v>
       </c>
       <c r="H99" t="n">
-        <v>-46.19725274666592</v>
+        <v>-46.46945395162574</v>
       </c>
       <c r="I99" t="n">
-        <v>33.87403433914288</v>
+        <v>33.74771640583563</v>
       </c>
       <c r="J99" t="n">
         <v>40.75210913078011</v>
       </c>
       <c r="K99" t="n">
-        <v>0.01973735972814835</v>
+        <v>0.01042868422871598</v>
       </c>
       <c r="L99" t="n">
-        <v>89.28092083628604</v>
+        <v>89.2475876482745</v>
       </c>
       <c r="M99" t="n">
-        <v>116.4862292659211</v>
+        <v>116.4725038355634</v>
       </c>
       <c r="N99" t="n">
-        <v>114.5934588861222</v>
+        <v>114.5899763142404</v>
       </c>
       <c r="O99" t="n">
-        <v>1.218541884602196</v>
+        <v>1.196205799644037</v>
       </c>
       <c r="P99" t="n">
-        <v>23.15674500315641</v>
+        <v>22.23209412311049</v>
       </c>
       <c r="Q99" t="n">
-        <v>-76.84325499684358</v>
+        <v>-77.76790587688951</v>
       </c>
       <c r="R99" t="n">
-        <v>-29.88217953124724</v>
+        <v>-30.14582495098744</v>
       </c>
       <c r="S99" t="n">
-        <v>-31.40343059972706</v>
+        <v>-31.7504773547737</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -20983,52 +20983,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1702.2900390625</v>
+        <v>1700.180053710938</v>
       </c>
       <c r="E105" t="n">
-        <v>-1.294391179181931</v>
+        <v>-1.416736598558099</v>
       </c>
       <c r="F105" t="n">
-        <v>-19.99183002317313</v>
+        <v>-20.09100000172121</v>
       </c>
       <c r="G105" t="n">
-        <v>-39.54726296383125</v>
+        <v>-39.62219401945701</v>
       </c>
       <c r="H105" t="n">
-        <v>6.613965542945177</v>
+        <v>6.48181773005454</v>
       </c>
       <c r="I105" t="n">
-        <v>32.61634461920802</v>
+        <v>32.57939364314927</v>
       </c>
       <c r="J105" t="n">
         <v>28.48067893451241</v>
       </c>
       <c r="K105" t="n">
-        <v>0.06654307770343193</v>
+        <v>0.06448447944222559</v>
       </c>
       <c r="L105" t="n">
-        <v>2172.940302953688</v>
+        <v>2172.739351967825</v>
       </c>
       <c r="M105" t="n">
-        <v>2563.285423241682</v>
+        <v>2563.202678718092</v>
       </c>
       <c r="N105" t="n">
-        <v>2518.57781971088</v>
+        <v>2518.55682483176</v>
       </c>
       <c r="O105" t="n">
-        <v>-10.24351898460986</v>
+        <v>-10.37817332043608</v>
       </c>
       <c r="P105" t="n">
-        <v>20.43085211340179</v>
+        <v>20.21066694895207</v>
       </c>
       <c r="Q105" t="n">
-        <v>-79.5691478865982</v>
+        <v>-79.78933305104793</v>
       </c>
       <c r="R105" t="n">
-        <v>-42.66146425061854</v>
+        <v>-42.7449151685622</v>
       </c>
       <c r="S105" t="n">
-        <v>-24.94195649665259</v>
+        <v>-25.03499080260214</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -21075,52 +21075,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.13289999961853</v>
+        <v>1.130100011825562</v>
       </c>
       <c r="E106" t="n">
-        <v>-4.463463267740342</v>
+        <v>-4.699583963938514</v>
       </c>
       <c r="F106" t="n">
-        <v>-19.13304348669609</v>
+        <v>-19.33290798591758</v>
       </c>
       <c r="G106" t="n">
-        <v>-38.19509555369977</v>
+        <v>-38.34784776312118</v>
       </c>
       <c r="H106" t="n">
-        <v>-46.56633559955915</v>
+        <v>-46.69839810119672</v>
       </c>
       <c r="I106" t="n">
-        <v>31.13452181864753</v>
+        <v>31.05770235716024</v>
       </c>
       <c r="J106" t="n">
         <v>27.33735214824244</v>
       </c>
       <c r="K106" t="n">
-        <v>-0.06828720843691453</v>
+        <v>-0.07317943058613398</v>
       </c>
       <c r="L106" t="n">
-        <v>1.429084713999837</v>
+        <v>1.428818048495745</v>
       </c>
       <c r="M106" t="n">
-        <v>1.726401910596965</v>
+        <v>1.726292107154103</v>
       </c>
       <c r="N106" t="n">
-        <v>1.403884851720968</v>
+        <v>1.403856991145913</v>
       </c>
       <c r="O106" t="n">
-        <v>0.01081567507073247</v>
+        <v>0.01063698639106733</v>
       </c>
       <c r="P106" t="n">
-        <v>14.30250890433869</v>
+        <v>13.79068239539513</v>
       </c>
       <c r="Q106" t="n">
-        <v>-85.69749109566131</v>
+        <v>-86.20931760460486</v>
       </c>
       <c r="R106" t="n">
-        <v>-34.8417272856151</v>
+        <v>-35.00556381280089</v>
       </c>
       <c r="S106" t="n">
-        <v>-28.80851386425977</v>
+        <v>-28.98446522114078</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -21631,52 +21631,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7.89799976348877</v>
+        <v>7.863999843597412</v>
       </c>
       <c r="E112" t="n">
-        <v>-3.284528239485107</v>
+        <v>-3.70087647835361</v>
       </c>
       <c r="F112" t="n">
-        <v>-17.33420281458788</v>
+        <v>-17.69006892831611</v>
       </c>
       <c r="G112" t="n">
-        <v>-31.35479824949888</v>
+        <v>-31.65030742021733</v>
       </c>
       <c r="H112" t="n">
-        <v>-37.43614169849635</v>
+        <v>-37.70547143185225</v>
       </c>
       <c r="I112" t="n">
-        <v>36.49948670222616</v>
+        <v>36.36926721491875</v>
       </c>
       <c r="J112" t="n">
         <v>37.3694402097832</v>
       </c>
       <c r="K112" t="n">
-        <v>0.1111642092275898</v>
+        <v>0.1004258722340331</v>
       </c>
       <c r="L112" t="n">
-        <v>9.599613601914257</v>
+        <v>9.596375514305556</v>
       </c>
       <c r="M112" t="n">
-        <v>12.00487418613386</v>
+        <v>12.00354085594204</v>
       </c>
       <c r="N112" t="n">
-        <v>13.29499986560374</v>
+        <v>13.29466155794313</v>
       </c>
       <c r="O112" t="n">
-        <v>0.1617549114878165</v>
+        <v>0.1595851160303632</v>
       </c>
       <c r="P112" t="n">
-        <v>22.78261775046749</v>
+        <v>21.89448279650346</v>
       </c>
       <c r="Q112" t="n">
-        <v>-77.21738224953251</v>
+        <v>-78.10551720349653</v>
       </c>
       <c r="R112" t="n">
-        <v>-26.77215509965519</v>
+        <v>-27.09504152583024</v>
       </c>
       <c r="S112" t="n">
-        <v>-16.07418048050102</v>
+        <v>-16.43547083577182</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -21690,10 +21690,10 @@
       </c>
       <c r="V112" t="inlineStr"/>
       <c r="W112" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="X112" t="n">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -21811,52 +21811,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.9599999785423279</v>
+        <v>0.9520000219345093</v>
       </c>
       <c r="E114" t="n">
-        <v>-3.471215098790492</v>
+        <v>-4.275617294494383</v>
       </c>
       <c r="F114" t="n">
-        <v>-23.11038065646967</v>
+        <v>-23.75112402322883</v>
       </c>
       <c r="G114" t="n">
-        <v>-47.3006400503732</v>
+        <v>-47.73979901108169</v>
       </c>
       <c r="H114" t="n">
-        <v>-73.81169171105115</v>
+        <v>-74.02992643462051</v>
       </c>
       <c r="I114" t="n">
-        <v>29.44836493776469</v>
+        <v>29.30067887596661</v>
       </c>
       <c r="J114" t="n">
         <v>26.52166259263409</v>
       </c>
       <c r="K114" t="n">
-        <v>0.01023870914419332</v>
+        <v>0.0006593353102953688</v>
       </c>
       <c r="L114" t="n">
-        <v>1.36972302415049</v>
+        <v>1.368961123521174</v>
       </c>
       <c r="M114" t="n">
-        <v>2.240024888372835</v>
+        <v>2.239711164584293</v>
       </c>
       <c r="N114" t="n">
-        <v>5.471766410008643</v>
+        <v>5.471686808450356</v>
       </c>
       <c r="O114" t="n">
-        <v>0.04371506317126939</v>
+        <v>0.04320452462991581</v>
       </c>
       <c r="P114" t="n">
-        <v>8.877725453754625</v>
+        <v>7.824151405318807</v>
       </c>
       <c r="Q114" t="n">
-        <v>-91.12227454624538</v>
+        <v>-92.1758485946812</v>
       </c>
       <c r="R114" t="n">
-        <v>-41.66484553178141</v>
+        <v>-42.00788141865216</v>
       </c>
       <c r="S114" t="n">
-        <v>-35.86656033325871</v>
+        <v>-36.40100277691701</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -21903,52 +21903,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.1615999937057495</v>
+        <v>0.1608999967575073</v>
       </c>
       <c r="E115" t="n">
-        <v>-11.59012510013049</v>
+        <v>-11.97308701247479</v>
       </c>
       <c r="F115" t="n">
-        <v>-35.84144742104294</v>
+        <v>-36.11936074256622</v>
       </c>
       <c r="G115" t="n">
-        <v>-52.28886725923167</v>
+        <v>-52.49553587690828</v>
       </c>
       <c r="H115" t="n">
-        <v>-74.67382436183352</v>
+        <v>-74.78352885656044</v>
       </c>
       <c r="I115" t="n">
-        <v>29.23090273824656</v>
+        <v>29.17333611217146</v>
       </c>
       <c r="J115" t="n">
         <v>37.74580140002006</v>
       </c>
       <c r="K115" t="n">
-        <v>-0.08323593830541311</v>
+        <v>-0.08655493421839235</v>
       </c>
       <c r="L115" t="n">
-        <v>0.2619999952244322</v>
+        <v>0.2619333288484091</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3955153028120089</v>
+        <v>0.3954878519512935</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5274792968047128</v>
+        <v>0.5274723316609492</v>
       </c>
       <c r="O115" t="n">
-        <v>0.005075609170052231</v>
+        <v>0.005030937000135904</v>
       </c>
       <c r="P115" t="n">
-        <v>8.538697977563677</v>
+        <v>8.055624968507088</v>
       </c>
       <c r="Q115" t="n">
-        <v>-91.46130202243633</v>
+        <v>-91.94437503149291</v>
       </c>
       <c r="R115" t="n">
-        <v>-55.22317234831105</v>
+        <v>-55.37653529610017</v>
       </c>
       <c r="S115" t="n">
-        <v>-43.50282532968257</v>
+        <v>-43.74755213286264</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -21991,52 +21991,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.010000228881836</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="E116" t="n">
-        <v>-11.30159284213311</v>
+        <v>-13.51536472664678</v>
       </c>
       <c r="F116" t="n">
-        <v>-34.53159009707947</v>
+        <v>-36.16557800972539</v>
       </c>
       <c r="G116" t="n">
-        <v>-47.67027184887979</v>
+        <v>-48.97633905591552</v>
       </c>
       <c r="H116" t="n">
-        <v>-69.31578737232242</v>
+        <v>-70.08161676419292</v>
       </c>
       <c r="I116" t="n">
-        <v>29.08252556054356</v>
+        <v>28.70904657367613</v>
       </c>
       <c r="J116" t="n">
-        <v>40.64460376582078</v>
+        <v>40.87324351276501</v>
       </c>
       <c r="K116" t="n">
-        <v>-0.1615493201299669</v>
+        <v>-0.1818166802905846</v>
       </c>
       <c r="L116" t="n">
-        <v>9.405539505025079</v>
+        <v>9.391253781656753</v>
       </c>
       <c r="M116" t="n">
-        <v>13.86597877449073</v>
+        <v>13.86009641780966</v>
       </c>
       <c r="N116" t="n">
-        <v>21.82441786453309</v>
+        <v>21.82292532627073</v>
       </c>
       <c r="O116" t="n">
-        <v>0.1156517916144741</v>
+        <v>0.1060791359556981</v>
       </c>
       <c r="P116" t="n">
-        <v>0.7541852914754125</v>
+        <v>3.374294323416341</v>
       </c>
       <c r="Q116" t="n">
-        <v>-99.24581470852459</v>
+        <v>-96.62570567658366</v>
       </c>
       <c r="R116" t="n">
-        <v>-63.07386301606874</v>
+        <v>-66.30233143682514</v>
       </c>
       <c r="S116" t="n">
-        <v>-39.39053360288219</v>
+        <v>-40.9032499745134</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); RSI scarico (29) — zona di interesse long; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (5.9758)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 41); RSI scarico (29) — zona di interesse long; breakdown minimi 50g — rottura supporto importante</t>
         </is>
       </c>
     </row>
@@ -25239,66 +25239,66 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>244.3899993896484</v>
+        <v>161.2079925537109</v>
       </c>
       <c r="E34" t="n">
-        <v>-9.699236564440749</v>
+        <v>1.216794267133126</v>
       </c>
       <c r="F34" t="n">
-        <v>2.127035634341268</v>
+        <v>5.253254629456672</v>
       </c>
       <c r="G34" t="n">
-        <v>31.15976868354067</v>
+        <v>12.9041882987706</v>
       </c>
       <c r="H34" t="n">
-        <v>40.96359615639513</v>
+        <v>48.02761473182682</v>
       </c>
       <c r="I34" t="n">
-        <v>57.63868494156021</v>
+        <v>62.41892438874681</v>
       </c>
       <c r="J34" t="n">
-        <v>17.79244118786136</v>
+        <v>23.75431164910174</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7162934623474356</v>
+        <v>0.8744058794799471</v>
       </c>
       <c r="L34" t="n">
-        <v>223.0963806226572</v>
+        <v>153.7311341631296</v>
       </c>
       <c r="M34" t="n">
-        <v>189.4980113608912</v>
+        <v>145.3912253972076</v>
       </c>
       <c r="N34" t="n">
-        <v>131.2276229382104</v>
+        <v>131.6605286511347</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6480664478010993</v>
+        <v>0.6303541586534944</v>
       </c>
       <c r="P34" t="n">
-        <v>63.92144308749887</v>
+        <v>98.7013294596899</v>
       </c>
       <c r="Q34" t="n">
-        <v>-36.07855691250112</v>
+        <v>-1.298670540310102</v>
       </c>
       <c r="R34" t="n">
-        <v>53.8583856609709</v>
+        <v>117.6809170861624</v>
       </c>
       <c r="S34" t="n">
-        <v>31.11051898712416</v>
+        <v>5.224405418242761</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -25306,12 +25306,16 @@
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Breakout 20d, Double Top</t>
+        </is>
+      </c>
       <c r="W34" t="n">
-        <v>69.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="X34" t="n">
-        <v>70.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -25320,73 +25324,73 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (161.46)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>COPPER</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.336999893188477</v>
+        <v>244.3899993896484</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3538020031434774</v>
+        <v>-9.699236564440749</v>
       </c>
       <c r="F35" t="n">
-        <v>7.461422239436621</v>
+        <v>2.127035634341268</v>
       </c>
       <c r="G35" t="n">
-        <v>40.94751238095642</v>
+        <v>31.15976868354067</v>
       </c>
       <c r="H35" t="n">
-        <v>41.48246848978361</v>
+        <v>40.96359615639513</v>
       </c>
       <c r="I35" t="n">
-        <v>68.41804461674975</v>
+        <v>57.63868494156021</v>
       </c>
       <c r="J35" t="n">
-        <v>57.80266600735187</v>
+        <v>17.79244118786136</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9177491211651808</v>
+        <v>0.7162934623474356</v>
       </c>
       <c r="L35" t="n">
-        <v>5.284393771019273</v>
+        <v>223.0963806226572</v>
       </c>
       <c r="M35" t="n">
-        <v>4.621211762580684</v>
+        <v>189.4980113608912</v>
       </c>
       <c r="N35" t="n">
-        <v>3.875259177022811</v>
+        <v>131.2276229382104</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1259198855522125</v>
+        <v>0.6480664478010993</v>
       </c>
       <c r="P35" t="n">
-        <v>86.45340232219083</v>
+        <v>63.92144308749887</v>
       </c>
       <c r="Q35" t="n">
-        <v>-13.54659767780918</v>
+        <v>-36.07855691250112</v>
       </c>
       <c r="R35" t="n">
-        <v>139.3910826575821</v>
+        <v>53.8583856609709</v>
       </c>
       <c r="S35" t="n">
-        <v>46.910861241877</v>
+        <v>31.11051898712416</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -25396,10 +25400,10 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="n">
-        <v>68.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="X35" t="n">
-        <v>80.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -25408,90 +25412,86 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 58); RSI in forza (68) — momentum positivo; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TRN</t>
+          <t>COPPER</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Terna</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.34000015258789</v>
+        <v>6.336999893188477</v>
       </c>
       <c r="E36" t="n">
-        <v>4.953308002045587</v>
+        <v>-0.3538020031434774</v>
       </c>
       <c r="F36" t="n">
-        <v>13.30264841595079</v>
+        <v>7.461422239436621</v>
       </c>
       <c r="G36" t="n">
-        <v>27.84371627341162</v>
+        <v>40.94751238095642</v>
       </c>
       <c r="H36" t="n">
-        <v>68.67862903018791</v>
+        <v>41.48246848978361</v>
       </c>
       <c r="I36" t="n">
-        <v>68.67604882307609</v>
+        <v>68.41804461674975</v>
       </c>
       <c r="J36" t="n">
-        <v>51.19901394989771</v>
+        <v>57.80266600735187</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9362995262028678</v>
+        <v>0.9177491211651808</v>
       </c>
       <c r="L36" t="n">
-        <v>9.107517851163342</v>
+        <v>5.284393771019273</v>
       </c>
       <c r="M36" t="n">
-        <v>8.197586810281013</v>
+        <v>4.621211762580684</v>
       </c>
       <c r="N36" t="n">
-        <v>6.704265670457473</v>
+        <v>3.875259177022811</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1185433289499326</v>
+        <v>0.1259198855522125</v>
       </c>
       <c r="P36" t="n">
-        <v>96.78014251598086</v>
+        <v>86.45340232219083</v>
       </c>
       <c r="Q36" t="n">
-        <v>-3.219857484019154</v>
+        <v>-13.54659767780918</v>
       </c>
       <c r="R36" t="n">
-        <v>108.4155316666334</v>
+        <v>139.3910826575821</v>
       </c>
       <c r="S36" t="n">
-        <v>29.83425239042761</v>
+        <v>46.910861241877</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="n">
         <v>68.90000000000001</v>
       </c>
       <c r="X36" t="n">
-        <v>76.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -25500,19 +25500,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (69) — momentum positivo; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (10.41)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 58); RSI in forza (68) — momentum positivo; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>TRN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -25521,69 +25521,69 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.177999973297119</v>
+        <v>10.34000015258789</v>
       </c>
       <c r="E37" t="n">
-        <v>6.388837658753421</v>
+        <v>4.953308002045587</v>
       </c>
       <c r="F37" t="n">
-        <v>3.553467823363077</v>
+        <v>13.30264841595079</v>
       </c>
       <c r="G37" t="n">
-        <v>60.9902233163486</v>
+        <v>27.84371627341162</v>
       </c>
       <c r="H37" t="n">
-        <v>166.1783588666849</v>
+        <v>68.67862903018791</v>
       </c>
       <c r="I37" t="n">
-        <v>72.39695098691317</v>
+        <v>68.67604882307609</v>
       </c>
       <c r="J37" t="n">
-        <v>21.40664501746133</v>
+        <v>51.19901394989771</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8448625012324789</v>
+        <v>0.9362995262028678</v>
       </c>
       <c r="L37" t="n">
-        <v>5.182447433971482</v>
+        <v>9.107517851163342</v>
       </c>
       <c r="M37" t="n">
-        <v>4.135418890798172</v>
+        <v>8.197586810281013</v>
       </c>
       <c r="N37" t="n">
-        <v>3.13171382834288</v>
+        <v>6.704265670457473</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.0138008832784724</v>
+        <v>0.1185433289499326</v>
       </c>
       <c r="P37" t="n">
-        <v>98.17886961519007</v>
+        <v>96.78014251598086</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1.821130384809936</v>
+        <v>-3.219857484019154</v>
       </c>
       <c r="R37" t="n">
-        <v>50.80371587360679</v>
+        <v>108.4155316666334</v>
       </c>
       <c r="S37" t="n">
-        <v>56.92151172032902</v>
+        <v>29.83425239042761</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="n">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="X37" t="n">
-        <v>78.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
@@ -25592,73 +25592,73 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); RSI ipercomprato (72) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (6.2060)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI in forza (69) — momentum positivo; candela di inversione bullish (engulfing); vicino alla resistenza dei 20g (10.41)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Intesa Sanpaolo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>173.6300048828125</v>
+        <v>6.177999973297119</v>
       </c>
       <c r="E38" t="n">
-        <v>-4.839417683954084</v>
+        <v>6.388837658753421</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.848495831823127</v>
+        <v>3.553467823363077</v>
       </c>
       <c r="G38" t="n">
-        <v>17.89909679202801</v>
+        <v>60.9902233163486</v>
       </c>
       <c r="H38" t="n">
-        <v>68.4583345269298</v>
+        <v>166.1783588666849</v>
       </c>
       <c r="I38" t="n">
-        <v>53.66408442764253</v>
+        <v>72.39695098691317</v>
       </c>
       <c r="J38" t="n">
-        <v>25.61504983575651</v>
+        <v>21.40664501746133</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6479336331912984</v>
+        <v>0.8448625012324789</v>
       </c>
       <c r="L38" t="n">
-        <v>167.6898850632844</v>
+        <v>5.182447433971482</v>
       </c>
       <c r="M38" t="n">
-        <v>155.5299113751362</v>
+        <v>4.135418890798172</v>
       </c>
       <c r="N38" t="n">
-        <v>137.7916160273205</v>
+        <v>3.13171382834288</v>
       </c>
       <c r="O38" t="n">
-        <v>2.879523324712669</v>
+        <v>-0.0138008832784724</v>
       </c>
       <c r="P38" t="n">
-        <v>49.24635459358535</v>
+        <v>98.17886961519007</v>
       </c>
       <c r="Q38" t="n">
-        <v>-50.75364540641465</v>
+        <v>-1.821130384809936</v>
       </c>
       <c r="R38" t="n">
-        <v>101.2829084114257</v>
+        <v>50.80371587360679</v>
       </c>
       <c r="S38" t="n">
-        <v>16.67114389031226</v>
+        <v>56.92151172032902</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -25668,14 +25668,14 @@
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
         </is>
       </c>
       <c r="W38" t="n">
         <v>68.8</v>
       </c>
       <c r="X38" t="n">
-        <v>75.7</v>
+        <v>78.5</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -25684,73 +25684,73 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); pattern: Bull Flag / Consolidation; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 21); RSI ipercomprato (72) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (6.2060)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Russell 2000</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2979.77001953125</v>
+        <v>173.6300048828125</v>
       </c>
       <c r="E39" t="n">
-        <v>2.069986018117165</v>
+        <v>-4.839417683954084</v>
       </c>
       <c r="F39" t="n">
-        <v>14.00407196830826</v>
+        <v>-1.848495831823127</v>
       </c>
       <c r="G39" t="n">
-        <v>33.62377335474647</v>
+        <v>17.89909679202801</v>
       </c>
       <c r="H39" t="n">
-        <v>31.47301214353093</v>
+        <v>68.4583345269298</v>
       </c>
       <c r="I39" t="n">
-        <v>71.83948392557866</v>
+        <v>53.66408442764253</v>
       </c>
       <c r="J39" t="n">
-        <v>17.91973201793244</v>
+        <v>25.61504983575651</v>
       </c>
       <c r="K39" t="n">
-        <v>0.9990733668052011</v>
+        <v>0.6479336331912984</v>
       </c>
       <c r="L39" t="n">
-        <v>2480.53587002425</v>
+        <v>167.6898850632844</v>
       </c>
       <c r="M39" t="n">
-        <v>2222.060622929183</v>
+        <v>155.5299113751362</v>
       </c>
       <c r="N39" t="n">
-        <v>1844.727346022564</v>
+        <v>137.7916160273205</v>
       </c>
       <c r="O39" t="n">
-        <v>55.53102420773743</v>
+        <v>2.879523324712669</v>
       </c>
       <c r="P39" t="n">
-        <v>98.39275786564239</v>
+        <v>49.24635459358535</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1.607242134357599</v>
+        <v>-50.75364540641465</v>
       </c>
       <c r="R39" t="n">
-        <v>143.5336908483408</v>
+        <v>101.2829084114257</v>
       </c>
       <c r="S39" t="n">
-        <v>35.65065677293126</v>
+        <v>16.67114389031226</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -25760,14 +25760,14 @@
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d</t>
+          <t>Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W39" t="n">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="X39" t="n">
-        <v>80.5</v>
+        <v>75.7</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -25776,73 +25776,73 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (72) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (2,996)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); pattern: Bull Flag / Consolidation; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Prysmian</t>
+          <t>Russell 2000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>153.1999969482422</v>
+        <v>2979.77001953125</v>
       </c>
       <c r="E40" t="n">
-        <v>3.513511451514995</v>
+        <v>2.069986018117165</v>
       </c>
       <c r="F40" t="n">
-        <v>52.51368999760142</v>
+        <v>14.00407196830826</v>
       </c>
       <c r="G40" t="n">
-        <v>134.9693314707625</v>
+        <v>33.62377335474647</v>
       </c>
       <c r="H40" t="n">
-        <v>488.0998135703942</v>
+        <v>31.47301214353093</v>
       </c>
       <c r="I40" t="n">
-        <v>86.4589979790658</v>
+        <v>71.83948392557866</v>
       </c>
       <c r="J40" t="n">
-        <v>33.94836623055959</v>
+        <v>17.91973201793244</v>
       </c>
       <c r="K40" t="n">
-        <v>1.064515176650402</v>
+        <v>0.9990733668052011</v>
       </c>
       <c r="L40" t="n">
-        <v>93.39837133296595</v>
+        <v>2480.53587002425</v>
       </c>
       <c r="M40" t="n">
-        <v>67.6487247907875</v>
+        <v>2222.060622929183</v>
       </c>
       <c r="N40" t="n">
-        <v>43.06773096885267</v>
+        <v>1844.727346022564</v>
       </c>
       <c r="O40" t="n">
-        <v>7.212776384853314</v>
+        <v>55.53102420773743</v>
       </c>
       <c r="P40" t="n">
-        <v>96.24826028426651</v>
+        <v>98.39275786564239</v>
       </c>
       <c r="Q40" t="n">
-        <v>-3.751739715733497</v>
+        <v>-1.607242134357599</v>
       </c>
       <c r="R40" t="n">
-        <v>196.3549564398878</v>
+        <v>143.5336908483408</v>
       </c>
       <c r="S40" t="n">
-        <v>136.3468029458738</v>
+        <v>35.65065677293126</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -25852,14 +25852,14 @@
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakout 20d, Breakout 50d</t>
         </is>
       </c>
       <c r="W40" t="n">
         <v>68.7</v>
       </c>
       <c r="X40" t="n">
-        <v>72.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -25868,73 +25868,73 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 34); RSI ipercomprato (86) — attenzione estensione</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (72) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (2,996)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Prysmian</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>161.2680053710938</v>
+        <v>153.1999969482422</v>
       </c>
       <c r="E41" t="n">
-        <v>1.254474191646815</v>
+        <v>3.513511451514995</v>
       </c>
       <c r="F41" t="n">
-        <v>5.292437205016132</v>
+        <v>52.51368999760142</v>
       </c>
       <c r="G41" t="n">
-        <v>12.94621908351516</v>
+        <v>134.9693314707625</v>
       </c>
       <c r="H41" t="n">
-        <v>48.08272089666264</v>
+        <v>488.0998135703942</v>
       </c>
       <c r="I41" t="n">
-        <v>62.4742998115506</v>
+        <v>86.4589979790658</v>
       </c>
       <c r="J41" t="n">
-        <v>23.75431164910174</v>
+        <v>33.94836623055959</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8765903030690091</v>
+        <v>1.064515176650402</v>
       </c>
       <c r="L41" t="n">
-        <v>153.736849669547</v>
+        <v>93.39837133296595</v>
       </c>
       <c r="M41" t="n">
-        <v>145.3935788410265</v>
+        <v>67.6487247907875</v>
       </c>
       <c r="N41" t="n">
-        <v>131.6613984021112</v>
+        <v>43.06773096885267</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6341840364579863</v>
+        <v>7.212776384853314</v>
       </c>
       <c r="P41" t="n">
-        <v>99.01182619130326</v>
+        <v>96.24826028426651</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.9881738086967505</v>
+        <v>-3.751739715733497</v>
       </c>
       <c r="R41" t="n">
-        <v>117.9300613300662</v>
+        <v>196.3549564398878</v>
       </c>
       <c r="S41" t="n">
-        <v>5.263577254121032</v>
+        <v>136.3468029458738</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -25944,14 +25944,14 @@
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Breakout 20d, Double Top</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W41" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="X41" t="n">
-        <v>77.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (161.46)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 34); RSI ipercomprato (86) — attenzione estensione</t>
         </is>
       </c>
     </row>
@@ -29297,52 +29297,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.147842049598694</v>
+        <v>1.14771032333374</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.49678126351328</v>
+        <v>-1.508085485287169</v>
       </c>
       <c r="F78" t="n">
-        <v>-4.07254456302325</v>
+        <v>-4.083553190399836</v>
       </c>
       <c r="G78" t="n">
-        <v>2.762851763942487</v>
+        <v>2.751058707011378</v>
       </c>
       <c r="H78" t="n">
-        <v>-5.348944287699664</v>
+        <v>-5.359806435542447</v>
       </c>
       <c r="I78" t="n">
-        <v>52.68486909696011</v>
+        <v>52.65805469037684</v>
       </c>
       <c r="J78" t="n">
         <v>42.06853630988682</v>
       </c>
       <c r="K78" t="n">
-        <v>0.5646954426769429</v>
+        <v>0.5640937331592796</v>
       </c>
       <c r="L78" t="n">
-        <v>1.143306453159664</v>
+        <v>1.143293907801097</v>
       </c>
       <c r="M78" t="n">
-        <v>1.122980177148537</v>
+        <v>1.122975011412656</v>
       </c>
       <c r="N78" t="n">
-        <v>1.132664145842384</v>
+        <v>1.132662236766081</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.0007230700807489693</v>
+        <v>-0.0007314765432416617</v>
       </c>
       <c r="P78" t="n">
-        <v>42.52615412458462</v>
+        <v>42.38727710552643</v>
       </c>
       <c r="Q78" t="n">
-        <v>-57.47384587541537</v>
+        <v>-57.61272289447358</v>
       </c>
       <c r="R78" t="n">
-        <v>26.48368006085859</v>
+        <v>26.42712389169031</v>
       </c>
       <c r="S78" t="n">
-        <v>5.702477424541996</v>
+        <v>5.690347016397124</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -29551,87 +29551,83 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COTTON</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>76.05000305175781</v>
+        <v>100.8489990234375</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.1313177572125346</v>
+        <v>1.960363248951036</v>
       </c>
       <c r="F81" t="n">
-        <v>20.38943368078863</v>
+        <v>3.978761980269607</v>
       </c>
       <c r="G81" t="n">
-        <v>3.384999423335566</v>
+        <v>0.06846620854970009</v>
       </c>
       <c r="H81" t="n">
-        <v>-13.01612400056721</v>
+        <v>10.48312924201196</v>
       </c>
       <c r="I81" t="n">
-        <v>54.91023517054392</v>
+        <v>50.58955737162892</v>
       </c>
       <c r="J81" t="n">
-        <v>35.18977543963702</v>
+        <v>29.35186553155452</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9296123318314276</v>
+        <v>0.5044435215891163</v>
       </c>
       <c r="L81" t="n">
-        <v>70.53157842223543</v>
+        <v>100.1664760551763</v>
       </c>
       <c r="M81" t="n">
-        <v>75.32485698897973</v>
+        <v>100.8157275218968</v>
       </c>
       <c r="N81" t="n">
-        <v>76.69232469889029</v>
+        <v>99.51482427881977</v>
       </c>
       <c r="O81" t="n">
-        <v>2.289291197511413</v>
+        <v>0.07363184511253995</v>
       </c>
       <c r="P81" t="n">
-        <v>54.4551116946682</v>
+        <v>82.41050886753925</v>
       </c>
       <c r="Q81" t="n">
-        <v>-45.5448883053318</v>
+        <v>-17.58949113246076</v>
       </c>
       <c r="R81" t="n">
-        <v>63.89477821476365</v>
+        <v>-10.41986516754799</v>
       </c>
       <c r="S81" t="n">
-        <v>9.314364503893602</v>
+        <v>-3.011160061947926</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W81" t="n">
-        <v>51.4</v>
+        <v>51.8</v>
       </c>
       <c r="X81" t="n">
-        <v>68.90000000000001</v>
+        <v>58</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -29640,73 +29636,73 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto</t>
+          <t>trend in sviluppo (ADX 29); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>COTTON</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.13289999961853</v>
+        <v>76.05000305175781</v>
       </c>
       <c r="E82" t="n">
-        <v>-14.90406906203746</v>
+        <v>-0.1313177572125346</v>
       </c>
       <c r="F82" t="n">
-        <v>-31.15041130647065</v>
+        <v>20.38943368078863</v>
       </c>
       <c r="G82" t="n">
-        <v>85.26817032199506</v>
+        <v>3.384999423335566</v>
       </c>
       <c r="H82" t="n">
-        <v>-28.82336327582329</v>
+        <v>-13.01612400056721</v>
       </c>
       <c r="I82" t="n">
-        <v>41.8132159016381</v>
+        <v>54.91023517054392</v>
       </c>
       <c r="J82" t="n">
-        <v>41.86732703313529</v>
+        <v>35.18977543963702</v>
       </c>
       <c r="K82" t="n">
-        <v>0.09907019873868352</v>
+        <v>0.9296123318314276</v>
       </c>
       <c r="L82" t="n">
-        <v>1.660426788570294</v>
+        <v>70.53157842223543</v>
       </c>
       <c r="M82" t="n">
-        <v>1.346903885269372</v>
+        <v>75.32485698897973</v>
       </c>
       <c r="N82" t="n">
-        <v>1.072770761916053</v>
+        <v>76.69232469889029</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.1897919313801558</v>
+        <v>2.289291197511413</v>
       </c>
       <c r="P82" t="n">
-        <v>3.014502865833013</v>
+        <v>54.4551116946682</v>
       </c>
       <c r="Q82" t="n">
-        <v>-96.98549713416699</v>
+        <v>-45.5448883053318</v>
       </c>
       <c r="R82" t="n">
-        <v>-62.69887545489238</v>
+        <v>63.89477821476365</v>
       </c>
       <c r="S82" t="n">
-        <v>122.4700912814173</v>
+        <v>9.314364503893602</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -29715,15 +29711,19 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr"/>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W82" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="X82" t="n">
-        <v>57.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -29732,90 +29732,90 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele</t>
+          <t>trend molto direzionale (ADX 35); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1264.5</v>
+        <v>1.130100011825562</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.090374724467308</v>
+        <v>-15.11438556652844</v>
       </c>
       <c r="F83" t="n">
-        <v>-25.10217595043553</v>
+        <v>-31.32057461122633</v>
       </c>
       <c r="G83" t="n">
-        <v>26.5892450790292</v>
+        <v>84.81027587808833</v>
       </c>
       <c r="H83" t="n">
-        <v>-57.2471846071137</v>
+        <v>-28.99927793205012</v>
       </c>
       <c r="I83" t="n">
-        <v>48.07656672616933</v>
+        <v>41.77450386360648</v>
       </c>
       <c r="J83" t="n">
-        <v>54.48887442357493</v>
+        <v>41.86732703313529</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5104507432818538</v>
+        <v>0.0980872218938981</v>
       </c>
       <c r="L83" t="n">
-        <v>1335.71630949511</v>
+        <v>1.660160123066202</v>
       </c>
       <c r="M83" t="n">
-        <v>1367.918880581469</v>
+        <v>1.346791885757653</v>
       </c>
       <c r="N83" t="n">
-        <v>1358.118977762846</v>
+        <v>1.072713619308033</v>
       </c>
       <c r="O83" t="n">
-        <v>22.41775763794303</v>
+        <v>-0.1899706200598209</v>
       </c>
       <c r="P83" t="n">
-        <v>26.50377675806433</v>
+        <v>2.906626514324389</v>
       </c>
       <c r="Q83" t="n">
-        <v>-73.49622324193567</v>
+        <v>-97.09337348567561</v>
       </c>
       <c r="R83" t="n">
-        <v>4.957912304106544</v>
+        <v>-62.75692785252249</v>
       </c>
       <c r="S83" t="n">
-        <v>14.27925892453683</v>
+        <v>121.9202514543378</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="X83" t="n">
-        <v>70.09999999999999</v>
+        <v>57.3</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -29824,19 +29824,19 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 54); pattern: Double Bottom</t>
+          <t>trend molto direzionale (ADX 42); evening star — inversione ribassista a 3 candele</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SOYBEAN</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -29845,69 +29845,69 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1122.75</v>
+        <v>1264.5</v>
       </c>
       <c r="E84" t="n">
-        <v>-5.392879713503262</v>
+        <v>-7.090374724467308</v>
       </c>
       <c r="F84" t="n">
-        <v>5.496828752642702</v>
+        <v>-25.10217595043553</v>
       </c>
       <c r="G84" t="n">
-        <v>6.220435193945129</v>
+        <v>26.5892450790292</v>
       </c>
       <c r="H84" t="n">
-        <v>-28.53278166772756</v>
+        <v>-57.2471846071137</v>
       </c>
       <c r="I84" t="n">
-        <v>50.0249290525538</v>
+        <v>48.07656672616933</v>
       </c>
       <c r="J84" t="n">
-        <v>26.04242815342785</v>
+        <v>54.48887442357493</v>
       </c>
       <c r="K84" t="n">
-        <v>0.7037393311686028</v>
+        <v>0.5104507432818538</v>
       </c>
       <c r="L84" t="n">
-        <v>1111.352901346763</v>
+        <v>1335.71630949511</v>
       </c>
       <c r="M84" t="n">
-        <v>1154.896721781048</v>
+        <v>1367.918880581469</v>
       </c>
       <c r="N84" t="n">
-        <v>1138.370827415582</v>
+        <v>1358.118977762846</v>
       </c>
       <c r="O84" t="n">
-        <v>25.08133838560368</v>
+        <v>22.41775763794303</v>
       </c>
       <c r="P84" t="n">
-        <v>61.71428571428571</v>
+        <v>26.50377675806433</v>
       </c>
       <c r="Q84" t="n">
-        <v>-38.28571428571428</v>
+        <v>-73.49622324193567</v>
       </c>
       <c r="R84" t="n">
-        <v>49.73666273375309</v>
+        <v>4.957912304106544</v>
       </c>
       <c r="S84" t="n">
-        <v>14.27480916030535</v>
+        <v>14.27925892453683</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Evening Star</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W84" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="X84" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -29916,86 +29916,90 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); candela di inversione bearish (engulfing); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 54); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>SOYBEAN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1.323451638221741</v>
+        <v>1122.75</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.561671648175134</v>
+        <v>-5.392879713503262</v>
       </c>
       <c r="F85" t="n">
-        <v>-4.142397007134369</v>
+        <v>5.496828752642702</v>
       </c>
       <c r="G85" t="n">
-        <v>-1.111695629107834</v>
+        <v>6.220435193945129</v>
       </c>
       <c r="H85" t="n">
-        <v>-5.148220896425215</v>
+        <v>-28.53278166772756</v>
       </c>
       <c r="I85" t="n">
-        <v>50.9108901180927</v>
+        <v>50.0249290525538</v>
       </c>
       <c r="J85" t="n">
-        <v>23.15604231256256</v>
+        <v>26.04242815342785</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5045241484652614</v>
+        <v>0.7037393311686028</v>
       </c>
       <c r="L85" t="n">
-        <v>1.32530941938235</v>
+        <v>1111.352901346763</v>
       </c>
       <c r="M85" t="n">
-        <v>1.306412963885962</v>
+        <v>1154.896721781048</v>
       </c>
       <c r="N85" t="n">
-        <v>1.339208121791936</v>
+        <v>1138.370827415582</v>
       </c>
       <c r="O85" t="n">
-        <v>-0.002257581256953824</v>
+        <v>25.08133838560368</v>
       </c>
       <c r="P85" t="n">
-        <v>26.68367303239584</v>
+        <v>61.71428571428571</v>
       </c>
       <c r="Q85" t="n">
-        <v>-73.31632696760416</v>
+        <v>-38.28571428571428</v>
       </c>
       <c r="R85" t="n">
-        <v>17.31004032594704</v>
+        <v>49.73666273375309</v>
       </c>
       <c r="S85" t="n">
-        <v>2.121497527016825</v>
+        <v>14.27480916030535</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bearish Engulfing, Evening Star</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="X85" t="n">
-        <v>54.1</v>
+        <v>72.7</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -30004,73 +30008,73 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23)</t>
+          <t>trend in sviluppo (ADX 26); candela di inversione bearish (engulfing); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HY</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>High Yield Corp ETF</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>80.01000213623047</v>
+        <v>1.323241353034973</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.3735467955211957</v>
+        <v>-1.57731265965203</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.368343901342306</v>
+        <v>-4.157627963344856</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.3611468300199427</v>
+        <v>-1.127408137939434</v>
       </c>
       <c r="H86" t="n">
-        <v>-8.497255372510592</v>
+        <v>-5.16329203579139</v>
       </c>
       <c r="I86" t="n">
-        <v>51.57717730929279</v>
+        <v>50.87797853586967</v>
       </c>
       <c r="J86" t="n">
-        <v>20.37678662143965</v>
+        <v>23.15604231256256</v>
       </c>
       <c r="K86" t="n">
-        <v>0.4522763442609523</v>
+        <v>0.5032516712225265</v>
       </c>
       <c r="L86" t="n">
-        <v>79.94279318690602</v>
+        <v>1.325289392221705</v>
       </c>
       <c r="M86" t="n">
-        <v>79.80299057906961</v>
+        <v>1.30640471740805</v>
       </c>
       <c r="N86" t="n">
-        <v>82.86962799062954</v>
+        <v>1.339205074180534</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.1184087141174007</v>
+        <v>-0.002271001166308795</v>
       </c>
       <c r="P86" t="n">
-        <v>57.00640966454955</v>
+        <v>26.43186081236564</v>
       </c>
       <c r="Q86" t="n">
-        <v>-42.99359033545045</v>
+        <v>-73.56813918763436</v>
       </c>
       <c r="R86" t="n">
-        <v>-3.158356752468289</v>
+        <v>17.18089597666274</v>
       </c>
       <c r="S86" t="n">
-        <v>1.099321143911736</v>
+        <v>2.105271291346211</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -30078,16 +30082,12 @@
         </is>
       </c>
       <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar, Volatility Squeeze</t>
-        </is>
-      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="X86" t="n">
-        <v>59.2</v>
+        <v>54.1</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -30096,73 +30096,73 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 23)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MONC</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>High Yield Corp ETF</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>52.84000015258789</v>
+        <v>80.01000213623047</v>
       </c>
       <c r="E87" t="n">
-        <v>-5.406373835957368</v>
+        <v>-0.3735467955211957</v>
       </c>
       <c r="F87" t="n">
-        <v>7.814735691129227</v>
+        <v>-1.368343901342306</v>
       </c>
       <c r="G87" t="n">
-        <v>-7.330761612799397</v>
+        <v>-0.3611468300199427</v>
       </c>
       <c r="H87" t="n">
-        <v>3.567227907672965</v>
+        <v>-8.497255372510592</v>
       </c>
       <c r="I87" t="n">
-        <v>48.91265911285257</v>
+        <v>51.57717730929279</v>
       </c>
       <c r="J87" t="n">
-        <v>18.27510877397818</v>
+        <v>20.37678662143965</v>
       </c>
       <c r="K87" t="n">
-        <v>0.4690854682032142</v>
+        <v>0.4522763442609523</v>
       </c>
       <c r="L87" t="n">
-        <v>53.81722898702708</v>
+        <v>79.94279318690602</v>
       </c>
       <c r="M87" t="n">
-        <v>52.97972959456948</v>
+        <v>79.80299057906961</v>
       </c>
       <c r="N87" t="n">
-        <v>42.25539841602705</v>
+        <v>82.86962799062954</v>
       </c>
       <c r="O87" t="n">
-        <v>0.1155895179169834</v>
+        <v>-0.1184087141174007</v>
       </c>
       <c r="P87" t="n">
-        <v>52.94117486087578</v>
+        <v>57.00640966454955</v>
       </c>
       <c r="Q87" t="n">
-        <v>-47.05882513912423</v>
+        <v>-42.99359033545045</v>
       </c>
       <c r="R87" t="n">
-        <v>14.01228768457946</v>
+        <v>-3.158356752468289</v>
       </c>
       <c r="S87" t="n">
-        <v>3.72988138417949</v>
+        <v>1.099321143911736</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -30172,14 +30172,14 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Double Top, Inside Bar, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W87" t="n">
-        <v>49.5</v>
+        <v>50.7</v>
       </c>
       <c r="X87" t="n">
-        <v>58.6</v>
+        <v>59.2</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -30188,19 +30188,19 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>pattern: Bull Flag / Consolidation</t>
+          <t>trend in sviluppo (ADX 20); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IVG</t>
+          <t>MONC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Iveco Group</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -30209,67 +30209,69 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.92500019073486</v>
+        <v>52.84000015258789</v>
       </c>
       <c r="E88" t="n">
-        <v>0.035920362166042</v>
+        <v>-5.406373835957368</v>
       </c>
       <c r="F88" t="n">
-        <v>-26.20561965327092</v>
+        <v>7.814735691129227</v>
       </c>
       <c r="G88" t="n">
-        <v>54.41340355568884</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
+        <v>-7.330761612799397</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.567227907672965</v>
+      </c>
       <c r="I88" t="n">
-        <v>44.382356250018</v>
+        <v>48.91265911285257</v>
       </c>
       <c r="J88" t="n">
-        <v>43.27248636361465</v>
+        <v>18.27510877397818</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2106589866305185</v>
+        <v>0.4690854682032142</v>
       </c>
       <c r="L88" t="n">
-        <v>15.68687917247175</v>
+        <v>53.81722898702708</v>
       </c>
       <c r="M88" t="n">
-        <v>14.74554512808352</v>
+        <v>52.97972959456948</v>
       </c>
       <c r="N88" t="n">
-        <v>12.84208748195073</v>
+        <v>42.25539841602705</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.6667598037803359</v>
+        <v>0.1155895179169834</v>
       </c>
       <c r="P88" t="n">
-        <v>3.29217855047128</v>
+        <v>52.94117486087578</v>
       </c>
       <c r="Q88" t="n">
-        <v>-96.70782144952872</v>
+        <v>-47.05882513912423</v>
       </c>
       <c r="R88" t="n">
-        <v>-35.66177303602888</v>
+        <v>14.01228768457946</v>
       </c>
       <c r="S88" t="n">
-        <v>-20.65526611916158</v>
+        <v>3.72988138417949</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W88" t="n">
         <v>49.5</v>
       </c>
       <c r="X88" t="n">
-        <v>58.2</v>
+        <v>58.6</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -30278,73 +30280,71 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 43); doji — indecisione del mercato</t>
+          <t>pattern: Bull Flag / Consolidation</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>IVG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Iveco Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>278.6099853515625</v>
+        <v>13.92500019073486</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.2113276610572812</v>
+        <v>0.035920362166042</v>
       </c>
       <c r="F89" t="n">
-        <v>-11.55238560267857</v>
+        <v>-26.20561965327092</v>
       </c>
       <c r="G89" t="n">
-        <v>-8.505475545449958</v>
-      </c>
-      <c r="H89" t="n">
-        <v>18.01507251382666</v>
-      </c>
+        <v>54.41340355568884</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="n">
-        <v>44.4052423578184</v>
+        <v>44.382356250018</v>
       </c>
       <c r="J89" t="n">
-        <v>17.47700286916833</v>
+        <v>43.27248636361465</v>
       </c>
       <c r="K89" t="n">
-        <v>0.07802985796994885</v>
+        <v>0.2106589866305185</v>
       </c>
       <c r="L89" t="n">
-        <v>298.9104035431631</v>
+        <v>15.68687917247175</v>
       </c>
       <c r="M89" t="n">
-        <v>282.1252747967791</v>
+        <v>14.74554512808352</v>
       </c>
       <c r="N89" t="n">
-        <v>225.5153413796808</v>
+        <v>12.84208748195073</v>
       </c>
       <c r="O89" t="n">
-        <v>-4.581451286481601</v>
+        <v>-0.6667598037803359</v>
       </c>
       <c r="P89" t="n">
-        <v>9.670929668545892</v>
+        <v>3.29217855047128</v>
       </c>
       <c r="Q89" t="n">
-        <v>-90.3290703314541</v>
+        <v>-96.70782144952872</v>
       </c>
       <c r="R89" t="n">
-        <v>-94.49612108649325</v>
+        <v>-35.66177303602888</v>
       </c>
       <c r="S89" t="n">
-        <v>-4.621546909378116</v>
+        <v>-20.65526611916158</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -30358,10 +30358,10 @@
       </c>
       <c r="V89" t="inlineStr"/>
       <c r="W89" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="X89" t="n">
-        <v>55.6</v>
+        <v>58.2</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -30370,90 +30370,90 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 43); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>100.7320022583008</v>
+        <v>278.6099853515625</v>
       </c>
       <c r="E90" t="n">
-        <v>1.842077169884271</v>
+        <v>-0.2113276610572812</v>
       </c>
       <c r="F90" t="n">
-        <v>3.858134319981321</v>
+        <v>-11.55238560267857</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.04762504621695918</v>
+        <v>-8.505475545449958</v>
       </c>
       <c r="H90" t="n">
-        <v>10.35495574650216</v>
+        <v>18.01507251382666</v>
       </c>
       <c r="I90" t="n">
-        <v>50.33788731551233</v>
+        <v>44.4052423578184</v>
       </c>
       <c r="J90" t="n">
-        <v>29.35186553155452</v>
+        <v>17.47700286916833</v>
       </c>
       <c r="K90" t="n">
-        <v>0.4972387150062632</v>
+        <v>0.07802985796994885</v>
       </c>
       <c r="L90" t="n">
-        <v>100.1553335061157</v>
+        <v>298.9104035431631</v>
       </c>
       <c r="M90" t="n">
-        <v>100.81113941346</v>
+        <v>282.1252747967791</v>
       </c>
       <c r="N90" t="n">
-        <v>99.51284128280051</v>
+        <v>225.5153413796808</v>
       </c>
       <c r="O90" t="n">
-        <v>0.0661653848872803</v>
+        <v>-4.581451286481601</v>
       </c>
       <c r="P90" t="n">
-        <v>80.59096361740072</v>
+        <v>9.670929668545892</v>
       </c>
       <c r="Q90" t="n">
-        <v>-19.40903638259929</v>
+        <v>-90.3290703314541</v>
       </c>
       <c r="R90" t="n">
-        <v>-11.12605113008034</v>
+        <v>-94.49612108649325</v>
       </c>
       <c r="S90" t="n">
-        <v>-3.123678586048273</v>
+        <v>-4.621546909378116</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="n">
-        <v>48.7</v>
+        <v>49.4</v>
       </c>
       <c r="X90" t="n">
-        <v>58.6</v>
+        <v>55.6</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 29); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -30663,52 +30663,52 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>63074.69921875</v>
+        <v>63000</v>
       </c>
       <c r="E93" t="n">
-        <v>-14.27702214860589</v>
+        <v>-14.37854367076511</v>
       </c>
       <c r="F93" t="n">
-        <v>-19.77384515113674</v>
+        <v>-19.8688567986714</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.4023413752674454</v>
+        <v>-0.520294649412989</v>
       </c>
       <c r="H93" t="n">
-        <v>9.219925940431061</v>
+        <v>9.090577037610469</v>
       </c>
       <c r="I93" t="n">
-        <v>42.49906545092831</v>
+        <v>42.46855576857836</v>
       </c>
       <c r="J93" t="n">
         <v>30.00632113396347</v>
       </c>
       <c r="K93" t="n">
-        <v>0.07507190214311525</v>
+        <v>0.07416139104240797</v>
       </c>
       <c r="L93" t="n">
-        <v>80229.53151969271</v>
+        <v>80222.41730838318</v>
       </c>
       <c r="M93" t="n">
-        <v>66716.59625830226</v>
+        <v>66713.60828955227</v>
       </c>
       <c r="N93" t="n">
-        <v>49915.317853668</v>
+        <v>49913.79337981596</v>
       </c>
       <c r="O93" t="n">
-        <v>-5951.312557391263</v>
+        <v>-5956.079687020891</v>
       </c>
       <c r="P93" t="n">
-        <v>5.911210846248604</v>
+        <v>5.799867631823629</v>
       </c>
       <c r="Q93" t="n">
-        <v>-94.08878915375139</v>
+        <v>-94.20013236817637</v>
       </c>
       <c r="R93" t="n">
-        <v>-67.857842710247</v>
+        <v>-67.91610144362539</v>
       </c>
       <c r="S93" t="n">
-        <v>-10.16943560999535</v>
+        <v>-10.2758217372844</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -30718,10 +30718,10 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="X93" t="n">
-        <v>58.2</v>
+        <v>58.3</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -31315,52 +31315,52 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>69.18000030517578</v>
+        <v>68.83000183105469</v>
       </c>
       <c r="E100" t="n">
-        <v>-15.9399417984773</v>
+        <v>-16.36522211034891</v>
       </c>
       <c r="F100" t="n">
-        <v>-34.39025276170498</v>
+        <v>-34.72218845583009</v>
       </c>
       <c r="G100" t="n">
-        <v>-54.67127887571331</v>
+        <v>-54.90060791817319</v>
       </c>
       <c r="H100" t="n">
-        <v>61.04851066429688</v>
+        <v>60.23372701666278</v>
       </c>
       <c r="I100" t="n">
-        <v>39.75067172441278</v>
+        <v>39.70104041897753</v>
       </c>
       <c r="J100" t="n">
         <v>26.98955752673374</v>
       </c>
       <c r="K100" t="n">
-        <v>0.130098871498916</v>
+        <v>0.1286977702876669</v>
       </c>
       <c r="L100" t="n">
-        <v>121.8435435838026</v>
+        <v>121.8102103957911</v>
       </c>
       <c r="M100" t="n">
-        <v>118.0192770327054</v>
+        <v>118.0008560603833</v>
       </c>
       <c r="N100" t="n">
-        <v>94.54806144705313</v>
+        <v>94.53860202883364</v>
       </c>
       <c r="O100" t="n">
-        <v>-14.26225347811457</v>
+        <v>-14.28458956307273</v>
       </c>
       <c r="P100" t="n">
-        <v>4.546421554369698</v>
+        <v>4.364882538815713</v>
       </c>
       <c r="Q100" t="n">
-        <v>-95.4535784456303</v>
+        <v>-95.63511746118429</v>
       </c>
       <c r="R100" t="n">
-        <v>-104.63321638096</v>
+        <v>-104.7680744765498</v>
       </c>
       <c r="S100" t="n">
-        <v>-63.44797497701682</v>
+        <v>-63.63290057585529</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -31859,52 +31859,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.1615999937057495</v>
+        <v>0.1608999967575073</v>
       </c>
       <c r="E106" t="n">
-        <v>-31.31792380709548</v>
+        <v>-31.61543151505686</v>
       </c>
       <c r="F106" t="n">
-        <v>-44.93962891492078</v>
+        <v>-45.1781319670856</v>
       </c>
       <c r="G106" t="n">
-        <v>-56.70044775270814</v>
+        <v>-56.88800688398228</v>
       </c>
       <c r="H106" t="n">
-        <v>-88.05130643758817</v>
+        <v>-88.10306416874502</v>
       </c>
       <c r="I106" t="n">
-        <v>36.7083763086374</v>
+        <v>36.68763757489113</v>
       </c>
       <c r="J106" t="n">
         <v>29.50544762995306</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1277556313645134</v>
+        <v>0.1272159112830145</v>
       </c>
       <c r="L106" t="n">
-        <v>0.4342835952423283</v>
+        <v>0.4342169288663053</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5078127525189843</v>
+        <v>0.5077847526410546</v>
       </c>
       <c r="N106" t="n">
-        <v>0.5008668626266887</v>
+        <v>0.5008525769746837</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.05192226255775707</v>
+        <v>-0.05196693472767344</v>
       </c>
       <c r="P106" t="n">
-        <v>1.426714999444151</v>
+        <v>1.345999238135036</v>
       </c>
       <c r="Q106" t="n">
-        <v>-98.57328500055584</v>
+        <v>-98.65400076186496</v>
       </c>
       <c r="R106" t="n">
-        <v>-103.5402367839942</v>
+        <v>-103.5925517780554</v>
       </c>
       <c r="S106" t="n">
-        <v>-52.72711580182583</v>
+        <v>-52.93188607386916</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -31955,52 +31955,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1702.2900390625</v>
+        <v>1700.180053710938</v>
       </c>
       <c r="E107" t="n">
-        <v>-15.06986238247711</v>
+        <v>-15.17513313080261</v>
       </c>
       <c r="F107" t="n">
-        <v>-30.37929940961125</v>
+        <v>-30.46559413908764</v>
       </c>
       <c r="G107" t="n">
-        <v>-34.60434087137251</v>
+        <v>-34.68539866977986</v>
       </c>
       <c r="H107" t="n">
-        <v>-38.61655405167471</v>
+        <v>-38.69263871927385</v>
       </c>
       <c r="I107" t="n">
-        <v>40.96430048693965</v>
+        <v>40.94822034820016</v>
       </c>
       <c r="J107" t="n">
         <v>13.77196504624608</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1790922400420079</v>
+        <v>0.1785530894373751</v>
       </c>
       <c r="L107" t="n">
-        <v>2589.267678356793</v>
+        <v>2589.06672737093</v>
       </c>
       <c r="M107" t="n">
-        <v>2454.005068713865</v>
+        <v>2453.920669299802</v>
       </c>
       <c r="N107" t="n">
-        <v>2027.227182880649</v>
+        <v>2027.184121955107</v>
       </c>
       <c r="O107" t="n">
-        <v>-187.7623016979054</v>
+        <v>-187.8969560337318</v>
       </c>
       <c r="P107" t="n">
-        <v>5.679471991277523</v>
+        <v>5.618263801455292</v>
       </c>
       <c r="Q107" t="n">
-        <v>-94.32052800872248</v>
+        <v>-94.3817361985447</v>
       </c>
       <c r="R107" t="n">
-        <v>-108.0787952656213</v>
+        <v>-108.1405660590261</v>
       </c>
       <c r="S107" t="n">
-        <v>-32.33601631253424</v>
+        <v>-32.41988569503239</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -32043,52 +32043,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>7.89799976348877</v>
+        <v>7.863999843597412</v>
       </c>
       <c r="E108" t="n">
-        <v>-13.46264045930045</v>
+        <v>-13.8351731739246</v>
       </c>
       <c r="F108" t="n">
-        <v>-20.77129439605144</v>
+        <v>-21.11236425225518</v>
       </c>
       <c r="G108" t="n">
-        <v>-33.35343329503262</v>
+        <v>-33.64033858711406</v>
       </c>
       <c r="H108" t="n">
-        <v>-79.2858397750351</v>
+        <v>-79.37501169316066</v>
       </c>
       <c r="I108" t="n">
-        <v>40.80554408031987</v>
+        <v>40.75843783436481</v>
       </c>
       <c r="J108" t="n">
         <v>20.55337850896174</v>
       </c>
       <c r="K108" t="n">
-        <v>0.1730382527961523</v>
+        <v>0.1716105394969771</v>
       </c>
       <c r="L108" t="n">
-        <v>12.55228917983446</v>
+        <v>12.54905109222576</v>
       </c>
       <c r="M108" t="n">
-        <v>12.83674326233272</v>
+        <v>12.83538326553707</v>
       </c>
       <c r="N108" t="n">
-        <v>10.97566110791633</v>
+        <v>10.97496723200018</v>
       </c>
       <c r="O108" t="n">
-        <v>-1.052419568152426</v>
+        <v>-1.05458936360988</v>
       </c>
       <c r="P108" t="n">
-        <v>4.211476526176972</v>
+        <v>4.047300506034596</v>
       </c>
       <c r="Q108" t="n">
-        <v>-95.78852347382303</v>
+        <v>-95.9526994939654</v>
       </c>
       <c r="R108" t="n">
-        <v>-105.4551321152539</v>
+        <v>-105.60785681783</v>
       </c>
       <c r="S108" t="n">
-        <v>-30.8542314900619</v>
+        <v>-31.15189553925982</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -32783,52 +32783,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.9599999785423279</v>
+        <v>0.9520000219345093</v>
       </c>
       <c r="E116" t="n">
-        <v>-19.07796128313426</v>
+        <v>-19.75230796315619</v>
       </c>
       <c r="F116" t="n">
-        <v>-37.82516648795951</v>
+        <v>-38.34328730182652</v>
       </c>
       <c r="G116" t="n">
-        <v>-78.36417964966851</v>
+        <v>-78.54447717867473</v>
       </c>
       <c r="H116" t="n">
-        <v>-97.3727900487383</v>
+        <v>-97.39468334673778</v>
       </c>
       <c r="I116" t="n">
-        <v>34.35750869111423</v>
+        <v>34.33009369120902</v>
       </c>
       <c r="J116" t="n">
         <v>29.28244893567739</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2091641092566715</v>
+        <v>0.208330718329973</v>
       </c>
       <c r="L116" t="n">
-        <v>2.995058527994535</v>
+        <v>2.994296627365219</v>
       </c>
       <c r="M116" t="n">
-        <v>4.498914031450106</v>
+        <v>4.498469589416338</v>
       </c>
       <c r="N116" t="n">
-        <v>6.5208460171801</v>
+        <v>6.520617446991305</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.06500110206312293</v>
+        <v>-0.06551164060447645</v>
       </c>
       <c r="P116" t="n">
-        <v>1.506832897863237</v>
+        <v>1.328007809749409</v>
       </c>
       <c r="Q116" t="n">
-        <v>-98.49316710213677</v>
+        <v>-98.67199219025059</v>
       </c>
       <c r="R116" t="n">
-        <v>-80.32285306468067</v>
+        <v>-80.39811211092784</v>
       </c>
       <c r="S116" t="n">
-        <v>-84.80620565288463</v>
+        <v>-84.93281992184492</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -32875,52 +32875,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.010000228881836</v>
+        <v>5.860000133514404</v>
       </c>
       <c r="E117" t="n">
-        <v>-32.92349802387528</v>
+        <v>-34.5976213699911</v>
       </c>
       <c r="F117" t="n">
-        <v>-40.52880963098645</v>
+        <v>-42.01311643418709</v>
       </c>
       <c r="G117" t="n">
-        <v>-78.33371312141936</v>
+        <v>-78.87446935673982</v>
       </c>
       <c r="H117" t="n">
-        <v>-81.74271793693943</v>
+        <v>-82.19839080654241</v>
       </c>
       <c r="I117" t="n">
-        <v>38.34601001625779</v>
+        <v>38.24742508721998</v>
       </c>
       <c r="J117" t="n">
-        <v>15.77413907764411</v>
+        <v>15.81613625954131</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1792590856182565</v>
+        <v>0.1761640505757236</v>
       </c>
       <c r="L117" t="n">
-        <v>16.54733500433906</v>
+        <v>16.53304928097074</v>
       </c>
       <c r="M117" t="n">
-        <v>20.04005648586459</v>
+        <v>20.03172314723306</v>
       </c>
       <c r="N117" t="n">
-        <v>21.30872004062441</v>
+        <v>21.30443432361391</v>
       </c>
       <c r="O117" t="n">
-        <v>-1.344047342819494</v>
+        <v>-1.353619998478271</v>
       </c>
       <c r="P117" t="n">
-        <v>0.1143919221576764</v>
+        <v>0.5381724934767353</v>
       </c>
       <c r="Q117" t="n">
-        <v>-99.88560807784232</v>
+        <v>-99.46182750652326</v>
       </c>
       <c r="R117" t="n">
-        <v>-85.14114702624134</v>
+        <v>-85.96591709353282</v>
       </c>
       <c r="S117" t="n">
-        <v>-82.52787248634156</v>
+        <v>-82.96394914083585</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; breakdown minimi 50g — rottura supporto importante; evening star — inversione ribassista a 3 candele; sul supporto dei 20g (5.9758)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; breakdown minimi 50g — rottura supporto importante; evening star — inversione ribassista a 3 candele</t>
         </is>
       </c>
     </row>
@@ -33208,7 +33208,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19/06/2026 18:04:56</t>
+          <t>19/06/2026 20:26:48</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33248,7 +33248,7 @@
         <v>16.78000068664551</v>
       </c>
       <c r="N2" t="n">
-        <v>100.7320022583008</v>
+        <v>100.8489990234375</v>
       </c>
       <c r="O2" t="n">
         <v>4172.89990234375</v>
@@ -33271,7 +33271,7 @@
         <v>4.717527417231073</v>
       </c>
       <c r="U2" t="n">
-        <v>3.692673998604442</v>
+        <v>3.669083563629744</v>
       </c>
       <c r="V2" t="n">
         <v>1.766907821710997</v>
@@ -33322,7 +33322,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.982264602279306</v>
+        <v>2.978332863116856</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33421,10 +33421,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.64576438713685</v>
+        <v>60.64583473472661</v>
       </c>
       <c r="C2" t="n">
-        <v>0.133820851149743</v>
+        <v>0.1338236650533333</v>
       </c>
       <c r="D2" t="n">
         <v>52.58620689655172</v>
@@ -33894,7 +33894,7 @@
         <v>0.911</v>
       </c>
       <c r="E21" t="n">
-        <v>0.908</v>
+        <v>0.909</v>
       </c>
     </row>
   </sheetData>
@@ -33983,43 +33983,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.502</v>
+        <v>-0.729</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.698</v>
+        <v>-0.703</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.761</v>
+        <v>-0.641</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.707</v>
+        <v>-0.502</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.698</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.634</v>
+        <v>-0.761</v>
       </c>
     </row>
     <row r="6">
@@ -34034,13 +34034,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.743</v>
+        <v>-0.754</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.675</v>
+        <v>-0.679</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.572</v>
+        <v>-0.575</v>
       </c>
     </row>
     <row r="7">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1089,7 +1089,7 @@
         <v>75.3</v>
       </c>
       <c r="X7" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -3689,12 +3689,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3703,52 +3703,46 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>100.8359985351562</v>
+        <v>162.5390014648438</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.02379741726161733</v>
+        <v>-0.05472889866934283</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5169712628650069</v>
+        <v>0.4797147519643774</v>
       </c>
       <c r="G36" t="n">
-        <v>1.312166956572924</v>
+        <v>1.607195881821077</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8561663827582722</v>
+        <v>1.788545325196367</v>
       </c>
       <c r="I36" t="n">
-        <v>57.61033255831512</v>
+        <v>78.30385849751123</v>
       </c>
       <c r="J36" t="n">
-        <v>58.25502657518414</v>
+        <v>51.34634873082719</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5844199673308406</v>
+        <v>0.9278053096179374</v>
       </c>
       <c r="L36" t="n">
-        <v>100.6157572340193</v>
+        <v>161.1720042985502</v>
       </c>
       <c r="M36" t="n">
-        <v>99.8808849937048</v>
+        <v>160.0562338794009</v>
       </c>
       <c r="N36" t="n">
-        <v>99.32828207060132</v>
+        <v>156.6626765739301</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.03068895546664074</v>
-      </c>
-      <c r="P36" t="n">
-        <v>60.16519806428222</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-39.83480193571778</v>
-      </c>
-      <c r="R36" t="n">
-        <v>19.27099384333514</v>
-      </c>
+        <v>0.1048596616097186</v>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="n">
-        <v>1.43445812344376</v>
+        <v>1.624983733753305</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3758,14 +3752,14 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Double Bottom, Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>66.2</v>
+        <v>66.3</v>
       </c>
       <c r="X36" t="n">
-        <v>68.2</v>
+        <v>64.3</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3774,19 +3768,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 58); pattern: Double Bottom; vicino alla resistenza dei 20g (101.80); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI ipercomprato (78) — attenzione estensione; pattern: Double Bottom; vicino alla resistenza dei 20g (162.84); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3795,52 +3789,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>161.3090057373047</v>
+        <v>100.8570022583008</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7567388235771189</v>
+        <v>-0.002972786072419353</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.3065337665262291</v>
+        <v>-0.4962493577564286</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8559480273860665</v>
+        <v>1.333269863638264</v>
       </c>
       <c r="H37" t="n">
-        <v>1.633737155356307</v>
+        <v>0.8771743067823801</v>
       </c>
       <c r="I37" t="n">
-        <v>55.61698673278401</v>
+        <v>57.99353004746195</v>
       </c>
       <c r="J37" t="n">
-        <v>51.34634873082719</v>
+        <v>58.25502657518414</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5569162958367979</v>
+        <v>0.5913828857782156</v>
       </c>
       <c r="L37" t="n">
-        <v>161.1850520546221</v>
+        <v>100.6177575886045</v>
       </c>
       <c r="M37" t="n">
-        <v>160.105362187554</v>
+        <v>99.88170866912223</v>
       </c>
       <c r="N37" t="n">
-        <v>156.708908704909</v>
+        <v>99.32849106287141</v>
       </c>
       <c r="O37" t="n">
-        <v>0.01473695750174442</v>
+        <v>-0.02934854692409439</v>
       </c>
       <c r="P37" t="n">
-        <v>45.03265424944661</v>
+        <v>61.03311842872681</v>
       </c>
       <c r="Q37" t="n">
-        <v>-54.96734575055339</v>
+        <v>-38.96688157127319</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3967209805096341</v>
+        <v>19.79282100035349</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8244266509491283</v>
+        <v>1.455586503255435</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3850,7 +3844,7 @@
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
+          <t>Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W37" t="n">
@@ -3866,7 +3860,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); pattern: Double Bottom; sul supporto dei 20g (159.89); vicino alla resistenza dei 20g (162.84); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 58); pattern: Double Bottom; vicino alla resistenza dei 20g (101.80); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -4805,52 +4799,52 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>81.75</v>
+        <v>82.19000244140625</v>
       </c>
       <c r="E48" t="n">
-        <v>1.371482458935369</v>
+        <v>1.917093465307262</v>
       </c>
       <c r="F48" t="n">
-        <v>14.63557263031541</v>
+        <v>15.25257485452753</v>
       </c>
       <c r="G48" t="n">
-        <v>22.47323996529416</v>
+        <v>23.13242681045211</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.997998244480693</v>
+        <v>-2.475905062906114</v>
       </c>
       <c r="I48" t="n">
-        <v>65.07873303212712</v>
+        <v>65.61314610942259</v>
       </c>
       <c r="J48" t="n">
         <v>19.1381050228664</v>
       </c>
       <c r="K48" t="n">
-        <v>1.107202501949674</v>
+        <v>1.125693225559595</v>
       </c>
       <c r="L48" t="n">
-        <v>73.81543298444106</v>
+        <v>73.8573379788607</v>
       </c>
       <c r="M48" t="n">
-        <v>75.68341874091468</v>
+        <v>75.70067373861689</v>
       </c>
       <c r="N48" t="n">
-        <v>96.84295600839476</v>
+        <v>96.8473341421401</v>
       </c>
       <c r="O48" t="n">
-        <v>1.610921903791314</v>
+        <v>1.639001831675933</v>
       </c>
       <c r="P48" t="n">
-        <v>95.33200135799376</v>
+        <v>97.75221817537843</v>
       </c>
       <c r="Q48" t="n">
-        <v>-4.667998642006238</v>
+        <v>-2.247781824621568</v>
       </c>
       <c r="R48" t="n">
-        <v>208.8925491345166</v>
+        <v>214.4834328801499</v>
       </c>
       <c r="S48" t="n">
-        <v>18.69709793433114</v>
+        <v>19.33596047719284</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4864,10 +4858,10 @@
         </is>
       </c>
       <c r="W48" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="X48" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4876,7 +4870,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>RSI in forza (65) — momentum positivo; vicino alla resistenza dei 20g (82.60)</t>
+          <t>RSI in forza (66) — momentum positivo; vicino alla resistenza dei 20g (82.60)</t>
         </is>
       </c>
     </row>
@@ -7113,73 +7107,69 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.33571982383728</v>
+        <v>1.33552360534668</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5863812681168312</v>
+        <v>0.5716050346918244</v>
       </c>
       <c r="F73" t="n">
-        <v>1.283632461295592</v>
+        <v>1.268753801018629</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.520930207781678</v>
+        <v>-0.5355437761158766</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.3325944224010557</v>
+        <v>-0.3472356574381497</v>
       </c>
       <c r="I73" t="n">
-        <v>53.61424822651581</v>
+        <v>53.44604511167641</v>
       </c>
       <c r="J73" t="n">
         <v>34.79252082454199</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6631633011854994</v>
+        <v>0.6581396890618093</v>
       </c>
       <c r="L73" t="n">
-        <v>1.329984573404389</v>
+        <v>1.329965885929094</v>
       </c>
       <c r="M73" t="n">
-        <v>1.336480710559331</v>
+        <v>1.336473015716562</v>
       </c>
       <c r="N73" t="n">
-        <v>1.338414275384924</v>
+        <v>1.338412322962132</v>
       </c>
       <c r="O73" t="n">
-        <v>0.001063158633224443</v>
+        <v>0.001050636427556501</v>
       </c>
       <c r="P73" t="n">
-        <v>71.82308073620418</v>
+        <v>71.16507027839519</v>
       </c>
       <c r="Q73" t="n">
-        <v>-28.17691926379583</v>
+        <v>-28.83492972160481</v>
       </c>
       <c r="R73" t="n">
-        <v>42.77033758552899</v>
+        <v>42.3195952542145</v>
       </c>
       <c r="S73" t="n">
-        <v>-0.5198615265181394</v>
+        <v>-0.5344752518426032</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="X73" t="n">
-        <v>62.4</v>
+        <v>56.4</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -7188,7 +7178,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (1.3461); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 35); pattern: Double Bottom; vicino alla resistenza dei 20g (1.3461); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7379,83 +7369,79 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>COTTON</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>72.56999969482422</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9688852296668493</v>
+        <v>1.723555302599666</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.130792661853075</v>
+        <v>7.2521374647327</v>
       </c>
       <c r="G76" t="n">
-        <v>-5.802182200911943</v>
+        <v>5.257477085340923</v>
       </c>
       <c r="H76" t="n">
-        <v>2.326567355442233</v>
+        <v>-24.73356863766768</v>
       </c>
       <c r="I76" t="n">
-        <v>43.1498933780203</v>
+        <v>51.67755511342694</v>
       </c>
       <c r="J76" t="n">
-        <v>14.64486009625032</v>
+        <v>36.97876607456516</v>
       </c>
       <c r="K76" t="n">
-        <v>0.3719258006802371</v>
+        <v>0.859439642414791</v>
       </c>
       <c r="L76" t="n">
-        <v>73.9394938126256</v>
+        <v>6.687766796962074</v>
       </c>
       <c r="M76" t="n">
-        <v>74.79148975701614</v>
+        <v>7.365478550225608</v>
       </c>
       <c r="N76" t="n">
-        <v>70.44261985394238</v>
+        <v>10.42381850983205</v>
       </c>
       <c r="O76" t="n">
-        <v>0.01847026383485018</v>
+        <v>0.1425425837437522</v>
       </c>
       <c r="P76" t="n">
-        <v>26.16434562224022</v>
+        <v>100.3564351617813</v>
       </c>
       <c r="Q76" t="n">
-        <v>-73.83565437775978</v>
+        <v>0.3564351617812837</v>
       </c>
       <c r="R76" t="n">
-        <v>-20.67858884527496</v>
+        <v>58.57887739433393</v>
       </c>
       <c r="S76" t="n">
-        <v>-5.42161277220049</v>
+        <v>2.896898036971352</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="X76" t="n">
-        <v>61.9</v>
+        <v>56.1</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -7464,77 +7450,77 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 15); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 37); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>COTTON</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5.513999938964844</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="E77" t="n">
-        <v>2.988416971911323</v>
+        <v>-0.9688852296668493</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.1810323783124401</v>
+        <v>-1.130792661853075</v>
       </c>
       <c r="G77" t="n">
-        <v>2.528824133529306</v>
+        <v>-5.802182200911943</v>
       </c>
       <c r="H77" t="n">
-        <v>-11.71949881557952</v>
+        <v>2.326567355442233</v>
       </c>
       <c r="I77" t="n">
-        <v>49.93210808971318</v>
+        <v>43.1498933780203</v>
       </c>
       <c r="J77" t="n">
-        <v>9.660583359844347</v>
+        <v>14.64486009625032</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7267940500573961</v>
+        <v>0.3719258006802371</v>
       </c>
       <c r="L77" t="n">
-        <v>5.483130379921562</v>
+        <v>73.9394938126256</v>
       </c>
       <c r="M77" t="n">
-        <v>5.638946845876156</v>
+        <v>74.79148975701614</v>
       </c>
       <c r="N77" t="n">
-        <v>5.914717133435826</v>
+        <v>70.44261985394238</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01521546702563684</v>
+        <v>0.01847026383485018</v>
       </c>
       <c r="P77" t="n">
-        <v>54.63914611740272</v>
+        <v>26.16434562224022</v>
       </c>
       <c r="Q77" t="n">
-        <v>-45.36085388259729</v>
+        <v>-73.83565437775978</v>
       </c>
       <c r="R77" t="n">
-        <v>48.25729487085574</v>
+        <v>-20.67858884527496</v>
       </c>
       <c r="S77" t="n">
-        <v>1.771866256775656</v>
+        <v>-5.42161277220049</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -7542,16 +7528,12 @@
           <t>Doji</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="X77" t="n">
-        <v>57</v>
+        <v>61.9</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7560,86 +7542,94 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 10); pattern: Double Bottom; doji — indecisione del mercato</t>
+          <t>mercato laterale — ATR basso (ADX 15); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6.860000133514404</v>
+        <v>5.513999938964844</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9874990400670081</v>
+        <v>2.988416971911323</v>
       </c>
       <c r="F78" t="n">
-        <v>6.476077217761445</v>
+        <v>-0.1810323783124401</v>
       </c>
       <c r="G78" t="n">
-        <v>4.495849899222781</v>
+        <v>2.528824133529306</v>
       </c>
       <c r="H78" t="n">
-        <v>-25.27818515247517</v>
+        <v>-11.71949881557952</v>
       </c>
       <c r="I78" t="n">
-        <v>50.66984660351347</v>
+        <v>49.93210808971318</v>
       </c>
       <c r="J78" t="n">
-        <v>36.97876607456516</v>
+        <v>9.660583359844347</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8210125301142134</v>
+        <v>0.7267940500573961</v>
       </c>
       <c r="L78" t="n">
-        <v>6.683004919448007</v>
+        <v>5.483130379921562</v>
       </c>
       <c r="M78" t="n">
-        <v>7.36351777713158</v>
+        <v>5.638946845876156</v>
       </c>
       <c r="N78" t="n">
-        <v>10.42332100024102</v>
+        <v>5.914717133435826</v>
       </c>
       <c r="O78" t="n">
-        <v>0.139351718811249</v>
+        <v>0.01521546702563684</v>
       </c>
       <c r="P78" t="n">
-        <v>95.63203600125796</v>
+        <v>54.63914611740272</v>
       </c>
       <c r="Q78" t="n">
-        <v>-4.367963998742047</v>
+        <v>-45.36085388259729</v>
       </c>
       <c r="R78" t="n">
-        <v>56.22699704652847</v>
+        <v>48.25729487085574</v>
       </c>
       <c r="S78" t="n">
-        <v>2.152351643857209</v>
+        <v>1.771866256775656</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W78" t="n">
         <v>45.2</v>
       </c>
       <c r="X78" t="n">
-        <v>55.9</v>
+        <v>57</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7648,7 +7638,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 37); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 10); pattern: Double Bottom; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -8221,52 +8211,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1734.300048828125</v>
+        <v>1744.18994140625</v>
       </c>
       <c r="E85" t="n">
-        <v>2.127621338579488</v>
+        <v>2.710006840431056</v>
       </c>
       <c r="F85" t="n">
-        <v>10.43956270324016</v>
+        <v>11.06934727382134</v>
       </c>
       <c r="G85" t="n">
-        <v>4.154170081990505</v>
+        <v>4.748112032445184</v>
       </c>
       <c r="H85" t="n">
-        <v>-25.12407657996185</v>
+        <v>-24.69709461694314</v>
       </c>
       <c r="I85" t="n">
-        <v>53.29702355776914</v>
+        <v>54.15421101017839</v>
       </c>
       <c r="J85" t="n">
         <v>20.44441239659244</v>
       </c>
       <c r="K85" t="n">
-        <v>0.699744063457921</v>
+        <v>0.7285309396920854</v>
       </c>
       <c r="L85" t="n">
-        <v>1671.577710322572</v>
+        <v>1672.519604853822</v>
       </c>
       <c r="M85" t="n">
-        <v>1806.856171142269</v>
+        <v>1807.244010066902</v>
       </c>
       <c r="N85" t="n">
-        <v>2269.826565215214</v>
+        <v>2269.924972106538</v>
       </c>
       <c r="O85" t="n">
-        <v>20.36943926654972</v>
+        <v>21.00058910629328</v>
       </c>
       <c r="P85" t="n">
-        <v>84.03007684216075</v>
+        <v>87.74352639744791</v>
       </c>
       <c r="Q85" t="n">
-        <v>-15.96992315783925</v>
+        <v>-12.25647360255209</v>
       </c>
       <c r="R85" t="n">
-        <v>68.14953325681815</v>
+        <v>71.83130038425395</v>
       </c>
       <c r="S85" t="n">
-        <v>3.218960794134507</v>
+        <v>3.807569688523627</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8280,10 +8270,10 @@
         </is>
       </c>
       <c r="W85" t="n">
-        <v>43.2</v>
+        <v>43.4</v>
       </c>
       <c r="X85" t="n">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -8751,83 +8741,79 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>20.44499969482422</v>
+        <v>0.1821999996900558</v>
       </c>
       <c r="E91" t="n">
-        <v>1.817727950722015</v>
+        <v>12.96212464858801</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.170897696261807</v>
+        <v>26.81929080679977</v>
       </c>
       <c r="G91" t="n">
-        <v>-12.8330856477199</v>
+        <v>7.277441751977953</v>
       </c>
       <c r="H91" t="n">
-        <v>-17.17642237330426</v>
+        <v>-27.14389290221047</v>
       </c>
       <c r="I91" t="n">
-        <v>35.36943537656649</v>
+        <v>59.73830029790061</v>
       </c>
       <c r="J91" t="n">
-        <v>49.89199583755958</v>
+        <v>38.18681898929582</v>
       </c>
       <c r="K91" t="n">
-        <v>0.2357528920674938</v>
+        <v>0.9583160521575457</v>
       </c>
       <c r="L91" t="n">
-        <v>21.44480031734003</v>
+        <v>0.1613835235165188</v>
       </c>
       <c r="M91" t="n">
-        <v>22.09834073766282</v>
+        <v>0.1859171884166575</v>
       </c>
       <c r="N91" t="n">
-        <v>19.75335525708702</v>
+        <v>0.2929863611985647</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.1333154045249789</v>
+        <v>0.004898882676287518</v>
       </c>
       <c r="P91" t="n">
-        <v>15.43339562124327</v>
+        <v>99.95689581386112</v>
       </c>
       <c r="Q91" t="n">
-        <v>-84.56660437875674</v>
+        <v>-0.04310418613887149</v>
       </c>
       <c r="R91" t="n">
-        <v>-84.6928807933466</v>
+        <v>75.73660974138078</v>
       </c>
       <c r="S91" t="n">
-        <v>-12.68418152712353</v>
+        <v>6.08380259786232</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar</t>
-        </is>
-      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="X91" t="n">
-        <v>64.3</v>
+        <v>63.7</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -8836,86 +8822,90 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 50); RSI scarico (35) — zona di interesse long; pattern: Double Top</t>
+          <t>trend molto direzionale (ADX 38)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.1752000004053116</v>
+        <v>20.44499969482422</v>
       </c>
       <c r="E92" t="n">
-        <v>8.622197134381416</v>
+        <v>1.817727950722015</v>
       </c>
       <c r="F92" t="n">
-        <v>21.94698045307024</v>
+        <v>-0.170897696261807</v>
       </c>
       <c r="G92" t="n">
-        <v>3.155915863885284</v>
+        <v>-12.8330856477199</v>
       </c>
       <c r="H92" t="n">
-        <v>-29.94297467192144</v>
+        <v>-17.17642237330426</v>
       </c>
       <c r="I92" t="n">
-        <v>56.08170835405709</v>
+        <v>35.36943537656649</v>
       </c>
       <c r="J92" t="n">
-        <v>37.62046887464285</v>
+        <v>49.89199583755958</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8455294719177382</v>
+        <v>0.2357528920674938</v>
       </c>
       <c r="L92" t="n">
-        <v>0.1607168569179717</v>
+        <v>21.44480031734003</v>
       </c>
       <c r="M92" t="n">
-        <v>0.1856426786407852</v>
+        <v>22.09834073766282</v>
       </c>
       <c r="N92" t="n">
-        <v>0.2929167094643882</v>
+        <v>19.75335525708702</v>
       </c>
       <c r="O92" t="n">
-        <v>0.004452159075209825</v>
+        <v>-0.1333154045249789</v>
       </c>
       <c r="P92" t="n">
-        <v>96.97900696046867</v>
+        <v>15.43339562124327</v>
       </c>
       <c r="Q92" t="n">
-        <v>-3.020993039531329</v>
+        <v>-84.56660437875674</v>
       </c>
       <c r="R92" t="n">
-        <v>58.21827863374145</v>
+        <v>-84.6928807933466</v>
       </c>
       <c r="S92" t="n">
-        <v>2.008135509107012</v>
+        <v>-12.68418152712353</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Double Top, Inside Bar</t>
+        </is>
+      </c>
       <c r="W92" t="n">
         <v>41.2</v>
       </c>
       <c r="X92" t="n">
-        <v>62.6</v>
+        <v>64.3</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -8924,90 +8914,90 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 38); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 50); RSI scarico (35) — zona di interesse long; pattern: Double Top</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Tenaris</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7.875</v>
+        <v>23.68000030517578</v>
       </c>
       <c r="E93" t="n">
-        <v>1.72440438203294</v>
+        <v>-0.837516175123687</v>
       </c>
       <c r="F93" t="n">
-        <v>8.47153404746679</v>
+        <v>-5.619768189864582</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2457725482807316</v>
+        <v>-14.48176291636287</v>
       </c>
       <c r="H93" t="n">
-        <v>-14.16286313394465</v>
+        <v>-6.329115261120021</v>
       </c>
       <c r="I93" t="n">
-        <v>51.53151370909507</v>
+        <v>31.31686685186551</v>
       </c>
       <c r="J93" t="n">
-        <v>23.49368802366068</v>
+        <v>46.90604926204401</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6162589460903292</v>
+        <v>0.08482012712002281</v>
       </c>
       <c r="L93" t="n">
-        <v>7.681124379824527</v>
+        <v>25.22706973010341</v>
       </c>
       <c r="M93" t="n">
-        <v>8.18730474927121</v>
+        <v>25.50369548459471</v>
       </c>
       <c r="N93" t="n">
-        <v>10.17527654730991</v>
+        <v>22.12538715960772</v>
       </c>
       <c r="O93" t="n">
-        <v>0.06907463655809587</v>
+        <v>-0.2220522757085613</v>
       </c>
       <c r="P93" t="n">
-        <v>76.51820129762586</v>
+        <v>2.089544080839735</v>
       </c>
       <c r="Q93" t="n">
-        <v>-23.48179870237413</v>
+        <v>-97.91045591916027</v>
       </c>
       <c r="R93" t="n">
-        <v>31.88373883478384</v>
+        <v>-131.3620125677935</v>
       </c>
       <c r="S93" t="n">
-        <v>-1.283871917174217</v>
+        <v>-13.51350974799381</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
         </is>
       </c>
       <c r="W93" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="X93" t="n">
-        <v>59.5</v>
+        <v>67.8</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -9016,73 +9006,73 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 47); RSI scarico (31) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (23.61); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tenaris</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>23.68000030517578</v>
+        <v>194.8300018310547</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.837516175123687</v>
+        <v>-1.391841266582972</v>
       </c>
       <c r="F94" t="n">
-        <v>-5.619768189864582</v>
+        <v>-0.4649042794377389</v>
       </c>
       <c r="G94" t="n">
-        <v>-14.48176291636287</v>
+        <v>-12.56171105516419</v>
       </c>
       <c r="H94" t="n">
-        <v>-6.329115261120021</v>
+        <v>9.831446249175624</v>
       </c>
       <c r="I94" t="n">
-        <v>31.31686685186551</v>
+        <v>41.15855680536166</v>
       </c>
       <c r="J94" t="n">
-        <v>46.90604926204401</v>
+        <v>25.99327297142875</v>
       </c>
       <c r="K94" t="n">
-        <v>0.08482012712002281</v>
+        <v>0.1815789893158984</v>
       </c>
       <c r="L94" t="n">
-        <v>25.22706973010341</v>
+        <v>202.75171786607</v>
       </c>
       <c r="M94" t="n">
-        <v>25.50369548459471</v>
+        <v>204.1884814568574</v>
       </c>
       <c r="N94" t="n">
-        <v>22.12538715960772</v>
+        <v>188.9462997597143</v>
       </c>
       <c r="O94" t="n">
-        <v>-0.2220522757085613</v>
+        <v>-1.000431665214234</v>
       </c>
       <c r="P94" t="n">
-        <v>2.089544080839735</v>
+        <v>20.79370926679602</v>
       </c>
       <c r="Q94" t="n">
-        <v>-97.91045591916027</v>
+        <v>-79.20629073320399</v>
       </c>
       <c r="R94" t="n">
-        <v>-131.3620125677935</v>
+        <v>-57.88591258461099</v>
       </c>
       <c r="S94" t="n">
-        <v>-13.51350974799381</v>
+        <v>-9.275901359229477</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9092,14 +9082,14 @@
       <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
+          <t>Outside Bar</t>
         </is>
       </c>
       <c r="W94" t="n">
         <v>41</v>
       </c>
       <c r="X94" t="n">
-        <v>67.8</v>
+        <v>59.7</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -9108,85 +9098,81 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); RSI scarico (31) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (23.61); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 26); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>194.8300018310547</v>
+        <v>7.941999912261963</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.391841266582972</v>
+        <v>2.58986802247696</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.4649042794377389</v>
+        <v>9.394401763543069</v>
       </c>
       <c r="G95" t="n">
-        <v>-12.56171105516419</v>
+        <v>1.098656099438511</v>
       </c>
       <c r="H95" t="n">
-        <v>9.831446249175624</v>
+        <v>-13.43256717980574</v>
       </c>
       <c r="I95" t="n">
-        <v>41.15855680536166</v>
+        <v>52.91208799379964</v>
       </c>
       <c r="J95" t="n">
-        <v>25.99327297142875</v>
+        <v>23.38371168862766</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1815789893158984</v>
+        <v>0.6583378098447404</v>
       </c>
       <c r="L95" t="n">
-        <v>202.75171786607</v>
+        <v>7.687505323849476</v>
       </c>
       <c r="M95" t="n">
-        <v>204.1884814568574</v>
+        <v>8.189932196810894</v>
       </c>
       <c r="N95" t="n">
-        <v>188.9462997597143</v>
+        <v>10.17594321310356</v>
       </c>
       <c r="O95" t="n">
-        <v>-1.000431665214234</v>
+        <v>0.07335041443464219</v>
       </c>
       <c r="P95" t="n">
-        <v>20.79370926679602</v>
+        <v>82.53126485784188</v>
       </c>
       <c r="Q95" t="n">
-        <v>-79.20629073320399</v>
+        <v>-17.46873514215812</v>
       </c>
       <c r="R95" t="n">
-        <v>-57.88591258461099</v>
+        <v>41.66116915245308</v>
       </c>
       <c r="S95" t="n">
-        <v>-9.275901359229477</v>
+        <v>-0.4440024669659537</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Outside Bar</t>
-        </is>
-      </c>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="n">
         <v>41</v>
       </c>
@@ -9200,7 +9186,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 23); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -9221,52 +9207,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.117200016975403</v>
+        <v>1.137699961662292</v>
       </c>
       <c r="E96" t="n">
-        <v>2.82596729122031</v>
+        <v>4.712761607203886</v>
       </c>
       <c r="F96" t="n">
-        <v>6.646207018352013</v>
+        <v>8.603100423045662</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.312560687477438</v>
+        <v>0.4982941428640419</v>
       </c>
       <c r="H96" t="n">
-        <v>-19.80774401053651</v>
+        <v>-18.33626460924583</v>
       </c>
       <c r="I96" t="n">
-        <v>48.67007224822937</v>
+        <v>51.92229010703826</v>
       </c>
       <c r="J96" t="n">
-        <v>21.86348540943463</v>
+        <v>21.34413613892223</v>
       </c>
       <c r="K96" t="n">
-        <v>0.5240132343631145</v>
+        <v>0.6021630511366372</v>
       </c>
       <c r="L96" t="n">
-        <v>1.104021619740909</v>
+        <v>1.105973995425375</v>
       </c>
       <c r="M96" t="n">
-        <v>1.186002820196554</v>
+        <v>1.18680673959604</v>
       </c>
       <c r="N96" t="n">
-        <v>1.506100625902931</v>
+        <v>1.506304605452055</v>
       </c>
       <c r="O96" t="n">
-        <v>0.007553291880341935</v>
+        <v>0.008861550458650613</v>
       </c>
       <c r="P96" t="n">
-        <v>70.53153894790879</v>
+        <v>83.98833409499245</v>
       </c>
       <c r="Q96" t="n">
-        <v>-29.46846105209123</v>
+        <v>-16.01166590500754</v>
       </c>
       <c r="R96" t="n">
-        <v>-7.003495122338932</v>
+        <v>10.29947933087513</v>
       </c>
       <c r="S96" t="n">
-        <v>-2.855976873059618</v>
+        <v>-1.073442796345536</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9276,10 +9262,10 @@
       <c r="U96" t="inlineStr"/>
       <c r="V96" t="inlineStr"/>
       <c r="W96" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="X96" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9288,7 +9274,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -9401,52 +9387,52 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>62120.51171875</v>
+        <v>62185.109375</v>
       </c>
       <c r="E98" t="n">
-        <v>1.033110238429069</v>
+        <v>1.138172188893982</v>
       </c>
       <c r="F98" t="n">
-        <v>4.34750571167366</v>
+        <v>4.456014223886573</v>
       </c>
       <c r="G98" t="n">
-        <v>-2.238929606144535</v>
+        <v>-2.137270172807515</v>
       </c>
       <c r="H98" t="n">
-        <v>-21.02379409558559</v>
+        <v>-20.94166860016082</v>
       </c>
       <c r="I98" t="n">
-        <v>46.26684627879301</v>
+        <v>46.51349577400001</v>
       </c>
       <c r="J98" t="n">
         <v>28.05262053307027</v>
       </c>
       <c r="K98" t="n">
-        <v>0.4857908765496323</v>
+        <v>0.4923568117219368</v>
       </c>
       <c r="L98" t="n">
-        <v>62086.98333455706</v>
+        <v>62093.13549229515</v>
       </c>
       <c r="M98" t="n">
-        <v>65982.86954519729</v>
+        <v>65985.40278661886</v>
       </c>
       <c r="N98" t="n">
-        <v>75889.39608204371</v>
+        <v>75890.03884479246</v>
       </c>
       <c r="O98" t="n">
-        <v>359.5232770435423</v>
+        <v>363.6457485535152</v>
       </c>
       <c r="P98" t="n">
-        <v>56.08792505997486</v>
+        <v>56.91650015331922</v>
       </c>
       <c r="Q98" t="n">
-        <v>-43.91207494002514</v>
+        <v>-43.08349984668079</v>
       </c>
       <c r="R98" t="n">
-        <v>-15.01315017604312</v>
+        <v>-14.23601452760458</v>
       </c>
       <c r="S98" t="n">
-        <v>-3.571507614757075</v>
+        <v>-3.471233897888648</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -9460,10 +9446,10 @@
         </is>
       </c>
       <c r="W98" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="X98" t="n">
-        <v>69.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -11057,52 +11043,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8830000162124634</v>
+        <v>0.8849999904632568</v>
       </c>
       <c r="E116" t="n">
-        <v>5.075271657389346</v>
+        <v>5.313264674208673</v>
       </c>
       <c r="F116" t="n">
-        <v>9.070785253474689</v>
+        <v>9.317828014534246</v>
       </c>
       <c r="G116" t="n">
-        <v>-7.671041686285829</v>
+        <v>-7.461918769140174</v>
       </c>
       <c r="H116" t="n">
-        <v>-28.02782404765484</v>
+        <v>-27.86480876335655</v>
       </c>
       <c r="I116" t="n">
-        <v>41.69625965215086</v>
+        <v>42.10328459094667</v>
       </c>
       <c r="J116" t="n">
-        <v>41.9827814357271</v>
+        <v>41.92978016425015</v>
       </c>
       <c r="K116" t="n">
-        <v>0.4245328661046455</v>
+        <v>0.4309656950866962</v>
       </c>
       <c r="L116" t="n">
-        <v>0.8969941235607181</v>
+        <v>0.8971845972988889</v>
       </c>
       <c r="M116" t="n">
-        <v>1.012233602815895</v>
+        <v>1.012312033178671</v>
       </c>
       <c r="N116" t="n">
-        <v>1.548766794104166</v>
+        <v>1.548786694345467</v>
       </c>
       <c r="O116" t="n">
-        <v>0.005838947100910527</v>
+        <v>0.005966580785291664</v>
       </c>
       <c r="P116" t="n">
-        <v>47.38926819773578</v>
+        <v>48.5153036997015</v>
       </c>
       <c r="Q116" t="n">
-        <v>-52.61073180226422</v>
+        <v>-51.48469630029851</v>
       </c>
       <c r="R116" t="n">
-        <v>-37.32760590764407</v>
+        <v>-36.32692057529458</v>
       </c>
       <c r="S116" t="n">
-        <v>-9.891799227130383</v>
+        <v>-9.687706273537843</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11116,10 +11102,10 @@
         </is>
       </c>
       <c r="W116" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="X116" t="n">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -13193,7 +13179,7 @@
         <v>76.8</v>
       </c>
       <c r="X21" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -15417,87 +15403,83 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>45.7599983215332</v>
+        <v>162.5390014648438</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.9523862210825129</v>
+        <v>0.4536379112437317</v>
       </c>
       <c r="F46" t="n">
-        <v>3.01665963040203</v>
+        <v>2.052487665405334</v>
       </c>
       <c r="G46" t="n">
-        <v>5.559400074375609</v>
+        <v>3.670658363273338</v>
       </c>
       <c r="H46" t="n">
-        <v>17.01828118450424</v>
+        <v>13.75989751079645</v>
       </c>
       <c r="I46" t="n">
-        <v>53.89785577945819</v>
+        <v>65.45319266692401</v>
       </c>
       <c r="J46" t="n">
-        <v>26.55932112184005</v>
+        <v>9.945181945279062</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5122357292179918</v>
+        <v>0.9788170950808129</v>
       </c>
       <c r="L46" t="n">
-        <v>45.16994268429265</v>
+        <v>159.0005133284217</v>
       </c>
       <c r="M46" t="n">
-        <v>44.07865702561099</v>
+        <v>155.9758671175692</v>
       </c>
       <c r="N46" t="n">
-        <v>38.99714510207828</v>
+        <v>146.2743544108127</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.09362646135646041</v>
+        <v>0.1672610832034351</v>
       </c>
       <c r="P46" t="n">
-        <v>57.97411596023506</v>
+        <v>96.18696861654195</v>
       </c>
       <c r="Q46" t="n">
-        <v>-42.02588403976493</v>
+        <v>-3.813031383458057</v>
       </c>
       <c r="R46" t="n">
-        <v>-4.14939351047682</v>
+        <v>110.0274831366821</v>
       </c>
       <c r="S46" t="n">
-        <v>-1.591401459068376</v>
+        <v>6.359075240754697</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="X46" t="n">
-        <v>72.40000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -15506,86 +15488,94 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Bear Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (65) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>199.25</v>
+        <v>45.7599983215332</v>
       </c>
       <c r="E47" t="n">
-        <v>5.989677205071087</v>
+        <v>-0.9523862210825129</v>
       </c>
       <c r="F47" t="n">
-        <v>10.90392738426855</v>
+        <v>3.01665963040203</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2969879829933575</v>
+        <v>5.559400074375609</v>
       </c>
       <c r="H47" t="n">
-        <v>59.11994733877801</v>
+        <v>17.01828118450424</v>
       </c>
       <c r="I47" t="n">
-        <v>61.00399934266526</v>
+        <v>53.89785577945819</v>
       </c>
       <c r="J47" t="n">
-        <v>25.90933183830862</v>
+        <v>26.55932112184005</v>
       </c>
       <c r="K47" t="n">
-        <v>0.6965404128151647</v>
+        <v>0.5122357292179918</v>
       </c>
       <c r="L47" t="n">
-        <v>186.3324815388961</v>
+        <v>45.16994268429265</v>
       </c>
       <c r="M47" t="n">
-        <v>176.8514671638395</v>
+        <v>44.07865702561099</v>
       </c>
       <c r="N47" t="n">
-        <v>134.8966729737741</v>
+        <v>38.99714510207828</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.04224641687515485</v>
+        <v>-0.09362646135646041</v>
       </c>
       <c r="P47" t="n">
-        <v>82.33082623823213</v>
+        <v>57.97411596023506</v>
       </c>
       <c r="Q47" t="n">
-        <v>-17.66917376176787</v>
+        <v>-42.02588403976493</v>
       </c>
       <c r="R47" t="n">
-        <v>31.07253660631657</v>
+        <v>-4.14939351047682</v>
       </c>
       <c r="S47" t="n">
-        <v>-0.4048773210429069</v>
+        <v>-1.591401459068376</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Bear Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W47" t="n">
-        <v>67.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="X47" t="n">
-        <v>66.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -15594,73 +15584,73 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); RSI in forza (61) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Bear Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>52.0099983215332</v>
+        <v>199.25</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7945733711944403</v>
+        <v>5.989677205071087</v>
       </c>
       <c r="F48" t="n">
-        <v>1.681323108503108</v>
+        <v>10.90392738426855</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9706853354545242</v>
+        <v>0.2969879829933575</v>
       </c>
       <c r="H48" t="n">
-        <v>25.90171046365608</v>
+        <v>59.11994733877801</v>
       </c>
       <c r="I48" t="n">
-        <v>58.74856606186125</v>
+        <v>61.00399934266526</v>
       </c>
       <c r="J48" t="n">
-        <v>18.48568976186834</v>
+        <v>25.90933183830862</v>
       </c>
       <c r="K48" t="n">
-        <v>0.665200043353758</v>
+        <v>0.6965404128151647</v>
       </c>
       <c r="L48" t="n">
-        <v>50.69319614821309</v>
+        <v>186.3324815388961</v>
       </c>
       <c r="M48" t="n">
-        <v>48.63919074658908</v>
+        <v>176.8514671638395</v>
       </c>
       <c r="N48" t="n">
-        <v>44.16581083382468</v>
+        <v>134.8966729737741</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.1124608706984098</v>
+        <v>-0.04224641687515485</v>
       </c>
       <c r="P48" t="n">
-        <v>70.58817944949283</v>
+        <v>82.33082623823213</v>
       </c>
       <c r="Q48" t="n">
-        <v>-29.41182055050717</v>
+        <v>-17.66917376176787</v>
       </c>
       <c r="R48" t="n">
-        <v>14.35640206828334</v>
+        <v>31.07253660631657</v>
       </c>
       <c r="S48" t="n">
-        <v>-2.438572534738537</v>
+        <v>-0.4048773210429069</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -15668,16 +15658,12 @@
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="n">
-        <v>67.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="X48" t="n">
-        <v>78.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -15686,90 +15672,90 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); RSI in forza (61) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UnitedHealth</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>425.3599853515625</v>
+        <v>52.0099983215332</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.5912802847137577</v>
+        <v>0.7945733711944403</v>
       </c>
       <c r="F49" t="n">
-        <v>11.84559650868184</v>
+        <v>1.681323108503108</v>
       </c>
       <c r="G49" t="n">
-        <v>53.75383869002424</v>
+        <v>0.9706853354545242</v>
       </c>
       <c r="H49" t="n">
-        <v>1.605190729024852</v>
+        <v>25.90171046365608</v>
       </c>
       <c r="I49" t="n">
-        <v>68.45871892016839</v>
+        <v>58.74856606186125</v>
       </c>
       <c r="J49" t="n">
-        <v>46.29858167286974</v>
+        <v>18.48568976186834</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8448360151512742</v>
+        <v>0.665200043353758</v>
       </c>
       <c r="L49" t="n">
-        <v>367.7965184471579</v>
+        <v>50.69319614821309</v>
       </c>
       <c r="M49" t="n">
-        <v>358.869380319478</v>
+        <v>48.63919074658908</v>
       </c>
       <c r="N49" t="n">
-        <v>413.4087611238132</v>
+        <v>44.16581083382468</v>
       </c>
       <c r="O49" t="n">
-        <v>10.24943012717425</v>
+        <v>-0.1124608706984098</v>
       </c>
       <c r="P49" t="n">
-        <v>97.21084141674864</v>
+        <v>70.58817944949283</v>
       </c>
       <c r="Q49" t="n">
-        <v>-2.789158583251366</v>
+        <v>-29.41182055050717</v>
       </c>
       <c r="R49" t="n">
-        <v>102.1131625874269</v>
+        <v>14.35640206828334</v>
       </c>
       <c r="S49" t="n">
-        <v>45.07997605974654</v>
+        <v>-2.438572534738537</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Doji, Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W49" t="n">
-        <v>67.40000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="X49" t="n">
-        <v>73.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -15778,90 +15764,90 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 46); RSI in forza (68) — momentum positivo; doji — indecisione del mercato; vicino alla resistenza dei 20g (430.20); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>UnitedHealth</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>161.3090057373047</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.3065337665262291</v>
+        <v>-0.5912802847137577</v>
       </c>
       <c r="F50" t="n">
-        <v>1.280216870814965</v>
+        <v>11.84559650868184</v>
       </c>
       <c r="G50" t="n">
-        <v>2.886142242780432</v>
+        <v>53.75383869002424</v>
       </c>
       <c r="H50" t="n">
-        <v>12.89903220067072</v>
+        <v>1.605190729024852</v>
       </c>
       <c r="I50" t="n">
-        <v>61.59488493731183</v>
+        <v>68.45871892016839</v>
       </c>
       <c r="J50" t="n">
-        <v>9.945181945279062</v>
+        <v>46.29858167286974</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8421170758851266</v>
+        <v>0.8448360151512742</v>
       </c>
       <c r="L50" t="n">
-        <v>158.8833708781799</v>
+        <v>367.7965184471579</v>
       </c>
       <c r="M50" t="n">
-        <v>155.9276319909991</v>
+        <v>358.869380319478</v>
       </c>
       <c r="N50" t="n">
-        <v>146.2621156473546</v>
+        <v>413.4087611238132</v>
       </c>
       <c r="O50" t="n">
-        <v>0.0887656293661947</v>
+        <v>10.24943012717425</v>
       </c>
       <c r="P50" t="n">
-        <v>80.39552560435685</v>
+        <v>97.21084141674864</v>
       </c>
       <c r="Q50" t="n">
-        <v>-19.60447439564314</v>
+        <v>-2.789158583251366</v>
       </c>
       <c r="R50" t="n">
-        <v>97.50717917701537</v>
+        <v>102.1131625874269</v>
       </c>
       <c r="S50" t="n">
-        <v>5.554214826010306</v>
+        <v>45.07997605974654</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Outside Bar</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Doji, Bearish Harami</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="X50" t="n">
-        <v>65.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -15870,7 +15856,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (62) — momentum positivo; vicino alla resistenza dei 20g (162.84)</t>
+          <t>trend molto direzionale (ADX 46); RSI in forza (68) — momentum positivo; doji — indecisione del mercato; vicino alla resistenza dei 20g (430.20); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -17057,87 +17043,87 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>194.8300018310547</v>
+        <v>100.8570022583008</v>
       </c>
       <c r="E64" t="n">
-        <v>1.194620613068387</v>
+        <v>-0.4962493577564286</v>
       </c>
       <c r="F64" t="n">
-        <v>-7.724731271072161</v>
+        <v>1.968454680117726</v>
       </c>
       <c r="G64" t="n">
-        <v>5.080631024695026</v>
+        <v>3.305341693810027</v>
       </c>
       <c r="H64" t="n">
-        <v>75.50670937917926</v>
+        <v>1.394391294436792</v>
       </c>
       <c r="I64" t="n">
-        <v>49.94825209714127</v>
+        <v>58.81973807094153</v>
       </c>
       <c r="J64" t="n">
-        <v>38.48623249475396</v>
+        <v>23.92436318009095</v>
       </c>
       <c r="K64" t="n">
-        <v>0.4859789103732932</v>
+        <v>0.8465928985168145</v>
       </c>
       <c r="L64" t="n">
-        <v>198.0818760593166</v>
+        <v>99.5022147256967</v>
       </c>
       <c r="M64" t="n">
-        <v>183.8457140851389</v>
+        <v>99.50448028849524</v>
       </c>
       <c r="N64" t="n">
-        <v>121.5173501707522</v>
+        <v>100.8406723189328</v>
       </c>
       <c r="O64" t="n">
-        <v>-1.341852259766574</v>
+        <v>0.271249380622652</v>
       </c>
       <c r="P64" t="n">
-        <v>42.28587547289163</v>
+        <v>77.38610354372992</v>
       </c>
       <c r="Q64" t="n">
-        <v>-57.71412452710837</v>
+        <v>-22.61389645627009</v>
       </c>
       <c r="R64" t="n">
-        <v>-8.241820378172243</v>
+        <v>132.9752759060356</v>
       </c>
       <c r="S64" t="n">
-        <v>6.575135076301453</v>
+        <v>4.105083730008574</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>Doji, Bullish Harami</t>
+          <t>Dark Cloud Cover</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W64" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="X64" t="n">
-        <v>66.7</v>
+        <v>64.7</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -17146,19 +17132,19 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 38); pattern: Bull Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 24); pattern: Double Bottom; segnale candlestick: Dark Cloud Cover; vicino alla resistenza dei 20g (101.80); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -17167,65 +17153,73 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>360.4500122070312</v>
+        <v>194.8300018310547</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.251979876222464</v>
+        <v>1.194620613068387</v>
       </c>
       <c r="F65" t="n">
-        <v>-19.32089865686997</v>
+        <v>-7.724731271072161</v>
       </c>
       <c r="G65" t="n">
-        <v>8.269253174613578</v>
+        <v>5.080631024695026</v>
       </c>
       <c r="H65" t="n">
-        <v>87.43175954604645</v>
+        <v>75.50670937917926</v>
       </c>
       <c r="I65" t="n">
-        <v>47.88141079622496</v>
+        <v>49.94825209714127</v>
       </c>
       <c r="J65" t="n">
-        <v>46.91427130167305</v>
+        <v>38.48623249475396</v>
       </c>
       <c r="K65" t="n">
-        <v>0.4300278298639281</v>
+        <v>0.4859789103732932</v>
       </c>
       <c r="L65" t="n">
-        <v>378.9388410521896</v>
+        <v>198.0818760593166</v>
       </c>
       <c r="M65" t="n">
-        <v>343.8291887564545</v>
+        <v>183.8457140851389</v>
       </c>
       <c r="N65" t="n">
-        <v>218.6351045798274</v>
+        <v>121.5173501707522</v>
       </c>
       <c r="O65" t="n">
-        <v>-4.823214049488474</v>
+        <v>-1.341852259766574</v>
       </c>
       <c r="P65" t="n">
-        <v>34.37866651108219</v>
+        <v>42.28587547289163</v>
       </c>
       <c r="Q65" t="n">
-        <v>-65.62133348891781</v>
+        <v>-57.71412452710837</v>
       </c>
       <c r="R65" t="n">
-        <v>-13.66309208060741</v>
+        <v>-8.241820378172243</v>
       </c>
       <c r="S65" t="n">
-        <v>10.84970855934644</v>
+        <v>6.575135076301453</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Doji, Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W65" t="n">
         <v>57.8</v>
       </c>
       <c r="X65" t="n">
-        <v>59.3</v>
+        <v>66.7</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -17234,90 +17228,86 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47)</t>
+          <t>trend molto direzionale (ADX 38); pattern: Bull Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SRG</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Snam</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6.300000190734863</v>
+        <v>360.4500122070312</v>
       </c>
       <c r="E66" t="n">
-        <v>0.1908410260734739</v>
+        <v>-1.251979876222464</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5426172653410832</v>
+        <v>-19.32089865686997</v>
       </c>
       <c r="G66" t="n">
-        <v>5.563007023999988</v>
+        <v>8.269253174613578</v>
       </c>
       <c r="H66" t="n">
-        <v>27.50455798806952</v>
+        <v>87.43175954604645</v>
       </c>
       <c r="I66" t="n">
-        <v>51.96496670911558</v>
+        <v>47.88141079622496</v>
       </c>
       <c r="J66" t="n">
-        <v>35.58602379266117</v>
+        <v>46.91427130167305</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2510335614273984</v>
+        <v>0.4300278298639281</v>
       </c>
       <c r="L66" t="n">
-        <v>6.318476631907341</v>
+        <v>378.9388410521896</v>
       </c>
       <c r="M66" t="n">
-        <v>5.942969085182042</v>
+        <v>343.8291887564545</v>
       </c>
       <c r="N66" t="n">
-        <v>5.151783232160574</v>
+        <v>218.6351045798274</v>
       </c>
       <c r="O66" t="n">
-        <v>-0.0649036570632468</v>
+        <v>-4.823214049488474</v>
       </c>
       <c r="P66" t="n">
-        <v>23.18064478399987</v>
+        <v>34.37866651108219</v>
       </c>
       <c r="Q66" t="n">
-        <v>-76.81935521600013</v>
+        <v>-65.62133348891781</v>
       </c>
       <c r="R66" t="n">
-        <v>-31.36153191080844</v>
+        <v>-13.66309208060741</v>
       </c>
       <c r="S66" t="n">
-        <v>0.3824118508469088</v>
+        <v>10.84970855934644</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="n">
-        <v>56.7</v>
+        <v>57.8</v>
       </c>
       <c r="X66" t="n">
-        <v>57.8</v>
+        <v>59.3</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -17326,94 +17316,90 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 47)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COTTON</t>
+          <t>SRG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Snam</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>72.56999969482422</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="E67" t="n">
-        <v>1.269879969593157</v>
+        <v>0.1908410260734739</v>
       </c>
       <c r="F67" t="n">
-        <v>-4.701249848088384</v>
+        <v>0.5426172653410832</v>
       </c>
       <c r="G67" t="n">
-        <v>18.85030799650118</v>
+        <v>5.563007023999988</v>
       </c>
       <c r="H67" t="n">
-        <v>8.556471729640268</v>
+        <v>27.50455798806952</v>
       </c>
       <c r="I67" t="n">
-        <v>51.43365594497557</v>
+        <v>51.96496670911558</v>
       </c>
       <c r="J67" t="n">
-        <v>53.77327295899294</v>
+        <v>35.58602379266117</v>
       </c>
       <c r="K67" t="n">
-        <v>0.4852848444333196</v>
+        <v>0.2510335614273984</v>
       </c>
       <c r="L67" t="n">
-        <v>72.89879919171818</v>
+        <v>6.318476631907341</v>
       </c>
       <c r="M67" t="n">
-        <v>69.89465859733369</v>
+        <v>5.942969085182042</v>
       </c>
       <c r="N67" t="n">
-        <v>74.61587121019546</v>
+        <v>5.151783232160574</v>
       </c>
       <c r="O67" t="n">
-        <v>-0.669309784827774</v>
+        <v>-0.0649036570632468</v>
       </c>
       <c r="P67" t="n">
-        <v>19.57594408119964</v>
+        <v>23.18064478399987</v>
       </c>
       <c r="Q67" t="n">
-        <v>-80.42405591880036</v>
+        <v>-76.81935521600013</v>
       </c>
       <c r="R67" t="n">
-        <v>-3.302390894746103</v>
+        <v>-31.36153191080844</v>
       </c>
       <c r="S67" t="n">
-        <v>16.84108675202516</v>
+        <v>0.3824118508469088</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="X67" t="n">
-        <v>68.90000000000001</v>
+        <v>57.8</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -17422,90 +17408,94 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 54); segnale candlestick: Bullish Harami; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 36); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>COTTON</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>53.22000122070312</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.151558191173152</v>
+        <v>1.269879969593157</v>
       </c>
       <c r="F68" t="n">
-        <v>-5.453898818426516</v>
+        <v>-4.701249848088384</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.05633573576877549</v>
+        <v>18.85030799650118</v>
       </c>
       <c r="H68" t="n">
-        <v>29.19043965277597</v>
+        <v>8.556471729640268</v>
       </c>
       <c r="I68" t="n">
-        <v>47.23245846132702</v>
+        <v>51.43365594497557</v>
       </c>
       <c r="J68" t="n">
-        <v>39.32818141035381</v>
+        <v>53.77327295899294</v>
       </c>
       <c r="K68" t="n">
-        <v>0.09312241121170396</v>
+        <v>0.4852848444333196</v>
       </c>
       <c r="L68" t="n">
-        <v>55.24565088251006</v>
+        <v>72.89879919171818</v>
       </c>
       <c r="M68" t="n">
-        <v>51.75728008136726</v>
+        <v>69.89465859733369</v>
       </c>
       <c r="N68" t="n">
-        <v>44.74849008361287</v>
+        <v>74.61587121019546</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.9826183617024498</v>
+        <v>-0.669309784827774</v>
       </c>
       <c r="P68" t="n">
-        <v>5.535076387200212</v>
+        <v>19.57594408119964</v>
       </c>
       <c r="Q68" t="n">
-        <v>-94.46492361279979</v>
+        <v>-80.42405591880036</v>
       </c>
       <c r="R68" t="n">
-        <v>-46.6246906824361</v>
+        <v>-3.302390894746103</v>
       </c>
       <c r="S68" t="n">
-        <v>-2.079111840188952</v>
+        <v>16.84108675202516</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>Bearish Engulfing, Dark Cloud Cover</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr"/>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W68" t="n">
-        <v>55.7</v>
+        <v>56.3</v>
       </c>
       <c r="X68" t="n">
-        <v>73.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -17514,73 +17504,73 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 39); candela di inversione bearish (engulfing); sul supporto dei 20g (52.62); in zona Fib Fib 38.2 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 54); segnale candlestick: Bullish Harami; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>393.4500122070312</v>
+        <v>53.22000122070312</v>
       </c>
       <c r="E69" t="n">
-        <v>3.61855654608938</v>
+        <v>-1.151558191173152</v>
       </c>
       <c r="F69" t="n">
-        <v>-9.71568771832596</v>
+        <v>-5.453898818426516</v>
       </c>
       <c r="G69" t="n">
-        <v>-4.295680906273591</v>
+        <v>-0.05633573576877549</v>
       </c>
       <c r="H69" t="n">
-        <v>38.07685395751766</v>
+        <v>29.19043965277597</v>
       </c>
       <c r="I69" t="n">
-        <v>48.26820570375626</v>
+        <v>47.23245846132702</v>
       </c>
       <c r="J69" t="n">
-        <v>22.37331337168784</v>
+        <v>39.32818141035381</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4875112880370385</v>
+        <v>0.09312241121170396</v>
       </c>
       <c r="L69" t="n">
-        <v>401.2855010012914</v>
+        <v>55.24565088251006</v>
       </c>
       <c r="M69" t="n">
-        <v>390.5369353308272</v>
+        <v>51.75728008136726</v>
       </c>
       <c r="N69" t="n">
-        <v>305.7547544525796</v>
+        <v>44.74849008361287</v>
       </c>
       <c r="O69" t="n">
-        <v>-1.190075207516891</v>
+        <v>-0.9826183617024498</v>
       </c>
       <c r="P69" t="n">
-        <v>48.39016890543676</v>
+        <v>5.535076387200212</v>
       </c>
       <c r="Q69" t="n">
-        <v>-51.60983109456324</v>
+        <v>-94.46492361279979</v>
       </c>
       <c r="R69" t="n">
-        <v>13.8179302691822</v>
+        <v>-46.6246906824361</v>
       </c>
       <c r="S69" t="n">
-        <v>-5.746931318050274</v>
+        <v>-2.079111840188952</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -17589,19 +17579,15 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>Shooting Star, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Bull Flag / Consolidation</t>
-        </is>
-      </c>
+          <t>Bearish Engulfing, Dark Cloud Cover</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="X69" t="n">
-        <v>61.7</v>
+        <v>73.7</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -17610,86 +17596,94 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); pattern: Bull Flag / Consolidation; shooting star — rifiuto di resistenza</t>
+          <t>trend molto direzionale (ADX 39); candela di inversione bearish (engulfing); sul supporto dei 20g (52.62); in zona Fib Fib 38.2 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>105.129997253418</v>
+        <v>393.4500122070312</v>
       </c>
       <c r="E70" t="n">
-        <v>-2.666424243914023</v>
+        <v>3.61855654608938</v>
       </c>
       <c r="F70" t="n">
-        <v>-16.03705932264064</v>
+        <v>-9.71568771832596</v>
       </c>
       <c r="G70" t="n">
-        <v>-14.17959407884247</v>
+        <v>-4.295680906273591</v>
       </c>
       <c r="H70" t="n">
-        <v>85.93915024954759</v>
+        <v>38.07685395751766</v>
       </c>
       <c r="I70" t="n">
-        <v>43.78949383832679</v>
+        <v>48.26820570375626</v>
       </c>
       <c r="J70" t="n">
-        <v>12.76901470666153</v>
+        <v>22.37331337168784</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1199911379863449</v>
+        <v>0.4875112880370385</v>
       </c>
       <c r="L70" t="n">
-        <v>113.6881686561895</v>
+        <v>401.2855010012914</v>
       </c>
       <c r="M70" t="n">
-        <v>103.7848022998892</v>
+        <v>390.5369353308272</v>
       </c>
       <c r="N70" t="n">
-        <v>74.53215347792992</v>
+        <v>305.7547544525796</v>
       </c>
       <c r="O70" t="n">
-        <v>-2.024940685476684</v>
+        <v>-1.190075207516891</v>
       </c>
       <c r="P70" t="n">
-        <v>8.819655121349898</v>
+        <v>48.39016890543676</v>
       </c>
       <c r="Q70" t="n">
-        <v>-91.1803448786501</v>
+        <v>-51.60983109456324</v>
       </c>
       <c r="R70" t="n">
-        <v>-131.5793396402712</v>
+        <v>13.8179302691822</v>
       </c>
       <c r="S70" t="n">
-        <v>-10.77824355451175</v>
+        <v>-5.746931318050274</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Shooting Star, Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W70" t="n">
-        <v>53.6</v>
+        <v>55.3</v>
       </c>
       <c r="X70" t="n">
-        <v>72</v>
+        <v>61.7</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -17698,94 +17692,86 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 13); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend in sviluppo (ADX 22); pattern: Bull Flag / Consolidation; shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>100.8359985351562</v>
+        <v>105.129997253418</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5169712628650069</v>
+        <v>-2.666424243914023</v>
       </c>
       <c r="F71" t="n">
-        <v>1.947219494224606</v>
+        <v>-16.03705932264064</v>
       </c>
       <c r="G71" t="n">
-        <v>3.283828097850372</v>
+        <v>-14.17959407884247</v>
       </c>
       <c r="H71" t="n">
-        <v>1.373275658680506</v>
+        <v>85.93915024954759</v>
       </c>
       <c r="I71" t="n">
-        <v>58.68477137666871</v>
+        <v>43.78949383832679</v>
       </c>
       <c r="J71" t="n">
-        <v>23.92436318009095</v>
+        <v>12.76901470666153</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8425789791257983</v>
+        <v>0.1199911379863449</v>
       </c>
       <c r="L71" t="n">
-        <v>99.50021437111151</v>
+        <v>113.6881686561895</v>
       </c>
       <c r="M71" t="n">
-        <v>99.50365661307781</v>
+        <v>103.7848022998892</v>
       </c>
       <c r="N71" t="n">
-        <v>100.8404633266627</v>
+        <v>74.53215347792992</v>
       </c>
       <c r="O71" t="n">
-        <v>0.2699089720800943</v>
+        <v>-2.024940685476684</v>
       </c>
       <c r="P71" t="n">
-        <v>76.88241783775575</v>
+        <v>8.819655121349898</v>
       </c>
       <c r="Q71" t="n">
-        <v>-23.11758216224425</v>
+        <v>-91.1803448786501</v>
       </c>
       <c r="R71" t="n">
-        <v>132.5194296385843</v>
+        <v>-131.5793396402712</v>
       </c>
       <c r="S71" t="n">
-        <v>4.083403585768286</v>
+        <v>-10.77824355451175</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Dark Cloud Cover</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="n">
         <v>53.6</v>
       </c>
       <c r="X71" t="n">
-        <v>60.7</v>
+        <v>72</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -17794,7 +17780,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 24); pattern: Double Bottom; candela di inversione bearish (engulfing); vicino alla resistenza dei 20g (101.80); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 13); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -18279,52 +18265,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.33571982383728</v>
+        <v>1.33552360534668</v>
       </c>
       <c r="E77" t="n">
-        <v>1.283632461295592</v>
+        <v>1.268753801018629</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6491640437973123</v>
+        <v>-0.6637587744611317</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.210165182989231</v>
+        <v>-1.224677502061344</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2324121204249296</v>
+        <v>0.2176878853985764</v>
       </c>
       <c r="I77" t="n">
-        <v>48.4515869316653</v>
+        <v>48.37516140821143</v>
       </c>
       <c r="J77" t="n">
         <v>8.445603970678251</v>
       </c>
       <c r="K77" t="n">
-        <v>0.391400582674666</v>
+        <v>0.3871741041073808</v>
       </c>
       <c r="L77" t="n">
-        <v>1.339176807361605</v>
+        <v>1.33915811988631</v>
       </c>
       <c r="M77" t="n">
-        <v>1.335786392606921</v>
+        <v>1.335778697764153</v>
       </c>
       <c r="N77" t="n">
-        <v>1.306193892697297</v>
+        <v>1.306191940274505</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.00246849174350889</v>
+        <v>-0.002481013949176832</v>
       </c>
       <c r="P77" t="n">
-        <v>41.6019858103477</v>
+        <v>41.22084730378082</v>
       </c>
       <c r="Q77" t="n">
-        <v>-58.3980141896523</v>
+        <v>-58.77915269621918</v>
       </c>
       <c r="R77" t="n">
-        <v>-73.89507710680574</v>
+        <v>-74.36476467415059</v>
       </c>
       <c r="S77" t="n">
-        <v>-1.931450225232878</v>
+        <v>-1.945856586858108</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -20761,12 +20747,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -20775,69 +20761,69 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.117200016975403</v>
+        <v>62185.109375</v>
       </c>
       <c r="E104" t="n">
-        <v>6.646207018352013</v>
+        <v>4.456014223886573</v>
       </c>
       <c r="F104" t="n">
-        <v>-16.08334758545227</v>
+        <v>-15.48603767174195</v>
       </c>
       <c r="G104" t="n">
-        <v>-21.99331964878756</v>
+        <v>-11.49882392314333</v>
       </c>
       <c r="H104" t="n">
-        <v>-50.48392513259583</v>
+        <v>-33.6726435800817</v>
       </c>
       <c r="I104" t="n">
-        <v>33.2205229616178</v>
+        <v>36.51220069319579</v>
       </c>
       <c r="J104" t="n">
-        <v>26.18980210004506</v>
+        <v>26.69989001937627</v>
       </c>
       <c r="K104" t="n">
-        <v>0.09265803056821419</v>
+        <v>0.1930743704751001</v>
       </c>
       <c r="L104" t="n">
-        <v>1.365846446371829</v>
+        <v>71772.30535502026</v>
       </c>
       <c r="M104" t="n">
-        <v>1.67662795795684</v>
+        <v>80724.72043081961</v>
       </c>
       <c r="N104" t="n">
-        <v>1.402479745942501</v>
+        <v>68716.60459259992</v>
       </c>
       <c r="O104" t="n">
-        <v>0.005028036821610404</v>
+        <v>-430.3895383852268</v>
       </c>
       <c r="P104" t="n">
-        <v>19.98564488905721</v>
+        <v>17.71787593868276</v>
       </c>
       <c r="Q104" t="n">
-        <v>-80.01435511094279</v>
+        <v>-82.28212406131723</v>
       </c>
       <c r="R104" t="n">
-        <v>-51.95938517842638</v>
+        <v>-70.15854316776078</v>
       </c>
       <c r="S104" t="n">
-        <v>-24.25028069437779</v>
+        <v>-9.599145383791363</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="n">
-        <v>33.2</v>
+        <v>32.9</v>
       </c>
       <c r="X104" t="n">
-        <v>67.8</v>
+        <v>76</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20846,19 +20832,19 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); RSI scarico (33) — zona di interesse long</t>
+          <t>trend in sviluppo (ADX 27); RSI scarico (37) — zona di interesse long; segnale candlestick: Piercing Pattern</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -20867,52 +20853,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>62120.51171875</v>
+        <v>1.137699961662292</v>
       </c>
       <c r="E105" t="n">
-        <v>4.34750571167366</v>
+        <v>8.603100423045662</v>
       </c>
       <c r="F105" t="n">
-        <v>-15.57383045592576</v>
+        <v>-14.54352776208303</v>
       </c>
       <c r="G105" t="n">
-        <v>-11.59075860987772</v>
+        <v>-20.56194423873603</v>
       </c>
       <c r="H105" t="n">
-        <v>-33.74154418688368</v>
+        <v>-49.57533510353211</v>
       </c>
       <c r="I105" t="n">
-        <v>36.42983580903336</v>
+        <v>34.41627093345076</v>
       </c>
       <c r="J105" t="n">
-        <v>26.69989001937627</v>
+        <v>26.18980210004506</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1908785508887948</v>
+        <v>0.1276460089856344</v>
       </c>
       <c r="L105" t="n">
-        <v>71766.15319728217</v>
+        <v>1.367798822056294</v>
       </c>
       <c r="M105" t="n">
-        <v>80722.18718939803</v>
+        <v>1.677431877356326</v>
       </c>
       <c r="N105" t="n">
-        <v>68715.96182985116</v>
+        <v>1.402683725491625</v>
       </c>
       <c r="O105" t="n">
-        <v>-434.5120098952057</v>
+        <v>0.00633629539991909</v>
       </c>
       <c r="P105" t="n">
-        <v>17.45994386854121</v>
+        <v>23.79872954829073</v>
       </c>
       <c r="Q105" t="n">
-        <v>-82.5400561314588</v>
+        <v>-76.20127045170926</v>
       </c>
       <c r="R105" t="n">
-        <v>-70.30089724334702</v>
+        <v>-49.37638176788406</v>
       </c>
       <c r="S105" t="n">
-        <v>-9.6930534494022</v>
+        <v>-22.8603191546199</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -20921,15 +20907,19 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V105" t="inlineStr"/>
+          <t>Bullish Engulfing</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W105" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="X105" t="n">
-        <v>76</v>
+        <v>73.8</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -20938,7 +20928,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); RSI scarico (36) — zona di interesse long; segnale candlestick: Piercing Pattern</t>
+          <t>trend in sviluppo (ADX 26); RSI scarico (34) — zona di interesse long; candela di inversione bullish (engulfing); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -21151,52 +21141,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>81.75</v>
+        <v>82.19000244140625</v>
       </c>
       <c r="E108" t="n">
-        <v>14.63557263031541</v>
+        <v>15.25257485452753</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.6662369520060385</v>
+        <v>-0.131593548272857</v>
       </c>
       <c r="G108" t="n">
-        <v>-6.082095390104958</v>
+        <v>-5.576601722580632</v>
       </c>
       <c r="H108" t="n">
-        <v>-44.85511153947856</v>
+        <v>-44.5583055999837</v>
       </c>
       <c r="I108" t="n">
-        <v>42.45507953361696</v>
+        <v>42.73060598087816</v>
       </c>
       <c r="J108" t="n">
         <v>36.41395833640571</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4951649903148991</v>
+        <v>0.5099045572523577</v>
       </c>
       <c r="L108" t="n">
-        <v>87.26788034839817</v>
+        <v>87.3097853428178</v>
       </c>
       <c r="M108" t="n">
-        <v>113.5392155872294</v>
+        <v>113.5564705849316</v>
       </c>
       <c r="N108" t="n">
-        <v>113.8718739651252</v>
+        <v>113.8762520988705</v>
       </c>
       <c r="O108" t="n">
-        <v>2.137061366050109</v>
+        <v>2.165141293934727</v>
       </c>
       <c r="P108" t="n">
-        <v>56.36506486564495</v>
+        <v>57.52749463248983</v>
       </c>
       <c r="Q108" t="n">
-        <v>-43.63493513435505</v>
+        <v>-42.47250536751017</v>
       </c>
       <c r="R108" t="n">
-        <v>-11.91060161917096</v>
+        <v>-11.48866578273564</v>
       </c>
       <c r="S108" t="n">
-        <v>-4.947493360158828</v>
+        <v>-4.435892932228381</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21210,10 +21200,10 @@
         </is>
       </c>
       <c r="W108" t="n">
-        <v>30.2</v>
+        <v>30.4</v>
       </c>
       <c r="X108" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21325,66 +21315,66 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>44.09000015258789</v>
+        <v>7.941999912261963</v>
       </c>
       <c r="E110" t="n">
-        <v>8.196319392853724</v>
+        <v>9.394401763543069</v>
       </c>
       <c r="F110" t="n">
-        <v>-4.629027494783566</v>
+        <v>-12.98053653321117</v>
       </c>
       <c r="G110" t="n">
-        <v>-31.0231517277977</v>
+        <v>-10.08142867014775</v>
       </c>
       <c r="H110" t="n">
-        <v>-23.48142837574729</v>
+        <v>-45.5601584207865</v>
       </c>
       <c r="I110" t="n">
-        <v>39.94198131806849</v>
+        <v>38.82459066275896</v>
       </c>
       <c r="J110" t="n">
-        <v>51.10608873255303</v>
+        <v>33.87766288270218</v>
       </c>
       <c r="K110" t="n">
-        <v>0.3595371872151207</v>
+        <v>0.2315483507451034</v>
       </c>
       <c r="L110" t="n">
-        <v>48.15215053864459</v>
+        <v>9.23058057424179</v>
       </c>
       <c r="M110" t="n">
-        <v>56.47599583205686</v>
+        <v>11.66232766525144</v>
       </c>
       <c r="N110" t="n">
-        <v>79.55544040805256</v>
+        <v>13.18343420274407</v>
       </c>
       <c r="O110" t="n">
-        <v>0.3101615918623946</v>
+        <v>0.1081229332336178</v>
       </c>
       <c r="P110" t="n">
-        <v>31.19755882664457</v>
+        <v>23.99992533203909</v>
       </c>
       <c r="Q110" t="n">
-        <v>-68.80244117335543</v>
+        <v>-76.00007466796092</v>
       </c>
       <c r="R110" t="n">
-        <v>-39.01470175992414</v>
+        <v>-45.01541943496667</v>
       </c>
       <c r="S110" t="n">
-        <v>-30.15998826767608</v>
+        <v>-9.563690298235572</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -21393,15 +21383,19 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr"/>
+          <t>Bullish Engulfing</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W110" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="X110" t="n">
-        <v>73.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21410,73 +21404,73 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); segnale candlestick: Bullish Harami</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 34); candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7.875</v>
+        <v>44.09000015258789</v>
       </c>
       <c r="E111" t="n">
-        <v>8.47153404746679</v>
+        <v>8.196319392853724</v>
       </c>
       <c r="F111" t="n">
-        <v>-13.71464588624155</v>
+        <v>-4.629027494783566</v>
       </c>
       <c r="G111" t="n">
-        <v>-10.83999533551873</v>
+        <v>-31.0231517277977</v>
       </c>
       <c r="H111" t="n">
-        <v>-46.01942115682998</v>
+        <v>-23.48142837574729</v>
       </c>
       <c r="I111" t="n">
-        <v>38.38795682491407</v>
+        <v>39.94198131806849</v>
       </c>
       <c r="J111" t="n">
-        <v>33.87766288270218</v>
+        <v>51.10608873255303</v>
       </c>
       <c r="K111" t="n">
-        <v>0.2125463296730772</v>
+        <v>0.3595371872151207</v>
       </c>
       <c r="L111" t="n">
-        <v>9.224199630216841</v>
+        <v>48.15215053864459</v>
       </c>
       <c r="M111" t="n">
-        <v>11.65970021771175</v>
+        <v>56.47599583205686</v>
       </c>
       <c r="N111" t="n">
-        <v>13.18276753695042</v>
+        <v>79.55544040805256</v>
       </c>
       <c r="O111" t="n">
-        <v>0.1038471553570701</v>
+        <v>0.3101615918623946</v>
       </c>
       <c r="P111" t="n">
-        <v>22.25133857875759</v>
+        <v>31.19755882664457</v>
       </c>
       <c r="Q111" t="n">
-        <v>-77.74866142124242</v>
+        <v>-68.80244117335543</v>
       </c>
       <c r="R111" t="n">
-        <v>-46.13052473036034</v>
+        <v>-39.01470175992414</v>
       </c>
       <c r="S111" t="n">
-        <v>-10.32662468280523</v>
+        <v>-30.15998826767608</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -21485,19 +21479,15 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Bullish Engulfing</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="X111" t="n">
-        <v>74.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21506,7 +21496,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 34); candela di inversione bullish (engulfing)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); segnale candlestick: Bullish Harami</t>
         </is>
       </c>
     </row>
@@ -21527,52 +21517,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1734.300048828125</v>
+        <v>1744.18994140625</v>
       </c>
       <c r="E112" t="n">
-        <v>10.43956270324016</v>
+        <v>11.06934727382134</v>
       </c>
       <c r="F112" t="n">
-        <v>-13.4728286971775</v>
+        <v>-12.97940518038053</v>
       </c>
       <c r="G112" t="n">
-        <v>-16.96999137287474</v>
+        <v>-16.49651052010192</v>
       </c>
       <c r="H112" t="n">
-        <v>-3.266556139210131</v>
+        <v>-2.714931079208693</v>
       </c>
       <c r="I112" t="n">
-        <v>36.34313375751061</v>
+        <v>36.6743814927552</v>
       </c>
       <c r="J112" t="n">
         <v>28.69207376073257</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2040007903305371</v>
+        <v>0.2131361118332369</v>
       </c>
       <c r="L112" t="n">
-        <v>2079.420697865473</v>
+        <v>2080.362592396723</v>
       </c>
       <c r="M112" t="n">
-        <v>2493.447901975914</v>
+        <v>2493.835740900546</v>
       </c>
       <c r="N112" t="n">
-        <v>2504.470904221236</v>
+        <v>2504.569311112561</v>
       </c>
       <c r="O112" t="n">
-        <v>-11.49461652623654</v>
+        <v>-10.86346668649276</v>
       </c>
       <c r="P112" t="n">
-        <v>23.77122092641841</v>
+        <v>24.80326961912234</v>
       </c>
       <c r="Q112" t="n">
-        <v>-76.22877907358159</v>
+        <v>-75.19673038087765</v>
       </c>
       <c r="R112" t="n">
-        <v>-54.60061854968914</v>
+        <v>-54.13814587912968</v>
       </c>
       <c r="S112" t="n">
-        <v>-11.78727645353631</v>
+        <v>-11.28424102982871</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -21590,10 +21580,10 @@
         </is>
       </c>
       <c r="W112" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="X112" t="n">
-        <v>78.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -21602,7 +21592,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29); RSI scarico (36) — zona di interesse long; candela di inversione bullish (engulfing)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29); RSI scarico (37) — zona di interesse long; candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -21623,52 +21613,52 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.8830000162124634</v>
+        <v>0.8849999904632568</v>
       </c>
       <c r="E113" t="n">
-        <v>9.070785253474689</v>
+        <v>9.317828014534246</v>
       </c>
       <c r="F113" t="n">
-        <v>-25.56858010826767</v>
+        <v>-25.39999469433757</v>
       </c>
       <c r="G113" t="n">
-        <v>-33.96175310867324</v>
+        <v>-33.81217803401275</v>
       </c>
       <c r="H113" t="n">
-        <v>-78.44038307452972</v>
+        <v>-78.39155104970953</v>
       </c>
       <c r="I113" t="n">
-        <v>30.14708984739833</v>
+        <v>30.23537581413767</v>
       </c>
       <c r="J113" t="n">
         <v>30.74187880899755</v>
       </c>
       <c r="K113" t="n">
-        <v>0.08610486546936738</v>
+        <v>0.08813179730437604</v>
       </c>
       <c r="L113" t="n">
-        <v>1.273624838772885</v>
+        <v>1.273815312511056</v>
       </c>
       <c r="M113" t="n">
-        <v>2.132226246514982</v>
+        <v>2.132304676877758</v>
       </c>
       <c r="N113" t="n">
-        <v>5.379993914878174</v>
+        <v>5.380013815119476</v>
       </c>
       <c r="O113" t="n">
-        <v>0.03069584243628987</v>
+        <v>0.0308234761206711</v>
       </c>
       <c r="P113" t="n">
-        <v>13.27275389797066</v>
+        <v>13.58813315294475</v>
       </c>
       <c r="Q113" t="n">
-        <v>-86.72724610202934</v>
+        <v>-86.41186684705525</v>
       </c>
       <c r="R113" t="n">
-        <v>-61.68186964988612</v>
+        <v>-61.51845920248106</v>
       </c>
       <c r="S113" t="n">
-        <v>-34.91977457559837</v>
+        <v>-34.77236939700853</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -21895,52 +21885,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.860000133514404</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="E116" t="n">
-        <v>6.476077217761445</v>
+        <v>7.2521374647327</v>
       </c>
       <c r="F116" t="n">
-        <v>-23.43680615840758</v>
+        <v>-22.87876859096326</v>
       </c>
       <c r="G116" t="n">
-        <v>-24.52820102446549</v>
+        <v>-23.97811818442498</v>
       </c>
       <c r="H116" t="n">
-        <v>-68.47425060713492</v>
+        <v>-68.24447241189071</v>
       </c>
       <c r="I116" t="n">
-        <v>34.19856920554345</v>
+        <v>34.5078055763031</v>
       </c>
       <c r="J116" t="n">
         <v>39.9463597661663</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1553246770848366</v>
+        <v>0.1641669434128665</v>
       </c>
       <c r="L116" t="n">
-        <v>8.915291592237082</v>
+        <v>8.920053469751149</v>
       </c>
       <c r="M116" t="n">
-        <v>13.31501734908934</v>
+        <v>13.31697812218337</v>
       </c>
       <c r="N116" t="n">
-        <v>21.5249256082565</v>
+        <v>21.52542311784752</v>
       </c>
       <c r="O116" t="n">
-        <v>0.1229191665423857</v>
+        <v>0.1261100314748882</v>
       </c>
       <c r="P116" t="n">
-        <v>24.39724972794592</v>
+        <v>25.44304846587029</v>
       </c>
       <c r="Q116" t="n">
-        <v>-75.60275027205408</v>
+        <v>-74.55695153412971</v>
       </c>
       <c r="R116" t="n">
-        <v>-57.50386578650181</v>
+        <v>-57.04378685423205</v>
       </c>
       <c r="S116" t="n">
-        <v>-26.12484222569351</v>
+        <v>-25.58639664537676</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -21962,7 +21952,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 40); RSI scarico (34) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 40); RSI scarico (35) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -21983,52 +21973,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1752000004053116</v>
+        <v>0.1821999996900558</v>
       </c>
       <c r="E117" t="n">
-        <v>21.94698045307024</v>
+        <v>26.81929080679977</v>
       </c>
       <c r="F117" t="n">
-        <v>-25.53774600545427</v>
+        <v>-22.56265625947009</v>
       </c>
       <c r="G117" t="n">
-        <v>-35.1742527805802</v>
+        <v>-32.5841832422288</v>
       </c>
       <c r="H117" t="n">
-        <v>-75.11275329803608</v>
+        <v>-74.11839993781932</v>
       </c>
       <c r="I117" t="n">
-        <v>34.19053376107006</v>
+        <v>35.46758846501636</v>
       </c>
       <c r="J117" t="n">
-        <v>37.32092758570399</v>
+        <v>37.03940095404671</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1665104025145221</v>
+        <v>0.2029452460801919</v>
       </c>
       <c r="L117" t="n">
-        <v>0.2431498516647076</v>
+        <v>0.2438165182632546</v>
       </c>
       <c r="M117" t="n">
-        <v>0.3772067024198456</v>
+        <v>0.3774812121957179</v>
       </c>
       <c r="N117" t="n">
-        <v>0.5219027479884625</v>
+        <v>0.521972399722639</v>
       </c>
       <c r="O117" t="n">
-        <v>0.004129276761449738</v>
+        <v>0.004576000362527408</v>
       </c>
       <c r="P117" t="n">
-        <v>24.41658743115481</v>
+        <v>29.09857894348664</v>
       </c>
       <c r="Q117" t="n">
-        <v>-75.58341256884519</v>
+        <v>-70.90142105651336</v>
       </c>
       <c r="R117" t="n">
-        <v>-58.54224891975711</v>
+        <v>-55.27942496097625</v>
       </c>
       <c r="S117" t="n">
-        <v>-37.82383504629524</v>
+        <v>-35.339627802019</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -22054,7 +22044,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long; candela di inversione bullish (engulfing)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (35) — zona di interesse long; candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -26579,79 +26569,87 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CAC 40</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8508.0703125</v>
+        <v>162.5390014648438</v>
       </c>
       <c r="E49" t="n">
-        <v>1.23846024593508</v>
+        <v>0.3804260658856196</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.8470085656848148</v>
+        <v>4.285930367741542</v>
       </c>
       <c r="G49" t="n">
-        <v>15.75022994563811</v>
+        <v>6.093187536683131</v>
       </c>
       <c r="H49" t="n">
-        <v>31.96596980688293</v>
+        <v>47.88776410497768</v>
       </c>
       <c r="I49" t="n">
-        <v>61.02375772956118</v>
+        <v>63.65245627563166</v>
       </c>
       <c r="J49" t="n">
-        <v>20.25340740770403</v>
+        <v>27.3767733214772</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9190424072220069</v>
+        <v>0.8767279602492908</v>
       </c>
       <c r="L49" t="n">
-        <v>8017.549061549589</v>
+        <v>154.6315885454979</v>
       </c>
       <c r="M49" t="n">
-        <v>7516.814290505398</v>
+        <v>146.0859737153522</v>
       </c>
       <c r="N49" t="n">
-        <v>6414.561488370104</v>
+        <v>131.9592172792647</v>
       </c>
       <c r="O49" t="n">
-        <v>20.4095634821403</v>
+        <v>0.7122027117553245</v>
       </c>
       <c r="P49" t="n">
-        <v>88.2001035003296</v>
+        <v>98.54505877621682</v>
       </c>
       <c r="Q49" t="n">
-        <v>-11.79989649967039</v>
+        <v>-1.454941223783176</v>
       </c>
       <c r="R49" t="n">
-        <v>116.1129330983738</v>
+        <v>122.5933705657518</v>
       </c>
       <c r="S49" t="n">
-        <v>17.59421036132602</v>
+        <v>7.517830973584338</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W49" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
       <c r="X49" t="n">
-        <v>71.8</v>
+        <v>74.3</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -26660,73 +26658,73 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); RSI in forza (61) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (64) — momentum positivo; pattern: Double Top; doji — indecisione del mercato; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>CAC 40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>334.4700012207031</v>
+        <v>8508.0703125</v>
       </c>
       <c r="E50" t="n">
-        <v>2.181289506411033</v>
+        <v>1.23846024593508</v>
       </c>
       <c r="F50" t="n">
-        <v>11.37862631259636</v>
+        <v>-0.8470085656848148</v>
       </c>
       <c r="G50" t="n">
-        <v>50.71647619881227</v>
+        <v>15.75022994563811</v>
       </c>
       <c r="H50" t="n">
-        <v>103.647095734312</v>
+        <v>31.96596980688293</v>
       </c>
       <c r="I50" t="n">
-        <v>69.45571405011987</v>
+        <v>61.02375772956118</v>
       </c>
       <c r="J50" t="n">
-        <v>42.19688223662929</v>
+        <v>20.25340740770403</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8674561455249195</v>
+        <v>0.9190424072220069</v>
       </c>
       <c r="L50" t="n">
-        <v>288.7435547467752</v>
+        <v>8017.549061549589</v>
       </c>
       <c r="M50" t="n">
-        <v>235.7457515951549</v>
+        <v>7516.814290505398</v>
       </c>
       <c r="N50" t="n">
-        <v>163.1935900089675</v>
+        <v>6414.561488370104</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.406551709366589</v>
+        <v>20.4095634821403</v>
       </c>
       <c r="P50" t="n">
-        <v>89.19893023317276</v>
+        <v>88.2001035003296</v>
       </c>
       <c r="Q50" t="n">
-        <v>-10.80106976682724</v>
+        <v>-11.79989649967039</v>
       </c>
       <c r="R50" t="n">
-        <v>56.90722939838383</v>
+        <v>116.1129330983738</v>
       </c>
       <c r="S50" t="n">
-        <v>33.93801040594171</v>
+        <v>17.59421036132602</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -26734,16 +26732,12 @@
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="n">
-        <v>75.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="X50" t="n">
-        <v>68.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -26752,73 +26746,73 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 42); RSI in forza (69) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); RSI in forza (61) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>161.3090057373047</v>
+        <v>334.4700012207031</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.3791915894270748</v>
+        <v>2.181289506411033</v>
       </c>
       <c r="F51" t="n">
-        <v>3.496758245120235</v>
+        <v>11.37862631259636</v>
       </c>
       <c r="G51" t="n">
-        <v>5.290339197422567</v>
+        <v>50.71647619881227</v>
       </c>
       <c r="H51" t="n">
-        <v>46.76863997867515</v>
+        <v>103.647095734312</v>
       </c>
       <c r="I51" t="n">
-        <v>62.07790566900657</v>
+        <v>69.45571405011987</v>
       </c>
       <c r="J51" t="n">
-        <v>27.3767733214772</v>
+        <v>42.19688223662929</v>
       </c>
       <c r="K51" t="n">
-        <v>0.834262985634021</v>
+        <v>0.8674561455249195</v>
       </c>
       <c r="L51" t="n">
-        <v>154.5144460952561</v>
+        <v>288.7435547467752</v>
       </c>
       <c r="M51" t="n">
-        <v>146.037738588782</v>
+        <v>235.7457515951549</v>
       </c>
       <c r="N51" t="n">
-        <v>131.9413912542279</v>
+        <v>163.1935900089675</v>
       </c>
       <c r="O51" t="n">
-        <v>0.633707257918084</v>
+        <v>-1.406551709366589</v>
       </c>
       <c r="P51" t="n">
-        <v>92.51950610934784</v>
+        <v>89.19893023317276</v>
       </c>
       <c r="Q51" t="n">
-        <v>-7.480493890652167</v>
+        <v>-10.80106976682724</v>
       </c>
       <c r="R51" t="n">
-        <v>117.7277068360608</v>
+        <v>56.90722939838383</v>
       </c>
       <c r="S51" t="n">
-        <v>6.704201804339194</v>
+        <v>33.93801040594171</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -26828,14 +26822,14 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>74.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="X51" t="n">
-        <v>73.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -26844,7 +26838,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (62) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 42); RSI in forza (69) — momentum positivo</t>
         </is>
       </c>
     </row>
@@ -26931,7 +26925,7 @@
         <v>74.8</v>
       </c>
       <c r="X52" t="n">
-        <v>75.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -29169,52 +29163,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.33571982383728</v>
+        <v>1.33552360534668</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7787287368721474</v>
+        <v>0.7639242474242192</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.9951092344026913</v>
+        <v>-1.009653145394662</v>
       </c>
       <c r="G77" t="n">
-        <v>3.068147522238185</v>
+        <v>3.053006715030793</v>
       </c>
       <c r="H77" t="n">
-        <v>-5.805036585693912</v>
+        <v>-5.818873913862211</v>
       </c>
       <c r="I77" t="n">
-        <v>52.84669771365773</v>
+        <v>52.81686770498219</v>
       </c>
       <c r="J77" t="n">
         <v>21.76605133944494</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5642498480439112</v>
+        <v>0.5630040009443538</v>
       </c>
       <c r="L77" t="n">
-        <v>1.326468604307592</v>
+        <v>1.326449916832296</v>
       </c>
       <c r="M77" t="n">
-        <v>1.307447174591824</v>
+        <v>1.307439479749056</v>
       </c>
       <c r="N77" t="n">
-        <v>1.332745557299034</v>
+        <v>1.332742713552793</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.002586746005575461</v>
+        <v>-0.002599268211243403</v>
       </c>
       <c r="P77" t="n">
-        <v>41.37457495981568</v>
+        <v>41.13960732139747</v>
       </c>
       <c r="Q77" t="n">
-        <v>-58.62542504018432</v>
+        <v>-58.86039267860253</v>
       </c>
       <c r="R77" t="n">
-        <v>16.95258365408186</v>
+        <v>16.83256107768281</v>
       </c>
       <c r="S77" t="n">
-        <v>5.201294770144127</v>
+        <v>5.185840601612202</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -29533,52 +29527,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>100.8359985351562</v>
+        <v>100.8570022583008</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.34984079228082</v>
+        <v>-0.329084074583641</v>
       </c>
       <c r="F81" t="n">
-        <v>3.304987096232614</v>
+        <v>3.326505099524479</v>
       </c>
       <c r="G81" t="n">
-        <v>-3.023662935444305</v>
+        <v>-3.003463163885889</v>
       </c>
       <c r="H81" t="n">
-        <v>12.00266566963932</v>
+        <v>12.02599536355171</v>
       </c>
       <c r="I81" t="n">
-        <v>50.48718623108566</v>
+        <v>50.53519597871013</v>
       </c>
       <c r="J81" t="n">
         <v>28.97798595210455</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5192793332233286</v>
+        <v>0.5206348224203413</v>
       </c>
       <c r="L81" t="n">
-        <v>100.2596236153622</v>
+        <v>100.2616239699474</v>
       </c>
       <c r="M81" t="n">
-        <v>100.8293707277074</v>
+        <v>100.8301944031248</v>
       </c>
       <c r="N81" t="n">
-        <v>99.52573066875539</v>
+        <v>99.52608367250572</v>
       </c>
       <c r="O81" t="n">
-        <v>0.222838218867911</v>
+        <v>0.2241786274104687</v>
       </c>
       <c r="P81" t="n">
-        <v>84.575927734375</v>
+        <v>84.9119873046875</v>
       </c>
       <c r="Q81" t="n">
-        <v>-15.424072265625</v>
+        <v>-15.0880126953125</v>
       </c>
       <c r="R81" t="n">
-        <v>7.461653926681876</v>
+        <v>7.592407415612625</v>
       </c>
       <c r="S81" t="n">
-        <v>-4.637790266396036</v>
+        <v>-4.617926710911957</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -30459,52 +30453,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.117200016975403</v>
+        <v>1.137699961662292</v>
       </c>
       <c r="E91" t="n">
-        <v>7.58549380540563</v>
+        <v>9.559622554609803</v>
       </c>
       <c r="F91" t="n">
-        <v>-18.88059015493246</v>
+        <v>-17.392098041086</v>
       </c>
       <c r="G91" t="n">
-        <v>119.3870507898388</v>
+        <v>123.412670497926</v>
       </c>
       <c r="H91" t="n">
-        <v>6.747285088257349</v>
+        <v>8.706033214406972</v>
       </c>
       <c r="I91" t="n">
-        <v>42.12121702573121</v>
+        <v>42.51769061805193</v>
       </c>
       <c r="J91" t="n">
         <v>38.94285314741881</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1399098967993894</v>
+        <v>0.1468364540557429</v>
       </c>
       <c r="L91" t="n">
-        <v>1.600550631375004</v>
+        <v>1.602503007059469</v>
       </c>
       <c r="M91" t="n">
-        <v>1.325589053401279</v>
+        <v>1.326392972800765</v>
       </c>
       <c r="N91" t="n">
-        <v>1.068587688079315</v>
+        <v>1.069001828376019</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.1913129211170445</v>
+        <v>-0.1900046625387358</v>
       </c>
       <c r="P91" t="n">
-        <v>4.06925890567292</v>
+        <v>4.845637591164653</v>
       </c>
       <c r="Q91" t="n">
-        <v>-95.93074109432708</v>
+        <v>-95.15436240883535</v>
       </c>
       <c r="R91" t="n">
-        <v>-66.67648163391191</v>
+        <v>-65.87569600819012</v>
       </c>
       <c r="S91" t="n">
-        <v>-42.5344402347026</v>
+        <v>-41.47998196519858</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -30522,10 +30516,10 @@
         </is>
       </c>
       <c r="W91" t="n">
-        <v>46.3</v>
+        <v>47</v>
       </c>
       <c r="X91" t="n">
-        <v>60.4</v>
+        <v>59.7</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -31027,52 +31021,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>62120.51171875</v>
+        <v>62185.109375</v>
       </c>
       <c r="E97" t="n">
-        <v>6.082175065845874</v>
+        <v>6.192487419842263</v>
       </c>
       <c r="F97" t="n">
-        <v>-7.27708801966539</v>
+        <v>-7.180667648537053</v>
       </c>
       <c r="G97" t="n">
-        <v>-11.52838305993272</v>
+        <v>-11.43638351033386</v>
       </c>
       <c r="H97" t="n">
-        <v>66.39635768217317</v>
+        <v>66.56938933335259</v>
       </c>
       <c r="I97" t="n">
-        <v>42.75396575274652</v>
+        <v>42.78939649109316</v>
       </c>
       <c r="J97" t="n">
         <v>30.22243585581547</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1251195392629449</v>
+        <v>0.1258709896313172</v>
       </c>
       <c r="L97" t="n">
-        <v>78115.7429806857</v>
+        <v>78121.89513842379</v>
       </c>
       <c r="M97" t="n">
-        <v>65924.57603590233</v>
+        <v>65927.10927732389</v>
       </c>
       <c r="N97" t="n">
-        <v>49822.43279285618</v>
+        <v>49823.73779601275</v>
       </c>
       <c r="O97" t="n">
-        <v>-6163.009006332389</v>
+        <v>-6158.88653482241</v>
       </c>
       <c r="P97" t="n">
-        <v>6.388205448775053</v>
+        <v>6.482577061209667</v>
       </c>
       <c r="Q97" t="n">
-        <v>-93.61179455122495</v>
+        <v>-93.51742293879033</v>
       </c>
       <c r="R97" t="n">
-        <v>-77.39484007158052</v>
+        <v>-77.34408143289298</v>
       </c>
       <c r="S97" t="n">
-        <v>-35.59240998263413</v>
+        <v>-35.52543404755701</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31299,52 +31293,52 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>81.75</v>
+        <v>82.19000244140625</v>
       </c>
       <c r="E100" t="n">
-        <v>11.18923025342209</v>
+        <v>11.78768325366171</v>
       </c>
       <c r="F100" t="n">
-        <v>-3.100982416058395</v>
+        <v>-2.579443525455316</v>
       </c>
       <c r="G100" t="n">
-        <v>-51.46351389009178</v>
+        <v>-51.20227630739282</v>
       </c>
       <c r="H100" t="n">
-        <v>149.1144170436271</v>
+        <v>150.4552237921127</v>
       </c>
       <c r="I100" t="n">
-        <v>42.23384254463648</v>
+        <v>42.3298994151066</v>
       </c>
       <c r="J100" t="n">
         <v>26.05158966061029</v>
       </c>
       <c r="K100" t="n">
-        <v>0.2093508487436035</v>
+        <v>0.2113270022384859</v>
       </c>
       <c r="L100" t="n">
-        <v>118.3993641150832</v>
+        <v>118.4412691095029</v>
       </c>
       <c r="M100" t="n">
-        <v>115.8009139559019</v>
+        <v>115.8234781836664</v>
       </c>
       <c r="N100" t="n">
-        <v>93.74171725701537</v>
+        <v>93.75345065545287</v>
       </c>
       <c r="O100" t="n">
-        <v>-12.44362154014203</v>
+        <v>-12.41554161225741</v>
       </c>
       <c r="P100" t="n">
-        <v>11.06629389336388</v>
+        <v>11.29451663134818</v>
       </c>
       <c r="Q100" t="n">
-        <v>-88.93370610663612</v>
+        <v>-88.70548336865183</v>
       </c>
       <c r="R100" t="n">
-        <v>-89.77867356494131</v>
+        <v>-89.59679363329131</v>
       </c>
       <c r="S100" t="n">
-        <v>-56.80647539104861</v>
+        <v>-56.57399519189412</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -31675,52 +31669,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.1752000004053116</v>
+        <v>0.1821999996900558</v>
       </c>
       <c r="E104" t="n">
-        <v>21.52994641196675</v>
+        <v>26.38559444844348</v>
       </c>
       <c r="F104" t="n">
-        <v>-37.78740222559433</v>
+        <v>-35.30173933224128</v>
       </c>
       <c r="G104" t="n">
-        <v>-48.74870264066296</v>
+        <v>-46.70099120214918</v>
       </c>
       <c r="H104" t="n">
-        <v>-89.94708413383485</v>
+        <v>-89.54542657841273</v>
       </c>
       <c r="I104" t="n">
-        <v>37.85284772416497</v>
+        <v>38.21413802174465</v>
       </c>
       <c r="J104" t="n">
         <v>30.70524078487225</v>
       </c>
       <c r="K104" t="n">
-        <v>0.1653066937928176</v>
+        <v>0.1711761778033555</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4081063735339389</v>
+        <v>0.4087730401324859</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4947862694680212</v>
+        <v>0.4950607792438936</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4934319096970697</v>
+        <v>0.4935733238240342</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.0484916294843331</v>
+        <v>-0.04804490588325543</v>
       </c>
       <c r="P104" t="n">
-        <v>4.158838951768646</v>
+        <v>4.956315205493219</v>
       </c>
       <c r="Q104" t="n">
-        <v>-95.84116104823136</v>
+        <v>-95.04368479450677</v>
       </c>
       <c r="R104" t="n">
-        <v>-99.6638241300659</v>
+        <v>-98.6930297432328</v>
       </c>
       <c r="S104" t="n">
-        <v>-83.76186950333013</v>
+        <v>-83.11308581840255</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -31734,7 +31728,7 @@
         </is>
       </c>
       <c r="W104" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="X104" t="n">
         <v>67.90000000000001</v>
@@ -31746,7 +31740,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); RSI scarico (38) — zona di interesse long</t>
+          <t>trend molto direzionale (ADX 31)</t>
         </is>
       </c>
     </row>
@@ -31767,52 +31761,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1734.300048828125</v>
+        <v>1744.18994140625</v>
       </c>
       <c r="E105" t="n">
-        <v>10.49425841328271</v>
+        <v>11.12435488761849</v>
       </c>
       <c r="F105" t="n">
-        <v>-11.74272538662992</v>
+        <v>-11.2394359092675</v>
       </c>
       <c r="G105" t="n">
-        <v>-31.06365688557683</v>
+        <v>-30.67054553867288</v>
       </c>
       <c r="H105" t="n">
-        <v>-36.12025845076299</v>
+        <v>-35.75598251000682</v>
       </c>
       <c r="I105" t="n">
-        <v>41.85041025051299</v>
+        <v>41.95918237642785</v>
       </c>
       <c r="J105" t="n">
         <v>13.65760872685721</v>
       </c>
       <c r="K105" t="n">
-        <v>0.223218396816747</v>
+        <v>0.2257813616949586</v>
       </c>
       <c r="L105" t="n">
-        <v>2496.407190472437</v>
+        <v>2497.349085003687</v>
       </c>
       <c r="M105" t="n">
-        <v>2411.829974770496</v>
+        <v>2412.217813695128</v>
       </c>
       <c r="N105" t="n">
-        <v>2011.319231713938</v>
+        <v>2011.519027523597</v>
       </c>
       <c r="O105" t="n">
-        <v>-192.3288807577522</v>
+        <v>-191.6977309180085</v>
       </c>
       <c r="P105" t="n">
-        <v>6.60804467188639</v>
+        <v>6.894938806859921</v>
       </c>
       <c r="Q105" t="n">
-        <v>-93.39195532811361</v>
+        <v>-93.10506119314007</v>
       </c>
       <c r="R105" t="n">
-        <v>-103.6894390440766</v>
+        <v>-103.4060933895197</v>
       </c>
       <c r="S105" t="n">
-        <v>-53.19919157069418</v>
+        <v>-52.9323087044635</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -31863,52 +31857,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7.875</v>
+        <v>7.941999912261963</v>
       </c>
       <c r="E106" t="n">
-        <v>9.535408733425999</v>
+        <v>10.46732781592985</v>
       </c>
       <c r="F106" t="n">
-        <v>-10.95387155673629</v>
+        <v>-10.19627374175646</v>
       </c>
       <c r="G106" t="n">
-        <v>-31.05559086833508</v>
+        <v>-30.46901698099864</v>
       </c>
       <c r="H106" t="n">
-        <v>-75.45856252444474</v>
+        <v>-75.24976580601368</v>
       </c>
       <c r="I106" t="n">
-        <v>41.28470891567208</v>
+        <v>41.42164839750207</v>
       </c>
       <c r="J106" t="n">
         <v>21.04094275559561</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2090676722969803</v>
+        <v>0.2118689467678845</v>
       </c>
       <c r="L106" t="n">
-        <v>12.04577940864002</v>
+        <v>12.05216035266497</v>
       </c>
       <c r="M106" t="n">
-        <v>12.59013474065598</v>
+        <v>12.59276218819566</v>
       </c>
       <c r="N106" t="n">
-        <v>10.85844209930851</v>
+        <v>10.85979563288956</v>
       </c>
       <c r="O106" t="n">
-        <v>-1.008269243550188</v>
+        <v>-1.00399346567364</v>
       </c>
       <c r="P106" t="n">
-        <v>4.116264276697987</v>
+        <v>4.439734487794018</v>
       </c>
       <c r="Q106" t="n">
-        <v>-95.88373572330201</v>
+        <v>-95.56026551220599</v>
       </c>
       <c r="R106" t="n">
-        <v>-101.3700100844139</v>
+        <v>-100.9548791744951</v>
       </c>
       <c r="S106" t="n">
-        <v>-58.60200676743318</v>
+        <v>-58.24979573068355</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -32113,7 +32107,7 @@
         <v>31.7</v>
       </c>
       <c r="X108" t="n">
-        <v>74.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -32795,52 +32789,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.860000133514404</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="E116" t="n">
-        <v>5.10837591670974</v>
+        <v>5.874467552541174</v>
       </c>
       <c r="F116" t="n">
-        <v>-25.14635690000799</v>
+        <v>-24.60077954339602</v>
       </c>
       <c r="G116" t="n">
-        <v>-72.57878209643083</v>
+        <v>-72.37892013969314</v>
       </c>
       <c r="H116" t="n">
-        <v>-62.22741389671366</v>
+        <v>-61.95210508307181</v>
       </c>
       <c r="I116" t="n">
-        <v>39.06875880868488</v>
+        <v>39.12523736802475</v>
       </c>
       <c r="J116" t="n">
         <v>16.96239899989589</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1993630347267451</v>
+        <v>0.2005941954561051</v>
       </c>
       <c r="L116" t="n">
-        <v>15.66924569277953</v>
+        <v>15.6740075702936</v>
       </c>
       <c r="M116" t="n">
-        <v>19.48377775493644</v>
+        <v>19.48648044217415</v>
       </c>
       <c r="N116" t="n">
-        <v>20.89202068915187</v>
+        <v>20.89342913179688</v>
       </c>
       <c r="O116" t="n">
-        <v>-1.139122060794444</v>
+        <v>-1.13593119586194</v>
       </c>
       <c r="P116" t="n">
-        <v>3.860233840988298</v>
+        <v>4.025704446241574</v>
       </c>
       <c r="Q116" t="n">
-        <v>-96.1397661590117</v>
+        <v>-95.97429555375842</v>
       </c>
       <c r="R116" t="n">
-        <v>-76.91513723012393</v>
+        <v>-76.81782086509412</v>
       </c>
       <c r="S116" t="n">
-        <v>-80.0567732925399</v>
+        <v>-79.91141533187478</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -32887,52 +32881,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.8830000162124634</v>
+        <v>0.8849999904632568</v>
       </c>
       <c r="E117" t="n">
-        <v>7.597765460510986</v>
+        <v>7.841471866414551</v>
       </c>
       <c r="F117" t="n">
-        <v>-47.14597252413528</v>
+        <v>-47.02625939609268</v>
       </c>
       <c r="G117" t="n">
-        <v>-77.68200704448147</v>
+        <v>-77.63145731580549</v>
       </c>
       <c r="H117" t="n">
-        <v>-96.23147643373947</v>
+        <v>-96.2229408165734</v>
       </c>
       <c r="I117" t="n">
-        <v>34.32033850341823</v>
+        <v>34.33417139702063</v>
       </c>
       <c r="J117" t="n">
         <v>33.95248828848647</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1950649160937174</v>
+        <v>0.1953159035392648</v>
       </c>
       <c r="L117" t="n">
-        <v>2.781902533386535</v>
+        <v>2.782093007124705</v>
       </c>
       <c r="M117" t="n">
-        <v>4.380402072131999</v>
+        <v>4.380510178848258</v>
       </c>
       <c r="N117" t="n">
-        <v>6.391146997305069</v>
+        <v>6.391203334607908</v>
       </c>
       <c r="O117" t="n">
-        <v>-0.04568465709804403</v>
+        <v>-0.04555702341366286</v>
       </c>
       <c r="P117" t="n">
-        <v>2.065291866635559</v>
+        <v>2.114366099097832</v>
       </c>
       <c r="Q117" t="n">
-        <v>-97.93470813336444</v>
+        <v>-97.88563390090216</v>
       </c>
       <c r="R117" t="n">
-        <v>-73.17221243535049</v>
+        <v>-73.14157403768723</v>
       </c>
       <c r="S117" t="n">
-        <v>-86.02487400551523</v>
+        <v>-85.99322067411389</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -33216,7 +33210,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03/07/2026 17:27:10</t>
+          <t>03/07/2026 19:23:31</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33256,7 +33250,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="N2" t="n">
-        <v>100.8359985351562</v>
+        <v>100.8570022583008</v>
       </c>
       <c r="O2" t="n">
         <v>4187.2998046875</v>
@@ -33279,7 +33273,7 @@
         <v>5.04197186167552</v>
       </c>
       <c r="U2" t="n">
-        <v>3.716700768701583</v>
+        <v>3.712475092739248</v>
       </c>
       <c r="V2" t="n">
         <v>1.213524452100483</v>
@@ -33330,7 +33324,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.989964428286335</v>
+        <v>2.98926014895928</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33429,10 +33423,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.83011859851605</v>
+        <v>64.8397735969493</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1213219406087812</v>
+        <v>0.1217081405461109</v>
       </c>
       <c r="D2" t="n">
         <v>55.17241379310344</v>
@@ -33887,22 +33881,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>RUSSELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>MSCIWORLD</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.924</v>
+        <v>0.931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.906</v>
+        <v>0.904</v>
       </c>
       <c r="E21" t="n">
-        <v>0.906</v>
+        <v>0.916</v>
       </c>
     </row>
   </sheetData>
@@ -34021,13 +34015,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-0.806</v>
       </c>
       <c r="D5" t="n">
         <v>-0.675</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.637</v>
+        <v>-0.636</v>
       </c>
     </row>
     <row r="6">
@@ -34105,13 +34099,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.657</v>
+        <v>-0.654</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.651</v>
+        <v>-0.65</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.671</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="10">
@@ -34122,17 +34116,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.556</v>
       </c>
       <c r="D10" t="n">
         <v>-0.647</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.633</v>
+        <v>-0.6850000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -34143,17 +34137,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.556</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>-0.647</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.633</v>
       </c>
     </row>
     <row r="12">
@@ -34294,13 +34288,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.607</v>
+        <v>-0.604</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.619</v>
+        <v>-0.618</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.555</v>
+        <v>-0.554</v>
       </c>
     </row>
     <row r="19">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1089,7 +1089,7 @@
         <v>75.3</v>
       </c>
       <c r="X7" t="n">
-        <v>68.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -3593,66 +3593,66 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MSCIWORLD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MSCI World ETF</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>156.1699981689453</v>
+        <v>161.3370056152344</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03202860192268453</v>
+        <v>-0.7395122639961338</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8524326854383757</v>
+        <v>-0.2892290607401815</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.995612056961293</v>
+        <v>0.8734545157581319</v>
       </c>
       <c r="H35" t="n">
-        <v>12.05424671044277</v>
+        <v>1.651378651693602</v>
       </c>
       <c r="I35" t="n">
-        <v>52.16795734087916</v>
+        <v>55.98624080733547</v>
       </c>
       <c r="J35" t="n">
-        <v>23.66507112143193</v>
+        <v>51.34634873082719</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5538400296627888</v>
+        <v>0.5648774089171957</v>
       </c>
       <c r="L35" t="n">
-        <v>155.8037604548409</v>
+        <v>161.187718709663</v>
       </c>
       <c r="M35" t="n">
-        <v>153.8972543060498</v>
+        <v>160.1064602219826</v>
       </c>
       <c r="N35" t="n">
-        <v>144.9799985099418</v>
+        <v>156.7091873106595</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.153957316628815</v>
+        <v>0.01652384429840703</v>
       </c>
       <c r="P35" t="n">
-        <v>48.98994050616003</v>
+        <v>46.04056926600718</v>
       </c>
       <c r="Q35" t="n">
-        <v>-51.01005949383998</v>
+        <v>-53.95943073399282</v>
       </c>
       <c r="R35" t="n">
-        <v>20.27515186218173</v>
+        <v>0.9822531698327827</v>
       </c>
       <c r="S35" t="n">
-        <v>-1.126938153648815</v>
+        <v>0.8419276678679033</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3661,19 +3661,19 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Evening Star</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Outside Bar, Volatility Squeeze</t>
+          <t>Double Top, Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>66.40000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="X35" t="n">
-        <v>70</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3682,84 +3682,94 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); pattern: Double Bottom; evening star — inversione ribassista a 3 candele</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (159.89); vicino alla resistenza dei 20g (162.84); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>MSCIWORLD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>MSCI World ETF</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>162.5390014648438</v>
+        <v>156.1699981689453</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.05472889866934283</v>
+        <v>0.03202860192268453</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4797147519643774</v>
+        <v>0.8524326854383757</v>
       </c>
       <c r="G36" t="n">
-        <v>1.607195881821077</v>
+        <v>-1.995612056961293</v>
       </c>
       <c r="H36" t="n">
-        <v>1.788545325196367</v>
+        <v>12.05424671044277</v>
       </c>
       <c r="I36" t="n">
-        <v>78.30385849751123</v>
+        <v>52.16795734087916</v>
       </c>
       <c r="J36" t="n">
-        <v>51.34634873082719</v>
+        <v>23.66507112143193</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9278053096179374</v>
+        <v>0.5538400296627888</v>
       </c>
       <c r="L36" t="n">
-        <v>161.1720042985502</v>
+        <v>155.8037604548409</v>
       </c>
       <c r="M36" t="n">
-        <v>160.0562338794009</v>
+        <v>153.8972543060498</v>
       </c>
       <c r="N36" t="n">
-        <v>156.6626765739301</v>
+        <v>144.9799985099418</v>
       </c>
       <c r="O36" t="n">
-        <v>0.1048596616097186</v>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+        <v>-0.153957316628815</v>
+      </c>
+      <c r="P36" t="n">
+        <v>48.98994050616003</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-51.01005949383998</v>
+      </c>
+      <c r="R36" t="n">
+        <v>20.27515186218173</v>
+      </c>
       <c r="S36" t="n">
-        <v>1.624983733753305</v>
+        <v>-1.126938153648815</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Double Bottom, Outside Bar, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>66.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="X36" t="n">
-        <v>64.3</v>
+        <v>70</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3768,7 +3778,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI ipercomprato (78) — attenzione estensione; pattern: Double Bottom; vicino alla resistenza dei 20g (162.84); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); pattern: Double Bottom; evening star — inversione ribassista a 3 candele</t>
         </is>
       </c>
     </row>
@@ -4799,52 +4809,52 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>82.19000244140625</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="E48" t="n">
-        <v>1.917093465307262</v>
+        <v>2.623903423294682</v>
       </c>
       <c r="F48" t="n">
-        <v>15.25257485452753</v>
+        <v>16.05186832749732</v>
       </c>
       <c r="G48" t="n">
-        <v>23.13242681045211</v>
+        <v>23.98636820989373</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.475905062906114</v>
+        <v>-1.799561192594379</v>
       </c>
       <c r="I48" t="n">
-        <v>65.61314610942259</v>
+        <v>66.28160320729185</v>
       </c>
       <c r="J48" t="n">
-        <v>19.1381050228664</v>
+        <v>19.18628673119542</v>
       </c>
       <c r="K48" t="n">
-        <v>1.125693225559595</v>
+        <v>1.148414066395675</v>
       </c>
       <c r="L48" t="n">
-        <v>73.8573379788607</v>
+        <v>73.91162366408204</v>
       </c>
       <c r="M48" t="n">
-        <v>75.70067373861689</v>
+        <v>75.72302666782568</v>
       </c>
       <c r="N48" t="n">
-        <v>96.8473341421401</v>
+        <v>96.85300578089458</v>
       </c>
       <c r="O48" t="n">
-        <v>1.639001831675933</v>
+        <v>1.6753778805764</v>
       </c>
       <c r="P48" t="n">
-        <v>97.75221817537843</v>
+        <v>99.086038124678</v>
       </c>
       <c r="Q48" t="n">
-        <v>-2.247781824621568</v>
+        <v>-0.913961875321999</v>
       </c>
       <c r="R48" t="n">
-        <v>214.4834328801499</v>
+        <v>222.2465830321673</v>
       </c>
       <c r="S48" t="n">
-        <v>19.33596047719284</v>
+        <v>20.16357282702879</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4854,14 +4864,14 @@
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakout 20d</t>
         </is>
       </c>
       <c r="W48" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="X48" t="n">
-        <v>63.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -4870,7 +4880,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>RSI in forza (66) — momentum positivo; vicino alla resistenza dei 20g (82.60)</t>
+          <t>RSI in forza (66) — momentum positivo; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (82.93); in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7107,66 +7117,70 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.33552360534668</v>
+        <v>1.334988713264465</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5716050346918244</v>
+        <v>0.5313249864670855</v>
       </c>
       <c r="F73" t="n">
-        <v>1.268753801018629</v>
+        <v>1.228194536946448</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.5355437761158766</v>
+        <v>-0.5753803989077988</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.3472356574381497</v>
+        <v>-0.3871476997294399</v>
       </c>
       <c r="I73" t="n">
-        <v>53.44604511167641</v>
+        <v>52.9812659969456</v>
       </c>
       <c r="J73" t="n">
         <v>34.79252082454199</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6581396890618093</v>
+        <v>0.6443909969799766</v>
       </c>
       <c r="L73" t="n">
-        <v>1.329965885929094</v>
+        <v>1.329914943826026</v>
       </c>
       <c r="M73" t="n">
-        <v>1.336473015716562</v>
+        <v>1.336452039556475</v>
       </c>
       <c r="N73" t="n">
-        <v>1.338412322962132</v>
+        <v>1.338407000652856</v>
       </c>
       <c r="O73" t="n">
-        <v>0.001050636427556501</v>
+        <v>0.001016500864475073</v>
       </c>
       <c r="P73" t="n">
-        <v>71.16507027839519</v>
+        <v>69.37133217135457</v>
       </c>
       <c r="Q73" t="n">
-        <v>-28.83492972160481</v>
+        <v>-30.62866782864544</v>
       </c>
       <c r="R73" t="n">
-        <v>42.3195952542145</v>
+        <v>41.08927004577082</v>
       </c>
       <c r="S73" t="n">
-        <v>-0.5344752518426032</v>
+        <v>-0.5743123025904073</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="X73" t="n">
         <v>56.4</v>
@@ -7178,7 +7192,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); pattern: Double Bottom; vicino alla resistenza dei 20g (1.3461); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 35); pattern: Double Bottom; doji — indecisione del mercato; vicino alla resistenza dei 20g (1.3461); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7369,79 +7383,83 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>COTTON</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6.909999847412109</v>
+        <v>72.56999969482422</v>
       </c>
       <c r="E76" t="n">
-        <v>1.723555302599666</v>
+        <v>-0.9688852296668493</v>
       </c>
       <c r="F76" t="n">
-        <v>7.2521374647327</v>
+        <v>-1.130792661853075</v>
       </c>
       <c r="G76" t="n">
-        <v>5.257477085340923</v>
+        <v>-5.802182200911943</v>
       </c>
       <c r="H76" t="n">
-        <v>-24.73356863766768</v>
+        <v>2.326567355442233</v>
       </c>
       <c r="I76" t="n">
-        <v>51.67755511342694</v>
+        <v>43.1498933780203</v>
       </c>
       <c r="J76" t="n">
-        <v>36.97876607456516</v>
+        <v>14.64486009625032</v>
       </c>
       <c r="K76" t="n">
-        <v>0.859439642414791</v>
+        <v>0.3719258006802371</v>
       </c>
       <c r="L76" t="n">
-        <v>6.687766796962074</v>
+        <v>73.9394938126256</v>
       </c>
       <c r="M76" t="n">
-        <v>7.365478550225608</v>
+        <v>74.79148975701614</v>
       </c>
       <c r="N76" t="n">
-        <v>10.42381850983205</v>
+        <v>70.44261985394238</v>
       </c>
       <c r="O76" t="n">
-        <v>0.1425425837437522</v>
+        <v>0.01847026383485018</v>
       </c>
       <c r="P76" t="n">
-        <v>100.3564351617813</v>
+        <v>26.16434562224022</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.3564351617812837</v>
+        <v>-73.83565437775978</v>
       </c>
       <c r="R76" t="n">
-        <v>58.57887739433393</v>
+        <v>-20.67858884527496</v>
       </c>
       <c r="S76" t="n">
-        <v>2.896898036971352</v>
+        <v>-5.42161277220049</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="X76" t="n">
-        <v>56.1</v>
+        <v>61.9</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -7450,77 +7468,77 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 37); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 15); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>COTTON</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>72.56999969482422</v>
+        <v>5.513999938964844</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.9688852296668493</v>
+        <v>2.988416971911323</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.130792661853075</v>
+        <v>-0.1810323783124401</v>
       </c>
       <c r="G77" t="n">
-        <v>-5.802182200911943</v>
+        <v>2.528824133529306</v>
       </c>
       <c r="H77" t="n">
-        <v>2.326567355442233</v>
+        <v>-11.71949881557952</v>
       </c>
       <c r="I77" t="n">
-        <v>43.1498933780203</v>
+        <v>49.93210808971318</v>
       </c>
       <c r="J77" t="n">
-        <v>14.64486009625032</v>
+        <v>9.660583359844347</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3719258006802371</v>
+        <v>0.7267940500573961</v>
       </c>
       <c r="L77" t="n">
-        <v>73.9394938126256</v>
+        <v>5.483130379921562</v>
       </c>
       <c r="M77" t="n">
-        <v>74.79148975701614</v>
+        <v>5.638946845876156</v>
       </c>
       <c r="N77" t="n">
-        <v>70.44261985394238</v>
+        <v>5.914717133435826</v>
       </c>
       <c r="O77" t="n">
-        <v>0.01847026383485018</v>
+        <v>0.01521546702563684</v>
       </c>
       <c r="P77" t="n">
-        <v>26.16434562224022</v>
+        <v>54.63914611740272</v>
       </c>
       <c r="Q77" t="n">
-        <v>-73.83565437775978</v>
+        <v>-45.36085388259729</v>
       </c>
       <c r="R77" t="n">
-        <v>-20.67858884527496</v>
+        <v>48.25729487085574</v>
       </c>
       <c r="S77" t="n">
-        <v>-5.42161277220049</v>
+        <v>1.771866256775656</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -7528,12 +7546,16 @@
           <t>Doji</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W77" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="X77" t="n">
-        <v>61.9</v>
+        <v>57</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7542,94 +7564,86 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 15); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 10); pattern: Double Bottom; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5.513999938964844</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="E78" t="n">
-        <v>2.988416971911323</v>
+        <v>2.754042493689002</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.1810323783124401</v>
+        <v>8.338630691847971</v>
       </c>
       <c r="G78" t="n">
-        <v>2.528824133529306</v>
+        <v>6.323763862087639</v>
       </c>
       <c r="H78" t="n">
-        <v>-11.71949881557952</v>
+        <v>-23.97109928426014</v>
       </c>
       <c r="I78" t="n">
-        <v>49.93210808971318</v>
+        <v>53.02111416353829</v>
       </c>
       <c r="J78" t="n">
-        <v>9.660583359844347</v>
+        <v>37.14692377733794</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7267940500573961</v>
+        <v>0.9106523592144119</v>
       </c>
       <c r="L78" t="n">
-        <v>5.483130379921562</v>
+        <v>6.694433479977443</v>
       </c>
       <c r="M78" t="n">
-        <v>5.638946845876156</v>
+        <v>7.368223654996642</v>
       </c>
       <c r="N78" t="n">
-        <v>5.914717133435826</v>
+        <v>10.42451502895305</v>
       </c>
       <c r="O78" t="n">
-        <v>0.01521546702563684</v>
+        <v>0.1470098311660166</v>
       </c>
       <c r="P78" t="n">
-        <v>54.63914611740272</v>
+        <v>99.68823676370866</v>
       </c>
       <c r="Q78" t="n">
-        <v>-45.36085388259729</v>
+        <v>-0.3117632362913401</v>
       </c>
       <c r="R78" t="n">
-        <v>48.25729487085574</v>
+        <v>65.45808773311462</v>
       </c>
       <c r="S78" t="n">
-        <v>1.771866256775656</v>
+        <v>3.939271508037145</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="n">
-        <v>45.2</v>
+        <v>44.9</v>
       </c>
       <c r="X78" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7638,7 +7652,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 10); pattern: Double Bottom; doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 37); vicino alla resistenza dei 20g (7.0609)</t>
         </is>
       </c>
     </row>
@@ -8109,66 +8123,66 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>390.489990234375</v>
+        <v>1764.400024414062</v>
       </c>
       <c r="E84" t="n">
-        <v>1.616006941502235</v>
+        <v>3.900116767509587</v>
       </c>
       <c r="F84" t="n">
-        <v>10.67369699156677</v>
+        <v>12.35631761732514</v>
       </c>
       <c r="G84" t="n">
-        <v>-11.51571630041562</v>
+        <v>5.961837664517433</v>
       </c>
       <c r="H84" t="n">
-        <v>4.560059757122703</v>
+        <v>-23.82455319677302</v>
       </c>
       <c r="I84" t="n">
-        <v>49.80110187594683</v>
+        <v>55.81156908631785</v>
       </c>
       <c r="J84" t="n">
-        <v>45.34042955827164</v>
+        <v>20.70025469109621</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5465301148068399</v>
+        <v>0.7856915835980655</v>
       </c>
       <c r="L84" t="n">
-        <v>386.6018465676733</v>
+        <v>1674.44437466409</v>
       </c>
       <c r="M84" t="n">
-        <v>398.6495915414451</v>
+        <v>1808.036562341718</v>
       </c>
       <c r="N84" t="n">
-        <v>427.8201890951816</v>
+        <v>2270.12606745985</v>
       </c>
       <c r="O84" t="n">
-        <v>1.082789350491073</v>
+        <v>22.29034938941281</v>
       </c>
       <c r="P84" t="n">
-        <v>78.57276426022005</v>
+        <v>95.33199342727954</v>
       </c>
       <c r="Q84" t="n">
-        <v>-21.42723573977995</v>
+        <v>-4.66800657272046</v>
       </c>
       <c r="R84" t="n">
-        <v>3.539648516898157</v>
+        <v>86.73405657287813</v>
       </c>
       <c r="S84" t="n">
-        <v>-8.623111906047509</v>
+        <v>5.010397173328895</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8176,12 +8190,16 @@
         </is>
       </c>
       <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W84" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="X84" t="n">
-        <v>59.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -8190,73 +8208,73 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 45); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1744.18994140625</v>
+        <v>390.489990234375</v>
       </c>
       <c r="E85" t="n">
-        <v>2.710006840431056</v>
+        <v>1.616006941502235</v>
       </c>
       <c r="F85" t="n">
-        <v>11.06934727382134</v>
+        <v>10.67369699156677</v>
       </c>
       <c r="G85" t="n">
-        <v>4.748112032445184</v>
+        <v>-11.51571630041562</v>
       </c>
       <c r="H85" t="n">
-        <v>-24.69709461694314</v>
+        <v>4.560059757122703</v>
       </c>
       <c r="I85" t="n">
-        <v>54.15421101017839</v>
+        <v>49.80110187594683</v>
       </c>
       <c r="J85" t="n">
-        <v>20.44441239659244</v>
+        <v>45.34042955827164</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7285309396920854</v>
+        <v>0.5465301148068399</v>
       </c>
       <c r="L85" t="n">
-        <v>1672.519604853822</v>
+        <v>386.6018465676733</v>
       </c>
       <c r="M85" t="n">
-        <v>1807.244010066902</v>
+        <v>398.6495915414451</v>
       </c>
       <c r="N85" t="n">
-        <v>2269.924972106538</v>
+        <v>427.8201890951816</v>
       </c>
       <c r="O85" t="n">
-        <v>21.00058910629328</v>
+        <v>1.082789350491073</v>
       </c>
       <c r="P85" t="n">
-        <v>87.74352639744791</v>
+        <v>78.57276426022005</v>
       </c>
       <c r="Q85" t="n">
-        <v>-12.25647360255209</v>
+        <v>-21.42723573977995</v>
       </c>
       <c r="R85" t="n">
-        <v>71.83130038425395</v>
+        <v>3.539648516898157</v>
       </c>
       <c r="S85" t="n">
-        <v>3.807569688523627</v>
+        <v>-8.623111906047509</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8264,16 +8282,12 @@
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="X85" t="n">
-        <v>68.8</v>
+        <v>59.2</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -8282,7 +8296,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 45); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -8649,66 +8663,66 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Brunello Cucinelli</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>82.33999633789062</v>
+        <v>62698.01171875</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.223613561651382</v>
+        <v>1.972359120132694</v>
       </c>
       <c r="F90" t="n">
-        <v>1.478921564294811</v>
+        <v>5.317566692840736</v>
       </c>
       <c r="G90" t="n">
-        <v>1.579075768379634</v>
+        <v>-1.330099067077828</v>
       </c>
       <c r="H90" t="n">
-        <v>7.213532638012077</v>
+        <v>-20.28959604009802</v>
       </c>
       <c r="I90" t="n">
-        <v>45.8851808697758</v>
+        <v>48.39434138306207</v>
       </c>
       <c r="J90" t="n">
-        <v>31.51892426920546</v>
+        <v>27.69677535557079</v>
       </c>
       <c r="K90" t="n">
-        <v>0.2724760646027921</v>
+        <v>0.5444593542232661</v>
       </c>
       <c r="L90" t="n">
-        <v>83.44553913114018</v>
+        <v>62141.98333455706</v>
       </c>
       <c r="M90" t="n">
-        <v>83.20928345388599</v>
+        <v>66005.51660402081</v>
       </c>
       <c r="N90" t="n">
-        <v>86.61875784929082</v>
+        <v>75895.14235070042</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.3183206989983882</v>
+        <v>396.3779778982425</v>
       </c>
       <c r="P90" t="n">
-        <v>22.79905760623027</v>
+        <v>63.49534731310589</v>
       </c>
       <c r="Q90" t="n">
-        <v>-77.20094239376974</v>
+        <v>-36.50465268689411</v>
       </c>
       <c r="R90" t="n">
-        <v>-57.19999918572849</v>
+        <v>-2.061225582050607</v>
       </c>
       <c r="S90" t="n">
-        <v>-0.9145633576240653</v>
+        <v>-2.675065315559633</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8716,16 +8730,12 @@
         </is>
       </c>
       <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Double Bottom, Inside Bar</t>
-        </is>
-      </c>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="n">
-        <v>41.7</v>
+        <v>42</v>
       </c>
       <c r="X90" t="n">
-        <v>63.9</v>
+        <v>63.2</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -8734,73 +8744,73 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 28); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Brunello Cucinelli</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.1821999996900558</v>
+        <v>82.33999633789062</v>
       </c>
       <c r="E91" t="n">
-        <v>12.96212464858801</v>
+        <v>-1.223613561651382</v>
       </c>
       <c r="F91" t="n">
-        <v>26.81929080679977</v>
+        <v>1.478921564294811</v>
       </c>
       <c r="G91" t="n">
-        <v>7.277441751977953</v>
+        <v>1.579075768379634</v>
       </c>
       <c r="H91" t="n">
-        <v>-27.14389290221047</v>
+        <v>7.213532638012077</v>
       </c>
       <c r="I91" t="n">
-        <v>59.73830029790061</v>
+        <v>45.8851808697758</v>
       </c>
       <c r="J91" t="n">
-        <v>38.18681898929582</v>
+        <v>31.51892426920546</v>
       </c>
       <c r="K91" t="n">
-        <v>0.9583160521575457</v>
+        <v>0.2724760646027921</v>
       </c>
       <c r="L91" t="n">
-        <v>0.1613835235165188</v>
+        <v>83.44553913114018</v>
       </c>
       <c r="M91" t="n">
-        <v>0.1859171884166575</v>
+        <v>83.20928345388599</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2929863611985647</v>
+        <v>86.61875784929082</v>
       </c>
       <c r="O91" t="n">
-        <v>0.004898882676287518</v>
+        <v>-0.3183206989983882</v>
       </c>
       <c r="P91" t="n">
-        <v>99.95689581386112</v>
+        <v>22.79905760623027</v>
       </c>
       <c r="Q91" t="n">
-        <v>-0.04310418613887149</v>
+        <v>-77.20094239376974</v>
       </c>
       <c r="R91" t="n">
-        <v>75.73660974138078</v>
+        <v>-57.19999918572849</v>
       </c>
       <c r="S91" t="n">
-        <v>6.08380259786232</v>
+        <v>-0.9145633576240653</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -8808,12 +8818,16 @@
         </is>
       </c>
       <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Double Bottom, Inside Bar</t>
+        </is>
+      </c>
       <c r="W91" t="n">
-        <v>41.3</v>
+        <v>41.7</v>
       </c>
       <c r="X91" t="n">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -8822,90 +8836,86 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 38)</t>
+          <t>trend molto direzionale (ADX 32); pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Eni</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>20.44499969482422</v>
+        <v>8.003000259399414</v>
       </c>
       <c r="E92" t="n">
-        <v>1.817727950722015</v>
+        <v>3.377832972274364</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.170897696261807</v>
+        <v>10.23463049134337</v>
       </c>
       <c r="G92" t="n">
-        <v>-12.8330856477199</v>
+        <v>1.875167454931481</v>
       </c>
       <c r="H92" t="n">
-        <v>-17.17642237330426</v>
+        <v>-12.7676662088706</v>
       </c>
       <c r="I92" t="n">
-        <v>35.36943537656649</v>
+        <v>54.10236676207693</v>
       </c>
       <c r="J92" t="n">
-        <v>49.89199583755958</v>
+        <v>23.42564059683689</v>
       </c>
       <c r="K92" t="n">
-        <v>0.2357528920674938</v>
+        <v>0.6960021632551494</v>
       </c>
       <c r="L92" t="n">
-        <v>21.44480031734003</v>
+        <v>7.69331488071971</v>
       </c>
       <c r="M92" t="n">
-        <v>22.09834073766282</v>
+        <v>8.192324367286872</v>
       </c>
       <c r="N92" t="n">
-        <v>19.75335525708702</v>
+        <v>10.1765501817318</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.1333154045249789</v>
+        <v>0.07724331408102098</v>
       </c>
       <c r="P92" t="n">
-        <v>15.43339562124327</v>
+        <v>88.00588343791685</v>
       </c>
       <c r="Q92" t="n">
-        <v>-84.56660437875674</v>
+        <v>-11.99411656208315</v>
       </c>
       <c r="R92" t="n">
-        <v>-84.6928807933466</v>
+        <v>52.55236837141192</v>
       </c>
       <c r="S92" t="n">
-        <v>-12.68418152712353</v>
+        <v>0.3206601465092884</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar</t>
-        </is>
-      </c>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="X92" t="n">
-        <v>64.3</v>
+        <v>59.6</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -8914,19 +8924,19 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 50); RSI scarico (35) — zona di interesse long; pattern: Double Top</t>
+          <t>trend in sviluppo (ADX 23); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tenaris</t>
+          <t>Eni</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8935,52 +8945,52 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>23.68000030517578</v>
+        <v>20.44499969482422</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.837516175123687</v>
+        <v>1.817727950722015</v>
       </c>
       <c r="F93" t="n">
-        <v>-5.619768189864582</v>
+        <v>-0.170897696261807</v>
       </c>
       <c r="G93" t="n">
-        <v>-14.48176291636287</v>
+        <v>-12.8330856477199</v>
       </c>
       <c r="H93" t="n">
-        <v>-6.329115261120021</v>
+        <v>-17.17642237330426</v>
       </c>
       <c r="I93" t="n">
-        <v>31.31686685186551</v>
+        <v>35.36943537656649</v>
       </c>
       <c r="J93" t="n">
-        <v>46.90604926204401</v>
+        <v>49.89199583755958</v>
       </c>
       <c r="K93" t="n">
-        <v>0.08482012712002281</v>
+        <v>0.2357528920674938</v>
       </c>
       <c r="L93" t="n">
-        <v>25.22706973010341</v>
+        <v>21.44480031734003</v>
       </c>
       <c r="M93" t="n">
-        <v>25.50369548459471</v>
+        <v>22.09834073766282</v>
       </c>
       <c r="N93" t="n">
-        <v>22.12538715960772</v>
+        <v>19.75335525708702</v>
       </c>
       <c r="O93" t="n">
-        <v>-0.2220522757085613</v>
+        <v>-0.1333154045249789</v>
       </c>
       <c r="P93" t="n">
-        <v>2.089544080839735</v>
+        <v>15.43339562124327</v>
       </c>
       <c r="Q93" t="n">
-        <v>-97.91045591916027</v>
+        <v>-84.56660437875674</v>
       </c>
       <c r="R93" t="n">
-        <v>-131.3620125677935</v>
+        <v>-84.6928807933466</v>
       </c>
       <c r="S93" t="n">
-        <v>-13.51350974799381</v>
+        <v>-12.68418152712353</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -8990,14 +9000,14 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W93" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="X93" t="n">
-        <v>67.8</v>
+        <v>64.3</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -9006,90 +9016,86 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); RSI scarico (31) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (23.61); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 50); RSI scarico (35) — zona di interesse long; pattern: Double Top</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>194.8300018310547</v>
+        <v>0.1817999929189682</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.391841266582972</v>
+        <v>12.71412456728864</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.4649042794377389</v>
+        <v>26.54086833087468</v>
       </c>
       <c r="G94" t="n">
-        <v>-12.56171105516419</v>
+        <v>7.041921976134091</v>
       </c>
       <c r="H94" t="n">
-        <v>9.831446249175624</v>
+        <v>-27.30384315579872</v>
       </c>
       <c r="I94" t="n">
-        <v>41.15855680536166</v>
+        <v>59.54583000729774</v>
       </c>
       <c r="J94" t="n">
-        <v>25.99327297142875</v>
+        <v>38.20070968919521</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1815789893158984</v>
+        <v>0.9523051444134021</v>
       </c>
       <c r="L94" t="n">
-        <v>202.75171786607</v>
+        <v>0.1613454276335581</v>
       </c>
       <c r="M94" t="n">
-        <v>204.1884814568574</v>
+        <v>0.1859015018766148</v>
       </c>
       <c r="N94" t="n">
-        <v>188.9462997597143</v>
+        <v>0.2929823810316882</v>
       </c>
       <c r="O94" t="n">
-        <v>-1.000431665214234</v>
+        <v>0.004873355178645476</v>
       </c>
       <c r="P94" t="n">
-        <v>20.79370926679602</v>
+        <v>98.6759191320066</v>
       </c>
       <c r="Q94" t="n">
-        <v>-79.20629073320399</v>
+        <v>-1.324080867993408</v>
       </c>
       <c r="R94" t="n">
-        <v>-57.88591258461099</v>
+        <v>75.41412588923626</v>
       </c>
       <c r="S94" t="n">
-        <v>-9.275901359229477</v>
+        <v>5.850903369464633</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Outside Bar</t>
-        </is>
-      </c>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="X94" t="n">
-        <v>59.7</v>
+        <v>63.7</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -9098,86 +9104,90 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 38)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Tenaris</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7.941999912261963</v>
+        <v>23.68000030517578</v>
       </c>
       <c r="E95" t="n">
-        <v>2.58986802247696</v>
+        <v>-0.837516175123687</v>
       </c>
       <c r="F95" t="n">
-        <v>9.394401763543069</v>
+        <v>-5.619768189864582</v>
       </c>
       <c r="G95" t="n">
-        <v>1.098656099438511</v>
+        <v>-14.48176291636287</v>
       </c>
       <c r="H95" t="n">
-        <v>-13.43256717980574</v>
+        <v>-6.329115261120021</v>
       </c>
       <c r="I95" t="n">
-        <v>52.91208799379964</v>
+        <v>31.31686685186551</v>
       </c>
       <c r="J95" t="n">
-        <v>23.38371168862766</v>
+        <v>46.90604926204401</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6583378098447404</v>
+        <v>0.08482012712002281</v>
       </c>
       <c r="L95" t="n">
-        <v>7.687505323849476</v>
+        <v>25.22706973010341</v>
       </c>
       <c r="M95" t="n">
-        <v>8.189932196810894</v>
+        <v>25.50369548459471</v>
       </c>
       <c r="N95" t="n">
-        <v>10.17594321310356</v>
+        <v>22.12538715960772</v>
       </c>
       <c r="O95" t="n">
-        <v>0.07335041443464219</v>
+        <v>-0.2220522757085613</v>
       </c>
       <c r="P95" t="n">
-        <v>82.53126485784188</v>
+        <v>2.089544080839735</v>
       </c>
       <c r="Q95" t="n">
-        <v>-17.46873514215812</v>
+        <v>-97.91045591916027</v>
       </c>
       <c r="R95" t="n">
-        <v>41.66116915245308</v>
+        <v>-131.3620125677935</v>
       </c>
       <c r="S95" t="n">
-        <v>-0.4440024669659537</v>
+        <v>-13.51350974799381</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
+        </is>
+      </c>
       <c r="W95" t="n">
         <v>41</v>
       </c>
       <c r="X95" t="n">
-        <v>59.7</v>
+        <v>67.8</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -9186,86 +9196,90 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 47); RSI scarico (31) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (23.61); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.137699961662292</v>
+        <v>194.8300018310547</v>
       </c>
       <c r="E96" t="n">
-        <v>4.712761607203886</v>
+        <v>-1.391841266582972</v>
       </c>
       <c r="F96" t="n">
-        <v>8.603100423045662</v>
+        <v>-0.4649042794377389</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4982941428640419</v>
+        <v>-12.56171105516419</v>
       </c>
       <c r="H96" t="n">
-        <v>-18.33626460924583</v>
+        <v>9.831446249175624</v>
       </c>
       <c r="I96" t="n">
-        <v>51.92229010703826</v>
+        <v>41.15855680536166</v>
       </c>
       <c r="J96" t="n">
-        <v>21.34413613892223</v>
+        <v>25.99327297142875</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6021630511366372</v>
+        <v>0.1815789893158984</v>
       </c>
       <c r="L96" t="n">
-        <v>1.105973995425375</v>
+        <v>202.75171786607</v>
       </c>
       <c r="M96" t="n">
-        <v>1.18680673959604</v>
+        <v>204.1884814568574</v>
       </c>
       <c r="N96" t="n">
-        <v>1.506304605452055</v>
+        <v>188.9462997597143</v>
       </c>
       <c r="O96" t="n">
-        <v>0.008861550458650613</v>
+        <v>-1.000431665214234</v>
       </c>
       <c r="P96" t="n">
-        <v>83.98833409499245</v>
+        <v>20.79370926679602</v>
       </c>
       <c r="Q96" t="n">
-        <v>-16.01166590500754</v>
+        <v>-79.20629073320399</v>
       </c>
       <c r="R96" t="n">
-        <v>10.29947933087513</v>
+        <v>-57.88591258461099</v>
       </c>
       <c r="S96" t="n">
-        <v>-1.073442796345536</v>
+        <v>-9.275901359229477</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W96" t="n">
-        <v>40.2</v>
+        <v>41</v>
       </c>
       <c r="X96" t="n">
-        <v>60.4</v>
+        <v>59.7</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9274,182 +9288,178 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 26); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>360.4500122070312</v>
+        <v>1.136399984359741</v>
       </c>
       <c r="E97" t="n">
-        <v>-2.406991990850182</v>
+        <v>4.593113002155214</v>
       </c>
       <c r="F97" t="n">
-        <v>-4.871867007116471</v>
+        <v>8.479006575551473</v>
       </c>
       <c r="G97" t="n">
-        <v>-25.15106698404559</v>
+        <v>0.3834611414284428</v>
       </c>
       <c r="H97" t="n">
-        <v>14.59228300599176</v>
+        <v>-18.42957655969577</v>
       </c>
       <c r="I97" t="n">
-        <v>39.62802974353724</v>
+        <v>51.72834257013492</v>
       </c>
       <c r="J97" t="n">
-        <v>30.17285108714634</v>
+        <v>21.27718461741929</v>
       </c>
       <c r="K97" t="n">
-        <v>0.08801324705436597</v>
+        <v>0.5972432581753909</v>
       </c>
       <c r="L97" t="n">
-        <v>386.498095764574</v>
+        <v>1.105850188063227</v>
       </c>
       <c r="M97" t="n">
-        <v>392.3199534757471</v>
+        <v>1.186755760093979</v>
       </c>
       <c r="N97" t="n">
-        <v>355.0082245455592</v>
+        <v>1.506291670354517</v>
       </c>
       <c r="O97" t="n">
-        <v>-2.45503104873473</v>
+        <v>0.008778588944185844</v>
       </c>
       <c r="P97" t="n">
-        <v>6.906060838008919</v>
+        <v>83.13498895072587</v>
       </c>
       <c r="Q97" t="n">
-        <v>-93.09393916199109</v>
+        <v>-16.86501104927413</v>
       </c>
       <c r="R97" t="n">
-        <v>-52.75529600430337</v>
+        <v>11.11621030352144</v>
       </c>
       <c r="S97" t="n">
-        <v>-24.78559273339948</v>
+        <v>-1.186479874061874</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>Breakdown 20d, Breakdown 50d, Outside Bar</t>
-        </is>
-      </c>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="X97" t="n">
-        <v>69.2</v>
+        <v>60.5</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 30); breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (356.43); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>62185.109375</v>
+        <v>360.4500122070312</v>
       </c>
       <c r="E98" t="n">
-        <v>1.138172188893982</v>
+        <v>-2.406991990850182</v>
       </c>
       <c r="F98" t="n">
-        <v>4.456014223886573</v>
+        <v>-4.871867007116471</v>
       </c>
       <c r="G98" t="n">
-        <v>-2.137270172807515</v>
+        <v>-25.15106698404559</v>
       </c>
       <c r="H98" t="n">
-        <v>-20.94166860016082</v>
+        <v>14.59228300599176</v>
       </c>
       <c r="I98" t="n">
-        <v>46.51349577400001</v>
+        <v>39.62802974353724</v>
       </c>
       <c r="J98" t="n">
-        <v>28.05262053307027</v>
+        <v>30.17285108714634</v>
       </c>
       <c r="K98" t="n">
-        <v>0.4923568117219368</v>
+        <v>0.08801324705436597</v>
       </c>
       <c r="L98" t="n">
-        <v>62093.13549229515</v>
+        <v>386.498095764574</v>
       </c>
       <c r="M98" t="n">
-        <v>65985.40278661886</v>
+        <v>392.3199534757471</v>
       </c>
       <c r="N98" t="n">
-        <v>75890.03884479246</v>
+        <v>355.0082245455592</v>
       </c>
       <c r="O98" t="n">
-        <v>363.6457485535152</v>
+        <v>-2.45503104873473</v>
       </c>
       <c r="P98" t="n">
-        <v>56.91650015331922</v>
+        <v>6.906060838008919</v>
       </c>
       <c r="Q98" t="n">
-        <v>-43.08349984668079</v>
+        <v>-93.09393916199109</v>
       </c>
       <c r="R98" t="n">
-        <v>-14.23601452760458</v>
+        <v>-52.75529600430337</v>
       </c>
       <c r="S98" t="n">
-        <v>-3.471233897888648</v>
+        <v>-24.78559273339948</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Breakdown 20d, Breakdown 50d, Outside Bar</t>
         </is>
       </c>
       <c r="W98" t="n">
-        <v>39.3</v>
+        <v>39.7</v>
       </c>
       <c r="X98" t="n">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -9458,7 +9468,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); pattern: Bear Flag / Consolidation</t>
+          <t>trend molto direzionale (ADX 30); breakdown minimi 50g — rottura supporto importante; sul supporto dei 20g (356.43); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -10399,66 +10409,70 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.144295692443848</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="E109" t="n">
-        <v>0.5710066102658784</v>
+        <v>0.5479882337015907</v>
       </c>
       <c r="F109" t="n">
-        <v>0.7151907420130277</v>
+        <v>0.6921393650368701</v>
       </c>
       <c r="G109" t="n">
-        <v>-1.433797862359387</v>
+        <v>-1.456357385563811</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.084910798157502</v>
+        <v>-2.107321296675324</v>
       </c>
       <c r="I109" t="n">
-        <v>43.23530794052655</v>
+        <v>42.87896660623295</v>
       </c>
       <c r="J109" t="n">
         <v>45.77819595267555</v>
       </c>
       <c r="K109" t="n">
-        <v>0.4058234016718369</v>
+        <v>0.3985569314885554</v>
       </c>
       <c r="L109" t="n">
-        <v>1.146906324225985</v>
+        <v>1.146881381101304</v>
       </c>
       <c r="M109" t="n">
-        <v>1.155256984870591</v>
+        <v>1.155246714172193</v>
       </c>
       <c r="N109" t="n">
-        <v>1.159072212002603</v>
+        <v>1.159069606004502</v>
       </c>
       <c r="O109" t="n">
-        <v>-5.104572813746655e-08</v>
+        <v>-1.676507115493803e-05</v>
       </c>
       <c r="P109" t="n">
-        <v>40.11236000764796</v>
+        <v>39.21860571075231</v>
       </c>
       <c r="Q109" t="n">
-        <v>-59.88763999235204</v>
+        <v>-60.78139428924769</v>
       </c>
       <c r="R109" t="n">
-        <v>-23.3258052016601</v>
+        <v>-23.9167743004216</v>
       </c>
       <c r="S109" t="n">
-        <v>-1.461269000870102</v>
+        <v>-1.483822236566501</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr">
         <is>
           <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W109" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="X109" t="n">
         <v>68</v>
@@ -10470,7 +10484,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 46); pattern: Double Top; sul supporto dei 20g (1.1325); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 46); pattern: Double Top; doji — indecisione del mercato; sul supporto dei 20g (1.1325); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -11061,7 +11075,7 @@
         <v>42.10328459094667</v>
       </c>
       <c r="J116" t="n">
-        <v>41.92978016425015</v>
+        <v>41.82325251481323</v>
       </c>
       <c r="K116" t="n">
         <v>0.4309656950866962</v>
@@ -11085,7 +11099,7 @@
         <v>-51.48469630029851</v>
       </c>
       <c r="R116" t="n">
-        <v>-36.32692057529458</v>
+        <v>-35.52136878030612</v>
       </c>
       <c r="S116" t="n">
         <v>-9.687706273537843</v>
@@ -13179,7 +13193,7 @@
         <v>76.8</v>
       </c>
       <c r="X21" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -15403,83 +15417,87 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>162.5390014648438</v>
+        <v>45.7599983215332</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4536379112437317</v>
+        <v>-0.9523862210825129</v>
       </c>
       <c r="F46" t="n">
-        <v>2.052487665405334</v>
+        <v>3.01665963040203</v>
       </c>
       <c r="G46" t="n">
-        <v>3.670658363273338</v>
+        <v>5.559400074375609</v>
       </c>
       <c r="H46" t="n">
-        <v>13.75989751079645</v>
+        <v>17.01828118450424</v>
       </c>
       <c r="I46" t="n">
-        <v>65.45319266692401</v>
+        <v>53.89785577945819</v>
       </c>
       <c r="J46" t="n">
-        <v>9.945181945279062</v>
+        <v>26.55932112184005</v>
       </c>
       <c r="K46" t="n">
-        <v>0.9788170950808129</v>
+        <v>0.5122357292179918</v>
       </c>
       <c r="L46" t="n">
-        <v>159.0005133284217</v>
+        <v>45.16994268429265</v>
       </c>
       <c r="M46" t="n">
-        <v>155.9758671175692</v>
+        <v>44.07865702561099</v>
       </c>
       <c r="N46" t="n">
-        <v>146.2743544108127</v>
+        <v>38.99714510207828</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1672610832034351</v>
+        <v>-0.09362646135646041</v>
       </c>
       <c r="P46" t="n">
-        <v>96.18696861654195</v>
+        <v>57.97411596023506</v>
       </c>
       <c r="Q46" t="n">
-        <v>-3.813031383458057</v>
+        <v>-42.02588403976493</v>
       </c>
       <c r="R46" t="n">
-        <v>110.0274831366821</v>
+        <v>-4.14939351047682</v>
       </c>
       <c r="S46" t="n">
-        <v>6.359075240754697</v>
+        <v>-1.591401459068376</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W46" t="n">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="X46" t="n">
-        <v>73.59999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -15488,94 +15506,86 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (65) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Bear Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>45.7599983215332</v>
+        <v>199.25</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.9523862210825129</v>
+        <v>5.989677205071087</v>
       </c>
       <c r="F47" t="n">
-        <v>3.01665963040203</v>
+        <v>10.90392738426855</v>
       </c>
       <c r="G47" t="n">
-        <v>5.559400074375609</v>
+        <v>0.2969879829933575</v>
       </c>
       <c r="H47" t="n">
-        <v>17.01828118450424</v>
+        <v>59.11994733877801</v>
       </c>
       <c r="I47" t="n">
-        <v>53.89785577945819</v>
+        <v>61.00399934266526</v>
       </c>
       <c r="J47" t="n">
-        <v>26.55932112184005</v>
+        <v>25.90933183830862</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5122357292179918</v>
+        <v>0.6965404128151647</v>
       </c>
       <c r="L47" t="n">
-        <v>45.16994268429265</v>
+        <v>186.3324815388961</v>
       </c>
       <c r="M47" t="n">
-        <v>44.07865702561099</v>
+        <v>176.8514671638395</v>
       </c>
       <c r="N47" t="n">
-        <v>38.99714510207828</v>
+        <v>134.8966729737741</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.09362646135646041</v>
+        <v>-0.04224641687515485</v>
       </c>
       <c r="P47" t="n">
-        <v>57.97411596023506</v>
+        <v>82.33082623823213</v>
       </c>
       <c r="Q47" t="n">
-        <v>-42.02588403976493</v>
+        <v>-17.66917376176787</v>
       </c>
       <c r="R47" t="n">
-        <v>-4.14939351047682</v>
+        <v>31.07253660631657</v>
       </c>
       <c r="S47" t="n">
-        <v>-1.591401459068376</v>
+        <v>-0.4048773210429069</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Bear Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="n">
-        <v>68.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="X47" t="n">
-        <v>72.40000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -15584,73 +15594,73 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); pattern: Bear Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); RSI in forza (61) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>199.25</v>
+        <v>52.0099983215332</v>
       </c>
       <c r="E48" t="n">
-        <v>5.989677205071087</v>
+        <v>0.7945733711944403</v>
       </c>
       <c r="F48" t="n">
-        <v>10.90392738426855</v>
+        <v>1.681323108503108</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2969879829933575</v>
+        <v>0.9706853354545242</v>
       </c>
       <c r="H48" t="n">
-        <v>59.11994733877801</v>
+        <v>25.90171046365608</v>
       </c>
       <c r="I48" t="n">
-        <v>61.00399934266526</v>
+        <v>58.74856606186125</v>
       </c>
       <c r="J48" t="n">
-        <v>25.90933183830862</v>
+        <v>18.48568976186834</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6965404128151647</v>
+        <v>0.665200043353758</v>
       </c>
       <c r="L48" t="n">
-        <v>186.3324815388961</v>
+        <v>50.69319614821309</v>
       </c>
       <c r="M48" t="n">
-        <v>176.8514671638395</v>
+        <v>48.63919074658908</v>
       </c>
       <c r="N48" t="n">
-        <v>134.8966729737741</v>
+        <v>44.16581083382468</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.04224641687515485</v>
+        <v>-0.1124608706984098</v>
       </c>
       <c r="P48" t="n">
-        <v>82.33082623823213</v>
+        <v>70.58817944949283</v>
       </c>
       <c r="Q48" t="n">
-        <v>-17.66917376176787</v>
+        <v>-29.41182055050717</v>
       </c>
       <c r="R48" t="n">
-        <v>31.07253660631657</v>
+        <v>14.35640206828334</v>
       </c>
       <c r="S48" t="n">
-        <v>-0.4048773210429069</v>
+        <v>-2.438572534738537</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -15658,12 +15668,16 @@
         </is>
       </c>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W48" t="n">
-        <v>67.59999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="X48" t="n">
-        <v>66.8</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -15672,90 +15686,90 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); RSI in forza (61) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>UnitedHealth</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>52.0099983215332</v>
+        <v>425.3599853515625</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7945733711944403</v>
+        <v>-0.5912802847137577</v>
       </c>
       <c r="F49" t="n">
-        <v>1.681323108503108</v>
+        <v>11.84559650868184</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9706853354545242</v>
+        <v>53.75383869002424</v>
       </c>
       <c r="H49" t="n">
-        <v>25.90171046365608</v>
+        <v>1.605190729024852</v>
       </c>
       <c r="I49" t="n">
-        <v>58.74856606186125</v>
+        <v>68.45871892016839</v>
       </c>
       <c r="J49" t="n">
-        <v>18.48568976186834</v>
+        <v>46.29858167286974</v>
       </c>
       <c r="K49" t="n">
-        <v>0.665200043353758</v>
+        <v>0.8448360151512742</v>
       </c>
       <c r="L49" t="n">
-        <v>50.69319614821309</v>
+        <v>367.7965184471579</v>
       </c>
       <c r="M49" t="n">
-        <v>48.63919074658908</v>
+        <v>358.869380319478</v>
       </c>
       <c r="N49" t="n">
-        <v>44.16581083382468</v>
+        <v>413.4087611238132</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.1124608706984098</v>
+        <v>10.24943012717425</v>
       </c>
       <c r="P49" t="n">
-        <v>70.58817944949283</v>
+        <v>97.21084141674864</v>
       </c>
       <c r="Q49" t="n">
-        <v>-29.41182055050717</v>
+        <v>-2.789158583251366</v>
       </c>
       <c r="R49" t="n">
-        <v>14.35640206828334</v>
+        <v>102.1131625874269</v>
       </c>
       <c r="S49" t="n">
-        <v>-2.438572534738537</v>
+        <v>45.07997605974654</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Doji, Bearish Harami</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="X49" t="n">
-        <v>78.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -15764,90 +15778,90 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Top; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 46); RSI in forza (68) — momentum positivo; doji — indecisione del mercato; vicino alla resistenza dei 20g (430.20); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UnitedHealth</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>425.3599853515625</v>
+        <v>161.3370056152344</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.5912802847137577</v>
+        <v>-0.2892290607401815</v>
       </c>
       <c r="F50" t="n">
-        <v>11.84559650868184</v>
+        <v>1.297797003406531</v>
       </c>
       <c r="G50" t="n">
-        <v>53.75383869002424</v>
+        <v>2.904001130511391</v>
       </c>
       <c r="H50" t="n">
-        <v>1.605190729024852</v>
+        <v>12.91862911719468</v>
       </c>
       <c r="I50" t="n">
-        <v>68.45871892016839</v>
+        <v>61.71018241587444</v>
       </c>
       <c r="J50" t="n">
-        <v>46.29858167286974</v>
+        <v>9.945181945279062</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8448360151512742</v>
+        <v>0.845492167440176</v>
       </c>
       <c r="L50" t="n">
-        <v>367.7965184471579</v>
+        <v>158.8860375332208</v>
       </c>
       <c r="M50" t="n">
-        <v>358.869380319478</v>
+        <v>155.9287300254277</v>
       </c>
       <c r="N50" t="n">
-        <v>413.4087611238132</v>
+        <v>146.2623942531051</v>
       </c>
       <c r="O50" t="n">
-        <v>10.24943012717425</v>
+        <v>0.09055251616285731</v>
       </c>
       <c r="P50" t="n">
-        <v>97.21084141674864</v>
+        <v>80.75500528934685</v>
       </c>
       <c r="Q50" t="n">
-        <v>-2.789158583251366</v>
+        <v>-19.24499471065313</v>
       </c>
       <c r="R50" t="n">
-        <v>102.1131625874269</v>
+        <v>97.79504397761916</v>
       </c>
       <c r="S50" t="n">
-        <v>45.07997605974654</v>
+        <v>5.572536835476449</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Doji, Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W50" t="n">
         <v>67.40000000000001</v>
       </c>
       <c r="X50" t="n">
-        <v>73.90000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -15856,7 +15870,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 46); RSI in forza (68) — momentum positivo; doji — indecisione del mercato; vicino alla resistenza dei 20g (430.20); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (62) — momentum positivo; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
@@ -18265,52 +18279,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.33552360534668</v>
+        <v>1.334988713264465</v>
       </c>
       <c r="E77" t="n">
-        <v>1.268753801018629</v>
+        <v>1.228194536946448</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.6637587744611317</v>
+        <v>-0.7035440457178632</v>
       </c>
       <c r="G77" t="n">
-        <v>-1.224677502061344</v>
+        <v>-1.26423811911881</v>
       </c>
       <c r="H77" t="n">
-        <v>0.2176878853985764</v>
+        <v>0.1775495849348996</v>
       </c>
       <c r="I77" t="n">
-        <v>48.37516140821143</v>
+        <v>48.1656696929986</v>
       </c>
       <c r="J77" t="n">
         <v>8.445603970678251</v>
       </c>
       <c r="K77" t="n">
-        <v>0.3871741041073808</v>
+        <v>0.3756807699251772</v>
       </c>
       <c r="L77" t="n">
-        <v>1.33915811988631</v>
+        <v>1.339107177783242</v>
       </c>
       <c r="M77" t="n">
-        <v>1.335778697764153</v>
+        <v>1.335757721604066</v>
       </c>
       <c r="N77" t="n">
-        <v>1.306191940274505</v>
+        <v>1.30618661796523</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.002481013949176832</v>
+        <v>-0.002515149512258438</v>
       </c>
       <c r="P77" t="n">
-        <v>41.22084730378082</v>
+        <v>40.18186280866199</v>
       </c>
       <c r="Q77" t="n">
-        <v>-58.77915269621918</v>
+        <v>-59.81813719133801</v>
       </c>
       <c r="R77" t="n">
-        <v>-74.36476467415059</v>
+        <v>-75.64335678897294</v>
       </c>
       <c r="S77" t="n">
-        <v>-1.945856586858108</v>
+        <v>-1.985128363657873</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -18328,7 +18342,7 @@
         </is>
       </c>
       <c r="W77" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="X77" t="n">
         <v>59</v>
@@ -18361,52 +18375,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.144295692443848</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="E78" t="n">
-        <v>0.7151907420130277</v>
+        <v>0.6921393650368701</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.801115465822423</v>
+        <v>-1.823590918525819</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.843574889172495</v>
+        <v>-2.865811747032609</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6247846442251737</v>
+        <v>0.6017539591131493</v>
       </c>
       <c r="I78" t="n">
-        <v>41.66360970463042</v>
+        <v>41.51846349056211</v>
       </c>
       <c r="J78" t="n">
         <v>16.14987160359328</v>
       </c>
       <c r="K78" t="n">
-        <v>0.1323338664952269</v>
+        <v>0.1277493789869589</v>
       </c>
       <c r="L78" t="n">
-        <v>1.159674693165957</v>
+        <v>1.159649750041276</v>
       </c>
       <c r="M78" t="n">
-        <v>1.155849568041267</v>
+        <v>1.155839297342869</v>
       </c>
       <c r="N78" t="n">
-        <v>1.123232149170123</v>
+        <v>1.123229543172022</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.003425579577398078</v>
+        <v>-0.003442293602824878</v>
       </c>
       <c r="P78" t="n">
-        <v>22.35794295043309</v>
+        <v>21.85977960183212</v>
       </c>
       <c r="Q78" t="n">
-        <v>-77.64205704956692</v>
+        <v>-78.14022039816788</v>
       </c>
       <c r="R78" t="n">
-        <v>-128.9925082517503</v>
+        <v>-129.4882190153232</v>
       </c>
       <c r="S78" t="n">
-        <v>-3.585072564952696</v>
+        <v>-3.607139711150398</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -20761,52 +20775,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>62185.109375</v>
+        <v>62698.01171875</v>
       </c>
       <c r="E104" t="n">
-        <v>4.456014223886573</v>
+        <v>5.317566692840736</v>
       </c>
       <c r="F104" t="n">
-        <v>-15.48603767174195</v>
+        <v>-14.7889671062411</v>
       </c>
       <c r="G104" t="n">
-        <v>-11.49882392314333</v>
+        <v>-10.76886684675199</v>
       </c>
       <c r="H104" t="n">
-        <v>-33.6726435800817</v>
+        <v>-33.12557601190606</v>
       </c>
       <c r="I104" t="n">
-        <v>36.51220069319579</v>
+        <v>37.15867609873862</v>
       </c>
       <c r="J104" t="n">
         <v>26.69989001937627</v>
       </c>
       <c r="K104" t="n">
-        <v>0.1930743704751001</v>
+        <v>0.2106601213417184</v>
       </c>
       <c r="L104" t="n">
-        <v>71772.30535502026</v>
+        <v>71821.15319728217</v>
       </c>
       <c r="M104" t="n">
-        <v>80724.72043081961</v>
+        <v>80744.83424822157</v>
       </c>
       <c r="N104" t="n">
-        <v>68716.60459259992</v>
+        <v>68721.70809850788</v>
       </c>
       <c r="O104" t="n">
-        <v>-430.3895383852268</v>
+        <v>-397.6573090405054</v>
       </c>
       <c r="P104" t="n">
-        <v>17.71787593868276</v>
+        <v>19.76584440973532</v>
       </c>
       <c r="Q104" t="n">
-        <v>-82.28212406131723</v>
+        <v>-80.23415559026468</v>
       </c>
       <c r="R104" t="n">
-        <v>-70.15854316776078</v>
+        <v>-67.94597034898517</v>
       </c>
       <c r="S104" t="n">
-        <v>-9.599145383791363</v>
+        <v>-8.85351977219926</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -20820,10 +20834,10 @@
       </c>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="n">
-        <v>32.9</v>
+        <v>33.2</v>
       </c>
       <c r="X104" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20853,52 +20867,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.137699961662292</v>
+        <v>1.136399984359741</v>
       </c>
       <c r="E105" t="n">
-        <v>8.603100423045662</v>
+        <v>8.479006575551473</v>
       </c>
       <c r="F105" t="n">
-        <v>-14.54352776208303</v>
+        <v>-14.64117343142373</v>
       </c>
       <c r="G105" t="n">
-        <v>-20.56194423873603</v>
+        <v>-20.65271304679467</v>
       </c>
       <c r="H105" t="n">
-        <v>-49.57533510353211</v>
+        <v>-49.63295215729239</v>
       </c>
       <c r="I105" t="n">
-        <v>34.41627093345076</v>
+        <v>34.34171722695334</v>
       </c>
       <c r="J105" t="n">
         <v>26.18980210004506</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1276460089856344</v>
+        <v>0.1253839427965282</v>
       </c>
       <c r="L105" t="n">
-        <v>1.367798822056294</v>
+        <v>1.367675014694147</v>
       </c>
       <c r="M105" t="n">
-        <v>1.677431877356326</v>
+        <v>1.677380897854265</v>
       </c>
       <c r="N105" t="n">
-        <v>1.402683725491625</v>
+        <v>1.402670790394087</v>
       </c>
       <c r="O105" t="n">
-        <v>0.00633629539991909</v>
+        <v>0.006253333885454126</v>
       </c>
       <c r="P105" t="n">
-        <v>23.79872954829073</v>
+        <v>23.55692774904588</v>
       </c>
       <c r="Q105" t="n">
-        <v>-76.20127045170926</v>
+        <v>-76.44307225095413</v>
       </c>
       <c r="R105" t="n">
-        <v>-49.37638176788406</v>
+        <v>-49.253050687848</v>
       </c>
       <c r="S105" t="n">
-        <v>-22.8603191546199</v>
+        <v>-22.94846175601239</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -21141,52 +21155,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>82.19000244140625</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="E108" t="n">
-        <v>15.25257485452753</v>
+        <v>16.05186832749732</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.131593548272857</v>
+        <v>0.5610084654653402</v>
       </c>
       <c r="G108" t="n">
-        <v>-5.576601722580632</v>
+        <v>-4.92176163736755</v>
       </c>
       <c r="H108" t="n">
-        <v>-44.5583055999837</v>
+        <v>-44.17380933584164</v>
       </c>
       <c r="I108" t="n">
-        <v>42.73060598087816</v>
+        <v>43.08363708821363</v>
       </c>
       <c r="J108" t="n">
-        <v>36.41395833640571</v>
+        <v>36.3706862521602</v>
       </c>
       <c r="K108" t="n">
-        <v>0.5099045572523577</v>
+        <v>0.5289891301356819</v>
       </c>
       <c r="L108" t="n">
-        <v>87.3097853428178</v>
+        <v>87.36407102803915</v>
       </c>
       <c r="M108" t="n">
-        <v>113.5564705849316</v>
+        <v>113.5788235141404</v>
       </c>
       <c r="N108" t="n">
-        <v>113.8762520988705</v>
+        <v>113.881923737625</v>
       </c>
       <c r="O108" t="n">
-        <v>2.165141293934727</v>
+        <v>2.201517342835194</v>
       </c>
       <c r="P108" t="n">
-        <v>57.52749463248983</v>
+        <v>59.03336039595818</v>
       </c>
       <c r="Q108" t="n">
-        <v>-42.47250536751017</v>
+        <v>-40.96663960404182</v>
       </c>
       <c r="R108" t="n">
-        <v>-11.48866578273564</v>
+        <v>-10.62427310283685</v>
       </c>
       <c r="S108" t="n">
-        <v>-4.435892932228381</v>
+        <v>-3.773141864619978</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21194,16 +21208,12 @@
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Bear Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
-        <v>30.4</v>
+        <v>30.9</v>
       </c>
       <c r="X108" t="n">
-        <v>72.09999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21212,7 +21222,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 36); pattern: Bear Flag / Consolidation</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 36)</t>
         </is>
       </c>
     </row>
@@ -21329,52 +21339,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>7.941999912261963</v>
+        <v>8.003000259399414</v>
       </c>
       <c r="E110" t="n">
-        <v>9.394401763543069</v>
+        <v>10.23463049134337</v>
       </c>
       <c r="F110" t="n">
-        <v>-12.98053653321117</v>
+        <v>-12.31216363748836</v>
       </c>
       <c r="G110" t="n">
-        <v>-10.08142867014775</v>
+        <v>-9.390788513282978</v>
       </c>
       <c r="H110" t="n">
-        <v>-45.5601584207865</v>
+        <v>-45.14202076388315</v>
       </c>
       <c r="I110" t="n">
-        <v>38.82459066275896</v>
+        <v>39.21677800075066</v>
       </c>
       <c r="J110" t="n">
         <v>33.87766288270218</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2315483507451034</v>
+        <v>0.2490921795993415</v>
       </c>
       <c r="L110" t="n">
-        <v>9.23058057424179</v>
+        <v>9.236390131112023</v>
       </c>
       <c r="M110" t="n">
-        <v>11.66232766525144</v>
+        <v>11.66471983572741</v>
       </c>
       <c r="N110" t="n">
-        <v>13.18343420274407</v>
+        <v>13.18404117137231</v>
       </c>
       <c r="O110" t="n">
-        <v>0.1081229332336178</v>
+        <v>0.1120158328799961</v>
       </c>
       <c r="P110" t="n">
-        <v>23.99992533203909</v>
+        <v>25.59193337128955</v>
       </c>
       <c r="Q110" t="n">
-        <v>-76.00007466796092</v>
+        <v>-74.40806662871046</v>
       </c>
       <c r="R110" t="n">
-        <v>-45.01541943496667</v>
+        <v>-43.34252854319253</v>
       </c>
       <c r="S110" t="n">
-        <v>-9.563690298235572</v>
+        <v>-8.869073533367523</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -21392,10 +21402,10 @@
         </is>
       </c>
       <c r="W110" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="X110" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21517,52 +21527,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1744.18994140625</v>
+        <v>1764.400024414062</v>
       </c>
       <c r="E112" t="n">
-        <v>11.06934727382134</v>
+        <v>12.35631761732514</v>
       </c>
       <c r="F112" t="n">
-        <v>-12.97940518038053</v>
+        <v>-11.97108985706443</v>
       </c>
       <c r="G112" t="n">
-        <v>-16.49651052010192</v>
+        <v>-15.5289482072095</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.714931079208693</v>
+        <v>-1.587680387277313</v>
       </c>
       <c r="I112" t="n">
-        <v>36.6743814927552</v>
+        <v>37.34068155257297</v>
       </c>
       <c r="J112" t="n">
         <v>28.69207376073257</v>
       </c>
       <c r="K112" t="n">
-        <v>0.2131361118332369</v>
+        <v>0.2320177061029869</v>
       </c>
       <c r="L112" t="n">
-        <v>2080.362592396723</v>
+        <v>2082.287362206991</v>
       </c>
       <c r="M112" t="n">
-        <v>2493.835740900546</v>
+        <v>2494.628293175362</v>
       </c>
       <c r="N112" t="n">
-        <v>2504.569311112561</v>
+        <v>2504.770406465872</v>
       </c>
       <c r="O112" t="n">
-        <v>-10.86346668649276</v>
+        <v>-9.573706403373251</v>
       </c>
       <c r="P112" t="n">
-        <v>24.80326961912234</v>
+        <v>26.91227025617528</v>
       </c>
       <c r="Q112" t="n">
-        <v>-75.19673038087765</v>
+        <v>-73.08772974382472</v>
       </c>
       <c r="R112" t="n">
-        <v>-54.13814587912968</v>
+        <v>-52.23476423891217</v>
       </c>
       <c r="S112" t="n">
-        <v>-11.28424102982871</v>
+        <v>-10.25628368967648</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -21580,10 +21590,10 @@
         </is>
       </c>
       <c r="W112" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="X112" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -21655,7 +21665,7 @@
         <v>-86.41186684705525</v>
       </c>
       <c r="R113" t="n">
-        <v>-61.51845920248106</v>
+        <v>-61.38706640133118</v>
       </c>
       <c r="S113" t="n">
         <v>-34.77236939700853</v>
@@ -21885,52 +21895,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.909999847412109</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="E116" t="n">
-        <v>7.2521374647327</v>
+        <v>8.338630691847971</v>
       </c>
       <c r="F116" t="n">
-        <v>-22.87876859096326</v>
+        <v>-22.0975096102715</v>
       </c>
       <c r="G116" t="n">
-        <v>-23.97811818442498</v>
+        <v>-23.20799591313374</v>
       </c>
       <c r="H116" t="n">
-        <v>-68.24447241189071</v>
+        <v>-67.92278030893101</v>
       </c>
       <c r="I116" t="n">
-        <v>34.5078055763031</v>
+        <v>34.93588890719694</v>
       </c>
       <c r="J116" t="n">
-        <v>39.9463597661663</v>
+        <v>39.80619071900788</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1641669434128665</v>
+        <v>0.1766774438436565</v>
       </c>
       <c r="L116" t="n">
-        <v>8.920053469751149</v>
+        <v>8.926720152766519</v>
       </c>
       <c r="M116" t="n">
-        <v>13.31697812218337</v>
+        <v>13.3197232269544</v>
       </c>
       <c r="N116" t="n">
-        <v>21.52542311784752</v>
+        <v>21.52611963696853</v>
       </c>
       <c r="O116" t="n">
-        <v>0.1261100314748882</v>
+        <v>0.130577278897154</v>
       </c>
       <c r="P116" t="n">
-        <v>25.44304846587029</v>
+        <v>26.90717866724965</v>
       </c>
       <c r="Q116" t="n">
-        <v>-74.55695153412971</v>
+        <v>-73.09282133275035</v>
       </c>
       <c r="R116" t="n">
-        <v>-57.04378685423205</v>
+        <v>-55.68633479871686</v>
       </c>
       <c r="S116" t="n">
-        <v>-25.58639664537676</v>
+        <v>-24.83256667087741</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -21973,52 +21983,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.1821999996900558</v>
+        <v>0.1817999929189682</v>
       </c>
       <c r="E117" t="n">
-        <v>26.81929080679977</v>
+        <v>26.54086833087468</v>
       </c>
       <c r="F117" t="n">
-        <v>-22.56265625947009</v>
+        <v>-22.73266428298242</v>
       </c>
       <c r="G117" t="n">
-        <v>-32.5841832422288</v>
+        <v>-32.73218973634179</v>
       </c>
       <c r="H117" t="n">
-        <v>-74.11839993781932</v>
+        <v>-74.17522109747389</v>
       </c>
       <c r="I117" t="n">
-        <v>35.46758846501636</v>
+        <v>35.39594934724062</v>
       </c>
       <c r="J117" t="n">
-        <v>37.03940095404671</v>
+        <v>37.03199990200294</v>
       </c>
       <c r="K117" t="n">
-        <v>0.2029452460801919</v>
+        <v>0.2008306792699845</v>
       </c>
       <c r="L117" t="n">
-        <v>0.2438165182632546</v>
+        <v>0.2437784223802939</v>
       </c>
       <c r="M117" t="n">
-        <v>0.3774812121957179</v>
+        <v>0.3774655256556752</v>
       </c>
       <c r="N117" t="n">
-        <v>0.521972399722639</v>
+        <v>0.5219684195557626</v>
       </c>
       <c r="O117" t="n">
-        <v>0.004576000362527408</v>
+        <v>0.004550472864885372</v>
       </c>
       <c r="P117" t="n">
-        <v>29.09857894348664</v>
+        <v>28.83103201513348</v>
       </c>
       <c r="Q117" t="n">
-        <v>-70.90142105651336</v>
+        <v>-71.16896798486651</v>
       </c>
       <c r="R117" t="n">
-        <v>-55.27942496097625</v>
+        <v>-55.34046220607726</v>
       </c>
       <c r="S117" t="n">
-        <v>-35.339627802019</v>
+        <v>-35.48158491916631</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -26569,87 +26579,79 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>CAC 40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>162.5390014648438</v>
+        <v>8508.0703125</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3804260658856196</v>
+        <v>1.23846024593508</v>
       </c>
       <c r="F49" t="n">
-        <v>4.285930367741542</v>
+        <v>-0.8470085656848148</v>
       </c>
       <c r="G49" t="n">
-        <v>6.093187536683131</v>
+        <v>15.75022994563811</v>
       </c>
       <c r="H49" t="n">
-        <v>47.88776410497768</v>
+        <v>31.96596980688293</v>
       </c>
       <c r="I49" t="n">
-        <v>63.65245627563166</v>
+        <v>61.02375772956118</v>
       </c>
       <c r="J49" t="n">
-        <v>27.3767733214772</v>
+        <v>20.25340740770403</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8767279602492908</v>
+        <v>0.9190424072220069</v>
       </c>
       <c r="L49" t="n">
-        <v>154.6315885454979</v>
+        <v>8017.549061549589</v>
       </c>
       <c r="M49" t="n">
-        <v>146.0859737153522</v>
+        <v>7516.814290505398</v>
       </c>
       <c r="N49" t="n">
-        <v>131.9592172792647</v>
+        <v>6414.561488370104</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7122027117553245</v>
+        <v>20.4095634821403</v>
       </c>
       <c r="P49" t="n">
-        <v>98.54505877621682</v>
+        <v>88.2001035003296</v>
       </c>
       <c r="Q49" t="n">
-        <v>-1.454941223783176</v>
+        <v>-11.79989649967039</v>
       </c>
       <c r="R49" t="n">
-        <v>122.5933705657518</v>
+        <v>116.1129330983738</v>
       </c>
       <c r="S49" t="n">
-        <v>7.517830973584338</v>
+        <v>17.59421036132602</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="n">
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="X49" t="n">
-        <v>74.3</v>
+        <v>71.8</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -26658,73 +26660,73 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (64) — momentum positivo; pattern: Double Top; doji — indecisione del mercato; vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); RSI in forza (61) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAC40</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CAC 40</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8508.0703125</v>
+        <v>334.4700012207031</v>
       </c>
       <c r="E50" t="n">
-        <v>1.23846024593508</v>
+        <v>2.181289506411033</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.8470085656848148</v>
+        <v>11.37862631259636</v>
       </c>
       <c r="G50" t="n">
-        <v>15.75022994563811</v>
+        <v>50.71647619881227</v>
       </c>
       <c r="H50" t="n">
-        <v>31.96596980688293</v>
+        <v>103.647095734312</v>
       </c>
       <c r="I50" t="n">
-        <v>61.02375772956118</v>
+        <v>69.45571405011987</v>
       </c>
       <c r="J50" t="n">
-        <v>20.25340740770403</v>
+        <v>42.19688223662929</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9190424072220069</v>
+        <v>0.8674561455249195</v>
       </c>
       <c r="L50" t="n">
-        <v>8017.549061549589</v>
+        <v>288.7435547467752</v>
       </c>
       <c r="M50" t="n">
-        <v>7516.814290505398</v>
+        <v>235.7457515951549</v>
       </c>
       <c r="N50" t="n">
-        <v>6414.561488370104</v>
+        <v>163.1935900089675</v>
       </c>
       <c r="O50" t="n">
-        <v>20.4095634821403</v>
+        <v>-1.406551709366589</v>
       </c>
       <c r="P50" t="n">
-        <v>88.2001035003296</v>
+        <v>89.19893023317276</v>
       </c>
       <c r="Q50" t="n">
-        <v>-11.79989649967039</v>
+        <v>-10.80106976682724</v>
       </c>
       <c r="R50" t="n">
-        <v>116.1129330983738</v>
+        <v>56.90722939838383</v>
       </c>
       <c r="S50" t="n">
-        <v>17.59421036132602</v>
+        <v>33.93801040594171</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -26732,12 +26734,16 @@
         </is>
       </c>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W50" t="n">
-        <v>75.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="X50" t="n">
-        <v>71.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -26746,73 +26752,73 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 20); RSI in forza (61) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 42); RSI in forza (69) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>334.4700012207031</v>
+        <v>161.3370056152344</v>
       </c>
       <c r="E51" t="n">
-        <v>2.181289506411033</v>
+        <v>-0.361899495523188</v>
       </c>
       <c r="F51" t="n">
-        <v>11.37862631259636</v>
+        <v>3.514723123049635</v>
       </c>
       <c r="G51" t="n">
-        <v>50.71647619881227</v>
+        <v>5.308615403584938</v>
       </c>
       <c r="H51" t="n">
-        <v>103.647095734312</v>
+        <v>46.79411595247169</v>
       </c>
       <c r="I51" t="n">
-        <v>69.45571405011987</v>
+        <v>62.12245903796074</v>
       </c>
       <c r="J51" t="n">
-        <v>42.19688223662929</v>
+        <v>27.3767733214772</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8674561455249195</v>
+        <v>0.8352508240058203</v>
       </c>
       <c r="L51" t="n">
-        <v>288.7435547467752</v>
+        <v>154.517112750297</v>
       </c>
       <c r="M51" t="n">
-        <v>235.7457515951549</v>
+        <v>146.0388366232106</v>
       </c>
       <c r="N51" t="n">
-        <v>163.1935900089675</v>
+        <v>131.9417970495603</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.406551709366589</v>
+        <v>0.6354941447147469</v>
       </c>
       <c r="P51" t="n">
-        <v>89.19893023317276</v>
+        <v>92.65667304038165</v>
       </c>
       <c r="Q51" t="n">
-        <v>-10.80106976682724</v>
+        <v>-7.343326959618355</v>
       </c>
       <c r="R51" t="n">
-        <v>56.90722939838383</v>
+        <v>117.8389047708363</v>
       </c>
       <c r="S51" t="n">
-        <v>33.93801040594171</v>
+        <v>6.722723427552046</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -26822,14 +26828,14 @@
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W51" t="n">
-        <v>75.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="X51" t="n">
-        <v>68.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -26838,7 +26844,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 42); RSI in forza (69) — momentum positivo</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (62) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
@@ -26925,7 +26931,7 @@
         <v>74.8</v>
       </c>
       <c r="X52" t="n">
-        <v>75.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -28799,52 +28805,52 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.144295692443848</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1830923221352032</v>
+        <v>0.1601627301765163</v>
       </c>
       <c r="F73" t="n">
-        <v>-3.05069133732615</v>
+        <v>-3.072880791023225</v>
       </c>
       <c r="G73" t="n">
-        <v>5.37590049069423</v>
+        <v>5.351782385088533</v>
       </c>
       <c r="H73" t="n">
-        <v>-6.128848976654078</v>
+        <v>-6.150333911284922</v>
       </c>
       <c r="I73" t="n">
-        <v>51.97781031781346</v>
+        <v>51.92693916380263</v>
       </c>
       <c r="J73" t="n">
         <v>41.53072495647007</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5296523543221597</v>
+        <v>0.5283683150152734</v>
       </c>
       <c r="L73" t="n">
-        <v>1.142914807816191</v>
+        <v>1.142889864691511</v>
       </c>
       <c r="M73" t="n">
-        <v>1.123285802906454</v>
+        <v>1.123275532208056</v>
       </c>
       <c r="N73" t="n">
-        <v>1.121889090770169</v>
+        <v>1.121885295077283</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.002672617964168154</v>
+        <v>-0.002689331989594954</v>
       </c>
       <c r="P73" t="n">
-        <v>16.83642020104055</v>
+        <v>16.46128338794474</v>
       </c>
       <c r="Q73" t="n">
-        <v>-83.16357979895945</v>
+        <v>-83.53871661205527</v>
       </c>
       <c r="R73" t="n">
-        <v>7.985410014807637</v>
+        <v>7.868568944549224</v>
       </c>
       <c r="S73" t="n">
-        <v>8.330468686342485</v>
+        <v>8.30567434843481</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -28858,7 +28864,7 @@
         </is>
       </c>
       <c r="W73" t="n">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="X73" t="n">
         <v>68.90000000000001</v>
@@ -29163,73 +29169,69 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.33552360534668</v>
+        <v>1.334988713264465</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7639242474242192</v>
+        <v>0.7235671732122473</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.009653145394662</v>
+        <v>-1.049299882102428</v>
       </c>
       <c r="G77" t="n">
-        <v>3.053006715030793</v>
+        <v>3.011732837789238</v>
       </c>
       <c r="H77" t="n">
-        <v>-5.818873913862211</v>
+        <v>-5.856594504075541</v>
       </c>
       <c r="I77" t="n">
-        <v>52.81686770498219</v>
+        <v>52.73535902336642</v>
       </c>
       <c r="J77" t="n">
         <v>21.76605133944494</v>
       </c>
       <c r="K77" t="n">
-        <v>0.5630040009443538</v>
+        <v>0.5596065079727398</v>
       </c>
       <c r="L77" t="n">
-        <v>1.326449916832296</v>
+        <v>1.326398974729228</v>
       </c>
       <c r="M77" t="n">
-        <v>1.307439479749056</v>
+        <v>1.307418503588969</v>
       </c>
       <c r="N77" t="n">
-        <v>1.332742713552793</v>
+        <v>1.332734961493631</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.002599268211243403</v>
+        <v>-0.002633403774325006</v>
       </c>
       <c r="P77" t="n">
-        <v>41.13960732139747</v>
+        <v>40.49908496806667</v>
       </c>
       <c r="Q77" t="n">
-        <v>-58.86039267860253</v>
+        <v>-59.50091503193333</v>
       </c>
       <c r="R77" t="n">
-        <v>16.83256107768281</v>
+        <v>16.50526806402261</v>
       </c>
       <c r="S77" t="n">
-        <v>5.185840601612202</v>
+        <v>5.143712500638453</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Piercing Pattern</t>
-        </is>
-      </c>
+      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr">
         <is>
           <t>Inside Bar</t>
         </is>
       </c>
       <c r="W77" t="n">
-        <v>56.8</v>
+        <v>56.5</v>
       </c>
       <c r="X77" t="n">
-        <v>63.5</v>
+        <v>57.5</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -29238,7 +29240,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); segnale candlestick: Piercing Pattern; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 22); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -30453,52 +30455,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.137699961662292</v>
+        <v>1.136399984359741</v>
       </c>
       <c r="E91" t="n">
-        <v>9.559622554609803</v>
+        <v>9.434435750182924</v>
       </c>
       <c r="F91" t="n">
-        <v>-17.392098041086</v>
+        <v>-17.48648883055308</v>
       </c>
       <c r="G91" t="n">
-        <v>123.412670497926</v>
+        <v>123.1573910652667</v>
       </c>
       <c r="H91" t="n">
-        <v>8.706033214406972</v>
+        <v>8.58182175216642</v>
       </c>
       <c r="I91" t="n">
-        <v>42.51769061805193</v>
+        <v>42.49271013357987</v>
       </c>
       <c r="J91" t="n">
         <v>38.94285314741881</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1468364540557429</v>
+        <v>0.1463956946851216</v>
       </c>
       <c r="L91" t="n">
-        <v>1.602503007059469</v>
+        <v>1.602379199697321</v>
       </c>
       <c r="M91" t="n">
-        <v>1.326392972800765</v>
+        <v>1.326341993298704</v>
       </c>
       <c r="N91" t="n">
-        <v>1.069001828376019</v>
+        <v>1.068975566208291</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.1900046625387358</v>
+        <v>-0.1900876240532008</v>
       </c>
       <c r="P91" t="n">
-        <v>4.845637591164653</v>
+        <v>4.796404547625306</v>
       </c>
       <c r="Q91" t="n">
-        <v>-95.15436240883535</v>
+        <v>-95.2035954523747</v>
       </c>
       <c r="R91" t="n">
-        <v>-65.87569600819012</v>
+        <v>-65.83751608109058</v>
       </c>
       <c r="S91" t="n">
-        <v>-41.47998196519858</v>
+        <v>-41.54684906351418</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -30519,7 +30521,7 @@
         <v>47</v>
       </c>
       <c r="X91" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -31021,52 +31023,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>62185.109375</v>
+        <v>62698.01171875</v>
       </c>
       <c r="E97" t="n">
-        <v>6.192487419842263</v>
+        <v>7.068362307475362</v>
       </c>
       <c r="F97" t="n">
-        <v>-7.180667648537053</v>
+        <v>-6.415094449633663</v>
       </c>
       <c r="G97" t="n">
-        <v>-11.43638351033386</v>
+        <v>-10.70591142585783</v>
       </c>
       <c r="H97" t="n">
-        <v>66.56938933335259</v>
+        <v>67.9432524823403</v>
       </c>
       <c r="I97" t="n">
-        <v>42.78939649109316</v>
+        <v>43.06916592609986</v>
       </c>
       <c r="J97" t="n">
         <v>30.22243585581547</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1258709896313172</v>
+        <v>0.1318602066049668</v>
       </c>
       <c r="L97" t="n">
-        <v>78121.89513842379</v>
+        <v>78170.7429806857</v>
       </c>
       <c r="M97" t="n">
-        <v>65927.10927732389</v>
+        <v>65947.22309472585</v>
       </c>
       <c r="N97" t="n">
-        <v>49823.73779601275</v>
+        <v>49834.09945952285</v>
       </c>
       <c r="O97" t="n">
-        <v>-6158.88653482241</v>
+        <v>-6126.154305477688</v>
       </c>
       <c r="P97" t="n">
-        <v>6.482577061209667</v>
+        <v>7.231883212718533</v>
       </c>
       <c r="Q97" t="n">
-        <v>-93.51742293879033</v>
+        <v>-92.76811678728147</v>
       </c>
       <c r="R97" t="n">
-        <v>-77.34408143289298</v>
+        <v>-76.55609529156209</v>
       </c>
       <c r="S97" t="n">
-        <v>-35.52543404755701</v>
+        <v>-34.99364828209581</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31080,10 +31082,10 @@
       </c>
       <c r="V97" t="inlineStr"/>
       <c r="W97" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="X97" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -31293,73 +31295,65 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>82.19000244140625</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="E100" t="n">
-        <v>11.78768325366171</v>
+        <v>12.56294719631848</v>
       </c>
       <c r="F100" t="n">
-        <v>-2.579443525455316</v>
+        <v>-1.90381770953344</v>
       </c>
       <c r="G100" t="n">
-        <v>-51.20227630739282</v>
+        <v>-50.86385695240214</v>
       </c>
       <c r="H100" t="n">
-        <v>150.4552237921127</v>
+        <v>152.1921674213626</v>
       </c>
       <c r="I100" t="n">
-        <v>42.3298994151066</v>
+        <v>42.45386201414408</v>
       </c>
       <c r="J100" t="n">
-        <v>26.05158966061029</v>
+        <v>26.04985559407729</v>
       </c>
       <c r="K100" t="n">
-        <v>0.2113270022384859</v>
+        <v>0.2138918221319564</v>
       </c>
       <c r="L100" t="n">
-        <v>118.4412691095029</v>
+        <v>118.4955547947242</v>
       </c>
       <c r="M100" t="n">
-        <v>115.8234781836664</v>
+        <v>115.8527089372471</v>
       </c>
       <c r="N100" t="n">
-        <v>93.75345065545287</v>
+        <v>93.76865064731484</v>
       </c>
       <c r="O100" t="n">
-        <v>-12.41554161225741</v>
+        <v>-12.37916556335694</v>
       </c>
       <c r="P100" t="n">
-        <v>11.29451663134818</v>
+        <v>11.59016701589431</v>
       </c>
       <c r="Q100" t="n">
-        <v>-88.70548336865183</v>
+        <v>-88.40983298410569</v>
       </c>
       <c r="R100" t="n">
-        <v>-89.59679363329131</v>
+        <v>-89.22438440900396</v>
       </c>
       <c r="S100" t="n">
-        <v>-56.57399519189412</v>
+        <v>-56.2728294934784</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="X100" t="n">
-        <v>70.7</v>
+        <v>64.7</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
@@ -31368,7 +31362,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26); segnale candlestick: Bullish Harami</t>
+          <t>trend in sviluppo (ADX 26)</t>
         </is>
       </c>
     </row>
@@ -31669,52 +31663,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.1821999996900558</v>
+        <v>0.1817999929189682</v>
       </c>
       <c r="E104" t="n">
-        <v>26.38559444844348</v>
+        <v>26.10812412114758</v>
       </c>
       <c r="F104" t="n">
-        <v>-35.30173933224128</v>
+        <v>-35.44377963075237</v>
       </c>
       <c r="G104" t="n">
-        <v>-46.70099120214918</v>
+        <v>-46.81800527705406</v>
       </c>
       <c r="H104" t="n">
-        <v>-89.54542657841273</v>
+        <v>-89.56837882959047</v>
       </c>
       <c r="I104" t="n">
-        <v>38.21413802174465</v>
+        <v>38.19360571134847</v>
       </c>
       <c r="J104" t="n">
         <v>30.70524078487225</v>
       </c>
       <c r="K104" t="n">
-        <v>0.1711761778033555</v>
+        <v>0.1708398670396497</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4087730401324859</v>
+        <v>0.4087349442495252</v>
       </c>
       <c r="M104" t="n">
-        <v>0.4950607792438936</v>
+        <v>0.4950450927038509</v>
       </c>
       <c r="N104" t="n">
-        <v>0.4935733238240342</v>
+        <v>0.4935652428791638</v>
       </c>
       <c r="O104" t="n">
-        <v>-0.04804490588325543</v>
+        <v>-0.04807043338089746</v>
       </c>
       <c r="P104" t="n">
-        <v>4.956315205493219</v>
+        <v>4.91074435779804</v>
       </c>
       <c r="Q104" t="n">
-        <v>-95.04368479450677</v>
+        <v>-95.08925564220196</v>
       </c>
       <c r="R104" t="n">
-        <v>-98.6930297432328</v>
+        <v>-98.71115876479834</v>
       </c>
       <c r="S104" t="n">
-        <v>-83.11308581840255</v>
+        <v>-83.1501598031825</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -31728,7 +31722,7 @@
         </is>
       </c>
       <c r="W104" t="n">
-        <v>34.8</v>
+        <v>34.7</v>
       </c>
       <c r="X104" t="n">
         <v>67.90000000000001</v>
@@ -31761,52 +31755,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1744.18994140625</v>
+        <v>1764.400024414062</v>
       </c>
       <c r="E105" t="n">
-        <v>11.12435488761849</v>
+        <v>12.4119626092051</v>
       </c>
       <c r="F105" t="n">
-        <v>-11.2394359092675</v>
+        <v>-10.21095940822332</v>
       </c>
       <c r="G105" t="n">
-        <v>-30.67054553867288</v>
+        <v>-29.86721902228436</v>
       </c>
       <c r="H105" t="n">
-        <v>-35.75598251000682</v>
+        <v>-35.01158140127132</v>
       </c>
       <c r="I105" t="n">
-        <v>41.95918237642785</v>
+        <v>42.18019856256061</v>
       </c>
       <c r="J105" t="n">
         <v>13.65760872685721</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2257813616949586</v>
+        <v>0.2310347574141265</v>
       </c>
       <c r="L105" t="n">
-        <v>2497.349085003687</v>
+        <v>2499.273854813955</v>
       </c>
       <c r="M105" t="n">
-        <v>2412.217813695128</v>
+        <v>2413.010365969944</v>
       </c>
       <c r="N105" t="n">
-        <v>2011.519027523597</v>
+        <v>2011.927312028805</v>
       </c>
       <c r="O105" t="n">
-        <v>-191.6977309180085</v>
+        <v>-190.407970634889</v>
       </c>
       <c r="P105" t="n">
-        <v>6.894938806859921</v>
+        <v>7.481209510658493</v>
       </c>
       <c r="Q105" t="n">
-        <v>-93.10506119314007</v>
+        <v>-92.51879048934151</v>
       </c>
       <c r="R105" t="n">
-        <v>-103.4060933895197</v>
+        <v>-102.2407203766606</v>
       </c>
       <c r="S105" t="n">
-        <v>-52.9323087044635</v>
+        <v>-52.3869312054384</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -31857,52 +31851,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>7.941999912261963</v>
+        <v>8.003000259399414</v>
       </c>
       <c r="E106" t="n">
-        <v>10.46732781592985</v>
+        <v>11.31579739771798</v>
       </c>
       <c r="F106" t="n">
-        <v>-10.19627374175646</v>
+        <v>-9.506515678736127</v>
       </c>
       <c r="G106" t="n">
-        <v>-30.46901698099864</v>
+        <v>-29.93496836001858</v>
       </c>
       <c r="H106" t="n">
-        <v>-75.24976580601368</v>
+        <v>-75.05966597042499</v>
       </c>
       <c r="I106" t="n">
-        <v>41.42164839750207</v>
+        <v>41.54577117058346</v>
       </c>
       <c r="J106" t="n">
         <v>21.04094275559561</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2118689467678845</v>
+        <v>0.2144250374371305</v>
       </c>
       <c r="L106" t="n">
-        <v>12.05216035266497</v>
+        <v>12.0579699095352</v>
       </c>
       <c r="M106" t="n">
-        <v>12.59276218819566</v>
+        <v>12.59515435867164</v>
       </c>
       <c r="N106" t="n">
-        <v>10.85979563288956</v>
+        <v>10.86102796313476</v>
       </c>
       <c r="O106" t="n">
-        <v>-1.00399346567364</v>
+        <v>-1.000100566027261</v>
       </c>
       <c r="P106" t="n">
-        <v>4.439734487794018</v>
+        <v>4.734239278909761</v>
       </c>
       <c r="Q106" t="n">
-        <v>-95.56026551220599</v>
+        <v>-95.26576072109025</v>
       </c>
       <c r="R106" t="n">
-        <v>-100.9548791744951</v>
+        <v>-100.3329189411848</v>
       </c>
       <c r="S106" t="n">
-        <v>-58.24979573068355</v>
+        <v>-57.92912373601937</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -32107,7 +32101,7 @@
         <v>31.7</v>
       </c>
       <c r="X108" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -32789,52 +32783,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.909999847412109</v>
+        <v>6.980000019073486</v>
       </c>
       <c r="E116" t="n">
-        <v>5.874467552541174</v>
+        <v>6.947004609978347</v>
       </c>
       <c r="F116" t="n">
-        <v>-24.60077954339602</v>
+        <v>-23.83696500046619</v>
       </c>
       <c r="G116" t="n">
-        <v>-72.37892013969314</v>
+        <v>-72.09911111300869</v>
       </c>
       <c r="H116" t="n">
-        <v>-61.95210508307181</v>
+        <v>-61.56666959329586</v>
       </c>
       <c r="I116" t="n">
-        <v>39.12523736802475</v>
+        <v>39.20413232289025</v>
       </c>
       <c r="J116" t="n">
         <v>16.96239899989589</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2005941954561051</v>
+        <v>0.2023200386775247</v>
       </c>
       <c r="L116" t="n">
-        <v>15.6740075702936</v>
+        <v>15.68067425330896</v>
       </c>
       <c r="M116" t="n">
-        <v>19.48648044217415</v>
+        <v>19.49026423523693</v>
       </c>
       <c r="N116" t="n">
-        <v>20.89342913179688</v>
+        <v>20.89540096761833</v>
       </c>
       <c r="O116" t="n">
-        <v>-1.13593119586194</v>
+        <v>-1.131463948439676</v>
       </c>
       <c r="P116" t="n">
-        <v>4.025704446241574</v>
+        <v>4.257365187267792</v>
       </c>
       <c r="Q116" t="n">
-        <v>-95.97429555375842</v>
+        <v>-95.74263481273221</v>
       </c>
       <c r="R116" t="n">
-        <v>-76.81782086509412</v>
+        <v>-76.53101202182465</v>
       </c>
       <c r="S116" t="n">
-        <v>-79.91141533187478</v>
+        <v>-79.70791252344425</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -32923,7 +32917,7 @@
         <v>-97.88563390090216</v>
       </c>
       <c r="R117" t="n">
-        <v>-73.14157403768723</v>
+        <v>-73.11694337034973</v>
       </c>
       <c r="S117" t="n">
         <v>-85.99322067411389</v>
@@ -33210,7 +33204,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03/07/2026 19:23:31</t>
+          <t>03/07/2026 21:07:22</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33423,10 +33417,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64.8397735969493</v>
+        <v>64.83242238611403</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1217081405461109</v>
+        <v>0.1214140921127003</v>
       </c>
       <c r="D2" t="n">
         <v>55.17241379310344</v>
@@ -33823,17 +33817,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.947</v>
       </c>
       <c r="D18" t="n">
         <v>0.909</v>
       </c>
       <c r="E18" t="n">
-        <v>0.877</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="19">
@@ -33844,17 +33838,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.947</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D19" t="n">
         <v>0.909</v>
       </c>
       <c r="E19" t="n">
-        <v>0.888</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="20">
@@ -33881,22 +33875,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RUSSELL</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MSCIWORLD</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.931</v>
+        <v>0.926</v>
       </c>
       <c r="D21" t="n">
-        <v>0.904</v>
+        <v>0.908</v>
       </c>
       <c r="E21" t="n">
-        <v>0.916</v>
+        <v>0.907</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -2235,52 +2235,52 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>162.3860015869141</v>
+        <v>162.3529968261719</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1937381838113872</v>
+        <v>0.1733739262749889</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01416270590197666</v>
+        <v>-0.006165053133166953</v>
       </c>
       <c r="G20" t="n">
-        <v>1.112076846527188</v>
+        <v>1.091525937755167</v>
       </c>
       <c r="H20" t="n">
-        <v>1.890533821607931</v>
+        <v>1.869824692386124</v>
       </c>
       <c r="I20" t="n">
-        <v>60.64604092099925</v>
+        <v>60.32969727694936</v>
       </c>
       <c r="J20" t="n">
         <v>24.2491396490032</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7330301684300683</v>
+        <v>0.7142914277787237</v>
       </c>
       <c r="L20" t="n">
-        <v>161.8342047309964</v>
+        <v>161.8310614204495</v>
       </c>
       <c r="M20" t="n">
-        <v>160.7957511688798</v>
+        <v>160.794456864537</v>
       </c>
       <c r="N20" t="n">
-        <v>157.2307166188995</v>
+        <v>157.23038821332</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.07560521941356635</v>
+        <v>-0.07771150613898214</v>
       </c>
       <c r="P20" t="n">
-        <v>79.69330983006031</v>
+        <v>78.20392761726389</v>
       </c>
       <c r="Q20" t="n">
-        <v>-20.30669016993968</v>
+        <v>-21.79607238273611</v>
       </c>
       <c r="R20" t="n">
-        <v>28.3908961440467</v>
+        <v>27.60057413905135</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6801456467008027</v>
+        <v>0.6596825274288953</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (61) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (160.62); vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (60) — momentum positivo; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (160.62); vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
@@ -2423,52 +2423,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.264500141143799</v>
+        <v>6.270500183105469</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5003154804925858</v>
+        <v>-0.4050162117817391</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4973151088494498</v>
+        <v>0.5935698928070776</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.459696530508061</v>
+        <v>-3.36723171148684</v>
       </c>
       <c r="H22" t="n">
-        <v>2.637834925668159</v>
+        <v>2.736139866610587</v>
       </c>
       <c r="I22" t="n">
-        <v>51.58998183120526</v>
+        <v>51.92718591234136</v>
       </c>
       <c r="J22" t="n">
         <v>29.8588005293929</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6662197673007209</v>
+        <v>0.6787963905002159</v>
       </c>
       <c r="L22" t="n">
-        <v>6.236540149633912</v>
+        <v>6.237111582201691</v>
       </c>
       <c r="M22" t="n">
-        <v>6.205960848648461</v>
+        <v>6.206196144411664</v>
       </c>
       <c r="N22" t="n">
-        <v>5.769826866986943</v>
+        <v>5.769886568897009</v>
       </c>
       <c r="O22" t="n">
-        <v>0.01765870905536184</v>
+        <v>0.01804161771616331</v>
       </c>
       <c r="P22" t="n">
-        <v>67.02558876230277</v>
+        <v>68.64067401539228</v>
       </c>
       <c r="Q22" t="n">
-        <v>-32.97441123769722</v>
+        <v>-31.35932598460772</v>
       </c>
       <c r="R22" t="n">
-        <v>30.16735452679625</v>
+        <v>31.08773308001905</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.347990475175222</v>
+        <v>-3.255418665810916</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3421,87 +3421,79 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1844.760009765625</v>
+        <v>1065.219970703125</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9893417404384874</v>
+        <v>-2.76048338713315</v>
       </c>
       <c r="F33" t="n">
-        <v>2.158167070190409</v>
+        <v>0.9514885120201377</v>
       </c>
       <c r="G33" t="n">
-        <v>17.00755959499951</v>
+        <v>-2.333434697640191</v>
       </c>
       <c r="H33" t="n">
-        <v>-15.36835156308102</v>
+        <v>15.04076425941605</v>
       </c>
       <c r="I33" t="n">
-        <v>57.33169353042391</v>
+        <v>51.35747364423131</v>
       </c>
       <c r="J33" t="n">
-        <v>46.76178806691241</v>
+        <v>15.57072832173356</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7251520713318569</v>
+        <v>0.5109689192756078</v>
       </c>
       <c r="L33" t="n">
-        <v>1785.042435387226</v>
+        <v>1065.498254723106</v>
       </c>
       <c r="M33" t="n">
-        <v>1809.761910222222</v>
+        <v>1028.129917249498</v>
       </c>
       <c r="N33" t="n">
-        <v>2209.692309509196</v>
+        <v>907.1116640975716</v>
       </c>
       <c r="O33" t="n">
-        <v>17.83363838153499</v>
+        <v>2.941155358447524</v>
       </c>
       <c r="P33" t="n">
-        <v>57.20294531923392</v>
+        <v>41.20801028369081</v>
       </c>
       <c r="Q33" t="n">
-        <v>-42.79705468076607</v>
+        <v>-58.79198971630919</v>
       </c>
       <c r="R33" t="n">
-        <v>59.51927986225201</v>
+        <v>4.143893368200481</v>
       </c>
       <c r="S33" t="n">
-        <v>17.3818906918827</v>
+        <v>-3.086053049953053</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="n">
         <v>54.9</v>
       </c>
       <c r="X33" t="n">
-        <v>69.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3510,19 +3502,19 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto</t>
+          <t>in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3531,52 +3523,52 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1065.219970703125</v>
+        <v>495.760009765625</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.76048338713315</v>
+        <v>-1.034054507632809</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9514885120201377</v>
+        <v>-11.1366045728502</v>
       </c>
       <c r="G34" t="n">
-        <v>-2.333434697640191</v>
+        <v>-2.272861397836079</v>
       </c>
       <c r="H34" t="n">
-        <v>15.04076425941605</v>
+        <v>78.08110337279568</v>
       </c>
       <c r="I34" t="n">
-        <v>51.35747364423131</v>
+        <v>46.07181224516254</v>
       </c>
       <c r="J34" t="n">
-        <v>15.57072832173356</v>
+        <v>22.84708152849888</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5109689192756078</v>
+        <v>0.04129788050723067</v>
       </c>
       <c r="L34" t="n">
-        <v>1065.498254723106</v>
+        <v>523.5279789596494</v>
       </c>
       <c r="M34" t="n">
-        <v>1028.129917249498</v>
+        <v>480.922352547149</v>
       </c>
       <c r="N34" t="n">
-        <v>907.1116640975716</v>
+        <v>328.1615440202385</v>
       </c>
       <c r="O34" t="n">
-        <v>2.941155358447524</v>
+        <v>-7.919427590411392</v>
       </c>
       <c r="P34" t="n">
-        <v>41.20801028369081</v>
+        <v>28.54964780525607</v>
       </c>
       <c r="Q34" t="n">
-        <v>-58.79198971630919</v>
+        <v>-71.45035219474393</v>
       </c>
       <c r="R34" t="n">
-        <v>4.143893368200481</v>
+        <v>-140.2585437901386</v>
       </c>
       <c r="S34" t="n">
-        <v>-3.086053049953053</v>
+        <v>-3.262560751706189</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3586,10 +3578,10 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="X34" t="n">
-        <v>60.4</v>
+        <v>56.3</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3598,86 +3590,90 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 23); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>XLRE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>495.760009765625</v>
+        <v>45.41999816894531</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.034054507632809</v>
+        <v>-0.08799145695761457</v>
       </c>
       <c r="F35" t="n">
-        <v>-11.1366045728502</v>
+        <v>2.182221348384328</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.272861397836079</v>
+        <v>0.7095337154120696</v>
       </c>
       <c r="H35" t="n">
-        <v>78.08110337279568</v>
+        <v>2.113306286832128</v>
       </c>
       <c r="I35" t="n">
-        <v>46.07181224516254</v>
+        <v>58.89327496316351</v>
       </c>
       <c r="J35" t="n">
-        <v>22.84708152849888</v>
+        <v>17.58998654524553</v>
       </c>
       <c r="K35" t="n">
-        <v>0.04129788050723067</v>
+        <v>0.9736716093971286</v>
       </c>
       <c r="L35" t="n">
-        <v>523.5279789596494</v>
+        <v>44.65602923604253</v>
       </c>
       <c r="M35" t="n">
-        <v>480.922352547149</v>
+        <v>44.31483953974693</v>
       </c>
       <c r="N35" t="n">
-        <v>328.1615440202385</v>
+        <v>42.97089120258735</v>
       </c>
       <c r="O35" t="n">
-        <v>-7.919427590411392</v>
+        <v>0.07976002071306521</v>
       </c>
       <c r="P35" t="n">
-        <v>28.54964780525607</v>
+        <v>73.21419535151674</v>
       </c>
       <c r="Q35" t="n">
-        <v>-71.45035219474393</v>
+        <v>-26.78580464848327</v>
       </c>
       <c r="R35" t="n">
-        <v>-140.2585437901386</v>
+        <v>203.6715065905865</v>
       </c>
       <c r="S35" t="n">
-        <v>-3.262560751706189</v>
+        <v>3.297695947207435</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W35" t="n">
-        <v>54.8</v>
+        <v>54.6</v>
       </c>
       <c r="X35" t="n">
-        <v>56.3</v>
+        <v>65.7</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3686,90 +3682,90 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Bottom; vicino alla resistenza dei 20g (45.94)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XLRE</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>45.41999816894531</v>
+        <v>1840.780029296875</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.08799145695761457</v>
+        <v>-1.202952445345951</v>
       </c>
       <c r="F36" t="n">
-        <v>2.182221348384328</v>
+        <v>1.937765767305333</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7095337154120696</v>
+        <v>16.75512144617855</v>
       </c>
       <c r="H36" t="n">
-        <v>2.113306286832128</v>
+        <v>-15.55094024997469</v>
       </c>
       <c r="I36" t="n">
-        <v>58.89327496316351</v>
+        <v>56.87580036160382</v>
       </c>
       <c r="J36" t="n">
-        <v>17.58998654524553</v>
+        <v>46.76178806691241</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9736716093971286</v>
+        <v>0.716035354112771</v>
       </c>
       <c r="L36" t="n">
-        <v>44.65602923604253</v>
+        <v>1784.663389628297</v>
       </c>
       <c r="M36" t="n">
-        <v>44.31483953974693</v>
+        <v>1809.605832556781</v>
       </c>
       <c r="N36" t="n">
-        <v>42.97089120258735</v>
+        <v>2209.652707713487</v>
       </c>
       <c r="O36" t="n">
-        <v>0.07976002071306521</v>
+        <v>17.57964532597934</v>
       </c>
       <c r="P36" t="n">
-        <v>73.21419535151674</v>
+        <v>55.48936237307377</v>
       </c>
       <c r="Q36" t="n">
-        <v>-26.78580464848327</v>
+        <v>-44.51063762692623</v>
       </c>
       <c r="R36" t="n">
-        <v>203.6715065905865</v>
+        <v>58.70032000754841</v>
       </c>
       <c r="S36" t="n">
-        <v>3.297695947207435</v>
+        <v>17.12864494183093</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W36" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
       <c r="X36" t="n">
-        <v>65.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -3778,7 +3774,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Bottom; vicino alla resistenza dei 20g (45.94)</t>
+          <t>trend molto direzionale (ADX 47); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
@@ -3891,52 +3887,52 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>81.80000305175781</v>
+        <v>81.76999664306641</v>
       </c>
       <c r="E38" t="n">
-        <v>3.60988754107745</v>
+        <v>3.571880688827567</v>
       </c>
       <c r="F38" t="n">
-        <v>14.54978134269644</v>
+        <v>14.50776144751007</v>
       </c>
       <c r="G38" t="n">
-        <v>7.560814949720229</v>
+        <v>7.521358792603472</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.444836564899855</v>
+        <v>-2.48062238390695</v>
       </c>
       <c r="I38" t="n">
-        <v>57.2358132349425</v>
+        <v>57.18941128081762</v>
       </c>
       <c r="J38" t="n">
         <v>45.58285256786808</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9947854556316883</v>
+        <v>0.9934734301506369</v>
       </c>
       <c r="L38" t="n">
-        <v>76.81993773720117</v>
+        <v>76.81707998399246</v>
       </c>
       <c r="M38" t="n">
-        <v>81.75251487962113</v>
+        <v>81.75133815771166</v>
       </c>
       <c r="N38" t="n">
-        <v>78.50230398325377</v>
+        <v>78.502005412023</v>
       </c>
       <c r="O38" t="n">
-        <v>2.048132377461972</v>
+        <v>2.046217438559737</v>
       </c>
       <c r="P38" t="n">
-        <v>98.20361500336038</v>
+        <v>98.00397154941189</v>
       </c>
       <c r="Q38" t="n">
-        <v>-1.796384996639614</v>
+        <v>-1.996028450588118</v>
       </c>
       <c r="R38" t="n">
-        <v>54.48675572917882</v>
+        <v>54.41785469854996</v>
       </c>
       <c r="S38" t="n">
-        <v>6.524289720665211</v>
+        <v>6.485213788468758</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4263,52 +4259,52 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.244000434875488</v>
+        <v>8.237000465393066</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.055594885245381</v>
+        <v>-1.139608444163887</v>
       </c>
       <c r="F42" t="n">
-        <v>3.153323438588496</v>
+        <v>3.065736092883631</v>
       </c>
       <c r="G42" t="n">
-        <v>12.29544181333697</v>
+        <v>12.20009190743654</v>
       </c>
       <c r="H42" t="n">
-        <v>-15.18457556186241</v>
+        <v>-15.25659222263235</v>
       </c>
       <c r="I42" t="n">
-        <v>56.10899056027493</v>
+        <v>55.93573932111558</v>
       </c>
       <c r="J42" t="n">
         <v>25.64458118142502</v>
       </c>
       <c r="K42" t="n">
-        <v>0.7552427501634977</v>
+        <v>0.7509800803735913</v>
       </c>
       <c r="L42" t="n">
-        <v>7.998006069115546</v>
+        <v>7.997339405355316</v>
       </c>
       <c r="M42" t="n">
-        <v>8.134456948225891</v>
+        <v>8.134182439618737</v>
       </c>
       <c r="N42" t="n">
-        <v>9.897204771028695</v>
+        <v>9.897135119591059</v>
       </c>
       <c r="O42" t="n">
-        <v>0.08522825581561908</v>
+        <v>0.08478153411645625</v>
       </c>
       <c r="P42" t="n">
-        <v>66.51187658338216</v>
+        <v>65.86214771683152</v>
       </c>
       <c r="Q42" t="n">
-        <v>-33.48812341661783</v>
+        <v>-34.13785228316848</v>
       </c>
       <c r="R42" t="n">
-        <v>68.91796100934754</v>
+        <v>68.50535437603649</v>
       </c>
       <c r="S42" t="n">
-        <v>13.10974632396573</v>
+        <v>13.01370499322019</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4329,7 +4325,7 @@
         <v>53.4</v>
       </c>
       <c r="X42" t="n">
-        <v>63.9</v>
+        <v>63.8</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4451,52 +4447,52 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.34551465511322</v>
+        <v>1.345243215560913</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.6361682571019767</v>
+        <v>-0.6562135787202328</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2946640229454234</v>
+        <v>0.2744309183874583</v>
       </c>
       <c r="G44" t="n">
-        <v>1.157137066233793</v>
+        <v>1.136729969296146</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.4036622737605966</v>
+        <v>-0.4237545003455079</v>
       </c>
       <c r="I44" t="n">
-        <v>57.02937211588618</v>
+        <v>56.79927129688107</v>
       </c>
       <c r="J44" t="n">
         <v>37.79440234339152</v>
       </c>
       <c r="K44" t="n">
-        <v>0.8323319777750371</v>
+        <v>0.8266598281057449</v>
       </c>
       <c r="L44" t="n">
-        <v>1.337161297981689</v>
+        <v>1.337135446595755</v>
       </c>
       <c r="M44" t="n">
-        <v>1.337858328071377</v>
+        <v>1.337847683383052</v>
       </c>
       <c r="N44" t="n">
-        <v>1.338596174843244</v>
+        <v>1.338593473952176</v>
       </c>
       <c r="O44" t="n">
-        <v>0.00242983278358758</v>
+        <v>0.00241251014549154</v>
       </c>
       <c r="P44" t="n">
-        <v>72.87402428447528</v>
+        <v>72.05117085862966</v>
       </c>
       <c r="Q44" t="n">
-        <v>-27.12597571552472</v>
+        <v>-27.94882914137034</v>
       </c>
       <c r="R44" t="n">
-        <v>80.36895719598726</v>
+        <v>79.87004706983714</v>
       </c>
       <c r="S44" t="n">
-        <v>1.917350924250005</v>
+        <v>1.896790464353071</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4639,52 +4635,52 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>100.7630004882812</v>
+        <v>100.754997253418</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0327579968708358</v>
+        <v>0.0248127624852934</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.2050121124287263</v>
+        <v>-0.2129384616082142</v>
       </c>
       <c r="G46" t="n">
-        <v>1.228651357750921</v>
+        <v>1.220611137950156</v>
       </c>
       <c r="H46" t="n">
-        <v>2.714579057677202</v>
+        <v>2.706420816099464</v>
       </c>
       <c r="I46" t="n">
-        <v>52.25412950038631</v>
+        <v>52.12884679839372</v>
       </c>
       <c r="J46" t="n">
         <v>34.83444672095906</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2281192295341598</v>
+        <v>0.2218353596235642</v>
       </c>
       <c r="L46" t="n">
-        <v>100.7767415652945</v>
+        <v>100.7759793524503</v>
       </c>
       <c r="M46" t="n">
-        <v>100.1919978016352</v>
+        <v>100.1916839492876</v>
       </c>
       <c r="N46" t="n">
-        <v>99.46539983229884</v>
+        <v>99.46532019812109</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.1200104494833438</v>
+        <v>-0.1205211972353011</v>
       </c>
       <c r="P46" t="n">
-        <v>33.0401611328125</v>
+        <v>32.39990234375</v>
       </c>
       <c r="Q46" t="n">
-        <v>-66.9598388671875</v>
+        <v>-67.60009765625</v>
       </c>
       <c r="R46" t="n">
-        <v>-27.08397612437632</v>
+        <v>-27.3136145553963</v>
       </c>
       <c r="S46" t="n">
-        <v>0.6723990159003046</v>
+        <v>0.6644029771790461</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4731,52 +4727,52 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>88.16000366210938</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="E47" t="n">
-        <v>4.665796211027073</v>
+        <v>4.582681737052652</v>
       </c>
       <c r="F47" t="n">
-        <v>15.98474040837785</v>
+        <v>15.89263762946558</v>
       </c>
       <c r="G47" t="n">
-        <v>11.65147503078667</v>
+        <v>11.56281327162954</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.456288624444103</v>
+        <v>-2.533747494046024</v>
       </c>
       <c r="I47" t="n">
-        <v>60.56867554598026</v>
+        <v>60.47543634238978</v>
       </c>
       <c r="J47" t="n">
         <v>53.00212719415311</v>
       </c>
       <c r="K47" t="n">
-        <v>1.022229343663846</v>
+        <v>1.01978644706191</v>
       </c>
       <c r="L47" t="n">
-        <v>81.19416603361091</v>
+        <v>81.1874986693996</v>
       </c>
       <c r="M47" t="n">
-        <v>86.11156704001108</v>
+        <v>86.1088216547476</v>
       </c>
       <c r="N47" t="n">
-        <v>83.08909913383954</v>
+        <v>83.08840254354881</v>
       </c>
       <c r="O47" t="n">
-        <v>2.381482795891696</v>
+        <v>2.377015092009929</v>
       </c>
       <c r="P47" t="n">
-        <v>99.1199338282228</v>
+        <v>98.73485504360463</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.8800661717771998</v>
+        <v>-1.265144956395367</v>
       </c>
       <c r="R47" t="n">
-        <v>69.07599957477206</v>
+        <v>68.92148411190841</v>
       </c>
       <c r="S47" t="n">
-        <v>10.82338187309637</v>
+        <v>10.73537769769337</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4793,7 +4789,7 @@
         <v>53</v>
       </c>
       <c r="X47" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -4802,7 +4798,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 53); RSI in forza (61) — momentum positivo; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (88.32); in zona Fib Fib 61.8 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 53); RSI in forza (60) — momentum positivo; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (88.32); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -5931,52 +5927,52 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>64142.98828125</v>
+        <v>64064.3515625</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5544928933495452</v>
+        <v>0.4312171372835572</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6034822471416623</v>
+        <v>0.4801464321021465</v>
       </c>
       <c r="G60" t="n">
-        <v>6.875714892133056</v>
+        <v>6.744689572633944</v>
       </c>
       <c r="H60" t="n">
-        <v>-17.90373973184609</v>
+        <v>-18.00438643855746</v>
       </c>
       <c r="I60" t="n">
-        <v>52.67416975063283</v>
+        <v>52.3772342136029</v>
       </c>
       <c r="J60" t="n">
         <v>14.92642088722812</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7041137263741017</v>
+        <v>0.6941943157389759</v>
       </c>
       <c r="L60" t="n">
-        <v>63363.24420462493</v>
+        <v>63355.75499331542</v>
       </c>
       <c r="M60" t="n">
-        <v>65008.34017405026</v>
+        <v>65005.25638115811</v>
       </c>
       <c r="N60" t="n">
-        <v>74293.94405501561</v>
+        <v>74293.16160010269</v>
       </c>
       <c r="O60" t="n">
-        <v>357.112573651993</v>
+        <v>352.0941619710825</v>
       </c>
       <c r="P60" t="n">
-        <v>67.75328338865648</v>
+        <v>65.89503494773533</v>
       </c>
       <c r="Q60" t="n">
-        <v>-32.24671661134352</v>
+        <v>-34.10496505226468</v>
       </c>
       <c r="R60" t="n">
-        <v>40.83586161776874</v>
+        <v>39.94727827483753</v>
       </c>
       <c r="S60" t="n">
-        <v>7.011818113982948</v>
+        <v>6.88062593741865</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -8323,73 +8319,77 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>5.690000057220459</v>
+        <v>1.144557595252991</v>
       </c>
       <c r="E86" t="n">
-        <v>0.636721843097976</v>
+        <v>-0.2151850716330839</v>
       </c>
       <c r="F86" t="n">
-        <v>1.861799000929687</v>
+        <v>0.1064431412831635</v>
       </c>
       <c r="G86" t="n">
-        <v>4.288860197476652</v>
+        <v>-0.5368037067612685</v>
       </c>
       <c r="H86" t="n">
-        <v>-10.81504772482161</v>
+        <v>-2.543211152239533</v>
       </c>
       <c r="I86" t="n">
-        <v>58.28725016974831</v>
+        <v>48.03048292792005</v>
       </c>
       <c r="J86" t="n">
-        <v>24.9886108658428</v>
+        <v>27.80186815968384</v>
       </c>
       <c r="K86" t="n">
-        <v>0.9934902166842764</v>
+        <v>0.748879542101891</v>
       </c>
       <c r="L86" t="n">
-        <v>5.553393229776174</v>
+        <v>1.144267941509143</v>
       </c>
       <c r="M86" t="n">
-        <v>5.618021448915357</v>
+        <v>1.151075079167404</v>
       </c>
       <c r="N86" t="n">
-        <v>5.879442380475271</v>
+        <v>1.157495226313116</v>
       </c>
       <c r="O86" t="n">
-        <v>0.02494928483548057</v>
+        <v>0.001247283037769461</v>
       </c>
       <c r="P86" t="n">
-        <v>87.78282544412211</v>
+        <v>71.76673122444588</v>
       </c>
       <c r="Q86" t="n">
-        <v>-12.21717455587788</v>
+        <v>-28.23326877555412</v>
       </c>
       <c r="R86" t="n">
-        <v>186.8389430423845</v>
+        <v>24.18756183346257</v>
       </c>
       <c r="S86" t="n">
-        <v>4.288860197476652</v>
+        <v>-0.1133150723923282</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr"/>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom</t>
@@ -8399,7 +8399,7 @@
         <v>48.3</v>
       </c>
       <c r="X86" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -8408,90 +8408,90 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); pattern: Double Bottom; vicino alla resistenza dei 20g (5.7440); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 28); pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (1.1325); vicino alla resistenza dei 20g (1.1478); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1657000035047531</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="E87" t="n">
-        <v>3.130003501987666</v>
+        <v>0.636721843097976</v>
       </c>
       <c r="F87" t="n">
-        <v>2.309841349871666</v>
+        <v>1.861799000929687</v>
       </c>
       <c r="G87" t="n">
-        <v>11.80384631471587</v>
+        <v>4.288860197476652</v>
       </c>
       <c r="H87" t="n">
-        <v>-35.03005343924271</v>
+        <v>-10.81504772482161</v>
       </c>
       <c r="I87" t="n">
-        <v>48.5881062391691</v>
+        <v>58.28725016974831</v>
       </c>
       <c r="J87" t="n">
-        <v>34.55846322069463</v>
+        <v>24.9886108658428</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5033443732934422</v>
+        <v>0.9934902166842764</v>
       </c>
       <c r="L87" t="n">
-        <v>0.1656961894428842</v>
+        <v>5.553393229776174</v>
       </c>
       <c r="M87" t="n">
-        <v>0.178536019411095</v>
+        <v>5.618021448915357</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2768711644983199</v>
+        <v>5.879442380475271</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0003836358489673094</v>
+        <v>0.02494928483548057</v>
       </c>
       <c r="P87" t="n">
-        <v>22.65783375656837</v>
+        <v>87.78282544412211</v>
       </c>
       <c r="Q87" t="n">
-        <v>-77.34216624343163</v>
+        <v>-12.21717455587788</v>
       </c>
       <c r="R87" t="n">
-        <v>-11.69079150996124</v>
+        <v>186.8389430423845</v>
       </c>
       <c r="S87" t="n">
-        <v>14.19710981139299</v>
+        <v>4.288860197476652</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Double Bottom, Outside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W87" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="X87" t="n">
-        <v>63.7</v>
+        <v>53.6</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -8500,90 +8500,90 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); pattern: Double Bottom</t>
+          <t>trend in sviluppo (ADX 25); pattern: Double Bottom; vicino alla resistenza dei 20g (5.7440); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>25520.244140625</v>
+        <v>0.1659000068902969</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.397518691764399</v>
+        <v>3.254483582948886</v>
       </c>
       <c r="F88" t="n">
-        <v>-2.896950576775703</v>
+        <v>2.433331477883893</v>
       </c>
       <c r="G88" t="n">
-        <v>-3.245695605214372</v>
+        <v>11.93879590618721</v>
       </c>
       <c r="H88" t="n">
-        <v>4.29844294261863</v>
+        <v>-34.95163334874236</v>
       </c>
       <c r="I88" t="n">
-        <v>44.21467486417375</v>
+        <v>48.73885321664058</v>
       </c>
       <c r="J88" t="n">
-        <v>17.81611933198217</v>
+        <v>34.55846322069463</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2068351582978948</v>
+        <v>0.5068481282905395</v>
       </c>
       <c r="L88" t="n">
-        <v>25959.62302976677</v>
+        <v>0.1657152373843646</v>
       </c>
       <c r="M88" t="n">
-        <v>25705.77367242578</v>
+        <v>0.1785438626811164</v>
       </c>
       <c r="N88" t="n">
-        <v>23878.78949457377</v>
+        <v>0.2768731545817582</v>
       </c>
       <c r="O88" t="n">
-        <v>-26.75176633125133</v>
+        <v>0.0003963995977883522</v>
       </c>
       <c r="P88" t="n">
-        <v>25.28792694431977</v>
+        <v>23.11799258027323</v>
       </c>
       <c r="Q88" t="n">
-        <v>-74.71207305568022</v>
+        <v>-76.88200741972676</v>
       </c>
       <c r="R88" t="n">
-        <v>-99.39191192479217</v>
+        <v>-11.30034235475716</v>
       </c>
       <c r="S88" t="n">
-        <v>-1.92691785464183</v>
+        <v>14.33494812218665</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Double Bottom, Outside Bar</t>
         </is>
       </c>
       <c r="W88" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="X88" t="n">
-        <v>64</v>
+        <v>63.7</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -8592,86 +8592,90 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 35); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>25.04999923706055</v>
+        <v>25520.244140625</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.3579958423744034</v>
+        <v>-1.397518691764399</v>
       </c>
       <c r="F89" t="n">
-        <v>3.640873636693565</v>
+        <v>-2.896950576775703</v>
       </c>
       <c r="G89" t="n">
-        <v>-3.801849630030041</v>
+        <v>-3.245695605214372</v>
       </c>
       <c r="H89" t="n">
-        <v>-9.107403038899186</v>
+        <v>4.29844294261863</v>
       </c>
       <c r="I89" t="n">
-        <v>53.63144198923111</v>
+        <v>44.21467486417375</v>
       </c>
       <c r="J89" t="n">
-        <v>48.04255309072217</v>
+        <v>17.81611933198217</v>
       </c>
       <c r="K89" t="n">
-        <v>0.8540572670834483</v>
+        <v>0.2068351582978948</v>
       </c>
       <c r="L89" t="n">
-        <v>24.65529389862379</v>
+        <v>25959.62302976677</v>
       </c>
       <c r="M89" t="n">
-        <v>25.20090211543189</v>
+        <v>25705.77367242578</v>
       </c>
       <c r="N89" t="n">
-        <v>25.75559584375596</v>
+        <v>23878.78949457377</v>
       </c>
       <c r="O89" t="n">
-        <v>0.1679315763273486</v>
+        <v>-26.75176633125133</v>
       </c>
       <c r="P89" t="n">
-        <v>70.44331318871299</v>
+        <v>25.28792694431977</v>
       </c>
       <c r="Q89" t="n">
-        <v>-29.556686811287</v>
+        <v>-74.71207305568022</v>
       </c>
       <c r="R89" t="n">
-        <v>61.20827981318443</v>
+        <v>-99.39191192479217</v>
       </c>
       <c r="S89" t="n">
-        <v>-3.356484709385044</v>
+        <v>-1.92691785464183</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W89" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="X89" t="n">
-        <v>56.4</v>
+        <v>64</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -8680,94 +8684,86 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 48); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Consumer Discr.</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>115.4400024414062</v>
+        <v>25.04999923706055</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.619221029301188</v>
+        <v>-0.3579958423744034</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.535308303617366</v>
+        <v>3.640873636693565</v>
       </c>
       <c r="G90" t="n">
-        <v>-2.549380944121804</v>
+        <v>-3.801849630030041</v>
       </c>
       <c r="H90" t="n">
-        <v>-4.127565044055459</v>
+        <v>-9.107403038899186</v>
       </c>
       <c r="I90" t="n">
-        <v>46.19877912952066</v>
+        <v>53.63144198923111</v>
       </c>
       <c r="J90" t="n">
-        <v>17.06620348943586</v>
+        <v>48.04255309072217</v>
       </c>
       <c r="K90" t="n">
-        <v>0.3574336648178763</v>
+        <v>0.8540572670834483</v>
       </c>
       <c r="L90" t="n">
-        <v>116.5310210712896</v>
+        <v>24.65529389862379</v>
       </c>
       <c r="M90" t="n">
-        <v>116.6307135888351</v>
+        <v>25.20090211543189</v>
       </c>
       <c r="N90" t="n">
-        <v>115.765754960062</v>
+        <v>25.75559584375596</v>
       </c>
       <c r="O90" t="n">
-        <v>0.003144564310692821</v>
+        <v>0.1679315763273486</v>
       </c>
       <c r="P90" t="n">
-        <v>20.96437534088383</v>
+        <v>70.44331318871299</v>
       </c>
       <c r="Q90" t="n">
-        <v>-79.03562465911617</v>
+        <v>-29.556686811287</v>
       </c>
       <c r="R90" t="n">
-        <v>-21.52196073937932</v>
+        <v>61.20827981318443</v>
       </c>
       <c r="S90" t="n">
-        <v>-0.04328982880600352</v>
+        <v>-3.356484709385044</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Shooting Star, Evening Star</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="n">
-        <v>47.2</v>
+        <v>47.6</v>
       </c>
       <c r="X90" t="n">
-        <v>65.2</v>
+        <v>56.4</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -8776,90 +8772,94 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 48); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prysmian</t>
+          <t>Consumer Discr.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>125.3499984741211</v>
+        <v>115.4400024414062</v>
       </c>
       <c r="E91" t="n">
-        <v>-4.531610387923035</v>
+        <v>-1.619221029301188</v>
       </c>
       <c r="F91" t="n">
-        <v>-7.182528218025441</v>
+        <v>-1.535308303617366</v>
       </c>
       <c r="G91" t="n">
-        <v>-15.16074553358978</v>
+        <v>-2.549380944121804</v>
       </c>
       <c r="H91" t="n">
-        <v>5.07124498541589</v>
+        <v>-4.127565044055459</v>
       </c>
       <c r="I91" t="n">
-        <v>33.67585940397817</v>
+        <v>46.19877912952066</v>
       </c>
       <c r="J91" t="n">
-        <v>31.93603390777067</v>
+        <v>17.06620348943586</v>
       </c>
       <c r="K91" t="n">
-        <v>-0.01093610515526593</v>
+        <v>0.3574336648178763</v>
       </c>
       <c r="L91" t="n">
-        <v>138.1182222872415</v>
+        <v>116.5310210712896</v>
       </c>
       <c r="M91" t="n">
-        <v>138.5855421895917</v>
+        <v>116.6307135888351</v>
       </c>
       <c r="N91" t="n">
-        <v>113.8312792799945</v>
+        <v>115.765754960062</v>
       </c>
       <c r="O91" t="n">
-        <v>-1.462543417745644</v>
+        <v>0.003144564310692821</v>
       </c>
       <c r="P91" t="n">
-        <v>7.904418261406647</v>
+        <v>20.96437534088383</v>
       </c>
       <c r="Q91" t="n">
-        <v>-92.09558173859335</v>
+        <v>-79.03562465911617</v>
       </c>
       <c r="R91" t="n">
-        <v>-176.7420186082932</v>
+        <v>-21.52196073937932</v>
       </c>
       <c r="S91" t="n">
-        <v>-18.17885054105456</v>
+        <v>-0.04328982880600352</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Shooting Star, Evening Star</t>
+        </is>
+      </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W91" t="n">
-        <v>46.8</v>
+        <v>47.2</v>
       </c>
       <c r="X91" t="n">
-        <v>69.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -8868,73 +8868,73 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); RSI scarico (34) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Prysmian</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>18.3700008392334</v>
+        <v>125.3499984741211</v>
       </c>
       <c r="E92" t="n">
-        <v>0.1089943179721553</v>
+        <v>-4.531610387923035</v>
       </c>
       <c r="F92" t="n">
-        <v>-4.571424211774556</v>
+        <v>-7.182528218025441</v>
       </c>
       <c r="G92" t="n">
-        <v>-11.7675258957851</v>
+        <v>-15.16074553358978</v>
       </c>
       <c r="H92" t="n">
-        <v>-5.309272162629597</v>
+        <v>5.07124498541589</v>
       </c>
       <c r="I92" t="n">
-        <v>36.09849894496958</v>
+        <v>33.67585940397817</v>
       </c>
       <c r="J92" t="n">
-        <v>36.43126861328262</v>
+        <v>31.93603390777067</v>
       </c>
       <c r="K92" t="n">
-        <v>0.1203324376278628</v>
+        <v>-0.01093610515526593</v>
       </c>
       <c r="L92" t="n">
-        <v>19.57947313077019</v>
+        <v>138.1182222872415</v>
       </c>
       <c r="M92" t="n">
-        <v>20.16216325889184</v>
+        <v>138.5855421895917</v>
       </c>
       <c r="N92" t="n">
-        <v>18.55880124038347</v>
+        <v>113.8312792799945</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.1005715349076347</v>
+        <v>-1.462543417745644</v>
       </c>
       <c r="P92" t="n">
-        <v>15.05377152689807</v>
+        <v>7.904418261406647</v>
       </c>
       <c r="Q92" t="n">
-        <v>-84.94622847310193</v>
+        <v>-92.09558173859335</v>
       </c>
       <c r="R92" t="n">
-        <v>-90.19373403243158</v>
+        <v>-176.7420186082932</v>
       </c>
       <c r="S92" t="n">
-        <v>-10.30272827229042</v>
+        <v>-18.17885054105456</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -8942,12 +8942,16 @@
         </is>
       </c>
       <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Breakdown 20d, Breakdown 50d, Double Top</t>
+        </is>
+      </c>
       <c r="W92" t="n">
         <v>46.8</v>
       </c>
       <c r="X92" t="n">
-        <v>68.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -8956,19 +8960,19 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); RSI scarico (36) — zona di interesse long</t>
+          <t>trend molto direzionale (ADX 32); RSI scarico (34) — zona di interesse long; pattern: Double Top; breakdown minimi 50g — rottura supporto importante; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Communication Svcs</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8977,65 +8981,65 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>110.6500015258789</v>
+        <v>18.3700008392334</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.775410539644373</v>
+        <v>0.1089943179721553</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.8867770236313022</v>
+        <v>-4.571424211774556</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.486821735650579</v>
+        <v>-11.7675258957851</v>
       </c>
       <c r="H93" t="n">
-        <v>-7.094875782117049</v>
+        <v>-5.309272162629597</v>
       </c>
       <c r="I93" t="n">
-        <v>48.88641587331934</v>
+        <v>36.09849894496958</v>
       </c>
       <c r="J93" t="n">
-        <v>20.63379468968709</v>
+        <v>36.43126861328262</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6331035154773208</v>
+        <v>0.1203324376278628</v>
       </c>
       <c r="L93" t="n">
-        <v>110.7882446230323</v>
+        <v>19.57947313077019</v>
       </c>
       <c r="M93" t="n">
-        <v>111.8345514115693</v>
+        <v>20.16216325889184</v>
       </c>
       <c r="N93" t="n">
-        <v>112.5257856257261</v>
+        <v>18.55880124038347</v>
       </c>
       <c r="O93" t="n">
-        <v>0.5184844050995951</v>
+        <v>-0.1005715349076347</v>
       </c>
       <c r="P93" t="n">
-        <v>55.81703817987616</v>
+        <v>15.05377152689807</v>
       </c>
       <c r="Q93" t="n">
-        <v>-44.18296182012384</v>
+        <v>-84.94622847310193</v>
       </c>
       <c r="R93" t="n">
-        <v>33.4056402258316</v>
+        <v>-90.19373403243158</v>
       </c>
       <c r="S93" t="n">
-        <v>1.327843056922418</v>
+        <v>-10.30272827229042</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="n">
-        <v>46.4</v>
+        <v>46.8</v>
       </c>
       <c r="X93" t="n">
-        <v>66.5</v>
+        <v>68.3</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -9044,94 +9048,86 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 36); RSI scarico (36) — zona di interesse long</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LDO</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Communication Svcs</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>50.75</v>
+        <v>110.6500015258789</v>
       </c>
       <c r="E94" t="n">
-        <v>2.29792254711354</v>
+        <v>-1.775410539644373</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.064839253426487</v>
+        <v>-0.8867770236313022</v>
       </c>
       <c r="G94" t="n">
-        <v>-2.02702558402611</v>
+        <v>-1.486821735650579</v>
       </c>
       <c r="H94" t="n">
-        <v>-8.178035860914768</v>
+        <v>-7.094875782117049</v>
       </c>
       <c r="I94" t="n">
-        <v>48.49774173353362</v>
+        <v>48.88641587331934</v>
       </c>
       <c r="J94" t="n">
-        <v>20.91440191514288</v>
+        <v>20.63379468968709</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5418163793158158</v>
+        <v>0.6331035154773208</v>
       </c>
       <c r="L94" t="n">
-        <v>51.02449582875671</v>
+        <v>110.7882446230323</v>
       </c>
       <c r="M94" t="n">
-        <v>51.79242360481434</v>
+        <v>111.8345514115693</v>
       </c>
       <c r="N94" t="n">
-        <v>52.02756098029904</v>
+        <v>112.5257856257261</v>
       </c>
       <c r="O94" t="n">
-        <v>-0.02800818341407642</v>
+        <v>0.5184844050995951</v>
       </c>
       <c r="P94" t="n">
-        <v>47.46544183853602</v>
+        <v>55.81703817987616</v>
       </c>
       <c r="Q94" t="n">
-        <v>-52.53455816146397</v>
+        <v>-44.18296182012384</v>
       </c>
       <c r="R94" t="n">
-        <v>-3.636537810063102</v>
+        <v>33.4056402258316</v>
       </c>
       <c r="S94" t="n">
-        <v>-3.627041118394481</v>
+        <v>1.327843056922418</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Double Top, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="n">
-        <v>45.4</v>
+        <v>46.4</v>
       </c>
       <c r="X94" t="n">
-        <v>66.3</v>
+        <v>66.5</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -9140,73 +9136,73 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); pattern: Double Top; candela di inversione bullish (engulfing)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>LDO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1251</v>
+        <v>50.75</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.9893153937475252</v>
+        <v>2.29792254711354</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.208248301205084</v>
+        <v>-2.064839253426487</v>
       </c>
       <c r="G95" t="n">
-        <v>-7.736560404547077</v>
+        <v>-2.02702558402611</v>
       </c>
       <c r="H95" t="n">
-        <v>-21.34054446705034</v>
+        <v>-8.178035860914768</v>
       </c>
       <c r="I95" t="n">
-        <v>47.09760196310562</v>
+        <v>48.49774173353362</v>
       </c>
       <c r="J95" t="n">
-        <v>13.8020232586546</v>
+        <v>20.91440191514288</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5791547171384305</v>
+        <v>0.5418163793158158</v>
       </c>
       <c r="L95" t="n">
-        <v>1260.80003182501</v>
+        <v>51.02449582875671</v>
       </c>
       <c r="M95" t="n">
-        <v>1318.204761083198</v>
+        <v>51.79242360481434</v>
       </c>
       <c r="N95" t="n">
-        <v>1412.360247204589</v>
+        <v>52.02756098029904</v>
       </c>
       <c r="O95" t="n">
-        <v>9.625231368292049</v>
+        <v>-0.02800818341407642</v>
       </c>
       <c r="P95" t="n">
-        <v>51.72415073830273</v>
+        <v>47.46544183853602</v>
       </c>
       <c r="Q95" t="n">
-        <v>-48.27584926169727</v>
+        <v>-52.53455816146397</v>
       </c>
       <c r="R95" t="n">
-        <v>11.62743417844947</v>
+        <v>-3.636537810063102</v>
       </c>
       <c r="S95" t="n">
-        <v>-7.271512664829083</v>
+        <v>-3.627041118394481</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9215,19 +9211,19 @@
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Bullish Engulfing, Piercing Pattern</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Outside Bar, Bull Flag / Consolidation</t>
+          <t>Double Top, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W95" t="n">
-        <v>44.6</v>
+        <v>45.4</v>
       </c>
       <c r="X95" t="n">
-        <v>78.09999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -9236,90 +9232,94 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 14); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 21); pattern: Double Top; candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.144033789634705</v>
+        <v>1250</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.2608514906022208</v>
+        <v>-1.068460625247325</v>
       </c>
       <c r="F96" t="n">
-        <v>0.06062952948981959</v>
+        <v>-1.287218526383982</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.5823229372894367</v>
+        <v>-7.810312154823218</v>
       </c>
       <c r="H96" t="n">
-        <v>-2.587812152442848</v>
+        <v>-21.4034217296666</v>
       </c>
       <c r="I96" t="n">
-        <v>47.38070494000235</v>
+        <v>46.97090894029174</v>
       </c>
       <c r="J96" t="n">
-        <v>27.80186815968384</v>
+        <v>13.8020232586546</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7116434464011179</v>
+        <v>0.5726050673442495</v>
       </c>
       <c r="L96" t="n">
-        <v>1.144218055259782</v>
+        <v>1260.704793729772</v>
       </c>
       <c r="M96" t="n">
-        <v>1.151054537770609</v>
+        <v>1318.165545396924</v>
       </c>
       <c r="N96" t="n">
-        <v>1.157490014316914</v>
+        <v>1412.350296955833</v>
       </c>
       <c r="O96" t="n">
-        <v>0.00121385498691586</v>
+        <v>9.561413704474404</v>
       </c>
       <c r="P96" t="n">
-        <v>67.26408230604486</v>
+        <v>50.70995170421836</v>
       </c>
       <c r="Q96" t="n">
-        <v>-32.73591769395514</v>
+        <v>-49.29004829578164</v>
       </c>
       <c r="R96" t="n">
-        <v>22.73365262078531</v>
+        <v>11.14254027192778</v>
       </c>
       <c r="S96" t="n">
-        <v>-0.1590281120629089</v>
+        <v>-7.345636155904356</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Outside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W96" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="X96" t="n">
-        <v>63.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 28); pattern: Double Bottom; sul supporto dei 20g (1.1325); vicino alla resistenza dei 20g (1.1478); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 14); pattern: Bull Flag / Consolidation; hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
@@ -9817,52 +9817,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>4020.199951171875</v>
+        <v>4023</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8681215542917009</v>
+        <v>0.9383756881615746</v>
       </c>
       <c r="F102" t="n">
-        <v>-2.044300686825062</v>
+        <v>-1.976075040239988</v>
       </c>
       <c r="G102" t="n">
-        <v>-7.174027527252102</v>
+        <v>-7.109374709332905</v>
       </c>
       <c r="H102" t="n">
-        <v>-17.2389684134026</v>
+        <v>-17.18132577564253</v>
       </c>
       <c r="I102" t="n">
-        <v>40.72261807774709</v>
+        <v>40.94652129391624</v>
       </c>
       <c r="J102" t="n">
         <v>32.59779164123098</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2824150503711397</v>
+        <v>0.2919082130730645</v>
       </c>
       <c r="L102" t="n">
-        <v>4105.855691055524</v>
+        <v>4106.122362372488</v>
       </c>
       <c r="M102" t="n">
-        <v>4272.00857418559</v>
+        <v>4272.118380021987</v>
       </c>
       <c r="N102" t="n">
-        <v>4305.136088740396</v>
+        <v>4305.163949922766</v>
       </c>
       <c r="O102" t="n">
-        <v>6.718216915316361</v>
+        <v>6.896909490102317</v>
       </c>
       <c r="P102" t="n">
-        <v>24.32542312870276</v>
+        <v>25.50588119048306</v>
       </c>
       <c r="Q102" t="n">
-        <v>-75.67457687129723</v>
+        <v>-74.49411880951695</v>
       </c>
       <c r="R102" t="n">
-        <v>-38.69571676715201</v>
+        <v>-38.2513937983228</v>
       </c>
       <c r="S102" t="n">
-        <v>-7.770308076809895</v>
+        <v>-7.706070565262102</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -9888,73 +9888,73 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 33); segnale candlestick: Piercing Pattern; sul supporto dei 20g (3,962); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 33); segnale candlestick: Piercing Pattern; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Brunello Cucinelli</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>75.11000061035156</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2151824114376866</v>
+        <v>-1.602099889609121</v>
       </c>
       <c r="F103" t="n">
-        <v>-2.294460266407095</v>
+        <v>2.465143631046574</v>
       </c>
       <c r="G103" t="n">
-        <v>4.558505893459652</v>
+        <v>-6.264236684317392</v>
       </c>
       <c r="H103" t="n">
-        <v>-13.20423786269529</v>
+        <v>-4.943403428944859</v>
       </c>
       <c r="I103" t="n">
-        <v>47.02156223819046</v>
+        <v>48.91949533778197</v>
       </c>
       <c r="J103" t="n">
-        <v>32.77350636953629</v>
+        <v>30.47668045538672</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2877380343625098</v>
+        <v>0.5443272808784403</v>
       </c>
       <c r="L103" t="n">
-        <v>76.47684372411008</v>
+        <v>82.50487742256489</v>
       </c>
       <c r="M103" t="n">
-        <v>76.59447083964668</v>
+        <v>82.76337010335882</v>
       </c>
       <c r="N103" t="n">
-        <v>94.3890012482974</v>
+        <v>86.12998645254716</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.5072443018185511</v>
+        <v>0.1482492766634119</v>
       </c>
       <c r="P103" t="n">
-        <v>16.39311685464279</v>
+        <v>65.87542802162039</v>
       </c>
       <c r="Q103" t="n">
-        <v>-83.6068831453572</v>
+        <v>-34.1245719783796</v>
       </c>
       <c r="R103" t="n">
-        <v>-48.75672660676867</v>
+        <v>13.87944452036177</v>
       </c>
       <c r="S103" t="n">
-        <v>6.674131646221948</v>
+        <v>-2.810577757251731</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -9963,15 +9963,15 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Evening Star</t>
         </is>
       </c>
       <c r="V103" t="inlineStr"/>
       <c r="W103" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="X103" t="n">
-        <v>66.7</v>
+        <v>70.2</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -9980,90 +9980,86 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 33); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 30); evening star — inversione ribassista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Brunello Cucinelli</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>82.30000305175781</v>
+        <v>74.98000335693359</v>
       </c>
       <c r="E104" t="n">
-        <v>-1.602099889609121</v>
+        <v>-0.3878858079749858</v>
       </c>
       <c r="F104" t="n">
-        <v>2.465143631046574</v>
+        <v>-2.463564935637208</v>
       </c>
       <c r="G104" t="n">
-        <v>-6.264236684317392</v>
+        <v>4.377540396492763</v>
       </c>
       <c r="H104" t="n">
-        <v>-4.943403428944859</v>
+        <v>-13.35446034431532</v>
       </c>
       <c r="I104" t="n">
-        <v>48.91949533778197</v>
+        <v>46.71925776236472</v>
       </c>
       <c r="J104" t="n">
-        <v>30.47668045538672</v>
+        <v>32.77350636953629</v>
       </c>
       <c r="K104" t="n">
-        <v>0.5443272808784403</v>
+        <v>0.2779729545198613</v>
       </c>
       <c r="L104" t="n">
-        <v>82.50487742256489</v>
+        <v>76.46446303330836</v>
       </c>
       <c r="M104" t="n">
-        <v>82.76337010335882</v>
+        <v>76.58937290814009</v>
       </c>
       <c r="N104" t="n">
-        <v>86.12998645254716</v>
+        <v>94.38770774328827</v>
       </c>
       <c r="O104" t="n">
-        <v>0.1482492766634119</v>
+        <v>-0.5155404228343884</v>
       </c>
       <c r="P104" t="n">
-        <v>65.87542802162039</v>
+        <v>15.14368239623916</v>
       </c>
       <c r="Q104" t="n">
-        <v>-34.1245719783796</v>
+        <v>-84.85631760376084</v>
       </c>
       <c r="R104" t="n">
-        <v>13.87944452036177</v>
+        <v>-49.42754845593316</v>
       </c>
       <c r="S104" t="n">
-        <v>-2.810577757251731</v>
+        <v>6.489504512523792</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
+      <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="n">
         <v>43.2</v>
       </c>
       <c r="X104" t="n">
-        <v>70.2</v>
+        <v>66.8</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -10072,7 +10068,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 30); evening star — inversione ribassista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 33); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -10185,52 +10181,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.088600039482117</v>
+        <v>1.088299989700317</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2127418380100332</v>
+        <v>0.1851202963680576</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2636083457859817</v>
+        <v>0.2359727838574077</v>
       </c>
       <c r="G106" t="n">
-        <v>3.961442512076974</v>
+        <v>3.932787719673936</v>
       </c>
       <c r="H106" t="n">
-        <v>-23.0146890090993</v>
+        <v>-23.03590839631846</v>
       </c>
       <c r="I106" t="n">
-        <v>45.31796748629424</v>
+        <v>45.25342951995341</v>
       </c>
       <c r="J106" t="n">
         <v>19.55178493607434</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4463115292509238</v>
+        <v>0.4442338758305422</v>
       </c>
       <c r="L106" t="n">
-        <v>1.102128871045833</v>
+        <v>1.102100294876138</v>
       </c>
       <c r="M106" t="n">
-        <v>1.151443981056859</v>
+        <v>1.151432214398749</v>
       </c>
       <c r="N106" t="n">
-        <v>1.454056876201487</v>
+        <v>1.454053890631519</v>
       </c>
       <c r="O106" t="n">
-        <v>0.003204051119803307</v>
+        <v>0.003184902643699904</v>
       </c>
       <c r="P106" t="n">
-        <v>26.38259645079642</v>
+        <v>26.14408132825537</v>
       </c>
       <c r="Q106" t="n">
-        <v>-73.61740354920357</v>
+        <v>-73.85591867174463</v>
       </c>
       <c r="R106" t="n">
-        <v>-25.41984628074806</v>
+        <v>-25.63589833764572</v>
       </c>
       <c r="S106" t="n">
-        <v>4.030098174155294</v>
+        <v>4.001424458258152</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10359,83 +10355,87 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Natural Gas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.8529999852180481</v>
+        <v>2.915999889373779</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.4396777134532681</v>
+        <v>2.029385881966461</v>
       </c>
       <c r="F108" t="n">
-        <v>1.041447499410464</v>
+        <v>-0.8163322237949244</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2792072576789595</v>
+        <v>-9.972219341259569</v>
       </c>
       <c r="H108" t="n">
-        <v>-32.73655583250831</v>
+        <v>9.050107043164735</v>
       </c>
       <c r="I108" t="n">
-        <v>43.73624518926984</v>
+        <v>40.67173092113308</v>
       </c>
       <c r="J108" t="n">
-        <v>24.76590693570633</v>
+        <v>30.95919064156459</v>
       </c>
       <c r="K108" t="n">
-        <v>0.5491796556764972</v>
+        <v>0.1737076022044502</v>
       </c>
       <c r="L108" t="n">
-        <v>0.8632416029059704</v>
+        <v>3.057469706655914</v>
       </c>
       <c r="M108" t="n">
-        <v>0.9441498142662117</v>
+        <v>3.071393447928864</v>
       </c>
       <c r="N108" t="n">
-        <v>1.458038154267449</v>
+        <v>3.248446278254432</v>
       </c>
       <c r="O108" t="n">
-        <v>0.008116526168243189</v>
+        <v>-0.04195148430325258</v>
       </c>
       <c r="P108" t="n">
-        <v>44.41656407227389</v>
+        <v>17.48118868677091</v>
       </c>
       <c r="Q108" t="n">
-        <v>-55.58343592772611</v>
+        <v>-82.51881131322909</v>
       </c>
       <c r="R108" t="n">
-        <v>6.409815270992517</v>
+        <v>-137.6408712001762</v>
       </c>
       <c r="S108" t="n">
-        <v>4.672848457905743</v>
+        <v>-7.281402001321191</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Hammer, Bullish Harami</t>
+        </is>
+      </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Double Bottom, Inside Bar, Bear Flag / Consolidation</t>
+          <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W108" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="X108" t="n">
-        <v>63.6</v>
+        <v>76.5</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -10444,90 +10444,90 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 25); pattern: Double Bottom</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 31); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>INW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Natural Gas</t>
+          <t>INWIT</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.92300009727478</v>
+        <v>6.309999942779541</v>
       </c>
       <c r="E109" t="n">
-        <v>2.274319674929859</v>
+        <v>1.121797663925772</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.578229918871187</v>
+        <v>-1.942501959774801</v>
       </c>
       <c r="G109" t="n">
-        <v>-9.756096842841966</v>
+        <v>-2.472949808354941</v>
       </c>
       <c r="H109" t="n">
-        <v>9.311894920355801</v>
+        <v>-13.20495241630836</v>
       </c>
       <c r="I109" t="n">
-        <v>41.131783265152</v>
+        <v>43.72400472934863</v>
       </c>
       <c r="J109" t="n">
-        <v>30.95919064156459</v>
+        <v>35.71328459527417</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1832138908680966</v>
+        <v>0.3825490205683507</v>
       </c>
       <c r="L109" t="n">
-        <v>3.058136393122676</v>
+        <v>6.420646618614047</v>
       </c>
       <c r="M109" t="n">
-        <v>3.071667965885767</v>
+        <v>6.62207396302829</v>
       </c>
       <c r="N109" t="n">
-        <v>3.248515932064392</v>
+        <v>7.664525957006608</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.04150474738877275</v>
+        <v>0.0001221422238193992</v>
       </c>
       <c r="P109" t="n">
-        <v>18.7970170791935</v>
+        <v>47.85712874666129</v>
       </c>
       <c r="Q109" t="n">
-        <v>-81.20298292080651</v>
+        <v>-52.14287125333871</v>
       </c>
       <c r="R109" t="n">
-        <v>-136.4712615024735</v>
+        <v>-11.77008165851754</v>
       </c>
       <c r="S109" t="n">
-        <v>-7.058819872753464</v>
+        <v>-0.8640978839966396</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom, Inside Bar</t>
-        </is>
-      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr"/>
       <c r="W109" t="n">
         <v>42</v>
       </c>
       <c r="X109" t="n">
-        <v>70.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -10536,19 +10536,19 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 31); pattern: Double Bottom; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 36); shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>INW</t>
+          <t>MONC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>INWIT</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10557,52 +10557,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>6.309999942779541</v>
+        <v>50.63999938964844</v>
       </c>
       <c r="E110" t="n">
-        <v>1.121797663925772</v>
+        <v>-2.764981549112766</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.942501959774801</v>
+        <v>1.401683584678914</v>
       </c>
       <c r="G110" t="n">
-        <v>-2.472949808354941</v>
+        <v>-5.838600708293828</v>
       </c>
       <c r="H110" t="n">
-        <v>-13.20495241630836</v>
+        <v>-12.0527999665038</v>
       </c>
       <c r="I110" t="n">
-        <v>43.72400472934863</v>
+        <v>44.52875436360058</v>
       </c>
       <c r="J110" t="n">
-        <v>35.71328459527417</v>
+        <v>16.2404493934273</v>
       </c>
       <c r="K110" t="n">
-        <v>0.3825490205683507</v>
+        <v>0.3814736647641905</v>
       </c>
       <c r="L110" t="n">
-        <v>6.420646618614047</v>
+        <v>51.24172779037816</v>
       </c>
       <c r="M110" t="n">
-        <v>6.62207396302829</v>
+        <v>52.07746808451166</v>
       </c>
       <c r="N110" t="n">
-        <v>7.664525957006608</v>
+        <v>52.82002685732885</v>
       </c>
       <c r="O110" t="n">
-        <v>0.0001221422238193992</v>
+        <v>0.108630701671621</v>
       </c>
       <c r="P110" t="n">
-        <v>47.85712874666129</v>
+        <v>43.4210295162112</v>
       </c>
       <c r="Q110" t="n">
-        <v>-52.14287125333871</v>
+        <v>-56.57897048378879</v>
       </c>
       <c r="R110" t="n">
-        <v>-11.77008165851754</v>
+        <v>5.570997129581982</v>
       </c>
       <c r="S110" t="n">
-        <v>-0.8640978839966396</v>
+        <v>-4.1635139223816</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10611,15 +10611,15 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
+          <t>Bearish Harami</t>
         </is>
       </c>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="X110" t="n">
-        <v>69.8</v>
+        <v>71</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -10628,90 +10628,90 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 36); shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; segnale candlestick: Bearish Harami; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MONC</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>50.63999938964844</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E111" t="n">
-        <v>-2.764981549112766</v>
+        <v>1.129308522785077</v>
       </c>
       <c r="F111" t="n">
-        <v>1.401683584678914</v>
+        <v>2.781085031701847</v>
       </c>
       <c r="G111" t="n">
-        <v>-5.838600708293828</v>
+        <v>-0.00492755765604258</v>
       </c>
       <c r="H111" t="n">
-        <v>-12.0527999665038</v>
+        <v>-29.17808089816042</v>
       </c>
       <c r="I111" t="n">
-        <v>44.52875436360058</v>
+        <v>46.64878404611062</v>
       </c>
       <c r="J111" t="n">
-        <v>16.2404493934273</v>
+        <v>30.06872461482107</v>
       </c>
       <c r="K111" t="n">
-        <v>0.3814736647641905</v>
+        <v>0.3803601446980671</v>
       </c>
       <c r="L111" t="n">
-        <v>51.24172779037816</v>
+        <v>6.639721142052233</v>
       </c>
       <c r="M111" t="n">
-        <v>52.07746808451166</v>
+        <v>7.056994284170479</v>
       </c>
       <c r="N111" t="n">
-        <v>52.82002685732885</v>
+        <v>9.932001677798553</v>
       </c>
       <c r="O111" t="n">
-        <v>0.108630701671621</v>
+        <v>0.01999038281234353</v>
       </c>
       <c r="P111" t="n">
-        <v>43.4210295162112</v>
+        <v>36.04090196516886</v>
       </c>
       <c r="Q111" t="n">
-        <v>-56.57897048378879</v>
+        <v>-63.95909803483114</v>
       </c>
       <c r="R111" t="n">
-        <v>5.570997129581982</v>
+        <v>-49.13550757256469</v>
       </c>
       <c r="S111" t="n">
-        <v>-4.1635139223816</v>
+        <v>2.412196313928017</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W111" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="X111" t="n">
-        <v>71</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; segnale candlestick: Bearish Harami; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 30); pattern: Double Top</t>
         </is>
       </c>
     </row>
@@ -10819,12 +10819,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -10833,69 +10833,73 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6.559999942779541</v>
+        <v>0.8510000109672546</v>
       </c>
       <c r="E113" t="n">
-        <v>0.8219248958825309</v>
+        <v>-0.6731104032825508</v>
       </c>
       <c r="F113" t="n">
-        <v>2.468680812237567</v>
+        <v>0.8045421104730055</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.3088636617260665</v>
+        <v>0.04408904445405426</v>
       </c>
       <c r="H113" t="n">
-        <v>-29.39334488716334</v>
+        <v>-32.89426410763831</v>
       </c>
       <c r="I113" t="n">
-        <v>46.10801176428571</v>
+        <v>43.34800565672011</v>
       </c>
       <c r="J113" t="n">
-        <v>30.06872461482107</v>
+        <v>24.76590693570633</v>
       </c>
       <c r="K113" t="n">
-        <v>0.3539587258268059</v>
+        <v>0.5286167868590688</v>
       </c>
       <c r="L113" t="n">
-        <v>6.637816381963993</v>
+        <v>0.8630511291677996</v>
       </c>
       <c r="M113" t="n">
-        <v>7.056209971192969</v>
+        <v>0.9440713839034355</v>
       </c>
       <c r="N113" t="n">
-        <v>9.931802673013214</v>
+        <v>1.458018254026147</v>
       </c>
       <c r="O113" t="n">
-        <v>0.01871403075321572</v>
+        <v>0.007988892483862052</v>
       </c>
       <c r="P113" t="n">
-        <v>33.54649821229342</v>
+        <v>42.02873591847482</v>
       </c>
       <c r="Q113" t="n">
-        <v>-66.45350178770657</v>
+        <v>-57.97126408152518</v>
       </c>
       <c r="R113" t="n">
-        <v>-51.45513291876181</v>
+        <v>5.229177175331806</v>
       </c>
       <c r="S113" t="n">
-        <v>2.100913335710719</v>
+        <v>4.427428756497997</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Dark Cloud Cover</t>
+        </is>
+      </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Bottom, Inside Bar, Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W113" t="n">
         <v>41.1</v>
       </c>
       <c r="X113" t="n">
-        <v>69.5</v>
+        <v>70.7</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -10904,7 +10908,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 30); pattern: Double Top</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 25); pattern: Double Bottom; segnale candlestick: Dark Cloud Cover</t>
         </is>
       </c>
     </row>
@@ -11021,52 +11025,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1604.5</v>
+        <v>1603.5</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.907437311441029</v>
+        <v>-1.968573218383096</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.8404904388564005</v>
+        <v>-0.9022913173613145</v>
       </c>
       <c r="G115" t="n">
-        <v>-11.45632020213513</v>
+        <v>-11.5115047953404</v>
       </c>
       <c r="H115" t="n">
-        <v>-24.47634737585315</v>
+        <v>-24.52341727465286</v>
       </c>
       <c r="I115" t="n">
-        <v>41.20551233031896</v>
+        <v>41.1064588236705</v>
       </c>
       <c r="J115" t="n">
         <v>30.20934758553455</v>
       </c>
       <c r="K115" t="n">
-        <v>0.4004870994847802</v>
+        <v>0.39406120053817</v>
       </c>
       <c r="L115" t="n">
-        <v>1646.070974414655</v>
+        <v>1645.975736319417</v>
       </c>
       <c r="M115" t="n">
-        <v>1753.735143674493</v>
+        <v>1753.695927988219</v>
       </c>
       <c r="N115" t="n">
-        <v>1806.072419069636</v>
+        <v>1806.062468820879</v>
       </c>
       <c r="O115" t="n">
-        <v>12.88983044080902</v>
+        <v>12.82601277699138</v>
       </c>
       <c r="P115" t="n">
-        <v>54.38467869977646</v>
+        <v>53.64775942176304</v>
       </c>
       <c r="Q115" t="n">
-        <v>-45.61532130022354</v>
+        <v>-46.35224057823695</v>
       </c>
       <c r="R115" t="n">
-        <v>-15.36771298000121</v>
+        <v>-15.61265614139438</v>
       </c>
       <c r="S115" t="n">
-        <v>-10.39816587083847</v>
+        <v>-10.45400995568058</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11201,52 +11205,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>56.15000152587891</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="E117" t="n">
-        <v>0.4508260070666514</v>
+        <v>0.5760535578102521</v>
       </c>
       <c r="F117" t="n">
-        <v>-6.117802835335107</v>
+        <v>-6.000764100297418</v>
       </c>
       <c r="G117" t="n">
-        <v>-19.66980949817514</v>
+        <v>-19.56966544354484</v>
       </c>
       <c r="H117" t="n">
-        <v>-31.30489828640575</v>
+        <v>-31.21925917642898</v>
       </c>
       <c r="I117" t="n">
-        <v>34.61713517757545</v>
+        <v>34.83862119838061</v>
       </c>
       <c r="J117" t="n">
         <v>42.67338853263151</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1688459666371548</v>
+        <v>0.1744170347823775</v>
       </c>
       <c r="L117" t="n">
-        <v>60.47162124136959</v>
+        <v>60.4782878789719</v>
       </c>
       <c r="M117" t="n">
-        <v>66.00655887282088</v>
+        <v>66.00930395889242</v>
       </c>
       <c r="N117" t="n">
-        <v>66.12240961740301</v>
+        <v>66.12310613177937</v>
       </c>
       <c r="O117" t="n">
-        <v>0.07647008656896848</v>
+        <v>0.08093730356060247</v>
       </c>
       <c r="P117" t="n">
-        <v>15.09188565718683</v>
+        <v>16.01051695162593</v>
       </c>
       <c r="Q117" t="n">
-        <v>-84.90811434281318</v>
+        <v>-83.98948304837407</v>
       </c>
       <c r="R117" t="n">
-        <v>-48.13919973935418</v>
+        <v>-47.87209930365136</v>
       </c>
       <c r="S117" t="n">
-        <v>-20.57541840478139</v>
+        <v>-20.47640333225918</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11255,7 +11259,7 @@
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
+          <t>Hammer, Bullish Engulfing, Piercing Pattern</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
@@ -11276,7 +11280,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); RSI scarico (35) — zona di interesse long; candela di inversione bullish (engulfing)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); RSI scarico (35) — zona di interesse long; hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
@@ -12543,52 +12547,52 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.264500141143799</v>
+        <v>6.270500183105469</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4973151088494498</v>
+        <v>0.5935698928070776</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.58144605529872</v>
+        <v>-2.48814006146939</v>
       </c>
       <c r="G14" t="n">
-        <v>7.434407494038719</v>
+        <v>7.537306518472886</v>
       </c>
       <c r="H14" t="n">
-        <v>35.85990150122525</v>
+        <v>35.99002602697341</v>
       </c>
       <c r="I14" t="n">
-        <v>59.22378637645028</v>
+        <v>59.36657047965787</v>
       </c>
       <c r="J14" t="n">
         <v>34.2296715164175</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6742538038492374</v>
+        <v>0.678552652582582</v>
       </c>
       <c r="L14" t="n">
-        <v>6.074921554307372</v>
+        <v>6.075492986875151</v>
       </c>
       <c r="M14" t="n">
-        <v>5.669593803754192</v>
+        <v>5.669829099517395</v>
       </c>
       <c r="N14" t="n">
-        <v>4.720332041544443</v>
+        <v>4.72039174345451</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.02339941832699607</v>
+        <v>-0.02301650966619462</v>
       </c>
       <c r="P14" t="n">
-        <v>55.01450137494928</v>
+        <v>55.7101582601446</v>
       </c>
       <c r="Q14" t="n">
-        <v>-44.98549862505072</v>
+        <v>-44.2898417398554</v>
       </c>
       <c r="R14" t="n">
-        <v>59.90405030850141</v>
+        <v>60.35494808035646</v>
       </c>
       <c r="S14" t="n">
-        <v>4.33008964411643</v>
+        <v>4.430015400621445</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -12605,7 +12609,7 @@
         <v>61.1</v>
       </c>
       <c r="X14" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -15855,52 +15859,52 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>88.16000366210938</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="E50" t="n">
-        <v>15.98474040837785</v>
+        <v>15.89263762946558</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9504200316637679</v>
+        <v>0.8702559153796807</v>
       </c>
       <c r="G50" t="n">
-        <v>22.85395908258872</v>
+        <v>22.75640149878899</v>
       </c>
       <c r="H50" t="n">
-        <v>37.94398978656736</v>
+        <v>37.83444930090645</v>
       </c>
       <c r="I50" t="n">
-        <v>51.77276114256325</v>
+        <v>51.73143790722</v>
       </c>
       <c r="J50" t="n">
         <v>38.90760141664225</v>
       </c>
       <c r="K50" t="n">
-        <v>0.3666338312376828</v>
+        <v>0.3653858197718414</v>
       </c>
       <c r="L50" t="n">
-        <v>86.54465828035156</v>
+        <v>86.53799091614025</v>
       </c>
       <c r="M50" t="n">
-        <v>81.57929901939515</v>
+        <v>81.57655363413167</v>
       </c>
       <c r="N50" t="n">
-        <v>77.59307021963889</v>
+        <v>77.59237362934816</v>
       </c>
       <c r="O50" t="n">
-        <v>-3.33133052979946</v>
+        <v>-3.335798233681227</v>
       </c>
       <c r="P50" t="n">
-        <v>32.2015807135011</v>
+        <v>32.07647827360815</v>
       </c>
       <c r="Q50" t="n">
-        <v>-67.7984192864989</v>
+        <v>-67.92352172639185</v>
       </c>
       <c r="R50" t="n">
-        <v>-35.41138018103164</v>
+        <v>-35.4816548826966</v>
       </c>
       <c r="S50" t="n">
-        <v>21.63355350296876</v>
+        <v>21.53696503583804</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -16403,52 +16407,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1.34551465511322</v>
+        <v>1.345243215560913</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2946640229454234</v>
+        <v>0.2744309183874583</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3081230152988779</v>
+        <v>0.2878871955695583</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.04441193374784547</v>
+        <v>-0.06457663427502647</v>
       </c>
       <c r="H56" t="n">
-        <v>1.660360214871215</v>
+        <v>1.639851599406295</v>
       </c>
       <c r="I56" t="n">
-        <v>52.40779471554531</v>
+        <v>52.30320426952532</v>
       </c>
       <c r="J56" t="n">
         <v>9.4071687978968</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6293351424338949</v>
+        <v>0.6234192846799461</v>
       </c>
       <c r="L56" t="n">
-        <v>1.339841717726978</v>
+        <v>1.339815866341044</v>
       </c>
       <c r="M56" t="n">
-        <v>1.336318539418003</v>
+        <v>1.336307894729678</v>
       </c>
       <c r="N56" t="n">
-        <v>1.306896763714068</v>
+        <v>1.306894062823</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.0006514728210724079</v>
+        <v>-0.0006687954591684481</v>
       </c>
       <c r="P56" t="n">
-        <v>60.62765129763073</v>
+        <v>60.10040197840061</v>
       </c>
       <c r="Q56" t="n">
-        <v>-39.37234870236927</v>
+        <v>-39.8995980215994</v>
       </c>
       <c r="R56" t="n">
-        <v>46.99030144476316</v>
+        <v>46.24538789828474</v>
       </c>
       <c r="S56" t="n">
-        <v>-0.2691065329109898</v>
+        <v>-0.2892259043136169</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -16474,7 +16478,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 9); pattern: Double Bottom; vicino alla resistenza dei 20g (1.3658); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 9); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -16859,52 +16863,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>162.3860015869141</v>
+        <v>162.3529968261719</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01416270590197666</v>
+        <v>-0.006165053133166953</v>
       </c>
       <c r="F61" t="n">
-        <v>1.408853203840565</v>
+        <v>1.388241975628635</v>
       </c>
       <c r="G61" t="n">
-        <v>4.657126678432344</v>
+        <v>4.635855242518949</v>
       </c>
       <c r="H61" t="n">
-        <v>11.21186334670918</v>
+        <v>11.18925966840205</v>
       </c>
       <c r="I61" t="n">
-        <v>64.58720821941432</v>
+        <v>64.48026550626027</v>
       </c>
       <c r="J61" t="n">
         <v>10.3239316069781</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9261137556512076</v>
+        <v>0.9220933993575708</v>
       </c>
       <c r="L61" t="n">
-        <v>159.5277018514977</v>
+        <v>159.5245585409508</v>
       </c>
       <c r="M61" t="n">
-        <v>156.4284402620061</v>
+        <v>156.4271459576633</v>
       </c>
       <c r="N61" t="n">
-        <v>146.5800415929563</v>
+        <v>146.5797131873768</v>
       </c>
       <c r="O61" t="n">
-        <v>0.147298906322161</v>
+        <v>0.1451926195967452</v>
       </c>
       <c r="P61" t="n">
-        <v>94.22266191278455</v>
+        <v>93.79892645848842</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.777338087215453</v>
+        <v>-6.201073541511578</v>
       </c>
       <c r="R61" t="n">
-        <v>84.62164868400939</v>
+        <v>84.31792080832172</v>
       </c>
       <c r="S61" t="n">
-        <v>4.187764792265791</v>
+        <v>4.166588753594813</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -16930,7 +16934,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (65) — momentum positivo; vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 10); RSI in forza (64) — momentum positivo; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
@@ -17315,52 +17319,52 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>81.80000305175781</v>
+        <v>81.76999664306641</v>
       </c>
       <c r="E66" t="n">
-        <v>14.54978134269644</v>
+        <v>14.50776144751007</v>
       </c>
       <c r="F66" t="n">
-        <v>-3.628645501088457</v>
+        <v>-3.663997067608682</v>
       </c>
       <c r="G66" t="n">
-        <v>23.21133273652676</v>
+        <v>23.16613555477156</v>
       </c>
       <c r="H66" t="n">
-        <v>34.05441238627566</v>
+        <v>34.00523767558033</v>
       </c>
       <c r="I66" t="n">
-        <v>50.57648566471132</v>
+        <v>50.55915695307965</v>
       </c>
       <c r="J66" t="n">
         <v>37.77868180426363</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3261715841225289</v>
+        <v>0.3255969459495746</v>
       </c>
       <c r="L66" t="n">
-        <v>81.97068070772866</v>
+        <v>81.96782295451995</v>
       </c>
       <c r="M66" t="n">
-        <v>77.146550718067</v>
+        <v>77.14537399615753</v>
       </c>
       <c r="N66" t="n">
-        <v>73.4135909859626</v>
+        <v>73.41329241473183</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.293931980675354</v>
+        <v>-3.295846919577599</v>
       </c>
       <c r="P66" t="n">
-        <v>33.6295337012733</v>
+        <v>33.56116639867889</v>
       </c>
       <c r="Q66" t="n">
-        <v>-66.3704662987267</v>
+        <v>-66.43883360132111</v>
       </c>
       <c r="R66" t="n">
-        <v>-39.72585028210182</v>
+        <v>-39.75736171679578</v>
       </c>
       <c r="S66" t="n">
-        <v>22.05312913906343</v>
+        <v>22.00835681707838</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -18127,52 +18131,52 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>100.7630004882812</v>
+        <v>100.754997253418</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.2050121124287263</v>
+        <v>-0.2129384616082142</v>
       </c>
       <c r="F75" t="n">
-        <v>1.015539336622817</v>
+        <v>1.007516043526779</v>
       </c>
       <c r="G75" t="n">
-        <v>3.029649636059162</v>
+        <v>3.021466369583159</v>
       </c>
       <c r="H75" t="n">
-        <v>0.4215708250239203</v>
+        <v>0.4135947086641778</v>
       </c>
       <c r="I75" t="n">
-        <v>57.8641990434618</v>
+        <v>57.80764824873598</v>
       </c>
       <c r="J75" t="n">
         <v>27.06929583167931</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7681544313446538</v>
+        <v>0.7664676143627946</v>
       </c>
       <c r="L75" t="n">
-        <v>99.74899924959212</v>
+        <v>99.74823703674799</v>
       </c>
       <c r="M75" t="n">
-        <v>99.60916019272518</v>
+        <v>99.60884634037761</v>
       </c>
       <c r="N75" t="n">
-        <v>100.8490079645164</v>
+        <v>100.8489283303386</v>
       </c>
       <c r="O75" t="n">
-        <v>0.2209830898866549</v>
+        <v>0.2204723421346976</v>
       </c>
       <c r="P75" t="n">
-        <v>75.1318675890232</v>
+        <v>74.93994375845041</v>
       </c>
       <c r="Q75" t="n">
-        <v>-24.8681324109768</v>
+        <v>-25.06005624154959</v>
       </c>
       <c r="R75" t="n">
-        <v>89.13453755731676</v>
+        <v>88.96356742278446</v>
       </c>
       <c r="S75" t="n">
-        <v>3.230201678326106</v>
+        <v>3.222002482738318</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -18683,52 +18687,52 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.144033789634705</v>
+        <v>1.144557595252991</v>
       </c>
       <c r="E81" t="n">
-        <v>0.06062952948981959</v>
+        <v>0.1064431412831635</v>
       </c>
       <c r="F81" t="n">
-        <v>-1.171491801235969</v>
+        <v>-1.12624232669214</v>
       </c>
       <c r="G81" t="n">
-        <v>-2.793733446089086</v>
+        <v>-2.749226728704612</v>
       </c>
       <c r="H81" t="n">
-        <v>1.925397140309393</v>
+        <v>1.972064551842045</v>
       </c>
       <c r="I81" t="n">
-        <v>41.62556627559405</v>
+        <v>41.95991331404283</v>
       </c>
       <c r="J81" t="n">
         <v>18.09394400576537</v>
       </c>
       <c r="K81" t="n">
-        <v>0.1968283780741039</v>
+        <v>0.2066378462885403</v>
       </c>
       <c r="L81" t="n">
-        <v>1.156619653355248</v>
+        <v>1.156669539604608</v>
       </c>
       <c r="M81" t="n">
-        <v>1.154841548463361</v>
+        <v>1.154862089860156</v>
       </c>
       <c r="N81" t="n">
-        <v>1.123506483681487</v>
+        <v>1.123511695677689</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.002967628577963568</v>
+        <v>-0.002934200527109967</v>
       </c>
       <c r="P81" t="n">
-        <v>21.85977960183212</v>
+        <v>22.85610629903406</v>
       </c>
       <c r="Q81" t="n">
-        <v>-78.14022039816788</v>
+        <v>-77.14389370096595</v>
       </c>
       <c r="R81" t="n">
-        <v>-94.15408421943275</v>
+        <v>-93.19137201890106</v>
       </c>
       <c r="S81" t="n">
-        <v>-3.072880791023225</v>
+        <v>-3.028501883629087</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -18971,52 +18975,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>56.15000152587891</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="E84" t="n">
-        <v>-6.117802835335107</v>
+        <v>-6.000764100297418</v>
       </c>
       <c r="F84" t="n">
-        <v>-17.25489534724881</v>
+        <v>-17.15174072718667</v>
       </c>
       <c r="G84" t="n">
-        <v>-31.75989756881713</v>
+        <v>-31.67482568608967</v>
       </c>
       <c r="H84" t="n">
-        <v>71.83866991321435</v>
+        <v>72.05289349515638</v>
       </c>
       <c r="I84" t="n">
-        <v>37.46373007210208</v>
+        <v>37.51406489222361</v>
       </c>
       <c r="J84" t="n">
         <v>13.41348995705084</v>
       </c>
       <c r="K84" t="n">
-        <v>0.02089631057997322</v>
+        <v>0.02252673150697514</v>
       </c>
       <c r="L84" t="n">
-        <v>68.39923617158644</v>
+        <v>68.40590280918875</v>
       </c>
       <c r="M84" t="n">
-        <v>63.61367463763136</v>
+        <v>63.6164197237029</v>
       </c>
       <c r="N84" t="n">
-        <v>42.36576147781383</v>
+        <v>42.3664579921902</v>
       </c>
       <c r="O84" t="n">
-        <v>-3.059300432233493</v>
+        <v>-3.054833215241871</v>
       </c>
       <c r="P84" t="n">
-        <v>3.393536087431851</v>
+        <v>3.600097979002956</v>
       </c>
       <c r="Q84" t="n">
-        <v>-96.60646391256815</v>
+        <v>-96.39990202099705</v>
       </c>
       <c r="R84" t="n">
-        <v>-139.9520537273678</v>
+        <v>-139.7687656862772</v>
       </c>
       <c r="S84" t="n">
-        <v>-39.41649726313311</v>
+        <v>-39.34097052069824</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -19042,7 +19046,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 13); RSI scarico (37) — zona di interesse long; breakdown minimi 20g — pressione ribassista; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 13); RSI scarico (38) — zona di interesse long; breakdown minimi 20g — pressione ribassista; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -19155,52 +19159,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1604.5</v>
+        <v>1603.5</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.8404904388564005</v>
+        <v>-0.9022913173613145</v>
       </c>
       <c r="F86" t="n">
-        <v>-6.12567014760852</v>
+        <v>-6.184177053094587</v>
       </c>
       <c r="G86" t="n">
-        <v>-26.04968262393172</v>
+        <v>-26.09577194607324</v>
       </c>
       <c r="H86" t="n">
-        <v>60.69103655483226</v>
+        <v>60.59088632949423</v>
       </c>
       <c r="I86" t="n">
-        <v>38.0356022555982</v>
+        <v>37.99942459549646</v>
       </c>
       <c r="J86" t="n">
         <v>16.1627974742278</v>
       </c>
       <c r="K86" t="n">
-        <v>0.1080032148447954</v>
+        <v>0.1068629120787456</v>
       </c>
       <c r="L86" t="n">
-        <v>1825.227737661272</v>
+        <v>1825.132499566034</v>
       </c>
       <c r="M86" t="n">
-        <v>1762.616197142208</v>
+        <v>1762.576981455933</v>
       </c>
       <c r="N86" t="n">
-        <v>1330.765282001001</v>
+        <v>1330.755331752245</v>
       </c>
       <c r="O86" t="n">
-        <v>-56.50130135480588</v>
+        <v>-56.5651190186237</v>
       </c>
       <c r="P86" t="n">
-        <v>11.06613174658436</v>
+        <v>10.9161842611517</v>
       </c>
       <c r="Q86" t="n">
-        <v>-88.93386825341564</v>
+        <v>-89.0838157388483</v>
       </c>
       <c r="R86" t="n">
-        <v>-103.4980051167578</v>
+        <v>-103.6040095808266</v>
       </c>
       <c r="S86" t="n">
-        <v>-32.17365853215512</v>
+        <v>-32.21593110396432</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -19226,7 +19230,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>RSI scarico (38) — zona di interesse long; doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -19247,52 +19251,52 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>4020.199951171875</v>
+        <v>4023</v>
       </c>
       <c r="E87" t="n">
-        <v>-2.044300686825062</v>
+        <v>-1.976075040239988</v>
       </c>
       <c r="F87" t="n">
-        <v>-4.621590719528468</v>
+        <v>-4.555160142348758</v>
       </c>
       <c r="G87" t="n">
-        <v>-20.5384123026844</v>
+        <v>-20.48306771081951</v>
       </c>
       <c r="H87" t="n">
-        <v>20.53127267728596</v>
+        <v>20.61522209594959</v>
       </c>
       <c r="I87" t="n">
-        <v>36.59702942234632</v>
+        <v>36.66637605166992</v>
       </c>
       <c r="J87" t="n">
         <v>38.00769331406385</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1137393422093603</v>
+        <v>0.1155370272645728</v>
       </c>
       <c r="L87" t="n">
-        <v>4382.272101537097</v>
+        <v>4382.538772854062</v>
       </c>
       <c r="M87" t="n">
-        <v>4223.424468330848</v>
+        <v>4223.534274167245</v>
       </c>
       <c r="N87" t="n">
-        <v>3133.547816828321</v>
+        <v>3133.57567801069</v>
       </c>
       <c r="O87" t="n">
-        <v>-94.50170072292079</v>
+        <v>-94.32300814813409</v>
       </c>
       <c r="P87" t="n">
-        <v>6.29087863988254</v>
+        <v>6.596160828267922</v>
       </c>
       <c r="Q87" t="n">
-        <v>-93.70912136011746</v>
+        <v>-93.40383917173207</v>
       </c>
       <c r="R87" t="n">
-        <v>-107.2538630932363</v>
+        <v>-107.0767519020541</v>
       </c>
       <c r="S87" t="n">
-        <v>-23.13928016113421</v>
+        <v>-23.08574706051046</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -19309,7 +19313,7 @@
         <v>48.1</v>
       </c>
       <c r="X87" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -19318,7 +19322,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 38); RSI scarico (37) — zona di interesse long; pattern: Double Bottom; sul supporto dei 20g (3,962); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 38); RSI scarico (37) — zona di interesse long; pattern: Double Bottom; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -20347,52 +20351,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2.92300009727478</v>
+        <v>2.915999889373779</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.578229918871187</v>
+        <v>-0.8163322237949244</v>
       </c>
       <c r="F99" t="n">
-        <v>-6.314096009942672</v>
+        <v>-6.538461656024941</v>
       </c>
       <c r="G99" t="n">
-        <v>-4.06957127847134</v>
+        <v>-4.299312271538347</v>
       </c>
       <c r="H99" t="n">
-        <v>-22.97760109324497</v>
+        <v>-23.16205979575539</v>
       </c>
       <c r="I99" t="n">
-        <v>45.32004615817164</v>
+        <v>45.20504527036633</v>
       </c>
       <c r="J99" t="n">
         <v>28.77506007135326</v>
       </c>
       <c r="K99" t="n">
-        <v>0.4310335051109058</v>
+        <v>0.423777674183516</v>
       </c>
       <c r="L99" t="n">
-        <v>3.110420037047466</v>
+        <v>3.109753350580704</v>
       </c>
       <c r="M99" t="n">
-        <v>3.256260784356345</v>
+        <v>3.255986266399443</v>
       </c>
       <c r="N99" t="n">
-        <v>3.331465397924958</v>
+        <v>3.331395744114997</v>
       </c>
       <c r="O99" t="n">
-        <v>0.03060677383982197</v>
+        <v>0.03016003692534248</v>
       </c>
       <c r="P99" t="n">
-        <v>45.92902741390737</v>
+        <v>45.19831673486981</v>
       </c>
       <c r="Q99" t="n">
-        <v>-54.07097258609263</v>
+        <v>-54.80168326513019</v>
       </c>
       <c r="R99" t="n">
-        <v>-11.92625491341721</v>
+        <v>-12.22978699837838</v>
       </c>
       <c r="S99" t="n">
-        <v>2.238549507714405</v>
+        <v>1.993701379683888</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -20413,7 +20417,7 @@
         <v>42.6</v>
       </c>
       <c r="X99" t="n">
-        <v>74.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -20531,52 +20535,52 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.208248301205084</v>
+        <v>-1.287218526383982</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.974608379253973</v>
+        <v>-2.05296600644882</v>
       </c>
       <c r="G101" t="n">
-        <v>-29.48934537092602</v>
+        <v>-29.54570880388291</v>
       </c>
       <c r="H101" t="n">
-        <v>27.91411042944785</v>
+        <v>27.8118609406953</v>
       </c>
       <c r="I101" t="n">
-        <v>40.23311911136501</v>
+        <v>40.18598942688391</v>
       </c>
       <c r="J101" t="n">
         <v>38.97801109389155</v>
       </c>
       <c r="K101" t="n">
-        <v>0.2111274409223329</v>
+        <v>0.2094581243710902</v>
       </c>
       <c r="L101" t="n">
-        <v>1382.513253290888</v>
+        <v>1382.41801519565</v>
       </c>
       <c r="M101" t="n">
-        <v>1393.858388701096</v>
+        <v>1393.819173014822</v>
       </c>
       <c r="N101" t="n">
-        <v>1364.90454423938</v>
+        <v>1364.894593990624</v>
       </c>
       <c r="O101" t="n">
-        <v>-25.02854685155409</v>
+        <v>-25.09236451537173</v>
       </c>
       <c r="P101" t="n">
-        <v>20.90420794114225</v>
+        <v>20.6711620178386</v>
       </c>
       <c r="Q101" t="n">
-        <v>-79.09579205885775</v>
+        <v>-79.3288379821614</v>
       </c>
       <c r="R101" t="n">
-        <v>-55.27164563190728</v>
+        <v>-55.38183801762253</v>
       </c>
       <c r="S101" t="n">
-        <v>-30.19752069616997</v>
+        <v>-30.25331804173658</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -20715,52 +20719,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>64142.98828125</v>
+        <v>64064.3515625</v>
       </c>
       <c r="E103" t="n">
-        <v>0.6034822471416623</v>
+        <v>0.4801464321021465</v>
       </c>
       <c r="F103" t="n">
-        <v>-2.385330470550762</v>
+        <v>-2.505002121643851</v>
       </c>
       <c r="G103" t="n">
-        <v>-5.197212554336394</v>
+        <v>-5.313436951310113</v>
       </c>
       <c r="H103" t="n">
-        <v>-38.38706043864095</v>
+        <v>-38.46259541961818</v>
       </c>
       <c r="I103" t="n">
-        <v>39.00255581819521</v>
+        <v>38.89516585769456</v>
       </c>
       <c r="J103" t="n">
         <v>24.67362293818111</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2817858153278959</v>
+        <v>0.2790437151829958</v>
       </c>
       <c r="L103" t="n">
-        <v>70461.39116130506</v>
+        <v>70453.90194999553</v>
       </c>
       <c r="M103" t="n">
-        <v>79484.52846747779</v>
+        <v>79481.44467458563</v>
       </c>
       <c r="N103" t="n">
-        <v>68647.13789734957</v>
+        <v>68646.35544243664</v>
       </c>
       <c r="O103" t="n">
-        <v>-61.67946884934918</v>
+        <v>-66.69788053025422</v>
       </c>
       <c r="P103" t="n">
-        <v>25.53549330580727</v>
+        <v>25.22150464377549</v>
       </c>
       <c r="Q103" t="n">
-        <v>-74.46450669419274</v>
+        <v>-74.77849535622451</v>
       </c>
       <c r="R103" t="n">
-        <v>-56.34803180363858</v>
+        <v>-56.56518783949212</v>
       </c>
       <c r="S103" t="n">
-        <v>-2.426466909351588</v>
+        <v>-2.54608812882845</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -20899,52 +20903,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.088600039482117</v>
+        <v>1.088299989700317</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2636083457859817</v>
+        <v>0.2359727838574077</v>
       </c>
       <c r="F105" t="n">
-        <v>-8.199242921933303</v>
+        <v>-8.224545876307054</v>
       </c>
       <c r="G105" t="n">
-        <v>-21.85648877694093</v>
+        <v>-21.87802739777606</v>
       </c>
       <c r="H105" t="n">
-        <v>-54.00006044776684</v>
+        <v>-54.01273936686002</v>
       </c>
       <c r="I105" t="n">
-        <v>33.45861721975997</v>
+        <v>33.43996726280264</v>
       </c>
       <c r="J105" t="n">
         <v>23.48912808815049</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1310713032447548</v>
+        <v>0.1306080344115905</v>
       </c>
       <c r="L105" t="n">
-        <v>1.318322247550839</v>
+        <v>1.318293671381144</v>
       </c>
       <c r="M105" t="n">
-        <v>1.632705288956394</v>
+        <v>1.632693522298285</v>
       </c>
       <c r="N105" t="n">
-        <v>1.396632850118438</v>
+        <v>1.39662986454847</v>
       </c>
       <c r="O105" t="n">
-        <v>0.008727485569607757</v>
+        <v>0.008708337093504354</v>
       </c>
       <c r="P105" t="n">
-        <v>14.66591661175035</v>
+        <v>14.61010596262616</v>
       </c>
       <c r="Q105" t="n">
-        <v>-85.33408338824965</v>
+        <v>-85.38989403737385</v>
       </c>
       <c r="R105" t="n">
-        <v>-52.44454961179932</v>
+        <v>-52.46750788620029</v>
       </c>
       <c r="S105" t="n">
-        <v>-19.46610518889245</v>
+        <v>-19.48830266885673</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -20977,83 +20981,79 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MONC</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>50.63999938964844</v>
+        <v>1840.780029296875</v>
       </c>
       <c r="E106" t="n">
-        <v>1.401683584678914</v>
+        <v>1.937765767305333</v>
       </c>
       <c r="F106" t="n">
-        <v>-5.978464879713097</v>
+        <v>6.735814301666365</v>
       </c>
       <c r="G106" t="n">
-        <v>-11.15789580763432</v>
+        <v>-5.977399415126728</v>
       </c>
       <c r="H106" t="n">
-        <v>-6.980160420496806</v>
+        <v>-26.66909746746089</v>
       </c>
       <c r="I106" t="n">
-        <v>45.82267571384584</v>
+        <v>39.9577989194613</v>
       </c>
       <c r="J106" t="n">
-        <v>12.39199950333294</v>
+        <v>28.72812942720754</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2420567970563151</v>
+        <v>0.3294318001983276</v>
       </c>
       <c r="L106" t="n">
-        <v>52.45464777962302</v>
+        <v>2036.911874774401</v>
       </c>
       <c r="M106" t="n">
-        <v>52.94788333493507</v>
+        <v>2443.706736343954</v>
       </c>
       <c r="N106" t="n">
-        <v>53.12442725514725</v>
+        <v>2493.785956909157</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.3530141458446967</v>
+        <v>14.72092850085181</v>
       </c>
       <c r="P106" t="n">
-        <v>28.89734584834403</v>
+        <v>34.88282034712188</v>
       </c>
       <c r="Q106" t="n">
-        <v>-71.10265415165597</v>
+        <v>-65.11717965287812</v>
       </c>
       <c r="R106" t="n">
-        <v>-93.99530417904518</v>
+        <v>-33.5125616094192</v>
       </c>
       <c r="S106" t="n">
-        <v>-13.34702159540383</v>
+        <v>-5.068759295816372</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Piercing Pattern</t>
-        </is>
-      </c>
+      <c r="U106" t="inlineStr"/>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="n">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="X106" t="n">
-        <v>73</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -21062,86 +21062,90 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 12); segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>MONC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>US Treasury 20Y+ ETF</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>84.51999664306641</v>
+        <v>50.63999938964844</v>
       </c>
       <c r="E107" t="n">
-        <v>0.05918719266104766</v>
+        <v>1.401683584678914</v>
       </c>
       <c r="F107" t="n">
-        <v>-1.457386089452584</v>
+        <v>-5.978464879713097</v>
       </c>
       <c r="G107" t="n">
-        <v>-5.469194518236309</v>
+        <v>-11.15789580763432</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.906382906370641</v>
+        <v>-6.980160420496806</v>
       </c>
       <c r="I107" t="n">
-        <v>42.15864765303414</v>
+        <v>45.82267571384584</v>
       </c>
       <c r="J107" t="n">
-        <v>32.46523133930327</v>
+        <v>12.39199950333294</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1877653985812749</v>
+        <v>0.2420567970563151</v>
       </c>
       <c r="L107" t="n">
-        <v>86.06939693568233</v>
+        <v>52.45464777962302</v>
       </c>
       <c r="M107" t="n">
-        <v>87.20282010154833</v>
+        <v>52.94788333493507</v>
       </c>
       <c r="N107" t="n">
-        <v>96.59778251814333</v>
+        <v>53.12442725514725</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.0388080693936852</v>
+        <v>-0.3530141458446967</v>
       </c>
       <c r="P107" t="n">
-        <v>34.86052809955287</v>
+        <v>28.89734584834403</v>
       </c>
       <c r="Q107" t="n">
-        <v>-65.13947190044712</v>
+        <v>-71.10265415165597</v>
       </c>
       <c r="R107" t="n">
-        <v>-79.63242945201701</v>
+        <v>-93.99530417904518</v>
       </c>
       <c r="S107" t="n">
-        <v>-6.936801445636698</v>
+        <v>-13.34702159540383</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr"/>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Piercing Pattern</t>
+        </is>
+      </c>
       <c r="V107" t="inlineStr"/>
       <c r="W107" t="n">
-        <v>40.8</v>
+        <v>41.2</v>
       </c>
       <c r="X107" t="n">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -21150,73 +21154,73 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 32); penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 12); segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>US Treasury 20Y+ ETF</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>5.690000057220459</v>
+        <v>84.51999664306641</v>
       </c>
       <c r="E108" t="n">
-        <v>1.861799000929687</v>
+        <v>0.05918719266104766</v>
       </c>
       <c r="F108" t="n">
-        <v>4.67255689809527</v>
+        <v>-1.457386089452584</v>
       </c>
       <c r="G108" t="n">
-        <v>-14.89679677536547</v>
+        <v>-5.469194518236309</v>
       </c>
       <c r="H108" t="n">
-        <v>-3.428379741057686</v>
+        <v>-2.906382906370641</v>
       </c>
       <c r="I108" t="n">
-        <v>46.8057691229236</v>
+        <v>42.15864765303414</v>
       </c>
       <c r="J108" t="n">
-        <v>33.74537130512127</v>
+        <v>32.46523133930327</v>
       </c>
       <c r="K108" t="n">
-        <v>0.3886640432765482</v>
+        <v>0.1877653985812749</v>
       </c>
       <c r="L108" t="n">
-        <v>5.763510368008495</v>
+        <v>86.06939693568233</v>
       </c>
       <c r="M108" t="n">
-        <v>5.95363903116899</v>
+        <v>87.20282010154833</v>
       </c>
       <c r="N108" t="n">
-        <v>7.424515839817265</v>
+        <v>96.59778251814333</v>
       </c>
       <c r="O108" t="n">
-        <v>-0.03313303595723727</v>
+        <v>-0.0388080693936852</v>
       </c>
       <c r="P108" t="n">
-        <v>28.45416687866679</v>
+        <v>34.86052809955287</v>
       </c>
       <c r="Q108" t="n">
-        <v>-71.54583312133322</v>
+        <v>-65.13947190044712</v>
       </c>
       <c r="R108" t="n">
-        <v>-41.73258582607045</v>
+        <v>-79.63242945201701</v>
       </c>
       <c r="S108" t="n">
-        <v>-10.78707665094031</v>
+        <v>-6.936801445636698</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21224,16 +21228,12 @@
         </is>
       </c>
       <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="X108" t="n">
-        <v>65.3</v>
+        <v>72.5</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21242,73 +21242,73 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 34); pattern: Double Bottom; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 32); penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>75.11000061035156</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.294460266407095</v>
+        <v>1.861799000929687</v>
       </c>
       <c r="F109" t="n">
-        <v>5.541701052777825</v>
+        <v>4.67255689809527</v>
       </c>
       <c r="G109" t="n">
-        <v>-9.277553063936594</v>
+        <v>-14.89679677536547</v>
       </c>
       <c r="H109" t="n">
-        <v>-56.59045376226843</v>
+        <v>-3.428379741057686</v>
       </c>
       <c r="I109" t="n">
-        <v>39.25693392606642</v>
+        <v>46.8057691229236</v>
       </c>
       <c r="J109" t="n">
-        <v>28.89258741042294</v>
+        <v>33.74537130512127</v>
       </c>
       <c r="K109" t="n">
-        <v>0.293021714958407</v>
+        <v>0.3886640432765482</v>
       </c>
       <c r="L109" t="n">
-        <v>85.18886541228741</v>
+        <v>5.763510368008495</v>
       </c>
       <c r="M109" t="n">
-        <v>110.6388803261062</v>
+        <v>5.95363903116899</v>
       </c>
       <c r="N109" t="n">
-        <v>113.1185182357455</v>
+        <v>7.424515839817265</v>
       </c>
       <c r="O109" t="n">
-        <v>2.322959120266162</v>
+        <v>-0.03313303595723727</v>
       </c>
       <c r="P109" t="n">
-        <v>38.82304187665731</v>
+        <v>28.45416687866679</v>
       </c>
       <c r="Q109" t="n">
-        <v>-61.17695812334269</v>
+        <v>-71.54583312133322</v>
       </c>
       <c r="R109" t="n">
-        <v>-22.62002245536266</v>
+        <v>-41.73258582607045</v>
       </c>
       <c r="S109" t="n">
-        <v>-10.13148613685224</v>
+        <v>-10.78707665094031</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -21316,33 +21316,37 @@
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W109" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="X109" t="n">
-        <v>69.90000000000001</v>
+        <v>65.3</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend in sviluppo (ADX 29)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 34); pattern: Double Bottom; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21351,52 +21355,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1844.760009765625</v>
+        <v>74.98000335693359</v>
       </c>
       <c r="E110" t="n">
-        <v>2.158167070190409</v>
+        <v>-2.463564935637208</v>
       </c>
       <c r="F110" t="n">
-        <v>6.966589543398549</v>
+        <v>5.359033882674913</v>
       </c>
       <c r="G110" t="n">
-        <v>-5.774111619739342</v>
+        <v>-9.434571687677895</v>
       </c>
       <c r="H110" t="n">
-        <v>-26.51054752928778</v>
+        <v>-56.66558519266611</v>
       </c>
       <c r="I110" t="n">
-        <v>40.09574242241328</v>
+        <v>39.19667828841532</v>
       </c>
       <c r="J110" t="n">
-        <v>28.72812942720754</v>
+        <v>28.89258741042294</v>
       </c>
       <c r="K110" t="n">
-        <v>0.3332358731067262</v>
+        <v>0.2889562169630622</v>
       </c>
       <c r="L110" t="n">
-        <v>2037.29092053333</v>
+        <v>85.17648472148569</v>
       </c>
       <c r="M110" t="n">
-        <v>2443.862814009395</v>
+        <v>110.6337823945996</v>
       </c>
       <c r="N110" t="n">
-        <v>2493.825558704867</v>
+        <v>113.1172247307364</v>
       </c>
       <c r="O110" t="n">
-        <v>14.97492155640725</v>
+        <v>2.314662999250324</v>
       </c>
       <c r="P110" t="n">
-        <v>35.29814676318892</v>
+        <v>38.47960588003383</v>
       </c>
       <c r="Q110" t="n">
-        <v>-64.70185323681109</v>
+        <v>-61.52039411996617</v>
       </c>
       <c r="R110" t="n">
-        <v>-33.27509157853736</v>
+        <v>-22.77849122974822</v>
       </c>
       <c r="S110" t="n">
-        <v>-4.863506914834614</v>
+        <v>-10.28702680888033</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -21409,7 +21413,7 @@
         <v>40</v>
       </c>
       <c r="X110" t="n">
-        <v>67.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21439,52 +21443,52 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.8529999852180481</v>
+        <v>0.8510000109672546</v>
       </c>
       <c r="E111" t="n">
-        <v>1.041447499410464</v>
+        <v>0.8045421104730055</v>
       </c>
       <c r="F111" t="n">
-        <v>-14.23015215180299</v>
+        <v>-14.43125120240499</v>
       </c>
       <c r="G111" t="n">
-        <v>-34.9997660876086</v>
+        <v>-35.15216795908941</v>
       </c>
       <c r="H111" t="n">
-        <v>-83.24969945128264</v>
+        <v>-83.28897280458982</v>
       </c>
       <c r="I111" t="n">
-        <v>29.72764059265423</v>
+        <v>29.62718607375589</v>
       </c>
       <c r="J111" t="n">
         <v>33.78429244159838</v>
       </c>
       <c r="K111" t="n">
-        <v>0.1407814881765472</v>
+        <v>0.1387801952276541</v>
       </c>
       <c r="L111" t="n">
-        <v>1.196283154012122</v>
+        <v>1.196092680273951</v>
       </c>
       <c r="M111" t="n">
-        <v>2.033400656352033</v>
+        <v>2.033322225989256</v>
       </c>
       <c r="N111" t="n">
-        <v>5.290231014852236</v>
+        <v>5.290211114610934</v>
       </c>
       <c r="O111" t="n">
-        <v>0.03152441937636796</v>
+        <v>0.03139678569198673</v>
       </c>
       <c r="P111" t="n">
-        <v>8.541999279272776</v>
+        <v>8.226620024298697</v>
       </c>
       <c r="Q111" t="n">
-        <v>-91.45800072072723</v>
+        <v>-91.7733799757013</v>
       </c>
       <c r="R111" t="n">
-        <v>-59.9803541880214</v>
+        <v>-60.09165367913462</v>
       </c>
       <c r="S111" t="n">
-        <v>-44.50664890378746</v>
+        <v>-44.63676059805002</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -21631,52 +21635,52 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>8.244000434875488</v>
+        <v>8.237000465393066</v>
       </c>
       <c r="E113" t="n">
-        <v>3.153323438588496</v>
+        <v>3.065736092883631</v>
       </c>
       <c r="F113" t="n">
-        <v>0.9524455722030645</v>
+        <v>0.86672698888135</v>
       </c>
       <c r="G113" t="n">
-        <v>-4.942757016668109</v>
+        <v>-5.023469991542728</v>
       </c>
       <c r="H113" t="n">
-        <v>-51.68773183091161</v>
+        <v>-51.72875371166982</v>
       </c>
       <c r="I113" t="n">
-        <v>41.05564454142528</v>
+        <v>41.00739489900327</v>
       </c>
       <c r="J113" t="n">
         <v>29.5381031611005</v>
       </c>
       <c r="K113" t="n">
-        <v>0.3488357580797583</v>
+        <v>0.3468004334035328</v>
       </c>
       <c r="L113" t="n">
-        <v>9.038650570813189</v>
+        <v>9.037983907052958</v>
       </c>
       <c r="M113" t="n">
-        <v>11.39405133739979</v>
+        <v>11.39377682879264</v>
       </c>
       <c r="N113" t="n">
-        <v>13.0847723667123</v>
+        <v>13.08470271527467</v>
       </c>
       <c r="O113" t="n">
-        <v>0.1624168516574289</v>
+        <v>0.1619701299582661</v>
       </c>
       <c r="P113" t="n">
-        <v>31.8816388372954</v>
+        <v>31.6989512262657</v>
       </c>
       <c r="Q113" t="n">
-        <v>-68.1183611627046</v>
+        <v>-68.30104877373429</v>
       </c>
       <c r="R113" t="n">
-        <v>-27.51595924529053</v>
+        <v>-27.62212563345416</v>
       </c>
       <c r="S113" t="n">
-        <v>-4.939255200735282</v>
+        <v>-5.019971148997026</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -21719,52 +21723,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>6.559999942779541</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E114" t="n">
-        <v>2.468680812237567</v>
+        <v>2.781085031701847</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.184438648765431</v>
+        <v>-2.889269533322736</v>
       </c>
       <c r="G114" t="n">
-        <v>-26.05570424339212</v>
+        <v>-25.83026453033473</v>
       </c>
       <c r="H114" t="n">
-        <v>-73.49743942271097</v>
+        <v>-73.41663900949862</v>
       </c>
       <c r="I114" t="n">
-        <v>33.9219438852698</v>
+        <v>34.05629685319285</v>
       </c>
       <c r="J114" t="n">
         <v>36.27820066964121</v>
       </c>
       <c r="K114" t="n">
-        <v>0.1799016099577985</v>
+        <v>0.1831215282510095</v>
       </c>
       <c r="L114" t="n">
-        <v>8.478874024498197</v>
+        <v>8.480778784586436</v>
       </c>
       <c r="M114" t="n">
-        <v>12.79171868876114</v>
+        <v>12.79250300173865</v>
       </c>
       <c r="N114" t="n">
-        <v>21.22759937867986</v>
+        <v>21.2277983834652</v>
       </c>
       <c r="O114" t="n">
-        <v>0.1452786600545108</v>
+        <v>0.1465550121136387</v>
       </c>
       <c r="P114" t="n">
-        <v>18.12241740611553</v>
+        <v>18.54073889599949</v>
       </c>
       <c r="Q114" t="n">
-        <v>-81.87758259388447</v>
+        <v>-81.4592611040005</v>
       </c>
       <c r="R114" t="n">
-        <v>-64.24866513868483</v>
+        <v>-64.03479172047159</v>
       </c>
       <c r="S114" t="n">
-        <v>-27.36031557960455</v>
+        <v>-27.13885333637466</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -21815,52 +21819,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.1657000035047531</v>
+        <v>0.1659000068902969</v>
       </c>
       <c r="E115" t="n">
-        <v>2.309841349871666</v>
+        <v>2.433331477883893</v>
       </c>
       <c r="F115" t="n">
-        <v>-9.347047330720581</v>
+        <v>-9.237627312254016</v>
       </c>
       <c r="G115" t="n">
-        <v>-38.9430534329182</v>
+        <v>-38.8693564156213</v>
       </c>
       <c r="H115" t="n">
-        <v>-79.41586685517295</v>
+        <v>-79.39102137399991</v>
       </c>
       <c r="I115" t="n">
-        <v>34.70987050436781</v>
+        <v>34.74754545128988</v>
       </c>
       <c r="J115" t="n">
         <v>33.76161581275937</v>
       </c>
       <c r="K115" t="n">
-        <v>0.1805905277395317</v>
+        <v>0.1815918003221288</v>
       </c>
       <c r="L115" t="n">
-        <v>0.229882039374931</v>
+        <v>0.2299010873164113</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3613150738530866</v>
+        <v>0.3613229171231079</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5158236138604487</v>
+        <v>0.515825603943887</v>
       </c>
       <c r="O115" t="n">
-        <v>0.005709410013415572</v>
+        <v>0.00572217376223659</v>
       </c>
       <c r="P115" t="n">
-        <v>18.06245751680889</v>
+        <v>18.19623098098547</v>
       </c>
       <c r="Q115" t="n">
-        <v>-81.93754248319111</v>
+        <v>-81.80376901901452</v>
       </c>
       <c r="R115" t="n">
-        <v>-57.60383906589519</v>
+        <v>-57.54636003954363</v>
       </c>
       <c r="S115" t="n">
-        <v>-39.43270904381371</v>
+        <v>-39.3596030511267</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -22789,52 +22793,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.264500141143799</v>
+        <v>6.270500183105469</v>
       </c>
       <c r="E8" t="n">
-        <v>1.162697220384001</v>
+        <v>1.259589297102393</v>
       </c>
       <c r="F8" t="n">
-        <v>4.33008964411643</v>
+        <v>4.430015400621445</v>
       </c>
       <c r="G8" t="n">
-        <v>45.23009728539427</v>
+        <v>45.36919644066233</v>
       </c>
       <c r="H8" t="n">
-        <v>33.78537734648186</v>
+        <v>33.91351492487613</v>
       </c>
       <c r="I8" t="n">
-        <v>66.51765966238273</v>
+        <v>66.57284815860496</v>
       </c>
       <c r="J8" t="n">
         <v>61.44032598308471</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8624499909200175</v>
+        <v>0.8641465782865859</v>
       </c>
       <c r="L8" t="n">
-        <v>5.365286006739959</v>
+        <v>5.365857439307738</v>
       </c>
       <c r="M8" t="n">
-        <v>4.680210007984827</v>
+        <v>4.68044530374803</v>
       </c>
       <c r="N8" t="n">
-        <v>3.90513018014615</v>
+        <v>3.905231021187522</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1054434352029907</v>
+        <v>0.1058263438637922</v>
       </c>
       <c r="P8" t="n">
-        <v>83.34048896180327</v>
+        <v>83.5981120606224</v>
       </c>
       <c r="Q8" t="n">
-        <v>-16.65951103819673</v>
+        <v>-16.4018879393776</v>
       </c>
       <c r="R8" t="n">
-        <v>103.3582102390184</v>
+        <v>103.5330335152855</v>
       </c>
       <c r="S8" t="n">
-        <v>53.52285131433752</v>
+        <v>53.66989314197057</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -23157,52 +23161,52 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56.15000152587891</v>
+        <v>56.22000122070312</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.593758255679571</v>
+        <v>-5.476066217709485</v>
       </c>
       <c r="F12" t="n">
-        <v>-39.41649726313311</v>
+        <v>-39.34097052069824</v>
       </c>
       <c r="G12" t="n">
-        <v>71.95970274030149</v>
+        <v>72.17407720845424</v>
       </c>
       <c r="H12" t="n">
-        <v>100.5858659831564</v>
+        <v>100.8359274083266</v>
       </c>
       <c r="I12" t="n">
-        <v>53.7047587690788</v>
+        <v>53.75344953604977</v>
       </c>
       <c r="J12" t="n">
         <v>65.17425855524525</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5550757372911717</v>
+        <v>0.5559157369986771</v>
       </c>
       <c r="L12" t="n">
-        <v>55.44766602068053</v>
+        <v>55.45433265828284</v>
       </c>
       <c r="M12" t="n">
-        <v>41.4161206607977</v>
+        <v>41.41886574686924</v>
       </c>
       <c r="N12" t="n">
-        <v>30.86391052190586</v>
+        <v>30.86508698736509</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1077503113424889</v>
+        <v>0.1122175283341225</v>
       </c>
       <c r="P12" t="n">
-        <v>25.83949934151423</v>
+        <v>25.91918026695585</v>
       </c>
       <c r="Q12" t="n">
-        <v>-74.16050065848577</v>
+        <v>-74.08081973304415</v>
       </c>
       <c r="R12" t="n">
-        <v>22.29026909929078</v>
+        <v>22.37798374309581</v>
       </c>
       <c r="S12" t="n">
-        <v>82.98843898694021</v>
+        <v>83.21656248716027</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -23985,52 +23989,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>162.3860015869141</v>
+        <v>162.3529968261719</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2859367876434815</v>
+        <v>0.2655537908510475</v>
       </c>
       <c r="F21" t="n">
-        <v>4.187764792265791</v>
+        <v>4.166588753594813</v>
       </c>
       <c r="G21" t="n">
-        <v>5.993320768732091</v>
+        <v>5.971777752966845</v>
       </c>
       <c r="H21" t="n">
-        <v>47.74855560946929</v>
+        <v>47.71852589212764</v>
       </c>
       <c r="I21" t="n">
-        <v>63.50945993850696</v>
+        <v>63.47846545760704</v>
       </c>
       <c r="J21" t="n">
         <v>27.3767733214772</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8715510774429333</v>
+        <v>0.8704303469204115</v>
       </c>
       <c r="L21" t="n">
-        <v>154.6170171285522</v>
+        <v>154.6138738180053</v>
       </c>
       <c r="M21" t="n">
-        <v>146.0799737201393</v>
+        <v>146.0786794157964</v>
       </c>
       <c r="N21" t="n">
-        <v>131.9569998897295</v>
+        <v>131.9565215598637</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7024386169814791</v>
+        <v>0.7003323302560629</v>
       </c>
       <c r="P21" t="n">
-        <v>97.79553680484024</v>
+        <v>97.63385175207395</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.204463195159764</v>
+        <v>-2.366148247926051</v>
       </c>
       <c r="R21" t="n">
-        <v>122.5972783329973</v>
+        <v>122.4672263145565</v>
       </c>
       <c r="S21" t="n">
-        <v>7.416623171973824</v>
+        <v>7.394790871696233</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -24060,7 +24064,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (64) — momentum positivo; pattern: Double Top; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (162.84)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 27); RSI in forza (63) — momentum positivo; pattern: Double Top; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (162.84)</t>
         </is>
       </c>
     </row>
@@ -24449,52 +24453,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>88.16000366210938</v>
+        <v>88.08999633789062</v>
       </c>
       <c r="E26" t="n">
-        <v>20.89962407549042</v>
+        <v>20.80361841726679</v>
       </c>
       <c r="F26" t="n">
-        <v>21.63355350296876</v>
+        <v>21.53696503583804</v>
       </c>
       <c r="G26" t="n">
-        <v>20.50300608140718</v>
+        <v>20.40731537512717</v>
       </c>
       <c r="H26" t="n">
-        <v>26.61210274251706</v>
+        <v>26.51156083963006</v>
       </c>
       <c r="I26" t="n">
-        <v>53.5809132491087</v>
+        <v>53.55530708083293</v>
       </c>
       <c r="J26" t="n">
         <v>21.82908187302554</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6926177874224227</v>
+        <v>0.6916011802095858</v>
       </c>
       <c r="L26" t="n">
-        <v>80.50891248159674</v>
+        <v>80.50224511738543</v>
       </c>
       <c r="M26" t="n">
-        <v>78.24202920849372</v>
+        <v>78.23928382323024</v>
       </c>
       <c r="N26" t="n">
-        <v>71.80258772786704</v>
+        <v>71.80141113418269</v>
       </c>
       <c r="O26" t="n">
-        <v>2.427941658315314</v>
+        <v>2.423473954433547</v>
       </c>
       <c r="P26" t="n">
-        <v>43.69249575757864</v>
+        <v>43.58859648914227</v>
       </c>
       <c r="Q26" t="n">
-        <v>-56.30750424242136</v>
+        <v>-56.41140351085773</v>
       </c>
       <c r="R26" t="n">
-        <v>40.94253469668924</v>
+        <v>40.81401764409831</v>
       </c>
       <c r="S26" t="n">
-        <v>20.86646656329574</v>
+        <v>20.77048723525143</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -25001,52 +25005,52 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>81.80000305175781</v>
+        <v>81.76999664306641</v>
       </c>
       <c r="E32" t="n">
-        <v>17.69784611763714</v>
+        <v>17.65467142887254</v>
       </c>
       <c r="F32" t="n">
-        <v>22.05312913906343</v>
+        <v>22.00835681707838</v>
       </c>
       <c r="G32" t="n">
-        <v>18.10568947263658</v>
+        <v>18.06236517612214</v>
       </c>
       <c r="H32" t="n">
-        <v>23.34138031991229</v>
+        <v>23.29613543325746</v>
       </c>
       <c r="I32" t="n">
-        <v>53.67393904786552</v>
+        <v>53.66127796058519</v>
       </c>
       <c r="J32" t="n">
         <v>20.16074759592006</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7024869095573084</v>
+        <v>0.7019729239872177</v>
       </c>
       <c r="L32" t="n">
-        <v>74.90259200365263</v>
+        <v>74.89973425044391</v>
       </c>
       <c r="M32" t="n">
-        <v>73.10754389771536</v>
+        <v>73.10636717580589</v>
       </c>
       <c r="N32" t="n">
-        <v>67.10948393352345</v>
+        <v>67.10897962413368</v>
       </c>
       <c r="O32" t="n">
-        <v>2.301518148721637</v>
+        <v>2.299603209819391</v>
       </c>
       <c r="P32" t="n">
-        <v>41.58139833072406</v>
+        <v>41.53487676961282</v>
       </c>
       <c r="Q32" t="n">
-        <v>-58.41860166927594</v>
+        <v>-58.46512323038718</v>
       </c>
       <c r="R32" t="n">
-        <v>36.31613495659167</v>
+        <v>36.25753271437716</v>
       </c>
       <c r="S32" t="n">
-        <v>20.29412213493795</v>
+        <v>20.24999506333296</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -25457,52 +25461,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4020.199951171875</v>
+        <v>4023</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.06711455013588274</v>
+        <v>0.002488196541805543</v>
       </c>
       <c r="F37" t="n">
-        <v>-23.13928016113421</v>
+        <v>-23.08574706051046</v>
       </c>
       <c r="G37" t="n">
-        <v>46.8137121383885</v>
+        <v>46.91596714252228</v>
       </c>
       <c r="H37" t="n">
-        <v>111.3114297593627</v>
+        <v>111.4586070959264</v>
       </c>
       <c r="I37" t="n">
-        <v>58.25885970876538</v>
+        <v>58.32159435106114</v>
       </c>
       <c r="J37" t="n">
         <v>84.28373204706031</v>
       </c>
       <c r="K37" t="n">
-        <v>0.570865470456523</v>
+        <v>0.5717654070261009</v>
       </c>
       <c r="L37" t="n">
-        <v>3863.383345623005</v>
+        <v>3863.650016939969</v>
       </c>
       <c r="M37" t="n">
-        <v>3075.94342288488</v>
+        <v>3076.053228721277</v>
       </c>
       <c r="N37" t="n">
-        <v>2353.710951277279</v>
+        <v>2353.75801092145</v>
       </c>
       <c r="O37" t="n">
-        <v>-35.88833972761677</v>
+        <v>-35.70964715283003</v>
       </c>
       <c r="P37" t="n">
-        <v>32.85885157823129</v>
+        <v>32.97890168337065</v>
       </c>
       <c r="Q37" t="n">
-        <v>-67.1411484217687</v>
+        <v>-67.02109831662935</v>
       </c>
       <c r="R37" t="n">
-        <v>18.91169262147276</v>
+        <v>18.97747444866109</v>
       </c>
       <c r="S37" t="n">
-        <v>51.30598235498211</v>
+        <v>51.41136620248401</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -25733,52 +25737,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1604.5</v>
+        <v>1603.5</v>
       </c>
       <c r="E40" t="n">
-        <v>3.502777095759613</v>
+        <v>3.43826928828328</v>
       </c>
       <c r="F40" t="n">
-        <v>-32.17365853215512</v>
+        <v>-32.21593110396432</v>
       </c>
       <c r="G40" t="n">
-        <v>61.80920124084304</v>
+        <v>61.70835412258759</v>
       </c>
       <c r="H40" t="n">
-        <v>35.88244695555123</v>
+        <v>35.79775861216979</v>
       </c>
       <c r="I40" t="n">
-        <v>53.2935454050812</v>
+        <v>53.2682984951701</v>
       </c>
       <c r="J40" t="n">
         <v>71.14495380194761</v>
       </c>
       <c r="K40" t="n">
-        <v>0.5525634896874799</v>
+        <v>0.5520330647356202</v>
       </c>
       <c r="L40" t="n">
-        <v>1585.411397510528</v>
+        <v>1585.31615941529</v>
       </c>
       <c r="M40" t="n">
-        <v>1307.983995214608</v>
+        <v>1307.944779528334</v>
       </c>
       <c r="N40" t="n">
-        <v>1136.770810910391</v>
+        <v>1136.754004187702</v>
       </c>
       <c r="O40" t="n">
-        <v>-9.370322907417489</v>
+        <v>-9.434140571235133</v>
       </c>
       <c r="P40" t="n">
-        <v>30.69917608807448</v>
+        <v>30.64364212755267</v>
       </c>
       <c r="Q40" t="n">
-        <v>-69.30082391192552</v>
+        <v>-69.35635787244733</v>
       </c>
       <c r="R40" t="n">
-        <v>13.08288072920266</v>
+        <v>13.02838148664089</v>
       </c>
       <c r="S40" t="n">
-        <v>68.9836756187467</v>
+        <v>68.87835703001579</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -27309,52 +27313,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.144033789634705</v>
+        <v>1.144557595252991</v>
       </c>
       <c r="E57" t="n">
-        <v>0.1601627301765163</v>
+        <v>0.2060219140938679</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.072880791023225</v>
+        <v>-3.028501883629087</v>
       </c>
       <c r="G57" t="n">
-        <v>5.351782385088533</v>
+        <v>5.400018596299905</v>
       </c>
       <c r="H57" t="n">
-        <v>-6.150333911284922</v>
+        <v>-6.107364042023244</v>
       </c>
       <c r="I57" t="n">
-        <v>51.92693916380263</v>
+        <v>52.02857392141421</v>
       </c>
       <c r="J57" t="n">
         <v>41.53072495647007</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5283683150152734</v>
+        <v>0.5309362635299427</v>
       </c>
       <c r="L57" t="n">
-        <v>1.142889864691511</v>
+        <v>1.142939750940871</v>
       </c>
       <c r="M57" t="n">
-        <v>1.123275532208056</v>
+        <v>1.123296073604852</v>
       </c>
       <c r="N57" t="n">
-        <v>1.121885295077283</v>
+        <v>1.121892886463055</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.002689331989594954</v>
+        <v>-0.002655903938741353</v>
       </c>
       <c r="P57" t="n">
-        <v>16.46128338794474</v>
+        <v>17.21155701413636</v>
       </c>
       <c r="Q57" t="n">
-        <v>-83.53871661205527</v>
+        <v>-82.78844298586364</v>
       </c>
       <c r="R57" t="n">
-        <v>8.168102410184488</v>
+        <v>8.401658367022565</v>
       </c>
       <c r="S57" t="n">
-        <v>8.30567434843481</v>
+        <v>8.35526302425016</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -27371,7 +27375,7 @@
         <v>58.1</v>
       </c>
       <c r="X57" t="n">
-        <v>68.2</v>
+        <v>68.3</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -29237,52 +29241,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.34551465511322</v>
+        <v>1.345243215560913</v>
       </c>
       <c r="E78" t="n">
-        <v>1.51773898929588</v>
+        <v>1.497259145752183</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.2691065329109898</v>
+        <v>-0.2892259043136169</v>
       </c>
       <c r="G78" t="n">
-        <v>3.823946078857476</v>
+        <v>3.803000988935712</v>
       </c>
       <c r="H78" t="n">
-        <v>-5.11430507357491</v>
+        <v>-5.133446991095692</v>
       </c>
       <c r="I78" t="n">
-        <v>54.28928356371395</v>
+        <v>54.25049603451004</v>
       </c>
       <c r="J78" t="n">
         <v>21.9800895457339</v>
       </c>
       <c r="K78" t="n">
-        <v>0.6259981573752565</v>
+        <v>0.6243013517504041</v>
       </c>
       <c r="L78" t="n">
-        <v>1.327401445381491</v>
+        <v>1.327375593995557</v>
       </c>
       <c r="M78" t="n">
-        <v>1.307831285622253</v>
+        <v>1.307820640933927</v>
       </c>
       <c r="N78" t="n">
-        <v>1.332887511375497</v>
+        <v>1.332883577468942</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.001961662756056751</v>
+        <v>-0.001978985394152789</v>
       </c>
       <c r="P78" t="n">
-        <v>53.10368553735643</v>
+        <v>52.77864221252152</v>
       </c>
       <c r="Q78" t="n">
-        <v>-46.89631446264357</v>
+        <v>-47.22135778747848</v>
       </c>
       <c r="R78" t="n">
-        <v>32.54701444647591</v>
+        <v>32.38488587667429</v>
       </c>
       <c r="S78" t="n">
-        <v>5.972735692031272</v>
+        <v>5.951357112597977</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -29973,52 +29977,52 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>100.7630004882812</v>
+        <v>100.754997253418</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.4219803763442442</v>
+        <v>-0.4298894925317986</v>
       </c>
       <c r="F86" t="n">
-        <v>3.230201678326106</v>
+        <v>3.222002482738318</v>
       </c>
       <c r="G86" t="n">
-        <v>-3.093866863621164</v>
+        <v>-3.101563761683201</v>
       </c>
       <c r="H86" t="n">
-        <v>11.92158375487229</v>
+        <v>11.91269423474366</v>
       </c>
       <c r="I86" t="n">
-        <v>50.32103636299556</v>
+        <v>50.30288680451639</v>
       </c>
       <c r="J86" t="n">
         <v>28.97798595210455</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5145676654511445</v>
+        <v>0.5140510383357962</v>
       </c>
       <c r="L86" t="n">
-        <v>100.2526714204217</v>
+        <v>100.2519092075776</v>
       </c>
       <c r="M86" t="n">
-        <v>100.8265080592025</v>
+        <v>100.8261942068549</v>
       </c>
       <c r="N86" t="n">
-        <v>99.52450381082471</v>
+        <v>99.52436930267575</v>
       </c>
       <c r="O86" t="n">
-        <v>0.2181796540530958</v>
+        <v>0.2176689063011383</v>
       </c>
       <c r="P86" t="n">
-        <v>83.407958984375</v>
+        <v>83.2799072265625</v>
       </c>
       <c r="Q86" t="n">
-        <v>-16.592041015625</v>
+        <v>-16.7200927734375</v>
       </c>
       <c r="R86" t="n">
-        <v>5.697407010271552</v>
+        <v>5.647445363952857</v>
       </c>
       <c r="S86" t="n">
-        <v>-4.706825681896087</v>
+        <v>-4.714394468566196</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -30161,52 +30165,52 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E88" t="n">
-        <v>4.249999999999998</v>
+        <v>4.166666666666674</v>
       </c>
       <c r="F88" t="n">
-        <v>-30.19752069616997</v>
+        <v>-30.25331804173658</v>
       </c>
       <c r="G88" t="n">
-        <v>13.05919566199729</v>
+        <v>12.96882060551288</v>
       </c>
       <c r="H88" t="n">
-        <v>-55.70426946998177</v>
+        <v>-55.73967772779953</v>
       </c>
       <c r="I88" t="n">
-        <v>47.93446518312913</v>
+        <v>47.90246514412587</v>
       </c>
       <c r="J88" t="n">
         <v>55.92754409715847</v>
       </c>
       <c r="K88" t="n">
-        <v>0.4894347553541144</v>
+        <v>0.4885684738517659</v>
       </c>
       <c r="L88" t="n">
-        <v>1322.090266413943</v>
+        <v>1321.995028318705</v>
       </c>
       <c r="M88" t="n">
-        <v>1360.903607294537</v>
+        <v>1360.864391608262</v>
       </c>
       <c r="N88" t="n">
-        <v>1353.884011836155</v>
+        <v>1353.867205113466</v>
       </c>
       <c r="O88" t="n">
-        <v>2.550577608613523</v>
+        <v>2.486759944795878</v>
       </c>
       <c r="P88" t="n">
-        <v>22.96923651864323</v>
+        <v>22.88540718828321</v>
       </c>
       <c r="Q88" t="n">
-        <v>-77.03076348135677</v>
+        <v>-77.11459281171679</v>
       </c>
       <c r="R88" t="n">
-        <v>-6.973286694897025</v>
+        <v>-7.066675511446096</v>
       </c>
       <c r="S88" t="n">
-        <v>26.33811195494518</v>
+        <v>26.23712225713948</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -30227,7 +30231,7 @@
         <v>49</v>
       </c>
       <c r="X88" t="n">
-        <v>73.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -30811,52 +30815,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.088600039482117</v>
+        <v>1.088299989700317</v>
       </c>
       <c r="E95" t="n">
-        <v>4.831338188966527</v>
+        <v>4.802443628054798</v>
       </c>
       <c r="F95" t="n">
-        <v>-20.95722214614792</v>
+        <v>-20.97900863097954</v>
       </c>
       <c r="G95" t="n">
-        <v>113.7708096337612</v>
+        <v>113.7118881911199</v>
       </c>
       <c r="H95" t="n">
-        <v>4.014587357676502</v>
+        <v>3.985917917010795</v>
       </c>
       <c r="I95" t="n">
-        <v>41.56980574060299</v>
+        <v>41.56384752868129</v>
       </c>
       <c r="J95" t="n">
         <v>38.94285314741881</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1303326678573417</v>
+        <v>0.1302327266646235</v>
       </c>
       <c r="L95" t="n">
-        <v>1.597815611859508</v>
+        <v>1.597787035689813</v>
       </c>
       <c r="M95" t="n">
-        <v>1.328984548475339</v>
+        <v>1.328972546484067</v>
       </c>
       <c r="N95" t="n">
-        <v>1.041945985440398</v>
+        <v>1.041939861975464</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.1931901227811191</v>
+        <v>-0.1932092712572225</v>
       </c>
       <c r="P95" t="n">
-        <v>2.986113888919238</v>
+        <v>2.974750333615383</v>
       </c>
       <c r="Q95" t="n">
-        <v>-97.01388611108077</v>
+        <v>-97.02524966638461</v>
       </c>
       <c r="R95" t="n">
-        <v>-66.01203027204744</v>
+        <v>-66.01818733709341</v>
       </c>
       <c r="S95" t="n">
-        <v>-44.00554092477963</v>
+        <v>-44.02097462367559</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -30999,52 +31003,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>64142.98828125</v>
+        <v>64064.3515625</v>
       </c>
       <c r="E97" t="n">
-        <v>9.535924992135314</v>
+        <v>9.401638362256781</v>
       </c>
       <c r="F97" t="n">
-        <v>-4.25827972111149</v>
+        <v>-4.37565521190092</v>
       </c>
       <c r="G97" t="n">
-        <v>-8.647985478569009</v>
+        <v>-8.759979366999481</v>
       </c>
       <c r="H97" t="n">
-        <v>71.81377496007988</v>
+        <v>71.60313819586071</v>
       </c>
       <c r="I97" t="n">
-        <v>43.8454913440569</v>
+        <v>43.80392858789092</v>
       </c>
       <c r="J97" t="n">
         <v>30.22243585581548</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1489483922494425</v>
+        <v>0.1480103528113647</v>
       </c>
       <c r="L97" t="n">
-        <v>78308.27289310856</v>
+        <v>78300.78368179903</v>
       </c>
       <c r="M97" t="n">
-        <v>66409.55412011087</v>
+        <v>66406.40865136088</v>
       </c>
       <c r="N97" t="n">
-        <v>49888.61692007069</v>
+        <v>49887.01208907579</v>
       </c>
       <c r="O97" t="n">
-        <v>-6034.3424576117</v>
+        <v>-6039.360869292605</v>
       </c>
       <c r="P97" t="n">
-        <v>9.342869524754443</v>
+        <v>9.227988051094094</v>
       </c>
       <c r="Q97" t="n">
-        <v>-90.65713047524555</v>
+        <v>-90.77201194890591</v>
       </c>
       <c r="R97" t="n">
-        <v>-73.24995371290107</v>
+        <v>-73.31214670127569</v>
       </c>
       <c r="S97" t="n">
-        <v>-33.4954723101469</v>
+        <v>-33.57700418104474</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31375,52 +31379,52 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2.92300009727478</v>
+        <v>2.915999889373779</v>
       </c>
       <c r="E101" t="n">
-        <v>-10.74809123183124</v>
+        <v>-10.9618380317444</v>
       </c>
       <c r="F101" t="n">
-        <v>2.238549507714405</v>
+        <v>1.993701379683888</v>
       </c>
       <c r="G101" t="n">
-        <v>7.979315801215447</v>
+        <v>7.720719278991228</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.109844690978868</v>
+        <v>-2.344278976240544</v>
       </c>
       <c r="I101" t="n">
-        <v>46.86215625162339</v>
+        <v>46.81340239157225</v>
       </c>
       <c r="J101" t="n">
         <v>47.66047596718737</v>
       </c>
       <c r="K101" t="n">
-        <v>0.2575080802090833</v>
+        <v>0.2546845812968515</v>
       </c>
       <c r="L101" t="n">
-        <v>3.302688060340363</v>
+        <v>3.302021373873601</v>
       </c>
       <c r="M101" t="n">
-        <v>3.361289401862388</v>
+        <v>3.361014883905486</v>
       </c>
       <c r="N101" t="n">
-        <v>3.311177605653608</v>
+        <v>3.311059955100649</v>
       </c>
       <c r="O101" t="n">
-        <v>-0.06699592656026868</v>
+        <v>-0.06744266347474814</v>
       </c>
       <c r="P101" t="n">
-        <v>8.233533849124674</v>
+        <v>8.102541937287439</v>
       </c>
       <c r="Q101" t="n">
-        <v>-91.76646615087533</v>
+        <v>-91.89745806271256</v>
       </c>
       <c r="R101" t="n">
-        <v>-46.69689837419935</v>
+        <v>-46.89166691574044</v>
       </c>
       <c r="S101" t="n">
-        <v>-13.08355128700663</v>
+        <v>-13.2917049615737</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -31434,10 +31438,10 @@
       </c>
       <c r="V101" t="inlineStr"/>
       <c r="W101" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="X101" t="n">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
@@ -31559,52 +31563,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>75.11000061035156</v>
+        <v>74.98000335693359</v>
       </c>
       <c r="E103" t="n">
-        <v>2.158081372465492</v>
+        <v>1.981270430048343</v>
       </c>
       <c r="F103" t="n">
-        <v>-10.97143400767803</v>
+        <v>-11.12552093299684</v>
       </c>
       <c r="G103" t="n">
-        <v>-55.40580426495991</v>
+        <v>-55.48298603725164</v>
       </c>
       <c r="H103" t="n">
-        <v>128.880538424394</v>
+        <v>128.4844015436296</v>
       </c>
       <c r="I103" t="n">
-        <v>40.74441293693928</v>
+        <v>40.71448607161677</v>
       </c>
       <c r="J103" t="n">
         <v>26.01849398425852</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1799327246173763</v>
+        <v>0.1793645071335024</v>
       </c>
       <c r="L103" t="n">
-        <v>117.766983220831</v>
+        <v>117.7546025300293</v>
       </c>
       <c r="M103" t="n">
-        <v>115.4604011666892</v>
+        <v>115.4537346408729</v>
       </c>
       <c r="N103" t="n">
-        <v>93.56465060662474</v>
+        <v>93.56118401320026</v>
       </c>
       <c r="O103" t="n">
-        <v>-12.86737078894011</v>
+        <v>-12.87566690995595</v>
       </c>
       <c r="P103" t="n">
-        <v>7.622224728482927</v>
+        <v>7.554797081921088</v>
       </c>
       <c r="Q103" t="n">
-        <v>-92.37777527151707</v>
+        <v>-92.44520291807891</v>
       </c>
       <c r="R103" t="n">
-        <v>-92.01876591278725</v>
+        <v>-92.07229817227775</v>
       </c>
       <c r="S103" t="n">
-        <v>-60.31479315300827</v>
+        <v>-60.3834786522695</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -31747,52 +31751,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.1657000035047531</v>
+        <v>0.1659000068902969</v>
       </c>
       <c r="E105" t="n">
-        <v>14.94013983909119</v>
+        <v>15.07887500273915</v>
       </c>
       <c r="F105" t="n">
-        <v>-41.16080111067005</v>
+        <v>-41.0897809614145</v>
       </c>
       <c r="G105" t="n">
-        <v>-51.52773897021164</v>
+        <v>-51.46923193275919</v>
       </c>
       <c r="H105" t="n">
-        <v>-90.49219069404721</v>
+        <v>-90.48071456845834</v>
       </c>
       <c r="I105" t="n">
-        <v>37.36515341096159</v>
+        <v>37.37570260752243</v>
       </c>
       <c r="J105" t="n">
         <v>30.70524078487225</v>
       </c>
       <c r="K105" t="n">
-        <v>0.1573951664765518</v>
+        <v>0.1575610798961233</v>
       </c>
       <c r="L105" t="n">
-        <v>0.4071957348545091</v>
+        <v>0.4072147827959894</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4913831528648294</v>
+        <v>0.4913911530002512</v>
       </c>
       <c r="N105" t="n">
-        <v>0.4783412952935924</v>
+        <v>0.4783453769953382</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.04912516334640404</v>
+        <v>-0.04911239959758302</v>
       </c>
       <c r="P105" t="n">
-        <v>3.076549992802101</v>
+        <v>3.09933541664969</v>
       </c>
       <c r="Q105" t="n">
-        <v>-96.9234500071979</v>
+        <v>-96.90066458335031</v>
       </c>
       <c r="R105" t="n">
-        <v>-98.64798304029402</v>
+        <v>-98.63289705490286</v>
       </c>
       <c r="S105" t="n">
-        <v>-84.64236144986184</v>
+        <v>-84.62382445747187</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -32119,52 +32123,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>8.244000434875488</v>
+        <v>8.237000465393066</v>
       </c>
       <c r="E109" t="n">
-        <v>14.66793107715916</v>
+        <v>14.57056669387298</v>
       </c>
       <c r="F109" t="n">
-        <v>-6.781419478064176</v>
+        <v>-6.86057124716013</v>
       </c>
       <c r="G109" t="n">
-        <v>-27.82504903318359</v>
+        <v>-27.88633268523506</v>
       </c>
       <c r="H109" t="n">
-        <v>-74.30861952749876</v>
+        <v>-74.330434043484</v>
       </c>
       <c r="I109" t="n">
-        <v>42.03221618423942</v>
+        <v>42.01823444884148</v>
       </c>
       <c r="J109" t="n">
         <v>21.04094275559561</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2245757344220339</v>
+        <v>0.2242797420049692</v>
       </c>
       <c r="L109" t="n">
-        <v>12.08091235891311</v>
+        <v>12.08024569515288</v>
       </c>
       <c r="M109" t="n">
-        <v>12.62231225876282</v>
+        <v>12.62203225998352</v>
       </c>
       <c r="N109" t="n">
-        <v>10.87978689004267</v>
+        <v>10.87964403352262</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.9847666522264666</v>
+        <v>-0.9852133739256295</v>
       </c>
       <c r="P109" t="n">
-        <v>5.897768826987742</v>
+        <v>5.863973534879125</v>
       </c>
       <c r="Q109" t="n">
-        <v>-94.10223117301226</v>
+        <v>-94.13602646512088</v>
       </c>
       <c r="R109" t="n">
-        <v>-96.69075625432892</v>
+        <v>-96.72148238585194</v>
       </c>
       <c r="S109" t="n">
-        <v>-56.66221279844401</v>
+        <v>-56.69901085422324</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -32215,52 +32219,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1844.760009765625</v>
+        <v>1840.780029296875</v>
       </c>
       <c r="E110" t="n">
-        <v>17.53179005401371</v>
+        <v>17.27822090334048</v>
       </c>
       <c r="F110" t="n">
-        <v>-6.121497899015848</v>
+        <v>-6.324036225312768</v>
       </c>
       <c r="G110" t="n">
-        <v>-26.67300616009333</v>
+        <v>-26.83120560163048</v>
       </c>
       <c r="H110" t="n">
-        <v>-32.0516696497685</v>
+        <v>-32.19826488505466</v>
       </c>
       <c r="I110" t="n">
-        <v>43.04023827244625</v>
+        <v>42.99813245401433</v>
       </c>
       <c r="J110" t="n">
         <v>13.65760872685721</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2521299650095779</v>
+        <v>0.251077604015107</v>
       </c>
       <c r="L110" t="n">
-        <v>2506.922594780993</v>
+        <v>2506.543549022064</v>
       </c>
       <c r="M110" t="n">
-        <v>2422.917707439187</v>
+        <v>2422.758508220437</v>
       </c>
       <c r="N110" t="n">
-        <v>2008.867128076608</v>
+        <v>2008.785903985409</v>
       </c>
       <c r="O110" t="n">
-        <v>-185.3008882338464</v>
+        <v>-185.5548812894018</v>
       </c>
       <c r="P110" t="n">
-        <v>9.812358034446914</v>
+        <v>9.696903488831408</v>
       </c>
       <c r="Q110" t="n">
-        <v>-90.18764196555308</v>
+        <v>-90.30309651116859</v>
       </c>
       <c r="R110" t="n">
-        <v>-94.81053185895071</v>
+        <v>-94.92617359579404</v>
       </c>
       <c r="S110" t="n">
-        <v>-50.21838356435313</v>
+        <v>-50.32578499330207</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -32687,52 +32691,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.8529999852180481</v>
+        <v>0.8510000109672546</v>
       </c>
       <c r="E115" t="n">
-        <v>3.942118530184691</v>
+        <v>3.698412124281125</v>
       </c>
       <c r="F115" t="n">
-        <v>-48.94169441920045</v>
+        <v>-49.06140754724305</v>
       </c>
       <c r="G115" t="n">
-        <v>-78.44026352025213</v>
+        <v>-78.49081324892812</v>
       </c>
       <c r="H115" t="n">
-        <v>-96.35951247192206</v>
+        <v>-96.36804808908813</v>
       </c>
       <c r="I115" t="n">
-        <v>34.11214062246292</v>
+        <v>34.09821401661303</v>
       </c>
       <c r="J115" t="n">
         <v>33.95248828848647</v>
       </c>
       <c r="K115" t="n">
-        <v>0.1913067476821492</v>
+        <v>0.1910566542904429</v>
       </c>
       <c r="L115" t="n">
-        <v>2.779045387577542</v>
+        <v>2.778854913839372</v>
       </c>
       <c r="M115" t="n">
-        <v>4.378780448835004</v>
+        <v>4.378672342118745</v>
       </c>
       <c r="N115" t="n">
-        <v>6.390301926009451</v>
+        <v>6.390245588706612</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.04759918899056492</v>
+        <v>-0.04772682267494632</v>
       </c>
       <c r="P115" t="n">
-        <v>1.329168141886983</v>
+        <v>1.28009390942471</v>
       </c>
       <c r="Q115" t="n">
-        <v>-98.67083185811302</v>
+        <v>-98.71990609057529</v>
       </c>
       <c r="R115" t="n">
-        <v>-73.30232524717712</v>
+        <v>-73.32090656382995</v>
       </c>
       <c r="S115" t="n">
-        <v>-86.49968058001988</v>
+        <v>-86.53133391142124</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -32875,52 +32879,52 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.559999942779541</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E117" t="n">
-        <v>0.5117968774772219</v>
+        <v>0.8182349930219823</v>
       </c>
       <c r="F117" t="n">
-        <v>-28.41984185192339</v>
+        <v>-28.20160986866642</v>
       </c>
       <c r="G117" t="n">
-        <v>-73.77796146102928</v>
+        <v>-73.69801629712558</v>
       </c>
       <c r="H117" t="n">
-        <v>-63.87927728082261</v>
+        <v>-63.76915323025298</v>
       </c>
       <c r="I117" t="n">
-        <v>38.7276721590366</v>
+        <v>38.75052999343363</v>
       </c>
       <c r="J117" t="n">
         <v>16.96239899989589</v>
       </c>
       <c r="K117" t="n">
-        <v>0.1920037801405718</v>
+        <v>0.1924929074918431</v>
       </c>
       <c r="L117" t="n">
-        <v>15.64067424604288</v>
+        <v>15.64257900613111</v>
       </c>
       <c r="M117" t="n">
-        <v>19.46756152841023</v>
+        <v>19.46864260846031</v>
       </c>
       <c r="N117" t="n">
-        <v>20.88356997955371</v>
+        <v>20.88413335929812</v>
       </c>
       <c r="O117" t="n">
-        <v>-1.158267372111995</v>
+        <v>-1.156991020052869</v>
       </c>
       <c r="P117" t="n">
-        <v>2.867403897229872</v>
+        <v>2.933592454943121</v>
       </c>
       <c r="Q117" t="n">
-        <v>-97.13259610277012</v>
+        <v>-97.06640754505688</v>
       </c>
       <c r="R117" t="n">
-        <v>-77.48245468574979</v>
+        <v>-77.44356490766094</v>
       </c>
       <c r="S117" t="n">
-        <v>-80.92892660152846</v>
+        <v>-80.87078314001252</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -33208,7 +33212,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/07/2026 20:56:41</t>
+          <t>17/07/2026 21:55:08</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33248,13 +33252,13 @@
         <v>18.77000045776367</v>
       </c>
       <c r="N2" t="n">
-        <v>100.7630004882812</v>
+        <v>100.754997253418</v>
       </c>
       <c r="O2" t="n">
-        <v>4020.199951171875</v>
+        <v>4023</v>
       </c>
       <c r="P2" t="n">
-        <v>81.80000305175781</v>
+        <v>81.76999664306641</v>
       </c>
       <c r="Q2" t="n">
         <v>4.653762108173187</v>
@@ -33271,7 +33275,7 @@
         <v>3.815913207353798</v>
       </c>
       <c r="U2" t="n">
-        <v>3.72747300968979</v>
+        <v>3.725164624214396</v>
       </c>
       <c r="V2" t="n">
         <v>0.9857960016205869</v>
@@ -33295,10 +33299,10 @@
         <v>0.5875869446908326</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5390677250942147</v>
+        <v>0.5394431830242339</v>
       </c>
       <c r="AD2" t="n">
-        <v>-20.91920068668609</v>
+        <v>-20.86412131199482</v>
       </c>
       <c r="AE2" t="n">
         <v>-2.879446194121005</v>
@@ -33322,7 +33326,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.74573173668003</v>
+        <v>2.745347005767464</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33421,10 +33425,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57.98302908743315</v>
+        <v>57.98306733031569</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09592876738628393</v>
+        <v>0.09593029710158595</v>
       </c>
       <c r="D2" t="n">
         <v>53.44827586206896</v>
@@ -33433,7 +33437,7 @@
         <v>16.13932802825844</v>
       </c>
       <c r="F2" t="n">
-        <v>11.08941539054056</v>
+        <v>11.08941539054062</v>
       </c>
     </row>
   </sheetData>
@@ -33783,7 +33787,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.871</v>
+        <v>0.87</v>
       </c>
       <c r="D16" t="n">
         <v>0.908</v>
@@ -33837,64 +33841,64 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.905</v>
+        <v>0.882</v>
       </c>
       <c r="D19" t="n">
-        <v>0.903</v>
+        <v>0.902</v>
       </c>
       <c r="E19" t="n">
-        <v>0.873</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.882</v>
+        <v>0.915</v>
       </c>
       <c r="D20" t="n">
         <v>0.902</v>
       </c>
       <c r="E20" t="n">
-        <v>0.914</v>
+        <v>0.924</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.915</v>
+        <v>0.903</v>
       </c>
       <c r="D21" t="n">
         <v>0.902</v>
       </c>
       <c r="E21" t="n">
-        <v>0.924</v>
+        <v>0.873</v>
       </c>
     </row>
   </sheetData>
@@ -34013,7 +34017,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.616</v>
+        <v>-0.615</v>
       </c>
       <c r="D5" t="n">
         <v>-0.646</v>
@@ -34124,7 +34128,7 @@
         <v>-0.632</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.62</v>
+        <v>-0.619</v>
       </c>
     </row>
     <row r="11">
@@ -34247,7 +34251,7 @@
         <v>-0.715</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.622</v>
+        <v>-0.621</v>
       </c>
       <c r="E16" t="n">
         <v>-0.628</v>
@@ -34340,7 +34344,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NIKKEI</t>
+          <t>EMERGING</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -34349,13 +34353,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>-0.587</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.585</v>
+        <v>-0.552</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1879,52 +1879,52 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6.572999954223633</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.704798071544111</v>
+        <v>-1.525344141737661</v>
       </c>
       <c r="F16" t="n">
-        <v>2.128652683098142</v>
+        <v>2.315105202755818</v>
       </c>
       <c r="G16" t="n">
-        <v>5.760254108548546</v>
+        <v>5.953336709171531</v>
       </c>
       <c r="H16" t="n">
-        <v>5.184827620202603</v>
+        <v>5.37685968587962</v>
       </c>
       <c r="I16" t="n">
-        <v>58.86133561428673</v>
+        <v>59.55461365800658</v>
       </c>
       <c r="J16" t="n">
-        <v>26.04965192483532</v>
+        <v>26.02347126370307</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7765573688239824</v>
+        <v>0.7942906439743983</v>
       </c>
       <c r="L16" t="n">
-        <v>6.439033582136014</v>
+        <v>6.44017644727157</v>
       </c>
       <c r="M16" t="n">
-        <v>6.32448585190375</v>
+        <v>6.324956443430156</v>
       </c>
       <c r="N16" t="n">
-        <v>5.865220287801378</v>
+        <v>5.865339691621511</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03100122295850949</v>
+        <v>0.03176704028011312</v>
       </c>
       <c r="P16" t="n">
-        <v>62.40232756099696</v>
+        <v>64.74609356810109</v>
       </c>
       <c r="Q16" t="n">
-        <v>-37.59767243900304</v>
+        <v>-35.25390643189891</v>
       </c>
       <c r="R16" t="n">
-        <v>103.9823810248665</v>
+        <v>105.1714189000503</v>
       </c>
       <c r="S16" t="n">
-        <v>5.446377640188871</v>
+        <v>5.638887208104104</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="W16" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>75.3</v>
@@ -5103,52 +5103,52 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.349181652069092</v>
+        <v>1.349272727966309</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1645963354083513</v>
+        <v>0.1713579011816568</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2293599715263772</v>
+        <v>0.2361259091396617</v>
       </c>
       <c r="G51" t="n">
-        <v>0.7137141612336917</v>
+        <v>0.7205127949574841</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.3337894935212971</v>
+        <v>-0.3270615710579516</v>
       </c>
       <c r="I51" t="n">
-        <v>58.49560138131013</v>
+        <v>58.55969226052518</v>
       </c>
       <c r="J51" t="n">
         <v>12.97541558281955</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7901449347094288</v>
+        <v>0.7929552566498163</v>
       </c>
       <c r="L51" t="n">
-        <v>1.340801327439734</v>
+        <v>1.340810001334707</v>
       </c>
       <c r="M51" t="n">
-        <v>1.339232108390285</v>
+        <v>1.339235679994098</v>
       </c>
       <c r="N51" t="n">
-        <v>1.338861195693146</v>
+        <v>1.338862101920979</v>
       </c>
       <c r="O51" t="n">
-        <v>0.001116642042540951</v>
+        <v>0.001122454293531674</v>
       </c>
       <c r="P51" t="n">
-        <v>93.31125457218586</v>
+        <v>93.69992216473605</v>
       </c>
       <c r="Q51" t="n">
-        <v>-6.688745427814152</v>
+        <v>-6.300077835263953</v>
       </c>
       <c r="R51" t="n">
-        <v>63.09650232843503</v>
+        <v>63.34427583259336</v>
       </c>
       <c r="S51" t="n">
-        <v>0.5680019804806147</v>
+        <v>0.574790777969536</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="W51" t="n">
-        <v>61.9</v>
+        <v>62</v>
       </c>
       <c r="X51" t="n">
         <v>68</v>
@@ -5567,52 +5567,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4396.10009765625</v>
+        <v>4401.2998046875</v>
       </c>
       <c r="E56" t="n">
-        <v>3.632722717026171</v>
+        <v>3.755299497583686</v>
       </c>
       <c r="F56" t="n">
-        <v>8.569805429133615</v>
+        <v>8.698221790938554</v>
       </c>
       <c r="G56" t="n">
-        <v>6.427637479373716</v>
+        <v>6.553520085007691</v>
       </c>
       <c r="H56" t="n">
-        <v>-6.8701764976836</v>
+        <v>-6.760022545924804</v>
       </c>
       <c r="I56" t="n">
-        <v>67.35055818852578</v>
+        <v>67.56113118253454</v>
       </c>
       <c r="J56" t="n">
         <v>25.48234535245033</v>
       </c>
       <c r="K56" t="n">
-        <v>1.265573665296714</v>
+        <v>1.271389201789016</v>
       </c>
       <c r="L56" t="n">
-        <v>4134.326648449945</v>
+        <v>4134.821858643398</v>
       </c>
       <c r="M56" t="n">
-        <v>4204.272719756441</v>
+        <v>4204.476629836097</v>
       </c>
       <c r="N56" t="n">
-        <v>4278.300835086881</v>
+        <v>4278.352573465301</v>
       </c>
       <c r="O56" t="n">
-        <v>41.68407105414982</v>
+        <v>42.0159042094204</v>
       </c>
       <c r="P56" t="n">
-        <v>91.63205749214556</v>
+        <v>92.83402438811036</v>
       </c>
       <c r="Q56" t="n">
-        <v>-8.367942507854435</v>
+        <v>-7.165975611889642</v>
       </c>
       <c r="R56" t="n">
-        <v>281.1794539836821</v>
+        <v>282.4489279250491</v>
       </c>
       <c r="S56" t="n">
-        <v>7.114836213832931</v>
+        <v>7.24153163810437</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5626,10 +5626,10 @@
         </is>
       </c>
       <c r="W56" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="X56" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5638,90 +5638,94 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); RSI in forza (67) — momentum positivo; pattern: Double Bottom; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (4,432); in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend in sviluppo (ADX 25); RSI in forza (68) — momentum positivo; pattern: Double Bottom; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (4,432); in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.952000141143799</v>
+        <v>0.2015500068664551</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8471736895117932</v>
+        <v>0.3795050782376297</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.5347604236009551</v>
+        <v>6.44084848023172</v>
       </c>
       <c r="G57" t="n">
-        <v>8.37581991114611</v>
+        <v>20.94718319997582</v>
       </c>
       <c r="H57" t="n">
-        <v>10.79672189556786</v>
+        <v>28.16680930805158</v>
       </c>
       <c r="I57" t="n">
-        <v>61.88130380530189</v>
+        <v>70.66977864387795</v>
       </c>
       <c r="J57" t="n">
-        <v>42.32817109432707</v>
+        <v>27.15839974878673</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8617229418086314</v>
+        <v>0.9648516737414284</v>
       </c>
       <c r="L57" t="n">
-        <v>5.75850460512098</v>
+        <v>0.1796694960770059</v>
       </c>
       <c r="M57" t="n">
-        <v>5.696320452547448</v>
+        <v>0.1779360720806342</v>
       </c>
       <c r="N57" t="n">
-        <v>5.867409499388407</v>
+        <v>0.257677387111932</v>
       </c>
       <c r="O57" t="n">
-        <v>0.02115506835360864</v>
+        <v>0.003849782170116603</v>
       </c>
       <c r="P57" t="n">
-        <v>52.71150729167852</v>
+        <v>83.78184954493226</v>
       </c>
       <c r="Q57" t="n">
-        <v>-47.28849270832148</v>
+        <v>-16.21815045506774</v>
       </c>
       <c r="R57" t="n">
-        <v>93.69255748532832</v>
+        <v>184.19577398376</v>
       </c>
       <c r="S57" t="n">
-        <v>7.281908661960346</v>
+        <v>20.96242353543205</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Inside Bar, Bull Flag / Consolidation</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W57" t="n">
         <v>60.6</v>
       </c>
       <c r="X57" t="n">
-        <v>66</v>
+        <v>66.5</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5730,94 +5734,90 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); RSI in forza (62) — momentum positivo; pattern: Bull Flag / Consolidation; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 27); RSI in forza (71) — momentum positivo; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.2013500034809113</v>
+        <v>5.952000141143799</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2798958489104164</v>
+        <v>0.8471736895117932</v>
       </c>
       <c r="F58" t="n">
-        <v>6.335224420043484</v>
+        <v>-0.5347604236009551</v>
       </c>
       <c r="G58" t="n">
-        <v>20.82716412139543</v>
+        <v>8.37581991114611</v>
       </c>
       <c r="H58" t="n">
-        <v>28.03962600414356</v>
+        <v>10.79672189556786</v>
       </c>
       <c r="I58" t="n">
-        <v>70.57694540816192</v>
+        <v>61.88130380530189</v>
       </c>
       <c r="J58" t="n">
-        <v>27.15839974878673</v>
+        <v>42.32817109432707</v>
       </c>
       <c r="K58" t="n">
-        <v>0.962125526098907</v>
+        <v>0.8617229418086314</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1796504481355255</v>
+        <v>5.75850460512098</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1779282288106128</v>
+        <v>5.696320452547448</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2576753970284938</v>
+        <v>5.867409499388407</v>
       </c>
       <c r="O58" t="n">
-        <v>0.003837018421295582</v>
+        <v>0.02115506835360864</v>
       </c>
       <c r="P58" t="n">
-        <v>83.42869877544405</v>
+        <v>52.71150729167852</v>
       </c>
       <c r="Q58" t="n">
-        <v>-16.57130122455595</v>
+        <v>-47.28849270832148</v>
       </c>
       <c r="R58" t="n">
-        <v>183.8013287784626</v>
+        <v>93.69255748532832</v>
       </c>
       <c r="S58" t="n">
-        <v>20.84238933346498</v>
+        <v>7.281908661960346</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="X58" t="n">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); RSI in forza (71) — momentum positivo; doji — indecisione del mercato</t>
+          <t>trend molto direzionale (ADX 42); RSI in forza (62) — momentum positivo; pattern: Bull Flag / Consolidation; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5939,52 +5939,52 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5899901989873113</v>
+        <v>0.7356672304123624</v>
       </c>
       <c r="F60" t="n">
-        <v>8.26278037247905</v>
+        <v>8.419569337536959</v>
       </c>
       <c r="G60" t="n">
-        <v>11.02178413820019</v>
+        <v>11.18256876403394</v>
       </c>
       <c r="H60" t="n">
-        <v>-6.852824582422123</v>
+        <v>-6.717926428305432</v>
       </c>
       <c r="I60" t="n">
-        <v>61.49931808804621</v>
+        <v>61.69101883332198</v>
       </c>
       <c r="J60" t="n">
         <v>16.98193479980409</v>
       </c>
       <c r="K60" t="n">
-        <v>1.008774239059671</v>
+        <v>1.016820934012039</v>
       </c>
       <c r="L60" t="n">
-        <v>1300.582437908639</v>
+        <v>1300.772914099115</v>
       </c>
       <c r="M60" t="n">
-        <v>1311.013185206602</v>
+        <v>1311.091616579151</v>
       </c>
       <c r="N60" t="n">
-        <v>1396.383445793871</v>
+        <v>1396.403346291383</v>
       </c>
       <c r="O60" t="n">
-        <v>14.53890080810787</v>
+        <v>14.66653613574316</v>
       </c>
       <c r="P60" t="n">
-        <v>81.49253731343283</v>
+        <v>82.68656716417911</v>
       </c>
       <c r="Q60" t="n">
-        <v>-18.50746268656716</v>
+        <v>-17.31343283582089</v>
       </c>
       <c r="R60" t="n">
-        <v>183.2329978431687</v>
+        <v>184.255811582171</v>
       </c>
       <c r="S60" t="n">
-        <v>9.057880972050981</v>
+        <v>9.215821422408776</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>57.2</v>
       </c>
       <c r="X60" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>RSI in forza (61) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>RSI in forza (62) — momentum positivo; pattern: Double Top; breakout massimi 20g — momentum di breve; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -6219,69 +6219,73 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1752.099975585938</v>
+        <v>1757.400024414062</v>
       </c>
       <c r="E63" t="n">
-        <v>1.336030976630287</v>
+        <v>1.642569370391112</v>
       </c>
       <c r="F63" t="n">
-        <v>6.168570789905781</v>
+        <v>6.489727468770856</v>
       </c>
       <c r="G63" t="n">
-        <v>8.234489914570386</v>
+        <v>8.561895935589581</v>
       </c>
       <c r="H63" t="n">
-        <v>-14.41480962409236</v>
+        <v>-14.15591704131894</v>
       </c>
       <c r="I63" t="n">
-        <v>60.68081257725825</v>
+        <v>61.16784277825715</v>
       </c>
       <c r="J63" t="n">
         <v>21.264352452531</v>
       </c>
       <c r="K63" t="n">
-        <v>1.006048250420325</v>
+        <v>1.023895526028824</v>
       </c>
       <c r="L63" t="n">
-        <v>1666.085240019149</v>
+        <v>1666.590006574208</v>
       </c>
       <c r="M63" t="n">
-        <v>1711.035859206149</v>
+        <v>1711.243704258232</v>
       </c>
       <c r="N63" t="n">
-        <v>1784.742202482478</v>
+        <v>1784.794939286738</v>
       </c>
       <c r="O63" t="n">
-        <v>21.6771573670929</v>
+        <v>22.01539410142361</v>
       </c>
       <c r="P63" t="n">
-        <v>78.60262939839645</v>
+        <v>81.17422059488109</v>
       </c>
       <c r="Q63" t="n">
-        <v>-21.39737060160356</v>
+        <v>-18.8257794051189</v>
       </c>
       <c r="R63" t="n">
-        <v>213.3281036581255</v>
+        <v>215.9229327997914</v>
       </c>
       <c r="S63" t="n">
-        <v>8.281317719659231</v>
+        <v>8.608865393356325</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Shooting Star</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr">
         <is>
           <t>Breakout 20d</t>
         </is>
       </c>
       <c r="W63" t="n">
-        <v>55.5</v>
+        <v>55.3</v>
       </c>
       <c r="X63" t="n">
-        <v>71</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6290,7 +6294,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); RSI in forza (61) — momentum positivo; breakout massimi 20g — momentum di breve</t>
+          <t>trend in sviluppo (ADX 21); RSI in forza (61) — momentum positivo; breakout massimi 20g — momentum di breve; shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
@@ -6939,83 +6943,83 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>64920.12890625</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="E71" t="n">
-        <v>1.023955782655528</v>
+        <v>3.842836134538574</v>
       </c>
       <c r="F71" t="n">
-        <v>2.265412095160824</v>
+        <v>10.78119788953336</v>
       </c>
       <c r="G71" t="n">
-        <v>1.597302940862555</v>
+        <v>5.667628901933508</v>
       </c>
       <c r="H71" t="n">
-        <v>6.658266834843007</v>
+        <v>-20.64182859498518</v>
       </c>
       <c r="I71" t="n">
-        <v>54.71469989583264</v>
+        <v>59.7187409059737</v>
       </c>
       <c r="J71" t="n">
-        <v>9.68448314630143</v>
+        <v>26.94047346472654</v>
       </c>
       <c r="K71" t="n">
-        <v>0.6349872818269188</v>
+        <v>1.143209223209154</v>
       </c>
       <c r="L71" t="n">
-        <v>64103.58223119122</v>
+        <v>59.90908485440914</v>
       </c>
       <c r="M71" t="n">
-        <v>64608.39969071216</v>
+        <v>63.01170142685386</v>
       </c>
       <c r="N71" t="n">
-        <v>72415.39319450894</v>
+        <v>65.15746944367264</v>
       </c>
       <c r="O71" t="n">
-        <v>38.12106387271879</v>
+        <v>0.9735760364921877</v>
       </c>
       <c r="P71" t="n">
-        <v>78.48895313762763</v>
+        <v>81.62926916357847</v>
       </c>
       <c r="Q71" t="n">
-        <v>-21.51104686237237</v>
+        <v>-18.37073083642152</v>
       </c>
       <c r="R71" t="n">
-        <v>31.17360486770403</v>
+        <v>160.4814944526017</v>
       </c>
       <c r="S71" t="n">
-        <v>0.190638614944727</v>
+        <v>6.672910858579573</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Breakout 20d, Outside Bar</t>
+        </is>
+      </c>
       <c r="W71" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="X71" t="n">
-        <v>64</v>
+        <v>69.3</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -7024,7 +7028,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 10); candela di inversione bullish (engulfing)</t>
+          <t>trend in sviluppo (ADX 27); breakout massimi 20g — momentum di breve; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7123,83 +7127,83 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>63.63000106811523</v>
+        <v>64981.390625</v>
       </c>
       <c r="E73" t="n">
-        <v>3.566141899239805</v>
+        <v>1.119286788160867</v>
       </c>
       <c r="F73" t="n">
-        <v>10.48601605536414</v>
+        <v>2.361914597838766</v>
       </c>
       <c r="G73" t="n">
-        <v>5.386072418470622</v>
+        <v>1.693174983992796</v>
       </c>
       <c r="H73" t="n">
-        <v>-20.85328226255614</v>
+        <v>6.758914644009151</v>
       </c>
       <c r="I73" t="n">
-        <v>59.35325384057069</v>
+        <v>55.00477426765675</v>
       </c>
       <c r="J73" t="n">
-        <v>26.94047346472654</v>
+        <v>9.68448314630143</v>
       </c>
       <c r="K73" t="n">
-        <v>1.130257219170099</v>
+        <v>0.6496756301239756</v>
       </c>
       <c r="L73" t="n">
-        <v>59.89289455260483</v>
+        <v>64109.41668059598</v>
       </c>
       <c r="M73" t="n">
-        <v>63.00503483199326</v>
+        <v>64610.80211105529</v>
       </c>
       <c r="N73" t="n">
-        <v>65.15577791960354</v>
+        <v>72416.00276384974</v>
       </c>
       <c r="O73" t="n">
-        <v>0.962727150496818</v>
+        <v>42.03064364479606</v>
       </c>
       <c r="P73" t="n">
-        <v>79.7703507434172</v>
+        <v>80.27409422558136</v>
       </c>
       <c r="Q73" t="n">
-        <v>-20.2296492565828</v>
+        <v>-19.72590577441863</v>
       </c>
       <c r="R73" t="n">
-        <v>158.9547725612874</v>
+        <v>32.6210484991408</v>
       </c>
       <c r="S73" t="n">
-        <v>6.38867575295452</v>
+        <v>0.2851832627699835</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Breakout 20d, Outside Bar</t>
-        </is>
-      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="n">
-        <v>53.7</v>
+        <v>53.4</v>
       </c>
       <c r="X73" t="n">
-        <v>69.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -7208,90 +7212,90 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); breakout massimi 20g — momentum di breve; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 10); candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1914.579956054688</v>
+        <v>543.27001953125</v>
       </c>
       <c r="E74" t="n">
-        <v>0.6583639542782738</v>
+        <v>2.018703448832349</v>
       </c>
       <c r="F74" t="n">
-        <v>1.702927448607872</v>
+        <v>7.601656552771607</v>
       </c>
       <c r="G74" t="n">
-        <v>3.997407398198116</v>
+        <v>-6.606496797202011</v>
       </c>
       <c r="H74" t="n">
-        <v>22.04356042110767</v>
+        <v>4.414766918545698</v>
       </c>
       <c r="I74" t="n">
-        <v>56.48125466791512</v>
+        <v>51.19438777497214</v>
       </c>
       <c r="J74" t="n">
-        <v>16.52740664239789</v>
+        <v>29.66772494535996</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6769008554654991</v>
+        <v>0.6408263750431481</v>
       </c>
       <c r="L74" t="n">
-        <v>1878.427704547179</v>
+        <v>533.4227167928658</v>
       </c>
       <c r="M74" t="n">
-        <v>1856.32037504732</v>
+        <v>537.0513529868008</v>
       </c>
       <c r="N74" t="n">
-        <v>2149.496240208364</v>
+        <v>434.1007636639795</v>
       </c>
       <c r="O74" t="n">
-        <v>-3.833689575641529</v>
+        <v>3.778539495702915</v>
       </c>
       <c r="P74" t="n">
-        <v>60.07084366502935</v>
+        <v>81.55512665422707</v>
       </c>
       <c r="Q74" t="n">
-        <v>-39.92915633497065</v>
+        <v>-18.44487334577294</v>
       </c>
       <c r="R74" t="n">
-        <v>30.97279744581115</v>
+        <v>21.90812322894541</v>
       </c>
       <c r="S74" t="n">
-        <v>2.857424102162276</v>
+        <v>-6.548664390123548</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="X74" t="n">
-        <v>62.1</v>
+        <v>55.9</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -7300,90 +7304,94 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>pattern: Double Top</t>
+          <t>trend in sviluppo (ADX 30); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>543.27001953125</v>
+        <v>1912.699951171875</v>
       </c>
       <c r="E75" t="n">
-        <v>2.018703448832349</v>
+        <v>0.5595233625696361</v>
       </c>
       <c r="F75" t="n">
-        <v>7.601656552771607</v>
+        <v>1.603061156999064</v>
       </c>
       <c r="G75" t="n">
-        <v>-6.606496797202011</v>
+        <v>3.895288062262225</v>
       </c>
       <c r="H75" t="n">
-        <v>4.414766918545698</v>
+        <v>21.92372082455183</v>
       </c>
       <c r="I75" t="n">
-        <v>51.19438777497214</v>
+        <v>56.27163963975374</v>
       </c>
       <c r="J75" t="n">
-        <v>29.66772494535996</v>
+        <v>16.52740664239789</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6408263750431481</v>
+        <v>0.6621522702665005</v>
       </c>
       <c r="L75" t="n">
-        <v>533.4227167928658</v>
+        <v>1878.248656463102</v>
       </c>
       <c r="M75" t="n">
-        <v>537.0513529868008</v>
+        <v>1856.246649365642</v>
       </c>
       <c r="N75" t="n">
-        <v>434.1007636639795</v>
+        <v>2149.477533692117</v>
       </c>
       <c r="O75" t="n">
-        <v>3.778539495702915</v>
+        <v>-3.953667095228319</v>
       </c>
       <c r="P75" t="n">
-        <v>81.55512665422707</v>
+        <v>58.85774239182832</v>
       </c>
       <c r="Q75" t="n">
-        <v>-18.44487334577294</v>
+        <v>-41.14225760817168</v>
       </c>
       <c r="R75" t="n">
-        <v>21.90812322894541</v>
+        <v>30.1424303224473</v>
       </c>
       <c r="S75" t="n">
-        <v>-6.548664390123548</v>
+        <v>2.75642416275832</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr"/>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W75" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="X75" t="n">
-        <v>55.9</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -7392,7 +7400,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 30); doji — indecisione del mercato</t>
+          <t>pattern: Double Top; shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
@@ -8147,83 +8155,83 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>157.8309936523438</v>
+        <v>313.6499938964844</v>
       </c>
       <c r="E84" t="n">
-        <v>0.1465656978949736</v>
+        <v>-2.487175548517073</v>
       </c>
       <c r="F84" t="n">
-        <v>-1.468323745090971</v>
+        <v>-5.555559129161947</v>
       </c>
       <c r="G84" t="n">
-        <v>-2.896540381120971</v>
+        <v>-12.1305552121491</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1014697680576271</v>
+        <v>8.267166268649472</v>
       </c>
       <c r="I84" t="n">
-        <v>27.78141185317025</v>
+        <v>47.3961617508234</v>
       </c>
       <c r="J84" t="n">
-        <v>41.8891037234813</v>
+        <v>11.40675439064747</v>
       </c>
       <c r="K84" t="n">
-        <v>0.1235717503473224</v>
+        <v>0.1558602951743189</v>
       </c>
       <c r="L84" t="n">
-        <v>160.5996441712822</v>
+        <v>322.0253708086825</v>
       </c>
       <c r="M84" t="n">
-        <v>160.8091371121495</v>
+        <v>311.6689571479606</v>
       </c>
       <c r="N84" t="n">
-        <v>157.7711802526508</v>
+        <v>317.3243769009007</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.7047221687179037</v>
+        <v>-2.737947062296656</v>
       </c>
       <c r="P84" t="n">
-        <v>29.51960130914459</v>
+        <v>18.01242236024845</v>
       </c>
       <c r="Q84" t="n">
-        <v>-70.48039869085541</v>
+        <v>-81.98757763975155</v>
       </c>
       <c r="R84" t="n">
-        <v>-140.4996342479482</v>
+        <v>-10.85111858030486</v>
       </c>
       <c r="S84" t="n">
-        <v>-2.791284193724763</v>
+        <v>-8.556853091403971</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom, Outside Bar</t>
-        </is>
-      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="X84" t="n">
-        <v>55.9</v>
+        <v>68.5</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -8232,90 +8240,90 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); RSI ipervenduto (28) — possibile rimbalzo; pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 11); shooting star — rifiuto di resistenza; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>MONC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Moncler</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>313.6499938964844</v>
+        <v>50.65999984741211</v>
       </c>
       <c r="E85" t="n">
-        <v>-2.487175548517073</v>
+        <v>-0.8222434780478682</v>
       </c>
       <c r="F85" t="n">
-        <v>-5.555559129161947</v>
+        <v>3.854040826489613</v>
       </c>
       <c r="G85" t="n">
-        <v>-12.1305552121491</v>
+        <v>1.117767246201185</v>
       </c>
       <c r="H85" t="n">
-        <v>8.267166268649472</v>
+        <v>0.1185797926885446</v>
       </c>
       <c r="I85" t="n">
-        <v>47.3961617508234</v>
+        <v>51.44938709376635</v>
       </c>
       <c r="J85" t="n">
-        <v>11.40675439064747</v>
+        <v>25.22521936625438</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1558602951743189</v>
+        <v>0.6084337810157767</v>
       </c>
       <c r="L85" t="n">
-        <v>322.0253708086825</v>
+        <v>50.16257018317914</v>
       </c>
       <c r="M85" t="n">
-        <v>311.6689571479606</v>
+        <v>51.07520757215306</v>
       </c>
       <c r="N85" t="n">
-        <v>317.3243769009007</v>
+        <v>52.4157766926041</v>
       </c>
       <c r="O85" t="n">
-        <v>-2.737947062296656</v>
+        <v>0.2783296050186269</v>
       </c>
       <c r="P85" t="n">
-        <v>18.01242236024845</v>
+        <v>66.01942286930827</v>
       </c>
       <c r="Q85" t="n">
-        <v>-81.98757763975155</v>
+        <v>-33.98057713069173</v>
       </c>
       <c r="R85" t="n">
-        <v>-10.85111858030486</v>
+        <v>67.06500247094428</v>
       </c>
       <c r="S85" t="n">
-        <v>-8.556853091403971</v>
+        <v>2.137099608670501</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
+          <t>Bearish Engulfing, Dark Cloud Cover</t>
         </is>
       </c>
       <c r="V85" t="inlineStr"/>
       <c r="W85" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="X85" t="n">
-        <v>68.5</v>
+        <v>62.9</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -8324,73 +8332,73 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 11); shooting star — rifiuto di resistenza; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 25); candela di inversione bearish (engulfing); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MONC</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Moncler</t>
+          <t>US Treasury 1-3Y ETF</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>50.65999984741211</v>
+        <v>81.91999816894531</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.8222434780478682</v>
+        <v>0.1466932918224639</v>
       </c>
       <c r="F86" t="n">
-        <v>3.854040826489613</v>
+        <v>-0.09756320860327961</v>
       </c>
       <c r="G86" t="n">
-        <v>1.117767246201185</v>
+        <v>0.01220181466132786</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1185797926885446</v>
+        <v>-0.4617313107188048</v>
       </c>
       <c r="I86" t="n">
-        <v>51.44938709376635</v>
+        <v>49.81337936284692</v>
       </c>
       <c r="J86" t="n">
-        <v>25.22521936625438</v>
+        <v>12.13731610947306</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6084337810157767</v>
+        <v>0.5484114083772653</v>
       </c>
       <c r="L86" t="n">
-        <v>50.16257018317914</v>
+        <v>81.9079832561074</v>
       </c>
       <c r="M86" t="n">
-        <v>51.07520757215306</v>
+        <v>81.99257057874478</v>
       </c>
       <c r="N86" t="n">
-        <v>52.4157766926041</v>
+        <v>82.34384417397428</v>
       </c>
       <c r="O86" t="n">
-        <v>0.2783296050186269</v>
+        <v>0.002240493646348915</v>
       </c>
       <c r="P86" t="n">
-        <v>66.01942286930827</v>
+        <v>58.61987319460156</v>
       </c>
       <c r="Q86" t="n">
-        <v>-33.98057713069173</v>
+        <v>-41.38012680539844</v>
       </c>
       <c r="R86" t="n">
-        <v>67.06500247094428</v>
+        <v>11.40666235928018</v>
       </c>
       <c r="S86" t="n">
-        <v>2.137099608670501</v>
+        <v>0.04885309827691309</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8399,15 +8407,19 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>Bearish Engulfing, Dark Cloud Cover</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom, Volatility Squeeze</t>
+        </is>
+      </c>
       <c r="W86" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="X86" t="n">
-        <v>62.9</v>
+        <v>56.2</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -8416,19 +8428,19 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); candela di inversione bearish (engulfing); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (81.75); vicino alla resistenza dei 20g (82.09); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>US Treasury 1-3Y ETF</t>
+          <t>High Yield Corp ETF</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -8437,52 +8449,52 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>81.91999816894531</v>
+        <v>79.61000061035156</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1466932918224639</v>
+        <v>0.1887761485114492</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.09756320860327961</v>
+        <v>0.1635596979458809</v>
       </c>
       <c r="G87" t="n">
-        <v>0.01220181466132786</v>
+        <v>-0.1755478240105801</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.4617313107188048</v>
+        <v>-0.6613411321854001</v>
       </c>
       <c r="I87" t="n">
-        <v>49.81337936284692</v>
+        <v>51.5798954183096</v>
       </c>
       <c r="J87" t="n">
-        <v>12.13731610947306</v>
+        <v>38.53560584075167</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5484114083772653</v>
+        <v>0.6449770364513217</v>
       </c>
       <c r="L87" t="n">
-        <v>81.9079832561074</v>
+        <v>79.52212280473012</v>
       </c>
       <c r="M87" t="n">
-        <v>81.99257057874478</v>
+        <v>79.66518136800799</v>
       </c>
       <c r="N87" t="n">
-        <v>82.34384417397428</v>
+        <v>79.97391678372844</v>
       </c>
       <c r="O87" t="n">
-        <v>0.002240493646348915</v>
+        <v>0.02791686755130132</v>
       </c>
       <c r="P87" t="n">
-        <v>58.61987319460156</v>
+        <v>78.33373599684651</v>
       </c>
       <c r="Q87" t="n">
-        <v>-41.38012680539844</v>
+        <v>-21.66626400315349</v>
       </c>
       <c r="R87" t="n">
-        <v>11.40666235928018</v>
+        <v>42.60148880317562</v>
       </c>
       <c r="S87" t="n">
-        <v>0.04885309827691309</v>
+        <v>-0.1254528607071204</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8492,14 +8504,14 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Volatility Squeeze</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W87" t="n">
-        <v>46.7</v>
+        <v>46.6</v>
       </c>
       <c r="X87" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -8508,90 +8520,94 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Bottom; sul supporto dei 20g (81.75); vicino alla resistenza dei 20g (82.09); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 39); pattern: Double Bottom; sul supporto dei 20g (79.14); vicino alla resistenza dei 20g (79.84); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HY</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>High Yield Corp ETF</t>
+          <t>Tenaris</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>79.61000061035156</v>
+        <v>23.13999938964844</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1887761485114492</v>
+        <v>0.7400961313704046</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1635596979458809</v>
+        <v>-4.969203173984738</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.1755478240105801</v>
+        <v>-3.783783269355867</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.6613411321854001</v>
+        <v>-12.54724039946197</v>
       </c>
       <c r="I88" t="n">
-        <v>51.5798954183096</v>
+        <v>35.7566061863219</v>
       </c>
       <c r="J88" t="n">
-        <v>38.53560584075167</v>
+        <v>22.1680380547603</v>
       </c>
       <c r="K88" t="n">
-        <v>0.6449770364513217</v>
+        <v>-0.05540585074915596</v>
       </c>
       <c r="L88" t="n">
-        <v>79.52212280473012</v>
+        <v>24.47005314980666</v>
       </c>
       <c r="M88" t="n">
-        <v>79.66518136800799</v>
+        <v>24.83695639498334</v>
       </c>
       <c r="N88" t="n">
-        <v>79.97391678372844</v>
+        <v>22.63734131382599</v>
       </c>
       <c r="O88" t="n">
-        <v>0.02791686755130132</v>
+        <v>-0.1368626431608738</v>
       </c>
       <c r="P88" t="n">
-        <v>78.33373599684651</v>
+        <v>6.825898797263834</v>
       </c>
       <c r="Q88" t="n">
-        <v>-21.66626400315349</v>
+        <v>-93.17410120273617</v>
       </c>
       <c r="R88" t="n">
-        <v>42.60148880317562</v>
+        <v>-206.2245526915879</v>
       </c>
       <c r="S88" t="n">
-        <v>-0.1254528607071204</v>
+        <v>-3.382051555273524</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Doji, Bullish Harami</t>
+        </is>
+      </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W88" t="n">
-        <v>46.6</v>
+        <v>46</v>
       </c>
       <c r="X88" t="n">
-        <v>56.4</v>
+        <v>63.2</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -8600,94 +8616,90 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 39); pattern: Double Bottom; sul supporto dei 20g (79.14); vicino alla resistenza dei 20g (79.84); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 22); RSI scarico (36) — zona di interesse long; doji — indecisione del mercato; sul supporto dei 20g (22.94)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tenaris</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>23.13999938964844</v>
+        <v>99.60399627685547</v>
       </c>
       <c r="E89" t="n">
-        <v>0.7400961313704046</v>
+        <v>-0.3661147738106219</v>
       </c>
       <c r="F89" t="n">
-        <v>-4.969203173984738</v>
+        <v>-0.1963995680447916</v>
       </c>
       <c r="G89" t="n">
-        <v>-3.783783269355867</v>
+        <v>-1.323564624764406</v>
       </c>
       <c r="H89" t="n">
-        <v>-12.54724039946197</v>
+        <v>1.802943586458094</v>
       </c>
       <c r="I89" t="n">
-        <v>35.7566061863219</v>
+        <v>36.20803542979736</v>
       </c>
       <c r="J89" t="n">
-        <v>22.1680380547603</v>
+        <v>28.48185096835964</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.05540585074915596</v>
+        <v>0.1061714486913847</v>
       </c>
       <c r="L89" t="n">
-        <v>24.47005314980666</v>
+        <v>100.4255084037462</v>
       </c>
       <c r="M89" t="n">
-        <v>24.83695639498334</v>
+        <v>100.3223423880777</v>
       </c>
       <c r="N89" t="n">
-        <v>22.63734131382599</v>
+        <v>99.61799677070802</v>
       </c>
       <c r="O89" t="n">
-        <v>-0.1368626431608738</v>
+        <v>-0.1823021419457249</v>
       </c>
       <c r="P89" t="n">
-        <v>6.825898797263834</v>
+        <v>8.985089083517503</v>
       </c>
       <c r="Q89" t="n">
-        <v>-93.17410120273617</v>
+        <v>-91.01491091648249</v>
       </c>
       <c r="R89" t="n">
-        <v>-206.2245526915879</v>
+        <v>-139.7693481287997</v>
       </c>
       <c r="S89" t="n">
-        <v>-3.382051555273524</v>
+        <v>-1.352881972202613</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Doji, Bullish Harami</t>
-        </is>
-      </c>
+      <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W89" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="X89" t="n">
-        <v>63.2</v>
+        <v>56.8</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -8696,90 +8708,94 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); RSI scarico (36) — zona di interesse long; doji — indecisione del mercato; sul supporto dei 20g (22.94)</t>
+          <t>trend in sviluppo (ADX 28); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; sul supporto dei 20g (99.40); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>INW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>INWIT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>99.61699676513672</v>
+        <v>6.440000057220459</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.3531103843712913</v>
+        <v>-0.1550349200059475</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.1833730270791478</v>
+        <v>0.6249993946403354</v>
       </c>
       <c r="G90" t="n">
-        <v>-1.310685203358808</v>
+        <v>-2.127657570043606</v>
       </c>
       <c r="H90" t="n">
-        <v>1.81623108519875</v>
+        <v>-10.36882242856186</v>
       </c>
       <c r="I90" t="n">
-        <v>36.34760022443221</v>
+        <v>50.76959748513046</v>
       </c>
       <c r="J90" t="n">
-        <v>28.48185096835964</v>
+        <v>19.66128725793924</v>
       </c>
       <c r="K90" t="n">
-        <v>0.110187314096681</v>
+        <v>0.6221613396839354</v>
       </c>
       <c r="L90" t="n">
-        <v>100.4267465454873</v>
+        <v>6.409578262485483</v>
       </c>
       <c r="M90" t="n">
-        <v>100.3228522111475</v>
+        <v>6.522794381366272</v>
       </c>
       <c r="N90" t="n">
-        <v>99.61812612880037</v>
+        <v>7.496868843404613</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.1814724811551245</v>
+        <v>0.0168160825896702</v>
       </c>
       <c r="P90" t="n">
-        <v>9.566246487135412</v>
+        <v>71.65355927163284</v>
       </c>
       <c r="Q90" t="n">
-        <v>-90.43375351286458</v>
+        <v>-28.34644072836717</v>
       </c>
       <c r="R90" t="n">
-        <v>-139.2471957023238</v>
+        <v>49.4343131679629</v>
       </c>
       <c r="S90" t="n">
-        <v>-1.340006377348624</v>
+        <v>-0.8468026067392054</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr"/>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W90" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="X90" t="n">
-        <v>56.7</v>
+        <v>60.3</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -8788,19 +8804,19 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; sul supporto dei 20g (99.40); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>pattern: Double Bottom; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>INW</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>INWIT</t>
+          <t>Prysmian</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8809,56 +8825,56 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>6.440000057220459</v>
+        <v>126</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.1550349200059475</v>
+        <v>1.204819277108427</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6249993946403354</v>
+        <v>5.131415606322975</v>
       </c>
       <c r="G91" t="n">
-        <v>-2.127657570043606</v>
+        <v>-5.476371256288237</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.36882242856186</v>
+        <v>-15.32258238182104</v>
       </c>
       <c r="I91" t="n">
-        <v>50.76959748513046</v>
+        <v>46.3377066291201</v>
       </c>
       <c r="J91" t="n">
-        <v>19.66128725793924</v>
+        <v>51.0283533172039</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6221613396839354</v>
+        <v>0.4938531897458566</v>
       </c>
       <c r="L91" t="n">
-        <v>6.409578262485483</v>
+        <v>126.6292701830862</v>
       </c>
       <c r="M91" t="n">
-        <v>6.522794381366272</v>
+        <v>131.9276506179893</v>
       </c>
       <c r="N91" t="n">
-        <v>7.496868843404613</v>
+        <v>115.0568492044149</v>
       </c>
       <c r="O91" t="n">
-        <v>0.0168160825896702</v>
+        <v>0.701328579980931</v>
       </c>
       <c r="P91" t="n">
-        <v>71.65355927163284</v>
+        <v>76.96079238017734</v>
       </c>
       <c r="Q91" t="n">
-        <v>-28.34644072836717</v>
+        <v>-23.03920761982267</v>
       </c>
       <c r="R91" t="n">
-        <v>49.4343131679629</v>
+        <v>2.07286691443711</v>
       </c>
       <c r="S91" t="n">
-        <v>-0.8468026067392054</v>
+        <v>-7.726109715104834</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -8866,16 +8882,12 @@
           <t>Doji</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="n">
-        <v>45.8</v>
+        <v>45.6</v>
       </c>
       <c r="X91" t="n">
-        <v>60.3</v>
+        <v>55.6</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -8884,90 +8896,90 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 51); doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prysmian</t>
+          <t>UnitedHealth</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>126</v>
+        <v>407.0799865722656</v>
       </c>
       <c r="E92" t="n">
-        <v>1.204819277108427</v>
+        <v>0.7698555195100765</v>
       </c>
       <c r="F92" t="n">
-        <v>5.131415606322975</v>
+        <v>-1.766411059853268</v>
       </c>
       <c r="G92" t="n">
-        <v>-5.476371256288237</v>
+        <v>-5.698667188866402</v>
       </c>
       <c r="H92" t="n">
-        <v>-15.32258238182104</v>
+        <v>7.131947682088091</v>
       </c>
       <c r="I92" t="n">
-        <v>46.3377066291201</v>
+        <v>44.00212737632333</v>
       </c>
       <c r="J92" t="n">
-        <v>51.0283533172039</v>
+        <v>27.17304770182536</v>
       </c>
       <c r="K92" t="n">
-        <v>0.4938531897458566</v>
+        <v>0.1073114720687491</v>
       </c>
       <c r="L92" t="n">
-        <v>126.6292701830862</v>
+        <v>416.4609876325408</v>
       </c>
       <c r="M92" t="n">
-        <v>131.9276506179893</v>
+        <v>407.4588950984793</v>
       </c>
       <c r="N92" t="n">
-        <v>115.0568492044149</v>
+        <v>368.5194789117269</v>
       </c>
       <c r="O92" t="n">
-        <v>0.701328579980931</v>
+        <v>-2.995956194236824</v>
       </c>
       <c r="P92" t="n">
-        <v>76.96079238017734</v>
+        <v>23.67345890171007</v>
       </c>
       <c r="Q92" t="n">
-        <v>-23.03920761982267</v>
+        <v>-76.32654109828992</v>
       </c>
       <c r="R92" t="n">
-        <v>2.07286691443711</v>
+        <v>-126.7928980056553</v>
       </c>
       <c r="S92" t="n">
-        <v>-7.726109715104834</v>
+        <v>-4.130754261838554</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W92" t="n">
-        <v>45.6</v>
+        <v>44.8</v>
       </c>
       <c r="X92" t="n">
-        <v>55.6</v>
+        <v>57</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -8976,90 +8988,94 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 51); doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 27); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UnitedHealth</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>407.0799865722656</v>
+        <v>8.194999694824219</v>
       </c>
       <c r="E93" t="n">
-        <v>0.7698555195100765</v>
+        <v>0.1952933019959247</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.766411059853268</v>
+        <v>-2.085804761618815</v>
       </c>
       <c r="G93" t="n">
-        <v>-5.698667188866402</v>
+        <v>-0.7517869536187272</v>
       </c>
       <c r="H93" t="n">
-        <v>7.131947682088091</v>
+        <v>10.77341697359606</v>
       </c>
       <c r="I93" t="n">
-        <v>44.00212737632333</v>
+        <v>48.82868449687415</v>
       </c>
       <c r="J93" t="n">
-        <v>27.17304770182536</v>
+        <v>13.01549381712716</v>
       </c>
       <c r="K93" t="n">
-        <v>0.1073114720687491</v>
+        <v>0.2924135823796408</v>
       </c>
       <c r="L93" t="n">
-        <v>416.4609876325408</v>
+        <v>8.249769438232244</v>
       </c>
       <c r="M93" t="n">
-        <v>407.4588950984793</v>
+        <v>8.245043019184431</v>
       </c>
       <c r="N93" t="n">
-        <v>368.5194789117269</v>
+        <v>9.604588728871036</v>
       </c>
       <c r="O93" t="n">
-        <v>-2.995956194236824</v>
+        <v>-0.04259006027427684</v>
       </c>
       <c r="P93" t="n">
-        <v>23.67345890171007</v>
+        <v>30.55939913955314</v>
       </c>
       <c r="Q93" t="n">
-        <v>-76.32654109828992</v>
+        <v>-69.44060086044686</v>
       </c>
       <c r="R93" t="n">
-        <v>-126.7928980056553</v>
+        <v>-42.82002504033733</v>
       </c>
       <c r="S93" t="n">
-        <v>-4.130754261838554</v>
+        <v>-1.795851784772062</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr"/>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W93" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="X93" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -9068,94 +9084,90 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 27); pattern: Double Bottom</t>
+          <t>mercato laterale — ATR basso (ADX 13); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>8.192999839782715</v>
+        <v>43.61000061035156</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1708422867540804</v>
+        <v>0.530197179744607</v>
       </c>
       <c r="F94" t="n">
-        <v>-2.109699112353924</v>
+        <v>-1.668540900179127</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.7760068494835681</v>
+        <v>-3.368048796341749</v>
       </c>
       <c r="H94" t="n">
-        <v>10.74638454105807</v>
+        <v>-2.482112209419363</v>
       </c>
       <c r="I94" t="n">
-        <v>48.77513491808957</v>
+        <v>35.92989132397517</v>
       </c>
       <c r="J94" t="n">
-        <v>13.01549381712716</v>
+        <v>21.59017862015685</v>
       </c>
       <c r="K94" t="n">
-        <v>0.2901186835521422</v>
+        <v>0.09949527227774116</v>
       </c>
       <c r="L94" t="n">
-        <v>8.249578975847339</v>
+        <v>44.67979885913768</v>
       </c>
       <c r="M94" t="n">
-        <v>8.24496459349653</v>
+        <v>44.96331546287011</v>
       </c>
       <c r="N94" t="n">
-        <v>9.604568829815896</v>
+        <v>44.48402667511554</v>
       </c>
       <c r="O94" t="n">
-        <v>-0.04271768635099956</v>
+        <v>-0.2353802504689988</v>
       </c>
       <c r="P94" t="n">
-        <v>30.35221610267663</v>
+        <v>18.0461510909409</v>
       </c>
       <c r="Q94" t="n">
-        <v>-69.64778389732336</v>
+        <v>-81.9538489090591</v>
       </c>
       <c r="R94" t="n">
-        <v>-42.9847187203161</v>
+        <v>-160.603434292863</v>
       </c>
       <c r="S94" t="n">
-        <v>-1.819816893767601</v>
+        <v>-3.963882940121011</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W94" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="X94" t="n">
-        <v>57.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -9164,73 +9176,73 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 13); doji — indecisione del mercato</t>
+          <t>trend in sviluppo (ADX 22); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>43.61000061035156</v>
+        <v>842.1900024414062</v>
       </c>
       <c r="E95" t="n">
-        <v>0.530197179744607</v>
+        <v>-1.723536588935681</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.668540900179127</v>
+        <v>3.360293192873298</v>
       </c>
       <c r="G95" t="n">
-        <v>-3.368048796341749</v>
+        <v>-10.25160228746381</v>
       </c>
       <c r="H95" t="n">
-        <v>-2.482112209419363</v>
+        <v>-6.15744710167514</v>
       </c>
       <c r="I95" t="n">
-        <v>35.92989132397517</v>
+        <v>42.89081504611152</v>
       </c>
       <c r="J95" t="n">
-        <v>21.59017862015685</v>
+        <v>39.06587009250406</v>
       </c>
       <c r="K95" t="n">
-        <v>0.09949527227774116</v>
+        <v>0.3356663273823108</v>
       </c>
       <c r="L95" t="n">
-        <v>44.67979885913768</v>
+        <v>870.507933179635</v>
       </c>
       <c r="M95" t="n">
-        <v>44.96331546287011</v>
+        <v>887.8429920437313</v>
       </c>
       <c r="N95" t="n">
-        <v>44.48402667511554</v>
+        <v>759.8566765641658</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.2353802504689988</v>
+        <v>1.271116060308092</v>
       </c>
       <c r="P95" t="n">
-        <v>18.0461510909409</v>
+        <v>41.62893235308569</v>
       </c>
       <c r="Q95" t="n">
-        <v>-81.9538489090591</v>
+        <v>-58.37106764691431</v>
       </c>
       <c r="R95" t="n">
-        <v>-160.603434292863</v>
+        <v>-26.17139191093932</v>
       </c>
       <c r="S95" t="n">
-        <v>-3.963882940121011</v>
+        <v>-11.57274428145859</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9238,16 +9250,12 @@
         </is>
       </c>
       <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="n">
-        <v>43.8</v>
+        <v>43.4</v>
       </c>
       <c r="X95" t="n">
-        <v>65.40000000000001</v>
+        <v>57.6</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -9256,73 +9264,73 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 39); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>842.1900024414062</v>
+        <v>157.7449951171875</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.723536588935681</v>
+        <v>0.09199810155886556</v>
       </c>
       <c r="F96" t="n">
-        <v>3.360293192873298</v>
+        <v>-1.522011424730607</v>
       </c>
       <c r="G96" t="n">
-        <v>-10.25160228746381</v>
+        <v>-2.949449857850373</v>
       </c>
       <c r="H96" t="n">
-        <v>-6.15744710167514</v>
+        <v>0.04692674347270831</v>
       </c>
       <c r="I96" t="n">
-        <v>42.89081504611152</v>
+        <v>26.92188019393616</v>
       </c>
       <c r="J96" t="n">
-        <v>39.06587009250406</v>
+        <v>41.8891037234813</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3356663273823108</v>
+        <v>0.1161732961604473</v>
       </c>
       <c r="L96" t="n">
-        <v>870.507933179635</v>
+        <v>160.5914538346006</v>
       </c>
       <c r="M96" t="n">
-        <v>887.8429920437313</v>
+        <v>160.8057646205748</v>
       </c>
       <c r="N96" t="n">
-        <v>759.8566765641658</v>
+        <v>157.7703245458333</v>
       </c>
       <c r="O96" t="n">
-        <v>1.271116060308092</v>
+        <v>-0.7102103943233309</v>
       </c>
       <c r="P96" t="n">
-        <v>41.62893235308569</v>
+        <v>28.53371956947265</v>
       </c>
       <c r="Q96" t="n">
-        <v>-58.37106764691431</v>
+        <v>-71.46628043052735</v>
       </c>
       <c r="R96" t="n">
-        <v>-26.17139191093932</v>
+        <v>-141.4388966422116</v>
       </c>
       <c r="S96" t="n">
-        <v>-11.57274428145859</v>
+        <v>-2.844251022167688</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9330,12 +9338,16 @@
         </is>
       </c>
       <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom, Outside Bar</t>
+        </is>
+      </c>
       <c r="W96" t="n">
-        <v>43.4</v>
+        <v>42.8</v>
       </c>
       <c r="X96" t="n">
-        <v>57.6</v>
+        <v>59.9</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9344,7 +9356,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 39); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 42); RSI ipervenduto (27) — possibile rimbalzo; pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -9545,52 +9557,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>77.05999755859375</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.2975848805914394</v>
+        <v>-0.2717027842995767</v>
       </c>
       <c r="F99" t="n">
-        <v>-8.987836039829645</v>
+        <v>-8.964209876024809</v>
       </c>
       <c r="G99" t="n">
-        <v>6.908983908201716</v>
+        <v>6.936736782719977</v>
       </c>
       <c r="H99" t="n">
-        <v>-19.24125022287715</v>
+        <v>-19.22028577847891</v>
       </c>
       <c r="I99" t="n">
-        <v>44.95003937498979</v>
+        <v>44.97652786293362</v>
       </c>
       <c r="J99" t="n">
         <v>41.05310618751616</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2386200440622014</v>
+        <v>0.2396126381726189</v>
       </c>
       <c r="L99" t="n">
-        <v>79.99126966786689</v>
+        <v>79.99317483667269</v>
       </c>
       <c r="M99" t="n">
-        <v>81.7986848724115</v>
+        <v>81.79946935368447</v>
       </c>
       <c r="N99" t="n">
-        <v>79.03641968487341</v>
+        <v>79.03661873236058</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.7918129453967978</v>
+        <v>-0.7905363194619823</v>
       </c>
       <c r="P99" t="n">
-        <v>14.6417413397865</v>
+        <v>14.74560567126186</v>
       </c>
       <c r="Q99" t="n">
-        <v>-85.35825866021351</v>
+        <v>-85.25439432873813</v>
       </c>
       <c r="R99" t="n">
-        <v>-43.54266547178163</v>
+        <v>-43.47944707522358</v>
       </c>
       <c r="S99" t="n">
-        <v>7.912048181958431</v>
+        <v>7.940061445416013</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9813,52 +9825,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>82.16000366210938</v>
+        <v>82.26999664306641</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.4000414719432244</v>
+        <v>-0.2667004805436579</v>
       </c>
       <c r="F102" t="n">
-        <v>-8.832666269281219</v>
+        <v>-8.710614585298993</v>
       </c>
       <c r="G102" t="n">
-        <v>7.680210191310799</v>
+        <v>7.824368745121646</v>
       </c>
       <c r="H102" t="n">
-        <v>-18.88636299783607</v>
+        <v>-18.7777708564965</v>
       </c>
       <c r="I102" t="n">
-        <v>45.95960380897286</v>
+        <v>46.08369943628299</v>
       </c>
       <c r="J102" t="n">
         <v>42.49076993119873</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2682406493920543</v>
+        <v>0.2727060705577267</v>
       </c>
       <c r="L102" t="n">
-        <v>85.04744894752623</v>
+        <v>85.05792446952213</v>
       </c>
       <c r="M102" t="n">
-        <v>86.65001470963861</v>
+        <v>86.65432815987222</v>
       </c>
       <c r="N102" t="n">
-        <v>83.75807490948796</v>
+        <v>83.75916936700993</v>
       </c>
       <c r="O102" t="n">
-        <v>-1.002458558509675</v>
+        <v>-0.9954390634286527</v>
       </c>
       <c r="P102" t="n">
-        <v>16.87607028753994</v>
+        <v>17.33667731629393</v>
       </c>
       <c r="Q102" t="n">
-        <v>-83.12392971246007</v>
+        <v>-82.66332268370607</v>
       </c>
       <c r="R102" t="n">
-        <v>-38.23294372199948</v>
+        <v>-37.94903023408202</v>
       </c>
       <c r="S102" t="n">
-        <v>8.091042432621487</v>
+        <v>8.235750994476131</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -9868,7 +9880,7 @@
       <c r="U102" t="inlineStr"/>
       <c r="V102" t="inlineStr"/>
       <c r="W102" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="X102" t="n">
         <v>70.90000000000001</v>
@@ -10071,83 +10083,83 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US Treasury 7-10Y ETF</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>93.16999816894531</v>
+        <v>6.466000080108643</v>
       </c>
       <c r="E105" t="n">
-        <v>0.2366877115936195</v>
+        <v>0.5564865390368157</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2366877115936195</v>
+        <v>-1.153427541967855</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.576246847511519</v>
+        <v>-1.729906884559507</v>
       </c>
       <c r="H105" t="n">
-        <v>-1.885005194592548</v>
+        <v>-3.072114578062446</v>
       </c>
       <c r="I105" t="n">
-        <v>45.75329955462659</v>
+        <v>47.80431924256052</v>
       </c>
       <c r="J105" t="n">
-        <v>17.44988265311932</v>
+        <v>15.65240816369779</v>
       </c>
       <c r="K105" t="n">
-        <v>0.4051900666300934</v>
+        <v>0.4463250615404396</v>
       </c>
       <c r="L105" t="n">
-        <v>93.32063755241718</v>
+        <v>6.5187346975102</v>
       </c>
       <c r="M105" t="n">
-        <v>93.75392936413807</v>
+        <v>6.741343657625428</v>
       </c>
       <c r="N105" t="n">
-        <v>94.87580117119576</v>
+        <v>9.282370179131425</v>
       </c>
       <c r="O105" t="n">
-        <v>0.01989233283350528</v>
+        <v>0.01495533483774626</v>
       </c>
       <c r="P105" t="n">
-        <v>49.48403334906402</v>
+        <v>45.4240884590573</v>
       </c>
       <c r="Q105" t="n">
-        <v>-50.51596665093598</v>
+        <v>-54.57591154094271</v>
       </c>
       <c r="R105" t="n">
-        <v>-16.04408270727113</v>
+        <v>-34.25358220015482</v>
       </c>
       <c r="S105" t="n">
-        <v>-0.4912945615363262</v>
+        <v>-1.607619587740095</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr"/>
       <c r="W105" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="X105" t="n">
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -10156,90 +10168,90 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; pattern: Double Bottom; sul supporto dei 20g (92.69); vicino alla resistenza dei 20g (94.10); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; segnale candlestick: Bullish Harami</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>US Treasury 7-10Y ETF</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>6.440999984741211</v>
+        <v>93.16999816894531</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1676956757296288</v>
+        <v>0.2366877115936195</v>
       </c>
       <c r="F106" t="n">
-        <v>-1.535607205991774</v>
+        <v>0.2366877115936195</v>
       </c>
       <c r="G106" t="n">
-        <v>-2.109857653074054</v>
+        <v>-0.576246847511519</v>
       </c>
       <c r="H106" t="n">
-        <v>-3.446875844578112</v>
+        <v>-1.885005194592548</v>
       </c>
       <c r="I106" t="n">
-        <v>47.11504472412232</v>
+        <v>45.75329955462659</v>
       </c>
       <c r="J106" t="n">
-        <v>15.65240816369779</v>
+        <v>17.44988265311932</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4083034786782729</v>
+        <v>0.4051900666300934</v>
       </c>
       <c r="L106" t="n">
-        <v>6.516353736046636</v>
+        <v>93.32063755241718</v>
       </c>
       <c r="M106" t="n">
-        <v>6.740363261728666</v>
+        <v>93.75392936413807</v>
       </c>
       <c r="N106" t="n">
-        <v>9.282121421963589</v>
+        <v>94.87580117119576</v>
       </c>
       <c r="O106" t="n">
-        <v>0.01335988715617763</v>
+        <v>0.01989233283350528</v>
       </c>
       <c r="P106" t="n">
-        <v>42.62887394904221</v>
+        <v>49.48403334906402</v>
       </c>
       <c r="Q106" t="n">
-        <v>-57.37112605095779</v>
+        <v>-50.51596665093598</v>
       </c>
       <c r="R106" t="n">
-        <v>-38.67648708531794</v>
+        <v>-16.04408270727113</v>
       </c>
       <c r="S106" t="n">
-        <v>-1.988043166963716</v>
+        <v>-0.4912945615363262</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>Doji, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W106" t="n">
         <v>35.8</v>
       </c>
       <c r="X106" t="n">
-        <v>71</v>
+        <v>71.3</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -10248,7 +10260,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; pattern: Double Bottom; sul supporto dei 20g (92.69); vicino alla resistenza dei 20g (94.10); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -10439,66 +10451,66 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>TIPS</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>US TIPS ETF</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>73.86000061035156</v>
+        <v>107.0800018310547</v>
       </c>
       <c r="E109" t="n">
-        <v>1.768447609786872</v>
+        <v>0.1964995593483954</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5598164511704695</v>
+        <v>-0.5110057013829494</v>
       </c>
       <c r="G109" t="n">
-        <v>-1.535224045761152</v>
+        <v>-0.9618950139734683</v>
       </c>
       <c r="H109" t="n">
-        <v>18.76544990996574</v>
+        <v>-3.8779170876588</v>
       </c>
       <c r="I109" t="n">
-        <v>47.46337040287582</v>
+        <v>35.75697863852582</v>
       </c>
       <c r="J109" t="n">
-        <v>22.7203339220038</v>
+        <v>31.01844240524748</v>
       </c>
       <c r="K109" t="n">
-        <v>0.3954551128362652</v>
+        <v>0.1985537314955397</v>
       </c>
       <c r="L109" t="n">
-        <v>74.28764670175201</v>
+        <v>107.5994139772882</v>
       </c>
       <c r="M109" t="n">
-        <v>75.32309434222647</v>
+        <v>108.4727915829042</v>
       </c>
       <c r="N109" t="n">
-        <v>90.63738813594624</v>
+        <v>109.7824158623418</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.07189332093656442</v>
+        <v>-0.008802084494784534</v>
       </c>
       <c r="P109" t="n">
-        <v>47.41562633909442</v>
+        <v>25.5999755859375</v>
       </c>
       <c r="Q109" t="n">
-        <v>-52.58437366090558</v>
+        <v>-74.4000244140625</v>
       </c>
       <c r="R109" t="n">
-        <v>-44.486750791088</v>
+        <v>-57.27168428346319</v>
       </c>
       <c r="S109" t="n">
-        <v>-2.121504280942754</v>
+        <v>-0.9710491529029364</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10507,19 +10519,19 @@
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Inside Bar, Bear Flag / Consolidation</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W109" t="n">
-        <v>34.8</v>
+        <v>34.6</v>
       </c>
       <c r="X109" t="n">
-        <v>69.2</v>
+        <v>77</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -10528,73 +10540,73 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 23); pattern: Bear Flag / Consolidation; segnale candlestick: Bullish Harami</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 31); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (106.76); vicino alla resistenza dei 20g (108.37)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TIPS</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>US TIPS ETF</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>107.0800018310547</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1964995593483954</v>
+        <v>1.534214606712037</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.5110057013829494</v>
+        <v>0.3283652661595138</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.9618950139734683</v>
+        <v>-1.761853229074284</v>
       </c>
       <c r="H110" t="n">
-        <v>-3.8779170876588</v>
+        <v>18.49209614809439</v>
       </c>
       <c r="I110" t="n">
-        <v>35.75697863852582</v>
+        <v>46.8650511984028</v>
       </c>
       <c r="J110" t="n">
-        <v>31.01844240524748</v>
+        <v>22.7203339220038</v>
       </c>
       <c r="K110" t="n">
-        <v>0.1985537314955397</v>
+        <v>0.3737165494584157</v>
       </c>
       <c r="L110" t="n">
-        <v>107.5994139772882</v>
+        <v>74.2714563999477</v>
       </c>
       <c r="M110" t="n">
-        <v>108.4727915829042</v>
+        <v>75.31642774736588</v>
       </c>
       <c r="N110" t="n">
-        <v>109.7824158623418</v>
+        <v>90.63569661187712</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.008802084494784534</v>
+        <v>-0.08274220693193401</v>
       </c>
       <c r="P110" t="n">
-        <v>25.5999755859375</v>
+        <v>44.86947578917297</v>
       </c>
       <c r="Q110" t="n">
-        <v>-74.4000244140625</v>
+        <v>-55.13052421082703</v>
       </c>
       <c r="R110" t="n">
-        <v>-57.27168428346319</v>
+        <v>-46.53035451156564</v>
       </c>
       <c r="S110" t="n">
-        <v>-0.9710491529029364</v>
+        <v>-2.346784065858298</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10603,19 +10615,19 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Bullish Harami</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Inside Bar, Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W110" t="n">
         <v>34.6</v>
       </c>
       <c r="X110" t="n">
-        <v>77</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -10624,7 +10636,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 31); RSI scarico (36) — zona di interesse long; pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (106.76); vicino alla resistenza dei 20g (108.37)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 23); pattern: Bear Flag / Consolidation; segnale candlestick: Bullish Harami</t>
         </is>
       </c>
     </row>
@@ -10645,52 +10657,52 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.8141999840736389</v>
+        <v>0.8133999705314636</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.7500414691628876</v>
+        <v>-0.8475621181903481</v>
       </c>
       <c r="F111" t="n">
-        <v>2.06102617736581</v>
+        <v>1.960743440117785</v>
       </c>
       <c r="G111" t="n">
-        <v>-4.087195775458019</v>
+        <v>-4.181437416023693</v>
       </c>
       <c r="H111" t="n">
-        <v>-13.64095257127572</v>
+        <v>-13.72580691760802</v>
       </c>
       <c r="I111" t="n">
-        <v>48.05094039743167</v>
+        <v>47.8876537496129</v>
       </c>
       <c r="J111" t="n">
         <v>23.19416919693623</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5617190597089854</v>
+        <v>0.5556675907776739</v>
       </c>
       <c r="L111" t="n">
-        <v>0.8150760375294139</v>
+        <v>0.8149998457634924</v>
       </c>
       <c r="M111" t="n">
-        <v>0.8663400520758016</v>
+        <v>0.8663086789957163</v>
       </c>
       <c r="N111" t="n">
-        <v>1.334810375217362</v>
+        <v>1.334802414883609</v>
       </c>
       <c r="O111" t="n">
-        <v>0.008276914583055756</v>
+        <v>0.008225859587771674</v>
       </c>
       <c r="P111" t="n">
-        <v>55.49971336425952</v>
+        <v>54.82535316989988</v>
       </c>
       <c r="Q111" t="n">
-        <v>-44.50028663574049</v>
+        <v>-45.17464683010012</v>
       </c>
       <c r="R111" t="n">
-        <v>11.63419483176751</v>
+        <v>11.11301258021213</v>
       </c>
       <c r="S111" t="n">
-        <v>-2.603111935474534</v>
+        <v>-2.698811801528944</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -10704,7 +10716,7 @@
         </is>
       </c>
       <c r="W111" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="X111" t="n">
         <v>69.59999999999999</v>
@@ -10723,66 +10735,66 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>US Treasury 20Y+ ETF</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.024600028991699</v>
+        <v>82.76000213623047</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.877071080111802</v>
+        <v>0.2908452531841244</v>
       </c>
       <c r="F112" t="n">
-        <v>-5.532860398700079</v>
+        <v>0.620063387514258</v>
       </c>
       <c r="G112" t="n">
-        <v>-5.88126562628668</v>
+        <v>-2.047574590223666</v>
       </c>
       <c r="H112" t="n">
-        <v>-6.297271948569383</v>
+        <v>-3.856876886852567</v>
       </c>
       <c r="I112" t="n">
-        <v>35.47489805986913</v>
+        <v>40.14983682880838</v>
       </c>
       <c r="J112" t="n">
-        <v>14.91272934107535</v>
+        <v>32.52789548612748</v>
       </c>
       <c r="K112" t="n">
-        <v>0.02310231174561308</v>
+        <v>0.2833191969651302</v>
       </c>
       <c r="L112" t="n">
-        <v>1.073761694582159</v>
+        <v>83.40854584020258</v>
       </c>
       <c r="M112" t="n">
-        <v>1.10961980305174</v>
+        <v>84.38201898320885</v>
       </c>
       <c r="N112" t="n">
-        <v>1.383597617377383</v>
+        <v>86.40649836022942</v>
       </c>
       <c r="O112" t="n">
-        <v>-0.00457051815127759</v>
+        <v>-0.005564233205044511</v>
       </c>
       <c r="P112" t="n">
-        <v>10.30046923642002</v>
+        <v>35.51036041927468</v>
       </c>
       <c r="Q112" t="n">
-        <v>-89.69953076357999</v>
+        <v>-64.48963958072532</v>
       </c>
       <c r="R112" t="n">
-        <v>-176.461208569767</v>
+        <v>-37.58428219590003</v>
       </c>
       <c r="S112" t="n">
-        <v>-6.185647016370477</v>
+        <v>-2.024386243353749</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -10792,14 +10804,14 @@
       <c r="U112" t="inlineStr"/>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Breakdown 20d, Double Top, Double Bottom</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W112" t="n">
-        <v>32.9</v>
+        <v>32.4</v>
       </c>
       <c r="X112" t="n">
-        <v>73.40000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -10808,73 +10820,73 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 15); RSI scarico (35) — zona di interesse long; pattern: Double Bottom; breakdown minimi 20g — pressione ribassista; sul supporto dei 20g (1.0143)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 33); sul supporto dei 20g (81.89); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>US Treasury 20Y+ ETF</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>82.76000213623047</v>
+        <v>1.022300004959106</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2908452531841244</v>
+        <v>-1.099582413554856</v>
       </c>
       <c r="F113" t="n">
-        <v>0.620063387514258</v>
+        <v>-5.744920407703891</v>
       </c>
       <c r="G113" t="n">
-        <v>-2.047574590223666</v>
+        <v>-6.092543534593775</v>
       </c>
       <c r="H113" t="n">
-        <v>-3.856876886852567</v>
+        <v>-6.507616005117855</v>
       </c>
       <c r="I113" t="n">
-        <v>40.14983682880838</v>
+        <v>35.08954275538798</v>
       </c>
       <c r="J113" t="n">
-        <v>32.52789548612748</v>
+        <v>14.91272934107535</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2833191969651302</v>
+        <v>0.009027652803244003</v>
       </c>
       <c r="L113" t="n">
-        <v>83.40854584020258</v>
+        <v>1.073542644674293</v>
       </c>
       <c r="M113" t="n">
-        <v>84.38201898320885</v>
+        <v>1.109529606030854</v>
       </c>
       <c r="N113" t="n">
-        <v>86.40649836022942</v>
+        <v>1.383574731566113</v>
       </c>
       <c r="O113" t="n">
-        <v>-0.005564233205044511</v>
+        <v>-0.004717300311762217</v>
       </c>
       <c r="P113" t="n">
-        <v>35.51036041927468</v>
+        <v>7.992094048282776</v>
       </c>
       <c r="Q113" t="n">
-        <v>-64.48963958072532</v>
+        <v>-92.00790595171722</v>
       </c>
       <c r="R113" t="n">
-        <v>-37.58428219590003</v>
+        <v>-178.3757062185155</v>
       </c>
       <c r="S113" t="n">
-        <v>-2.024386243353749</v>
+        <v>-6.396241648772383</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -10884,14 +10896,14 @@
       <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakdown 20d, Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W113" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="X113" t="n">
-        <v>71.3</v>
+        <v>74</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -10900,7 +10912,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 33); sul supporto dei 20g (81.89); in zona Fib Fib 78.6 — livello strutturale; penalizzato dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 15); RSI scarico (35) — zona di interesse long; pattern: Double Bottom; breakdown minimi 20g — pressione ribassista; sul supporto dei 20g (1.0143)</t>
         </is>
       </c>
     </row>
@@ -11105,52 +11117,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.670000076293945</v>
+        <v>2.671000003814697</v>
       </c>
       <c r="E116" t="n">
-        <v>1.136362507487831</v>
+        <v>1.174238548435502</v>
       </c>
       <c r="F116" t="n">
-        <v>-2.803054361606261</v>
+        <v>-2.766653650707496</v>
       </c>
       <c r="G116" t="n">
-        <v>-11.35458161023408</v>
+        <v>-11.32138348630012</v>
       </c>
       <c r="H116" t="n">
-        <v>-3.155600078037335</v>
+        <v>-3.119331397158831</v>
       </c>
       <c r="I116" t="n">
-        <v>36.39450161627529</v>
+        <v>36.48209428466012</v>
       </c>
       <c r="J116" t="n">
         <v>50.60466185741553</v>
       </c>
       <c r="K116" t="n">
-        <v>0.1710086878515423</v>
+        <v>0.1731424217285341</v>
       </c>
       <c r="L116" t="n">
-        <v>2.809692548186695</v>
+        <v>2.809787779379147</v>
       </c>
       <c r="M116" t="n">
-        <v>2.929540128991426</v>
+        <v>2.929579341835377</v>
       </c>
       <c r="N116" t="n">
-        <v>3.1813594382675</v>
+        <v>3.181369387795069</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.008352388867814448</v>
+        <v>-0.008288575829453443</v>
       </c>
       <c r="P116" t="n">
-        <v>14.40003712972005</v>
+        <v>14.66668446858724</v>
       </c>
       <c r="Q116" t="n">
-        <v>-85.59996287027995</v>
+        <v>-85.33331553141277</v>
       </c>
       <c r="R116" t="n">
-        <v>-46.90727593373438</v>
+        <v>-46.80907036381087</v>
       </c>
       <c r="S116" t="n">
-        <v>-9.183672641890272</v>
+        <v>-9.149661502390593</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11159,7 +11171,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Piercing Pattern</t>
+          <t>Bullish Engulfing, Piercing Pattern</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -11171,7 +11183,7 @@
         <v>27.8</v>
       </c>
       <c r="X116" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -11180,7 +11192,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); RSI scarico (36) — zona di interesse long; segnale candlestick: Piercing Pattern; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 51); RSI scarico (36) — zona di interesse long; candela di inversione bullish (engulfing); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -12839,52 +12851,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6.572999954223633</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="E17" t="n">
-        <v>2.128652683098142</v>
+        <v>2.315105202755818</v>
       </c>
       <c r="F17" t="n">
-        <v>7.498567421942814</v>
+        <v>7.694823597157496</v>
       </c>
       <c r="G17" t="n">
-        <v>15.02318682762893</v>
+        <v>15.23318042334996</v>
       </c>
       <c r="H17" t="n">
-        <v>41.27887670390488</v>
+        <v>41.53680434559804</v>
       </c>
       <c r="I17" t="n">
-        <v>66.25581007999997</v>
+        <v>66.49456234460931</v>
       </c>
       <c r="J17" t="n">
         <v>36.23501837343277</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8647977020974583</v>
+        <v>0.8737094119364792</v>
       </c>
       <c r="L17" t="n">
-        <v>6.16943867795759</v>
+        <v>6.170581543093147</v>
       </c>
       <c r="M17" t="n">
-        <v>5.755895128678126</v>
+        <v>5.756365720204531</v>
       </c>
       <c r="N17" t="n">
-        <v>4.771529400734692</v>
+        <v>4.771648804554824</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.002204323813302433</v>
+        <v>-0.001438506491698799</v>
       </c>
       <c r="P17" t="n">
-        <v>80.26652041380954</v>
+        <v>81.49666727279482</v>
       </c>
       <c r="Q17" t="n">
-        <v>-19.73347958619044</v>
+        <v>-18.50333272720518</v>
       </c>
       <c r="R17" t="n">
-        <v>101.6886620092638</v>
+        <v>102.5032604478715</v>
       </c>
       <c r="S17" t="n">
-        <v>23.03228256605767</v>
+        <v>23.25689807288178</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -12894,10 +12906,10 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>77.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -16551,52 +16563,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.349181652069092</v>
+        <v>1.349272727966309</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2293599715263772</v>
+        <v>0.2361259091396617</v>
       </c>
       <c r="F57" t="n">
-        <v>1.147880710492055</v>
+        <v>1.154708652432368</v>
       </c>
       <c r="G57" t="n">
-        <v>1.043318413394645</v>
+        <v>1.050139296904407</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.05316247866435919</v>
+        <v>-0.04641561260131377</v>
       </c>
       <c r="I57" t="n">
-        <v>53.4785695022907</v>
+        <v>53.51060011841153</v>
       </c>
       <c r="J57" t="n">
         <v>9.831358251632462</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6894929849345829</v>
+        <v>0.6913687420781293</v>
       </c>
       <c r="L57" t="n">
-        <v>1.340769656048774</v>
+        <v>1.340778329943747</v>
       </c>
       <c r="M57" t="n">
-        <v>1.33709133212856</v>
+        <v>1.337094903732372</v>
       </c>
       <c r="N57" t="n">
-        <v>1.308057298125865</v>
+        <v>1.308058204353698</v>
       </c>
       <c r="O57" t="n">
-        <v>0.0006513357682905748</v>
+        <v>0.0006571480192812969</v>
       </c>
       <c r="P57" t="n">
-        <v>68.49481823438389</v>
+        <v>68.67366932680355</v>
       </c>
       <c r="Q57" t="n">
-        <v>-31.50518176561611</v>
+        <v>-31.32633067319645</v>
       </c>
       <c r="R57" t="n">
-        <v>62.16357320647989</v>
+        <v>62.41026055805194</v>
       </c>
       <c r="S57" t="n">
-        <v>0.4924484751997804</v>
+        <v>0.4992321724834881</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -17847,52 +17859,52 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>4396.10009765625</v>
+        <v>4401.2998046875</v>
       </c>
       <c r="E71" t="n">
-        <v>8.569805429133615</v>
+        <v>8.698221790938554</v>
       </c>
       <c r="F71" t="n">
-        <v>6.890847591243299</v>
+        <v>7.017278081780298</v>
       </c>
       <c r="G71" t="n">
-        <v>-12.99158638978228</v>
+        <v>-12.88867284141514</v>
       </c>
       <c r="H71" t="n">
-        <v>33.66475807073004</v>
+        <v>33.82285674158179</v>
       </c>
       <c r="I71" t="n">
-        <v>51.66586780771447</v>
+        <v>51.82215453877165</v>
       </c>
       <c r="J71" t="n">
         <v>46.69977840016973</v>
       </c>
       <c r="K71" t="n">
-        <v>0.4933263440232275</v>
+        <v>0.4977782180756851</v>
       </c>
       <c r="L71" t="n">
-        <v>4329.819079289384</v>
+        <v>4330.314289482836</v>
       </c>
       <c r="M71" t="n">
-        <v>4217.726163352375</v>
+        <v>4217.930073432031</v>
       </c>
       <c r="N71" t="n">
-        <v>3164.25462221311</v>
+        <v>3164.30636059153</v>
       </c>
       <c r="O71" t="n">
-        <v>-41.56298240942182</v>
+        <v>-41.23114925415197</v>
       </c>
       <c r="P71" t="n">
-        <v>54.01768931767168</v>
+        <v>54.66546629114378</v>
       </c>
       <c r="Q71" t="n">
-        <v>-45.98231068232833</v>
+        <v>-45.33453370885621</v>
       </c>
       <c r="R71" t="n">
-        <v>-24.63145902401129</v>
+        <v>-24.25013407367093</v>
       </c>
       <c r="S71" t="n">
-        <v>-3.813666383944159</v>
+        <v>-3.699897192137036</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -17909,7 +17921,7 @@
         <v>60.4</v>
       </c>
       <c r="X71" t="n">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -18491,52 +18503,52 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>157.8309936523438</v>
+        <v>157.7449951171875</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.468323745090971</v>
+        <v>-1.522011424730607</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.240962384230494</v>
+        <v>-2.294229070568155</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.8636609517368887</v>
+        <v>-0.9176780984430866</v>
       </c>
       <c r="H78" t="n">
-        <v>9.773322956973796</v>
+        <v>9.713509958556465</v>
       </c>
       <c r="I78" t="n">
-        <v>46.37816173197313</v>
+        <v>46.15683927091028</v>
       </c>
       <c r="J78" t="n">
         <v>10.97004758314641</v>
       </c>
       <c r="K78" t="n">
-        <v>0.2087579534198086</v>
+        <v>0.1984125518729986</v>
       </c>
       <c r="L78" t="n">
-        <v>159.7574400243448</v>
+        <v>159.7492496876632</v>
       </c>
       <c r="M78" t="n">
-        <v>156.8925690771447</v>
+        <v>156.8891965855699</v>
       </c>
       <c r="N78" t="n">
-        <v>146.9946142522579</v>
+        <v>146.9937585454404</v>
       </c>
       <c r="O78" t="n">
-        <v>-0.2918901912649507</v>
+        <v>-0.2973784168703779</v>
       </c>
       <c r="P78" t="n">
-        <v>31.16876904784682</v>
+        <v>30.20595591149499</v>
       </c>
       <c r="Q78" t="n">
-        <v>-68.83123095215318</v>
+        <v>-69.794044088505</v>
       </c>
       <c r="R78" t="n">
-        <v>-80.18611692658943</v>
+        <v>-80.97736501180712</v>
       </c>
       <c r="S78" t="n">
-        <v>-0.05889055603216509</v>
+        <v>-0.1133462039070277</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -18553,7 +18565,7 @@
         <v>54.8</v>
       </c>
       <c r="X78" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -19037,12 +19049,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -19051,52 +19063,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>63.63000106811523</v>
+        <v>1757.400024414062</v>
       </c>
       <c r="E84" t="n">
-        <v>10.48601605536414</v>
+        <v>6.489727468770856</v>
       </c>
       <c r="F84" t="n">
-        <v>4.925546946981041</v>
+        <v>8.709640662780039</v>
       </c>
       <c r="G84" t="n">
-        <v>-21.36095123689838</v>
+        <v>-13.70912081502643</v>
       </c>
       <c r="H84" t="n">
-        <v>93.45130844633304</v>
+        <v>67.1008943621086</v>
       </c>
       <c r="I84" t="n">
-        <v>46.81776796642703</v>
+        <v>47.47911350884907</v>
       </c>
       <c r="J84" t="n">
-        <v>14.86486989527701</v>
+        <v>18.96823238228148</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3379659857151244</v>
+        <v>0.4000967991554171</v>
       </c>
       <c r="L84" t="n">
-        <v>66.24620509759608</v>
+        <v>1785.71292216433</v>
       </c>
       <c r="M84" t="n">
-        <v>63.20402895097076</v>
+        <v>1752.099362108789</v>
       </c>
       <c r="N84" t="n">
-        <v>42.88778595682619</v>
+        <v>1340.717778330742</v>
       </c>
       <c r="O84" t="n">
-        <v>-1.864435083033229</v>
+        <v>-25.5773155833054</v>
       </c>
       <c r="P84" t="n">
-        <v>25.43324004088471</v>
+        <v>33.99310593006429</v>
       </c>
       <c r="Q84" t="n">
-        <v>-74.56675995911529</v>
+        <v>-66.00689406993571</v>
       </c>
       <c r="R84" t="n">
-        <v>-59.93295047053684</v>
+        <v>-35.35647827159382</v>
       </c>
       <c r="S84" t="n">
-        <v>-8.261244942061264</v>
+        <v>-10.81903754253738</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -19106,31 +19118,27 @@
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="X84" t="n">
-        <v>65.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>mercato laterale — ATR basso (ADX 15)</t>
-        </is>
-      </c>
+      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -19139,52 +19147,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1752.099975585938</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="E85" t="n">
-        <v>6.168570789905781</v>
+        <v>10.78119788953336</v>
       </c>
       <c r="F85" t="n">
-        <v>8.381789066332757</v>
+        <v>5.205873059776134</v>
       </c>
       <c r="G85" t="n">
-        <v>-13.96936086666446</v>
+        <v>-21.15085389173226</v>
       </c>
       <c r="H85" t="n">
-        <v>66.59694370372745</v>
+        <v>93.96814590765491</v>
       </c>
       <c r="I85" t="n">
-        <v>47.20220690986926</v>
+        <v>46.99395103986621</v>
       </c>
       <c r="J85" t="n">
-        <v>18.96823238228148</v>
+        <v>14.86486989527701</v>
       </c>
       <c r="K85" t="n">
-        <v>0.393144094613169</v>
+        <v>0.3427136626528636</v>
       </c>
       <c r="L85" t="n">
-        <v>1785.208155609271</v>
+        <v>66.26239539940039</v>
       </c>
       <c r="M85" t="n">
-        <v>1751.891517056706</v>
+        <v>63.21069554583136</v>
       </c>
       <c r="N85" t="n">
-        <v>1340.665041526482</v>
+        <v>42.88947748089529</v>
       </c>
       <c r="O85" t="n">
-        <v>-25.91555231763611</v>
+        <v>-1.85358619703786</v>
       </c>
       <c r="P85" t="n">
-        <v>33.19837693561666</v>
+        <v>25.93510926838629</v>
       </c>
       <c r="Q85" t="n">
-        <v>-66.80162306438334</v>
+        <v>-74.0648907316137</v>
       </c>
       <c r="R85" t="n">
-        <v>-35.91188781890074</v>
+        <v>-59.46648330523919</v>
       </c>
       <c r="S85" t="n">
-        <v>-11.08799364188723</v>
+        <v>-8.016149544931261</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -19197,14 +19205,18 @@
         <v>49.5</v>
       </c>
       <c r="X85" t="n">
-        <v>63.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>mercato laterale — ATR basso (ADX 15)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -19687,52 +19699,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="E91" t="n">
-        <v>8.26278037247905</v>
+        <v>8.419569337536959</v>
       </c>
       <c r="F91" t="n">
-        <v>9.438146705896067</v>
+        <v>9.596637866947333</v>
       </c>
       <c r="G91" t="n">
-        <v>-11.13827799403151</v>
+        <v>-11.00958614463836</v>
       </c>
       <c r="H91" t="n">
-        <v>43.65962941189805</v>
+        <v>43.86768101133598</v>
       </c>
       <c r="I91" t="n">
-        <v>49.73284535191798</v>
+        <v>49.85472545361231</v>
       </c>
       <c r="J91" t="n">
         <v>40.94516405492782</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5283992771114766</v>
+        <v>0.5323677403621039</v>
       </c>
       <c r="L91" t="n">
-        <v>1362.074709309924</v>
+        <v>1362.2651855004</v>
       </c>
       <c r="M91" t="n">
-        <v>1383.327782048294</v>
+        <v>1383.406213420843</v>
       </c>
       <c r="N91" t="n">
-        <v>1363.149123718516</v>
+        <v>1363.169024216028</v>
       </c>
       <c r="O91" t="n">
-        <v>-2.141487799121954</v>
+        <v>-2.013852471486665</v>
       </c>
       <c r="P91" t="n">
-        <v>57.10943048020252</v>
+        <v>57.62931617135158</v>
       </c>
       <c r="Q91" t="n">
-        <v>-42.89056951979748</v>
+        <v>-42.37068382864842</v>
       </c>
       <c r="R91" t="n">
-        <v>-7.303802206024752</v>
+        <v>-7.073646152917236</v>
       </c>
       <c r="S91" t="n">
-        <v>-3.074118987022056</v>
+        <v>-2.933748413505799</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -19750,7 +19762,7 @@
         </is>
       </c>
       <c r="W91" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="X91" t="n">
         <v>62.2</v>
@@ -19783,70 +19795,66 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>99.61699676513672</v>
+        <v>99.60399627685547</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.1833730270791478</v>
+        <v>-0.1963995680447916</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.232405153373828</v>
+        <v>-1.245294790695439</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.7403386216582097</v>
+        <v>-0.7532924759848125</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2889307649164952</v>
+        <v>0.2758425860766689</v>
       </c>
       <c r="I92" t="n">
-        <v>49.47807958806289</v>
+        <v>49.40603379359559</v>
       </c>
       <c r="J92" t="n">
         <v>34.32611197126474</v>
       </c>
       <c r="K92" t="n">
-        <v>0.4758366461455093</v>
+        <v>0.4730584663839454</v>
       </c>
       <c r="L92" t="n">
-        <v>99.87407708695079</v>
+        <v>99.87283894520972</v>
       </c>
       <c r="M92" t="n">
-        <v>99.68356880513862</v>
+        <v>99.68305898206876</v>
       </c>
       <c r="N92" t="n">
-        <v>100.8300671511398</v>
+        <v>100.8299377930475</v>
       </c>
       <c r="O92" t="n">
-        <v>0.01490810323211367</v>
+        <v>0.01407844244153594</v>
       </c>
       <c r="P92" t="n">
-        <v>47.6498021300069</v>
+        <v>47.33804025460553</v>
       </c>
       <c r="Q92" t="n">
-        <v>-52.3501978699931</v>
+        <v>-52.66195974539447</v>
       </c>
       <c r="R92" t="n">
-        <v>-2.690020497653747</v>
+        <v>-2.99273289603512</v>
       </c>
       <c r="S92" t="n">
-        <v>-0.03312068262599777</v>
+        <v>-0.04616683223179763</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W92" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="X92" t="n">
         <v>60.1</v>
@@ -19858,7 +19866,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 34); pattern: Double Bottom; doji — indecisione del mercato; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 34); pattern: Double Bottom; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -20071,52 +20079,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>82.16000366210938</v>
+        <v>82.26999664306641</v>
       </c>
       <c r="E95" t="n">
-        <v>-8.832666269281219</v>
+        <v>-8.710614585298993</v>
       </c>
       <c r="F95" t="n">
-        <v>14.42896959612028</v>
+        <v>14.58216315640153</v>
       </c>
       <c r="G95" t="n">
-        <v>-20.34127967005272</v>
+        <v>-20.23463532100489</v>
       </c>
       <c r="H95" t="n">
-        <v>28.57590250422035</v>
+        <v>28.74803549065303</v>
       </c>
       <c r="I95" t="n">
-        <v>47.48044968116274</v>
+        <v>47.5405178797277</v>
       </c>
       <c r="J95" t="n">
         <v>28.3348472111897</v>
       </c>
       <c r="K95" t="n">
-        <v>0.2812778244592558</v>
+        <v>0.2832609772470092</v>
       </c>
       <c r="L95" t="n">
-        <v>87.22888003570141</v>
+        <v>87.23935555769731</v>
       </c>
       <c r="M95" t="n">
-        <v>82.47204900076841</v>
+        <v>82.47636245100202</v>
       </c>
       <c r="N95" t="n">
-        <v>77.94306991036873</v>
+        <v>77.94416436789071</v>
       </c>
       <c r="O95" t="n">
-        <v>-1.63063197991414</v>
+        <v>-1.623612484833118</v>
       </c>
       <c r="P95" t="n">
-        <v>26.64598561256207</v>
+        <v>26.88981842007436</v>
       </c>
       <c r="Q95" t="n">
-        <v>-73.35401438743793</v>
+        <v>-73.11018157992565</v>
       </c>
       <c r="R95" t="n">
-        <v>-46.46407720555299</v>
+        <v>-46.32933651293509</v>
       </c>
       <c r="S95" t="n">
-        <v>-26.7670898705798</v>
+        <v>-26.66904817473931</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -20163,52 +20171,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>77.05999755859375</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="E96" t="n">
-        <v>-8.987836039829645</v>
+        <v>-8.964209876024809</v>
       </c>
       <c r="F96" t="n">
-        <v>12.18517225170759</v>
+        <v>12.21429479028662</v>
       </c>
       <c r="G96" t="n">
-        <v>-21.93293660893622</v>
+        <v>-21.91267090875744</v>
       </c>
       <c r="H96" t="n">
-        <v>26.76426451395335</v>
+        <v>26.7971716897383</v>
       </c>
       <c r="I96" t="n">
-        <v>47.2983560261265</v>
+        <v>47.30924691630658</v>
       </c>
       <c r="J96" t="n">
         <v>28.44184216763671</v>
       </c>
       <c r="K96" t="n">
-        <v>0.2649589061574672</v>
+        <v>0.2653341840829447</v>
       </c>
       <c r="L96" t="n">
-        <v>82.35644363393116</v>
+        <v>82.35834880273697</v>
       </c>
       <c r="M96" t="n">
-        <v>77.89094188098086</v>
+        <v>77.89172636225383</v>
       </c>
       <c r="N96" t="n">
-        <v>73.7226958330447</v>
+        <v>73.72289488053187</v>
       </c>
       <c r="O96" t="n">
-        <v>-1.753363597974439</v>
+        <v>-1.752086972039623</v>
       </c>
       <c r="P96" t="n">
-        <v>23.61535840442624</v>
+        <v>23.6625049335732</v>
       </c>
       <c r="Q96" t="n">
-        <v>-76.38464159557377</v>
+        <v>-76.3374950664268</v>
       </c>
       <c r="R96" t="n">
-        <v>-45.81489224641275</v>
+        <v>-45.78946719639335</v>
       </c>
       <c r="S96" t="n">
-        <v>-21.62327319184242</v>
+        <v>-21.60292710506146</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -20443,52 +20451,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>64920.12890625</v>
+        <v>64981.390625</v>
       </c>
       <c r="E99" t="n">
-        <v>2.265412095160824</v>
+        <v>2.361914597838766</v>
       </c>
       <c r="F99" t="n">
-        <v>2.159389161396374</v>
+        <v>2.25579161579561</v>
       </c>
       <c r="G99" t="n">
-        <v>-10.81164232381525</v>
+        <v>-10.72747995113076</v>
       </c>
       <c r="H99" t="n">
-        <v>-38.55292233080137</v>
+        <v>-38.4949379482439</v>
       </c>
       <c r="I99" t="n">
-        <v>41.03658896802904</v>
+        <v>41.12678494775887</v>
       </c>
       <c r="J99" t="n">
         <v>28.25173352339345</v>
       </c>
       <c r="K99" t="n">
-        <v>0.3394786816153517</v>
+        <v>0.3416044058823377</v>
       </c>
       <c r="L99" t="n">
-        <v>68971.6470554503</v>
+        <v>68977.48150485507</v>
       </c>
       <c r="M99" t="n">
-        <v>77817.46389641527</v>
+        <v>77819.8663167584</v>
       </c>
       <c r="N99" t="n">
-        <v>68501.15276762795</v>
+        <v>68501.76233696875</v>
       </c>
       <c r="O99" t="n">
-        <v>416.2679179464758</v>
+        <v>420.1774977185478</v>
       </c>
       <c r="P99" t="n">
-        <v>28.63853917207814</v>
+        <v>28.8831511728056</v>
       </c>
       <c r="Q99" t="n">
-        <v>-71.36146082792186</v>
+        <v>-71.1168488271944</v>
       </c>
       <c r="R99" t="n">
-        <v>-58.06203845166726</v>
+        <v>-57.84803688516004</v>
       </c>
       <c r="S99" t="n">
-        <v>-4.311405316352579</v>
+        <v>-4.221109011125623</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -20502,7 +20510,7 @@
       </c>
       <c r="V99" t="inlineStr"/>
       <c r="W99" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="X99" t="n">
         <v>70.90000000000001</v>
@@ -21091,52 +21099,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.024600028991699</v>
+        <v>1.022300004959106</v>
       </c>
       <c r="E106" t="n">
-        <v>-5.532860398700079</v>
+        <v>-5.744920407703891</v>
       </c>
       <c r="F106" t="n">
-        <v>-11.358572359262</v>
+        <v>-11.55755479932465</v>
       </c>
       <c r="G106" t="n">
-        <v>-29.21838191053928</v>
+        <v>-29.37727261721999</v>
       </c>
       <c r="H106" t="n">
-        <v>-52.98239855757448</v>
+        <v>-53.08794375590799</v>
       </c>
       <c r="I106" t="n">
-        <v>31.84204444155451</v>
+        <v>31.76609185462615</v>
       </c>
       <c r="J106" t="n">
         <v>18.82525741358344</v>
       </c>
       <c r="K106" t="n">
-        <v>0.129350458904973</v>
+        <v>0.1260679502304877</v>
       </c>
       <c r="L106" t="n">
-        <v>1.25461535293586</v>
+        <v>1.254396303027994</v>
       </c>
       <c r="M106" t="n">
-        <v>1.569599819065582</v>
+        <v>1.569509622044696</v>
       </c>
       <c r="N106" t="n">
-        <v>1.383577158939686</v>
+        <v>1.383554273128417</v>
       </c>
       <c r="O106" t="n">
-        <v>0.01286470739353249</v>
+        <v>0.01271792523304788</v>
       </c>
       <c r="P106" t="n">
-        <v>2.761618238308146</v>
+        <v>2.333803115462632</v>
       </c>
       <c r="Q106" t="n">
-        <v>-97.23838176169185</v>
+        <v>-97.66619688453737</v>
       </c>
       <c r="R106" t="n">
-        <v>-61.92390023383015</v>
+        <v>-62.13126756150904</v>
       </c>
       <c r="S106" t="n">
-        <v>-26.0154110601648</v>
+        <v>-26.18149180171092</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -21275,52 +21283,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1914.579956054688</v>
+        <v>1912.699951171875</v>
       </c>
       <c r="E108" t="n">
-        <v>1.702927448607872</v>
+        <v>1.603061156999064</v>
       </c>
       <c r="F108" t="n">
-        <v>7.379334448599018</v>
+        <v>7.273894259257174</v>
       </c>
       <c r="G108" t="n">
-        <v>-12.07344300776448</v>
+        <v>-12.15978171404392</v>
       </c>
       <c r="H108" t="n">
-        <v>-24.51187350839342</v>
+        <v>-24.58599840766952</v>
       </c>
       <c r="I108" t="n">
-        <v>43.13610088954027</v>
+        <v>43.06822760807148</v>
       </c>
       <c r="J108" t="n">
         <v>32.43204889549959</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4245831592618058</v>
+        <v>0.4227276322774749</v>
       </c>
       <c r="L108" t="n">
-        <v>2007.615437591977</v>
+        <v>2007.4363895079</v>
       </c>
       <c r="M108" t="n">
-        <v>2385.132378576169</v>
+        <v>2385.05865289449</v>
       </c>
       <c r="N108" t="n">
-        <v>2474.035680960359</v>
+        <v>2474.016974444112</v>
       </c>
       <c r="O108" t="n">
-        <v>43.90129030935574</v>
+        <v>43.78131278976878</v>
       </c>
       <c r="P108" t="n">
-        <v>44.52360476494459</v>
+        <v>44.31848375873422</v>
       </c>
       <c r="Q108" t="n">
-        <v>-55.47639523505541</v>
+        <v>-55.68151624126578</v>
       </c>
       <c r="R108" t="n">
-        <v>-25.65897764442774</v>
+        <v>-25.81171765782172</v>
       </c>
       <c r="S108" t="n">
-        <v>-6.74452622969417</v>
+        <v>-6.836097618751458</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21371,52 +21379,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.670000076293945</v>
+        <v>2.671000003814697</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.803054361606261</v>
+        <v>-2.766653650707496</v>
       </c>
       <c r="F109" t="n">
-        <v>-16.45807279614257</v>
+        <v>-16.42678595353553</v>
       </c>
       <c r="G109" t="n">
-        <v>-14.72372914370496</v>
+        <v>-14.69179278128556</v>
       </c>
       <c r="H109" t="n">
-        <v>-22.54133868261529</v>
+        <v>-22.51233005154462</v>
       </c>
       <c r="I109" t="n">
-        <v>40.93105467360591</v>
+        <v>40.9478396023931</v>
       </c>
       <c r="J109" t="n">
         <v>23.62840631753764</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2207043117821255</v>
+        <v>0.2216578438302673</v>
       </c>
       <c r="L109" t="n">
-        <v>3.017648224800151</v>
+        <v>3.017743455992603</v>
       </c>
       <c r="M109" t="n">
-        <v>3.199718426231934</v>
+        <v>3.199757639075885</v>
       </c>
       <c r="N109" t="n">
-        <v>3.315445710466544</v>
+        <v>3.315455659994114</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.01161535803102393</v>
+        <v>-0.01155154499266292</v>
       </c>
       <c r="P109" t="n">
-        <v>6.545471044281986</v>
+        <v>6.666674373125344</v>
       </c>
       <c r="Q109" t="n">
-        <v>-93.45452895571802</v>
+        <v>-93.33332562687465</v>
       </c>
       <c r="R109" t="n">
-        <v>-41.03477604790076</v>
+        <v>-40.98197457516815</v>
       </c>
       <c r="S109" t="n">
-        <v>-13.73182385743386</v>
+        <v>-13.69951602184392</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -21459,52 +21467,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>73.86000061035156</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="E110" t="n">
-        <v>0.5598164511704695</v>
+        <v>0.3283652661595138</v>
       </c>
       <c r="F110" t="n">
-        <v>-9.288576640738755</v>
+        <v>-9.497360498660035</v>
       </c>
       <c r="G110" t="n">
-        <v>-19.93654123252686</v>
+        <v>-20.12081744803492</v>
       </c>
       <c r="H110" t="n">
-        <v>-53.18933157250163</v>
+        <v>-53.29707226914421</v>
       </c>
       <c r="I110" t="n">
-        <v>38.71751846767551</v>
+        <v>38.56888622975971</v>
       </c>
       <c r="J110" t="n">
         <v>17.08330755691708</v>
       </c>
       <c r="K110" t="n">
-        <v>0.3009099579257874</v>
+        <v>0.2953279641032308</v>
       </c>
       <c r="L110" t="n">
-        <v>82.51671788544238</v>
+        <v>82.50052758363806</v>
       </c>
       <c r="M110" t="n">
-        <v>106.6065043866423</v>
+        <v>106.5998377917817</v>
       </c>
       <c r="N110" t="n">
-        <v>111.9929629469798</v>
+        <v>111.9912714229107</v>
       </c>
       <c r="O110" t="n">
-        <v>2.265912877331974</v>
+        <v>2.255063991336604</v>
       </c>
       <c r="P110" t="n">
-        <v>35.52070290800938</v>
+        <v>35.07158964568386</v>
       </c>
       <c r="Q110" t="n">
-        <v>-64.47929709199062</v>
+        <v>-64.92841035431614</v>
       </c>
       <c r="R110" t="n">
-        <v>-31.96262096083305</v>
+        <v>-32.2384002717545</v>
       </c>
       <c r="S110" t="n">
-        <v>-14.24426311772994</v>
+        <v>-14.44164083403202</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -21513,7 +21521,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
+          <t>Doji, Bullish Harami</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -21525,7 +21533,7 @@
         <v>29</v>
       </c>
       <c r="X110" t="n">
-        <v>77.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21534,7 +21542,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); segnale candlestick: Bullish Harami</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -21651,52 +21659,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>8.192999839782715</v>
+        <v>8.194999694824219</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.109699112353924</v>
+        <v>-2.085804761618815</v>
       </c>
       <c r="F112" t="n">
-        <v>1.721766559273097</v>
+        <v>1.746596144487578</v>
       </c>
       <c r="G112" t="n">
-        <v>-13.59533914776534</v>
+        <v>-13.57424836294978</v>
       </c>
       <c r="H112" t="n">
-        <v>-41.73735206015598</v>
+        <v>-41.7231305475852</v>
       </c>
       <c r="I112" t="n">
-        <v>41.59781609404167</v>
+        <v>41.60831930040294</v>
       </c>
       <c r="J112" t="n">
         <v>23.09023807369082</v>
       </c>
       <c r="K112" t="n">
-        <v>0.3491669990461723</v>
+        <v>0.3497578797669609</v>
       </c>
       <c r="L112" t="n">
-        <v>8.891782559254459</v>
+        <v>8.891973021639364</v>
       </c>
       <c r="M112" t="n">
-        <v>11.06552683044892</v>
+        <v>11.06560525613682</v>
       </c>
       <c r="N112" t="n">
-        <v>12.94657428477863</v>
+        <v>12.94659418383377</v>
       </c>
       <c r="O112" t="n">
-        <v>0.22383026923616</v>
+        <v>0.2239578953128829</v>
       </c>
       <c r="P112" t="n">
-        <v>30.55060776609017</v>
+        <v>30.60280067076718</v>
       </c>
       <c r="Q112" t="n">
-        <v>-69.44939223390983</v>
+        <v>-69.39719932923282</v>
       </c>
       <c r="R112" t="n">
-        <v>-33.07037883548133</v>
+        <v>-33.027238587856</v>
       </c>
       <c r="S112" t="n">
-        <v>-5.667380174496472</v>
+        <v>-5.644354229296244</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -21743,69 +21751,65 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6.440999984741211</v>
+        <v>6.466000080108643</v>
       </c>
       <c r="E113" t="n">
-        <v>-1.535607205991774</v>
+        <v>-1.153427541967855</v>
       </c>
       <c r="F113" t="n">
-        <v>-6.885175656416909</v>
+        <v>-6.523759805737517</v>
       </c>
       <c r="G113" t="n">
-        <v>-35.16953223982178</v>
+        <v>-34.91789928211967</v>
       </c>
       <c r="H113" t="n">
-        <v>-69.14256165591115</v>
+        <v>-69.02279160417626</v>
       </c>
       <c r="I113" t="n">
-        <v>34.02742695141634</v>
+        <v>34.13027884573117</v>
       </c>
       <c r="J113" t="n">
         <v>32.47669137590711</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2420450971017585</v>
+        <v>0.2460803350575874</v>
       </c>
       <c r="L113" t="n">
-        <v>7.974494481779084</v>
+        <v>7.976875443242649</v>
       </c>
       <c r="M113" t="n">
-        <v>12.08427318398338</v>
+        <v>12.08525357988014</v>
       </c>
       <c r="N113" t="n">
-        <v>20.79343054683992</v>
+        <v>20.79367930400775</v>
       </c>
       <c r="O113" t="n">
-        <v>0.2101757310188388</v>
+        <v>0.2117711787004066</v>
       </c>
       <c r="P113" t="n">
-        <v>15.63340304527034</v>
+        <v>16.15630740101804</v>
       </c>
       <c r="Q113" t="n">
-        <v>-84.36659695472966</v>
+        <v>-83.84369259898196</v>
       </c>
       <c r="R113" t="n">
-        <v>-54.7466739951774</v>
+        <v>-54.43816414206836</v>
       </c>
       <c r="S113" t="n">
-        <v>-28.5801662460427</v>
+        <v>-28.30295732519115</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
+      <c r="U113" t="inlineStr"/>
       <c r="V113" t="inlineStr"/>
       <c r="W113" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="X113" t="n">
-        <v>76.7</v>
+        <v>70.7</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
@@ -21814,7 +21818,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 32); RSI scarico (34) — zona di interesse long; shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 32); RSI scarico (34) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -21923,52 +21927,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.2013500034809113</v>
+        <v>0.2015500068664551</v>
       </c>
       <c r="E115" t="n">
-        <v>6.335224420043484</v>
+        <v>6.44084848023172</v>
       </c>
       <c r="F115" t="n">
-        <v>6.328488589633552</v>
+        <v>6.434105959040259</v>
       </c>
       <c r="G115" t="n">
-        <v>-25.38364358390349</v>
+        <v>-25.3095262576449</v>
       </c>
       <c r="H115" t="n">
-        <v>-70.60472380813816</v>
+        <v>-70.57552512596419</v>
       </c>
       <c r="I115" t="n">
-        <v>41.84113466068154</v>
+        <v>41.87842150021287</v>
       </c>
       <c r="J115" t="n">
         <v>24.58003765593954</v>
       </c>
       <c r="K115" t="n">
-        <v>0.4472185125769882</v>
+        <v>0.4483481740801193</v>
       </c>
       <c r="L115" t="n">
-        <v>0.2186896702945342</v>
+        <v>0.2187087182360146</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3414917727680416</v>
+        <v>0.3414996160380629</v>
       </c>
       <c r="N115" t="n">
-        <v>0.5039436192883897</v>
+        <v>0.503945609371828</v>
       </c>
       <c r="O115" t="n">
-        <v>0.01101513596465356</v>
+        <v>0.01102789971347461</v>
       </c>
       <c r="P115" t="n">
-        <v>41.90717385367643</v>
+        <v>42.040947317853</v>
       </c>
       <c r="Q115" t="n">
-        <v>-58.09282614632357</v>
+        <v>-57.959052682147</v>
       </c>
       <c r="R115" t="n">
-        <v>-16.00789101530941</v>
+        <v>-15.93578414489769</v>
       </c>
       <c r="S115" t="n">
-        <v>-19.65122976276712</v>
+        <v>-19.57141836076109</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -21976,12 +21980,16 @@
         </is>
       </c>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Bear Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W115" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="X115" t="n">
-        <v>73.5</v>
+        <v>78</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -21990,7 +21998,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 25)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 25); pattern: Bear Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -22011,52 +22019,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8141999840736389</v>
+        <v>0.8133999705314636</v>
       </c>
       <c r="E116" t="n">
-        <v>2.06102617736581</v>
+        <v>1.960743440117785</v>
       </c>
       <c r="F116" t="n">
-        <v>-7.414676512786256</v>
+        <v>-7.505648649908958</v>
       </c>
       <c r="G116" t="n">
-        <v>-43.43897044087761</v>
+        <v>-43.4945459634664</v>
       </c>
       <c r="H116" t="n">
-        <v>-79.96689201111857</v>
+        <v>-79.98657606662884</v>
       </c>
       <c r="I116" t="n">
-        <v>29.50412932938383</v>
+        <v>29.4565033438091</v>
       </c>
       <c r="J116" t="n">
         <v>35.21750737921953</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2000332740512312</v>
+        <v>0.1991791140203023</v>
       </c>
       <c r="L116" t="n">
-        <v>1.094234822757696</v>
+        <v>1.094158630991775</v>
       </c>
       <c r="M116" t="n">
-        <v>1.894115398864675</v>
+        <v>1.89408402578459</v>
       </c>
       <c r="N116" t="n">
-        <v>5.157560687840824</v>
+        <v>5.157552727507071</v>
       </c>
       <c r="O116" t="n">
-        <v>0.03575669213033189</v>
+        <v>0.03570563713504787</v>
       </c>
       <c r="P116" t="n">
-        <v>9.617141096495194</v>
+        <v>9.500286130119946</v>
       </c>
       <c r="Q116" t="n">
-        <v>-90.38285890350481</v>
+        <v>-90.49971386988005</v>
       </c>
       <c r="R116" t="n">
-        <v>-50.94223048052952</v>
+        <v>-50.99148596854174</v>
       </c>
       <c r="S116" t="n">
-        <v>-42.31701097251344</v>
+        <v>-42.37368890579496</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22082,7 +22090,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 35); RSI scarico (30) — zona di interesse long; shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 35); RSI scarico (29) — zona di interesse long; shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
@@ -25837,52 +25845,52 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6.572999954223633</v>
+        <v>6.585000038146973</v>
       </c>
       <c r="E40" t="n">
-        <v>2.128652683098142</v>
+        <v>2.315105202755818</v>
       </c>
       <c r="F40" t="n">
-        <v>17.63758106551576</v>
+        <v>17.85234766450499</v>
       </c>
       <c r="G40" t="n">
-        <v>61.0831944968518</v>
+        <v>61.37727815211789</v>
       </c>
       <c r="H40" t="n">
-        <v>52.98497938052569</v>
+        <v>53.26427842272285</v>
       </c>
       <c r="I40" t="n">
-        <v>69.21744753567742</v>
+        <v>69.31775623737389</v>
       </c>
       <c r="J40" t="n">
         <v>65.51300591416762</v>
       </c>
       <c r="K40" t="n">
-        <v>0.9105809623933999</v>
+        <v>0.9137708838449491</v>
       </c>
       <c r="L40" t="n">
-        <v>5.495084943125683</v>
+        <v>5.496227808261239</v>
       </c>
       <c r="M40" t="n">
-        <v>4.761988543086033</v>
+        <v>4.762459134612438</v>
       </c>
       <c r="N40" t="n">
-        <v>3.970135630878761</v>
+        <v>3.970337312961506</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1149854615678131</v>
+        <v>0.1157512788894167</v>
       </c>
       <c r="P40" t="n">
-        <v>92.11711214753444</v>
+        <v>92.60851609325466</v>
       </c>
       <c r="Q40" t="n">
-        <v>-7.882887852465562</v>
+        <v>-7.391483906745332</v>
       </c>
       <c r="R40" t="n">
-        <v>115.5650428016174</v>
+        <v>115.8797723120903</v>
       </c>
       <c r="S40" t="n">
-        <v>64.90215387795648</v>
+        <v>65.20320966670685</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -26661,52 +26669,52 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>63.63000106811523</v>
+        <v>63.79999923706055</v>
       </c>
       <c r="E49" t="n">
-        <v>10.48601605536414</v>
+        <v>10.78119788953336</v>
       </c>
       <c r="F49" t="n">
-        <v>-14.80787389445797</v>
+        <v>-14.58026890933473</v>
       </c>
       <c r="G49" t="n">
-        <v>107.3651692213287</v>
+        <v>107.9191798842065</v>
       </c>
       <c r="H49" t="n">
-        <v>143.1874597426621</v>
+        <v>143.8371756341087</v>
       </c>
       <c r="I49" t="n">
-        <v>58.29841689677807</v>
+        <v>58.39092784330057</v>
       </c>
       <c r="J49" t="n">
         <v>66.64832201930004</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6308266097967631</v>
+        <v>0.6329021312589682</v>
       </c>
       <c r="L49" t="n">
-        <v>56.35110680488924</v>
+        <v>56.36729710669356</v>
       </c>
       <c r="M49" t="n">
-        <v>42.34579894454542</v>
+        <v>42.35246553940602</v>
       </c>
       <c r="N49" t="n">
-        <v>31.50604555716289</v>
+        <v>31.50890266924601</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.3869092623024564</v>
+        <v>-0.3760603763070858</v>
       </c>
       <c r="P49" t="n">
-        <v>32.51418787907033</v>
+        <v>32.71312084414287</v>
       </c>
       <c r="Q49" t="n">
-        <v>-67.48581212092968</v>
+        <v>-67.28687915585714</v>
       </c>
       <c r="R49" t="n">
-        <v>32.70314796607369</v>
+        <v>32.91136673516584</v>
       </c>
       <c r="S49" t="n">
-        <v>119.8686934826874</v>
+        <v>120.4561093977122</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -27021,52 +27029,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4396.10009765625</v>
+        <v>4401.2998046875</v>
       </c>
       <c r="E53" t="n">
-        <v>8.569805429133615</v>
+        <v>8.698221790938554</v>
       </c>
       <c r="F53" t="n">
-        <v>-5.411395014963305</v>
+        <v>-5.299515616521255</v>
       </c>
       <c r="G53" t="n">
-        <v>65.45352268183102</v>
+        <v>65.649221102277</v>
       </c>
       <c r="H53" t="n">
-        <v>148.2550246463732</v>
+        <v>148.548660680249</v>
       </c>
       <c r="I53" t="n">
-        <v>63.92274391643522</v>
+        <v>63.99055002414293</v>
       </c>
       <c r="J53" t="n">
         <v>81.22281339030067</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6789146461198236</v>
+        <v>0.6806499909064408</v>
       </c>
       <c r="L53" t="n">
-        <v>3916.608575374672</v>
+        <v>3917.103785568124</v>
       </c>
       <c r="M53" t="n">
-        <v>3128.855804159576</v>
+        <v>3129.059714239233</v>
       </c>
       <c r="N53" t="n">
-        <v>2389.351612154146</v>
+        <v>2389.439002188285</v>
       </c>
       <c r="O53" t="n">
-        <v>-42.96315633061977</v>
+        <v>-42.63132317534951</v>
       </c>
       <c r="P53" t="n">
-        <v>48.75339329459127</v>
+        <v>48.97729659628715</v>
       </c>
       <c r="Q53" t="n">
-        <v>-51.24660670540873</v>
+        <v>-51.02270340371285</v>
       </c>
       <c r="R53" t="n">
-        <v>29.61982872539392</v>
+        <v>29.74116865135854</v>
       </c>
       <c r="S53" t="n">
-        <v>67.20295828762815</v>
+        <v>67.40072594044331</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -27501,52 +27509,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1752.099975585938</v>
+        <v>1757.400024414062</v>
       </c>
       <c r="E58" t="n">
-        <v>6.168570789905781</v>
+        <v>6.489727468770856</v>
       </c>
       <c r="F58" t="n">
-        <v>-10.14871920072116</v>
+        <v>-9.87692182491987</v>
       </c>
       <c r="G58" t="n">
-        <v>84.52869674417455</v>
+        <v>85.08689040695761</v>
       </c>
       <c r="H58" t="n">
-        <v>63.67117941017633</v>
+        <v>64.16627972107077</v>
       </c>
       <c r="I58" t="n">
-        <v>56.90980886950501</v>
+        <v>57.03203756827361</v>
       </c>
       <c r="J58" t="n">
         <v>70.12215192714979</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6153653527854321</v>
+        <v>0.618287900026565</v>
       </c>
       <c r="L58" t="n">
-        <v>1605.232854609847</v>
+        <v>1605.737621164907</v>
       </c>
       <c r="M58" t="n">
-        <v>1326.94336992519</v>
+        <v>1327.151214977273</v>
       </c>
       <c r="N58" t="n">
-        <v>1144.965116535987</v>
+        <v>1145.05419298688</v>
       </c>
       <c r="O58" t="n">
-        <v>-16.3604842523963</v>
+        <v>-16.02224751806557</v>
       </c>
       <c r="P58" t="n">
-        <v>30.19287140950866</v>
+        <v>30.52912626246589</v>
       </c>
       <c r="Q58" t="n">
-        <v>-69.80712859049135</v>
+        <v>-69.47087373753411</v>
       </c>
       <c r="R58" t="n">
-        <v>26.60332500730641</v>
+        <v>26.88423795871399</v>
       </c>
       <c r="S58" t="n">
-        <v>95.98433731386326</v>
+        <v>96.57718393893317</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -28057,52 +28065,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>82.16000366210938</v>
+        <v>82.26999664306641</v>
       </c>
       <c r="E64" t="n">
-        <v>-8.832666269281219</v>
+        <v>-8.710614585298993</v>
       </c>
       <c r="F64" t="n">
-        <v>-30.57878773012842</v>
+        <v>-30.48584900399817</v>
       </c>
       <c r="G64" t="n">
-        <v>12.64052771057924</v>
+        <v>12.79132696650933</v>
       </c>
       <c r="H64" t="n">
-        <v>9.357123207363859</v>
+        <v>9.503526754519619</v>
       </c>
       <c r="I64" t="n">
-        <v>50.90014672211893</v>
+        <v>50.94403116512592</v>
       </c>
       <c r="J64" t="n">
         <v>23.79402312962622</v>
       </c>
       <c r="K64" t="n">
-        <v>0.58953599685405</v>
+        <v>0.5911608400683511</v>
       </c>
       <c r="L64" t="n">
-        <v>80.83506035832559</v>
+        <v>80.84553588032149</v>
       </c>
       <c r="M64" t="n">
-        <v>78.4861372050415</v>
+        <v>78.49045065527511</v>
       </c>
       <c r="N64" t="n">
-        <v>72.2733022201628</v>
+        <v>72.2751508416915</v>
       </c>
       <c r="O64" t="n">
-        <v>1.767403049716411</v>
+        <v>1.774422544797432</v>
       </c>
       <c r="P64" t="n">
-        <v>34.78777589326366</v>
+        <v>34.95101867367421</v>
       </c>
       <c r="Q64" t="n">
-        <v>-65.21222410673634</v>
+        <v>-65.04898132632579</v>
       </c>
       <c r="R64" t="n">
-        <v>36.15461499352307</v>
+        <v>36.35378628190855</v>
       </c>
       <c r="S64" t="n">
-        <v>10.07503260176053</v>
+        <v>10.22239726126812</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -28120,7 +28128,7 @@
         </is>
       </c>
       <c r="W64" t="n">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="X64" t="n">
         <v>86.8</v>
@@ -28249,52 +28257,52 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>157.8309936523438</v>
+        <v>157.7449951171875</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.468323745090971</v>
+        <v>-1.522011424730607</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.257505722964603</v>
+        <v>-1.311308272571587</v>
       </c>
       <c r="G66" t="n">
-        <v>4.403533582529073</v>
+        <v>4.346646460770143</v>
       </c>
       <c r="H66" t="n">
-        <v>42.78824663978105</v>
+        <v>42.71044455690498</v>
       </c>
       <c r="I66" t="n">
-        <v>56.7582463422116</v>
+        <v>56.63540734286958</v>
       </c>
       <c r="J66" t="n">
         <v>26.49181088905198</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6928083908869902</v>
+        <v>0.689523895023894</v>
       </c>
       <c r="L66" t="n">
-        <v>154.7332832395356</v>
+        <v>154.7250929028541</v>
       </c>
       <c r="M66" t="n">
-        <v>146.4621357309101</v>
+        <v>146.4587632393354</v>
       </c>
       <c r="N66" t="n">
-        <v>132.4489117159586</v>
+        <v>132.4476653603766</v>
       </c>
       <c r="O66" t="n">
-        <v>0.2792841797458285</v>
+        <v>0.2737959541404016</v>
       </c>
       <c r="P66" t="n">
-        <v>71.11439935535118</v>
+        <v>70.71034678550228</v>
       </c>
       <c r="Q66" t="n">
-        <v>-28.88560064464881</v>
+        <v>-29.28965321449772</v>
       </c>
       <c r="R66" t="n">
-        <v>57.64302619341528</v>
+        <v>57.2774359371099</v>
       </c>
       <c r="S66" t="n">
-        <v>0.5325001185752631</v>
+        <v>0.4777222353108623</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -28315,7 +28323,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="X66" t="n">
-        <v>66.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -29073,52 +29081,52 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>77.05999755859375</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="E75" t="n">
-        <v>-8.987836039829645</v>
+        <v>-8.964209876024809</v>
       </c>
       <c r="F75" t="n">
-        <v>-23.98895280499161</v>
+        <v>-23.96922083319944</v>
       </c>
       <c r="G75" t="n">
-        <v>13.32352582146139</v>
+        <v>13.35294386919808</v>
       </c>
       <c r="H75" t="n">
-        <v>4.886343103638069</v>
+        <v>4.913570913803533</v>
       </c>
       <c r="I75" t="n">
-        <v>51.13051657993568</v>
+        <v>51.13963046273994</v>
       </c>
       <c r="J75" t="n">
         <v>21.8831417623618</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6045490039766411</v>
+        <v>0.6048958239072868</v>
       </c>
       <c r="L75" t="n">
-        <v>75.35538189969418</v>
+        <v>75.35728706849999</v>
       </c>
       <c r="M75" t="n">
-        <v>73.39979189734588</v>
+        <v>73.40057637861885</v>
       </c>
       <c r="N75" t="n">
-        <v>67.78724040551616</v>
+        <v>67.787576611776</v>
       </c>
       <c r="O75" t="n">
-        <v>1.792317776359991</v>
+        <v>1.793594402294806</v>
       </c>
       <c r="P75" t="n">
-        <v>34.23255303951807</v>
+        <v>34.26356741359223</v>
       </c>
       <c r="Q75" t="n">
-        <v>-65.76744696048193</v>
+        <v>-65.73643258640777</v>
       </c>
       <c r="R75" t="n">
-        <v>37.38068568308518</v>
+        <v>37.41894933369007</v>
       </c>
       <c r="S75" t="n">
-        <v>7.445616629952245</v>
+        <v>7.473508810822937</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -29136,7 +29144,7 @@
         </is>
       </c>
       <c r="W75" t="n">
-        <v>67.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="X75" t="n">
         <v>84.3</v>
@@ -29713,52 +29721,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="E82" t="n">
-        <v>8.26278037247905</v>
+        <v>8.419569337536959</v>
       </c>
       <c r="F82" t="n">
-        <v>-6.131046367968329</v>
+        <v>-5.995102915930628</v>
       </c>
       <c r="G82" t="n">
-        <v>39.46677266968768</v>
+        <v>39.66875206529912</v>
       </c>
       <c r="H82" t="n">
-        <v>-50.27723595602409</v>
+        <v>-50.20522616016027</v>
       </c>
       <c r="I82" t="n">
-        <v>51.99592141663119</v>
+        <v>52.05438789736753</v>
       </c>
       <c r="J82" t="n">
         <v>56.84920134306351</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5891578924412896</v>
+        <v>0.5909607427785891</v>
       </c>
       <c r="L82" t="n">
-        <v>1329.820758117662</v>
+        <v>1330.011234308138</v>
       </c>
       <c r="M82" t="n">
-        <v>1363.044602471379</v>
+        <v>1363.123033843927</v>
       </c>
       <c r="N82" t="n">
-        <v>1361.522618228697</v>
+        <v>1361.556231674075</v>
       </c>
       <c r="O82" t="n">
-        <v>1.325093007781362</v>
+        <v>1.452728335416651</v>
       </c>
       <c r="P82" t="n">
-        <v>27.48414623035082</v>
+        <v>27.6679866733632</v>
       </c>
       <c r="Q82" t="n">
-        <v>-72.51585376964918</v>
+        <v>-72.3320133266368</v>
       </c>
       <c r="R82" t="n">
-        <v>14.88842933003648</v>
+        <v>15.07824309717685</v>
       </c>
       <c r="S82" t="n">
-        <v>52.95159626296397</v>
+        <v>53.17310472967356</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -29805,52 +29813,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.349181652069092</v>
+        <v>1.349272727966309</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2293599715263772</v>
+        <v>0.2361259091396617</v>
       </c>
       <c r="F83" t="n">
-        <v>2.421777956598947</v>
+        <v>2.428691892396717</v>
       </c>
       <c r="G83" t="n">
-        <v>6.261548376241977</v>
+        <v>6.26872151400526</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.535114768280811</v>
+        <v>-2.52853544528453</v>
       </c>
       <c r="I83" t="n">
-        <v>54.83183011258097</v>
+        <v>54.84549599584849</v>
       </c>
       <c r="J83" t="n">
         <v>19.76960125542902</v>
       </c>
       <c r="K83" t="n">
-        <v>0.6320079401983372</v>
+        <v>0.632639314576406</v>
       </c>
       <c r="L83" t="n">
-        <v>1.329525724046725</v>
+        <v>1.329534397941698</v>
       </c>
       <c r="M83" t="n">
-        <v>1.309605071489875</v>
+        <v>1.309608643093688</v>
       </c>
       <c r="N83" t="n">
-        <v>1.337587221957279</v>
+        <v>1.337588541897819</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.001654442994937277</v>
+        <v>-0.001648630743946555</v>
       </c>
       <c r="P83" t="n">
-        <v>57.49483956249768</v>
+        <v>57.60390109090079</v>
       </c>
       <c r="Q83" t="n">
-        <v>-42.50516043750232</v>
+        <v>-42.39609890909922</v>
       </c>
       <c r="R83" t="n">
-        <v>36.2838488630007</v>
+        <v>36.33738516196265</v>
       </c>
       <c r="S83" t="n">
-        <v>7.512235028826497</v>
+        <v>7.519492593626631</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -30373,70 +30381,66 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>99.61699676513672</v>
+        <v>99.60399627685547</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.1833730270791478</v>
+        <v>-0.1963995680447916</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.3431395783087932</v>
+        <v>-0.3561452689853861</v>
       </c>
       <c r="G89" t="n">
-        <v>-5.790619654183649</v>
+        <v>-5.802914422997629</v>
       </c>
       <c r="H89" t="n">
-        <v>7.763948652294395</v>
+        <v>7.749884948337349</v>
       </c>
       <c r="I89" t="n">
-        <v>47.83754034600351</v>
+        <v>47.80887083255893</v>
       </c>
       <c r="J89" t="n">
         <v>28.18418023281943</v>
       </c>
       <c r="K89" t="n">
-        <v>0.4652795483609715</v>
+        <v>0.464305732751713</v>
       </c>
       <c r="L89" t="n">
-        <v>100.1091481996569</v>
+        <v>100.1079100579158</v>
       </c>
       <c r="M89" t="n">
-        <v>100.7381869143481</v>
+        <v>100.7376770912782</v>
       </c>
       <c r="N89" t="n">
-        <v>99.4368876461097</v>
+        <v>99.43666915050832</v>
       </c>
       <c r="O89" t="n">
-        <v>0.1853668190842548</v>
+        <v>0.1845371582936657</v>
       </c>
       <c r="P89" t="n">
-        <v>65.0718994140625</v>
+        <v>64.8638916015625</v>
       </c>
       <c r="Q89" t="n">
-        <v>-34.9281005859375</v>
+        <v>-35.1361083984375</v>
       </c>
       <c r="R89" t="n">
-        <v>-10.50511446639646</v>
+        <v>-10.58979353124496</v>
       </c>
       <c r="S89" t="n">
-        <v>-8.17863514918178</v>
+        <v>-8.190618270701954</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U89" t="inlineStr"/>
       <c r="V89" t="inlineStr">
         <is>
           <t>Double Top</t>
         </is>
       </c>
       <c r="W89" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="X89" t="n">
         <v>59</v>
@@ -30448,7 +30452,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 28); pattern: Double Top; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -31023,52 +31027,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>64920.12890625</v>
+        <v>64981.390625</v>
       </c>
       <c r="E96" t="n">
-        <v>3.353378748269864</v>
+        <v>3.450907907983658</v>
       </c>
       <c r="F96" t="n">
-        <v>-4.855668693719073</v>
+        <v>-4.765885981279306</v>
       </c>
       <c r="G96" t="n">
-        <v>-32.68971985615139</v>
+        <v>-32.62620267710957</v>
       </c>
       <c r="H96" t="n">
-        <v>85.26992056366379</v>
+        <v>85.44475006504688</v>
       </c>
       <c r="I96" t="n">
-        <v>44.33717131528878</v>
+        <v>44.37138703921371</v>
       </c>
       <c r="J96" t="n">
         <v>30.35693503158459</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1955329061074113</v>
+        <v>0.1962520549010159</v>
       </c>
       <c r="L96" t="n">
-        <v>76918.6736854599</v>
+        <v>76924.50813486466</v>
       </c>
       <c r="M96" t="n">
-        <v>65879.33650525085</v>
+        <v>65881.73892559398</v>
       </c>
       <c r="N96" t="n">
-        <v>49914.28040803288</v>
+        <v>49915.51801851268</v>
       </c>
       <c r="O96" t="n">
-        <v>-5644.515005613886</v>
+        <v>-5640.605425841814</v>
       </c>
       <c r="P96" t="n">
-        <v>10.47820504816507</v>
+        <v>10.56770314321327</v>
       </c>
       <c r="Q96" t="n">
-        <v>-89.52179495183492</v>
+        <v>-89.43229685678672</v>
       </c>
       <c r="R96" t="n">
-        <v>-67.18633085636949</v>
+        <v>-67.13552366084913</v>
       </c>
       <c r="S96" t="n">
-        <v>-30.51409330828541</v>
+        <v>-30.44852310464358</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -31299,52 +31303,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.024600028991699</v>
+        <v>1.022300004959106</v>
       </c>
       <c r="E99" t="n">
-        <v>-3.388377246917074</v>
+        <v>-3.605251195650561</v>
       </c>
       <c r="F99" t="n">
-        <v>-23.55208488338469</v>
+        <v>-23.72369530407038</v>
       </c>
       <c r="G99" t="n">
-        <v>-47.29751762719112</v>
+        <v>-47.41582425670982</v>
       </c>
       <c r="H99" t="n">
-        <v>45.05064514024948</v>
+        <v>44.7250351848272</v>
       </c>
       <c r="I99" t="n">
-        <v>40.4698733821733</v>
+        <v>40.43596092142761</v>
       </c>
       <c r="J99" t="n">
         <v>35.88593820922106</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1485862357244083</v>
+        <v>0.1478562775705213</v>
       </c>
       <c r="L99" t="n">
-        <v>1.540805344906972</v>
+        <v>1.540586294999106</v>
       </c>
       <c r="M99" t="n">
-        <v>1.307525941052893</v>
+        <v>1.307435744032007</v>
       </c>
       <c r="N99" t="n">
-        <v>1.037305858702902</v>
+        <v>1.03725939357093</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.1881435197476378</v>
+        <v>-0.1882903019081224</v>
       </c>
       <c r="P99" t="n">
-        <v>0.5622905676892722</v>
+        <v>0.4751835211924212</v>
       </c>
       <c r="Q99" t="n">
-        <v>-99.43770943231073</v>
+        <v>-99.52481647880758</v>
       </c>
       <c r="R99" t="n">
-        <v>-67.70381648239699</v>
+        <v>-67.75244807708307</v>
       </c>
       <c r="S99" t="n">
-        <v>-50.74341331822831</v>
+        <v>-50.85398459475174</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -31571,52 +31575,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>73.86000061035156</v>
+        <v>73.69000244140625</v>
       </c>
       <c r="E102" t="n">
-        <v>1.470428393588774</v>
+        <v>1.236881319577643</v>
       </c>
       <c r="F102" t="n">
-        <v>-11.12604230450394</v>
+        <v>-11.33059700190858</v>
       </c>
       <c r="G102" t="n">
-        <v>-68.9329361943123</v>
+        <v>-69.00444098605114</v>
       </c>
       <c r="H102" t="n">
-        <v>107.7262941832429</v>
+        <v>107.2481857434767</v>
       </c>
       <c r="I102" t="n">
-        <v>40.52872265758026</v>
+        <v>40.48646375499934</v>
       </c>
       <c r="J102" t="n">
         <v>25.2501758559911</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2070763832007775</v>
+        <v>0.206330660943851</v>
       </c>
       <c r="L102" t="n">
-        <v>113.3854289474588</v>
+        <v>113.3692386456545</v>
       </c>
       <c r="M102" t="n">
-        <v>113.2141586072089</v>
+        <v>113.2054407523912</v>
       </c>
       <c r="N102" t="n">
-        <v>92.43400261673062</v>
+        <v>92.42952898070574</v>
       </c>
       <c r="O102" t="n">
-        <v>-11.65307916666502</v>
+        <v>-11.66392805266039</v>
       </c>
       <c r="P102" t="n">
-        <v>6.973868274894588</v>
+        <v>6.885692746947473</v>
       </c>
       <c r="Q102" t="n">
-        <v>-93.02613172510542</v>
+        <v>-93.11430725305253</v>
       </c>
       <c r="R102" t="n">
-        <v>-91.56904896482028</v>
+        <v>-91.64145786567272</v>
       </c>
       <c r="S102" t="n">
-        <v>-68.11402721179672</v>
+        <v>-68.18741682653055</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -31847,52 +31851,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2013500034809113</v>
+        <v>0.2015500068664551</v>
       </c>
       <c r="E105" t="n">
-        <v>19.87688292797478</v>
+        <v>19.995958080791</v>
       </c>
       <c r="F105" t="n">
-        <v>-16.64700411491714</v>
+        <v>-16.56420857936197</v>
       </c>
       <c r="G105" t="n">
-        <v>-81.33819849050158</v>
+        <v>-81.3196614981116</v>
       </c>
       <c r="H105" t="n">
-        <v>-85.44603660501608</v>
+        <v>-85.43157997774141</v>
       </c>
       <c r="I105" t="n">
-        <v>39.31843847439191</v>
+        <v>39.32910154678673</v>
       </c>
       <c r="J105" t="n">
         <v>31.07283787478976</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2200775344620811</v>
+        <v>0.2202518764284006</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3877864627847863</v>
+        <v>0.3878055107262667</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4808443318767792</v>
+        <v>0.4808521751468005</v>
       </c>
       <c r="N105" t="n">
-        <v>0.4720447460399798</v>
+        <v>0.472048786512415</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.04119246436190098</v>
+        <v>-0.04117970061307996</v>
       </c>
       <c r="P105" t="n">
-        <v>7.137983040120815</v>
+        <v>7.160768463968405</v>
       </c>
       <c r="Q105" t="n">
-        <v>-92.86201695987918</v>
+        <v>-92.83923153603159</v>
       </c>
       <c r="R105" t="n">
-        <v>-85.67408338821556</v>
+        <v>-85.65823195988867</v>
       </c>
       <c r="S105" t="n">
-        <v>-76.13672069594664</v>
+        <v>-76.11301701296436</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -31935,52 +31939,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1914.579956054688</v>
+        <v>1912.699951171875</v>
       </c>
       <c r="E106" t="n">
-        <v>2.915264704867226</v>
+        <v>2.814207969394134</v>
       </c>
       <c r="F106" t="n">
-        <v>-9.033475101454203</v>
+        <v>-9.122798877377436</v>
       </c>
       <c r="G106" t="n">
-        <v>-48.33426326289388</v>
+        <v>-48.38499597689348</v>
       </c>
       <c r="H106" t="n">
-        <v>-15.82590094806584</v>
+        <v>-15.90855496140362</v>
       </c>
       <c r="I106" t="n">
-        <v>43.81185272258118</v>
+        <v>43.79101750594824</v>
       </c>
       <c r="J106" t="n">
         <v>14.06284679828849</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2937453291856659</v>
+        <v>0.2932403086473542</v>
       </c>
       <c r="L106" t="n">
-        <v>2451.852016092773</v>
+        <v>2451.672968008696</v>
       </c>
       <c r="M106" t="n">
-        <v>2395.389860933333</v>
+        <v>2395.316135251654</v>
       </c>
       <c r="N106" t="n">
-        <v>1999.871564588556</v>
+        <v>1999.833584691933</v>
       </c>
       <c r="O106" t="n">
-        <v>-163.6156733609554</v>
+        <v>-163.7356508805428</v>
       </c>
       <c r="P106" t="n">
-        <v>11.83775243951907</v>
+        <v>11.78321571221492</v>
       </c>
       <c r="Q106" t="n">
-        <v>-88.16224756048094</v>
+        <v>-88.21678428778507</v>
       </c>
       <c r="R106" t="n">
-        <v>-76.97031044890112</v>
+        <v>-77.02642429333281</v>
       </c>
       <c r="S106" t="n">
-        <v>-42.54878553558412</v>
+        <v>-42.6051992483544</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -31997,7 +32001,7 @@
         <v>34.5</v>
       </c>
       <c r="X106" t="n">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -32027,52 +32031,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8.192999839782715</v>
+        <v>8.194999694824219</v>
       </c>
       <c r="E107" t="n">
-        <v>0.3884788246613757</v>
+        <v>0.4129829634887061</v>
       </c>
       <c r="F107" t="n">
-        <v>-6.659551584688394</v>
+        <v>-6.636767821721234</v>
       </c>
       <c r="G107" t="n">
-        <v>-56.93031721628623</v>
+        <v>-56.91980420225775</v>
       </c>
       <c r="H107" t="n">
-        <v>-57.97866049341594</v>
+        <v>-57.96840337278779</v>
       </c>
       <c r="I107" t="n">
-        <v>41.93507984858807</v>
+        <v>41.93939469550789</v>
       </c>
       <c r="J107" t="n">
         <v>20.61208013114089</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2485688123432393</v>
+        <v>0.2486550725159678</v>
       </c>
       <c r="L107" t="n">
-        <v>11.70350842531297</v>
+        <v>11.70369888769787</v>
       </c>
       <c r="M107" t="n">
-        <v>12.4248253722435</v>
+        <v>12.4249037979314</v>
       </c>
       <c r="N107" t="n">
-        <v>10.78428964159503</v>
+        <v>10.78433004270698</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.8626042452081313</v>
+        <v>-0.8624766191314071</v>
       </c>
       <c r="P107" t="n">
-        <v>5.65154203797076</v>
+        <v>5.66119717796419</v>
       </c>
       <c r="Q107" t="n">
-        <v>-94.34845796202924</v>
+        <v>-94.33880282203582</v>
       </c>
       <c r="R107" t="n">
-        <v>-87.52131908769854</v>
+        <v>-87.51198579958442</v>
       </c>
       <c r="S107" t="n">
-        <v>-59.03779782645762</v>
+        <v>-59.0277992339848</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -32307,52 +32311,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.670000076293945</v>
+        <v>2.671000003814697</v>
       </c>
       <c r="E110" t="n">
-        <v>-2.803054361606261</v>
+        <v>-2.766653650707496</v>
       </c>
       <c r="F110" t="n">
-        <v>-7.420249028365777</v>
+        <v>-7.385577478472261</v>
       </c>
       <c r="G110" t="n">
-        <v>-20.60659699900266</v>
+        <v>-20.57686379811936</v>
       </c>
       <c r="H110" t="n">
-        <v>-26.84931488953382</v>
+        <v>-26.82191961570846</v>
       </c>
       <c r="I110" t="n">
-        <v>45.12570354768854</v>
+        <v>45.13266568708318</v>
       </c>
       <c r="J110" t="n">
         <v>48.09674867775514</v>
       </c>
       <c r="K110" t="n">
-        <v>0.1889634406441408</v>
+        <v>0.1893300715321292</v>
       </c>
       <c r="L110" t="n">
-        <v>3.227266634365697</v>
+        <v>3.227361865558149</v>
       </c>
       <c r="M110" t="n">
-        <v>3.327704980041429</v>
+        <v>3.32774419288538</v>
       </c>
       <c r="N110" t="n">
-        <v>3.299978762450895</v>
+        <v>3.299995567955445</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.09701795036822089</v>
+        <v>-0.09695413732985989</v>
       </c>
       <c r="P110" t="n">
-        <v>3.499252108949258</v>
+        <v>3.517963327172254</v>
       </c>
       <c r="Q110" t="n">
-        <v>-96.50074789105074</v>
+        <v>-96.48203667282775</v>
       </c>
       <c r="R110" t="n">
-        <v>-73.06709319069755</v>
+        <v>-73.03962725057175</v>
       </c>
       <c r="S110" t="n">
-        <v>-26.50701480899016</v>
+        <v>-26.4794913421831</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -32753,12 +32757,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -32767,69 +32771,69 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.8141999840736389</v>
+        <v>6.466000080108643</v>
       </c>
       <c r="E115" t="n">
-        <v>7.406878847793852</v>
+        <v>1.376261158432257</v>
       </c>
       <c r="F115" t="n">
-        <v>-34.94831108592437</v>
+        <v>-27.42422785998162</v>
       </c>
       <c r="G115" t="n">
-        <v>-90.92031168276212</v>
+        <v>-85.59682113858167</v>
       </c>
       <c r="H115" t="n">
-        <v>-95.03603032871546</v>
+        <v>-45.91631900959613</v>
       </c>
       <c r="I115" t="n">
-        <v>34.08254188070559</v>
+        <v>38.69048468663637</v>
       </c>
       <c r="J115" t="n">
-        <v>37.34832998198571</v>
+        <v>17.78710309672154</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2017056582358515</v>
+        <v>0.2053794909081976</v>
       </c>
       <c r="L115" t="n">
-        <v>2.583735794131132</v>
+        <v>14.75123210104521</v>
       </c>
       <c r="M115" t="n">
-        <v>4.181245522644197</v>
+        <v>18.75547956768486</v>
       </c>
       <c r="N115" t="n">
-        <v>6.266098188785008</v>
+        <v>20.45878307599015</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.02121652887085235</v>
+        <v>-0.9760674356453176</v>
       </c>
       <c r="P115" t="n">
-        <v>1.595804795345534</v>
+        <v>2.556317833783572</v>
       </c>
       <c r="Q115" t="n">
-        <v>-98.40419520465447</v>
+        <v>-97.44368216621643</v>
       </c>
       <c r="R115" t="n">
-        <v>-63.12237836381983</v>
+        <v>-68.41662505678295</v>
       </c>
       <c r="S115" t="n">
-        <v>-82.72426894111928</v>
+        <v>-71.093657403973</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Doji, Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="X115" t="n">
-        <v>70.7</v>
+        <v>78.7</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -32838,19 +32842,19 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -32859,69 +32863,69 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.440999984741211</v>
+        <v>0.8133999705314636</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9843007245388113</v>
+        <v>7.301343402839544</v>
       </c>
       <c r="F116" t="n">
-        <v>-27.70483429400365</v>
+        <v>-35.01222932848223</v>
       </c>
       <c r="G116" t="n">
-        <v>-85.65250948387528</v>
+        <v>-90.92923316858207</v>
       </c>
       <c r="H116" t="n">
-        <v>-46.12542775779137</v>
+        <v>-95.04090780726821</v>
       </c>
       <c r="I116" t="n">
-        <v>38.65978879291108</v>
+        <v>34.07659755736076</v>
       </c>
       <c r="J116" t="n">
-        <v>17.78710309672154</v>
+        <v>37.34832998198571</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2047057638203031</v>
+        <v>0.2015951643079891</v>
       </c>
       <c r="L116" t="n">
-        <v>14.74885113958165</v>
+        <v>2.583659602365211</v>
       </c>
       <c r="M116" t="n">
-        <v>18.75412821117851</v>
+        <v>4.181202278668944</v>
       </c>
       <c r="N116" t="n">
-        <v>20.45808862889662</v>
+        <v>6.266075966186614</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.9776628833268841</v>
+        <v>-0.0212675838661367</v>
       </c>
       <c r="P116" t="n">
-        <v>2.473581742127088</v>
+        <v>1.57641465498776</v>
       </c>
       <c r="Q116" t="n">
-        <v>-97.52641825787292</v>
+        <v>-98.42358534501224</v>
       </c>
       <c r="R116" t="n">
-        <v>-68.46663173010623</v>
+        <v>-63.12986099126602</v>
       </c>
       <c r="S116" t="n">
-        <v>-71.20542067534186</v>
+        <v>-82.74124366363024</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>Doji, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W116" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="X116" t="n">
-        <v>79.2</v>
+        <v>70.7</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -32930,7 +32934,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -33280,7 +33284,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07/08/2026 20:41:07</t>
+          <t>07/08/2026 21:39:33</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33320,13 +33324,13 @@
         <v>14.89999961853027</v>
       </c>
       <c r="N2" t="n">
-        <v>99.61699676513672</v>
+        <v>99.60399627685547</v>
       </c>
       <c r="O2" t="n">
-        <v>4396.10009765625</v>
+        <v>4401.2998046875</v>
       </c>
       <c r="P2" t="n">
-        <v>77.05999755859375</v>
+        <v>77.08000183105469</v>
       </c>
       <c r="Q2" t="n">
         <v>4.848132803194405</v>
@@ -33343,7 +33347,7 @@
         <v>4.602283658886883</v>
       </c>
       <c r="U2" t="n">
-        <v>4.268729934468897</v>
+        <v>4.274106379785453</v>
       </c>
       <c r="V2" t="n">
         <v>0.1914504993315261</v>
@@ -33367,10 +33371,10 @@
         <v>0.5875869446908326</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5666800754070127</v>
+        <v>0.5673503445790304</v>
       </c>
       <c r="AD2" t="n">
-        <v>-11.17645969229983</v>
+        <v>-11.07139921214272</v>
       </c>
       <c r="AE2" t="n">
         <v>-3.8779170876588</v>
@@ -33394,7 +33398,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.827945382350551</v>
+        <v>2.828841456569978</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33493,10 +33497,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66.95407684520659</v>
+        <v>66.95454175475568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09296942463084361</v>
+        <v>0.09298802101280722</v>
       </c>
       <c r="D2" t="n">
         <v>68.96551724137932</v>
@@ -33867,43 +33871,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.864</v>
+        <v>0.879</v>
       </c>
       <c r="D17" t="n">
-        <v>0.893</v>
+        <v>0.892</v>
       </c>
       <c r="E17" t="n">
-        <v>0.88</v>
+        <v>0.902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.879</v>
+        <v>0.863</v>
       </c>
       <c r="D18" t="n">
         <v>0.892</v>
       </c>
       <c r="E18" t="n">
-        <v>0.902</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="19">
@@ -34022,13 +34026,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.847</v>
+        <v>-0.85</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.725</v>
+        <v>-0.727</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.659</v>
+        <v>-0.661</v>
       </c>
     </row>
     <row r="3">
@@ -34043,13 +34047,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.886</v>
+        <v>-0.888</v>
       </c>
       <c r="D3" t="n">
         <v>-0.717</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.546</v>
+        <v>-0.547</v>
       </c>
     </row>
     <row r="4">
@@ -34085,7 +34089,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.869</v>
+        <v>-0.87</v>
       </c>
       <c r="D5" t="n">
         <v>-0.697</v>
@@ -34127,10 +34131,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.734</v>
+        <v>-0.735</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.676</v>
+        <v>-0.677</v>
       </c>
       <c r="E7" t="n">
         <v>-0.554</v>
@@ -34202,43 +34206,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.531</v>
+        <v>-0.704</v>
       </c>
       <c r="D11" t="n">
         <v>-0.664</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.652</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.704</v>
+        <v>-0.531</v>
       </c>
       <c r="D12" t="n">
         <v>-0.664</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.49</v>
+        <v>-0.652</v>
       </c>
     </row>
     <row r="13">
@@ -34259,7 +34263,7 @@
         <v>-0.66</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5639999999999999</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="14">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1933,66 +1933,66 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>COPPER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26323.880859375</v>
+        <v>6.635499954223633</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01683789272399761</v>
+        <v>0.9892711093429263</v>
       </c>
       <c r="F17" t="n">
-        <v>1.240592515206007</v>
+        <v>1.865213638274876</v>
       </c>
       <c r="G17" t="n">
-        <v>5.013709303548675</v>
+        <v>6.449024627623734</v>
       </c>
       <c r="H17" t="n">
-        <v>7.636576940416195</v>
+        <v>3.46145050097828</v>
       </c>
       <c r="I17" t="n">
-        <v>70.23316665013105</v>
+        <v>61.33794866335038</v>
       </c>
       <c r="J17" t="n">
-        <v>41.03378071759984</v>
+        <v>24.44975727853035</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8935911163143055</v>
+        <v>0.8431428473399664</v>
       </c>
       <c r="L17" t="n">
-        <v>25661.18336679272</v>
+        <v>6.457529240760283</v>
       </c>
       <c r="M17" t="n">
-        <v>25242.35131995667</v>
+        <v>6.336588286670772</v>
       </c>
       <c r="N17" t="n">
-        <v>24449.11648605994</v>
+        <v>5.872860133427221</v>
       </c>
       <c r="O17" t="n">
-        <v>98.50990381389119</v>
+        <v>0.02745718472059597</v>
       </c>
       <c r="P17" t="n">
-        <v>93.06304857262214</v>
+        <v>80.5057587235039</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.936951427377865</v>
+        <v>-19.49424127649611</v>
       </c>
       <c r="R17" t="n">
-        <v>142.7800102447119</v>
+        <v>85.75661009708607</v>
       </c>
       <c r="S17" t="n">
-        <v>4.816511977761628</v>
+        <v>6.457567229221817</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2001,19 +2001,19 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
+          <t>Bullish Harami</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Inside Bar</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W17" t="n">
         <v>71.3</v>
       </c>
       <c r="X17" t="n">
-        <v>73.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2022,73 +2022,73 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); RSI in forza (70) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (26,445)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (61) — momentum positivo; segnale candlestick: Bullish Harami; vicino alla resistenza dei 20g (6.7280); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COPPER</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>6.634500026702881</v>
+        <v>26323.880859375</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9740526703135188</v>
+        <v>0.01683789272399761</v>
       </c>
       <c r="F18" t="n">
-        <v>1.849863200293278</v>
+        <v>1.240592515206007</v>
       </c>
       <c r="G18" t="n">
-        <v>6.432983438562356</v>
+        <v>5.013709303548675</v>
       </c>
       <c r="H18" t="n">
-        <v>3.445859520282557</v>
+        <v>7.636576940416195</v>
       </c>
       <c r="I18" t="n">
-        <v>61.30017824127069</v>
+        <v>70.23316665013105</v>
       </c>
       <c r="J18" t="n">
-        <v>24.44975727853035</v>
+        <v>41.03378071759984</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8417318370670407</v>
+        <v>0.8935911163143055</v>
       </c>
       <c r="L18" t="n">
-        <v>6.45743400956783</v>
+        <v>25661.18336679272</v>
       </c>
       <c r="M18" t="n">
-        <v>6.336549073826821</v>
+        <v>25242.35131995667</v>
       </c>
       <c r="N18" t="n">
-        <v>5.872850183899652</v>
+        <v>24449.11648605994</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0273933716822346</v>
+        <v>98.50990381389119</v>
       </c>
       <c r="P18" t="n">
-        <v>80.29502592204393</v>
+        <v>93.06304857262214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-19.70497407795606</v>
+        <v>-6.936951427377865</v>
       </c>
       <c r="R18" t="n">
-        <v>85.62898383136557</v>
+        <v>142.7800102447119</v>
       </c>
       <c r="S18" t="n">
-        <v>6.441524752844874</v>
+        <v>4.816511977761628</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2097,19 +2097,19 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>71.2</v>
+        <v>71.3</v>
       </c>
       <c r="X18" t="n">
-        <v>81.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 24); RSI in forza (61) — momentum positivo; segnale candlestick: Bullish Harami; vicino alla resistenza dei 20g (6.7280); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); RSI in forza (70) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (26,445)</t>
         </is>
       </c>
     </row>
@@ -4827,52 +4827,52 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4450.2001953125</v>
+        <v>4448.60009765625</v>
       </c>
       <c r="E48" t="n">
-        <v>2.522634484598796</v>
+        <v>2.485771822257399</v>
       </c>
       <c r="F48" t="n">
-        <v>10.32551377599673</v>
+        <v>10.28584553900291</v>
       </c>
       <c r="G48" t="n">
-        <v>8.433032563067822</v>
+        <v>8.394044779676202</v>
       </c>
       <c r="H48" t="n">
-        <v>-5.690126282375907</v>
+        <v>-5.724035994585208</v>
       </c>
       <c r="I48" t="n">
-        <v>69.71448527114683</v>
+        <v>69.6539301440294</v>
       </c>
       <c r="J48" t="n">
         <v>29.86167817959711</v>
       </c>
       <c r="K48" t="n">
-        <v>1.209451341388755</v>
+        <v>1.20770369812415</v>
       </c>
       <c r="L48" t="n">
-        <v>4159.636155658935</v>
+        <v>4159.483765405959</v>
       </c>
       <c r="M48" t="n">
-        <v>4211.829587144765</v>
+        <v>4211.766838217069</v>
       </c>
       <c r="N48" t="n">
-        <v>4279.465518675841</v>
+        <v>4279.449597306128</v>
       </c>
       <c r="O48" t="n">
-        <v>48.66935724396966</v>
+        <v>48.56724274966757</v>
       </c>
       <c r="P48" t="n">
-        <v>99.17421193360092</v>
+        <v>98.80713278362941</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.8257880663990959</v>
+        <v>-1.192867216370588</v>
       </c>
       <c r="R48" t="n">
-        <v>281.3012866701166</v>
+        <v>280.9532213484588</v>
       </c>
       <c r="S48" t="n">
-        <v>11.33850876438578</v>
+        <v>11.29847629863023</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>62.7</v>
       </c>
       <c r="X48" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -5177,87 +5177,83 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>66.00499725341797</v>
+        <v>1.350803732872009</v>
       </c>
       <c r="E52" t="n">
-        <v>4.220609628755478</v>
+        <v>0.3917376109303872</v>
       </c>
       <c r="F52" t="n">
-        <v>14.4588715608553</v>
+        <v>0.1215716683495849</v>
       </c>
       <c r="G52" t="n">
-        <v>10.35964376853247</v>
+        <v>0.6889118854960907</v>
       </c>
       <c r="H52" t="n">
-        <v>-22.78762732391525</v>
+        <v>-0.1350790406717706</v>
       </c>
       <c r="I52" t="n">
-        <v>64.27400754783923</v>
+        <v>59.43357148183372</v>
       </c>
       <c r="J52" t="n">
-        <v>29.28444435627946</v>
+        <v>14.75121283926878</v>
       </c>
       <c r="K52" t="n">
-        <v>1.187654569624477</v>
+        <v>0.825234373378632</v>
       </c>
       <c r="L52" t="n">
-        <v>60.44932153826879</v>
+        <v>1.341439521763292</v>
       </c>
       <c r="M52" t="n">
-        <v>63.11145241526407</v>
+        <v>1.339548415863195</v>
       </c>
       <c r="N52" t="n">
-        <v>65.16129218999889</v>
+        <v>1.338944080939617</v>
       </c>
       <c r="O52" t="n">
-        <v>1.155120204732956</v>
+        <v>0.001120142102940253</v>
       </c>
       <c r="P52" t="n">
-        <v>97.28528858549781</v>
+        <v>91.45971238383483</v>
       </c>
       <c r="Q52" t="n">
-        <v>-2.714711414502188</v>
+        <v>-8.54028761616518</v>
       </c>
       <c r="R52" t="n">
-        <v>188.7190448407754</v>
+        <v>84.97482429994095</v>
       </c>
       <c r="S52" t="n">
-        <v>14.5244101512489</v>
+        <v>0.9050351166056458</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="inlineStr">
         <is>
-          <t>Breakout 20d, Outside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W52" t="n">
         <v>61.7</v>
       </c>
       <c r="X52" t="n">
-        <v>76.09999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5266,90 +5262,94 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 29); RSI in forza (64) — momentum positivo; breakout massimi 20g — momentum di breve; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (66.25)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 15); pattern: Double Bottom; vicino alla resistenza dei 20g (1.3545); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1.350858449935913</v>
+        <v>65.87999725341797</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3958041832891945</v>
+        <v>4.023237054773299</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1256272970851402</v>
+        <v>14.24210980734479</v>
       </c>
       <c r="G53" t="n">
-        <v>0.6929904955057964</v>
+        <v>10.15064511623189</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1310338080973361</v>
+        <v>-22.9338518066988</v>
       </c>
       <c r="I53" t="n">
-        <v>59.47101624466355</v>
+        <v>64.04696171170841</v>
       </c>
       <c r="J53" t="n">
-        <v>14.75121283926878</v>
+        <v>29.28444435627946</v>
       </c>
       <c r="K53" t="n">
-        <v>0.8268534858734369</v>
+        <v>1.180783091980365</v>
       </c>
       <c r="L53" t="n">
-        <v>1.341444732912235</v>
+        <v>60.43741677636402</v>
       </c>
       <c r="M53" t="n">
-        <v>1.339550561630407</v>
+        <v>63.10655045447976</v>
       </c>
       <c r="N53" t="n">
-        <v>1.338944625388014</v>
+        <v>65.16004840890436</v>
       </c>
       <c r="O53" t="n">
-        <v>0.001123634018129433</v>
+        <v>1.147142996755751</v>
       </c>
       <c r="P53" t="n">
-        <v>91.67277858754282</v>
+        <v>95.90024726842361</v>
       </c>
       <c r="Q53" t="n">
-        <v>-8.327221412457178</v>
+        <v>-4.099752731576389</v>
       </c>
       <c r="R53" t="n">
-        <v>85.12165937353583</v>
+        <v>187.6831352561057</v>
       </c>
       <c r="S53" t="n">
-        <v>0.9091224811282217</v>
+        <v>14.30752428101785</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Breakout 20d, Outside Bar</t>
         </is>
       </c>
       <c r="W53" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="X53" t="n">
-        <v>62.1</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); mercato laterale — ATR basso (ADX 15); pattern: Double Bottom; vicino alla resistenza dei 20g (1.3545); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 29); RSI in forza (64) — momentum positivo; breakout massimi 20g — momentum di breve; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (66.25)</t>
         </is>
       </c>
     </row>
@@ -5755,52 +5755,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.193450003862381</v>
+        <v>0.1926800012588501</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.6185328357348641</v>
+        <v>-1.014107852180157</v>
       </c>
       <c r="F58" t="n">
-        <v>1.139219599905883</v>
+        <v>0.7366480782924345</v>
       </c>
       <c r="G58" t="n">
-        <v>13.93889298509541</v>
+        <v>13.48537402675845</v>
       </c>
       <c r="H58" t="n">
-        <v>17.05300958508165</v>
+        <v>16.58709529026594</v>
       </c>
       <c r="I58" t="n">
-        <v>61.79682405064874</v>
+        <v>60.97962765673175</v>
       </c>
       <c r="J58" t="n">
         <v>35.68018412212253</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7287433686707853</v>
+        <v>0.7175138385967814</v>
       </c>
       <c r="L58" t="n">
-        <v>0.1837652371365727</v>
+        <v>0.183691903555284</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1799290439604028</v>
+        <v>0.1798988477798722</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2558429180483968</v>
+        <v>0.2558352563309487</v>
       </c>
       <c r="O58" t="n">
-        <v>0.002025608264732514</v>
+        <v>0.00197646849744163</v>
       </c>
       <c r="P58" t="n">
-        <v>69.4794801826954</v>
+        <v>68.11986813810189</v>
       </c>
       <c r="Q58" t="n">
-        <v>-30.5205198173046</v>
+        <v>-31.8801318618981</v>
       </c>
       <c r="R58" t="n">
-        <v>89.46485009755646</v>
+        <v>88.17279134964616</v>
       </c>
       <c r="S58" t="n">
-        <v>11.59633211432087</v>
+        <v>11.15213741513825</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="W58" t="n">
-        <v>59.9</v>
+        <v>59.7</v>
       </c>
       <c r="X58" t="n">
-        <v>65.90000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); RSI in forza (62) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 36); RSI in forza (61) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -6031,52 +6031,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1386</v>
+        <v>1388.5</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8660231879407565</v>
+        <v>1.047960459203279</v>
       </c>
       <c r="F61" t="n">
-        <v>10.80022167632622</v>
+        <v>11.00007777603098</v>
       </c>
       <c r="G61" t="n">
-        <v>9.452732097945438</v>
+        <v>9.650157660892678</v>
       </c>
       <c r="H61" t="n">
-        <v>-8.442333512081635</v>
+        <v>-8.277186206006748</v>
       </c>
       <c r="I61" t="n">
-        <v>62.06083660060436</v>
+        <v>62.31101606210636</v>
       </c>
       <c r="J61" t="n">
         <v>16.98340973193296</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9688663202324567</v>
+        <v>0.9787414548229145</v>
       </c>
       <c r="L61" t="n">
-        <v>1308.122883895267</v>
+        <v>1308.360979133362</v>
       </c>
       <c r="M61" t="n">
-        <v>1313.693866758446</v>
+        <v>1313.791905974133</v>
       </c>
       <c r="N61" t="n">
-        <v>1396.212154119669</v>
+        <v>1396.237029741559</v>
       </c>
       <c r="O61" t="n">
-        <v>14.4780127203332</v>
+        <v>14.63755687987722</v>
       </c>
       <c r="P61" t="n">
-        <v>96.25850340136054</v>
+        <v>97.95918367346938</v>
       </c>
       <c r="Q61" t="n">
-        <v>-3.741496598639456</v>
+        <v>-2.040816326530612</v>
       </c>
       <c r="R61" t="n">
-        <v>144.1185157170654</v>
+        <v>145.335047404828</v>
       </c>
       <c r="S61" t="n">
-        <v>11.53134742565911</v>
+        <v>11.73252229475301</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="W61" t="n">
-        <v>57.8</v>
+        <v>57.9</v>
       </c>
       <c r="X61" t="n">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -6219,52 +6219,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1763.800048828125</v>
+        <v>1764.099975585938</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7828166066684572</v>
+        <v>0.7999542994858277</v>
       </c>
       <c r="F63" t="n">
-        <v>9.011127863295743</v>
+        <v>9.029664745731614</v>
       </c>
       <c r="G63" t="n">
-        <v>9.004392524598327</v>
+        <v>9.022928261718267</v>
       </c>
       <c r="H63" t="n">
-        <v>-16.62490906035807</v>
+        <v>-16.61073147785689</v>
       </c>
       <c r="I63" t="n">
-        <v>61.83272514621716</v>
+        <v>61.86102212500258</v>
       </c>
       <c r="J63" t="n">
         <v>23.40748699441878</v>
       </c>
       <c r="K63" t="n">
-        <v>0.9773176144134179</v>
+        <v>0.9782830080907</v>
       </c>
       <c r="L63" t="n">
-        <v>1675.219076685764</v>
+        <v>1675.247641138889</v>
       </c>
       <c r="M63" t="n">
-        <v>1713.029687480444</v>
+        <v>1713.041449314084</v>
       </c>
       <c r="N63" t="n">
-        <v>1784.514120361177</v>
+        <v>1784.517104707026</v>
       </c>
       <c r="O63" t="n">
-        <v>21.81209493450411</v>
+        <v>21.83123555950411</v>
       </c>
       <c r="P63" t="n">
-        <v>92.44281568554588</v>
+        <v>92.60243607875645</v>
       </c>
       <c r="Q63" t="n">
-        <v>-7.557184314454124</v>
+        <v>-7.397563921243544</v>
       </c>
       <c r="R63" t="n">
-        <v>183.5668769360632</v>
+        <v>183.708194641704</v>
       </c>
       <c r="S63" t="n">
-        <v>10.08613797160918</v>
+        <v>10.10485765497908</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6311,52 +6311,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>82.33999633789062</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E64" t="n">
-        <v>5.321048882676238</v>
+        <v>5.269893490022493</v>
       </c>
       <c r="F64" t="n">
-        <v>2.489420078622473</v>
+        <v>2.439640033867896</v>
       </c>
       <c r="G64" t="n">
-        <v>15.30596851317734</v>
+        <v>15.24996335412141</v>
       </c>
       <c r="H64" t="n">
-        <v>-16.03956704994643</v>
+        <v>-16.0803473968999</v>
       </c>
       <c r="I64" t="n">
-        <v>52.77370816412802</v>
+        <v>52.72163850819427</v>
       </c>
       <c r="J64" t="n">
         <v>36.18276506733786</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5178378684956672</v>
+        <v>0.5156591733604313</v>
       </c>
       <c r="L64" t="n">
-        <v>80.31146609532972</v>
+        <v>80.30765721093611</v>
       </c>
       <c r="M64" t="n">
-        <v>81.86211203067521</v>
+        <v>81.86054366651314</v>
       </c>
       <c r="N64" t="n">
-        <v>79.08032451166976</v>
+        <v>79.07992656852416</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.3890130318283616</v>
+        <v>-0.3915653099177495</v>
       </c>
       <c r="P64" t="n">
-        <v>42.05606217916241</v>
+        <v>41.84841274148358</v>
       </c>
       <c r="Q64" t="n">
-        <v>-57.94393782083759</v>
+        <v>-58.15158725851642</v>
       </c>
       <c r="R64" t="n">
-        <v>-11.29420252534594</v>
+        <v>-11.42601655869958</v>
       </c>
       <c r="S64" t="n">
-        <v>5.374964142626526</v>
+        <v>5.323782562839985</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6364,16 +6364,12 @@
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Bear Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="X64" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -6382,7 +6378,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); pattern: Bear Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 36); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -6403,52 +6399,52 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>87.87999725341797</v>
+        <v>87.84999847412109</v>
       </c>
       <c r="E65" t="n">
-        <v>5.182518304610717</v>
+        <v>5.14661312423832</v>
       </c>
       <c r="F65" t="n">
-        <v>4.906291960191633</v>
+        <v>4.870481072643562</v>
       </c>
       <c r="G65" t="n">
-        <v>15.61635940479684</v>
+        <v>15.57689252089503</v>
       </c>
       <c r="H65" t="n">
-        <v>-15.67028305778756</v>
+        <v>-15.69906991083469</v>
       </c>
       <c r="I65" t="n">
-        <v>52.97616909521314</v>
+        <v>52.94329187828763</v>
       </c>
       <c r="J65" t="n">
         <v>36.75611276627295</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5114527082952891</v>
+        <v>0.5101420235467256</v>
       </c>
       <c r="L65" t="n">
-        <v>85.43698864288699</v>
+        <v>85.43413161628729</v>
       </c>
       <c r="M65" t="n">
-        <v>86.75062146075396</v>
+        <v>86.74944503803644</v>
       </c>
       <c r="N65" t="n">
-        <v>83.8127822815617</v>
+        <v>83.81248378624531</v>
       </c>
       <c r="O65" t="n">
-        <v>-0.5194143776824776</v>
+        <v>-0.5213288296945793</v>
       </c>
       <c r="P65" t="n">
-        <v>40.8291373801917</v>
+        <v>40.70351437699681</v>
       </c>
       <c r="Q65" t="n">
-        <v>-59.1708626198083</v>
+        <v>-59.29648562300319</v>
       </c>
       <c r="R65" t="n">
-        <v>-9.709260557949857</v>
+        <v>-9.79039193601761</v>
       </c>
       <c r="S65" t="n">
-        <v>5.498192117489364</v>
+        <v>5.462179178476356</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7025,52 +7021,52 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>76.33000183105469</v>
+        <v>76.36000061035156</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1546658636722098</v>
+        <v>0.1940280757083856</v>
       </c>
       <c r="F72" t="n">
-        <v>3.202511670300767</v>
+        <v>3.243071729205704</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.879262190303155</v>
+        <v>-1.840699340998964</v>
       </c>
       <c r="H72" t="n">
-        <v>17.49935728851268</v>
+        <v>17.54553621163946</v>
       </c>
       <c r="I72" t="n">
-        <v>55.47595233189941</v>
+        <v>55.56940262101482</v>
       </c>
       <c r="J72" t="n">
         <v>18.54045115859727</v>
       </c>
       <c r="K72" t="n">
-        <v>0.8069924822477651</v>
+        <v>0.8112016751816603</v>
       </c>
       <c r="L72" t="n">
-        <v>74.76398707186431</v>
+        <v>74.76684409846402</v>
       </c>
       <c r="M72" t="n">
-        <v>75.41201742270405</v>
+        <v>75.41319384542159</v>
       </c>
       <c r="N72" t="n">
-        <v>90.20778819500798</v>
+        <v>90.20808669032436</v>
       </c>
       <c r="O72" t="n">
-        <v>0.3469032780480773</v>
+        <v>0.3488177300601904</v>
       </c>
       <c r="P72" t="n">
-        <v>81.4094630590678</v>
+        <v>81.842798118982</v>
       </c>
       <c r="Q72" t="n">
-        <v>-18.5905369409322</v>
+        <v>-18.15720188101801</v>
       </c>
       <c r="R72" t="n">
-        <v>68.35714613066493</v>
+        <v>68.69310946888353</v>
       </c>
       <c r="S72" t="n">
-        <v>-2.277089205537375</v>
+        <v>-2.238682707923767</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7087,7 +7083,7 @@
         <v>53.3</v>
       </c>
       <c r="X72" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -7475,66 +7471,66 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>EMERGING</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>MSCI Emerging ETF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>8.284000396728516</v>
+        <v>65.16999816894531</v>
       </c>
       <c r="E77" t="n">
-        <v>1.283202928238025</v>
+        <v>-0.716028679270897</v>
       </c>
       <c r="F77" t="n">
-        <v>1.65118740641792</v>
+        <v>1.321515046881272</v>
       </c>
       <c r="G77" t="n">
-        <v>-3.488936020007061</v>
+        <v>-2.585954136734026</v>
       </c>
       <c r="H77" t="n">
-        <v>5.703166554571681</v>
+        <v>-4.006482906402642</v>
       </c>
       <c r="I77" t="n">
-        <v>51.30666146754172</v>
+        <v>50.56130510980558</v>
       </c>
       <c r="J77" t="n">
-        <v>10.93930039873569</v>
+        <v>30.29610338339609</v>
       </c>
       <c r="K77" t="n">
-        <v>0.4539603705372157</v>
+        <v>0.6596932484089787</v>
       </c>
       <c r="L77" t="n">
-        <v>8.249900235195604</v>
+        <v>64.86061069906778</v>
       </c>
       <c r="M77" t="n">
-        <v>8.245603037514739</v>
+        <v>65.22136509811855</v>
       </c>
       <c r="N77" t="n">
-        <v>9.564550401594289</v>
+        <v>60.90116822497977</v>
       </c>
       <c r="O77" t="n">
-        <v>-0.02068678923784134</v>
+        <v>0.3136998832564111</v>
       </c>
       <c r="P77" t="n">
-        <v>62.33311943102502</v>
+        <v>80.4387531582849</v>
       </c>
       <c r="Q77" t="n">
-        <v>-37.66688056897498</v>
+        <v>-19.56124684171509</v>
       </c>
       <c r="R77" t="n">
-        <v>-20.69599756511646</v>
+        <v>33.03988097157313</v>
       </c>
       <c r="S77" t="n">
-        <v>-4.208223946918432</v>
+        <v>1.038756851077993</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7543,19 +7539,15 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="X77" t="n">
-        <v>53.4</v>
+        <v>52.3</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7564,90 +7556,90 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 11); pattern: Double Top; segnale candlestick: Bullish Harami</t>
+          <t>trend molto direzionale (ADX 30); doji — indecisione del mercato; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>EMERGING</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MSCI Emerging ETF</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>65.16999816894531</v>
+        <v>8.300999641418457</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.716028679270897</v>
+        <v>1.491041878878097</v>
       </c>
       <c r="F78" t="n">
-        <v>1.321515046881272</v>
+        <v>1.859781482346157</v>
       </c>
       <c r="G78" t="n">
-        <v>-2.585954136734026</v>
+        <v>-3.290889772625127</v>
       </c>
       <c r="H78" t="n">
-        <v>-4.006482906402642</v>
+        <v>5.920075524478596</v>
       </c>
       <c r="I78" t="n">
-        <v>50.56130510980558</v>
+        <v>51.75203254073033</v>
       </c>
       <c r="J78" t="n">
-        <v>30.29610338339609</v>
+        <v>10.93930039873569</v>
       </c>
       <c r="K78" t="n">
-        <v>0.6596932484089787</v>
+        <v>0.4761196334933379</v>
       </c>
       <c r="L78" t="n">
-        <v>64.86061069906778</v>
+        <v>8.25151921088036</v>
       </c>
       <c r="M78" t="n">
-        <v>65.22136509811855</v>
+        <v>8.246269674561404</v>
       </c>
       <c r="N78" t="n">
-        <v>60.90116822497977</v>
+        <v>9.564719548307622</v>
       </c>
       <c r="O78" t="n">
-        <v>0.3136998832564111</v>
+        <v>-0.01960193715506349</v>
       </c>
       <c r="P78" t="n">
-        <v>80.4387531582849</v>
+        <v>65.09269143030978</v>
       </c>
       <c r="Q78" t="n">
-        <v>-19.56124684171509</v>
+        <v>-34.90730856969022</v>
       </c>
       <c r="R78" t="n">
-        <v>33.03988097157313</v>
+        <v>-18.81025390169438</v>
       </c>
       <c r="S78" t="n">
-        <v>1.038756851077993</v>
+        <v>-4.01165371968214</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Double Top</t>
+        </is>
+      </c>
       <c r="W78" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="X78" t="n">
-        <v>52.3</v>
+        <v>56.4</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7656,7 +7648,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 30); doji — indecisione del mercato; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 11); pattern: Double Top</t>
         </is>
       </c>
     </row>
@@ -8049,52 +8041,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>99.82099914550781</v>
+        <v>99.80699920654297</v>
       </c>
       <c r="E83" t="n">
-        <v>0.2218882276831868</v>
+        <v>0.2078320638485343</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.1390555624629197</v>
+        <v>-0.1530611037725116</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.137963812324605</v>
+        <v>-1.151829256313497</v>
       </c>
       <c r="H83" t="n">
-        <v>1.920560197276777</v>
+        <v>1.906265793952455</v>
       </c>
       <c r="I83" t="n">
-        <v>40.35320455941665</v>
+        <v>40.10428151676784</v>
       </c>
       <c r="J83" t="n">
         <v>31.50273904683265</v>
       </c>
       <c r="K83" t="n">
-        <v>0.2185442140008116</v>
+        <v>0.2139553295771063</v>
       </c>
       <c r="L83" t="n">
-        <v>100.3675916115695</v>
+        <v>100.3662582840491</v>
       </c>
       <c r="M83" t="n">
-        <v>100.3025312402845</v>
+        <v>100.3019822230702</v>
       </c>
       <c r="N83" t="n">
-        <v>99.61997731151368</v>
+        <v>99.6198380086384</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.1576662606267803</v>
+        <v>-0.1585597040251117</v>
       </c>
       <c r="P83" t="n">
-        <v>18.7945545144601</v>
+        <v>18.16955664319945</v>
       </c>
       <c r="Q83" t="n">
-        <v>-81.2054454855399</v>
+        <v>-81.83044335680056</v>
       </c>
       <c r="R83" t="n">
-        <v>-112.6235208657086</v>
+        <v>-113.165771785895</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.44056047726504</v>
+        <v>-1.454383481938792</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8315,66 +8307,66 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>PST</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>Poste Italiane</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1878.260009765625</v>
+        <v>26.8700008392334</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.593912328458391</v>
+        <v>-1.430665393888131</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.482591435755876</v>
+        <v>0.5990331720144404</v>
       </c>
       <c r="G86" t="n">
-        <v>-1.339397610594228</v>
+        <v>-6.474064506226407</v>
       </c>
       <c r="H86" t="n">
-        <v>14.68842680205034</v>
+        <v>11.9117058854137</v>
       </c>
       <c r="I86" t="n">
-        <v>50.68552701471896</v>
+        <v>43.7706306752854</v>
       </c>
       <c r="J86" t="n">
-        <v>14.34743001288129</v>
+        <v>58.89907669844546</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3668247391759451</v>
+        <v>0.3825090447922988</v>
       </c>
       <c r="L86" t="n">
-        <v>1883.819783612215</v>
+        <v>27.21875946133878</v>
       </c>
       <c r="M86" t="n">
-        <v>1861.251929532273</v>
+        <v>26.95709665664276</v>
       </c>
       <c r="N86" t="n">
-        <v>2142.130607005329</v>
+        <v>23.81376780306037</v>
       </c>
       <c r="O86" t="n">
-        <v>-4.272157813164803</v>
+        <v>0.01021670802146765</v>
       </c>
       <c r="P86" t="n">
-        <v>49.07862816212092</v>
+        <v>51.30898051708126</v>
       </c>
       <c r="Q86" t="n">
-        <v>-50.92137183787908</v>
+        <v>-48.69101948291874</v>
       </c>
       <c r="R86" t="n">
-        <v>-5.765665492107298</v>
+        <v>-21.69594070340735</v>
       </c>
       <c r="S86" t="n">
-        <v>-2.599263672572305</v>
+        <v>-6.376306184873515</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8391,7 +8383,7 @@
         <v>47.5</v>
       </c>
       <c r="X86" t="n">
-        <v>61.2</v>
+        <v>58.3</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -8400,73 +8392,73 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 14); pattern: Double Top</t>
+          <t>trend molto direzionale (ADX 59); pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PST</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Poste Italiane</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>26.8700008392334</v>
+        <v>1874.31005859375</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.430665393888131</v>
+        <v>-1.800858778522207</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5990331720144404</v>
+        <v>-1.689771991901023</v>
       </c>
       <c r="G87" t="n">
-        <v>-6.474064506226407</v>
+        <v>-1.546879301094872</v>
       </c>
       <c r="H87" t="n">
-        <v>11.9117058854137</v>
+        <v>14.44723884964125</v>
       </c>
       <c r="I87" t="n">
-        <v>43.7706306752854</v>
+        <v>50.12259427364712</v>
       </c>
       <c r="J87" t="n">
-        <v>58.89907669844546</v>
+        <v>14.34743001288129</v>
       </c>
       <c r="K87" t="n">
-        <v>0.3825090447922988</v>
+        <v>0.3348674279544128</v>
       </c>
       <c r="L87" t="n">
-        <v>27.21875946133878</v>
+        <v>1883.443597786322</v>
       </c>
       <c r="M87" t="n">
-        <v>26.95709665664276</v>
+        <v>1861.097029486317</v>
       </c>
       <c r="N87" t="n">
-        <v>23.81376780306037</v>
+        <v>2142.091304008594</v>
       </c>
       <c r="O87" t="n">
-        <v>0.01021670802146765</v>
+        <v>-4.524234469147803</v>
       </c>
       <c r="P87" t="n">
-        <v>51.30898051708126</v>
+        <v>45.66412321679753</v>
       </c>
       <c r="Q87" t="n">
-        <v>-48.69101948291874</v>
+        <v>-54.33587678320247</v>
       </c>
       <c r="R87" t="n">
-        <v>-21.69594070340735</v>
+        <v>-8.191487246540399</v>
       </c>
       <c r="S87" t="n">
-        <v>-6.376306184873515</v>
+        <v>-2.804095884618407</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8480,10 +8472,10 @@
         </is>
       </c>
       <c r="W87" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="X87" t="n">
-        <v>58.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -8492,7 +8484,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 59); pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 14); pattern: Double Top</t>
         </is>
       </c>
     </row>
@@ -8513,52 +8505,52 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>159.302001953125</v>
+        <v>159.2319946289062</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5637339989280843</v>
+        <v>0.5195399659316813</v>
       </c>
       <c r="F88" t="n">
-        <v>1.091495991108604</v>
+        <v>1.047070026281816</v>
       </c>
       <c r="G88" t="n">
-        <v>-1.885284525660247</v>
+        <v>-1.928402305805055</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9192238550253196</v>
+        <v>0.8748735974158484</v>
       </c>
       <c r="I88" t="n">
-        <v>40.34387729779904</v>
+        <v>39.83138461641207</v>
       </c>
       <c r="J88" t="n">
         <v>44.96335154892356</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2873317435977492</v>
+        <v>0.2807162690911035</v>
       </c>
       <c r="L88" t="n">
-        <v>160.5258644392312</v>
+        <v>160.5191970750199</v>
       </c>
       <c r="M88" t="n">
-        <v>160.771811660742</v>
+        <v>160.7690662754785</v>
       </c>
       <c r="N88" t="n">
-        <v>157.7921063557077</v>
+        <v>157.791409765417</v>
       </c>
       <c r="O88" t="n">
-        <v>-0.5189218293061086</v>
+        <v>-0.5233895331878641</v>
       </c>
       <c r="P88" t="n">
-        <v>46.3831469499065</v>
+        <v>45.58058743578037</v>
       </c>
       <c r="Q88" t="n">
-        <v>-53.6168530500935</v>
+        <v>-54.41941256421963</v>
       </c>
       <c r="R88" t="n">
-        <v>-89.01895982052211</v>
+        <v>-89.77724429810786</v>
       </c>
       <c r="S88" t="n">
-        <v>-1.591324289363671</v>
+        <v>-1.634571254134642</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -8576,7 +8568,7 @@
         </is>
       </c>
       <c r="W88" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="X88" t="n">
         <v>56.6</v>
@@ -9411,87 +9403,79 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>64089.75</v>
+        <v>18.07999992370605</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.164527778458824</v>
+        <v>-1.202182090308268</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.7860211308487131</v>
+        <v>0.5002787867311786</v>
       </c>
       <c r="G98" t="n">
-        <v>-1.748086564092566</v>
+        <v>-6.07792247425426</v>
       </c>
       <c r="H98" t="n">
-        <v>3.967908360585848</v>
+        <v>-16.79705336134874</v>
       </c>
       <c r="I98" t="n">
-        <v>49.38098458569804</v>
+        <v>44.63823861314415</v>
       </c>
       <c r="J98" t="n">
-        <v>8.519186858395495</v>
+        <v>46.59975205283782</v>
       </c>
       <c r="K98" t="n">
-        <v>0.4470756125998775</v>
+        <v>0.4827933053897912</v>
       </c>
       <c r="L98" t="n">
-        <v>64225.77964624496</v>
+        <v>18.30361554335708</v>
       </c>
       <c r="M98" t="n">
-        <v>64606.30744443932</v>
+        <v>19.1245912837036</v>
       </c>
       <c r="N98" t="n">
-        <v>72184.33288668036</v>
+        <v>18.47125365616803</v>
       </c>
       <c r="O98" t="n">
-        <v>43.80343063838468</v>
+        <v>0.1435848706376834</v>
       </c>
       <c r="P98" t="n">
-        <v>58.68048507127575</v>
+        <v>66.8367386658674</v>
       </c>
       <c r="Q98" t="n">
-        <v>-41.31951492872425</v>
+        <v>-33.16326133413261</v>
       </c>
       <c r="R98" t="n">
-        <v>8.076453659769733</v>
+        <v>0.1476656406179367</v>
       </c>
       <c r="S98" t="n">
-        <v>-3.631862957929932</v>
+        <v>-2.952223627678974</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>Double Top, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="n">
         <v>40.8</v>
       </c>
       <c r="X98" t="n">
-        <v>71.7</v>
+        <v>66.3</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -9500,86 +9484,94 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 9); pattern: Double Top; evening star — inversione ribassista a 3 candele; in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 47); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>18.07999992370605</v>
+        <v>63987</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.202182090308268</v>
+        <v>-1.322982832047948</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5002787867311786</v>
+        <v>-0.9450830140485311</v>
       </c>
       <c r="G99" t="n">
-        <v>-6.07792247425426</v>
+        <v>-1.90560604428307</v>
       </c>
       <c r="H99" t="n">
-        <v>-16.79705336134874</v>
+        <v>3.801224880246945</v>
       </c>
       <c r="I99" t="n">
-        <v>44.63823861314415</v>
+        <v>48.78482302930971</v>
       </c>
       <c r="J99" t="n">
-        <v>46.59975205283782</v>
+        <v>8.519186858395495</v>
       </c>
       <c r="K99" t="n">
-        <v>0.4827933053897912</v>
+        <v>0.4175831793489211</v>
       </c>
       <c r="L99" t="n">
-        <v>18.30361554335708</v>
+        <v>64215.99393195924</v>
       </c>
       <c r="M99" t="n">
-        <v>19.1245912837036</v>
+        <v>64602.27803267461</v>
       </c>
       <c r="N99" t="n">
-        <v>18.47125365616803</v>
+        <v>72183.31049862067</v>
       </c>
       <c r="O99" t="n">
-        <v>0.1435848706376834</v>
+        <v>37.24616568112783</v>
       </c>
       <c r="P99" t="n">
-        <v>66.8367386658674</v>
+        <v>55.44438006025868</v>
       </c>
       <c r="Q99" t="n">
-        <v>-33.16326133413261</v>
+        <v>-44.55561993974133</v>
       </c>
       <c r="R99" t="n">
-        <v>0.1476656406179367</v>
+        <v>4.735493354792358</v>
       </c>
       <c r="S99" t="n">
-        <v>-2.952223627678974</v>
+        <v>-3.786362329218984</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
+          <t>Trend Bearish</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Double Top, Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W99" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="X99" t="n">
-        <v>66.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -9588,199 +9580,199 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); mercato laterale — ATR basso (ADX 9); pattern: Double Top; evening star — inversione ribassista a 3 candele; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>469.5599975585938</v>
+        <v>0.8098999857902527</v>
       </c>
       <c r="E100" t="n">
-        <v>-2.855012456798967</v>
+        <v>1.471136787313809</v>
       </c>
       <c r="F100" t="n">
-        <v>-3.111591415080106</v>
+        <v>-3.801267672123643</v>
       </c>
       <c r="G100" t="n">
-        <v>-15.8328729266657</v>
+        <v>-1.966009115345679</v>
       </c>
       <c r="H100" t="n">
-        <v>2.347476800514792</v>
+        <v>-15.44093088572633</v>
       </c>
       <c r="I100" t="n">
-        <v>44.68172159918535</v>
+        <v>47.50928247822632</v>
       </c>
       <c r="J100" t="n">
-        <v>15.04708530159436</v>
+        <v>18.98200701068858</v>
       </c>
       <c r="K100" t="n">
-        <v>0.263970198372337</v>
+        <v>0.5563016323327816</v>
       </c>
       <c r="L100" t="n">
-        <v>496.0338688703811</v>
+        <v>0.8133074331712139</v>
       </c>
       <c r="M100" t="n">
-        <v>486.4966178313173</v>
+        <v>0.8597938674138964</v>
       </c>
       <c r="N100" t="n">
-        <v>352.8105362161292</v>
+        <v>1.319257391057636</v>
       </c>
       <c r="O100" t="n">
-        <v>-2.769676351312202</v>
+        <v>0.004769669184591225</v>
       </c>
       <c r="P100" t="n">
-        <v>33.12718864969681</v>
+        <v>51.87509012320062</v>
       </c>
       <c r="Q100" t="n">
-        <v>-66.87281135030319</v>
+        <v>-48.12490987679939</v>
       </c>
       <c r="R100" t="n">
-        <v>-68.57879389671669</v>
+        <v>9.806212577780512</v>
       </c>
       <c r="S100" t="n">
-        <v>-12.13159215418609</v>
+        <v>-4.246317132705846</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
+          <t>Trend Bearish</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Outside Bar, Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W100" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="X100" t="n">
-        <v>61.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Bull Flag / Consolidation; segnale candlestick: Bullish Harami</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INW</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>INWIT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6.385000228881836</v>
+        <v>469.5599975585938</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.8540345939431759</v>
+        <v>-2.855012456798967</v>
       </c>
       <c r="F101" t="n">
-        <v>-2.444611849457889</v>
+        <v>-3.111591415080106</v>
       </c>
       <c r="G101" t="n">
-        <v>-1.693605213478422</v>
+        <v>-15.8328729266657</v>
       </c>
       <c r="H101" t="n">
-        <v>-10.13370567570443</v>
+        <v>2.347476800514792</v>
       </c>
       <c r="I101" t="n">
-        <v>48.61699378978204</v>
+        <v>44.68172159918535</v>
       </c>
       <c r="J101" t="n">
-        <v>19.05416294785229</v>
+        <v>15.04708530159436</v>
       </c>
       <c r="K101" t="n">
-        <v>0.5228518950312435</v>
+        <v>0.263970198372337</v>
       </c>
       <c r="L101" t="n">
-        <v>6.407237497380374</v>
+        <v>496.0338688703811</v>
       </c>
       <c r="M101" t="n">
-        <v>6.517390689111981</v>
+        <v>486.4966178313173</v>
       </c>
       <c r="N101" t="n">
-        <v>7.485805474105879</v>
+        <v>352.8105362161292</v>
       </c>
       <c r="O101" t="n">
-        <v>0.01177010159105375</v>
+        <v>-2.769676351312202</v>
       </c>
       <c r="P101" t="n">
-        <v>62.99216559997777</v>
+        <v>33.12718864969681</v>
       </c>
       <c r="Q101" t="n">
-        <v>-37.00783440002223</v>
+        <v>-66.87281135030319</v>
       </c>
       <c r="R101" t="n">
-        <v>25.06896399554066</v>
+        <v>-68.57879389671669</v>
       </c>
       <c r="S101" t="n">
-        <v>-0.7769963378757683</v>
+        <v>-12.13159215418609</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="n">
-        <v>37.9</v>
+        <v>38.9</v>
       </c>
       <c r="X101" t="n">
-        <v>64.3</v>
+        <v>61.3</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
           <t>SELL</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; in zona Fib Fib 78.6 — livello strutturale</t>
-        </is>
-      </c>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IVG</t>
+          <t>INW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Iveco Group</t>
+          <t>INWIT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9789,69 +9781,73 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>13.90999984741211</v>
+        <v>6.385000228881836</v>
       </c>
       <c r="E102" t="n">
-        <v>0.1439849070915988</v>
+        <v>-0.8540345939431759</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1439849070915988</v>
+        <v>-2.444611849457889</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.3581675544286012</v>
+        <v>-1.693605213478422</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.1435783009727576</v>
+        <v>-10.13370567570443</v>
       </c>
       <c r="I102" t="n">
-        <v>43.18427653945757</v>
+        <v>48.61699378978204</v>
       </c>
       <c r="J102" t="n">
-        <v>39.31002588049616</v>
+        <v>19.05416294785229</v>
       </c>
       <c r="K102" t="n">
-        <v>0.366756131003225</v>
+        <v>0.5228518950312435</v>
       </c>
       <c r="L102" t="n">
-        <v>13.9166741307842</v>
+        <v>6.407237497380374</v>
       </c>
       <c r="M102" t="n">
-        <v>14.14284667015572</v>
+        <v>6.517390689111981</v>
       </c>
       <c r="N102" t="n">
-        <v>15.80007768991262</v>
+        <v>7.485805474105879</v>
       </c>
       <c r="O102" t="n">
-        <v>0.001984858888358327</v>
+        <v>0.01177010159105375</v>
       </c>
       <c r="P102" t="n">
-        <v>58.3331346509946</v>
+        <v>62.99216559997777</v>
       </c>
       <c r="Q102" t="n">
-        <v>-41.6668653490054</v>
+        <v>-37.00783440002223</v>
       </c>
       <c r="R102" t="n">
-        <v>-64.46052998557063</v>
+        <v>25.06896399554066</v>
       </c>
       <c r="S102" t="n">
-        <v>-0.3581675544286012</v>
+        <v>-0.7769963378757683</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Bottom</t>
         </is>
       </c>
       <c r="W102" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="X102" t="n">
-        <v>64.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -9860,19 +9856,19 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 39); pattern: Double Bottom; sul supporto dei 20g (13.84); vicino alla resistenza dei 20g (13.97)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IG_IT</t>
+          <t>IVG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Italgas</t>
+          <t>Iveco Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9881,65 +9877,69 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8.802000045776367</v>
+        <v>13.90999984741211</v>
       </c>
       <c r="E103" t="n">
-        <v>-1.344988640244482</v>
+        <v>0.1439849070915988</v>
       </c>
       <c r="F103" t="n">
-        <v>-2.675803128461007</v>
+        <v>0.1439849070915988</v>
       </c>
       <c r="G103" t="n">
-        <v>-11.44868795420061</v>
+        <v>-0.3581675544286012</v>
       </c>
       <c r="H103" t="n">
-        <v>-14.54369045843309</v>
+        <v>-0.1435783009727576</v>
       </c>
       <c r="I103" t="n">
-        <v>23.81347145094797</v>
+        <v>43.18427653945757</v>
       </c>
       <c r="J103" t="n">
-        <v>34.81626615742476</v>
+        <v>39.31002588049616</v>
       </c>
       <c r="K103" t="n">
-        <v>0.08552434239305773</v>
+        <v>0.366756131003225</v>
       </c>
       <c r="L103" t="n">
-        <v>9.484746537148963</v>
+        <v>13.9166741307842</v>
       </c>
       <c r="M103" t="n">
-        <v>9.85166361379957</v>
+        <v>14.14284667015572</v>
       </c>
       <c r="N103" t="n">
-        <v>9.640357250596107</v>
+        <v>15.80007768991262</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.08418613205409042</v>
+        <v>0.001984858888358327</v>
       </c>
       <c r="P103" t="n">
-        <v>4.971569261613593</v>
+        <v>58.3331346509946</v>
       </c>
       <c r="Q103" t="n">
-        <v>-95.0284307383864</v>
+        <v>-41.6668653490054</v>
       </c>
       <c r="R103" t="n">
-        <v>-139.5653298407796</v>
+        <v>-64.46052998557063</v>
       </c>
       <c r="S103" t="n">
-        <v>-11.2880456894776</v>
+        <v>-0.3581675544286012</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bearish</t>
         </is>
       </c>
       <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W103" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="X103" t="n">
-        <v>64.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -9948,94 +9948,86 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); RSI ipervenduto (24) — possibile rimbalzo; sul supporto dei 20g (8.7320)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 39); pattern: Double Bottom; sul supporto dei 20g (13.84); vicino alla resistenza dei 20g (13.97)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>IG_IT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Italgas</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.8048999905586243</v>
+        <v>8.802000045776367</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8446949932823689</v>
+        <v>-1.344988640244482</v>
       </c>
       <c r="F104" t="n">
-        <v>-4.395159771601531</v>
+        <v>-2.675803128461007</v>
       </c>
       <c r="G104" t="n">
-        <v>-2.571231359524995</v>
+        <v>-11.44868795420061</v>
       </c>
       <c r="H104" t="n">
-        <v>-15.96296440811215</v>
+        <v>-14.54369045843309</v>
       </c>
       <c r="I104" t="n">
-        <v>46.25777067353273</v>
+        <v>23.81347145094797</v>
       </c>
       <c r="J104" t="n">
-        <v>18.98200701068858</v>
+        <v>34.81626615742476</v>
       </c>
       <c r="K104" t="n">
-        <v>0.5160878677271936</v>
+        <v>0.08552434239305773</v>
       </c>
       <c r="L104" t="n">
-        <v>0.8128312431491541</v>
+        <v>9.484746537148963</v>
       </c>
       <c r="M104" t="n">
-        <v>0.8595977891695188</v>
+        <v>9.85166361379957</v>
       </c>
       <c r="N104" t="n">
-        <v>1.319207639861301</v>
+        <v>9.640357250596107</v>
       </c>
       <c r="O104" t="n">
-        <v>0.004450581169809271</v>
+        <v>-0.08418613205409042</v>
       </c>
       <c r="P104" t="n">
-        <v>47.66041427280186</v>
+        <v>4.971569261613593</v>
       </c>
       <c r="Q104" t="n">
-        <v>-52.33958572719814</v>
+        <v>-95.0284307383864</v>
       </c>
       <c r="R104" t="n">
-        <v>6.305185272126752</v>
+        <v>-139.5653298407796</v>
       </c>
       <c r="S104" t="n">
-        <v>-4.837461676658606</v>
+        <v>-11.2880456894776</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>Shooting Star, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>Outside Bar, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="X104" t="n">
-        <v>68.2</v>
+        <v>64.8</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -10044,7 +10036,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); pattern: Bull Flag / Consolidation; shooting star — rifiuto di resistenza</t>
+          <t>trend molto direzionale (ADX 35); RSI ipervenduto (24) — possibile rimbalzo; sul supporto dei 20g (8.7320)</t>
         </is>
       </c>
     </row>
@@ -10065,52 +10057,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>6.456999778747559</v>
+        <v>6.435999870300293</v>
       </c>
       <c r="E105" t="n">
-        <v>0.6341642825340665</v>
+        <v>0.306874781370392</v>
       </c>
       <c r="F105" t="n">
-        <v>-2.978299548950059</v>
+        <v>-3.293840341374443</v>
       </c>
       <c r="G105" t="n">
-        <v>-1.812821134913678</v>
+        <v>-2.132152378140395</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.74943971429199</v>
+        <v>-3.065724820753823</v>
       </c>
       <c r="I105" t="n">
-        <v>47.84056478210304</v>
+        <v>47.16788372437386</v>
       </c>
       <c r="J105" t="n">
         <v>15.48093665252258</v>
       </c>
       <c r="K105" t="n">
-        <v>0.454408537020637</v>
+        <v>0.4223344645316442</v>
       </c>
       <c r="L105" t="n">
-        <v>6.498038659947228</v>
+        <v>6.496038668666536</v>
       </c>
       <c r="M105" t="n">
-        <v>6.707027541447125</v>
+        <v>6.706204015625665</v>
       </c>
       <c r="N105" t="n">
-        <v>9.198286752394532</v>
+        <v>9.198077798081624</v>
       </c>
       <c r="O105" t="n">
-        <v>0.004752926230229854</v>
+        <v>0.00341276113274068</v>
       </c>
       <c r="P105" t="n">
-        <v>44.41778137945374</v>
+        <v>42.06982038418272</v>
       </c>
       <c r="Q105" t="n">
-        <v>-55.58221862054626</v>
+        <v>-57.93017961581728</v>
       </c>
       <c r="R105" t="n">
-        <v>-9.440992768550492</v>
+        <v>-13.74580419415131</v>
       </c>
       <c r="S105" t="n">
-        <v>-1.590482612742306</v>
+        <v>-1.910536960935705</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10119,15 +10111,15 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>Shooting Star, Bullish Harami</t>
+          <t>Doji, Shooting Star, Bullish Harami</t>
         </is>
       </c>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="n">
-        <v>36.9</v>
+        <v>35.6</v>
       </c>
       <c r="X105" t="n">
-        <v>63.8</v>
+        <v>64.8</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -10136,7 +10128,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -10885,52 +10877,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.019600033760071</v>
+        <v>1.019000053405762</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.9053239047104311</v>
+        <v>-0.9636358475362261</v>
       </c>
       <c r="F114" t="n">
-        <v>-3.903249179730739</v>
+        <v>-3.95979700308895</v>
       </c>
       <c r="G114" t="n">
-        <v>-8.318665934904622</v>
+        <v>-8.37261552050148</v>
       </c>
       <c r="H114" t="n">
-        <v>-10.34528338218573</v>
+        <v>-10.39804041127631</v>
       </c>
       <c r="I114" t="n">
-        <v>36.56155082725045</v>
+        <v>36.45416894271093</v>
       </c>
       <c r="J114" t="n">
         <v>21.23269830921472</v>
       </c>
       <c r="K114" t="n">
-        <v>0.1045689650828796</v>
+        <v>0.1007033277368367</v>
       </c>
       <c r="L114" t="n">
-        <v>1.061761730436745</v>
+        <v>1.061704589450621</v>
       </c>
       <c r="M114" t="n">
-        <v>1.100361442425882</v>
+        <v>1.100337913784536</v>
       </c>
       <c r="N114" t="n">
-        <v>1.373084513022361</v>
+        <v>1.373078543068586</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.004609365483713521</v>
+        <v>-0.00464765482826218</v>
       </c>
       <c r="P114" t="n">
-        <v>7.187499050518493</v>
+        <v>6.422900582449937</v>
       </c>
       <c r="Q114" t="n">
-        <v>-92.8125009494815</v>
+        <v>-93.57709941755006</v>
       </c>
       <c r="R114" t="n">
-        <v>-116.5495998242151</v>
+        <v>-116.9784548365211</v>
       </c>
       <c r="S114" t="n">
-        <v>-10.75499819590603</v>
+        <v>-10.80751412963474</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -10947,7 +10939,7 @@
         <v>30.4</v>
       </c>
       <c r="X114" t="n">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -10956,7 +10948,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 21); RSI scarico (37) — zona di interesse long; pattern: Double Top; sul supporto dei 20g (1.0140)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 21); RSI scarico (36) — zona di interesse long; pattern: Double Top; sul supporto dei 20g (1.0140)</t>
         </is>
       </c>
     </row>
@@ -10977,52 +10969,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.776000022888184</v>
+        <v>2.778000116348267</v>
       </c>
       <c r="E115" t="n">
-        <v>4.282497541252361</v>
+        <v>4.357632533908595</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.1797869904381355</v>
+        <v>-0.1078670503882773</v>
       </c>
       <c r="G115" t="n">
-        <v>-5.578232351713785</v>
+        <v>-5.510201963239103</v>
       </c>
       <c r="H115" t="n">
-        <v>-4.604813023716914</v>
+        <v>-4.536081291720695</v>
       </c>
       <c r="I115" t="n">
-        <v>45.0862899867275</v>
+        <v>45.22676289460227</v>
       </c>
       <c r="J115" t="n">
         <v>48.595717788062</v>
       </c>
       <c r="K115" t="n">
-        <v>0.4491989975045235</v>
+        <v>0.4539918385031514</v>
       </c>
       <c r="L115" t="n">
-        <v>2.80579438218088</v>
+        <v>2.805984867272317</v>
       </c>
       <c r="M115" t="n">
-        <v>2.923217520727734</v>
+        <v>2.923295955765385</v>
       </c>
       <c r="N115" t="n">
-        <v>3.177247199984403</v>
+        <v>3.177267101411866</v>
       </c>
       <c r="O115" t="n">
-        <v>0.001138731587258607</v>
+        <v>0.001266372879297623</v>
       </c>
       <c r="P115" t="n">
-        <v>42.66668955485027</v>
+        <v>43.20004781087239</v>
       </c>
       <c r="Q115" t="n">
-        <v>-57.33331044514974</v>
+        <v>-56.7999521891276</v>
       </c>
       <c r="R115" t="n">
-        <v>-12.48838995495978</v>
+        <v>-12.27417030042326</v>
       </c>
       <c r="S115" t="n">
-        <v>-4.176736223385613</v>
+        <v>-4.107696064299438</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12983,52 +12975,52 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.634500026702881</v>
+        <v>6.635499954223633</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9740526703135188</v>
+        <v>0.9892711093429263</v>
       </c>
       <c r="F19" t="n">
-        <v>6.432983438562356</v>
+        <v>6.449024627623734</v>
       </c>
       <c r="G19" t="n">
-        <v>24.18343034451427</v>
+        <v>24.20214681585697</v>
       </c>
       <c r="H19" t="n">
-        <v>37.36025116978128</v>
+        <v>37.38095360325016</v>
       </c>
       <c r="I19" t="n">
-        <v>67.53626965539036</v>
+        <v>67.55622833827189</v>
       </c>
       <c r="J19" t="n">
         <v>38.11523049838756</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9169870995449049</v>
+        <v>0.9177982867095908</v>
       </c>
       <c r="L19" t="n">
-        <v>6.213514810549256</v>
+        <v>6.213610041741709</v>
       </c>
       <c r="M19" t="n">
-        <v>5.790256026032104</v>
+        <v>5.790295238876055</v>
       </c>
       <c r="N19" t="n">
-        <v>4.790096335807641</v>
+        <v>4.79010628533521</v>
       </c>
       <c r="O19" t="n">
-        <v>0.007890805209611884</v>
+        <v>0.00795461824797325</v>
       </c>
       <c r="P19" t="n">
-        <v>88.30517339994142</v>
+        <v>88.43024251001836</v>
       </c>
       <c r="Q19" t="n">
-        <v>-11.69482660005857</v>
+        <v>-11.56975748998165</v>
       </c>
       <c r="R19" t="n">
-        <v>91.83499458418004</v>
+        <v>91.90047806564316</v>
       </c>
       <c r="S19" t="n">
-        <v>21.35540547730379</v>
+        <v>21.37369571910654</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -13042,7 +13034,7 @@
         </is>
       </c>
       <c r="W19" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="X19" t="n">
         <v>80.3</v>
@@ -13487,22 +13479,18 @@
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
           <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W24" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="X24" t="n">
         <v>75.8</v>
       </c>
-      <c r="X24" t="n">
-        <v>79.3</v>
-      </c>
       <c r="Y24" t="inlineStr">
         <is>
           <t>HIGH CONVICTION BUY</t>
@@ -13510,7 +13498,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 60); pattern: Bear Flag / Consolidation; segnale candlestick: Bearish Harami</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 60); pattern: Bear Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -16887,52 +16875,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4450.2001953125</v>
+        <v>4448.60009765625</v>
       </c>
       <c r="E61" t="n">
-        <v>2.522634484598796</v>
+        <v>2.485771822257399</v>
       </c>
       <c r="F61" t="n">
-        <v>8.433032563067822</v>
+        <v>8.394044779676202</v>
       </c>
       <c r="G61" t="n">
-        <v>-2.629960388578034</v>
+        <v>-2.664970402809608</v>
       </c>
       <c r="H61" t="n">
-        <v>33.93325490443306</v>
+        <v>33.88509835464632</v>
       </c>
       <c r="I61" t="n">
-        <v>53.4804328686505</v>
+        <v>53.43224984760439</v>
       </c>
       <c r="J61" t="n">
         <v>46.38489005131441</v>
       </c>
       <c r="K61" t="n">
-        <v>0.546499521824748</v>
+        <v>0.5451310067680324</v>
       </c>
       <c r="L61" t="n">
-        <v>4336.510259751761</v>
+        <v>4336.357869498785</v>
       </c>
       <c r="M61" t="n">
-        <v>4224.755444691426</v>
+        <v>4224.692695763729</v>
       </c>
       <c r="N61" t="n">
-        <v>3176.367122585003</v>
+        <v>3176.351201215289</v>
       </c>
       <c r="O61" t="n">
-        <v>-16.92908848231836</v>
+        <v>-17.03120297662044</v>
       </c>
       <c r="P61" t="n">
-        <v>60.75745317623014</v>
+        <v>60.55811378829998</v>
       </c>
       <c r="Q61" t="n">
-        <v>-39.24254682376987</v>
+        <v>-39.44188621170001</v>
       </c>
       <c r="R61" t="n">
-        <v>8.813086699989835</v>
+        <v>8.690841870607485</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.9305388398820114</v>
+        <v>-0.9661598918911385</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -17075,52 +17063,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.350858449935913</v>
+        <v>1.350803732872009</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3958041832891945</v>
+        <v>0.3917376109303872</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6929904955057964</v>
+        <v>0.6889118854960907</v>
       </c>
       <c r="G63" t="n">
-        <v>0.6173430903736676</v>
+        <v>0.6132675444924907</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5227815362747301</v>
+        <v>-0.5268109009501365</v>
       </c>
       <c r="I63" t="n">
-        <v>54.16661116923902</v>
+        <v>54.14665542004524</v>
       </c>
       <c r="J63" t="n">
         <v>9.93512391241479</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7120542908780375</v>
+        <v>0.7109343157211865</v>
       </c>
       <c r="L63" t="n">
-        <v>1.341416077844224</v>
+        <v>1.34141086669528</v>
       </c>
       <c r="M63" t="n">
-        <v>1.337493737378945</v>
+        <v>1.337491591611733</v>
       </c>
       <c r="N63" t="n">
-        <v>1.308447234264188</v>
+        <v>1.308446689815791</v>
       </c>
       <c r="O63" t="n">
-        <v>0.001035513062007089</v>
+        <v>0.001032021146817909</v>
       </c>
       <c r="P63" t="n">
-        <v>71.78764476052916</v>
+        <v>71.68019364610426</v>
       </c>
       <c r="Q63" t="n">
-        <v>-28.21235523947085</v>
+        <v>-28.31980635389575</v>
       </c>
       <c r="R63" t="n">
-        <v>85.22910004692299</v>
+        <v>85.08632966445248</v>
       </c>
       <c r="S63" t="n">
-        <v>1.296819898540691</v>
+        <v>1.292716830178553</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -18091,52 +18079,52 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>87.87999725341797</v>
+        <v>87.84999847412109</v>
       </c>
       <c r="E74" t="n">
-        <v>5.182518304610717</v>
+        <v>5.14661312423832</v>
       </c>
       <c r="F74" t="n">
-        <v>15.61635940479684</v>
+        <v>15.57689252089503</v>
       </c>
       <c r="G74" t="n">
-        <v>-21.66860206700212</v>
+        <v>-21.6953413295425</v>
       </c>
       <c r="H74" t="n">
-        <v>32.21001299763233</v>
+        <v>32.16488169216225</v>
       </c>
       <c r="I74" t="n">
-        <v>50.92242164720521</v>
+        <v>50.90486210788146</v>
       </c>
       <c r="J74" t="n">
         <v>25.4715707072706</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4115580461799326</v>
+        <v>0.4109560410062949</v>
       </c>
       <c r="L74" t="n">
-        <v>87.41066438933119</v>
+        <v>87.40780736273149</v>
       </c>
       <c r="M74" t="n">
-        <v>82.73649754782429</v>
+        <v>82.73532112510676</v>
       </c>
       <c r="N74" t="n">
-        <v>78.07383844545352</v>
+        <v>78.07353995013713</v>
       </c>
       <c r="O74" t="n">
-        <v>-1.23967974036232</v>
+        <v>-1.241594192374421</v>
       </c>
       <c r="P74" t="n">
-        <v>41.69211889877094</v>
+        <v>41.62161648479842</v>
       </c>
       <c r="Q74" t="n">
-        <v>-58.30788110122906</v>
+        <v>-58.37838351520159</v>
       </c>
       <c r="R74" t="n">
-        <v>-28.01811343061334</v>
+        <v>-28.05905622758671</v>
       </c>
       <c r="S74" t="n">
-        <v>-21.93302168281116</v>
+        <v>-21.95967068288063</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -18271,52 +18259,52 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1386</v>
+        <v>1388.5</v>
       </c>
       <c r="E76" t="n">
-        <v>0.8660231879407565</v>
+        <v>1.047960459203279</v>
       </c>
       <c r="F76" t="n">
-        <v>9.452732097945438</v>
+        <v>9.650157660892678</v>
       </c>
       <c r="G76" t="n">
-        <v>-2.723192553231413</v>
+        <v>-2.54772933633608</v>
       </c>
       <c r="H76" t="n">
-        <v>30.68074975527815</v>
+        <v>30.91646539336486</v>
       </c>
       <c r="I76" t="n">
-        <v>50.09162627485274</v>
+        <v>50.25323004701611</v>
       </c>
       <c r="J76" t="n">
         <v>40.97071224419879</v>
       </c>
       <c r="K76" t="n">
-        <v>0.5401111660548317</v>
+        <v>0.5450708472735458</v>
       </c>
       <c r="L76" t="n">
-        <v>1363.758748496429</v>
+        <v>1363.996843734525</v>
       </c>
       <c r="M76" t="n">
-        <v>1383.172597072609</v>
+        <v>1383.270636288295</v>
       </c>
       <c r="N76" t="n">
-        <v>1363.38947616052</v>
+        <v>1363.414351782411</v>
       </c>
       <c r="O76" t="n">
-        <v>6.181767322469732</v>
+        <v>6.341311482013751</v>
       </c>
       <c r="P76" t="n">
-        <v>60.77900482800202</v>
+        <v>61.45522888269164</v>
       </c>
       <c r="Q76" t="n">
-        <v>-39.22099517199798</v>
+        <v>-38.54477111730836</v>
       </c>
       <c r="R76" t="n">
-        <v>4.328374740353783</v>
+        <v>4.637119008327004</v>
       </c>
       <c r="S76" t="n">
-        <v>-0.3522916333348003</v>
+        <v>-0.1725518996287034</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -18330,10 +18318,10 @@
       </c>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="X76" t="n">
-        <v>64.2</v>
+        <v>64.3</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -18827,52 +18815,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>159.302001953125</v>
+        <v>159.2319946289062</v>
       </c>
       <c r="E82" t="n">
-        <v>0.5637339989280843</v>
+        <v>0.5195399659316813</v>
       </c>
       <c r="F82" t="n">
-        <v>-1.885284525660247</v>
+        <v>-1.928402305805055</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8725754265314078</v>
+        <v>0.8282456691769191</v>
       </c>
       <c r="H82" t="n">
-        <v>10.97936052812487</v>
+        <v>10.93058921339671</v>
       </c>
       <c r="I82" t="n">
-        <v>50.65656088576884</v>
+        <v>50.45264367841794</v>
       </c>
       <c r="J82" t="n">
         <v>11.01236137530571</v>
       </c>
       <c r="K82" t="n">
-        <v>0.4085624689211041</v>
+        <v>0.3993646964751139</v>
       </c>
       <c r="L82" t="n">
-        <v>159.7638702110497</v>
+        <v>159.7572028468384</v>
       </c>
       <c r="M82" t="n">
-        <v>157.0088345290706</v>
+        <v>157.0060891438071</v>
       </c>
       <c r="N82" t="n">
-        <v>147.1227698677566</v>
+        <v>147.1220732774659</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.3639582484488841</v>
+        <v>-0.3684259523306395</v>
       </c>
       <c r="P82" t="n">
-        <v>46.3831469499065</v>
+        <v>45.58058743578037</v>
       </c>
       <c r="Q82" t="n">
-        <v>-53.6168530500935</v>
+        <v>-54.41941256421963</v>
       </c>
       <c r="R82" t="n">
-        <v>-33.91499047187949</v>
+        <v>-34.61634517431101</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.2517111725842458</v>
+        <v>-0.2955468476579348</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -19011,52 +18999,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>66.00499725341797</v>
+        <v>65.87999725341797</v>
       </c>
       <c r="E84" t="n">
-        <v>4.220609628755478</v>
+        <v>4.023237054773299</v>
       </c>
       <c r="F84" t="n">
-        <v>10.35964376853247</v>
+        <v>10.15064511623189</v>
       </c>
       <c r="G84" t="n">
-        <v>-4.837086688884606</v>
+        <v>-5.017305833780838</v>
       </c>
       <c r="H84" t="n">
-        <v>83.219970736164</v>
+        <v>82.87298948784898</v>
       </c>
       <c r="I84" t="n">
-        <v>49.37226609391137</v>
+        <v>49.24509478227358</v>
       </c>
       <c r="J84" t="n">
         <v>14.48180432461838</v>
       </c>
       <c r="K84" t="n">
-        <v>0.415509810215035</v>
+        <v>0.4119786363272357</v>
       </c>
       <c r="L84" t="n">
-        <v>66.19755488849896</v>
+        <v>66.1856501265942</v>
       </c>
       <c r="M84" t="n">
-        <v>63.30264284265748</v>
+        <v>63.29774088187317</v>
       </c>
       <c r="N84" t="n">
-        <v>43.11146186438996</v>
+        <v>43.11021808329544</v>
       </c>
       <c r="O84" t="n">
-        <v>-1.190707569188683</v>
+        <v>-1.198684777165889</v>
       </c>
       <c r="P84" t="n">
-        <v>32.444712624572</v>
+        <v>32.07568715902195</v>
       </c>
       <c r="Q84" t="n">
-        <v>-67.55528737542801</v>
+        <v>-67.92431284097805</v>
       </c>
       <c r="R84" t="n">
-        <v>-32.8545983861241</v>
+        <v>-33.21023575174782</v>
       </c>
       <c r="S84" t="n">
-        <v>-5.090230798378393</v>
+        <v>-5.269970539971802</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -19066,10 +19054,10 @@
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="X84" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -19078,7 +19066,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 14)</t>
+          <t>mercato laterale — ATR basso (ADX 14); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -19177,87 +19165,79 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>TEN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>Tenaris</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>99.82099914550781</v>
+        <v>23.29999923706055</v>
       </c>
       <c r="E86" t="n">
-        <v>0.2218882276831868</v>
+        <v>0.6914427468986295</v>
       </c>
       <c r="F86" t="n">
-        <v>-1.137963812324605</v>
+        <v>-3.439701419698205</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1715982107481473</v>
+        <v>-4.859128400078728</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6361494995166472</v>
+        <v>53.23906184789657</v>
       </c>
       <c r="I86" t="n">
-        <v>50.69759647376054</v>
+        <v>47.77666230553107</v>
       </c>
       <c r="J86" t="n">
-        <v>34.2614850083754</v>
+        <v>26.30941379728321</v>
       </c>
       <c r="K86" t="n">
-        <v>0.5257436649476608</v>
+        <v>0.1030360653954909</v>
       </c>
       <c r="L86" t="n">
-        <v>99.86755733956032</v>
+        <v>24.25621784606045</v>
       </c>
       <c r="M86" t="n">
-        <v>99.68831777174442</v>
+        <v>22.02321043437484</v>
       </c>
       <c r="N86" t="n">
-        <v>100.8197443656193</v>
+        <v>17.329418382962</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.03691489908954043</v>
+        <v>-0.5891533036096077</v>
       </c>
       <c r="P86" t="n">
-        <v>49.89869334698253</v>
+        <v>8.502024916765864</v>
       </c>
       <c r="Q86" t="n">
-        <v>-50.10130665301747</v>
+        <v>-91.49797508323414</v>
       </c>
       <c r="R86" t="n">
-        <v>1.049916387326594</v>
+        <v>-53.15943685711282</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.3285096109420182</v>
+        <v>-8.303819846604432</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Bullish Engulfing, Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom, Inside Bar, Bull Flag / Consolidation, Volatility Squeeze</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="X86" t="n">
-        <v>60.7</v>
+        <v>58.1</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -19266,73 +19246,73 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 34); pattern: Double Bottom; candela di inversione bullish (engulfing); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 26)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TEN</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tenaris</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>23.29999923706055</v>
+        <v>1764.099975585938</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6914427468986295</v>
+        <v>0.7999542994858277</v>
       </c>
       <c r="F87" t="n">
-        <v>-3.439701419698205</v>
+        <v>9.022928261718267</v>
       </c>
       <c r="G87" t="n">
-        <v>-4.859128400078728</v>
+        <v>-10.4790420459941</v>
       </c>
       <c r="H87" t="n">
-        <v>53.23906184789657</v>
+        <v>51.20425554265366</v>
       </c>
       <c r="I87" t="n">
-        <v>47.77666230553107</v>
+        <v>47.88020682538669</v>
       </c>
       <c r="J87" t="n">
-        <v>26.30941379728321</v>
+        <v>20.02705418345082</v>
       </c>
       <c r="K87" t="n">
-        <v>0.1030360653954909</v>
+        <v>0.4175731086446355</v>
       </c>
       <c r="L87" t="n">
-        <v>24.25621784606045</v>
+        <v>1783.025517148999</v>
       </c>
       <c r="M87" t="n">
-        <v>22.02321043437484</v>
+        <v>1752.294924473487</v>
       </c>
       <c r="N87" t="n">
-        <v>17.329418382962</v>
+        <v>1344.697861291599</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.5891533036096077</v>
+        <v>-13.81376754890438</v>
       </c>
       <c r="P87" t="n">
-        <v>8.502024916765864</v>
+        <v>34.9977467608085</v>
       </c>
       <c r="Q87" t="n">
-        <v>-91.49797508323414</v>
+        <v>-65.0022532391915</v>
       </c>
       <c r="R87" t="n">
-        <v>-53.15943685711282</v>
+        <v>-22.036501696221</v>
       </c>
       <c r="S87" t="n">
-        <v>-8.303819846604432</v>
+        <v>-5.693360493423527</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -19342,10 +19322,10 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="X87" t="n">
-        <v>58.1</v>
+        <v>61.6</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -19354,86 +19334,94 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 26)</t>
+          <t>trend in sviluppo (ADX 20)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1763.800048828125</v>
+        <v>99.80699920654297</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7828166066684572</v>
+        <v>0.2078320638485343</v>
       </c>
       <c r="F88" t="n">
-        <v>9.004392524598327</v>
+        <v>-1.151829256313497</v>
       </c>
       <c r="G88" t="n">
-        <v>-10.49426211914586</v>
+        <v>0.1575491001104323</v>
       </c>
       <c r="H88" t="n">
-        <v>51.17854826825881</v>
+        <v>0.6220352353567105</v>
       </c>
       <c r="I88" t="n">
-        <v>47.86367013280282</v>
+        <v>50.61640417411565</v>
       </c>
       <c r="J88" t="n">
-        <v>20.02705418345082</v>
+        <v>34.2614850083754</v>
       </c>
       <c r="K88" t="n">
-        <v>0.4171791262283541</v>
+        <v>0.5227403799104249</v>
       </c>
       <c r="L88" t="n">
-        <v>1782.996952695874</v>
+        <v>99.86622401203986</v>
       </c>
       <c r="M88" t="n">
-        <v>1752.283162639847</v>
+        <v>99.68776875453013</v>
       </c>
       <c r="N88" t="n">
-        <v>1344.69487694575</v>
+        <v>100.819605062744</v>
       </c>
       <c r="O88" t="n">
-        <v>-13.83290817390438</v>
+        <v>-0.03780834248787174</v>
       </c>
       <c r="P88" t="n">
-        <v>34.95277349766055</v>
+        <v>49.54426492317499</v>
       </c>
       <c r="Q88" t="n">
-        <v>-65.04722650233946</v>
+        <v>-50.45573507682501</v>
       </c>
       <c r="R88" t="n">
-        <v>-22.06899284194315</v>
+        <v>0.701918476362239</v>
       </c>
       <c r="S88" t="n">
-        <v>-5.709394213177998</v>
+        <v>-0.3424885812381206</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bullish Engulfing, Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom, Inside Bar, Bull Flag / Consolidation, Volatility Squeeze</t>
+        </is>
+      </c>
       <c r="W88" t="n">
-        <v>51.3</v>
+        <v>51</v>
       </c>
       <c r="X88" t="n">
-        <v>61.6</v>
+        <v>60.9</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -19442,7 +19430,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20)</t>
+          <t>trend molto direzionale (ADX 34); pattern: Double Bottom; candela di inversione bullish (engulfing); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -19647,52 +19635,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>82.33999633789062</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E91" t="n">
-        <v>5.321048882676238</v>
+        <v>5.269893490022493</v>
       </c>
       <c r="F91" t="n">
-        <v>15.30596851317734</v>
+        <v>15.24996335412141</v>
       </c>
       <c r="G91" t="n">
-        <v>-16.25305472592959</v>
+        <v>-16.2937313799745</v>
       </c>
       <c r="H91" t="n">
-        <v>27.50076494778861</v>
+        <v>27.4388366650403</v>
       </c>
       <c r="I91" t="n">
-        <v>50.50117735602426</v>
+        <v>50.47754579219954</v>
       </c>
       <c r="J91" t="n">
         <v>26.09737203781677</v>
       </c>
       <c r="K91" t="n">
-        <v>0.388772113141122</v>
+        <v>0.3879733549173063</v>
       </c>
       <c r="L91" t="n">
-        <v>82.45138539795931</v>
+        <v>82.44757651356571</v>
       </c>
       <c r="M91" t="n">
-        <v>78.1076138665132</v>
+        <v>78.10604550235114</v>
       </c>
       <c r="N91" t="n">
-        <v>73.84106140876594</v>
+        <v>73.84066346562034</v>
       </c>
       <c r="O91" t="n">
-        <v>-1.37772132727953</v>
+        <v>-1.380273605368918</v>
       </c>
       <c r="P91" t="n">
-        <v>36.05938089163041</v>
+        <v>35.96512379560128</v>
       </c>
       <c r="Q91" t="n">
-        <v>-63.94061910836959</v>
+        <v>-64.03487620439873</v>
       </c>
       <c r="R91" t="n">
-        <v>-32.75268652737489</v>
+        <v>-32.80764323053499</v>
       </c>
       <c r="S91" t="n">
-        <v>-17.36250818720409</v>
+        <v>-17.4026459695985</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -20281,77 +20269,73 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>64089.75</v>
+        <v>330.8800048828125</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.164527778458824</v>
+        <v>0.6999873408422008</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5199819827149676</v>
+        <v>-18.8542287231654</v>
       </c>
       <c r="G98" t="n">
-        <v>-5.535336813912462</v>
+        <v>-10.07717888720314</v>
       </c>
       <c r="H98" t="n">
-        <v>-39.42003991112711</v>
+        <v>12.10950344261095</v>
       </c>
       <c r="I98" t="n">
-        <v>40.10820544346564</v>
+        <v>39.6479422540747</v>
       </c>
       <c r="J98" t="n">
-        <v>32.98532090271173</v>
+        <v>15.49864363403116</v>
       </c>
       <c r="K98" t="n">
-        <v>0.3138335303657721</v>
+        <v>0.1673203134804838</v>
       </c>
       <c r="L98" t="n">
-        <v>68500.22102494256</v>
+        <v>374.1367409387458</v>
       </c>
       <c r="M98" t="n">
-        <v>77276.28721367427</v>
+        <v>380.5245775440309</v>
       </c>
       <c r="N98" t="n">
-        <v>68456.51698378073</v>
+        <v>308.0419714560096</v>
       </c>
       <c r="O98" t="n">
-        <v>492.2232600753505</v>
+        <v>-8.93304496849359</v>
       </c>
       <c r="P98" t="n">
-        <v>25.80300847667737</v>
+        <v>21.47160771628078</v>
       </c>
       <c r="Q98" t="n">
-        <v>-74.19699152332262</v>
+        <v>-78.52839228371921</v>
       </c>
       <c r="R98" t="n">
-        <v>-58.04129750972866</v>
+        <v>-122.0515863065959</v>
       </c>
       <c r="S98" t="n">
-        <v>-2.827949487280024</v>
+        <v>-8.553735963857633</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>Dark Cloud Cover</t>
-        </is>
-      </c>
+      <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr">
         <is>
           <t>Inside Bar</t>
@@ -20361,7 +20345,7 @@
         <v>40.1</v>
       </c>
       <c r="X98" t="n">
-        <v>68.90000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -20370,99 +20354,103 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 33); segnale candlestick: Dark Cloud Cover</t>
+          <t>in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>330.8800048828125</v>
+        <v>63987</v>
       </c>
       <c r="E99" t="n">
-        <v>0.6999873408422008</v>
+        <v>-1.322982832047948</v>
       </c>
       <c r="F99" t="n">
-        <v>-18.8542287231654</v>
+        <v>0.3588262885716231</v>
       </c>
       <c r="G99" t="n">
-        <v>-10.07717888720314</v>
+        <v>-5.686784496925279</v>
       </c>
       <c r="H99" t="n">
-        <v>12.10950344261095</v>
+        <v>-39.51716294404785</v>
       </c>
       <c r="I99" t="n">
-        <v>39.6479422540747</v>
+        <v>39.99952296977688</v>
       </c>
       <c r="J99" t="n">
-        <v>15.49864363403116</v>
+        <v>32.98532090271173</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1673203134804838</v>
+        <v>0.3103347425696449</v>
       </c>
       <c r="L99" t="n">
-        <v>374.1367409387458</v>
+        <v>68490.43531065685</v>
       </c>
       <c r="M99" t="n">
-        <v>380.5245775440309</v>
+        <v>77272.25780190957</v>
       </c>
       <c r="N99" t="n">
-        <v>308.0419714560096</v>
+        <v>68455.49459572104</v>
       </c>
       <c r="O99" t="n">
-        <v>-8.93304496849359</v>
+        <v>485.6659951180873</v>
       </c>
       <c r="P99" t="n">
-        <v>21.47160771628078</v>
+        <v>25.38495965091397</v>
       </c>
       <c r="Q99" t="n">
-        <v>-78.52839228371921</v>
+        <v>-74.61504034908603</v>
       </c>
       <c r="R99" t="n">
-        <v>-122.0515863065959</v>
+        <v>-58.43043732851375</v>
       </c>
       <c r="S99" t="n">
-        <v>-8.553735963857633</v>
+        <v>-2.9837377091124</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Dark Cloud Cover</t>
+        </is>
+      </c>
       <c r="V99" t="inlineStr">
         <is>
           <t>Inside Bar</t>
         </is>
       </c>
       <c r="W99" t="n">
-        <v>40.1</v>
+        <v>39.4</v>
       </c>
       <c r="X99" t="n">
-        <v>60.6</v>
+        <v>70</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 33); segnale candlestick: Dark Cloud Cover</t>
         </is>
       </c>
     </row>
@@ -20859,52 +20847,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>76.33000183105469</v>
+        <v>76.36000061035156</v>
       </c>
       <c r="E104" t="n">
-        <v>0.1546658636722098</v>
+        <v>0.1940280757083856</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.7074428682470324</v>
+        <v>-0.6684194772374141</v>
       </c>
       <c r="G104" t="n">
-        <v>-11.37644869813709</v>
+        <v>-11.34161837857421</v>
       </c>
       <c r="H104" t="n">
-        <v>-49.92458701543266</v>
+        <v>-49.90490666398122</v>
       </c>
       <c r="I104" t="n">
-        <v>40.80607410492632</v>
+        <v>40.83235219252515</v>
       </c>
       <c r="J104" t="n">
         <v>16.92527847437997</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3935449132195512</v>
+        <v>0.3945658920461924</v>
       </c>
       <c r="L104" t="n">
-        <v>82.13018444910028</v>
+        <v>82.1330414757</v>
       </c>
       <c r="M104" t="n">
-        <v>105.507813572609</v>
+        <v>105.5089899953265</v>
       </c>
       <c r="N104" t="n">
-        <v>111.6612789838929</v>
+        <v>111.6615774792093</v>
       </c>
       <c r="O104" t="n">
-        <v>2.462943579456617</v>
+        <v>2.464858031468719</v>
       </c>
       <c r="P104" t="n">
-        <v>42.0461279349981</v>
+        <v>42.12538084530525</v>
       </c>
       <c r="Q104" t="n">
-        <v>-57.9538720650019</v>
+        <v>-57.87461915469475</v>
       </c>
       <c r="R104" t="n">
-        <v>-17.25399359411415</v>
+        <v>-17.19883289495714</v>
       </c>
       <c r="S104" t="n">
-        <v>-6.254297966950951</v>
+        <v>-6.217454569101378</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -21139,52 +21127,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>2.776000022888184</v>
+        <v>2.778000116348267</v>
       </c>
       <c r="E107" t="n">
-        <v>4.282497541252361</v>
+        <v>4.357632533908595</v>
       </c>
       <c r="F107" t="n">
-        <v>-5.578232351713785</v>
+        <v>-5.510201963239103</v>
       </c>
       <c r="G107" t="n">
-        <v>-10.30694677780952</v>
+        <v>-10.24232340328306</v>
       </c>
       <c r="H107" t="n">
-        <v>-26.63847564331118</v>
+        <v>-26.58561904969527</v>
       </c>
       <c r="I107" t="n">
-        <v>43.62521389239195</v>
+        <v>43.67241988822813</v>
       </c>
       <c r="J107" t="n">
         <v>20.00695050300951</v>
       </c>
       <c r="K107" t="n">
-        <v>0.3522130173829165</v>
+        <v>0.3542275146395398</v>
       </c>
       <c r="L107" t="n">
-        <v>2.993944756259721</v>
+        <v>2.994135241351158</v>
       </c>
       <c r="M107" t="n">
-        <v>3.182800590572368</v>
+        <v>3.182879025610019</v>
       </c>
       <c r="N107" t="n">
-        <v>3.309717949090873</v>
+        <v>3.309737850518336</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.01195373571899791</v>
+        <v>-0.01182609442695889</v>
       </c>
       <c r="P107" t="n">
-        <v>19.39394867671916</v>
+        <v>19.63638423362592</v>
       </c>
       <c r="Q107" t="n">
-        <v>-80.60605132328084</v>
+        <v>-80.36361576637408</v>
       </c>
       <c r="R107" t="n">
-        <v>-30.44533980542037</v>
+        <v>-30.32895695799438</v>
       </c>
       <c r="S107" t="n">
-        <v>-10.30694677780952</v>
+        <v>-10.24232340328306</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -21217,12 +21205,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21231,73 +21219,69 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1878.260009765625</v>
+        <v>1.019000053405762</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.593912328458391</v>
+        <v>-0.9636358475362261</v>
       </c>
       <c r="F108" t="n">
-        <v>4.013312768674093</v>
+        <v>-6.146777003962523</v>
       </c>
       <c r="G108" t="n">
-        <v>-8.513600322310355</v>
+        <v>-26.41977557321915</v>
       </c>
       <c r="H108" t="n">
-        <v>-25.19238278895049</v>
+        <v>-55.02086627535274</v>
       </c>
       <c r="I108" t="n">
-        <v>42.0458157624094</v>
+        <v>31.63281467464695</v>
       </c>
       <c r="J108" t="n">
-        <v>35.72909943308087</v>
+        <v>19.87920407781435</v>
       </c>
       <c r="K108" t="n">
-        <v>0.3929955489289945</v>
+        <v>0.1603163619008224</v>
       </c>
       <c r="L108" t="n">
-        <v>1994.787722836902</v>
+        <v>1.23254761626598</v>
       </c>
       <c r="M108" t="n">
-        <v>2365.032836528968</v>
+        <v>1.548170251872494</v>
       </c>
       <c r="N108" t="n">
-        <v>2468.049469923369</v>
+        <v>1.3799920343388</v>
       </c>
       <c r="O108" t="n">
-        <v>45.0348903826858</v>
+        <v>0.01270776365757711</v>
       </c>
       <c r="P108" t="n">
-        <v>42.83881598520411</v>
+        <v>1.71999684249645</v>
       </c>
       <c r="Q108" t="n">
-        <v>-57.16118401479589</v>
+        <v>-98.28000315750354</v>
       </c>
       <c r="R108" t="n">
-        <v>-26.37065520051099</v>
+        <v>-64.91769096098847</v>
       </c>
       <c r="S108" t="n">
-        <v>-5.260859636051163</v>
+        <v>-23.22621218361993</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Trend Bearish</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Dark Cloud Cover</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
       <c r="V108" t="inlineStr">
         <is>
           <t>Inside Bar</t>
         </is>
       </c>
       <c r="W108" t="n">
-        <v>32.3</v>
+        <v>31.6</v>
       </c>
       <c r="X108" t="n">
-        <v>73.2</v>
+        <v>68.2</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21306,19 +21290,19 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 36); candela di inversione bearish (engulfing)</t>
+          <t>RSI scarico (32) — zona di interesse long; sul supporto dei 20g (1.0098)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21327,69 +21311,73 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.019600033760071</v>
+        <v>1874.31005859375</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.9053239047104311</v>
+        <v>-1.800858778522207</v>
       </c>
       <c r="F109" t="n">
-        <v>-6.091516859669099</v>
+        <v>3.794574412682317</v>
       </c>
       <c r="G109" t="n">
-        <v>-26.37645203366272</v>
+        <v>-8.705994777677917</v>
       </c>
       <c r="H109" t="n">
-        <v>-54.99438286497564</v>
+        <v>-25.3497020278906</v>
       </c>
       <c r="I109" t="n">
-        <v>31.65393656302163</v>
+        <v>41.93459204591151</v>
       </c>
       <c r="J109" t="n">
-        <v>19.87920407781435</v>
+        <v>35.72909943308087</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1611576777816177</v>
+        <v>0.3891397478292329</v>
       </c>
       <c r="L109" t="n">
-        <v>1.232604757252105</v>
+        <v>1994.411537011009</v>
       </c>
       <c r="M109" t="n">
-        <v>1.548193780513839</v>
+        <v>2364.877936483012</v>
       </c>
       <c r="N109" t="n">
-        <v>1.379998004292574</v>
+        <v>2468.010166926633</v>
       </c>
       <c r="O109" t="n">
-        <v>0.01274605300212561</v>
+        <v>44.78281372670335</v>
       </c>
       <c r="P109" t="n">
-        <v>1.831595967264848</v>
+        <v>42.38364641773054</v>
       </c>
       <c r="Q109" t="n">
-        <v>-98.16840403273515</v>
+        <v>-57.61635358226946</v>
       </c>
       <c r="R109" t="n">
-        <v>-64.86107397098266</v>
+        <v>-26.72569703285862</v>
       </c>
       <c r="S109" t="n">
-        <v>-23.18100829549278</v>
+        <v>-5.460094553771477</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr"/>
+          <t>Trend Bearish</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bearish Engulfing, Dark Cloud Cover</t>
+        </is>
+      </c>
       <c r="V109" t="inlineStr">
         <is>
           <t>Inside Bar</t>
         </is>
       </c>
       <c r="W109" t="n">
-        <v>31.6</v>
+        <v>31.1</v>
       </c>
       <c r="X109" t="n">
-        <v>68.2</v>
+        <v>73.2</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -21398,7 +21386,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>RSI scarico (32) — zona di interesse long; sul supporto dei 20g (1.0098)</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 36); candela di inversione bearish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -21511,52 +21499,52 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>8.284000396728516</v>
+        <v>8.300999641418457</v>
       </c>
       <c r="E111" t="n">
-        <v>1.283202928238025</v>
+        <v>1.491041878878097</v>
       </c>
       <c r="F111" t="n">
-        <v>3.653824261599303</v>
+        <v>3.866527863396207</v>
       </c>
       <c r="G111" t="n">
-        <v>-4.619617314720204</v>
+        <v>-4.423891290307203</v>
       </c>
       <c r="H111" t="n">
-        <v>-39.60831214056329</v>
+        <v>-39.48438492786462</v>
       </c>
       <c r="I111" t="n">
-        <v>42.34577528391851</v>
+        <v>42.47660197787808</v>
       </c>
       <c r="J111" t="n">
         <v>25.8886820955453</v>
       </c>
       <c r="K111" t="n">
-        <v>0.3806538825521587</v>
+        <v>0.3856991578535867</v>
       </c>
       <c r="L111" t="n">
-        <v>8.832696226453606</v>
+        <v>8.834315202138363</v>
       </c>
       <c r="M111" t="n">
-        <v>10.95592163601833</v>
+        <v>10.95658827306499</v>
       </c>
       <c r="N111" t="n">
-        <v>12.90004305832018</v>
+        <v>12.90021220503352</v>
       </c>
       <c r="O111" t="n">
-        <v>0.2222278973914682</v>
+        <v>0.2233127494742446</v>
       </c>
       <c r="P111" t="n">
-        <v>33.52488778086462</v>
+        <v>33.97661533782949</v>
       </c>
       <c r="Q111" t="n">
-        <v>-66.47511221913538</v>
+        <v>-66.02338466217051</v>
       </c>
       <c r="R111" t="n">
-        <v>-31.17463182067034</v>
+        <v>-30.75974334070289</v>
       </c>
       <c r="S111" t="n">
-        <v>-1.442686697628059</v>
+        <v>-1.240441429089467</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -21574,10 +21562,10 @@
         </is>
       </c>
       <c r="W111" t="n">
-        <v>29</v>
+        <v>29.1</v>
       </c>
       <c r="X111" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21799,52 +21787,52 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.193450003862381</v>
+        <v>0.1926800012588501</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.6185328357348641</v>
+        <v>-1.014107852180157</v>
       </c>
       <c r="F114" t="n">
-        <v>19.44380679342914</v>
+        <v>18.96837624098515</v>
       </c>
       <c r="G114" t="n">
-        <v>-22.8037266251955</v>
+        <v>-23.11099636050017</v>
       </c>
       <c r="H114" t="n">
-        <v>-71.12251135328285</v>
+        <v>-71.2374544445077</v>
       </c>
       <c r="I114" t="n">
-        <v>40.39289079219674</v>
+        <v>40.28385321539977</v>
       </c>
       <c r="J114" t="n">
         <v>25.79929474502616</v>
       </c>
       <c r="K114" t="n">
-        <v>0.4151630698639269</v>
+        <v>0.4107969863722611</v>
       </c>
       <c r="L114" t="n">
-        <v>0.215708912887348</v>
+        <v>0.2156355793060593</v>
       </c>
       <c r="M114" t="n">
-        <v>0.3354339225194796</v>
+        <v>0.3354037263389489</v>
       </c>
       <c r="N114" t="n">
-        <v>0.50078816665905</v>
+        <v>0.5007805049416019</v>
       </c>
       <c r="O114" t="n">
-        <v>0.01171294103927505</v>
+        <v>0.01166380127198416</v>
       </c>
       <c r="P114" t="n">
-        <v>37.96209189841557</v>
+        <v>37.42824278161073</v>
       </c>
       <c r="Q114" t="n">
-        <v>-62.03790810158444</v>
+        <v>-62.57175721838927</v>
       </c>
       <c r="R114" t="n">
-        <v>-17.23223720049405</v>
+        <v>-17.53017280590311</v>
       </c>
       <c r="S114" t="n">
-        <v>-19.2484617833448</v>
+        <v>-19.56988278838227</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -21895,52 +21883,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6.456999778747559</v>
+        <v>6.435999870300293</v>
       </c>
       <c r="E115" t="n">
-        <v>0.6341642825340665</v>
+        <v>0.306874781370392</v>
       </c>
       <c r="F115" t="n">
-        <v>0.8597949854292519</v>
+        <v>0.5317716722373689</v>
       </c>
       <c r="G115" t="n">
-        <v>-28.40275549759712</v>
+        <v>-28.63560908767709</v>
       </c>
       <c r="H115" t="n">
-        <v>-69.33396833506352</v>
+        <v>-69.43370255830513</v>
       </c>
       <c r="I115" t="n">
-        <v>34.27260207206307</v>
+        <v>34.09441206127575</v>
       </c>
       <c r="J115" t="n">
         <v>36.66171433726061</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2685593878358307</v>
+        <v>0.2651971026397268</v>
       </c>
       <c r="L115" t="n">
-        <v>7.827843680705436</v>
+        <v>7.825843689424744</v>
       </c>
       <c r="M115" t="n">
-        <v>11.86266552456274</v>
+        <v>11.86184199874128</v>
       </c>
       <c r="N115" t="n">
-        <v>20.6505362657836</v>
+        <v>20.65032731147069</v>
       </c>
       <c r="O115" t="n">
-        <v>0.2248225834482918</v>
+        <v>0.2234824183508033</v>
       </c>
       <c r="P115" t="n">
-        <v>16.74288634624597</v>
+        <v>16.28233689317982</v>
       </c>
       <c r="Q115" t="n">
-        <v>-83.25711365375403</v>
+        <v>-83.71766310682018</v>
       </c>
       <c r="R115" t="n">
-        <v>-56.62048435498</v>
+        <v>-56.8904389905497</v>
       </c>
       <c r="S115" t="n">
-        <v>-24.88108339179357</v>
+        <v>-25.12539041138218</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -21949,7 +21937,7 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>Shooting Star, Bullish Harami</t>
+          <t>Doji, Shooting Star, Bullish Harami</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
@@ -21958,10 +21946,10 @@
         </is>
       </c>
       <c r="W115" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="X115" t="n">
-        <v>69.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -21970,7 +21958,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long; shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -22087,73 +22075,69 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.8048999905586243</v>
+        <v>0.8098999857902527</v>
       </c>
       <c r="E117" t="n">
-        <v>0.8446949932823689</v>
+        <v>1.471136787313809</v>
       </c>
       <c r="F117" t="n">
-        <v>-4.65619982687846</v>
+        <v>-4.063929294113167</v>
       </c>
       <c r="G117" t="n">
-        <v>-42.97588033431112</v>
+        <v>-42.62164958544707</v>
       </c>
       <c r="H117" t="n">
-        <v>-80.00154461036129</v>
+        <v>-79.87731528651855</v>
       </c>
       <c r="I117" t="n">
-        <v>28.9778135762209</v>
+        <v>29.30147032664718</v>
       </c>
       <c r="J117" t="n">
         <v>39.95462635165084</v>
       </c>
       <c r="K117" t="n">
-        <v>0.2212867475312223</v>
+        <v>0.2266260105208471</v>
       </c>
       <c r="L117" t="n">
-        <v>1.065296821106981</v>
+        <v>1.065773011129041</v>
       </c>
       <c r="M117" t="n">
-        <v>1.850796641821802</v>
+        <v>1.85099272006618</v>
       </c>
       <c r="N117" t="n">
-        <v>5.114092597596593</v>
+        <v>5.114142348792928</v>
       </c>
       <c r="O117" t="n">
-        <v>0.03784090568382931</v>
+        <v>0.03815999369861117</v>
       </c>
       <c r="P117" t="n">
-        <v>8.258726054504633</v>
+        <v>8.989056535010825</v>
       </c>
       <c r="Q117" t="n">
-        <v>-91.74127394549537</v>
+        <v>-91.01094346498917</v>
       </c>
       <c r="R117" t="n">
-        <v>-50.89356142277671</v>
+        <v>-50.57296632118706</v>
       </c>
       <c r="S117" t="n">
-        <v>-36.01799894304466</v>
+        <v>-35.6205462110937</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
+      <c r="U117" t="inlineStr"/>
       <c r="V117" t="inlineStr">
         <is>
           <t>Inside Bar</t>
         </is>
       </c>
       <c r="W117" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="X117" t="n">
-        <v>76.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -22162,7 +22146,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 40); RSI scarico (29) — zona di interesse long; shooting star — rifiuto di resistenza</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 40); RSI scarico (29) — zona di interesse long</t>
         </is>
       </c>
     </row>
@@ -25561,52 +25545,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.634500026702881</v>
+        <v>6.635499954223633</v>
       </c>
       <c r="E37" t="n">
-        <v>3.08421628966451</v>
+        <v>3.099752764818375</v>
       </c>
       <c r="F37" t="n">
-        <v>18.73825348483684</v>
+        <v>18.75614927908624</v>
       </c>
       <c r="G37" t="n">
-        <v>62.59036446577588</v>
+        <v>62.61486948942259</v>
       </c>
       <c r="H37" t="n">
-        <v>54.4163786480843</v>
+        <v>54.43965171855589</v>
       </c>
       <c r="I37" t="n">
-        <v>69.72470818756912</v>
+        <v>69.73281763820482</v>
       </c>
       <c r="J37" t="n">
         <v>65.50118230776258</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9267899675982085</v>
+        <v>0.9270506427638858</v>
       </c>
       <c r="L37" t="n">
-        <v>5.500942092885611</v>
+        <v>5.501037324078063</v>
       </c>
       <c r="M37" t="n">
-        <v>4.764400310634239</v>
+        <v>4.76443952347819</v>
       </c>
       <c r="N37" t="n">
-        <v>3.971169245542278</v>
+        <v>3.971186051046828</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1189102525180552</v>
+        <v>0.1189740655564166</v>
       </c>
       <c r="P37" t="n">
-        <v>96.11145198451118</v>
+        <v>96.15303765793929</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.888548015488829</v>
+        <v>-3.846962342060706</v>
       </c>
       <c r="R37" t="n">
-        <v>116.1943391823109</v>
+        <v>116.2205436680626</v>
       </c>
       <c r="S37" t="n">
-        <v>66.44505582320323</v>
+        <v>66.47014181179934</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -26557,52 +26541,52 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>66.00499725341797</v>
+        <v>65.87999725341797</v>
       </c>
       <c r="E48" t="n">
-        <v>14.60991770955218</v>
+        <v>14.39286990544895</v>
       </c>
       <c r="F48" t="n">
-        <v>-11.62806922492954</v>
+        <v>-11.79542763424016</v>
       </c>
       <c r="G48" t="n">
-        <v>115.1050950047356</v>
+        <v>114.6977298355143</v>
       </c>
       <c r="H48" t="n">
-        <v>152.2644561202671</v>
+        <v>151.786718701478</v>
       </c>
       <c r="I48" t="n">
-        <v>59.554712086896</v>
+        <v>59.49048128636552</v>
       </c>
       <c r="J48" t="n">
         <v>66.6685827765011</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6596750360173439</v>
+        <v>0.6581650862313918</v>
       </c>
       <c r="L48" t="n">
-        <v>56.57729691777521</v>
+        <v>56.56539215587046</v>
       </c>
       <c r="M48" t="n">
-        <v>42.43893604985141</v>
+        <v>42.4340340890671</v>
       </c>
       <c r="N48" t="n">
-        <v>31.54596145943689</v>
+        <v>31.54386061910075</v>
       </c>
       <c r="O48" t="n">
-        <v>-0.2353425541805656</v>
+        <v>-0.2433197621577765</v>
       </c>
       <c r="P48" t="n">
-        <v>35.2934238914902</v>
+        <v>35.14714807694265</v>
       </c>
       <c r="Q48" t="n">
-        <v>-64.70657610850979</v>
+        <v>-64.85285192305734</v>
       </c>
       <c r="R48" t="n">
-        <v>36.54446601791349</v>
+        <v>36.39222311777953</v>
       </c>
       <c r="S48" t="n">
-        <v>128.0753145658755</v>
+        <v>127.6433864466867</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -27013,52 +26997,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4450.2001953125</v>
+        <v>4448.60009765625</v>
       </c>
       <c r="E53" t="n">
-        <v>9.905907188820052</v>
+        <v>9.866389824031362</v>
       </c>
       <c r="F53" t="n">
-        <v>-4.247351282295075</v>
+        <v>-4.281779753390447</v>
       </c>
       <c r="G53" t="n">
-        <v>67.48965733204741</v>
+        <v>67.42943536530861</v>
       </c>
       <c r="H53" t="n">
-        <v>151.3101464085423</v>
+        <v>151.2197862542545</v>
       </c>
       <c r="I53" t="n">
-        <v>64.61597610717538</v>
+        <v>64.59585519012705</v>
       </c>
       <c r="J53" t="n">
         <v>81.24586303544928</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6968954262802877</v>
+        <v>0.696366040377339</v>
       </c>
       <c r="L53" t="n">
-        <v>3921.760965627648</v>
+        <v>3921.608575374672</v>
       </c>
       <c r="M53" t="n">
-        <v>3130.977376616684</v>
+        <v>3130.914627688988</v>
       </c>
       <c r="N53" t="n">
-        <v>2390.260857492907</v>
+        <v>2390.233965095323</v>
       </c>
       <c r="O53" t="n">
-        <v>-39.5106144858903</v>
+        <v>-39.6127289801924</v>
       </c>
       <c r="P53" t="n">
-        <v>51.08298425317873</v>
+        <v>51.01408284274982</v>
       </c>
       <c r="Q53" t="n">
-        <v>-48.91701574682127</v>
+        <v>-48.98591715725018</v>
       </c>
       <c r="R53" t="n">
-        <v>31.38180591341519</v>
+        <v>31.34456249910081</v>
       </c>
       <c r="S53" t="n">
-        <v>69.26062216489002</v>
+        <v>69.19976343653286</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -27389,52 +27373,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>87.87999725341797</v>
+        <v>87.84999847412109</v>
       </c>
       <c r="E57" t="n">
-        <v>-2.485580808805532</v>
+        <v>-2.51886840132951</v>
       </c>
       <c r="F57" t="n">
-        <v>-25.74567098736873</v>
+        <v>-25.77101849871951</v>
       </c>
       <c r="G57" t="n">
-        <v>20.48258063058501</v>
+        <v>20.44145260989298</v>
       </c>
       <c r="H57" t="n">
-        <v>16.97058494091712</v>
+        <v>16.93065577760877</v>
       </c>
       <c r="I57" t="n">
-        <v>53.28724972489348</v>
+        <v>53.27414654611403</v>
       </c>
       <c r="J57" t="n">
         <v>23.79402312962622</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6729394342108349</v>
+        <v>0.6725090845144677</v>
       </c>
       <c r="L57" t="n">
-        <v>81.37982165273593</v>
+        <v>81.37696462613623</v>
       </c>
       <c r="M57" t="n">
-        <v>78.71045067921045</v>
+        <v>78.70927425649293</v>
       </c>
       <c r="N57" t="n">
-        <v>72.36943656623522</v>
+        <v>72.36893238507056</v>
       </c>
       <c r="O57" t="n">
-        <v>2.132439677765735</v>
+        <v>2.130525225753634</v>
       </c>
       <c r="P57" t="n">
-        <v>43.27693265264367</v>
+        <v>43.23241086499198</v>
       </c>
       <c r="Q57" t="n">
-        <v>-56.72306734735633</v>
+        <v>-56.76758913500802</v>
       </c>
       <c r="R57" t="n">
-        <v>49.25956551691252</v>
+        <v>49.20632645986981</v>
       </c>
       <c r="S57" t="n">
-        <v>17.73847531087431</v>
+        <v>17.69828401995499</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -27481,52 +27465,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1763.800048828125</v>
+        <v>1764.099975585938</v>
       </c>
       <c r="E58" t="n">
-        <v>6.877537213950657</v>
+        <v>6.895711288297046</v>
       </c>
       <c r="F58" t="n">
-        <v>-9.548715444711542</v>
+        <v>-9.53333458533654</v>
       </c>
       <c r="G58" t="n">
-        <v>85.76093194609004</v>
+        <v>85.79251980894549</v>
       </c>
       <c r="H58" t="n">
-        <v>64.76413347296824</v>
+        <v>64.79215091881714</v>
       </c>
       <c r="I58" t="n">
-        <v>57.17871261920904</v>
+        <v>57.18556174780583</v>
       </c>
       <c r="J58" t="n">
         <v>70.09463525266655</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6218133661326974</v>
+        <v>0.6219784822885914</v>
       </c>
       <c r="L58" t="n">
-        <v>1606.347147299579</v>
+        <v>1606.375711752704</v>
       </c>
       <c r="M58" t="n">
-        <v>1327.402196326844</v>
+        <v>1327.413958160484</v>
       </c>
       <c r="N58" t="n">
-        <v>1145.16175642241</v>
+        <v>1145.166797208256</v>
       </c>
       <c r="O58" t="n">
-        <v>-15.6138129115842</v>
+        <v>-15.5946722865842</v>
       </c>
       <c r="P58" t="n">
-        <v>30.93516766662304</v>
+        <v>30.95419613807994</v>
       </c>
       <c r="Q58" t="n">
-        <v>-69.06483233337696</v>
+        <v>-69.04580386192005</v>
       </c>
       <c r="R58" t="n">
-        <v>26.25865380297376</v>
+        <v>26.27456212103062</v>
       </c>
       <c r="S58" t="n">
-        <v>97.29307033871643</v>
+        <v>97.32661919305789</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -27665,52 +27649,52 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>159.302001953125</v>
+        <v>159.2319946289062</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5499938891684764</v>
+        <v>-0.5936984800461564</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.3372110117666804</v>
+        <v>-0.3810091128307103</v>
       </c>
       <c r="G60" t="n">
-        <v>5.376590020791649</v>
+        <v>5.3302809159957</v>
       </c>
       <c r="H60" t="n">
-        <v>44.11905430436296</v>
+        <v>44.05571932277401</v>
       </c>
       <c r="I60" t="n">
-        <v>58.94510156105067</v>
+        <v>58.83721396456278</v>
       </c>
       <c r="J60" t="n">
         <v>26.49181088905198</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7480388817258341</v>
+        <v>0.7454540543856292</v>
       </c>
       <c r="L60" t="n">
-        <v>154.8733792681815</v>
+        <v>154.8667119039701</v>
       </c>
       <c r="M60" t="n">
-        <v>146.5198223309408</v>
+        <v>146.5170769456773</v>
       </c>
       <c r="N60" t="n">
-        <v>132.4702306768395</v>
+        <v>132.4692160779377</v>
       </c>
       <c r="O60" t="n">
-        <v>0.373160492958069</v>
+        <v>0.3686927890763134</v>
       </c>
       <c r="P60" t="n">
-        <v>78.02573433471841</v>
+        <v>77.69681432221543</v>
       </c>
       <c r="Q60" t="n">
-        <v>-21.97426566528159</v>
+        <v>-22.30318567778457</v>
       </c>
       <c r="R60" t="n">
-        <v>67.16770646802752</v>
+        <v>66.87454042482354</v>
       </c>
       <c r="S60" t="n">
-        <v>1.46947795005532</v>
+        <v>1.424885876170112</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -27724,7 +27708,7 @@
         </is>
       </c>
       <c r="W60" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="X60" t="n">
         <v>67.2</v>
@@ -28037,52 +28021,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>82.33999633789062</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E64" t="n">
-        <v>-2.751862385074755</v>
+        <v>-2.799096691201719</v>
       </c>
       <c r="F64" t="n">
-        <v>-18.78082603211495</v>
+        <v>-18.82027492461476</v>
       </c>
       <c r="G64" t="n">
-        <v>21.08822990866268</v>
+        <v>21.02941625258501</v>
       </c>
       <c r="H64" t="n">
-        <v>12.07294810101081</v>
+        <v>12.01851324941381</v>
       </c>
       <c r="I64" t="n">
-        <v>53.65435711243139</v>
+        <v>53.634304191136</v>
       </c>
       <c r="J64" t="n">
         <v>21.8831417623618</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6946005206932256</v>
+        <v>0.693931920476632</v>
       </c>
       <c r="L64" t="n">
-        <v>75.85823892629388</v>
+        <v>75.85443004190027</v>
       </c>
       <c r="M64" t="n">
-        <v>73.60685067300457</v>
+        <v>73.6052823088425</v>
       </c>
       <c r="N64" t="n">
-        <v>67.87597988079847</v>
+        <v>67.875307724729</v>
       </c>
       <c r="O64" t="n">
-        <v>2.129274963414818</v>
+        <v>2.12672268532543</v>
       </c>
       <c r="P64" t="n">
-        <v>42.41859717443911</v>
+        <v>42.3565920833267</v>
       </c>
       <c r="Q64" t="n">
-        <v>-57.58140282556089</v>
+        <v>-57.6434079166733</v>
       </c>
       <c r="R64" t="n">
-        <v>47.49647875170321</v>
+        <v>47.42116358119581</v>
       </c>
       <c r="S64" t="n">
-        <v>14.80757799279271</v>
+        <v>14.75181490655162</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -29685,52 +29669,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.350858449935913</v>
+        <v>1.350803732872009</v>
       </c>
       <c r="E82" t="n">
-        <v>0.3539276135005931</v>
+        <v>0.3498627373690555</v>
       </c>
       <c r="F82" t="n">
-        <v>2.549070392373087</v>
+        <v>2.544916601101921</v>
       </c>
       <c r="G82" t="n">
-        <v>6.393612978046437</v>
+        <v>6.38930346203419</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.413982887043098</v>
+        <v>-2.417935647848457</v>
       </c>
       <c r="I82" t="n">
-        <v>55.08211417295613</v>
+        <v>55.07399072106924</v>
       </c>
       <c r="J82" t="n">
         <v>19.76960125542902</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6436087272597922</v>
+        <v>0.6432309732216114</v>
       </c>
       <c r="L82" t="n">
-        <v>1.32968541908166</v>
+        <v>1.329680207932717</v>
       </c>
       <c r="M82" t="n">
-        <v>1.309670828268967</v>
+        <v>1.309668682501755</v>
       </c>
       <c r="N82" t="n">
-        <v>1.337611523375639</v>
+        <v>1.337610730374713</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.001547433672382248</v>
+        <v>-0.001550925587571431</v>
       </c>
       <c r="P82" t="n">
-        <v>59.50277079092449</v>
+        <v>59.43724822346764</v>
       </c>
       <c r="Q82" t="n">
-        <v>-40.49722920907552</v>
+        <v>-40.56275177653236</v>
       </c>
       <c r="R82" t="n">
-        <v>38.58688364702147</v>
+        <v>38.55483182553233</v>
       </c>
       <c r="S82" t="n">
-        <v>7.645854016363907</v>
+        <v>7.641493777825614</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -29869,52 +29853,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1386</v>
+        <v>1388.5</v>
       </c>
       <c r="E84" t="n">
-        <v>8.654752785123797</v>
+        <v>8.850738991446171</v>
       </c>
       <c r="F84" t="n">
-        <v>-5.79118773787407</v>
+        <v>-5.621258422826947</v>
       </c>
       <c r="G84" t="n">
-        <v>39.97172115871626</v>
+        <v>40.22419540323052</v>
       </c>
       <c r="H84" t="n">
-        <v>-50.09721146636452</v>
+        <v>-50.00719922153473</v>
       </c>
       <c r="I84" t="n">
-        <v>52.14182107114132</v>
+        <v>52.21443882646062</v>
       </c>
       <c r="J84" t="n">
         <v>56.80503147328202</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5936635291530695</v>
+        <v>0.5959144534471759</v>
       </c>
       <c r="L84" t="n">
-        <v>1330.296948593853</v>
+        <v>1330.535043831948</v>
       </c>
       <c r="M84" t="n">
-        <v>1363.240680902751</v>
+        <v>1363.338720118437</v>
       </c>
       <c r="N84" t="n">
-        <v>1361.606651842142</v>
+        <v>1361.648668648865</v>
       </c>
       <c r="O84" t="n">
-        <v>1.644181326869585</v>
+        <v>1.803725486413612</v>
       </c>
       <c r="P84" t="n">
-        <v>27.94374733788177</v>
+        <v>28.17354789164724</v>
       </c>
       <c r="Q84" t="n">
-        <v>-72.05625266211823</v>
+        <v>-71.82645210835275</v>
       </c>
       <c r="R84" t="n">
-        <v>13.41551717886666</v>
+        <v>13.65330620784576</v>
       </c>
       <c r="S84" t="n">
-        <v>53.50536742973793</v>
+        <v>53.78225301312489</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -30333,52 +30317,52 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>99.82099914550781</v>
+        <v>99.80699920654297</v>
       </c>
       <c r="E89" t="n">
-        <v>0.021038169446852</v>
+        <v>0.007010174921062706</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.1390555624629197</v>
+        <v>-0.1530611037725116</v>
       </c>
       <c r="G89" t="n">
-        <v>-5.597691354115097</v>
+        <v>-5.610931319357848</v>
       </c>
       <c r="H89" t="n">
-        <v>7.984634908226074</v>
+        <v>7.969490015760594</v>
       </c>
       <c r="I89" t="n">
-        <v>48.2952987258393</v>
+        <v>48.26163604710534</v>
       </c>
       <c r="J89" t="n">
         <v>28.18218733317379</v>
       </c>
       <c r="K89" t="n">
-        <v>0.4805704745384063</v>
+        <v>0.4795206193144286</v>
       </c>
       <c r="L89" t="n">
-        <v>100.1285769977874</v>
+        <v>100.127243670267</v>
       </c>
       <c r="M89" t="n">
-        <v>100.7461870076959</v>
+        <v>100.7456379904816</v>
       </c>
       <c r="N89" t="n">
-        <v>99.4403162575445</v>
+        <v>99.44008096445265</v>
       </c>
       <c r="O89" t="n">
-        <v>0.1983857744127824</v>
+        <v>0.1974923310144512</v>
       </c>
       <c r="P89" t="n">
-        <v>68.3359375</v>
+        <v>68.1119384765625</v>
       </c>
       <c r="Q89" t="n">
-        <v>-31.6640625</v>
+        <v>-31.8880615234375</v>
       </c>
       <c r="R89" t="n">
-        <v>-9.194487716678333</v>
+        <v>-9.285857062551569</v>
       </c>
       <c r="S89" t="n">
-        <v>-7.990597187721715</v>
+        <v>-8.003501546870496</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -30975,52 +30959,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>64089.75</v>
+        <v>63987</v>
       </c>
       <c r="E96" t="n">
-        <v>2.031408705262616</v>
+        <v>1.867829860837955</v>
       </c>
       <c r="F96" t="n">
-        <v>-6.072638639667394</v>
+        <v>-6.223224909387182</v>
       </c>
       <c r="G96" t="n">
-        <v>-33.55067065441527</v>
+        <v>-33.65720358035521</v>
       </c>
       <c r="H96" t="n">
-        <v>82.90017428326371</v>
+        <v>82.60694497736681</v>
       </c>
       <c r="I96" t="n">
-        <v>43.86920366013594</v>
+        <v>43.81075032184185</v>
       </c>
       <c r="J96" t="n">
         <v>30.35693503158459</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1858303775221952</v>
+        <v>0.1846357060202676</v>
       </c>
       <c r="L96" t="n">
-        <v>76839.58998010276</v>
+        <v>76829.80426581705</v>
       </c>
       <c r="M96" t="n">
-        <v>65846.77262657437</v>
+        <v>65842.74321480967</v>
       </c>
       <c r="N96" t="n">
-        <v>49897.50507659349</v>
+        <v>49895.42931901773</v>
       </c>
       <c r="O96" t="n">
-        <v>-5697.507847494236</v>
+        <v>-5704.065112451498</v>
       </c>
       <c r="P96" t="n">
-        <v>9.265092980890904</v>
+        <v>9.114984080033429</v>
       </c>
       <c r="Q96" t="n">
-        <v>-90.7349070191091</v>
+        <v>-90.88501591996658</v>
       </c>
       <c r="R96" t="n">
-        <v>-67.7814655292259</v>
+        <v>-67.8665916557779</v>
       </c>
       <c r="S96" t="n">
-        <v>-31.40287206104756</v>
+        <v>-31.51284838168741</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -31251,52 +31235,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.019600033760071</v>
+        <v>1.019000053405762</v>
       </c>
       <c r="E99" t="n">
-        <v>-3.85983697697454</v>
+        <v>-3.916410346103572</v>
       </c>
       <c r="F99" t="n">
-        <v>-23.92514676142034</v>
+        <v>-23.96991276366512</v>
       </c>
       <c r="G99" t="n">
-        <v>-47.55470301963967</v>
+        <v>-47.58556428564815</v>
       </c>
       <c r="H99" t="n">
-        <v>44.34280548231037</v>
+        <v>44.25786742355427</v>
       </c>
       <c r="I99" t="n">
-        <v>40.39622392960196</v>
+        <v>40.38740428552422</v>
       </c>
       <c r="J99" t="n">
         <v>35.88651149710995</v>
       </c>
       <c r="K99" t="n">
-        <v>0.1470001030567175</v>
+        <v>0.1468099511749442</v>
       </c>
       <c r="L99" t="n">
-        <v>1.540329154884912</v>
+        <v>1.540272013898787</v>
       </c>
       <c r="M99" t="n">
-        <v>1.307329862808515</v>
+        <v>1.30730633416717</v>
       </c>
       <c r="N99" t="n">
-        <v>1.037204848698222</v>
+        <v>1.037192727882984</v>
       </c>
       <c r="O99" t="n">
-        <v>-0.1884626077624197</v>
+        <v>-0.1885008971069684</v>
       </c>
       <c r="P99" t="n">
-        <v>0.3729295823457755</v>
+        <v>0.3502069864600778</v>
       </c>
       <c r="Q99" t="n">
-        <v>-99.62707041765422</v>
+        <v>-99.64979301353992</v>
       </c>
       <c r="R99" t="n">
-        <v>-67.81749776693633</v>
+        <v>-67.83018180335523</v>
       </c>
       <c r="S99" t="n">
-        <v>-50.98378291764898</v>
+        <v>-51.01262635264134</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -31527,52 +31511,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>76.33000183105469</v>
+        <v>76.36000061035156</v>
       </c>
       <c r="E102" t="n">
-        <v>4.863768224705778</v>
+        <v>4.904981181128543</v>
       </c>
       <c r="F102" t="n">
-        <v>-8.153949396535188</v>
+        <v>-8.117852588789242</v>
       </c>
       <c r="G102" t="n">
-        <v>-67.89400192827391</v>
+        <v>-67.88138381315332</v>
       </c>
       <c r="H102" t="n">
-        <v>114.673006828312</v>
+        <v>114.7573763815461</v>
       </c>
       <c r="I102" t="n">
-        <v>41.13602501706706</v>
+        <v>41.14332463019267</v>
       </c>
       <c r="J102" t="n">
         <v>25.2501758559911</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2179639249342612</v>
+        <v>0.2180967552060976</v>
       </c>
       <c r="L102" t="n">
-        <v>113.6206671589543</v>
+        <v>113.623524185554</v>
       </c>
       <c r="M102" t="n">
-        <v>113.3408253364757</v>
+        <v>113.342363735414</v>
       </c>
       <c r="N102" t="n">
-        <v>92.49900264885439</v>
+        <v>92.49979209041483</v>
       </c>
       <c r="O102" t="n">
-        <v>-11.49544945913296</v>
+        <v>-11.49353500712086</v>
       </c>
       <c r="P102" t="n">
-        <v>8.255021260345744</v>
+        <v>8.270581182071266</v>
       </c>
       <c r="Q102" t="n">
-        <v>-91.74497873965426</v>
+        <v>-91.72941881792873</v>
       </c>
       <c r="R102" t="n">
-        <v>-89.24546786261638</v>
+        <v>-89.23264145976722</v>
       </c>
       <c r="S102" t="n">
-        <v>-67.04770726785767</v>
+        <v>-67.03475654686612</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -31807,52 +31791,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.193450003862381</v>
+        <v>0.1926800012588501</v>
       </c>
       <c r="E105" t="n">
-        <v>15.17349423649468</v>
+        <v>14.71506110830028</v>
       </c>
       <c r="F105" t="n">
-        <v>-19.91737225155309</v>
+        <v>-20.23613074538991</v>
       </c>
       <c r="G105" t="n">
-        <v>-82.07039726009387</v>
+        <v>-82.14176371403214</v>
       </c>
       <c r="H105" t="n">
-        <v>-86.01706368860576</v>
+        <v>-86.07272094965414</v>
       </c>
       <c r="I105" t="n">
-        <v>38.89423537488427</v>
+        <v>38.85257142778556</v>
       </c>
       <c r="J105" t="n">
         <v>31.07283787478976</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2132106971196107</v>
+        <v>0.2125434483104486</v>
       </c>
       <c r="L105" t="n">
-        <v>0.3870340818687358</v>
+        <v>0.3869607482874472</v>
       </c>
       <c r="M105" t="n">
-        <v>0.4805345279701701</v>
+        <v>0.4805043317896395</v>
       </c>
       <c r="N105" t="n">
-        <v>0.4718851500880903</v>
+        <v>0.4718695944799381</v>
       </c>
       <c r="O105" t="n">
-        <v>-0.04169662388171604</v>
+        <v>-0.04174576364900685</v>
       </c>
       <c r="P105" t="n">
-        <v>6.237974076699722</v>
+        <v>6.150251383218846</v>
       </c>
       <c r="Q105" t="n">
-        <v>-93.76202592330027</v>
+        <v>-93.84974861678116</v>
       </c>
       <c r="R105" t="n">
-        <v>-86.29988217877033</v>
+        <v>-86.36084439178013</v>
       </c>
       <c r="S105" t="n">
-        <v>-77.07300027945692</v>
+        <v>-77.16425822271614</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -31895,52 +31879,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1878.260009765625</v>
+        <v>1874.31005859375</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9629425390654145</v>
+        <v>0.7506190635483634</v>
       </c>
       <c r="F106" t="n">
-        <v>-10.75912739817316</v>
+        <v>-10.9467995455223</v>
       </c>
       <c r="G106" t="n">
-        <v>-49.31437212559365</v>
+        <v>-49.42096320147176</v>
       </c>
       <c r="H106" t="n">
-        <v>-17.42269963324394</v>
+        <v>-17.59635839329743</v>
       </c>
       <c r="I106" t="n">
-        <v>43.40658274197425</v>
+        <v>43.36215512974873</v>
       </c>
       <c r="J106" t="n">
         <v>14.06284679828849</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2840148904781798</v>
+        <v>0.2829600259375427</v>
       </c>
       <c r="L106" t="n">
-        <v>2448.392973589053</v>
+        <v>2448.01678776316</v>
       </c>
       <c r="M106" t="n">
-        <v>2393.965549314154</v>
+        <v>2393.810649268199</v>
       </c>
       <c r="N106" t="n">
-        <v>1999.137828299888</v>
+        <v>1999.058031306516</v>
       </c>
       <c r="O106" t="n">
-        <v>-165.9335274831065</v>
+        <v>-166.1856041390897</v>
       </c>
       <c r="P106" t="n">
-        <v>10.78415357678388</v>
+        <v>10.66957014570099</v>
       </c>
       <c r="Q106" t="n">
-        <v>-89.21584642321612</v>
+        <v>-89.33042985429901</v>
       </c>
       <c r="R106" t="n">
-        <v>-77.95602337129405</v>
+        <v>-78.07372967100821</v>
       </c>
       <c r="S106" t="n">
-        <v>-43.63864601228566</v>
+        <v>-43.75717305064817</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -31966,7 +31950,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 14)</t>
+          <t>mercato laterale — ATR basso (ADX 14); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -32065,83 +32049,83 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Natural Gas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>8.284000396728516</v>
+        <v>2.778000116348267</v>
       </c>
       <c r="E108" t="n">
-        <v>1.503504781286824</v>
+        <v>1.128508830210118</v>
       </c>
       <c r="F108" t="n">
-        <v>-5.622808882690567</v>
+        <v>-3.675448830818961</v>
       </c>
       <c r="G108" t="n">
-        <v>-56.45193747779709</v>
+        <v>-17.39517735138292</v>
       </c>
       <c r="H108" t="n">
-        <v>-57.51192481985473</v>
+        <v>-23.89040975987658</v>
       </c>
       <c r="I108" t="n">
-        <v>42.13077363799381</v>
+        <v>45.92988193677788</v>
       </c>
       <c r="J108" t="n">
-        <v>20.61208013114089</v>
+        <v>48.09674867775514</v>
       </c>
       <c r="K108" t="n">
-        <v>0.2524992731980692</v>
+        <v>0.229245021364071</v>
       </c>
       <c r="L108" t="n">
-        <v>11.71217514502209</v>
+        <v>3.237552352466108</v>
       </c>
       <c r="M108" t="n">
-        <v>12.42839402153549</v>
+        <v>3.331940275729834</v>
       </c>
       <c r="N108" t="n">
-        <v>10.78612803668484</v>
+        <v>3.301793889174497</v>
       </c>
       <c r="O108" t="n">
-        <v>-0.8567968022577437</v>
+        <v>-0.09012564011974025</v>
       </c>
       <c r="P108" t="n">
-        <v>6.090885439646017</v>
+        <v>5.520210904071724</v>
       </c>
       <c r="Q108" t="n">
-        <v>-93.90911456035398</v>
+        <v>-94.47978909592828</v>
       </c>
       <c r="R108" t="n">
-        <v>-87.09647945237012</v>
+        <v>-70.09362109895565</v>
       </c>
       <c r="S108" t="n">
-        <v>-58.58282610859931</v>
+        <v>-23.53426382863892</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="n">
         <v>33.6</v>
       </c>
       <c r="X108" t="n">
-        <v>66</v>
+        <v>78.5</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -32150,73 +32134,73 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21)</t>
+          <t>trend molto direzionale (ADX 48); hammer — segnale di rimbalzo da supporto</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Natural Gas</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.776000022888184</v>
+        <v>8.300999641418457</v>
       </c>
       <c r="E109" t="n">
-        <v>1.055698729177745</v>
+        <v>1.711795803984661</v>
       </c>
       <c r="F109" t="n">
-        <v>-3.744800197546816</v>
+        <v>-5.429141465003562</v>
       </c>
       <c r="G109" t="n">
-        <v>-17.45465084261084</v>
+        <v>-56.36257435187544</v>
       </c>
       <c r="H109" t="n">
-        <v>-23.945206839543</v>
+        <v>-57.42473684885015</v>
       </c>
       <c r="I109" t="n">
-        <v>45.91307383310952</v>
+        <v>42.16718384310372</v>
       </c>
       <c r="J109" t="n">
-        <v>48.09674867775514</v>
+        <v>20.61208013114089</v>
       </c>
       <c r="K109" t="n">
-        <v>0.2284868828110785</v>
+        <v>0.2532346970487732</v>
       </c>
       <c r="L109" t="n">
-        <v>3.237361867374672</v>
+        <v>11.71379412070685</v>
       </c>
       <c r="M109" t="n">
-        <v>3.331861840692183</v>
+        <v>12.42906065858216</v>
       </c>
       <c r="N109" t="n">
-        <v>3.301760274158361</v>
+        <v>10.78647145576949</v>
       </c>
       <c r="O109" t="n">
-        <v>-0.09025328141177963</v>
+        <v>-0.8557119501749658</v>
       </c>
       <c r="P109" t="n">
-        <v>5.482784006200311</v>
+        <v>6.172956431721781</v>
       </c>
       <c r="Q109" t="n">
-        <v>-94.5172159937997</v>
+        <v>-93.82704356827821</v>
       </c>
       <c r="R109" t="n">
-        <v>-70.14881546271269</v>
+        <v>-87.01708569709473</v>
       </c>
       <c r="S109" t="n">
-        <v>-23.58931732483452</v>
+        <v>-58.49783568855733</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -32224,12 +32208,16 @@
         </is>
       </c>
       <c r="U109" t="inlineStr"/>
-      <c r="V109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W109" t="n">
-        <v>33.2</v>
+        <v>33.6</v>
       </c>
       <c r="X109" t="n">
-        <v>72.5</v>
+        <v>66</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -32238,7 +32226,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 48)</t>
+          <t>trend in sviluppo (ADX 21)</t>
         </is>
       </c>
     </row>
@@ -32721,12 +32709,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AVAX</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Avalanche</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -32735,69 +32723,69 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6.456999778747559</v>
+        <v>0.8098999857902527</v>
       </c>
       <c r="E115" t="n">
-        <v>1.235151215657493</v>
+        <v>6.839635659752208</v>
       </c>
       <c r="F115" t="n">
-        <v>-27.52524917341819</v>
+        <v>-35.29186568692347</v>
       </c>
       <c r="G115" t="n">
-        <v>-85.61686953770081</v>
+        <v>-90.96826383818033</v>
       </c>
       <c r="H115" t="n">
-        <v>-45.9916003924603</v>
+        <v>-95.06224632169364</v>
       </c>
       <c r="I115" t="n">
-        <v>38.67943737685291</v>
+        <v>34.05057908631323</v>
       </c>
       <c r="J115" t="n">
-        <v>17.78710309672154</v>
+        <v>37.34832998198571</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2051368975205141</v>
+        <v>0.2011118873561748</v>
       </c>
       <c r="L115" t="n">
-        <v>14.75037492948701</v>
+        <v>2.583326270485096</v>
       </c>
       <c r="M115" t="n">
-        <v>18.75499306490858</v>
+        <v>4.181013090304554</v>
       </c>
       <c r="N115" t="n">
-        <v>20.45853306761902</v>
+        <v>6.265978744388248</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.9766418138518373</v>
+        <v>-0.02149094471571811</v>
       </c>
       <c r="P115" t="n">
-        <v>2.52653195707381</v>
+        <v>1.491584596739472</v>
       </c>
       <c r="Q115" t="n">
-        <v>-97.47346804292619</v>
+        <v>-98.50841540326053</v>
       </c>
       <c r="R115" t="n">
-        <v>-68.43462844881114</v>
+        <v>-63.16259575300078</v>
       </c>
       <c r="S115" t="n">
-        <v>-71.13389337542175</v>
+        <v>-82.81550649374827</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>Doji, Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W115" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="X115" t="n">
-        <v>78.7</v>
+        <v>70.8</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -32806,19 +32794,19 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>AVAX</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Avalanche</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -32827,69 +32815,69 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8048999905586243</v>
+        <v>6.435999870300293</v>
       </c>
       <c r="E116" t="n">
-        <v>6.180050923093106</v>
+        <v>0.9059071425554288</v>
       </c>
       <c r="F116" t="n">
-        <v>-35.69134755961083</v>
+        <v>-27.76095665123257</v>
       </c>
       <c r="G116" t="n">
-        <v>-91.02402212751819</v>
+        <v>-85.66364736536738</v>
       </c>
       <c r="H116" t="n">
-        <v>-95.09273001755689</v>
+        <v>-46.16725030511395</v>
       </c>
       <c r="I116" t="n">
-        <v>34.01337406827352</v>
+        <v>38.65364580816925</v>
       </c>
       <c r="J116" t="n">
-        <v>37.34832998198571</v>
+        <v>17.78710309672154</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2004218389852192</v>
+        <v>0.2045710621443485</v>
       </c>
       <c r="L116" t="n">
-        <v>2.582850080463035</v>
+        <v>14.74837493820632</v>
       </c>
       <c r="M116" t="n">
-        <v>4.180742820292034</v>
+        <v>18.75385793472224</v>
       </c>
       <c r="N116" t="n">
-        <v>6.265839855631813</v>
+        <v>20.45794973682881</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.0218100327305002</v>
+        <v>-0.9779819789493258</v>
       </c>
       <c r="P116" t="n">
-        <v>1.370398386483752</v>
+        <v>2.457034208183853</v>
       </c>
       <c r="Q116" t="n">
-        <v>-98.62960161351624</v>
+        <v>-97.54296579181614</v>
       </c>
       <c r="R116" t="n">
-        <v>-63.20935693087302</v>
+        <v>-68.47663278105753</v>
       </c>
       <c r="S116" t="n">
-        <v>-82.92159661240083</v>
+        <v>-71.22777375595706</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Doji, Bullish Harami</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr"/>
       <c r="W116" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="X116" t="n">
-        <v>70.8</v>
+        <v>79.2</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -32898,7 +32886,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -33248,7 +33236,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10/08/2026 20:43:13</t>
+          <t>10/08/2026 21:41:53</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33288,13 +33276,13 @@
         <v>15.46000003814697</v>
       </c>
       <c r="N2" t="n">
-        <v>99.82099914550781</v>
+        <v>99.80699920654297</v>
       </c>
       <c r="O2" t="n">
-        <v>4450.2001953125</v>
+        <v>4448.60009765625</v>
       </c>
       <c r="P2" t="n">
-        <v>82.33999633789062</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="Q2" t="n">
         <v>4.590278849989482</v>
@@ -33311,7 +33299,7 @@
         <v>4.608931281696762</v>
       </c>
       <c r="U2" t="n">
-        <v>4.035132350518991</v>
+        <v>4.032778793475087</v>
       </c>
       <c r="V2" t="n">
         <v>0.1767539181906337</v>
@@ -33335,10 +33323,10 @@
         <v>0.5875869446908326</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5739890539135348</v>
+        <v>0.5737826725150423</v>
       </c>
       <c r="AD2" t="n">
-        <v>-9.829216678072205</v>
+        <v>-9.861638154123465</v>
       </c>
       <c r="AE2" t="n">
         <v>-3.997841205503305</v>
@@ -33362,7 +33350,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.783967254933362</v>
+        <v>2.783574995426044</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33461,10 +33449,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67.08923234195062</v>
+        <v>67.08909192326639</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08421424843719365</v>
+        <v>0.0842086316898244</v>
       </c>
       <c r="D2" t="n">
         <v>66.37931034482759</v>
@@ -33473,7 +33461,7 @@
         <v>26.79422095860699</v>
       </c>
       <c r="F2" t="n">
-        <v>13.97758075913531</v>
+        <v>13.97758075913526</v>
       </c>
     </row>
   </sheetData>
@@ -33844,13 +33832,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.893</v>
+        <v>0.884</v>
       </c>
       <c r="D17" t="n">
-        <v>0.907</v>
+        <v>0.903</v>
       </c>
       <c r="E17" t="n">
-        <v>0.919</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="18">
@@ -34086,64 +34074,64 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.714</v>
+        <v>-0.888</v>
       </c>
       <c r="D7" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.411</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.714</v>
       </c>
       <c r="D8" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.487</v>
+        <v>-0.411</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.888</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>-0.6860000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.57</v>
+        <v>-0.487</v>
       </c>
     </row>
     <row r="10">

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1057,7 +1057,7 @@
         <v>59.45189214237357</v>
       </c>
       <c r="J7" t="n">
-        <v>45.48506481856237</v>
+        <v>45.49387701016571</v>
       </c>
       <c r="K7" t="n">
         <v>0.6349690574998039</v>
@@ -1081,7 +1081,7 @@
         <v>-30.88644465945194</v>
       </c>
       <c r="R7" t="n">
-        <v>36.17999935045594</v>
+        <v>36.20298872690184</v>
       </c>
       <c r="S7" t="n">
         <v>16.52470469000078</v>
@@ -1097,7 +1097,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>73.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>72</v>
       </c>
       <c r="X15" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>71.5</v>
       </c>
       <c r="X17" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2331,52 +2331,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62.59000015258789</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="E21" t="n">
-        <v>1.098369095221718</v>
+        <v>1.082219326916345</v>
       </c>
       <c r="F21" t="n">
-        <v>4.004652434680755</v>
+        <v>3.988038407624428</v>
       </c>
       <c r="G21" t="n">
-        <v>8.512482353387796</v>
+        <v>8.495148231542604</v>
       </c>
       <c r="H21" t="n">
-        <v>3.317923837537484</v>
+        <v>3.301419510645753</v>
       </c>
       <c r="I21" t="n">
-        <v>69.70080469550281</v>
+        <v>69.67052649108493</v>
       </c>
       <c r="J21" t="n">
         <v>16.71774063606276</v>
       </c>
       <c r="K21" t="n">
-        <v>1.04087288397453</v>
+        <v>1.039682943952847</v>
       </c>
       <c r="L21" t="n">
-        <v>59.4280122561169</v>
+        <v>59.4270600350185</v>
       </c>
       <c r="M21" t="n">
-        <v>58.04584444220059</v>
+        <v>58.04545235116007</v>
       </c>
       <c r="N21" t="n">
-        <v>54.15483481283852</v>
+        <v>54.15473532705212</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3201667765963807</v>
+        <v>0.319528707074028</v>
       </c>
       <c r="P21" t="n">
-        <v>98.38419824921138</v>
+        <v>98.20469515978583</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.615801750788622</v>
+        <v>-1.795304840214171</v>
       </c>
       <c r="R21" t="n">
-        <v>101.4529146277792</v>
+        <v>101.35497825868</v>
       </c>
       <c r="S21" t="n">
-        <v>8.025546489632408</v>
+        <v>8.008290152438446</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>70.7</v>
       </c>
       <c r="X23" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>-5.502503435584083</v>
       </c>
       <c r="R26" t="n">
-        <v>76.609654232198</v>
+        <v>76.73747204935968</v>
       </c>
       <c r="S26" t="n">
         <v>6.847287847059813</v>
@@ -2857,7 +2857,7 @@
         <v>70.40000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2939,11 +2939,7 @@
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
         <v>70.2</v>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 22); doji — indecisione del mercato; vicino alla resistenza dei 20g (566.01)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 22); vicino alla resistenza dei 20g (566.01)</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3037,7 @@
         <v>70</v>
       </c>
       <c r="X28" t="n">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3163,52 +3159,52 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6.611499786376953</v>
+        <v>6.612500190734863</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1818259983360049</v>
+        <v>0.1969847881038822</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2577863577212236</v>
+        <v>0.2729566412616347</v>
       </c>
       <c r="G30" t="n">
-        <v>6.294212369631613</v>
+        <v>6.310296041523156</v>
       </c>
       <c r="H30" t="n">
-        <v>5.412945779462652</v>
+        <v>5.428896104463843</v>
       </c>
       <c r="I30" t="n">
-        <v>60.16679657438586</v>
+        <v>60.22158029545299</v>
       </c>
       <c r="J30" t="n">
         <v>28.41905066473698</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6972092755844057</v>
+        <v>0.6989092740677343</v>
       </c>
       <c r="L30" t="n">
-        <v>6.512277483477563</v>
+        <v>6.512372760083078</v>
       </c>
       <c r="M30" t="n">
-        <v>6.383483437725217</v>
+        <v>6.383522669268665</v>
       </c>
       <c r="N30" t="n">
-        <v>5.908057497281198</v>
+        <v>5.908067451553416</v>
       </c>
       <c r="O30" t="n">
-        <v>0.002422558214908249</v>
+        <v>0.002486401683903627</v>
       </c>
       <c r="P30" t="n">
-        <v>73.36062770541621</v>
+        <v>73.56562863368542</v>
       </c>
       <c r="Q30" t="n">
-        <v>-26.63937229458379</v>
+        <v>-26.43437136631458</v>
       </c>
       <c r="R30" t="n">
-        <v>55.4356828708416</v>
+        <v>55.55677651319472</v>
       </c>
       <c r="S30" t="n">
-        <v>4.961105105541574</v>
+        <v>4.976987061278004</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3351,52 +3347,52 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>57.59000015258789</v>
+        <v>57.58000183105469</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9800544984863491</v>
+        <v>-0.9972455603148189</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3805590995968555</v>
+        <v>-0.3978542410874142</v>
       </c>
       <c r="G32" t="n">
-        <v>2.364027498638643</v>
+        <v>2.346255863673319</v>
       </c>
       <c r="H32" t="n">
-        <v>11.3065293474</v>
+        <v>11.28720518580575</v>
       </c>
       <c r="I32" t="n">
-        <v>58.35555854483728</v>
+        <v>58.22257096132398</v>
       </c>
       <c r="J32" t="n">
         <v>25.27650725696409</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6026038316330756</v>
+        <v>0.5994830286997923</v>
       </c>
       <c r="L32" t="n">
-        <v>57.27898420287129</v>
+        <v>57.27803198177288</v>
       </c>
       <c r="M32" t="n">
-        <v>55.81276869339925</v>
+        <v>55.81237660235873</v>
       </c>
       <c r="N32" t="n">
-        <v>53.32924559971638</v>
+        <v>53.32914611392998</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.07222781652678234</v>
+        <v>-0.07286588604912936</v>
       </c>
       <c r="P32" t="n">
-        <v>63.22870568834772</v>
+        <v>62.78035037060732</v>
       </c>
       <c r="Q32" t="n">
-        <v>-36.77129431165228</v>
+        <v>-37.21964962939268</v>
       </c>
       <c r="R32" t="n">
-        <v>40.53121032255871</v>
+        <v>40.30640572153265</v>
       </c>
       <c r="S32" t="n">
-        <v>2.76588010659915</v>
+        <v>2.748038705153988</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3409,7 +3405,7 @@
         <v>68.5</v>
       </c>
       <c r="X32" t="n">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3597,7 +3593,7 @@
         <v>68.40000000000001</v>
       </c>
       <c r="X34" t="n">
-        <v>75.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3683,7 +3679,7 @@
         <v>68.2</v>
       </c>
       <c r="X35" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3775,7 +3771,7 @@
         <v>68.09999999999999</v>
       </c>
       <c r="X36" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -4327,7 +4323,7 @@
         <v>67.2</v>
       </c>
       <c r="X42" t="n">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4511,7 +4507,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="X44" t="n">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -4913,52 +4909,52 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.354481220245361</v>
+        <v>1.354646444320679</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4009157679249808</v>
+        <v>0.4131630019366783</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4010577171600582</v>
+        <v>0.4133049684871937</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4889658328856017</v>
+        <v>0.5012238075338793</v>
       </c>
       <c r="H49" t="n">
-        <v>0.82487262911346</v>
+        <v>0.8371715787778289</v>
       </c>
       <c r="I49" t="n">
-        <v>62.01866861770345</v>
+        <v>62.14776567513972</v>
       </c>
       <c r="J49" t="n">
         <v>38.41069313285799</v>
       </c>
       <c r="K49" t="n">
-        <v>0.8696531855361933</v>
+        <v>0.8740748408574956</v>
       </c>
       <c r="L49" t="n">
-        <v>1.345181659724876</v>
+        <v>1.345197395351097</v>
       </c>
       <c r="M49" t="n">
-        <v>1.341592616363169</v>
+        <v>1.341599095738671</v>
       </c>
       <c r="N49" t="n">
-        <v>1.339520567075759</v>
+        <v>1.339522211096409</v>
       </c>
       <c r="O49" t="n">
-        <v>0.0009142838691062732</v>
+        <v>0.0009248280835994532</v>
       </c>
       <c r="P49" t="n">
-        <v>90.85921722849504</v>
+        <v>91.42581494411695</v>
       </c>
       <c r="Q49" t="n">
-        <v>-9.140782771504959</v>
+        <v>-8.574185055883051</v>
       </c>
       <c r="R49" t="n">
-        <v>125.3224667173033</v>
+        <v>125.8234295751943</v>
       </c>
       <c r="S49" t="n">
-        <v>0.732768009813145</v>
+        <v>0.745055724253052</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4967,7 +4963,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>Shooting Star, Morning Star</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -4976,10 +4972,10 @@
         </is>
       </c>
       <c r="W49" t="n">
-        <v>65.2</v>
+        <v>65.5</v>
       </c>
       <c r="X49" t="n">
-        <v>64.8</v>
+        <v>70.8</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -4988,7 +4984,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 38); RSI in forza (62) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (1.3571); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 38); RSI in forza (62) — momentum positivo; pattern: Double Bottom; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3571); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5009,52 +5005,52 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4474.2001953125</v>
+        <v>4473.10009765625</v>
       </c>
       <c r="E50" t="n">
-        <v>2.141363689615683</v>
+        <v>2.116249597734221</v>
       </c>
       <c r="F50" t="n">
-        <v>2.576926857216288</v>
+        <v>2.551705670882431</v>
       </c>
       <c r="G50" t="n">
-        <v>11.50099059875753</v>
+        <v>11.4735752009048</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.719929811916532</v>
+        <v>-1.74409450507963</v>
       </c>
       <c r="I50" t="n">
-        <v>69.48914261381778</v>
+        <v>69.4395199056662</v>
       </c>
       <c r="J50" t="n">
         <v>46.49469745471913</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9425834757632103</v>
+        <v>0.9411991339266381</v>
       </c>
       <c r="L50" t="n">
-        <v>4251.251332287609</v>
+        <v>4251.146561082252</v>
       </c>
       <c r="M50" t="n">
-        <v>4243.700099449424</v>
+        <v>4243.656958364865</v>
       </c>
       <c r="N50" t="n">
-        <v>4284.621022163579</v>
+        <v>4284.610075918244</v>
       </c>
       <c r="O50" t="n">
-        <v>37.56205937093335</v>
+        <v>37.49185370854037</v>
       </c>
       <c r="P50" t="n">
-        <v>97.37520227822856</v>
+        <v>97.14043970311339</v>
       </c>
       <c r="Q50" t="n">
-        <v>-2.624797721771441</v>
+        <v>-2.859560296886609</v>
       </c>
       <c r="R50" t="n">
-        <v>152.2211058235784</v>
+        <v>152.0441725010764</v>
       </c>
       <c r="S50" t="n">
-        <v>11.56771665052678</v>
+        <v>11.54028484635115</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5159,7 +5155,7 @@
         <v>64.5</v>
       </c>
       <c r="X51" t="n">
-        <v>65.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -5175,83 +5171,79 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1783.5</v>
+        <v>1051.31005859375</v>
       </c>
       <c r="E52" t="n">
-        <v>1.914285714285713</v>
+        <v>1.143908539930272</v>
       </c>
       <c r="F52" t="n">
-        <v>2.235597592433369</v>
+        <v>1.623961940390606</v>
       </c>
       <c r="G52" t="n">
-        <v>11.06613188245673</v>
+        <v>-1.30582532171204</v>
       </c>
       <c r="H52" t="n">
-        <v>-9.379603570747408</v>
+        <v>11.08986800653873</v>
       </c>
       <c r="I52" t="n">
-        <v>62.22809817850584</v>
+        <v>51.63894483295077</v>
       </c>
       <c r="J52" t="n">
-        <v>32.23032295245881</v>
+        <v>24.36206032052416</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8666104799083744</v>
+        <v>0.5735687689216362</v>
       </c>
       <c r="L52" t="n">
-        <v>1705.31955018094</v>
+        <v>1044.159035684962</v>
       </c>
       <c r="M52" t="n">
-        <v>1719.774096850351</v>
+        <v>1036.369368806466</v>
       </c>
       <c r="N52" t="n">
-        <v>1782.806643258025</v>
+        <v>933.0207369921553</v>
       </c>
       <c r="O52" t="n">
-        <v>12.6815291612493</v>
+        <v>0.6662468490121238</v>
       </c>
       <c r="P52" t="n">
-        <v>94.34147532393293</v>
+        <v>73.97254980614841</v>
       </c>
       <c r="Q52" t="n">
-        <v>-5.658524676067073</v>
+        <v>-26.02745019385158</v>
       </c>
       <c r="R52" t="n">
-        <v>114.1482662514057</v>
+        <v>9.676639464735302</v>
       </c>
       <c r="S52" t="n">
-        <v>12.01482569367787</v>
+        <v>-0.3525938219601343</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Breakout 20d</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="n">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="X52" t="n">
-        <v>78.90000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
@@ -5260,86 +5252,90 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); RSI in forza (62) — momentum positivo; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (1,795); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1051.31005859375</v>
+        <v>65.90499877929688</v>
       </c>
       <c r="E53" t="n">
-        <v>1.143908539930272</v>
+        <v>1.411029469341019</v>
       </c>
       <c r="F53" t="n">
-        <v>1.623961940390606</v>
+        <v>1.227223200970662</v>
       </c>
       <c r="G53" t="n">
-        <v>-1.30582532171204</v>
+        <v>17.60769637900548</v>
       </c>
       <c r="H53" t="n">
-        <v>11.08986800653873</v>
+        <v>-14.49015809763344</v>
       </c>
       <c r="I53" t="n">
-        <v>51.63894483295077</v>
+        <v>63.17885598373778</v>
       </c>
       <c r="J53" t="n">
-        <v>24.36206032052416</v>
+        <v>42.17630999648538</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5735687689216362</v>
+        <v>0.8800119402130157</v>
       </c>
       <c r="L53" t="n">
-        <v>1044.159035684962</v>
+        <v>62.28877764706668</v>
       </c>
       <c r="M53" t="n">
-        <v>1036.369368806466</v>
+        <v>63.46699042872713</v>
       </c>
       <c r="N53" t="n">
-        <v>933.0207369921553</v>
+        <v>65.15571572215134</v>
       </c>
       <c r="O53" t="n">
-        <v>0.6662468490121238</v>
+        <v>0.8858528676631506</v>
       </c>
       <c r="P53" t="n">
-        <v>73.97254980614841</v>
+        <v>91.27232760660893</v>
       </c>
       <c r="Q53" t="n">
-        <v>-26.02745019385158</v>
+        <v>-8.727672393391069</v>
       </c>
       <c r="R53" t="n">
-        <v>9.676639464735302</v>
+        <v>124.8828349038944</v>
       </c>
       <c r="S53" t="n">
-        <v>-0.3525938219601343</v>
+        <v>16.02584581388304</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Double Top, Outside Bar</t>
+        </is>
+      </c>
       <c r="W53" t="n">
-        <v>64.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="X53" t="n">
-        <v>65.5</v>
+        <v>76</v>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
@@ -5348,90 +5344,86 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 42); RSI in forza (63) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (66.74)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>TIT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Telecom Italia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>65.95500183105469</v>
+        <v>7.685999870300293</v>
       </c>
       <c r="E54" t="n">
-        <v>1.487971447177161</v>
+        <v>0.7075458730843476</v>
       </c>
       <c r="F54" t="n">
-        <v>1.304025722399538</v>
+        <v>2.466337082617298</v>
       </c>
       <c r="G54" t="n">
-        <v>17.69692699638019</v>
+        <v>-1.398334893223963</v>
       </c>
       <c r="H54" t="n">
-        <v>-14.42528057499264</v>
+        <v>6.072316706746395</v>
       </c>
       <c r="I54" t="n">
-        <v>63.29698534553561</v>
+        <v>54.94310386816033</v>
       </c>
       <c r="J54" t="n">
-        <v>42.17630999648538</v>
+        <v>41.0268982447862</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8832525122194367</v>
+        <v>0.8409107339789135</v>
       </c>
       <c r="L54" t="n">
-        <v>62.29353984247219</v>
+        <v>7.598662490827632</v>
       </c>
       <c r="M54" t="n">
-        <v>63.46895133271763</v>
+        <v>7.564821635199546</v>
       </c>
       <c r="N54" t="n">
-        <v>65.15621326495491</v>
+        <v>6.516625992423518</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8890439456100792</v>
+        <v>0.02714442752380418</v>
       </c>
       <c r="P54" t="n">
-        <v>91.79812193390266</v>
+        <v>92.39903454634212</v>
       </c>
       <c r="Q54" t="n">
-        <v>-8.201878066097336</v>
+        <v>-7.600965453657885</v>
       </c>
       <c r="R54" t="n">
-        <v>125.2562443110395</v>
+        <v>40.47257848685192</v>
       </c>
       <c r="S54" t="n">
-        <v>16.11387625893173</v>
+        <v>-2.051742694857284</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Double Top, Outside Bar</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="X54" t="n">
-        <v>76.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5440,19 +5432,19 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 42); RSI in forza (63) — momentum positivo; pattern: Double Top; vicino alla resistenza dei 20g (66.74)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 41); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TIT</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Telecom Italia</t>
+          <t>Reply</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5461,65 +5453,65 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7.685999870300293</v>
+        <v>117.1999969482422</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7075458730843476</v>
+        <v>-2.819238448505035</v>
       </c>
       <c r="F55" t="n">
-        <v>2.466337082617298</v>
+        <v>0.4284490257713935</v>
       </c>
       <c r="G55" t="n">
-        <v>-1.398334893223963</v>
+        <v>20.82473912189917</v>
       </c>
       <c r="H55" t="n">
-        <v>6.072316706746395</v>
+        <v>13.23671202728713</v>
       </c>
       <c r="I55" t="n">
-        <v>54.94310386816033</v>
+        <v>65.21642624928265</v>
       </c>
       <c r="J55" t="n">
-        <v>41.0268982447862</v>
+        <v>74.88590204797376</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8409107339789135</v>
+        <v>0.6847213728448109</v>
       </c>
       <c r="L55" t="n">
-        <v>7.598662490827632</v>
+        <v>111.9539006037836</v>
       </c>
       <c r="M55" t="n">
-        <v>7.564821635199546</v>
+        <v>105.1937416476779</v>
       </c>
       <c r="N55" t="n">
-        <v>6.516625992423518</v>
+        <v>105.4310199082202</v>
       </c>
       <c r="O55" t="n">
-        <v>0.02714442752380418</v>
+        <v>0.3782355409454192</v>
       </c>
       <c r="P55" t="n">
-        <v>92.39903454634212</v>
+        <v>72.19249569673694</v>
       </c>
       <c r="Q55" t="n">
-        <v>-7.600965453657885</v>
+        <v>-27.80750430326306</v>
       </c>
       <c r="R55" t="n">
-        <v>40.47257848685192</v>
+        <v>56.61846727193323</v>
       </c>
       <c r="S55" t="n">
-        <v>-2.051742694857284</v>
+        <v>19.8363939582062</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="X55" t="n">
-        <v>65</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5528,86 +5520,90 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 41); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 75); RSI in forza (65) — momentum positivo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Reply</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>117.1999969482422</v>
+        <v>506</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.819238448505035</v>
+        <v>-1.631060947824137</v>
       </c>
       <c r="F56" t="n">
-        <v>0.4284490257713935</v>
+        <v>7.760457157950107</v>
       </c>
       <c r="G56" t="n">
-        <v>20.82473912189917</v>
+        <v>2.065513561534749</v>
       </c>
       <c r="H56" t="n">
-        <v>13.23671202728713</v>
+        <v>20.19288147879668</v>
       </c>
       <c r="I56" t="n">
-        <v>65.21642624928265</v>
+        <v>51.9346563583324</v>
       </c>
       <c r="J56" t="n">
-        <v>74.88590204797376</v>
+        <v>17.4242075285986</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6847213728448109</v>
+        <v>0.59543619330438</v>
       </c>
       <c r="L56" t="n">
-        <v>111.9539006037836</v>
+        <v>495.2393240910492</v>
       </c>
       <c r="M56" t="n">
-        <v>105.1937416476779</v>
+        <v>487.6552510080832</v>
       </c>
       <c r="N56" t="n">
-        <v>105.4310199082202</v>
+        <v>359.6145293269944</v>
       </c>
       <c r="O56" t="n">
-        <v>0.3782355409454192</v>
+        <v>2.645567615420714</v>
       </c>
       <c r="P56" t="n">
-        <v>72.19249569673694</v>
+        <v>77.25730113599593</v>
       </c>
       <c r="Q56" t="n">
-        <v>-27.80750430326306</v>
+        <v>-22.74269886400407</v>
       </c>
       <c r="R56" t="n">
-        <v>56.61846727193323</v>
+        <v>38.83763894529073</v>
       </c>
       <c r="S56" t="n">
-        <v>19.8363939582062</v>
+        <v>0.4825530989610138</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bearish Harami</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="n">
-        <v>63.6</v>
+        <v>63.2</v>
       </c>
       <c r="X56" t="n">
-        <v>65.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5616,91 +5612,87 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 75); RSI in forza (65) — momentum positivo</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); segnale candlestick: Bearish Harami; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>DiaSorin</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>506</v>
+        <v>74.5</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.631060947824137</v>
+        <v>0.107500447491371</v>
       </c>
       <c r="F57" t="n">
-        <v>7.760457157950107</v>
+        <v>-2.333506565000087</v>
       </c>
       <c r="G57" t="n">
-        <v>2.065513561534749</v>
+        <v>6.764117660179014</v>
       </c>
       <c r="H57" t="n">
-        <v>20.19288147879668</v>
+        <v>9.946867844276142</v>
       </c>
       <c r="I57" t="n">
-        <v>51.9346563583324</v>
+        <v>58.49275328926535</v>
       </c>
       <c r="J57" t="n">
-        <v>17.4242075285986</v>
+        <v>14.03163813881592</v>
       </c>
       <c r="K57" t="n">
-        <v>0.59543619330438</v>
+        <v>0.6704734915751338</v>
       </c>
       <c r="L57" t="n">
-        <v>495.2393240910492</v>
+        <v>72.84788794307315</v>
       </c>
       <c r="M57" t="n">
-        <v>487.6552510080832</v>
+        <v>70.36648926120414</v>
       </c>
       <c r="N57" t="n">
-        <v>359.6145293269944</v>
+        <v>70.62152498363596</v>
       </c>
       <c r="O57" t="n">
-        <v>2.645567615420714</v>
+        <v>0.09180697451634257</v>
       </c>
       <c r="P57" t="n">
-        <v>77.25730113599593</v>
+        <v>84.68334646098391</v>
       </c>
       <c r="Q57" t="n">
-        <v>-22.74269886400407</v>
+        <v>-15.31665353901609</v>
       </c>
       <c r="R57" t="n">
-        <v>38.83763894529073</v>
+        <v>53.35596366949357</v>
       </c>
       <c r="S57" t="n">
-        <v>0.4825530989610138</v>
+        <v>7.472591356001623</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="X57" t="n">
         <v>63.2</v>
       </c>
-      <c r="X57" t="n">
-        <v>71.3</v>
-      </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -5708,73 +5700,73 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); segnale candlestick: Bearish Harami; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>mercato laterale — ATR basso (ADX 14)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DiaSorin</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>74.5</v>
+        <v>26.8700008392334</v>
       </c>
       <c r="E58" t="n">
-        <v>0.107500447491371</v>
+        <v>0.2986185926544316</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.333506565000087</v>
+        <v>-0.665428476539609</v>
       </c>
       <c r="G58" t="n">
-        <v>6.764117660179014</v>
+        <v>7.26547567905802</v>
       </c>
       <c r="H58" t="n">
-        <v>9.946867844276142</v>
+        <v>6.079750967887199</v>
       </c>
       <c r="I58" t="n">
-        <v>58.49275328926535</v>
+        <v>65.56419023029363</v>
       </c>
       <c r="J58" t="n">
-        <v>14.03163813881592</v>
+        <v>46.70926518833675</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6704734915751338</v>
+        <v>0.8347759068721949</v>
       </c>
       <c r="L58" t="n">
-        <v>72.84788794307315</v>
+        <v>25.92983229857106</v>
       </c>
       <c r="M58" t="n">
-        <v>70.36648926120414</v>
+        <v>25.56491153701868</v>
       </c>
       <c r="N58" t="n">
-        <v>70.62152498363596</v>
+        <v>25.74497297173641</v>
       </c>
       <c r="O58" t="n">
-        <v>0.09180697451634257</v>
+        <v>0.138374600295479</v>
       </c>
       <c r="P58" t="n">
-        <v>84.68334646098391</v>
+        <v>87.54717986071324</v>
       </c>
       <c r="Q58" t="n">
-        <v>-15.31665353901609</v>
+        <v>-12.45282013928675</v>
       </c>
       <c r="R58" t="n">
-        <v>53.35596366949357</v>
+        <v>100.5402500440422</v>
       </c>
       <c r="S58" t="n">
-        <v>7.472591356001623</v>
+        <v>8.565659956498584</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -5784,10 +5776,10 @@
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="n">
-        <v>61.6</v>
+        <v>61.5</v>
       </c>
       <c r="X58" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5796,73 +5788,73 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 14)</t>
+          <t>trend molto direzionale (ADX 47); RSI in forza (66) — momentum positivo; vicino alla resistenza dei 20g (27.20); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.8700008392334</v>
+        <v>1781.800048828125</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2986185926544316</v>
+        <v>1.817145647321428</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.665428476539609</v>
+        <v>2.138151265584698</v>
       </c>
       <c r="G59" t="n">
-        <v>7.26547567905802</v>
+        <v>10.96026869151241</v>
       </c>
       <c r="H59" t="n">
-        <v>6.079750967887199</v>
+        <v>-9.465978815550146</v>
       </c>
       <c r="I59" t="n">
-        <v>65.56419023029363</v>
+        <v>62.05571329083102</v>
       </c>
       <c r="J59" t="n">
-        <v>46.70926518833675</v>
+        <v>32.23032295245881</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8347759068721949</v>
+        <v>0.8613570622137618</v>
       </c>
       <c r="L59" t="n">
-        <v>25.92983229857106</v>
+        <v>1705.157650069332</v>
       </c>
       <c r="M59" t="n">
-        <v>25.56491153701868</v>
+        <v>1719.707432098513</v>
       </c>
       <c r="N59" t="n">
-        <v>25.74497297173641</v>
+        <v>1782.789728320992</v>
       </c>
       <c r="O59" t="n">
-        <v>0.138374600295479</v>
+        <v>12.57304224885614</v>
       </c>
       <c r="P59" t="n">
-        <v>87.54717986071324</v>
+        <v>93.51223084984757</v>
       </c>
       <c r="Q59" t="n">
-        <v>-12.45282013928675</v>
+        <v>-6.487769150152439</v>
       </c>
       <c r="R59" t="n">
-        <v>100.5402500440422</v>
+        <v>113.5544691747743</v>
       </c>
       <c r="S59" t="n">
-        <v>8.565659956498584</v>
+        <v>11.90805825089383</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -5870,21 +5862,25 @@
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Breakout 20d</t>
+        </is>
+      </c>
       <c r="W59" t="n">
-        <v>61.5</v>
+        <v>59.9</v>
       </c>
       <c r="X59" t="n">
-        <v>63.5</v>
+        <v>74.8</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); RSI in forza (66) — momentum positivo; vicino alla resistenza dei 20g (27.20); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 32); RSI in forza (62) — momentum positivo; breakout massimi 20g — momentum di breve; vicino alla resistenza dei 20g (1,795); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5905,52 +5901,52 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>9.475000381469727</v>
+        <v>9.503000259399414</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9641700828626476</v>
+        <v>1.262532544474904</v>
       </c>
       <c r="F60" t="n">
-        <v>9.275350013000505</v>
+        <v>9.598273109349066</v>
       </c>
       <c r="G60" t="n">
-        <v>13.30840195051899</v>
+        <v>13.64324324817499</v>
       </c>
       <c r="H60" t="n">
-        <v>14.64638480351146</v>
+        <v>14.98518001726747</v>
       </c>
       <c r="I60" t="n">
-        <v>70.54040104368326</v>
+        <v>70.89556734169442</v>
       </c>
       <c r="J60" t="n">
         <v>35.32093328393831</v>
       </c>
       <c r="K60" t="n">
-        <v>1.002764005467513</v>
+        <v>1.013619195755784</v>
       </c>
       <c r="L60" t="n">
-        <v>8.70071765367172</v>
+        <v>8.703384308712643</v>
       </c>
       <c r="M60" t="n">
-        <v>8.456689991863424</v>
+        <v>8.45778802629204</v>
       </c>
       <c r="N60" t="n">
-        <v>9.532615477612664</v>
+        <v>9.532894083363207</v>
       </c>
       <c r="O60" t="n">
-        <v>0.1244951206312908</v>
+        <v>0.1262820074279421</v>
       </c>
       <c r="P60" t="n">
-        <v>85.31691975648842</v>
+        <v>87.01304328234563</v>
       </c>
       <c r="Q60" t="n">
-        <v>-14.68308024351158</v>
+        <v>-12.98695671765436</v>
       </c>
       <c r="R60" t="n">
-        <v>201.9536642632277</v>
+        <v>203.5525540328231</v>
       </c>
       <c r="S60" t="n">
-        <v>12.45122476972997</v>
+        <v>12.78353299556965</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -5964,10 +5960,10 @@
       </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="X60" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -6059,7 +6055,7 @@
         <v>58.3</v>
       </c>
       <c r="X61" t="n">
-        <v>66</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -6151,7 +6147,7 @@
         <v>57.7</v>
       </c>
       <c r="X62" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6243,7 +6239,7 @@
         <v>57.3</v>
       </c>
       <c r="X63" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6273,52 +6269,52 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>90.87999725341797</v>
+        <v>91.09999847412109</v>
       </c>
       <c r="E64" t="n">
-        <v>2.666064956901937</v>
+        <v>2.914597750673065</v>
       </c>
       <c r="F64" t="n">
-        <v>3.602366608231455</v>
+        <v>3.853165989947849</v>
       </c>
       <c r="G64" t="n">
-        <v>3.155503776896751</v>
+        <v>3.405221398364988</v>
       </c>
       <c r="H64" t="n">
-        <v>-18.92952855445568</v>
+        <v>-18.73327411761559</v>
       </c>
       <c r="I64" t="n">
-        <v>56.49569626191597</v>
+        <v>56.76122119961413</v>
       </c>
       <c r="J64" t="n">
         <v>15.53260554796924</v>
       </c>
       <c r="K64" t="n">
-        <v>0.6221690229510282</v>
+        <v>0.631841967928207</v>
       </c>
       <c r="L64" t="n">
-        <v>86.81065486371475</v>
+        <v>86.83160736092456</v>
       </c>
       <c r="M64" t="n">
-        <v>87.13534739192907</v>
+        <v>87.14397489078017</v>
       </c>
       <c r="N64" t="n">
-        <v>84.05835420559629</v>
+        <v>84.06054327246896</v>
       </c>
       <c r="O64" t="n">
-        <v>0.343496992239912</v>
+        <v>0.3575369561822215</v>
       </c>
       <c r="P64" t="n">
-        <v>84.94335899676273</v>
+        <v>86.40905646106951</v>
       </c>
       <c r="Q64" t="n">
-        <v>-15.05664100323728</v>
+        <v>-13.59094353893049</v>
       </c>
       <c r="R64" t="n">
-        <v>22.09384857021304</v>
+        <v>22.88747915004176</v>
       </c>
       <c r="S64" t="n">
-        <v>1.860564906974749</v>
+        <v>2.107147755767702</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6328,10 +6324,10 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="X64" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -6423,7 +6419,7 @@
         <v>57</v>
       </c>
       <c r="X65" t="n">
-        <v>63.4</v>
+        <v>63.3</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6527,87 +6523,83 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Consumer Discr.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1330.5</v>
+        <v>116.75</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6049149338374304</v>
+        <v>-1.226731798374847</v>
       </c>
       <c r="F67" t="n">
-        <v>-3.390934710107818</v>
+        <v>-2.440041960076722</v>
       </c>
       <c r="G67" t="n">
-        <v>6.953376205787776</v>
+        <v>1.134786495919093</v>
       </c>
       <c r="H67" t="n">
-        <v>-6.157430231454875</v>
+        <v>0.3696701395322632</v>
       </c>
       <c r="I67" t="n">
-        <v>52.94605759849054</v>
+        <v>50.31404471568584</v>
       </c>
       <c r="J67" t="n">
-        <v>22.47135368428625</v>
+        <v>31.04017394032804</v>
       </c>
       <c r="K67" t="n">
-        <v>0.5880170696252258</v>
+        <v>0.5737840371615658</v>
       </c>
       <c r="L67" t="n">
-        <v>1320.192133150358</v>
+        <v>116.9247709722083</v>
       </c>
       <c r="M67" t="n">
-        <v>1318.441150000216</v>
+        <v>116.4016686853075</v>
       </c>
       <c r="N67" t="n">
-        <v>1393.491844299864</v>
+        <v>115.7699568043066</v>
       </c>
       <c r="O67" t="n">
-        <v>0.6448291817725149</v>
+        <v>0.1939774491401186</v>
       </c>
       <c r="P67" t="n">
-        <v>64.41947565543072</v>
+        <v>58.99997287326389</v>
       </c>
       <c r="Q67" t="n">
-        <v>-35.58052434456929</v>
+        <v>-41.00002712673611</v>
       </c>
       <c r="R67" t="n">
-        <v>33.38433004568005</v>
+        <v>26.23325641979875</v>
       </c>
       <c r="S67" t="n">
-        <v>5.511498810467885</v>
+        <v>1.867201272360131</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Double Top, Volatility Squeeze</t>
         </is>
       </c>
       <c r="W67" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="X67" t="n">
-        <v>70.5</v>
+        <v>68.8</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -6616,73 +6608,73 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); shooting star — rifiuto di resistenza; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 31); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Consumer Discr.</t>
+          <t>WTI Crude</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>116.75</v>
+        <v>84.94999694824219</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.226731798374847</v>
+        <v>3.094654581483747</v>
       </c>
       <c r="F68" t="n">
-        <v>-2.440041960076722</v>
+        <v>3.433580651564982</v>
       </c>
       <c r="G68" t="n">
-        <v>1.134786495919093</v>
+        <v>2.982178625504739</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3696701395322632</v>
+        <v>-21.82036252050584</v>
       </c>
       <c r="I68" t="n">
-        <v>50.31404471568584</v>
+        <v>56.38083153800805</v>
       </c>
       <c r="J68" t="n">
-        <v>31.04017394032804</v>
+        <v>16.56389361187937</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5737840371615658</v>
+        <v>0.6388807569802067</v>
       </c>
       <c r="L68" t="n">
-        <v>116.9247709722083</v>
+        <v>81.38726583171425</v>
       </c>
       <c r="M68" t="n">
-        <v>116.4016686853075</v>
+        <v>82.06824597731054</v>
       </c>
       <c r="N68" t="n">
-        <v>115.7699568043066</v>
+        <v>79.27044647525243</v>
       </c>
       <c r="O68" t="n">
-        <v>0.1939774491401186</v>
+        <v>0.3090600802244186</v>
       </c>
       <c r="P68" t="n">
-        <v>58.99997287326389</v>
+        <v>84.7980597303436</v>
       </c>
       <c r="Q68" t="n">
-        <v>-41.00002712673611</v>
+        <v>-15.20194026965641</v>
       </c>
       <c r="R68" t="n">
-        <v>26.23325641979875</v>
+        <v>19.1071172376673</v>
       </c>
       <c r="S68" t="n">
-        <v>1.867201272360131</v>
+        <v>2.066554754218108</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6690,16 +6682,12 @@
         </is>
       </c>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Double Top, Volatility Squeeze</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="n">
-        <v>56.6</v>
+        <v>56.3</v>
       </c>
       <c r="X68" t="n">
-        <v>68.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -6708,73 +6696,73 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 31); pattern: Double Top; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>in zona Fib Fib 61.8 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.158077597618103</v>
+        <v>1328</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3937453792970613</v>
+        <v>0.415879017013232</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2107749499547396</v>
+        <v>-3.572462453982095</v>
       </c>
       <c r="G69" t="n">
-        <v>1.189347278197461</v>
+        <v>6.7524115755627</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.3833248855290905</v>
+        <v>-6.333759749997803</v>
       </c>
       <c r="I69" t="n">
-        <v>62.58075726877307</v>
+        <v>52.56914262713447</v>
       </c>
       <c r="J69" t="n">
-        <v>49.27999259891681</v>
+        <v>22.47135368428625</v>
       </c>
       <c r="K69" t="n">
-        <v>0.8278820695867036</v>
+        <v>0.5757521165540814</v>
       </c>
       <c r="L69" t="n">
-        <v>1.150664974148637</v>
+        <v>1319.954037912263</v>
       </c>
       <c r="M69" t="n">
-        <v>1.150289743536566</v>
+        <v>1318.34311078453</v>
       </c>
       <c r="N69" t="n">
-        <v>1.155817007891325</v>
+        <v>1393.466968677973</v>
       </c>
       <c r="O69" t="n">
-        <v>0.0008943075054257334</v>
+        <v>0.4852850222284957</v>
       </c>
       <c r="P69" t="n">
-        <v>84.93913077862187</v>
+        <v>62.54681647940075</v>
       </c>
       <c r="Q69" t="n">
-        <v>-15.06086922137812</v>
+        <v>-37.45318352059925</v>
       </c>
       <c r="R69" t="n">
-        <v>107.2930312813577</v>
+        <v>32.14868654426305</v>
       </c>
       <c r="S69" t="n">
-        <v>1.33989289202181</v>
+        <v>5.313243457573358</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -6788,14 +6776,14 @@
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Outside Bar</t>
         </is>
       </c>
       <c r="W69" t="n">
         <v>56.2</v>
       </c>
       <c r="X69" t="n">
-        <v>64.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -6804,86 +6792,94 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 49); RSI in forza (63) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (1.1617); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 22); shooting star — rifiuto di resistenza; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WTI Crude</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>84.72000122070312</v>
+        <v>1.158211708068848</v>
       </c>
       <c r="E70" t="n">
-        <v>2.815533558085659</v>
+        <v>0.4053714140916709</v>
       </c>
       <c r="F70" t="n">
-        <v>3.153542011323229</v>
+        <v>0.2223797959733931</v>
       </c>
       <c r="G70" t="n">
-        <v>2.703362122298025</v>
+        <v>1.201065447171579</v>
       </c>
       <c r="H70" t="n">
-        <v>-22.03202800899069</v>
+        <v>-0.3717888388697355</v>
       </c>
       <c r="I70" t="n">
-        <v>56.05622110070212</v>
+        <v>62.72154973098756</v>
       </c>
       <c r="J70" t="n">
-        <v>16.52161132560384</v>
+        <v>49.27999259891681</v>
       </c>
       <c r="K70" t="n">
-        <v>0.6262053501779516</v>
+        <v>0.8318428751803607</v>
       </c>
       <c r="L70" t="n">
-        <v>81.36536147671053</v>
+        <v>1.150677746572518</v>
       </c>
       <c r="M70" t="n">
-        <v>82.05922653701488</v>
+        <v>1.150295002769929</v>
       </c>
       <c r="N70" t="n">
-        <v>79.26815796055055</v>
+        <v>1.155818342323671</v>
       </c>
       <c r="O70" t="n">
-        <v>0.2943822902048343</v>
+        <v>0.0009028661210858258</v>
       </c>
       <c r="P70" t="n">
-        <v>82.97703329628376</v>
+        <v>85.49518334906756</v>
       </c>
       <c r="Q70" t="n">
-        <v>-17.02296670371623</v>
+        <v>-14.50481665093244</v>
       </c>
       <c r="R70" t="n">
-        <v>17.40821122907129</v>
+        <v>107.7065635520576</v>
       </c>
       <c r="S70" t="n">
-        <v>1.790217233777636</v>
+        <v>1.351628494836432</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W70" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="X70" t="n">
-        <v>67.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -6892,7 +6888,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>in zona Fib Fib 61.8 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 49); RSI in forza (63) — momentum positivo; pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (1.1617); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6967,7 @@
         <v>56</v>
       </c>
       <c r="X71" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -7151,7 +7147,7 @@
         <v>53.9</v>
       </c>
       <c r="X73" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -7243,7 +7239,7 @@
         <v>53.9</v>
       </c>
       <c r="X74" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -7335,7 +7331,7 @@
         <v>53.8</v>
       </c>
       <c r="X75" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -7427,7 +7423,7 @@
         <v>53.6</v>
       </c>
       <c r="X76" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -7457,52 +7453,52 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>75.70999908447266</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="E77" t="n">
-        <v>1.570965666452873</v>
+        <v>1.772204604759597</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2443006696347672</v>
+        <v>0.4429111338130953</v>
       </c>
       <c r="G77" t="n">
-        <v>2.115071949552982</v>
+        <v>2.317388906268003</v>
       </c>
       <c r="H77" t="n">
-        <v>3.127765655715797</v>
+        <v>3.332089026418528</v>
       </c>
       <c r="I77" t="n">
-        <v>52.63086048046871</v>
+        <v>53.20315397593733</v>
       </c>
       <c r="J77" t="n">
         <v>15.49357908344949</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7195417938519855</v>
+        <v>0.7445282794030461</v>
       </c>
       <c r="L77" t="n">
-        <v>75.10480244361047</v>
+        <v>75.11908830321798</v>
       </c>
       <c r="M77" t="n">
-        <v>75.42477362352851</v>
+        <v>75.43065603630806</v>
       </c>
       <c r="N77" t="n">
-        <v>89.21183697050439</v>
+        <v>89.21332952300071</v>
       </c>
       <c r="O77" t="n">
-        <v>0.1363476414896993</v>
+        <v>0.1459203884403635</v>
       </c>
       <c r="P77" t="n">
-        <v>64.07068222752801</v>
+        <v>66.89685011866139</v>
       </c>
       <c r="Q77" t="n">
-        <v>-35.929317772472</v>
+        <v>-33.10314988133861</v>
       </c>
       <c r="R77" t="n">
-        <v>39.25568644876941</v>
+        <v>41.22889355594357</v>
       </c>
       <c r="S77" t="n">
-        <v>2.728488061771284</v>
+        <v>2.932020357991583</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7516,10 +7512,10 @@
       </c>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="X77" t="n">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -7528,7 +7524,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>candela di inversione bullish (engulfing); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7611,7 @@
         <v>51.2</v>
       </c>
       <c r="X78" t="n">
-        <v>60.4</v>
+        <v>60.3</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
@@ -7799,7 +7795,7 @@
         <v>50.2</v>
       </c>
       <c r="X80" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
@@ -7921,52 +7917,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1905.77001953125</v>
+        <v>1904.93994140625</v>
       </c>
       <c r="E82" t="n">
-        <v>1.698398856490768</v>
+        <v>1.65410305197442</v>
       </c>
       <c r="F82" t="n">
-        <v>1.471406987353574</v>
+        <v>1.427210051527128</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8016706712966837</v>
+        <v>0.7577654461487615</v>
       </c>
       <c r="H82" t="n">
-        <v>6.443919939139331</v>
+        <v>6.397557173131241</v>
       </c>
       <c r="I82" t="n">
-        <v>55.64138199405378</v>
+        <v>55.50343948740878</v>
       </c>
       <c r="J82" t="n">
         <v>13.71496930460695</v>
       </c>
       <c r="K82" t="n">
-        <v>0.7182653502111828</v>
+        <v>0.7094372514993392</v>
       </c>
       <c r="L82" t="n">
-        <v>1883.833584584578</v>
+        <v>1883.754529525054</v>
       </c>
       <c r="M82" t="n">
-        <v>1866.577866572745</v>
+        <v>1866.545314489411</v>
       </c>
       <c r="N82" t="n">
-        <v>2124.589307318718</v>
+        <v>2124.581047834887</v>
       </c>
       <c r="O82" t="n">
-        <v>-3.717492365385702</v>
+        <v>-3.770466012109397</v>
       </c>
       <c r="P82" t="n">
-        <v>65.11166394469976</v>
+        <v>64.18926984368133</v>
       </c>
       <c r="Q82" t="n">
-        <v>-34.88833605530024</v>
+        <v>-35.81073015631867</v>
       </c>
       <c r="R82" t="n">
-        <v>35.28247802138117</v>
+        <v>34.2739996115982</v>
       </c>
       <c r="S82" t="n">
-        <v>-0.7384816258269034</v>
+        <v>-0.7817160214844465</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -7983,7 +7979,7 @@
         <v>49.5</v>
       </c>
       <c r="X82" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -8013,52 +8009,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>159.4720001220703</v>
+        <v>159.3699951171875</v>
       </c>
       <c r="E83" t="n">
-        <v>0.02885680535351653</v>
+        <v>-0.03512586256962935</v>
       </c>
       <c r="F83" t="n">
-        <v>1.00131963668677</v>
+        <v>0.9367149405970165</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.788445848761178</v>
+        <v>-1.851266093400217</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3675542721881753</v>
+        <v>0.3033549591064277</v>
       </c>
       <c r="I83" t="n">
-        <v>43.5876599773614</v>
+        <v>42.82969750430601</v>
       </c>
       <c r="J83" t="n">
         <v>60.87622743205132</v>
       </c>
       <c r="K83" t="n">
-        <v>0.394547714856688</v>
+        <v>0.3850268281467185</v>
       </c>
       <c r="L83" t="n">
-        <v>159.9795047362465</v>
+        <v>159.9697899738767</v>
       </c>
       <c r="M83" t="n">
-        <v>160.4661604565469</v>
+        <v>160.462160260277</v>
       </c>
       <c r="N83" t="n">
-        <v>157.8538039703203</v>
+        <v>157.8527889951474</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.0489072765226588</v>
+        <v>-0.05541699763200048</v>
       </c>
       <c r="P83" t="n">
-        <v>48.86987312935217</v>
+        <v>47.68748043347914</v>
       </c>
       <c r="Q83" t="n">
-        <v>-51.13012687064783</v>
+        <v>-52.31251956652086</v>
       </c>
       <c r="R83" t="n">
-        <v>-34.15265969038867</v>
+        <v>-35.14224302860826</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.87062703642854</v>
+        <v>-1.933394714520209</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8067,7 +8063,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>Hammer, Bullish Engulfing, Piercing Pattern</t>
+          <t>Doji</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8076,10 +8072,10 @@
         </is>
       </c>
       <c r="W83" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="X83" t="n">
-        <v>56.6</v>
+        <v>61.5</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -8088,7 +8084,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 61); pattern: Double Top; hammer — segnale di rimbalzo da supporto; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 61); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8171,7 @@
         <v>48.9</v>
       </c>
       <c r="X84" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
@@ -8191,83 +8187,87 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>64320.421875</v>
+        <v>84.68000030517578</v>
       </c>
       <c r="E85" t="n">
-        <v>2.390642707570612</v>
+        <v>-1.637816346490262</v>
       </c>
       <c r="F85" t="n">
-        <v>1.447875466629545</v>
+        <v>-0.3178300797714084</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9345223799518187</v>
+        <v>-0.5986643052173224</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.951533914612591</v>
+        <v>-1.420257507603861</v>
       </c>
       <c r="I85" t="n">
-        <v>53.38593957314423</v>
+        <v>48.00503316353664</v>
       </c>
       <c r="J85" t="n">
-        <v>12.34161519005113</v>
+        <v>23.8275261848747</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6738321139275414</v>
+        <v>0.3729447625526355</v>
       </c>
       <c r="L85" t="n">
-        <v>63787.91662256891</v>
+        <v>85.1281701954557</v>
       </c>
       <c r="M85" t="n">
-        <v>64297.02940797366</v>
+        <v>84.69869596293962</v>
       </c>
       <c r="N85" t="n">
-        <v>71585.92690500974</v>
+        <v>83.21057586101175</v>
       </c>
       <c r="O85" t="n">
-        <v>-68.21223827772205</v>
+        <v>-0.03925026502498091</v>
       </c>
       <c r="P85" t="n">
-        <v>62.89387679595486</v>
+        <v>20.39801939234289</v>
       </c>
       <c r="Q85" t="n">
-        <v>-37.10612320404514</v>
+        <v>-79.60198060765711</v>
       </c>
       <c r="R85" t="n">
-        <v>2.191259948154777</v>
+        <v>-19.21185978018592</v>
       </c>
       <c r="S85" t="n">
-        <v>0.7030671817237044</v>
+        <v>-0.2121144283303567</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Evening Star</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W85" t="n">
-        <v>48.8</v>
+        <v>48.3</v>
       </c>
       <c r="X85" t="n">
-        <v>61.6</v>
+        <v>66.2</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -8276,94 +8276,90 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Bottom</t>
+          <t>trend in sviluppo (ADX 24); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>84.68000030517578</v>
+        <v>0.1738699972629547</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.637816346490262</v>
+        <v>-0.5587796741443385</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.3178300797714084</v>
+        <v>-4.679668646315649</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.5986643052173224</v>
+        <v>11.86529399995033</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.420257507603861</v>
+        <v>1.000298026679047</v>
       </c>
       <c r="I86" t="n">
-        <v>48.00503316353664</v>
+        <v>43.30364954937615</v>
       </c>
       <c r="J86" t="n">
-        <v>23.8275261848747</v>
+        <v>40.28857809510627</v>
       </c>
       <c r="K86" t="n">
-        <v>0.3729447625526355</v>
+        <v>0.2766617741387287</v>
       </c>
       <c r="L86" t="n">
-        <v>85.1281701954557</v>
+        <v>0.181059733139665</v>
       </c>
       <c r="M86" t="n">
-        <v>84.69869596293962</v>
+        <v>0.179661588245401</v>
       </c>
       <c r="N86" t="n">
-        <v>83.21057586101175</v>
+        <v>0.2506514237780752</v>
       </c>
       <c r="O86" t="n">
-        <v>-0.03925026502498091</v>
+        <v>-0.002601752855172425</v>
       </c>
       <c r="P86" t="n">
-        <v>20.39801939234289</v>
+        <v>2.526042313070386</v>
       </c>
       <c r="Q86" t="n">
-        <v>-79.60198060765711</v>
+        <v>-97.47395768692961</v>
       </c>
       <c r="R86" t="n">
-        <v>-19.21185978018592</v>
+        <v>-53.00722291942981</v>
       </c>
       <c r="S86" t="n">
-        <v>-0.2121144283303567</v>
+        <v>7.600146587244949</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>Evening Star</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="X86" t="n">
-        <v>66.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -8372,86 +8368,94 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 24); pattern: Double Bottom; evening star — inversione ribassista a 3 candele; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 40); shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>IVG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Iveco Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.1733700037002563</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.8447402815664584</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>-4.953778917330598</v>
+        <v>0.2875626332984327</v>
       </c>
       <c r="G87" t="n">
-        <v>11.5436057974438</v>
+        <v>-0.07163487718130357</v>
       </c>
       <c r="H87" t="n">
-        <v>0.7098540188633651</v>
+        <v>0.2875626332984327</v>
       </c>
       <c r="I87" t="n">
-        <v>42.86454970253813</v>
+        <v>53.82823632877994</v>
       </c>
       <c r="J87" t="n">
-        <v>40.28857809510627</v>
+        <v>35.963441704354</v>
       </c>
       <c r="K87" t="n">
-        <v>0.2668753696042518</v>
+        <v>0.7677262333421225</v>
       </c>
       <c r="L87" t="n">
-        <v>0.1810121147051223</v>
+        <v>13.92668563889073</v>
       </c>
       <c r="M87" t="n">
-        <v>0.179641980654707</v>
+        <v>14.10622919906891</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2506464487177498</v>
+        <v>15.70937057667093</v>
       </c>
       <c r="O87" t="n">
-        <v>-0.002633661276267709</v>
+        <v>0.009875908987026852</v>
       </c>
       <c r="P87" t="n">
-        <v>1.20401988746616</v>
+        <v>84.61504603308512</v>
       </c>
       <c r="Q87" t="n">
-        <v>-98.79598011253384</v>
+        <v>-15.38495396691487</v>
       </c>
       <c r="R87" t="n">
-        <v>-53.84298514450396</v>
+        <v>65.32730317107156</v>
       </c>
       <c r="S87" t="n">
-        <v>7.290723561501999</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W87" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="X87" t="n">
-        <v>58.9</v>
+        <v>61.7</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -8460,94 +8464,90 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 40)</t>
+          <t>trend molto direzionale (ADX 36); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (13.84); vicino alla resistenza dei 20g (13.97)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IVG</t>
+          <t>XLC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Iveco Group</t>
+          <t>Communication Svcs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.94999980926514</v>
+        <v>110.8199996948242</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>-1.885787791914695</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2875626332984327</v>
+        <v>-0.3865171282478985</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.07163487718130357</v>
+        <v>-1.624502269211492</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2875626332984327</v>
+        <v>-4.531359453186424</v>
       </c>
       <c r="I88" t="n">
-        <v>53.82823632877994</v>
+        <v>50.73028278994234</v>
       </c>
       <c r="J88" t="n">
-        <v>35.963441704354</v>
+        <v>14.46229078529567</v>
       </c>
       <c r="K88" t="n">
-        <v>0.7677262333421225</v>
+        <v>0.6054778166210792</v>
       </c>
       <c r="L88" t="n">
-        <v>13.92668563889073</v>
+        <v>110.6707366043788</v>
       </c>
       <c r="M88" t="n">
-        <v>14.10622919906891</v>
+        <v>110.9470269871317</v>
       </c>
       <c r="N88" t="n">
-        <v>15.70937057667093</v>
+        <v>112.0674871587099</v>
       </c>
       <c r="O88" t="n">
-        <v>0.009875908987026852</v>
+        <v>0.283405544716941</v>
       </c>
       <c r="P88" t="n">
-        <v>84.61504603308512</v>
+        <v>66.52929888117511</v>
       </c>
       <c r="Q88" t="n">
-        <v>-15.38495396691487</v>
+        <v>-33.47070111882488</v>
       </c>
       <c r="R88" t="n">
-        <v>65.32730317107156</v>
+        <v>56.7331818835012</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>0.1536359390881259</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
           <t>Bearish</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+      <c r="U88" t="inlineStr"/>
       <c r="V88" t="inlineStr">
         <is>
           <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W88" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="X88" t="n">
-        <v>61.7</v>
+        <v>61.6</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -8556,90 +8556,94 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (13.84); vicino alla resistenza dei 20g (13.97)</t>
+          <t>mercato laterale — ATR basso (ADX 14); pattern: Double Bottom; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>XLC</t>
+          <t>TRN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Communication Svcs</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>110.8199996948242</v>
+        <v>9.744000434875488</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.885787791914695</v>
+        <v>-0.1434713919705843</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.3865171282478985</v>
+        <v>-1.575749390563552</v>
       </c>
       <c r="G89" t="n">
-        <v>-1.624502269211492</v>
+        <v>-3.14115279881122</v>
       </c>
       <c r="H89" t="n">
-        <v>-4.531359453186424</v>
+        <v>-2.227565495016892</v>
       </c>
       <c r="I89" t="n">
-        <v>50.73028278994234</v>
+        <v>32.98343306929048</v>
       </c>
       <c r="J89" t="n">
-        <v>14.46229078529567</v>
+        <v>37.18129471223103</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6054778166210792</v>
+        <v>0.09387218505786502</v>
       </c>
       <c r="L89" t="n">
-        <v>110.6707366043788</v>
+        <v>10.00064164357595</v>
       </c>
       <c r="M89" t="n">
-        <v>110.9470269871317</v>
+        <v>10.07345896569414</v>
       </c>
       <c r="N89" t="n">
-        <v>112.0674871587099</v>
+        <v>9.707489172167369</v>
       </c>
       <c r="O89" t="n">
-        <v>0.283405544716941</v>
+        <v>-0.03957564158900662</v>
       </c>
       <c r="P89" t="n">
-        <v>66.52929888117511</v>
+        <v>5.128243445184078</v>
       </c>
       <c r="Q89" t="n">
-        <v>-33.47070111882488</v>
+        <v>-94.87175655481592</v>
       </c>
       <c r="R89" t="n">
-        <v>56.7331818835012</v>
+        <v>-133.259571281846</v>
       </c>
       <c r="S89" t="n">
-        <v>0.1536359390881259</v>
+        <v>-5.855071731970163</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W89" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="X89" t="n">
-        <v>61.7</v>
+        <v>61.4</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -8648,73 +8652,73 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 14); pattern: Double Bottom; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 37); RSI scarico (33) — zona di interesse long; pattern: Double Top; doji — indecisione del mercato; sul supporto dei 20g (9.7080); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TRN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Terna</t>
+          <t>Alphabet</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9.744000434875488</v>
+        <v>344</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.1434713919705843</v>
+        <v>-0.5492899479648372</v>
       </c>
       <c r="F90" t="n">
-        <v>-1.575749390563552</v>
+        <v>-3.78160366668473</v>
       </c>
       <c r="G90" t="n">
-        <v>-3.14115279881122</v>
+        <v>-0.798797214704372</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.227565495016892</v>
+        <v>-13.33702879926316</v>
       </c>
       <c r="I90" t="n">
-        <v>32.98343306929048</v>
+        <v>46.02805647655305</v>
       </c>
       <c r="J90" t="n">
-        <v>37.18129471223103</v>
+        <v>19.47637902554306</v>
       </c>
       <c r="K90" t="n">
-        <v>0.09387218505786502</v>
+        <v>0.4682558023586039</v>
       </c>
       <c r="L90" t="n">
-        <v>10.00064164357595</v>
+        <v>349.6707855895519</v>
       </c>
       <c r="M90" t="n">
-        <v>10.07345896569414</v>
+        <v>352.3587876095594</v>
       </c>
       <c r="N90" t="n">
-        <v>9.707489172167369</v>
+        <v>323.8025832793517</v>
       </c>
       <c r="O90" t="n">
-        <v>-0.03957564158900662</v>
+        <v>-0.4338942085576218</v>
       </c>
       <c r="P90" t="n">
-        <v>5.128243445184078</v>
+        <v>25.23088283372603</v>
       </c>
       <c r="Q90" t="n">
-        <v>-94.87175655481592</v>
+        <v>-74.76911716627397</v>
       </c>
       <c r="R90" t="n">
-        <v>-133.259571281846</v>
+        <v>-10.3116485080265</v>
       </c>
       <c r="S90" t="n">
-        <v>-5.855071731970163</v>
+        <v>-2.269948139449873</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -8723,19 +8727,19 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Evening Star</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W90" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="X90" t="n">
-        <v>61.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -8744,73 +8748,73 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 37); RSI scarico (33) — zona di interesse long; pattern: Double Top; doji — indecisione del mercato; sul supporto dei 20g (9.7080); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>pattern: Double Top; evening star — inversione ribassista a 3 candele</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ENEL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>Enel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>344</v>
+        <v>9.467000007629395</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.5492899479648372</v>
+        <v>-0.2948907663734901</v>
       </c>
       <c r="F91" t="n">
-        <v>-3.78160366668473</v>
+        <v>-4.729800282157837</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.798797214704372</v>
+        <v>-5.367850040143174</v>
       </c>
       <c r="H91" t="n">
-        <v>-13.33702879926316</v>
+        <v>-2.089147493643406</v>
       </c>
       <c r="I91" t="n">
-        <v>46.02805647655305</v>
+        <v>32.76732553495455</v>
       </c>
       <c r="J91" t="n">
-        <v>19.47637902554306</v>
+        <v>16.1251057430247</v>
       </c>
       <c r="K91" t="n">
-        <v>0.4682558023586039</v>
+        <v>-0.1151339726485842</v>
       </c>
       <c r="L91" t="n">
-        <v>349.6707855895519</v>
+        <v>9.830919255784472</v>
       </c>
       <c r="M91" t="n">
-        <v>352.3587876095594</v>
+        <v>9.868737733211393</v>
       </c>
       <c r="N91" t="n">
-        <v>323.8025832793517</v>
+        <v>9.409189529188293</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.4338942085576218</v>
+        <v>-0.05270097442680063</v>
       </c>
       <c r="P91" t="n">
-        <v>25.23088283372603</v>
+        <v>1.550421982103464</v>
       </c>
       <c r="Q91" t="n">
-        <v>-74.76911716627397</v>
+        <v>-98.44957801789654</v>
       </c>
       <c r="R91" t="n">
-        <v>-10.3116485080265</v>
+        <v>-170.0500567198522</v>
       </c>
       <c r="S91" t="n">
-        <v>-2.269948139449873</v>
+        <v>-6.894179763665475</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -8819,19 +8823,19 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>Evening Star</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Breakdown 20d, Breakdown 50d</t>
         </is>
       </c>
       <c r="W91" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="X91" t="n">
-        <v>65.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -8840,94 +8844,90 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>pattern: Double Top; evening star — inversione ribassista a 3 candele</t>
+          <t>RSI scarico (33) — zona di interesse long; breakdown minimi 50g — rottura supporto importante; shooting star — rifiuto di resistenza; sul supporto dei 20g (9.4570)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ENEL</t>
+          <t>HY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Enel</t>
+          <t>High Yield Corp ETF</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9.467000007629395</v>
+        <v>79.61000061035156</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.2948907663734901</v>
+        <v>-0.1254528607071204</v>
       </c>
       <c r="F92" t="n">
-        <v>-4.729800282157837</v>
+        <v>0.1635596979458809</v>
       </c>
       <c r="G92" t="n">
-        <v>-5.367850040143174</v>
+        <v>-0.05022085971253532</v>
       </c>
       <c r="H92" t="n">
-        <v>-2.089147493643406</v>
+        <v>0.08800565001068072</v>
       </c>
       <c r="I92" t="n">
-        <v>32.76732553495455</v>
+        <v>50.87558734859363</v>
       </c>
       <c r="J92" t="n">
-        <v>16.1251057430247</v>
+        <v>33.12835290843169</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.1151339726485842</v>
+        <v>0.6955265156545837</v>
       </c>
       <c r="L92" t="n">
-        <v>9.830919255784472</v>
+        <v>79.5705581987209</v>
       </c>
       <c r="M92" t="n">
-        <v>9.868737733211393</v>
+        <v>79.65617438340909</v>
       </c>
       <c r="N92" t="n">
-        <v>9.409189529188293</v>
+        <v>79.95327806176864</v>
       </c>
       <c r="O92" t="n">
-        <v>-0.05270097442680063</v>
+        <v>0.04044955675833924</v>
       </c>
       <c r="P92" t="n">
-        <v>1.550421982103464</v>
+        <v>65.27783664646294</v>
       </c>
       <c r="Q92" t="n">
-        <v>-98.44957801789654</v>
+        <v>-34.72216335353706</v>
       </c>
       <c r="R92" t="n">
-        <v>-170.0500567198522</v>
+        <v>54.05195809920398</v>
       </c>
       <c r="S92" t="n">
-        <v>-6.894179763665475</v>
+        <v>-0.08785102228429098</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
       <c r="V92" t="inlineStr">
         <is>
-          <t>Breakdown 20d, Breakdown 50d</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W92" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="X92" t="n">
-        <v>64.7</v>
+        <v>56.9</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -8936,90 +8936,86 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>RSI scarico (33) — zona di interesse long; breakdown minimi 50g — rottura supporto importante; shooting star — rifiuto di resistenza; sul supporto dei 20g (9.4570)</t>
+          <t>trend molto direzionale (ADX 33); pattern: Double Bottom; sul supporto dei 20g (79.14); vicino alla resistenza dei 20g (79.86); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HY</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>High Yield Corp ETF</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>79.61000061035156</v>
+        <v>49.06000137329102</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.1254528607071204</v>
+        <v>5.1548658384305</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1635596979458809</v>
+        <v>2.625250622536557</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.05022085971253532</v>
+        <v>-12.37721039012041</v>
       </c>
       <c r="H93" t="n">
-        <v>0.08800565001068072</v>
+        <v>-11.23575001454582</v>
       </c>
       <c r="I93" t="n">
-        <v>50.87558734859363</v>
+        <v>45.67593186154362</v>
       </c>
       <c r="J93" t="n">
-        <v>33.12835290843169</v>
+        <v>36.84167280312119</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6955265156545837</v>
+        <v>0.5525333717717191</v>
       </c>
       <c r="L93" t="n">
-        <v>79.5705581987209</v>
+        <v>49.41484796520847</v>
       </c>
       <c r="M93" t="n">
-        <v>79.65617438340909</v>
+        <v>52.45223899267671</v>
       </c>
       <c r="N93" t="n">
-        <v>79.95327806176864</v>
+        <v>42.40848209649783</v>
       </c>
       <c r="O93" t="n">
-        <v>0.04044955675833924</v>
+        <v>0.6248277849660617</v>
       </c>
       <c r="P93" t="n">
-        <v>65.27783664646294</v>
+        <v>92.60810833098793</v>
       </c>
       <c r="Q93" t="n">
-        <v>-34.72216335353706</v>
+        <v>-7.391891669012058</v>
       </c>
       <c r="R93" t="n">
-        <v>54.05195809920398</v>
+        <v>4.737883253103628</v>
       </c>
       <c r="S93" t="n">
-        <v>-0.08785102228429098</v>
+        <v>-8.810405076185102</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>Bearish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="n">
-        <v>45.8</v>
+        <v>44.8</v>
       </c>
       <c r="X93" t="n">
-        <v>56.9</v>
+        <v>57.2</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -9028,86 +9024,90 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 33); pattern: Double Bottom; sul supporto dei 20g (79.14); vicino alla resistenza dei 20g (79.86); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 37)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>49.06000137329102</v>
+        <v>64281.4296875</v>
       </c>
       <c r="E94" t="n">
-        <v>5.1548658384305</v>
+        <v>2.328571672861646</v>
       </c>
       <c r="F94" t="n">
-        <v>2.625250622536557</v>
+        <v>1.386375954245156</v>
       </c>
       <c r="G94" t="n">
-        <v>-12.37721039012041</v>
+        <v>0.8733340713690252</v>
       </c>
       <c r="H94" t="n">
-        <v>-11.23575001454582</v>
+        <v>-2.010972644369657</v>
       </c>
       <c r="I94" t="n">
-        <v>45.67593186154362</v>
+        <v>53.1430230765973</v>
       </c>
       <c r="J94" t="n">
-        <v>36.84167280312119</v>
+        <v>12.34161519005113</v>
       </c>
       <c r="K94" t="n">
-        <v>0.5525333717717191</v>
+        <v>0.6616335985338028</v>
       </c>
       <c r="L94" t="n">
-        <v>49.41484796520847</v>
+        <v>63784.20308090225</v>
       </c>
       <c r="M94" t="n">
-        <v>52.45223899267671</v>
+        <v>64295.5003025815</v>
       </c>
       <c r="N94" t="n">
-        <v>42.40848209649783</v>
+        <v>71585.53892304456</v>
       </c>
       <c r="O94" t="n">
-        <v>0.6248277849660617</v>
+        <v>-70.7006285911078</v>
       </c>
       <c r="P94" t="n">
-        <v>92.60810833098793</v>
+        <v>61.5557748042178</v>
       </c>
       <c r="Q94" t="n">
-        <v>-7.391891669012058</v>
+        <v>-38.4442251957822</v>
       </c>
       <c r="R94" t="n">
-        <v>4.737883253103628</v>
+        <v>0.7862259220121779</v>
       </c>
       <c r="S94" t="n">
-        <v>-8.810405076185102</v>
+        <v>0.6420191854122903</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bearish</t>
         </is>
       </c>
       <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W94" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="X94" t="n">
-        <v>57.2</v>
+        <v>65.5</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 37)</t>
+          <t>mercato laterale — ATR basso (ADX 12); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
@@ -9137,52 +9137,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>99.59300231933594</v>
+        <v>99.56400299072266</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.07725077859324081</v>
+        <v>-0.1063461223737461</v>
       </c>
       <c r="F95" t="n">
-        <v>-0.217408320374346</v>
+        <v>-0.246462853309537</v>
       </c>
       <c r="G95" t="n">
-        <v>-1.148384794703783</v>
+        <v>-1.177168247421678</v>
       </c>
       <c r="H95" t="n">
-        <v>0.6294847842261975</v>
+        <v>0.6001836543326977</v>
       </c>
       <c r="I95" t="n">
-        <v>38.03400707505514</v>
+        <v>37.65314466920759</v>
       </c>
       <c r="J95" t="n">
         <v>51.31321487528458</v>
       </c>
       <c r="K95" t="n">
-        <v>0.2461730390704203</v>
+        <v>0.2373113660685466</v>
       </c>
       <c r="L95" t="n">
-        <v>100.1411297142801</v>
+        <v>100.1383678734598</v>
       </c>
       <c r="M95" t="n">
-        <v>100.2118221852359</v>
+        <v>100.2106849566628</v>
       </c>
       <c r="N95" t="n">
-        <v>99.62909222729775</v>
+        <v>99.62880367676428</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.06608094389779001</v>
+        <v>-0.06793161330217218</v>
       </c>
       <c r="P95" t="n">
-        <v>13.5540991544035</v>
+        <v>12.23953379792146</v>
       </c>
       <c r="Q95" t="n">
-        <v>-86.4459008455965</v>
+        <v>-87.76046620207855</v>
       </c>
       <c r="R95" t="n">
-        <v>-89.58762789718288</v>
+        <v>-90.52862693247599</v>
       </c>
       <c r="S95" t="n">
-        <v>-1.383300895122375</v>
+        <v>-1.412015945351808</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 51); pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (99.29); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 51); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (99.29); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>44.3</v>
       </c>
       <c r="X96" t="n">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>43.8</v>
       </c>
       <c r="X97" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>43</v>
       </c>
       <c r="X99" t="n">
-        <v>63.3</v>
+        <v>63.2</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -9759,7 +9759,7 @@
         <v>42.2</v>
       </c>
       <c r="X101" t="n">
-        <v>64.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         <v>35.4</v>
       </c>
       <c r="X104" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>34.8</v>
       </c>
       <c r="X106" t="n">
-        <v>67.3</v>
+        <v>67.2</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
@@ -10249,52 +10249,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6.328999996185303</v>
+        <v>6.330999851226807</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1145599530295138</v>
+        <v>0.1461944304462781</v>
       </c>
       <c r="F107" t="n">
-        <v>0.217660038683043</v>
+        <v>0.2493270939519343</v>
       </c>
       <c r="G107" t="n">
-        <v>-1.049320962928224</v>
+        <v>-1.018054251844036</v>
       </c>
       <c r="H107" t="n">
-        <v>-7.868191618751608</v>
+        <v>-7.839079553403982</v>
       </c>
       <c r="I107" t="n">
-        <v>44.6890078599963</v>
+        <v>44.77447415184204</v>
       </c>
       <c r="J107" t="n">
         <v>12.73099831969866</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2900986099009846</v>
+        <v>0.2939371033394778</v>
       </c>
       <c r="L107" t="n">
-        <v>6.427556105210614</v>
+        <v>6.427746567595518</v>
       </c>
       <c r="M107" t="n">
-        <v>6.621917570732095</v>
+        <v>6.621995996419997</v>
       </c>
       <c r="N107" t="n">
-        <v>9.006302293780927</v>
+        <v>9.006322192836066</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.005951145029264644</v>
+        <v>-0.005823518952542635</v>
       </c>
       <c r="P107" t="n">
-        <v>20.52680076140593</v>
+        <v>20.78104729688769</v>
       </c>
       <c r="Q107" t="n">
-        <v>-79.47319923859406</v>
+        <v>-79.21895270311231</v>
       </c>
       <c r="R107" t="n">
-        <v>-85.3877636855071</v>
+        <v>-84.93855280220485</v>
       </c>
       <c r="S107" t="n">
-        <v>-3.583098778167781</v>
+        <v>-3.5526326972528</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="W107" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="X107" t="n">
         <v>71.3</v>
@@ -10499,7 +10499,7 @@
         <v>33.3</v>
       </c>
       <c r="X109" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -10529,52 +10529,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.7588000297546387</v>
+        <v>0.7608000040054321</v>
       </c>
       <c r="E110" t="n">
-        <v>0.1172965223842137</v>
+        <v>0.381176342168299</v>
       </c>
       <c r="F110" t="n">
-        <v>-1.881164050509043</v>
+        <v>-1.622551586458065</v>
       </c>
       <c r="G110" t="n">
-        <v>0.1889498977023063</v>
+        <v>0.4530185747610549</v>
       </c>
       <c r="H110" t="n">
-        <v>-25.00337853082981</v>
+        <v>-24.80570944022192</v>
       </c>
       <c r="I110" t="n">
-        <v>36.74319914364161</v>
+        <v>37.52714613513474</v>
       </c>
       <c r="J110" t="n">
         <v>7.333634205240194</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2339094782481924</v>
+        <v>0.2487190992463494</v>
       </c>
       <c r="L110" t="n">
-        <v>0.7892657379925117</v>
+        <v>0.7894562117306825</v>
       </c>
       <c r="M110" t="n">
-        <v>0.8370161520875015</v>
+        <v>0.8370945824502777</v>
       </c>
       <c r="N110" t="n">
-        <v>1.281922912900774</v>
+        <v>1.281942813142075</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.002987943173326917</v>
+        <v>-0.002860309488945782</v>
       </c>
       <c r="P110" t="n">
-        <v>5.775822286543949</v>
+        <v>7.517596046982315</v>
       </c>
       <c r="Q110" t="n">
-        <v>-94.22417771345606</v>
+        <v>-92.48240395301768</v>
       </c>
       <c r="R110" t="n">
-        <v>-78.09576362540261</v>
+        <v>-76.6071140684008</v>
       </c>
       <c r="S110" t="n">
-        <v>-0.2765111389753772</v>
+        <v>-0.01366928064568951</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Doji, Piercing Pattern</t>
+          <t>Bullish Engulfing, Piercing Pattern</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
@@ -10592,10 +10592,10 @@
         </is>
       </c>
       <c r="W110" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="X110" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 7); RSI scarico (37) — zona di interesse long; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (0.7484)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; mercato laterale — ATR basso (ADX 7); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; candela di inversione bullish (engulfing)</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
         <v>32.3</v>
       </c>
       <c r="X111" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -10901,73 +10901,69 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.000100016593933</v>
+        <v>1.00189995765686</v>
       </c>
       <c r="E114" t="n">
-        <v>0.819279743572876</v>
+        <v>1.000730357045754</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.4255397433919228</v>
+        <v>-0.2463295075546323</v>
       </c>
       <c r="G114" t="n">
-        <v>-6.117260891815002</v>
+        <v>-5.948294394047693</v>
       </c>
       <c r="H114" t="n">
-        <v>-17.75418841610497</v>
+        <v>-17.6061656073185</v>
       </c>
       <c r="I114" t="n">
-        <v>36.92910045175707</v>
+        <v>37.56970389481019</v>
       </c>
       <c r="J114" t="n">
         <v>47.71075223902492</v>
       </c>
       <c r="K114" t="n">
-        <v>0.2150528816545116</v>
+        <v>0.2275327759021555</v>
       </c>
       <c r="L114" t="n">
-        <v>1.031473506641595</v>
+        <v>1.031644929599969</v>
       </c>
       <c r="M114" t="n">
-        <v>1.076380431998655</v>
+        <v>1.076451017922691</v>
       </c>
       <c r="N114" t="n">
-        <v>1.348027385884358</v>
+        <v>1.348045295745681</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.002517113587590502</v>
+        <v>-0.002402245553945061</v>
       </c>
       <c r="P114" t="n">
-        <v>12.7276837596899</v>
+        <v>14.68940683829199</v>
       </c>
       <c r="Q114" t="n">
-        <v>-87.2723162403101</v>
+        <v>-85.31059316170801</v>
       </c>
       <c r="R114" t="n">
-        <v>-69.36929442233665</v>
+        <v>-68.41299186709286</v>
       </c>
       <c r="S114" t="n">
-        <v>-6.354077030690542</v>
+        <v>-6.185536745387632</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
           <t>Trend Bearish</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
+      <c r="U114" t="inlineStr"/>
       <c r="V114" t="inlineStr">
         <is>
           <t>Outside Bar</t>
         </is>
       </c>
       <c r="W114" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="X114" t="n">
-        <v>72.8</v>
+        <v>66.7</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -10976,7 +10972,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 48); RSI scarico (37) — zona di interesse long; segnale candlestick: Bullish Harami; sul supporto dei 20g (0.9884)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 48); RSI scarico (38) — zona di interesse long; sul supporto dei 20g (0.9884)</t>
         </is>
       </c>
     </row>
@@ -10997,52 +10993,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.70199990272522</v>
+        <v>2.703999996185303</v>
       </c>
       <c r="E115" t="n">
-        <v>-1.134289677086331</v>
+        <v>-1.061106602414907</v>
       </c>
       <c r="F115" t="n">
-        <v>-3.292770600616013</v>
+        <v>-3.221185291945439</v>
       </c>
       <c r="G115" t="n">
-        <v>-7.179667113281751</v>
+        <v>-7.110958990612238</v>
       </c>
       <c r="H115" t="n">
-        <v>-10.64814927967864</v>
+        <v>-10.58200862138632</v>
       </c>
       <c r="I115" t="n">
-        <v>41.27523920061635</v>
+        <v>41.3929242073435</v>
       </c>
       <c r="J115" t="n">
         <v>40.1278341940553</v>
       </c>
       <c r="K115" t="n">
-        <v>0.3222726362575351</v>
+        <v>0.3278624903772221</v>
       </c>
       <c r="L115" t="n">
-        <v>2.781930690051327</v>
+        <v>2.782121175142763</v>
       </c>
       <c r="M115" t="n">
-        <v>2.89148338636307</v>
+        <v>2.891561821400721</v>
       </c>
       <c r="N115" t="n">
-        <v>3.156394852953484</v>
+        <v>3.156414754380947</v>
       </c>
       <c r="O115" t="n">
-        <v>0.01195333543184743</v>
+        <v>0.01208097672388679</v>
       </c>
       <c r="P115" t="n">
-        <v>40.18690235198829</v>
+        <v>41.12152552248766</v>
       </c>
       <c r="Q115" t="n">
-        <v>-59.81309764801171</v>
+        <v>-58.87847447751233</v>
       </c>
       <c r="R115" t="n">
-        <v>-37.90873730980691</v>
+        <v>-37.61549099102061</v>
       </c>
       <c r="S115" t="n">
-        <v>-5.524475460350031</v>
+        <v>-5.454542120019745</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11059,7 +11055,7 @@
         <v>28.1</v>
       </c>
       <c r="X115" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -11151,7 +11147,7 @@
         <v>26.3</v>
       </c>
       <c r="X116" t="n">
-        <v>78.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -11243,7 +11239,7 @@
         <v>23.4</v>
       </c>
       <c r="X117" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -11481,7 +11477,7 @@
         <v>80.5</v>
       </c>
       <c r="X2" t="n">
-        <v>88</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -12305,7 +12301,7 @@
         <v>78.2</v>
       </c>
       <c r="X11" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -12393,7 +12389,7 @@
         <v>78.2</v>
       </c>
       <c r="X12" t="n">
-        <v>73.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -12485,7 +12481,7 @@
         <v>77.8</v>
       </c>
       <c r="X13" t="n">
-        <v>71.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -12761,7 +12757,7 @@
         <v>77.5</v>
       </c>
       <c r="X16" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -12857,7 +12853,7 @@
         <v>77.5</v>
       </c>
       <c r="X17" t="n">
-        <v>78.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -13045,7 +13041,7 @@
         <v>76.90000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -13171,52 +13167,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.611499786376953</v>
+        <v>6.612500190734863</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1818259983360049</v>
+        <v>0.1969847881038822</v>
       </c>
       <c r="F21" t="n">
-        <v>6.294212369631613</v>
+        <v>6.310296041523156</v>
       </c>
       <c r="G21" t="n">
-        <v>20.93469502744409</v>
+        <v>20.95299399134593</v>
       </c>
       <c r="H21" t="n">
-        <v>37.65354618226975</v>
+        <v>37.67437492187982</v>
       </c>
       <c r="I21" t="n">
-        <v>67.08926351609827</v>
+        <v>67.11136275597067</v>
       </c>
       <c r="J21" t="n">
         <v>37.41612245653306</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9124324329979286</v>
+        <v>0.9134132871343061</v>
       </c>
       <c r="L21" t="n">
-        <v>6.248402281712755</v>
+        <v>6.24849755831827</v>
       </c>
       <c r="M21" t="n">
-        <v>5.821142945824692</v>
+        <v>5.82118217736814</v>
       </c>
       <c r="N21" t="n">
-        <v>4.807613726320477</v>
+        <v>4.807623680592695</v>
       </c>
       <c r="O21" t="n">
-        <v>0.009219166444151855</v>
+        <v>0.009283009913147233</v>
       </c>
       <c r="P21" t="n">
-        <v>84.00982062001755</v>
+        <v>84.13287162812085</v>
       </c>
       <c r="Q21" t="n">
-        <v>-15.99017937998245</v>
+        <v>-15.86712837187915</v>
       </c>
       <c r="R21" t="n">
-        <v>81.08153351251238</v>
+        <v>81.14501225943123</v>
       </c>
       <c r="S21" t="n">
-        <v>18.84773586359594</v>
+        <v>18.86571904392225</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -13263,52 +13259,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>57.59000015258789</v>
+        <v>57.58000183105469</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9800544984863491</v>
+        <v>-0.9972455603148189</v>
       </c>
       <c r="F22" t="n">
-        <v>2.364027498638643</v>
+        <v>2.346255863673319</v>
       </c>
       <c r="G22" t="n">
-        <v>20.45596841325434</v>
+        <v>20.43505579822398</v>
       </c>
       <c r="H22" t="n">
-        <v>15.27222019202679</v>
+        <v>15.2522075384711</v>
       </c>
       <c r="I22" t="n">
-        <v>68.06107765943486</v>
+        <v>67.99271895614318</v>
       </c>
       <c r="J22" t="n">
         <v>49.93137166535269</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8580676300110285</v>
+        <v>0.8572348580824287</v>
       </c>
       <c r="L22" t="n">
-        <v>54.79172424668243</v>
+        <v>54.79077202558403</v>
       </c>
       <c r="M22" t="n">
-        <v>53.13293923366265</v>
+        <v>53.13254714262213</v>
       </c>
       <c r="N22" t="n">
-        <v>46.06436292084595</v>
+        <v>46.06426343505955</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5312050053426549</v>
+        <v>0.530566935820308</v>
       </c>
       <c r="P22" t="n">
-        <v>89.60710065579921</v>
+        <v>89.48037920704573</v>
       </c>
       <c r="Q22" t="n">
-        <v>-10.39289934420079</v>
+        <v>-10.51962079295427</v>
       </c>
       <c r="R22" t="n">
-        <v>116.3318229497082</v>
+        <v>116.2454286912017</v>
       </c>
       <c r="S22" t="n">
-        <v>16.27296905296922</v>
+        <v>16.2527826572906</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -13329,7 +13325,7 @@
         <v>76.3</v>
       </c>
       <c r="X22" t="n">
-        <v>87.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -13509,7 +13505,7 @@
         <v>76.09999999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -13693,7 +13689,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -13877,7 +13873,7 @@
         <v>75.09999999999999</v>
       </c>
       <c r="X28" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -13969,7 +13965,7 @@
         <v>74.7</v>
       </c>
       <c r="X29" t="n">
-        <v>75.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -14241,7 +14237,7 @@
         <v>74.3</v>
       </c>
       <c r="X32" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -14875,11 +14871,7 @@
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
           <t>Bear Flag / Consolidation</t>
@@ -14898,7 +14890,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); RSI in forza (61) — momentum positivo; pattern: Bear Flag / Consolidation; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); RSI in forza (61) — momentum positivo; pattern: Bear Flag / Consolidation</t>
         </is>
       </c>
     </row>
@@ -14985,7 +14977,7 @@
         <v>72.5</v>
       </c>
       <c r="X40" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -15077,7 +15069,7 @@
         <v>72.09999999999999</v>
       </c>
       <c r="X41" t="n">
-        <v>70.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
@@ -15169,7 +15161,7 @@
         <v>71</v>
       </c>
       <c r="X42" t="n">
-        <v>73.3</v>
+        <v>73.2</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -15241,7 +15233,7 @@
         <v>-13.48916181302316</v>
       </c>
       <c r="R43" t="n">
-        <v>66.18612803447365</v>
+        <v>66.20150615447001</v>
       </c>
       <c r="S43" t="n">
         <v>-4.664491854056985</v>
@@ -15353,7 +15345,7 @@
         <v>70.3</v>
       </c>
       <c r="X44" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -15383,52 +15375,52 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>62.59000015258789</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="E45" t="n">
-        <v>1.098369095221718</v>
+        <v>1.082219326916345</v>
       </c>
       <c r="F45" t="n">
-        <v>8.512482353387796</v>
+        <v>8.495148231542604</v>
       </c>
       <c r="G45" t="n">
-        <v>0.04795201188996234</v>
+        <v>0.03197004048054453</v>
       </c>
       <c r="H45" t="n">
-        <v>42.08853856217347</v>
+        <v>42.06584089655172</v>
       </c>
       <c r="I45" t="n">
-        <v>63.62369059211341</v>
+        <v>63.60876460595017</v>
       </c>
       <c r="J45" t="n">
         <v>18.9024833221388</v>
       </c>
       <c r="K45" t="n">
-        <v>0.9998224484497189</v>
+        <v>0.9991058350503246</v>
       </c>
       <c r="L45" t="n">
-        <v>57.40980307789044</v>
+        <v>57.40885085679204</v>
       </c>
       <c r="M45" t="n">
-        <v>53.59894741698155</v>
+        <v>53.59855532594102</v>
       </c>
       <c r="N45" t="n">
-        <v>45.72146250281013</v>
+        <v>45.72136301702373</v>
       </c>
       <c r="O45" t="n">
-        <v>0.247837377699538</v>
+        <v>0.2471993081771853</v>
       </c>
       <c r="P45" t="n">
-        <v>99.10536639858879</v>
+        <v>99.00597951818787</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.8946336014112103</v>
+        <v>-0.9940204818121251</v>
       </c>
       <c r="R45" t="n">
-        <v>113.1799110652852</v>
+        <v>113.1132243823528</v>
       </c>
       <c r="S45" t="n">
-        <v>5.63713105922008</v>
+        <v>5.620256254944622</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -15605,7 +15597,7 @@
         <v>-2.5192696177457</v>
       </c>
       <c r="R47" t="n">
-        <v>122.930860983945</v>
+        <v>123.0444339612373</v>
       </c>
       <c r="S47" t="n">
         <v>1.874652311732983</v>
@@ -15621,7 +15613,7 @@
         <v>69.7</v>
       </c>
       <c r="X47" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -15713,7 +15705,7 @@
         <v>69.7</v>
       </c>
       <c r="X48" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
@@ -15805,7 +15797,7 @@
         <v>69.59999999999999</v>
       </c>
       <c r="X49" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -15897,7 +15889,7 @@
         <v>68.59999999999999</v>
       </c>
       <c r="X50" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -16365,7 +16357,7 @@
         <v>67.3</v>
       </c>
       <c r="X55" t="n">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -16461,7 +16453,7 @@
         <v>66.90000000000001</v>
       </c>
       <c r="X56" t="n">
-        <v>69.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -16583,52 +16575,52 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4474.2001953125</v>
+        <v>4473.10009765625</v>
       </c>
       <c r="E58" t="n">
-        <v>2.141363689615683</v>
+        <v>2.116249597734221</v>
       </c>
       <c r="F58" t="n">
-        <v>11.50099059875753</v>
+        <v>11.4735752009048</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.3962556698018704</v>
+        <v>-0.4207458224343319</v>
       </c>
       <c r="H58" t="n">
-        <v>30.39753610932536</v>
+        <v>30.3654745077893</v>
       </c>
       <c r="I58" t="n">
-        <v>54.40085693638698</v>
+        <v>54.36658945792722</v>
       </c>
       <c r="J58" t="n">
         <v>46.58169649545812</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5810754392092095</v>
+        <v>0.5801171159399799</v>
       </c>
       <c r="L58" t="n">
-        <v>4343.609049231894</v>
+        <v>4343.504278026537</v>
       </c>
       <c r="M58" t="n">
-        <v>4231.907669093911</v>
+        <v>4231.864528009352</v>
       </c>
       <c r="N58" t="n">
-        <v>3188.223515273313</v>
+        <v>3188.212569027977</v>
       </c>
       <c r="O58" t="n">
-        <v>1.134804185529219</v>
+        <v>1.064598523135508</v>
       </c>
       <c r="P58" t="n">
-        <v>81.31262579472784</v>
+        <v>81.13781282830776</v>
       </c>
       <c r="Q58" t="n">
-        <v>-18.68737420527217</v>
+        <v>-18.86218717169225</v>
       </c>
       <c r="R58" t="n">
-        <v>19.68010998217452</v>
+        <v>19.59719163011285</v>
       </c>
       <c r="S58" t="n">
-        <v>-3.811669454745781</v>
+        <v>-3.835319839702245</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -16737,7 +16729,7 @@
         <v>66.5</v>
       </c>
       <c r="X59" t="n">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -17047,52 +17039,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.354481220245361</v>
+        <v>1.354646444320679</v>
       </c>
       <c r="E63" t="n">
-        <v>0.4009157679249808</v>
+        <v>0.4131630019366783</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4889658328856017</v>
+        <v>0.5012238075338793</v>
       </c>
       <c r="G63" t="n">
-        <v>1.56848056852974</v>
+        <v>1.580870225936937</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6081665986688245</v>
+        <v>-0.5960424558439814</v>
       </c>
       <c r="I63" t="n">
-        <v>55.59313437428791</v>
+        <v>55.65394163249478</v>
       </c>
       <c r="J63" t="n">
         <v>9.437466610925743</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7744566514494324</v>
+        <v>0.7779199827230453</v>
       </c>
       <c r="L63" t="n">
-        <v>1.342506492254453</v>
+        <v>1.342522227880673</v>
       </c>
       <c r="M63" t="n">
-        <v>1.338092625331539</v>
+        <v>1.338099104707041</v>
       </c>
       <c r="N63" t="n">
-        <v>1.308894563624632</v>
+        <v>1.308896207645282</v>
       </c>
       <c r="O63" t="n">
-        <v>0.001537979653319149</v>
+        <v>0.001548523867812329</v>
       </c>
       <c r="P63" t="n">
-        <v>93.77862361785836</v>
+        <v>94.16425991775318</v>
       </c>
       <c r="Q63" t="n">
-        <v>-6.221376382141645</v>
+        <v>-5.835740082246819</v>
       </c>
       <c r="R63" t="n">
-        <v>112.0735130959923</v>
+        <v>112.5099260666018</v>
       </c>
       <c r="S63" t="n">
-        <v>2.377110339687971</v>
+        <v>2.389598636414947</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -17101,7 +17093,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>Shooting Star, Morning Star</t>
+          <t>Morning Star</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -17110,10 +17102,10 @@
         </is>
       </c>
       <c r="W63" t="n">
-        <v>63.9</v>
+        <v>64.2</v>
       </c>
       <c r="X63" t="n">
-        <v>65.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -17122,7 +17114,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 9); pattern: Double Bottom; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (1.3658); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 9); pattern: Double Bottom; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3658); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -17205,7 +17197,7 @@
         <v>63.7</v>
       </c>
       <c r="X64" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -17235,52 +17227,52 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.158077597618103</v>
+        <v>1.158211708068848</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3937453792970613</v>
+        <v>0.4053714140916709</v>
       </c>
       <c r="F65" t="n">
-        <v>1.189347278197461</v>
+        <v>1.201065447171579</v>
       </c>
       <c r="G65" t="n">
-        <v>0.396059045082664</v>
+        <v>0.407685347809883</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.167916983651939</v>
+        <v>-0.1563559918154378</v>
       </c>
       <c r="I65" t="n">
-        <v>51.23956419039097</v>
+        <v>51.31593281653922</v>
       </c>
       <c r="J65" t="n">
         <v>28.68618473852175</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5209375595196939</v>
+        <v>0.5234759388862971</v>
       </c>
       <c r="L65" t="n">
-        <v>1.154684815237662</v>
+        <v>1.154697587661542</v>
       </c>
       <c r="M65" t="n">
-        <v>1.154187370981148</v>
+        <v>1.15419263021451</v>
       </c>
       <c r="N65" t="n">
-        <v>1.124851451313169</v>
+        <v>1.124852785745515</v>
       </c>
       <c r="O65" t="n">
-        <v>0.0004850893103177586</v>
+        <v>0.0004936479259776737</v>
       </c>
       <c r="P65" t="n">
-        <v>70.91323792782683</v>
+        <v>71.28565706321857</v>
       </c>
       <c r="Q65" t="n">
-        <v>-29.08676207217317</v>
+        <v>-28.71434293678144</v>
       </c>
       <c r="R65" t="n">
-        <v>13.30306311303171</v>
+        <v>13.61164157051207</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3381561031444269</v>
+        <v>0.3497757004577329</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -17298,7 +17290,7 @@
         </is>
       </c>
       <c r="W65" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="X65" t="n">
         <v>72.5</v>
@@ -17573,7 +17565,7 @@
         <v>61.2</v>
       </c>
       <c r="X68" t="n">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -17773,83 +17765,83 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DiaSorin</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>74.5</v>
+        <v>91.09999847412109</v>
       </c>
       <c r="E71" t="n">
-        <v>0.107500447491371</v>
+        <v>2.914597750673065</v>
       </c>
       <c r="F71" t="n">
-        <v>7.472591356001623</v>
+        <v>3.405221398364988</v>
       </c>
       <c r="G71" t="n">
-        <v>27.87504659515998</v>
+        <v>-19.07257819926091</v>
       </c>
       <c r="H71" t="n">
-        <v>-20.1671664770355</v>
+        <v>22.72665277417332</v>
       </c>
       <c r="I71" t="n">
-        <v>57.75197560117043</v>
+        <v>52.84434346804213</v>
       </c>
       <c r="J71" t="n">
-        <v>25.314641660463</v>
+        <v>22.04935717431122</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8736971336816569</v>
+        <v>0.4983471131546252</v>
       </c>
       <c r="L71" t="n">
-        <v>69.27243623458227</v>
+        <v>87.81717687996117</v>
       </c>
       <c r="M71" t="n">
-        <v>71.76216385434412</v>
+        <v>83.08859175880413</v>
       </c>
       <c r="N71" t="n">
-        <v>90.75357068711736</v>
+        <v>78.2262347298869</v>
       </c>
       <c r="O71" t="n">
-        <v>1.241976497390965</v>
+        <v>-0.7745709576143716</v>
       </c>
       <c r="P71" t="n">
-        <v>84.72833031126467</v>
+        <v>49.25968879244713</v>
       </c>
       <c r="Q71" t="n">
-        <v>-15.27166968873533</v>
+        <v>-50.74031120755286</v>
       </c>
       <c r="R71" t="n">
-        <v>114.4379710477334</v>
+        <v>-8.632471581048188</v>
       </c>
       <c r="S71" t="n">
-        <v>20.82387315011773</v>
+        <v>-16.44501559746914</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Inside Bar</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W71" t="n">
         <v>58.9</v>
       </c>
       <c r="X71" t="n">
-        <v>61</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
@@ -17858,90 +17850,90 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); pattern: Double Bottom</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 22); pattern: Bear Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>DiaSorin</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>90.87999725341797</v>
+        <v>74.5</v>
       </c>
       <c r="E72" t="n">
-        <v>2.666064956901937</v>
+        <v>0.107500447491371</v>
       </c>
       <c r="F72" t="n">
-        <v>3.155503776896751</v>
+        <v>7.472591356001623</v>
       </c>
       <c r="G72" t="n">
-        <v>-19.26801323639297</v>
+        <v>27.87504659515998</v>
       </c>
       <c r="H72" t="n">
-        <v>22.43027501483894</v>
+        <v>-20.1671664770355</v>
       </c>
       <c r="I72" t="n">
-        <v>52.71600831648347</v>
+        <v>57.75197560117043</v>
       </c>
       <c r="J72" t="n">
-        <v>22.04935717431122</v>
+        <v>25.314641660463</v>
       </c>
       <c r="K72" t="n">
-        <v>0.49361505280243</v>
+        <v>0.8736971336816569</v>
       </c>
       <c r="L72" t="n">
-        <v>87.79622438275135</v>
+        <v>69.27243623458227</v>
       </c>
       <c r="M72" t="n">
-        <v>83.07996425995303</v>
+        <v>71.76216385434412</v>
       </c>
       <c r="N72" t="n">
-        <v>78.22404566301422</v>
+        <v>90.75357068711736</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.788610921556681</v>
+        <v>1.241976497390965</v>
       </c>
       <c r="P72" t="n">
-        <v>48.74264718275438</v>
+        <v>84.72833031126467</v>
       </c>
       <c r="Q72" t="n">
-        <v>-51.25735281724562</v>
+        <v>-15.27166968873533</v>
       </c>
       <c r="R72" t="n">
-        <v>-8.975152844562922</v>
+        <v>114.4379710477334</v>
       </c>
       <c r="S72" t="n">
-        <v>-16.64679604612205</v>
+        <v>20.82387315011773</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Double Top, Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W72" t="n">
-        <v>58.8</v>
+        <v>58.9</v>
       </c>
       <c r="X72" t="n">
-        <v>82.7</v>
+        <v>60.9</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
@@ -17950,7 +17942,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 22); pattern: Bear Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend in sviluppo (ADX 25); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
@@ -17971,52 +17963,52 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>84.72000122070312</v>
+        <v>84.94999694824219</v>
       </c>
       <c r="E73" t="n">
-        <v>2.815533558085659</v>
+        <v>3.094654581483747</v>
       </c>
       <c r="F73" t="n">
-        <v>2.703362122298025</v>
+        <v>2.982178625504739</v>
       </c>
       <c r="G73" t="n">
-        <v>-14.97390431587593</v>
+        <v>-14.7430776107897</v>
       </c>
       <c r="H73" t="n">
-        <v>16.0865954011417</v>
+        <v>16.40174436929698</v>
       </c>
       <c r="I73" t="n">
-        <v>51.96746258590206</v>
+        <v>52.10481622466365</v>
       </c>
       <c r="J73" t="n">
-        <v>23.17497298725271</v>
+        <v>23.15624494543293</v>
       </c>
       <c r="K73" t="n">
-        <v>0.4633344645197356</v>
+        <v>0.46862092134329</v>
       </c>
       <c r="L73" t="n">
-        <v>82.6726145628092</v>
+        <v>82.69451891781291</v>
       </c>
       <c r="M73" t="n">
-        <v>78.36918404066779</v>
+        <v>78.37820348096345</v>
       </c>
       <c r="N73" t="n">
-        <v>73.95891477081986</v>
+        <v>73.96120328552173</v>
       </c>
       <c r="O73" t="n">
-        <v>-0.9785505171312154</v>
+        <v>-0.9638727271116312</v>
       </c>
       <c r="P73" t="n">
-        <v>41.66863110538112</v>
+        <v>42.21069032264445</v>
       </c>
       <c r="Q73" t="n">
-        <v>-58.33136889461888</v>
+        <v>-57.78930967735555</v>
       </c>
       <c r="R73" t="n">
-        <v>-16.91268107561004</v>
+        <v>-16.29772376240538</v>
       </c>
       <c r="S73" t="n">
-        <v>-24.04518511268063</v>
+        <v>-23.83898489244462</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -18024,12 +18016,16 @@
         </is>
       </c>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Bear Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W73" t="n">
-        <v>58.5</v>
+        <v>58.4</v>
       </c>
       <c r="X73" t="n">
-        <v>78.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -18038,7 +18034,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 23); in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 23); pattern: Bear Flag / Consolidation; in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -18059,52 +18055,52 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1783.5</v>
+        <v>1781.800048828125</v>
       </c>
       <c r="E74" t="n">
-        <v>1.914285714285713</v>
+        <v>1.817145647321428</v>
       </c>
       <c r="F74" t="n">
-        <v>11.06613188245673</v>
+        <v>10.96026869151241</v>
       </c>
       <c r="G74" t="n">
-        <v>-4.656258779146771</v>
+        <v>-4.747136101613458</v>
       </c>
       <c r="H74" t="n">
-        <v>47.29930030364334</v>
+        <v>47.15890130270834</v>
       </c>
       <c r="I74" t="n">
-        <v>49.06421831518202</v>
+        <v>48.96768180071066</v>
       </c>
       <c r="J74" t="n">
         <v>21.73110488473156</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4574496953592717</v>
+        <v>0.455172978529106</v>
       </c>
       <c r="L74" t="n">
-        <v>1781.855742109263</v>
+        <v>1781.693841997656</v>
       </c>
       <c r="M74" t="n">
-        <v>1752.987396560957</v>
+        <v>1752.920731809119</v>
       </c>
       <c r="N74" t="n">
-        <v>1348.524396129656</v>
+        <v>1348.507481192623</v>
       </c>
       <c r="O74" t="n">
-        <v>-4.202820911811642</v>
+        <v>-4.311307824204803</v>
       </c>
       <c r="P74" t="n">
-        <v>57.79607560991198</v>
+        <v>57.40742652966735</v>
       </c>
       <c r="Q74" t="n">
-        <v>-42.20392439008803</v>
+        <v>-42.59257347033265</v>
       </c>
       <c r="R74" t="n">
-        <v>-12.60508937808454</v>
+        <v>-12.7953889603345</v>
       </c>
       <c r="S74" t="n">
-        <v>-9.18118160429403</v>
+        <v>-9.267745975900466</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -18389,7 +18385,7 @@
         <v>56.9</v>
       </c>
       <c r="X77" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -18593,66 +18589,66 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>TRN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>159.4720001220703</v>
+        <v>9.744000434875488</v>
       </c>
       <c r="E80" t="n">
-        <v>0.02885680535351653</v>
+        <v>-0.1434713919705843</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.788445848761178</v>
+        <v>-5.855071731970163</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.1452653888013189</v>
+        <v>1.903369117229925</v>
       </c>
       <c r="H80" t="n">
-        <v>11.36779463537319</v>
+        <v>8.968910879874903</v>
       </c>
       <c r="I80" t="n">
-        <v>51.15487513336662</v>
+        <v>45.82416252152284</v>
       </c>
       <c r="J80" t="n">
-        <v>10.66711700623928</v>
+        <v>20.27159236104294</v>
       </c>
       <c r="K80" t="n">
-        <v>0.4314708786190705</v>
+        <v>0.09769700902956517</v>
       </c>
       <c r="L80" t="n">
-        <v>159.7467572568999</v>
+        <v>9.999911663084241</v>
       </c>
       <c r="M80" t="n">
-        <v>157.1101010406604</v>
+        <v>9.617973787792952</v>
       </c>
       <c r="N80" t="n">
-        <v>147.247045946964</v>
+        <v>8.376728776677156</v>
       </c>
       <c r="O80" t="n">
-        <v>-0.4116943875956509</v>
+        <v>-0.08729357112746794</v>
       </c>
       <c r="P80" t="n">
-        <v>48.33199515105716</v>
+        <v>17.9803956572599</v>
       </c>
       <c r="Q80" t="n">
-        <v>-51.66800484894284</v>
+        <v>-82.0196043427401</v>
       </c>
       <c r="R80" t="n">
-        <v>-17.0863797004378</v>
+        <v>-75.84384734961139</v>
       </c>
       <c r="S80" t="n">
-        <v>-0.0119111377461345</v>
+        <v>-2.851438740876033</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -18661,15 +18657,19 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>Hammer</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Double Top, Inside Bar</t>
+        </is>
+      </c>
       <c r="W80" t="n">
         <v>56.1</v>
       </c>
       <c r="X80" t="n">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
@@ -18678,19 +18678,19 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>mercato laterale — ATR basso (ADX 11); hammer — segnale di rimbalzo da supporto; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 20); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TRN</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Terna</t>
+          <t>Reply</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -18699,61 +18699,61 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>9.744000434875488</v>
+        <v>117.1999969482422</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.1434713919705843</v>
+        <v>-2.819238448505035</v>
       </c>
       <c r="F81" t="n">
-        <v>-5.855071731970163</v>
+        <v>19.8363939582062</v>
       </c>
       <c r="G81" t="n">
-        <v>1.903369117229925</v>
+        <v>50.06401951093138</v>
       </c>
       <c r="H81" t="n">
-        <v>8.968910879874903</v>
+        <v>-19.22812403975319</v>
       </c>
       <c r="I81" t="n">
-        <v>45.82416252152284</v>
+        <v>61.65200557128303</v>
       </c>
       <c r="J81" t="n">
-        <v>20.27159236104294</v>
+        <v>28.67138143768508</v>
       </c>
       <c r="K81" t="n">
-        <v>0.09769700902956517</v>
+        <v>0.9362239888519652</v>
       </c>
       <c r="L81" t="n">
-        <v>9.999911663084241</v>
+        <v>103.8303637693025</v>
       </c>
       <c r="M81" t="n">
-        <v>9.617973787792952</v>
+        <v>107.8703589809816</v>
       </c>
       <c r="N81" t="n">
-        <v>8.376728776677156</v>
+        <v>117.6303129436492</v>
       </c>
       <c r="O81" t="n">
-        <v>-0.08729357112746794</v>
+        <v>3.403479527470426</v>
       </c>
       <c r="P81" t="n">
-        <v>17.9803956572599</v>
+        <v>85.39324494236486</v>
       </c>
       <c r="Q81" t="n">
-        <v>-82.0196043427401</v>
+        <v>-14.60675505763515</v>
       </c>
       <c r="R81" t="n">
-        <v>-75.84384734961139</v>
+        <v>146.3767170104552</v>
       </c>
       <c r="S81" t="n">
-        <v>-2.851438740876033</v>
+        <v>42.83972283865909</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Bearish Harami</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -18762,10 +18762,10 @@
         </is>
       </c>
       <c r="W81" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="X81" t="n">
-        <v>62.6</v>
+        <v>68.3</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -18774,94 +18774,90 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 29); RSI in forza (62) — momentum positivo; pattern: Double Top; segnale candlestick: Bearish Harami</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Reply</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>117.1999969482422</v>
+        <v>159.3699951171875</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.819238448505035</v>
+        <v>-0.03512586256962935</v>
       </c>
       <c r="F82" t="n">
-        <v>19.8363939582062</v>
+        <v>-1.851266093400217</v>
       </c>
       <c r="G82" t="n">
-        <v>50.06401951093138</v>
+        <v>-0.2091366808387396</v>
       </c>
       <c r="H82" t="n">
-        <v>-19.22812403975319</v>
+        <v>11.29655910545651</v>
       </c>
       <c r="I82" t="n">
-        <v>61.65200557128303</v>
+        <v>50.83471467815142</v>
       </c>
       <c r="J82" t="n">
-        <v>28.67138143768508</v>
+        <v>10.66711700623928</v>
       </c>
       <c r="K82" t="n">
-        <v>0.9362239888519652</v>
+        <v>0.4180129814552445</v>
       </c>
       <c r="L82" t="n">
-        <v>103.8303637693025</v>
+        <v>159.7370424945301</v>
       </c>
       <c r="M82" t="n">
-        <v>107.8703589809816</v>
+        <v>157.1061008443905</v>
       </c>
       <c r="N82" t="n">
-        <v>117.6303129436492</v>
+        <v>147.246030971791</v>
       </c>
       <c r="O82" t="n">
-        <v>3.403479527470426</v>
+        <v>-0.4182041087049926</v>
       </c>
       <c r="P82" t="n">
-        <v>85.39324494236486</v>
+        <v>47.16261626005167</v>
       </c>
       <c r="Q82" t="n">
-        <v>-14.60675505763515</v>
+        <v>-52.83738373994833</v>
       </c>
       <c r="R82" t="n">
-        <v>146.3767170104552</v>
+        <v>-18.18302207396995</v>
       </c>
       <c r="S82" t="n">
-        <v>42.83972283865909</v>
+        <v>-0.07586772877660186</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>Bearish Harami</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Double Top, Inside Bar</t>
-        </is>
-      </c>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
       <c r="X82" t="n">
-        <v>68.3</v>
+        <v>57.5</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -18870,7 +18866,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 29); RSI in forza (62) — momentum positivo; pattern: Double Top; segnale candlestick: Bearish Harami</t>
+          <t>mercato laterale — ATR basso (ADX 11); doji — indecisione del mercato; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -18953,7 +18949,7 @@
         <v>55.2</v>
       </c>
       <c r="X83" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -18983,52 +18979,52 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>65.95500183105469</v>
+        <v>65.90499877929688</v>
       </c>
       <c r="E84" t="n">
-        <v>1.487971447177161</v>
+        <v>1.411029469341019</v>
       </c>
       <c r="F84" t="n">
-        <v>17.69692699638019</v>
+        <v>17.60769637900548</v>
       </c>
       <c r="G84" t="n">
-        <v>-5.162120112749824</v>
+        <v>-5.234020397564477</v>
       </c>
       <c r="H84" t="n">
-        <v>81.78938025071587</v>
+        <v>81.65155865209046</v>
       </c>
       <c r="I84" t="n">
-        <v>49.39700489788795</v>
+        <v>49.34235176419917</v>
       </c>
       <c r="J84" t="n">
         <v>16.99746909908013</v>
       </c>
       <c r="K84" t="n">
-        <v>0.4255919258323003</v>
+        <v>0.4241752209832129</v>
       </c>
       <c r="L84" t="n">
-        <v>66.08682209151199</v>
+        <v>66.08205989610649</v>
       </c>
       <c r="M84" t="n">
-        <v>63.36833864395712</v>
+        <v>63.36637773996662</v>
       </c>
       <c r="N84" t="n">
-        <v>43.3183213340707</v>
+        <v>43.31782379126714</v>
       </c>
       <c r="O84" t="n">
-        <v>-0.7224203697579379</v>
+        <v>-0.7256114477048778</v>
       </c>
       <c r="P84" t="n">
-        <v>46.65246850800257</v>
+        <v>46.43923585015542</v>
       </c>
       <c r="Q84" t="n">
-        <v>-53.34753149199743</v>
+        <v>-53.56076414984458</v>
       </c>
       <c r="R84" t="n">
-        <v>-23.61598072858632</v>
+        <v>-23.75967925746704</v>
       </c>
       <c r="S84" t="n">
-        <v>-9.321507833096732</v>
+        <v>-9.390254724329584</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -19038,7 +19034,7 @@
       <c r="U84" t="inlineStr"/>
       <c r="V84" t="inlineStr"/>
       <c r="W84" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="X84" t="n">
         <v>63.5</v>
@@ -19133,7 +19129,7 @@
         <v>52</v>
       </c>
       <c r="X85" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -19413,7 +19409,7 @@
         <v>49.2</v>
       </c>
       <c r="X88" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -19601,7 +19597,7 @@
         <v>47.2</v>
       </c>
       <c r="X90" t="n">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -19631,52 +19627,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>99.59300231933594</v>
+        <v>99.56400299072266</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.07725077859324081</v>
+        <v>-0.1063461223737461</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.148384794703783</v>
+        <v>-1.177168247421678</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.5561649506306221</v>
+        <v>-0.5851208449605738</v>
       </c>
       <c r="H91" t="n">
-        <v>1.4391953654187</v>
+        <v>1.409658465313646</v>
       </c>
       <c r="I91" t="n">
-        <v>49.31860443390087</v>
+        <v>49.13693869460087</v>
       </c>
       <c r="J91" t="n">
         <v>33.03382232287145</v>
       </c>
       <c r="K91" t="n">
-        <v>0.4808265984093253</v>
+        <v>0.4745895778959949</v>
       </c>
       <c r="L91" t="n">
-        <v>99.82839782037938</v>
+        <v>99.82563597955907</v>
       </c>
       <c r="M91" t="n">
-        <v>99.6788905249699</v>
+        <v>99.67775329639683</v>
       </c>
       <c r="N91" t="n">
-        <v>100.8121363559862</v>
+        <v>100.8118478054527</v>
       </c>
       <c r="O91" t="n">
-        <v>-0.09066185559161288</v>
+        <v>-0.0925125249959951</v>
       </c>
       <c r="P91" t="n">
-        <v>27.6393926507742</v>
+        <v>26.68859594266703</v>
       </c>
       <c r="Q91" t="n">
-        <v>-72.3606073492258</v>
+        <v>-73.31140405733296</v>
       </c>
       <c r="R91" t="n">
-        <v>-15.79614285968699</v>
+        <v>-16.56051707913631</v>
       </c>
       <c r="S91" t="n">
-        <v>-0.43686540567206</v>
+        <v>-0.4658560374497078</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -19685,7 +19681,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>Hammer, Bearish Harami</t>
+          <t>Hammer</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -19694,10 +19690,10 @@
         </is>
       </c>
       <c r="W91" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="X91" t="n">
-        <v>56.7</v>
+        <v>62.7</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -19727,52 +19723,52 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1330.5</v>
+        <v>1328</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6049149338374304</v>
+        <v>0.415879017013232</v>
       </c>
       <c r="F92" t="n">
-        <v>6.953376205787776</v>
+        <v>6.7524115755627</v>
       </c>
       <c r="G92" t="n">
-        <v>-4.342513721610364</v>
+        <v>-4.522253455316461</v>
       </c>
       <c r="H92" t="n">
-        <v>27.98191912712444</v>
+        <v>27.74144201489761</v>
       </c>
       <c r="I92" t="n">
-        <v>46.73097631196204</v>
+        <v>46.55504870522173</v>
       </c>
       <c r="J92" t="n">
         <v>40.97465263512212</v>
       </c>
       <c r="K92" t="n">
-        <v>0.4459571000516021</v>
+        <v>0.4408596638219468</v>
       </c>
       <c r="L92" t="n">
-        <v>1355.119593310829</v>
+        <v>1354.881498072733</v>
       </c>
       <c r="M92" t="n">
-        <v>1378.714463641599</v>
+        <v>1378.616424425912</v>
       </c>
       <c r="N92" t="n">
-        <v>1362.12576405936</v>
+        <v>1362.100888437469</v>
       </c>
       <c r="O92" t="n">
-        <v>6.046063542002152</v>
+        <v>5.886519382458133</v>
       </c>
       <c r="P92" t="n">
-        <v>65.96489324439571</v>
+        <v>64.990234375</v>
       </c>
       <c r="Q92" t="n">
-        <v>-34.03510675560429</v>
+        <v>-35.009765625</v>
       </c>
       <c r="R92" t="n">
-        <v>-10.30644541252428</v>
+        <v>-10.62811316024573</v>
       </c>
       <c r="S92" t="n">
-        <v>-10.78852231327249</v>
+        <v>-10.95615004286048</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -19790,10 +19786,10 @@
         </is>
       </c>
       <c r="W92" t="n">
-        <v>45.6</v>
+        <v>45.5</v>
       </c>
       <c r="X92" t="n">
-        <v>72.7</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -19889,7 +19885,7 @@
         <v>44.6</v>
       </c>
       <c r="X93" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -20011,52 +20007,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>9.475000381469727</v>
+        <v>9.503000259399414</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9641700828626476</v>
+        <v>1.262532544474904</v>
       </c>
       <c r="F95" t="n">
-        <v>13.18694488856018</v>
+        <v>13.52142726455163</v>
       </c>
       <c r="G95" t="n">
-        <v>12.72700825864157</v>
+        <v>13.06013146112648</v>
       </c>
       <c r="H95" t="n">
-        <v>-28.74284192560458</v>
+        <v>-28.53226760925928</v>
       </c>
       <c r="I95" t="n">
-        <v>50.30984332977362</v>
+        <v>50.48201639498513</v>
       </c>
       <c r="J95" t="n">
         <v>19.48943010362635</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7214043621302496</v>
+        <v>0.72915248066108</v>
       </c>
       <c r="L95" t="n">
-        <v>8.988697203511993</v>
+        <v>8.991363858552916</v>
       </c>
       <c r="M95" t="n">
-        <v>10.93931138084122</v>
+        <v>10.94040941526983</v>
       </c>
       <c r="N95" t="n">
-        <v>12.87703576058433</v>
+        <v>12.87731436633487</v>
       </c>
       <c r="O95" t="n">
-        <v>0.3361247510898155</v>
+        <v>0.3379116378864682</v>
       </c>
       <c r="P95" t="n">
-        <v>82.13838398339944</v>
+        <v>83.07611059999971</v>
       </c>
       <c r="Q95" t="n">
-        <v>-17.86161601660057</v>
+        <v>-16.92388940000029</v>
       </c>
       <c r="R95" t="n">
-        <v>62.9509429559967</v>
+        <v>63.68168341859458</v>
       </c>
       <c r="S95" t="n">
-        <v>7.528382264241085</v>
+        <v>7.846142840089043</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -20070,7 +20066,7 @@
         </is>
       </c>
       <c r="W95" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="X95" t="n">
         <v>63.4</v>
@@ -20375,52 +20371,52 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>64320.421875</v>
+        <v>64281.4296875</v>
       </c>
       <c r="E99" t="n">
-        <v>2.390642707570612</v>
+        <v>2.328571672861646</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.5725432142778208</v>
+        <v>-0.6328179128046951</v>
       </c>
       <c r="G99" t="n">
-        <v>-2.47820777211708</v>
+        <v>-2.537327222783559</v>
       </c>
       <c r="H99" t="n">
-        <v>-39.0628243966486</v>
+        <v>-39.09976559988672</v>
       </c>
       <c r="I99" t="n">
-        <v>41.23537677945078</v>
+        <v>41.17469143245089</v>
       </c>
       <c r="J99" t="n">
         <v>34.41894056095592</v>
       </c>
       <c r="K99" t="n">
-        <v>0.336675696118335</v>
+        <v>0.3353641516969452</v>
       </c>
       <c r="L99" t="n">
-        <v>67992.61722622353</v>
+        <v>67988.90368455688</v>
       </c>
       <c r="M99" t="n">
-        <v>76720.32189114708</v>
+        <v>76718.79278575492</v>
       </c>
       <c r="N99" t="n">
-        <v>68407.61628458909</v>
+        <v>68407.22830262392</v>
       </c>
       <c r="O99" t="n">
-        <v>533.6939300088252</v>
+        <v>531.2055396954338</v>
       </c>
       <c r="P99" t="n">
-        <v>32.29362672052905</v>
+        <v>32.1020452502305</v>
       </c>
       <c r="Q99" t="n">
-        <v>-67.70637327947095</v>
+        <v>-67.8979547497695</v>
       </c>
       <c r="R99" t="n">
-        <v>-65.31565674657995</v>
+        <v>-65.47140345739295</v>
       </c>
       <c r="S99" t="n">
-        <v>-6.757535916068558</v>
+        <v>-6.814061161652118</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -20438,7 +20434,7 @@
         </is>
       </c>
       <c r="W99" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="X99" t="n">
         <v>70.3</v>
@@ -20537,7 +20533,7 @@
         <v>39.3</v>
       </c>
       <c r="X100" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
@@ -20721,7 +20717,7 @@
         <v>35.6</v>
       </c>
       <c r="X102" t="n">
-        <v>66.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
@@ -20737,66 +20733,66 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>SOL</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>US Treasury 7-10Y ETF</t>
+          <t>Solana</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>92.83999633789062</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.2149662249233075</v>
+        <v>1.772204604759597</v>
       </c>
       <c r="F103" t="n">
-        <v>-1.065643690350637</v>
+        <v>-0.648628697116127</v>
       </c>
       <c r="G103" t="n">
-        <v>-1.860467404459776</v>
+        <v>-6.831536186972564</v>
       </c>
       <c r="H103" t="n">
-        <v>-1.537813727391679</v>
+        <v>-50.35807846832162</v>
       </c>
       <c r="I103" t="n">
-        <v>37.96605582404076</v>
+        <v>40.93310559599517</v>
       </c>
       <c r="J103" t="n">
-        <v>41.43537560135021</v>
+        <v>18.21793026728699</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1546062528993552</v>
+        <v>0.391557775392169</v>
       </c>
       <c r="L103" t="n">
-        <v>94.02658446102787</v>
+        <v>81.37869883615363</v>
       </c>
       <c r="M103" t="n">
-        <v>94.80007490746264</v>
+        <v>104.2776738330174</v>
       </c>
       <c r="N103" t="n">
-        <v>97.10695338529929</v>
+        <v>111.287403931817</v>
       </c>
       <c r="O103" t="n">
-        <v>-0.09404901995732751</v>
+        <v>2.378059566342573</v>
       </c>
       <c r="P103" t="n">
-        <v>6.275896853113368</v>
+        <v>56.42722317423826</v>
       </c>
       <c r="Q103" t="n">
-        <v>-93.72410314688663</v>
+        <v>-43.57277682576174</v>
       </c>
       <c r="R103" t="n">
-        <v>-70.7507353037613</v>
+        <v>-22.39199460054381</v>
       </c>
       <c r="S103" t="n">
-        <v>-2.540421734275222</v>
+        <v>-7.323350761760461</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -20805,19 +20801,19 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>Evening Star</t>
+          <t>Piercing Pattern</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>Double Bottom, Inside Bar</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W103" t="n">
-        <v>33.9</v>
+        <v>34</v>
       </c>
       <c r="X103" t="n">
-        <v>74.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -20826,73 +20822,73 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 41); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; evening star — inversione ribassista a 3 candele; sul supporto dei 20g (92.69); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); segnale candlestick: Piercing Pattern</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SOL</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Solana</t>
+          <t>US Treasury 7-10Y ETF</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Bond</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>75.70999908447266</v>
+        <v>92.83999633789062</v>
       </c>
       <c r="E104" t="n">
-        <v>1.570965666452873</v>
+        <v>-0.2149662249233075</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.8450808085541661</v>
+        <v>-1.065643690350637</v>
       </c>
       <c r="G104" t="n">
-        <v>-7.015762546362292</v>
+        <v>-1.860467404459776</v>
       </c>
       <c r="H104" t="n">
-        <v>-50.45623776066807</v>
+        <v>-1.537813727391679</v>
       </c>
       <c r="I104" t="n">
-        <v>40.79749619833746</v>
+        <v>37.96605582404076</v>
       </c>
       <c r="J104" t="n">
-        <v>18.21793026728699</v>
+        <v>41.43537560135021</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3865026659829368</v>
+        <v>0.1546062528993552</v>
       </c>
       <c r="L104" t="n">
-        <v>81.36441297654612</v>
+        <v>94.02658446102787</v>
       </c>
       <c r="M104" t="n">
-        <v>104.2717914202379</v>
+        <v>94.80007490746264</v>
       </c>
       <c r="N104" t="n">
-        <v>111.2859113793207</v>
+        <v>97.10695338529929</v>
       </c>
       <c r="O104" t="n">
-        <v>2.368486819391897</v>
+        <v>-0.09404901995732751</v>
       </c>
       <c r="P104" t="n">
-        <v>55.87921313551716</v>
+        <v>6.275896853113368</v>
       </c>
       <c r="Q104" t="n">
-        <v>-44.12078686448284</v>
+        <v>-93.72410314688663</v>
       </c>
       <c r="R104" t="n">
-        <v>-22.69904280772421</v>
+        <v>-70.7507353037613</v>
       </c>
       <c r="S104" t="n">
-        <v>-7.506604633197722</v>
+        <v>-2.540421734275222</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -20901,19 +20897,19 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>Piercing Pattern</t>
+          <t>Evening Star</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Bottom, Inside Bar</t>
         </is>
       </c>
       <c r="W104" t="n">
         <v>33.9</v>
       </c>
       <c r="X104" t="n">
-        <v>74</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20922,7 +20918,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); segnale candlestick: Piercing Pattern</t>
+          <t>EMA allineate al ribasso (EMA20&lt;EMA50&lt;EMA200); trend molto direzionale (ADX 41); RSI scarico (38) — zona di interesse long; pattern: Double Bottom; evening star — inversione ribassista a 3 candele; sul supporto dei 20g (92.69); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21005,7 @@
         <v>33.6</v>
       </c>
       <c r="X105" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -21039,52 +21035,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2.70199990272522</v>
+        <v>2.703999996185303</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.134289677086331</v>
+        <v>-1.061106602414907</v>
       </c>
       <c r="F106" t="n">
-        <v>-7.179667113281751</v>
+        <v>-7.110958990612238</v>
       </c>
       <c r="G106" t="n">
-        <v>-12.69790378843653</v>
+        <v>-12.63328041391005</v>
       </c>
       <c r="H106" t="n">
-        <v>-24.54622074603775</v>
+        <v>-24.49036781640877</v>
       </c>
       <c r="I106" t="n">
-        <v>41.99264943599878</v>
+        <v>42.03073680852913</v>
       </c>
       <c r="J106" t="n">
         <v>18.13201987209406</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2845058097288533</v>
+        <v>0.2864342764463698</v>
       </c>
       <c r="L106" t="n">
-        <v>2.962435270554198</v>
+        <v>2.962625755645635</v>
       </c>
       <c r="M106" t="n">
-        <v>3.162325516497378</v>
+        <v>3.162403951535028</v>
       </c>
       <c r="N106" t="n">
-        <v>3.304895198130162</v>
+        <v>3.304915099557626</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.01636290731681775</v>
+        <v>-0.01623526602477837</v>
       </c>
       <c r="P106" t="n">
-        <v>10.42423766024979</v>
+        <v>10.66667321715654</v>
       </c>
       <c r="Q106" t="n">
-        <v>-89.57576233975021</v>
+        <v>-89.33332678284346</v>
       </c>
       <c r="R106" t="n">
-        <v>-47.68771843812635</v>
+        <v>-47.56099075838164</v>
       </c>
       <c r="S106" t="n">
-        <v>-3.500001830714117</v>
+        <v>-3.428569920208968</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -21093,12 +21089,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>Hammer</t>
+          <t>Hammer, Morning Star</t>
         </is>
       </c>
       <c r="V106" t="inlineStr"/>
       <c r="W106" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="X106" t="n">
         <v>80.09999999999999</v>
@@ -21197,7 +21193,7 @@
         <v>32.8</v>
       </c>
       <c r="X107" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -21227,52 +21223,52 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1905.77001953125</v>
+        <v>1904.93994140625</v>
       </c>
       <c r="E108" t="n">
-        <v>1.698398856490768</v>
+        <v>1.65410305197442</v>
       </c>
       <c r="F108" t="n">
-        <v>1.830687586350566</v>
+        <v>1.786334162090109</v>
       </c>
       <c r="G108" t="n">
-        <v>-3.873259057298295</v>
+        <v>-3.915128067759333</v>
       </c>
       <c r="H108" t="n">
-        <v>-25.17110827471075</v>
+        <v>-25.20370078351433</v>
       </c>
       <c r="I108" t="n">
-        <v>43.22714561604216</v>
+        <v>43.19390868795493</v>
       </c>
       <c r="J108" t="n">
         <v>36.09168693629608</v>
       </c>
       <c r="K108" t="n">
-        <v>0.4319801429904085</v>
+        <v>0.4311600749164429</v>
       </c>
       <c r="L108" t="n">
-        <v>1985.937858506524</v>
+        <v>1985.858803447</v>
       </c>
       <c r="M108" t="n">
-        <v>2346.859875766017</v>
+        <v>2346.827323682684</v>
       </c>
       <c r="N108" t="n">
-        <v>2463.031652639253</v>
+        <v>2463.023393155422</v>
       </c>
       <c r="O108" t="n">
-        <v>47.31732911424888</v>
+        <v>47.26435546752538</v>
       </c>
       <c r="P108" t="n">
-        <v>61.47650075756109</v>
+        <v>61.34868992961571</v>
       </c>
       <c r="Q108" t="n">
-        <v>-38.52349924243891</v>
+        <v>-38.6513100703843</v>
       </c>
       <c r="R108" t="n">
-        <v>-24.15940595089975</v>
+        <v>-24.24127346708854</v>
       </c>
       <c r="S108" t="n">
-        <v>-9.636131313432994</v>
+        <v>-9.675490244425911</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -21323,52 +21319,52 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.000100016593933</v>
+        <v>1.00189995765686</v>
       </c>
       <c r="E109" t="n">
-        <v>0.819279743572876</v>
+        <v>1.000730357045754</v>
       </c>
       <c r="F109" t="n">
-        <v>-8.743423980980836</v>
+        <v>-8.579183949270618</v>
       </c>
       <c r="G109" t="n">
-        <v>-24.65018405787391</v>
+        <v>-24.51457239349244</v>
       </c>
       <c r="H109" t="n">
-        <v>-53.85240641734762</v>
+        <v>-53.76935177554532</v>
       </c>
       <c r="I109" t="n">
-        <v>31.35837703111092</v>
+        <v>31.50039797449259</v>
       </c>
       <c r="J109" t="n">
         <v>22.29427526871542</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1750106390870413</v>
+        <v>0.1774354671757966</v>
       </c>
       <c r="L109" t="n">
-        <v>1.208080886410938</v>
+        <v>1.208252309369312</v>
       </c>
       <c r="M109" t="n">
-        <v>1.525658982614631</v>
+        <v>1.525729568538667</v>
       </c>
       <c r="N109" t="n">
-        <v>1.376804948366154</v>
+        <v>1.376822858227476</v>
       </c>
       <c r="O109" t="n">
-        <v>0.01133029139105793</v>
+        <v>0.01144515942470353</v>
       </c>
       <c r="P109" t="n">
-        <v>2.82984625886164</v>
+        <v>3.266011614610543</v>
       </c>
       <c r="Q109" t="n">
-        <v>-97.17015374113836</v>
+        <v>-96.73398838538945</v>
       </c>
       <c r="R109" t="n">
-        <v>-70.5210340491233</v>
+        <v>-70.34483872575925</v>
       </c>
       <c r="S109" t="n">
-        <v>-24.54899539223888</v>
+        <v>-24.4132016124376</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -21398,7 +21394,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); RSI scarico (31) — zona di interesse long; segnale candlestick: Bullish Harami; sul supporto dei 20g (0.9884)</t>
+          <t>trend in sviluppo (ADX 22); RSI scarico (32) — zona di interesse long; segnale candlestick: Bullish Harami; sul supporto dei 20g (0.9884)</t>
         </is>
       </c>
     </row>
@@ -21481,7 +21477,7 @@
         <v>28.4</v>
       </c>
       <c r="X110" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21569,7 +21565,7 @@
         <v>28.1</v>
       </c>
       <c r="X111" t="n">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21687,52 +21683,52 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>6.328999996185303</v>
+        <v>6.330999851226807</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1145599530295138</v>
+        <v>0.1461944304462781</v>
       </c>
       <c r="F113" t="n">
-        <v>-1.964046546872045</v>
+        <v>-1.933068873324872</v>
       </c>
       <c r="G113" t="n">
-        <v>-26.37019680694498</v>
+        <v>-26.3469310567144</v>
       </c>
       <c r="H113" t="n">
-        <v>-66.88978417613633</v>
+        <v>-66.87932191794697</v>
       </c>
       <c r="I113" t="n">
-        <v>33.58253205545469</v>
+        <v>33.60079856593615</v>
       </c>
       <c r="J113" t="n">
         <v>39.1228243100481</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2722861748887663</v>
+        <v>0.2726057779846602</v>
       </c>
       <c r="L113" t="n">
-        <v>7.673443158728009</v>
+        <v>7.673633621112914</v>
       </c>
       <c r="M113" t="n">
-        <v>11.64056341058505</v>
+        <v>11.64064183627296</v>
       </c>
       <c r="N113" t="n">
-        <v>20.5067011158978</v>
+        <v>20.50672101495294</v>
       </c>
       <c r="O113" t="n">
-        <v>0.2266763368109914</v>
+        <v>0.2268039628877148</v>
       </c>
       <c r="P113" t="n">
-        <v>16.34470972974849</v>
+        <v>16.39615022931743</v>
       </c>
       <c r="Q113" t="n">
-        <v>-83.65529027025151</v>
+        <v>-83.60384977068257</v>
       </c>
       <c r="R113" t="n">
-        <v>-58.56719385815288</v>
+        <v>-58.540763770466</v>
       </c>
       <c r="S113" t="n">
-        <v>-30.10515237251877</v>
+        <v>-30.08306680394756</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -21861,12 +21857,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -21875,52 +21871,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.1733700037002563</v>
+        <v>0.7608000040054321</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.8447402815664584</v>
+        <v>0.381176342168299</v>
       </c>
       <c r="F115" t="n">
-        <v>4.450453997784876</v>
+        <v>-7.01687494208636</v>
       </c>
       <c r="G115" t="n">
-        <v>-27.63042543342448</v>
+        <v>-39.52353431309701</v>
       </c>
       <c r="H115" t="n">
-        <v>-72.64806019659925</v>
+        <v>-80.09362406756308</v>
       </c>
       <c r="I115" t="n">
-        <v>37.71564283343346</v>
+        <v>27.71617526049084</v>
       </c>
       <c r="J115" t="n">
-        <v>23.75626923280495</v>
+        <v>42.69676028620942</v>
       </c>
       <c r="K115" t="n">
-        <v>0.322541221556366</v>
+        <v>0.2076352123359838</v>
       </c>
       <c r="L115" t="n">
-        <v>0.2100736564830118</v>
+        <v>1.032248188559735</v>
       </c>
       <c r="M115" t="n">
-        <v>0.3283775555879991</v>
+        <v>1.806281234079708</v>
       </c>
       <c r="N115" t="n">
-        <v>0.4978164266199274</v>
+        <v>5.070313353757882</v>
       </c>
       <c r="O115" t="n">
-        <v>0.01039086519709506</v>
+        <v>0.0362994537564596</v>
       </c>
       <c r="P115" t="n">
-        <v>30.06407899398124</v>
+        <v>2.09500886533276</v>
       </c>
       <c r="Q115" t="n">
-        <v>-69.93592100601876</v>
+        <v>-97.90499113466724</v>
       </c>
       <c r="R115" t="n">
-        <v>-38.93936812378541</v>
+        <v>-56.98120232043372</v>
       </c>
       <c r="S115" t="n">
-        <v>-30.7702450667243</v>
+        <v>-38.79393011920699</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -21928,12 +21924,16 @@
         </is>
       </c>
       <c r="U115" t="inlineStr"/>
-      <c r="V115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Inside Bar</t>
+        </is>
+      </c>
       <c r="W115" t="n">
         <v>21</v>
       </c>
       <c r="X115" t="n">
-        <v>74.5</v>
+        <v>72</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -21942,19 +21942,19 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 24); RSI scarico (38) — zona di interesse long</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); RSI ipervenduto (28) — possibile rimbalzo</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -21963,52 +21963,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.7588000297546387</v>
+        <v>0.1738699972629547</v>
       </c>
       <c r="E116" t="n">
-        <v>0.1172965223842137</v>
+        <v>-0.5587796741443385</v>
       </c>
       <c r="F116" t="n">
-        <v>-7.261306928015754</v>
+        <v>4.751685776669223</v>
       </c>
       <c r="G116" t="n">
-        <v>-39.68251351067327</v>
+        <v>-27.42171388790783</v>
       </c>
       <c r="H116" t="n">
-        <v>-80.14595350904821</v>
+        <v>-72.56917807433398</v>
       </c>
       <c r="I116" t="n">
-        <v>27.57798956478918</v>
+        <v>37.78241698906499</v>
       </c>
       <c r="J116" t="n">
-        <v>42.69676028620942</v>
+        <v>23.75626923280495</v>
       </c>
       <c r="K116" t="n">
-        <v>0.205575221589803</v>
+        <v>0.3253289046108054</v>
       </c>
       <c r="L116" t="n">
-        <v>1.032057714821564</v>
+        <v>0.2101212749175544</v>
       </c>
       <c r="M116" t="n">
-        <v>1.806202803716931</v>
+        <v>0.3283971631786932</v>
       </c>
       <c r="N116" t="n">
-        <v>5.07029345351658</v>
+        <v>0.4978214016802527</v>
       </c>
       <c r="O116" t="n">
-        <v>0.03617182007207848</v>
+        <v>0.01042277361819034</v>
       </c>
       <c r="P116" t="n">
-        <v>1.75822157359782</v>
+        <v>30.49758570071268</v>
       </c>
       <c r="Q116" t="n">
-        <v>-98.24177842640218</v>
+        <v>-69.50241429928732</v>
       </c>
       <c r="R116" t="n">
-        <v>-57.11311133484763</v>
+        <v>-38.74079279157549</v>
       </c>
       <c r="S116" t="n">
-        <v>-38.95482728417727</v>
+        <v>-30.57058866091566</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -22017,19 +22017,15 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Doji</t>
-        </is>
-      </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>Inside Bar</t>
-        </is>
-      </c>
+          <t>Shooting Star</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr"/>
       <c r="W116" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="X116" t="n">
-        <v>72</v>
+        <v>80.5</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -22038,7 +22034,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 43); RSI ipervenduto (28) — possibile rimbalzo; doji — indecisione del mercato; sul supporto dei 20g (0.7484)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend in sviluppo (ADX 24); RSI scarico (38) — zona di interesse long; shooting star — rifiuto di resistenza</t>
         </is>
       </c>
     </row>
@@ -22723,7 +22719,7 @@
         <v>80.59999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -22845,52 +22841,52 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62.59000015258789</v>
+        <v>62.58000183105469</v>
       </c>
       <c r="E8" t="n">
-        <v>5.104955423131918</v>
+        <v>5.088165630249808</v>
       </c>
       <c r="F8" t="n">
-        <v>2.171077158823853</v>
+        <v>2.15475603279196</v>
       </c>
       <c r="G8" t="n">
-        <v>31.037372453421</v>
+        <v>31.01644013548743</v>
       </c>
       <c r="H8" t="n">
-        <v>132.3742394416195</v>
+        <v>132.3371192569845</v>
       </c>
       <c r="I8" t="n">
-        <v>67.72666874065887</v>
+        <v>67.71832951862228</v>
       </c>
       <c r="J8" t="n">
         <v>35.88733826701044</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9503697870707559</v>
+        <v>0.9501053752925555</v>
       </c>
       <c r="L8" t="n">
-        <v>51.62384637613923</v>
+        <v>51.62289415504083</v>
       </c>
       <c r="M8" t="n">
-        <v>45.69647891326969</v>
+        <v>45.69608682222918</v>
       </c>
       <c r="N8" t="n">
-        <v>40.46667652803082</v>
+        <v>40.46653669136602</v>
       </c>
       <c r="O8" t="n">
-        <v>1.268422459901665</v>
+        <v>1.267784390379318</v>
       </c>
       <c r="P8" t="n">
-        <v>95.93648324107799</v>
+        <v>95.88978393419121</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.063516758922</v>
+        <v>-4.110216065808785</v>
       </c>
       <c r="R8" t="n">
-        <v>172.990696573634</v>
+        <v>172.9504412498936</v>
       </c>
       <c r="S8" t="n">
-        <v>46.13588016988095</v>
+        <v>46.11253596930713</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -23639,7 +23635,7 @@
         <v>80.2</v>
       </c>
       <c r="X16" t="n">
-        <v>79.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -24271,7 +24267,7 @@
         <v>79.7</v>
       </c>
       <c r="X23" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -24551,7 +24547,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -25045,52 +25041,52 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.611499786376953</v>
+        <v>6.612500190734863</v>
       </c>
       <c r="E32" t="n">
-        <v>2.726847725503001</v>
+        <v>2.742391609562533</v>
       </c>
       <c r="F32" t="n">
-        <v>18.32661608110779</v>
+        <v>18.34452040935541</v>
       </c>
       <c r="G32" t="n">
-        <v>62.02670217889042</v>
+        <v>62.05121888828992</v>
       </c>
       <c r="H32" t="n">
-        <v>53.88105363416153</v>
+        <v>53.90433780290229</v>
       </c>
       <c r="I32" t="n">
-        <v>69.54474038822018</v>
+        <v>69.55295046015129</v>
       </c>
       <c r="J32" t="n">
         <v>65.50546420259818</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9207685712453032</v>
+        <v>0.921031484571444</v>
       </c>
       <c r="L32" t="n">
-        <v>5.498751583722733</v>
+        <v>5.498846860328248</v>
       </c>
       <c r="M32" t="n">
-        <v>4.763485501095766</v>
+        <v>4.763524732639214</v>
       </c>
       <c r="N32" t="n">
-        <v>3.978774561898913</v>
+        <v>3.97879151790498</v>
       </c>
       <c r="O32" t="n">
-        <v>0.1174423565737053</v>
+        <v>0.1175062000427</v>
       </c>
       <c r="P32" t="n">
-        <v>94.62365061281865</v>
+        <v>94.66502383298628</v>
       </c>
       <c r="Q32" t="n">
-        <v>-5.376349387181362</v>
+        <v>-5.334976167013711</v>
       </c>
       <c r="R32" t="n">
-        <v>115.9453090249404</v>
+        <v>115.9715367357235</v>
       </c>
       <c r="S32" t="n">
-        <v>65.86803023429859</v>
+        <v>65.89312818569326</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -25375,7 +25371,7 @@
         <v>78.2</v>
       </c>
       <c r="X35" t="n">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -26275,7 +26271,7 @@
         <v>77.5</v>
       </c>
       <c r="X45" t="n">
-        <v>71.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
@@ -26305,52 +26301,52 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>65.95500183105469</v>
+        <v>65.90499877929688</v>
       </c>
       <c r="E46" t="n">
-        <v>14.52310653643887</v>
+        <v>14.43628211577892</v>
       </c>
       <c r="F46" t="n">
-        <v>-11.69500645980579</v>
+        <v>-11.7619539094287</v>
       </c>
       <c r="G46" t="n">
-        <v>114.9421638552051</v>
+        <v>114.7792078420779</v>
       </c>
       <c r="H46" t="n">
-        <v>152.0733786480183</v>
+        <v>151.8822720169914</v>
       </c>
       <c r="I46" t="n">
-        <v>59.52908196527758</v>
+        <v>59.5033799433844</v>
       </c>
       <c r="J46" t="n">
         <v>66.68121173491031</v>
       </c>
       <c r="K46" t="n">
-        <v>0.659071229701533</v>
+        <v>0.6584671734042117</v>
       </c>
       <c r="L46" t="n">
-        <v>56.57252619099025</v>
+        <v>56.56776399558474</v>
       </c>
       <c r="M46" t="n">
-        <v>42.42518807920513</v>
+        <v>42.42322717521463</v>
       </c>
       <c r="N46" t="n">
-        <v>31.45202031561492</v>
+        <v>31.4511728062631</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.2386013938904625</v>
+        <v>-0.2417924718373961</v>
       </c>
       <c r="P46" t="n">
-        <v>35.2349189224515</v>
+        <v>35.1764050254456</v>
       </c>
       <c r="Q46" t="n">
-        <v>-64.7650810775485</v>
+        <v>-64.8235949745544</v>
       </c>
       <c r="R46" t="n">
-        <v>37.07399911768816</v>
+        <v>37.01315225440177</v>
       </c>
       <c r="S46" t="n">
-        <v>127.9025591358801</v>
+        <v>127.7297773430845</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -26363,7 +26359,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="X46" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
@@ -26455,7 +26451,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="X47" t="n">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
@@ -26723,7 +26719,7 @@
         <v>77</v>
       </c>
       <c r="X50" t="n">
-        <v>71</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -26841,52 +26837,52 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4474.2001953125</v>
+        <v>4473.10009765625</v>
       </c>
       <c r="E52" t="n">
-        <v>10.49863148363044</v>
+        <v>10.4714625416503</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.73095573414749</v>
+        <v>-3.754625964656444</v>
       </c>
       <c r="G52" t="n">
-        <v>68.39293170163718</v>
+        <v>68.35152795093151</v>
       </c>
       <c r="H52" t="n">
-        <v>152.6654660007166</v>
+        <v>152.6033416712658</v>
       </c>
       <c r="I52" t="n">
-        <v>64.91204766094971</v>
+        <v>64.89844893362583</v>
       </c>
       <c r="J52" t="n">
         <v>81.28036353622588</v>
       </c>
       <c r="K52" t="n">
-        <v>0.704817307359132</v>
+        <v>0.7044549529886872</v>
       </c>
       <c r="L52" t="n">
-        <v>3924.046398879126</v>
+        <v>3923.941627673769</v>
       </c>
       <c r="M52" t="n">
-        <v>3131.560737416525</v>
+        <v>3131.517596331966</v>
       </c>
       <c r="N52" t="n">
-        <v>2391.693141910052</v>
+        <v>2391.674496187065</v>
       </c>
       <c r="O52" t="n">
-        <v>-37.98106230107612</v>
+        <v>-38.0512679634694</v>
       </c>
       <c r="P52" t="n">
-        <v>52.11644233233692</v>
+        <v>52.06907129855715</v>
       </c>
       <c r="Q52" t="n">
-        <v>-47.88355766766308</v>
+        <v>-47.93092870144285</v>
       </c>
       <c r="R52" t="n">
-        <v>32.70016931765218</v>
+        <v>32.67461581932546</v>
       </c>
       <c r="S52" t="n">
-        <v>70.17344737581787</v>
+        <v>70.13160583935505</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -27015,66 +27011,66 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SRG</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Snam</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5.693999767303467</v>
+        <v>91.09999847412109</v>
       </c>
       <c r="E54" t="n">
-        <v>-5.036692047881264</v>
+        <v>1.087434196262538</v>
       </c>
       <c r="F54" t="n">
-        <v>-13.12175994093447</v>
+        <v>-23.02492636361005</v>
       </c>
       <c r="G54" t="n">
-        <v>29.05710643508579</v>
+        <v>24.89716948844776</v>
       </c>
       <c r="H54" t="n">
-        <v>16.79999522673779</v>
+        <v>21.25649115470529</v>
       </c>
       <c r="I54" t="n">
-        <v>53.43285946832963</v>
+        <v>54.65795480828837</v>
       </c>
       <c r="J54" t="n">
-        <v>63.4650979248115</v>
+        <v>23.79402312962622</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5453602742769268</v>
+        <v>0.7185848397100425</v>
       </c>
       <c r="L54" t="n">
-        <v>5.668004252079503</v>
+        <v>81.68648332593827</v>
       </c>
       <c r="M54" t="n">
-        <v>5.184936806596469</v>
+        <v>78.83021948673</v>
       </c>
       <c r="N54" t="n">
-        <v>4.773183176931191</v>
+        <v>72.41175276337188</v>
       </c>
       <c r="O54" t="n">
-        <v>0.01116219285628056</v>
+        <v>2.337894964975354</v>
       </c>
       <c r="P54" t="n">
-        <v>38.78187840081576</v>
+        <v>48.05580079149593</v>
       </c>
       <c r="Q54" t="n">
-        <v>-61.21812159918424</v>
+        <v>-51.94419920850407</v>
       </c>
       <c r="R54" t="n">
-        <v>24.1038846929383</v>
+        <v>60.67456328847583</v>
       </c>
       <c r="S54" t="n">
-        <v>33.13069519112452</v>
+        <v>22.05251771043748</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -27082,12 +27078,16 @@
         </is>
       </c>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Inside Bar, Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W54" t="n">
         <v>74.90000000000001</v>
       </c>
       <c r="X54" t="n">
-        <v>69.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -27096,73 +27096,73 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 63); in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); pattern: Bull Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>SRG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>Snam</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>90.87999725341797</v>
+        <v>5.693999767303467</v>
       </c>
       <c r="E55" t="n">
-        <v>0.843313896664033</v>
+        <v>-5.036692047881264</v>
       </c>
       <c r="F55" t="n">
-        <v>-23.21081670880615</v>
+        <v>-13.12175994093447</v>
       </c>
       <c r="G55" t="n">
-        <v>24.59555005694327</v>
+        <v>29.05710643508579</v>
       </c>
       <c r="H55" t="n">
-        <v>20.96366375054468</v>
+        <v>16.79999522673779</v>
       </c>
       <c r="I55" t="n">
-        <v>54.57516562058164</v>
+        <v>53.43285946832963</v>
       </c>
       <c r="J55" t="n">
-        <v>23.79402312962622</v>
+        <v>63.4650979248115</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7155029658658204</v>
+        <v>0.5453602742769268</v>
       </c>
       <c r="L55" t="n">
-        <v>81.66553082872845</v>
+        <v>5.668004252079503</v>
       </c>
       <c r="M55" t="n">
-        <v>78.8215919878789</v>
+        <v>5.184936806596469</v>
       </c>
       <c r="N55" t="n">
-        <v>72.40802392912268</v>
+        <v>4.773183176931191</v>
       </c>
       <c r="O55" t="n">
-        <v>2.323855001033044</v>
+        <v>0.01116219285628056</v>
       </c>
       <c r="P55" t="n">
-        <v>47.72929258480115</v>
+        <v>38.78187840081576</v>
       </c>
       <c r="Q55" t="n">
-        <v>-52.27070741519885</v>
+        <v>-61.21812159918424</v>
       </c>
       <c r="R55" t="n">
-        <v>60.29093665497356</v>
+        <v>24.1038846929383</v>
       </c>
       <c r="S55" t="n">
-        <v>21.75776794824278</v>
+        <v>33.13069519112452</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -27170,16 +27170,12 @@
         </is>
       </c>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Inside Bar, Bull Flag / Consolidation</t>
-        </is>
-      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="n">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="X55" t="n">
-        <v>88.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -27188,7 +27184,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 24); pattern: Bull Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 63); in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -27209,52 +27205,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1783.5</v>
+        <v>1781.800048828125</v>
       </c>
       <c r="E56" t="n">
-        <v>8.07125657340071</v>
+        <v>7.968247961537545</v>
       </c>
       <c r="F56" t="n">
-        <v>-8.53846153846154</v>
+        <v>-8.625638521634615</v>
       </c>
       <c r="G56" t="n">
-        <v>87.83570300157977</v>
+        <v>87.65666654324644</v>
       </c>
       <c r="H56" t="n">
-        <v>66.60439047174218</v>
+        <v>66.44559073592949</v>
       </c>
       <c r="I56" t="n">
-        <v>57.62296354014948</v>
+        <v>57.5849060954734</v>
       </c>
       <c r="J56" t="n">
         <v>70.12050055584359</v>
       </c>
       <c r="K56" t="n">
-        <v>0.6326390632463593</v>
+        <v>0.6317064940000263</v>
       </c>
       <c r="L56" t="n">
-        <v>1608.222978135355</v>
+        <v>1608.061078023748</v>
       </c>
       <c r="M56" t="n">
-        <v>1327.722766374725</v>
+        <v>1327.656101622887</v>
       </c>
       <c r="N56" t="n">
-        <v>1139.841454271014</v>
+        <v>1139.812641539287</v>
       </c>
       <c r="O56" t="n">
-        <v>-14.35922499014885</v>
+        <v>-14.46771190254199</v>
       </c>
       <c r="P56" t="n">
-        <v>32.18500599818931</v>
+        <v>32.07715475947997</v>
       </c>
       <c r="Q56" t="n">
-        <v>-67.81499400181069</v>
+        <v>-67.92284524052003</v>
       </c>
       <c r="R56" t="n">
-        <v>28.20766001680711</v>
+        <v>28.1177548681055</v>
       </c>
       <c r="S56" t="n">
-        <v>99.496644295302</v>
+        <v>99.30649315750838</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -27359,7 +27355,7 @@
         <v>74.5</v>
       </c>
       <c r="X57" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -27471,66 +27467,66 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>USD/JPY</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>159.4720001220703</v>
+        <v>57.58000183105469</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4438664159844508</v>
+        <v>1.123995819777734</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.2308564686205883</v>
+        <v>16.62953833662662</v>
       </c>
       <c r="G59" t="n">
-        <v>5.489042012189138</v>
+        <v>12.154268912974</v>
       </c>
       <c r="H59" t="n">
-        <v>44.27285008245418</v>
+        <v>56.93650582243015</v>
       </c>
       <c r="I59" t="n">
-        <v>59.20873833576759</v>
+        <v>66.89640200355356</v>
       </c>
       <c r="J59" t="n">
-        <v>26.49181088905198</v>
+        <v>19.86950721443645</v>
       </c>
       <c r="K59" t="n">
-        <v>0.7542961546142998</v>
+        <v>1.057769173256318</v>
       </c>
       <c r="L59" t="n">
-        <v>154.8895695699858</v>
+        <v>51.75425715088088</v>
       </c>
       <c r="M59" t="n">
-        <v>146.5264889258014</v>
+        <v>45.77703753826754</v>
       </c>
       <c r="N59" t="n">
-        <v>132.4726944184184</v>
+        <v>35.67215074900028</v>
       </c>
       <c r="O59" t="n">
-        <v>0.3840093789534382</v>
+        <v>-0.0959289127722025</v>
       </c>
       <c r="P59" t="n">
-        <v>78.82444790474797</v>
+        <v>92.27190049679854</v>
       </c>
       <c r="Q59" t="n">
-        <v>-21.17555209525202</v>
+        <v>-7.728099503201468</v>
       </c>
       <c r="R59" t="n">
-        <v>68.8568335593509</v>
+        <v>71.88239303292785</v>
       </c>
       <c r="S59" t="n">
-        <v>1.577760490411739</v>
+        <v>19.13925025770713</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -27538,16 +27534,12 @@
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Double Top, Double Bottom</t>
-        </is>
-      </c>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="n">
         <v>73.7</v>
       </c>
       <c r="X59" t="n">
-        <v>68.2</v>
+        <v>80.5</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -27556,94 +27548,90 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); pattern: Double Bottom</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (67) — momentum positivo; vicino alla resistenza dei 20g (58.41); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>USD/JPY</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>44.18000030517578</v>
+        <v>159.3699951171875</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3833104279462596</v>
+        <v>-0.5075467102340858</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.726300081098688</v>
+        <v>-0.2946730130000574</v>
       </c>
       <c r="G60" t="n">
-        <v>6.547691167483194</v>
+        <v>5.421566779939591</v>
       </c>
       <c r="H60" t="n">
-        <v>39.74379448054386</v>
+        <v>44.18056709380507</v>
       </c>
       <c r="I60" t="n">
-        <v>56.34310707355802</v>
+        <v>59.05026457848447</v>
       </c>
       <c r="J60" t="n">
-        <v>23.46157883937678</v>
+        <v>26.49181088905198</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6025074505088488</v>
+        <v>0.7505448881262168</v>
       </c>
       <c r="L60" t="n">
-        <v>42.99073303793445</v>
+        <v>154.879854807616</v>
       </c>
       <c r="M60" t="n">
-        <v>39.16700982719708</v>
+        <v>146.5224887295315</v>
       </c>
       <c r="N60" t="n">
-        <v>32.98767025082888</v>
+        <v>132.4712160850143</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.2464275507605569</v>
+        <v>0.3774996578440968</v>
       </c>
       <c r="P60" t="n">
-        <v>52.52460417200307</v>
+        <v>78.34519108618163</v>
       </c>
       <c r="Q60" t="n">
-        <v>-47.47539582799693</v>
+        <v>-21.65480891381837</v>
       </c>
       <c r="R60" t="n">
-        <v>17.18993747935134</v>
+        <v>68.43076653689202</v>
       </c>
       <c r="S60" t="n">
-        <v>16.73932852460074</v>
+        <v>1.51278707848439</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Bull Flag / Consolidation</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W60" t="n">
-        <v>73.5</v>
+        <v>73.7</v>
       </c>
       <c r="X60" t="n">
-        <v>78.40000000000001</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
@@ -27652,19 +27640,19 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 23); pattern: Bull Flag / Consolidation; doji — indecisione del mercato</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 26); pattern: Double Bottom</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -27673,52 +27661,52 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>57.59000015258789</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="E61" t="n">
-        <v>1.141555218749168</v>
+        <v>-0.3833104279462596</v>
       </c>
       <c r="F61" t="n">
-        <v>16.64979015301209</v>
+        <v>-3.726300081098688</v>
       </c>
       <c r="G61" t="n">
-        <v>12.17374363347163</v>
+        <v>6.547691167483194</v>
       </c>
       <c r="H61" t="n">
-        <v>56.96375663166273</v>
+        <v>39.74379448054386</v>
       </c>
       <c r="I61" t="n">
-        <v>66.91050790698543</v>
+        <v>56.34310707355802</v>
       </c>
       <c r="J61" t="n">
-        <v>19.86950721443645</v>
+        <v>23.46157883937678</v>
       </c>
       <c r="K61" t="n">
-        <v>1.058541583254802</v>
+        <v>0.6025074505088488</v>
       </c>
       <c r="L61" t="n">
-        <v>51.75520937197928</v>
+        <v>42.99073303793445</v>
       </c>
       <c r="M61" t="n">
-        <v>45.77742962930806</v>
+        <v>39.16700982719708</v>
       </c>
       <c r="N61" t="n">
-        <v>35.67229058566507</v>
+        <v>32.98767025082888</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.09529084324985559</v>
+        <v>-0.2464275507605569</v>
       </c>
       <c r="P61" t="n">
-        <v>92.36499472371331</v>
+        <v>52.52460417200307</v>
       </c>
       <c r="Q61" t="n">
-        <v>-7.635005276286687</v>
+        <v>-47.47539582799693</v>
       </c>
       <c r="R61" t="n">
-        <v>71.92229656081166</v>
+        <v>17.18993747935134</v>
       </c>
       <c r="S61" t="n">
-        <v>19.15993786613752</v>
+        <v>16.73932852460074</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -27727,15 +27715,19 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>Shooting Star</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr"/>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Bull Flag / Consolidation</t>
+        </is>
+      </c>
       <c r="W61" t="n">
-        <v>73.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="X61" t="n">
-        <v>86.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
@@ -27744,7 +27736,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; RSI in forza (67) — momentum positivo; shooting star — rifiuto di resistenza; vicino alla resistenza dei 20g (58.41); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 23); pattern: Bull Flag / Consolidation; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -27923,7 +27915,7 @@
         <v>72.90000000000001</v>
       </c>
       <c r="X63" t="n">
-        <v>87.09999999999999</v>
+        <v>87</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -28015,7 +28007,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="X64" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -28045,52 +28037,52 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>84.72000122070312</v>
+        <v>84.94999694824219</v>
       </c>
       <c r="E65" t="n">
-        <v>0.05905639877072932</v>
+        <v>0.3306942073368013</v>
       </c>
       <c r="F65" t="n">
-        <v>-16.43321807463667</v>
+        <v>-16.20635307782261</v>
       </c>
       <c r="G65" t="n">
-        <v>24.58823708926929</v>
+        <v>24.92646610035616</v>
       </c>
       <c r="H65" t="n">
-        <v>15.31237214248182</v>
+        <v>15.62541926881595</v>
       </c>
       <c r="I65" t="n">
-        <v>54.87475709952128</v>
+        <v>54.97367618025019</v>
       </c>
       <c r="J65" t="n">
         <v>21.8831417623618</v>
       </c>
       <c r="K65" t="n">
-        <v>0.7339340630253438</v>
+        <v>0.7376849636061121</v>
       </c>
       <c r="L65" t="n">
-        <v>76.0848967798302</v>
+        <v>76.10680113483392</v>
       </c>
       <c r="M65" t="n">
-        <v>73.68837114923197</v>
+        <v>73.69739058952763</v>
       </c>
       <c r="N65" t="n">
-        <v>67.81311337370445</v>
+        <v>67.81701160637462</v>
       </c>
       <c r="O65" t="n">
-        <v>2.281092917554821</v>
+        <v>2.295770707574405</v>
       </c>
       <c r="P65" t="n">
-        <v>46.10852700707919</v>
+        <v>46.46510950930635</v>
       </c>
       <c r="Q65" t="n">
-        <v>-53.89147299292081</v>
+        <v>-53.53489049069365</v>
       </c>
       <c r="R65" t="n">
-        <v>56.62073486862073</v>
+        <v>57.34434093098958</v>
       </c>
       <c r="S65" t="n">
-        <v>18.12604542489515</v>
+        <v>18.44673104065706</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -28291,7 +28283,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="X67" t="n">
-        <v>74.8</v>
+        <v>74.7</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -28479,7 +28471,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="X69" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -28509,52 +28501,52 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.158077597618103</v>
+        <v>1.158211708068848</v>
       </c>
       <c r="E70" t="n">
-        <v>0.4968120237095919</v>
+        <v>0.5084499940724019</v>
       </c>
       <c r="F70" t="n">
-        <v>1.053857615473808</v>
+        <v>1.065560094152418</v>
       </c>
       <c r="G70" t="n">
-        <v>9.635201594782639</v>
+        <v>9.647897830625208</v>
       </c>
       <c r="H70" t="n">
-        <v>-2.698320853608571</v>
+        <v>-2.687052893607123</v>
       </c>
       <c r="I70" t="n">
-        <v>54.58463255849598</v>
+        <v>54.60967935964386</v>
       </c>
       <c r="J70" t="n">
         <v>39.17040127944836</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5775189443162064</v>
+        <v>0.5782604390084265</v>
       </c>
       <c r="L70" t="n">
-        <v>1.145053114754498</v>
+        <v>1.145065887178378</v>
       </c>
       <c r="M70" t="n">
-        <v>1.124903680840073</v>
+        <v>1.124908940073435</v>
       </c>
       <c r="N70" t="n">
-        <v>1.120817408903727</v>
+        <v>1.120819352533448</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.002533892284479203</v>
+        <v>-0.002525333668818935</v>
       </c>
       <c r="P70" t="n">
-        <v>36.5769491490695</v>
+        <v>36.76904241931656</v>
       </c>
       <c r="Q70" t="n">
-        <v>-63.4230508509305</v>
+        <v>-63.23095758068344</v>
       </c>
       <c r="R70" t="n">
-        <v>20.23498036609826</v>
+        <v>20.29542544049429</v>
       </c>
       <c r="S70" t="n">
-        <v>11.28778404440303</v>
+        <v>11.30067165652095</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -28939,7 +28931,7 @@
         <v>67.3</v>
       </c>
       <c r="X74" t="n">
-        <v>73.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -29491,7 +29483,7 @@
         <v>61.6</v>
       </c>
       <c r="X80" t="n">
-        <v>74</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
@@ -29579,7 +29571,7 @@
         <v>60.7</v>
       </c>
       <c r="X81" t="n">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -29609,52 +29601,52 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.354481220245361</v>
+        <v>1.354646444320679</v>
       </c>
       <c r="E82" t="n">
-        <v>0.6230596083531603</v>
+        <v>0.6353339402013436</v>
       </c>
       <c r="F82" t="n">
-        <v>2.824089383072415</v>
+        <v>2.836632203773592</v>
       </c>
       <c r="G82" t="n">
-        <v>6.678942371536989</v>
+        <v>6.691955419887696</v>
       </c>
       <c r="H82" t="n">
-        <v>-2.152273952675554</v>
+        <v>-2.140338165145661</v>
       </c>
       <c r="I82" t="n">
-        <v>55.61350207823694</v>
+        <v>55.63743752359425</v>
       </c>
       <c r="J82" t="n">
         <v>19.66387474828739</v>
       </c>
       <c r="K82" t="n">
-        <v>0.668489563836137</v>
+        <v>0.6696178810499693</v>
       </c>
       <c r="L82" t="n">
-        <v>1.330030444825417</v>
+        <v>1.330046180451638</v>
       </c>
       <c r="M82" t="n">
-        <v>1.309812897692866</v>
+        <v>1.309819377068369</v>
       </c>
       <c r="N82" t="n">
-        <v>1.337664027293167</v>
+        <v>1.337666421844983</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.001316236934685223</v>
+        <v>-0.001305692720192042</v>
       </c>
       <c r="P82" t="n">
-        <v>63.84096430947208</v>
+        <v>64.03881676806724</v>
       </c>
       <c r="Q82" t="n">
-        <v>-36.15903569052792</v>
+        <v>-35.96118323193276</v>
       </c>
       <c r="R82" t="n">
-        <v>43.12378210448897</v>
+        <v>43.21987940950148</v>
       </c>
       <c r="S82" t="n">
-        <v>7.934541705206644</v>
+        <v>7.947707915694835</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -29667,7 +29659,7 @@
         <v>60.3</v>
       </c>
       <c r="X82" t="n">
-        <v>62.1</v>
+        <v>62</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -29943,7 +29935,7 @@
         <v>53.4</v>
       </c>
       <c r="X85" t="n">
-        <v>64.8</v>
+        <v>64.7</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -30039,7 +30031,7 @@
         <v>52.4</v>
       </c>
       <c r="X86" t="n">
-        <v>57.8</v>
+        <v>57.7</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -30221,7 +30213,7 @@
         <v>46.3</v>
       </c>
       <c r="X88" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -30309,7 +30301,7 @@
         <v>45.3</v>
       </c>
       <c r="X89" t="n">
-        <v>58.6</v>
+        <v>58.5</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -30405,7 +30397,7 @@
         <v>45.1</v>
       </c>
       <c r="X90" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -30531,52 +30523,52 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1330.5</v>
+        <v>1328</v>
       </c>
       <c r="E92" t="n">
-        <v>4.303859004767108</v>
+        <v>4.107872798444734</v>
       </c>
       <c r="F92" t="n">
-        <v>-9.563618531920248</v>
+        <v>-9.733547846967372</v>
       </c>
       <c r="G92" t="n">
-        <v>34.36679293049924</v>
+        <v>34.11431868598498</v>
       </c>
       <c r="H92" t="n">
-        <v>-52.09548330158584</v>
+        <v>-52.18549554641564</v>
       </c>
       <c r="I92" t="n">
-        <v>50.48889616078429</v>
+        <v>50.41091216603986</v>
       </c>
       <c r="J92" t="n">
         <v>56.77545406727184</v>
       </c>
       <c r="K92" t="n">
-        <v>0.5434199936500771</v>
+        <v>0.5411473213546926</v>
       </c>
       <c r="L92" t="n">
-        <v>1325.010541472236</v>
+        <v>1324.77244623414</v>
       </c>
       <c r="M92" t="n">
-        <v>1360.182084538678</v>
+        <v>1360.084045322991</v>
       </c>
       <c r="N92" t="n">
-        <v>1348.402158336724</v>
+        <v>1348.359785455368</v>
       </c>
       <c r="O92" t="n">
-        <v>-1.902806508647437</v>
+        <v>-2.062350668191456</v>
       </c>
       <c r="P92" t="n">
-        <v>22.84217504428822</v>
+        <v>22.61237449052275</v>
       </c>
       <c r="Q92" t="n">
-        <v>-77.15782495571177</v>
+        <v>-77.38762550947725</v>
       </c>
       <c r="R92" t="n">
-        <v>6.818549655254465</v>
+        <v>6.578290956886582</v>
       </c>
       <c r="S92" t="n">
-        <v>47.35850747854711</v>
+        <v>47.08162189516014</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -30590,10 +30582,10 @@
         </is>
       </c>
       <c r="W92" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="X92" t="n">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
@@ -30685,7 +30677,7 @@
         <v>43.6</v>
       </c>
       <c r="X93" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
@@ -30715,52 +30707,52 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>99.59300231933594</v>
+        <v>99.56400299072266</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.2074155572064695</v>
+        <v>-0.2364729998182047</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.3671436259483962</v>
+        <v>-0.3961545592005788</v>
       </c>
       <c r="G94" t="n">
-        <v>-5.813311583714132</v>
+        <v>-5.840736710628402</v>
       </c>
       <c r="H94" t="n">
-        <v>7.737991874744554</v>
+        <v>7.706620901305161</v>
       </c>
       <c r="I94" t="n">
-        <v>47.78497500598198</v>
+        <v>47.72121204174462</v>
       </c>
       <c r="J94" t="n">
         <v>28.11233397905131</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4634822887175435</v>
+        <v>0.4613105680695599</v>
       </c>
       <c r="L94" t="n">
-        <v>100.1068831169928</v>
+        <v>100.1041212761725</v>
       </c>
       <c r="M94" t="n">
-        <v>100.7628408562013</v>
+        <v>100.7617036276282</v>
       </c>
       <c r="N94" t="n">
-        <v>99.84552351605099</v>
+        <v>99.8450320020067</v>
       </c>
       <c r="O94" t="n">
-        <v>0.1839837436588359</v>
+        <v>0.1821330742544538</v>
       </c>
       <c r="P94" t="n">
-        <v>64.68798828125</v>
+        <v>64.2239990234375</v>
       </c>
       <c r="Q94" t="n">
-        <v>-35.31201171875</v>
+        <v>-35.7760009765625</v>
       </c>
       <c r="R94" t="n">
-        <v>-11.24072467808511</v>
+        <v>-11.42938779647771</v>
       </c>
       <c r="S94" t="n">
-        <v>-8.200751884616608</v>
+        <v>-8.227481840542772</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -30807,52 +30799,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>64320.421875</v>
+        <v>64281.4296875</v>
       </c>
       <c r="E95" t="n">
-        <v>2.398640225980597</v>
+        <v>2.336564343033243</v>
       </c>
       <c r="F95" t="n">
-        <v>-5.73457521207108</v>
+        <v>-5.791720594687533</v>
       </c>
       <c r="G95" t="n">
-        <v>-33.31150617971161</v>
+        <v>-33.35193393468167</v>
       </c>
       <c r="H95" t="n">
-        <v>83.55846872410248</v>
+        <v>83.44719230487108</v>
       </c>
       <c r="I95" t="n">
-        <v>44.01238933656319</v>
+        <v>43.9903301520951</v>
       </c>
       <c r="J95" t="n">
         <v>30.35693503158459</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1885171535427497</v>
+        <v>0.1880625262031072</v>
       </c>
       <c r="L95" t="n">
-        <v>76861.50448125586</v>
+        <v>76857.79093958921</v>
       </c>
       <c r="M95" t="n">
-        <v>66255.78810245493</v>
+        <v>66254.22841495494</v>
       </c>
       <c r="N95" t="n">
-        <v>50015.00188598184</v>
+        <v>50014.20612705326</v>
       </c>
       <c r="O95" t="n">
-        <v>-5683.038591045558</v>
+        <v>-5685.52698135895</v>
       </c>
       <c r="P95" t="n">
-        <v>9.602084724102419</v>
+        <v>9.545120496290705</v>
       </c>
       <c r="Q95" t="n">
-        <v>-90.39791527589757</v>
+        <v>-90.45487950370929</v>
       </c>
       <c r="R95" t="n">
-        <v>-67.59031720645977</v>
+        <v>-67.62263248835812</v>
       </c>
       <c r="S95" t="n">
-        <v>-31.15597722807828</v>
+        <v>-31.19771170316294</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -30869,7 +30861,7 @@
         <v>42.2</v>
       </c>
       <c r="X95" t="n">
-        <v>61.9</v>
+        <v>61.8</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -30961,7 +30953,7 @@
         <v>41.1</v>
       </c>
       <c r="X96" t="n">
-        <v>64.90000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -31057,7 +31049,7 @@
         <v>40.7</v>
       </c>
       <c r="X97" t="n">
-        <v>66.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -31149,7 +31141,7 @@
         <v>39.8</v>
       </c>
       <c r="X98" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
@@ -31241,7 +31233,7 @@
         <v>39.4</v>
       </c>
       <c r="X99" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
@@ -31337,7 +31329,7 @@
         <v>38.3</v>
       </c>
       <c r="X100" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
@@ -31367,52 +31359,52 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1.000100016593933</v>
+        <v>1.00189995765686</v>
       </c>
       <c r="E101" t="n">
-        <v>-5.698533296344643</v>
+        <v>-5.528813188957526</v>
       </c>
       <c r="F101" t="n">
-        <v>-25.38009075410834</v>
+        <v>-25.24579274737396</v>
       </c>
       <c r="G101" t="n">
-        <v>-48.55772788972404</v>
+        <v>-48.46514409169861</v>
       </c>
       <c r="H101" t="n">
-        <v>41.58222575347932</v>
+        <v>41.83703992974763</v>
       </c>
       <c r="I101" t="n">
-        <v>40.12795927237301</v>
+        <v>40.15409065989427</v>
       </c>
       <c r="J101" t="n">
         <v>35.92508428025589</v>
       </c>
       <c r="K101" t="n">
-        <v>0.1408395542638116</v>
+        <v>0.1414065030615588</v>
       </c>
       <c r="L101" t="n">
-        <v>1.538464726404625</v>
+        <v>1.538636149362999</v>
       </c>
       <c r="M101" t="n">
-        <v>1.312179147927719</v>
+        <v>1.312251145570236</v>
       </c>
       <c r="N101" t="n">
-        <v>1.021522608431164</v>
+        <v>1.021559341922244</v>
       </c>
       <c r="O101" t="n">
-        <v>-0.1897408468553554</v>
+        <v>-0.18962597882171</v>
       </c>
       <c r="P101" t="n">
-        <v>0.4387291680340215</v>
+        <v>0.5063506732849664</v>
       </c>
       <c r="Q101" t="n">
-        <v>-99.56127083196598</v>
+        <v>-99.49364932671503</v>
       </c>
       <c r="R101" t="n">
-        <v>-68.76892964179333</v>
+        <v>-68.73093320473983</v>
       </c>
       <c r="S101" t="n">
-        <v>-51.92122607464862</v>
+        <v>-51.83469576967157</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -31459,52 +31451,52 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>75.70999908447266</v>
+        <v>75.86000061035156</v>
       </c>
       <c r="E102" t="n">
-        <v>4.011995360083542</v>
+        <v>4.218070623620584</v>
       </c>
       <c r="F102" t="n">
-        <v>-8.899983750928353</v>
+        <v>-8.719490531932184</v>
       </c>
       <c r="G102" t="n">
-        <v>-68.15478807407129</v>
+        <v>-68.0916942893851</v>
       </c>
       <c r="H102" t="n">
-        <v>112.9292907185552</v>
+        <v>113.3511599418854</v>
       </c>
       <c r="I102" t="n">
-        <v>40.9847530772621</v>
+        <v>41.02142259062838</v>
       </c>
       <c r="J102" t="n">
         <v>25.2501758559911</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2152218363899661</v>
+        <v>0.2158846889052321</v>
       </c>
       <c r="L102" t="n">
-        <v>113.5616192783275</v>
+        <v>113.575905137935</v>
       </c>
       <c r="M102" t="n">
-        <v>113.3090303238305</v>
+        <v>113.316722709773</v>
       </c>
       <c r="N102" t="n">
-        <v>92.48268678710222</v>
+        <v>92.48663419567799</v>
       </c>
       <c r="O102" t="n">
-        <v>-11.53501658598036</v>
+        <v>-11.52544383902968</v>
       </c>
       <c r="P102" t="n">
-        <v>7.933435034754581</v>
+        <v>8.011238600635931</v>
       </c>
       <c r="Q102" t="n">
-        <v>-92.06656496524542</v>
+        <v>-91.98876139936407</v>
       </c>
       <c r="R102" t="n">
-        <v>-89.51049961013936</v>
+        <v>-89.44638901343016</v>
       </c>
       <c r="S102" t="n">
-        <v>-67.31536757848262</v>
+        <v>-67.25061067985226</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -31739,52 +31731,52 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1905.77001953125</v>
+        <v>1904.93994140625</v>
       </c>
       <c r="E105" t="n">
-        <v>2.441700283347314</v>
+        <v>2.397080726096679</v>
       </c>
       <c r="F105" t="n">
-        <v>-9.452057416378945</v>
+        <v>-9.491496522688792</v>
       </c>
       <c r="G105" t="n">
-        <v>-48.57200306563814</v>
+        <v>-48.59440306922214</v>
       </c>
       <c r="H105" t="n">
-        <v>-16.21322792661273</v>
+        <v>-16.24972213417697</v>
       </c>
       <c r="I105" t="n">
-        <v>43.72265894391953</v>
+        <v>43.71342903718465</v>
       </c>
       <c r="J105" t="n">
         <v>14.06284679828849</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2913800009965401</v>
+        <v>0.2911573039065912</v>
       </c>
       <c r="L105" t="n">
-        <v>2451.006880435652</v>
+        <v>2450.927825376128</v>
       </c>
       <c r="M105" t="n">
-        <v>2400.678191471472</v>
+        <v>2400.644988346472</v>
       </c>
       <c r="N105" t="n">
-        <v>1991.1715625314</v>
+        <v>1991.154622161502</v>
       </c>
       <c r="O105" t="n">
-        <v>-164.2061760012868</v>
+        <v>-164.2591496480105</v>
       </c>
       <c r="P105" t="n">
-        <v>11.58218655767584</v>
+        <v>11.55810696896938</v>
       </c>
       <c r="Q105" t="n">
-        <v>-88.41781344232416</v>
+        <v>-88.44189303103062</v>
       </c>
       <c r="R105" t="n">
-        <v>-77.13562806366652</v>
+        <v>-77.16039809463153</v>
       </c>
       <c r="S105" t="n">
-        <v>-42.813147204589</v>
+        <v>-42.8380555382581</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -31801,7 +31793,7 @@
         <v>34.5</v>
       </c>
       <c r="X105" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
@@ -31831,52 +31823,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.1733700037002563</v>
+        <v>0.1738699972629547</v>
       </c>
       <c r="E106" t="n">
-        <v>3.218551167139649</v>
+        <v>3.516230177540147</v>
       </c>
       <c r="F106" t="n">
-        <v>-28.22990337621589</v>
+        <v>-28.02292070597166</v>
       </c>
       <c r="G106" t="n">
-        <v>-83.93147980719098</v>
+        <v>-83.88513870730621</v>
       </c>
       <c r="H106" t="n">
-        <v>-87.46848450945784</v>
+        <v>-87.43234401835559</v>
       </c>
       <c r="I106" t="n">
-        <v>37.82120896966304</v>
+        <v>37.84922470129558</v>
       </c>
       <c r="J106" t="n">
         <v>31.07283787478976</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1959318037361512</v>
+        <v>0.1963589441526053</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3851173446007741</v>
+        <v>0.3851649630353168</v>
       </c>
       <c r="M106" t="n">
-        <v>0.4772111490758782</v>
+        <v>0.4772311488183861</v>
       </c>
       <c r="N106" t="n">
-        <v>0.4607944432153647</v>
+        <v>0.4608046471656238</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.04299829333064749</v>
+        <v>-0.04296638490955224</v>
       </c>
       <c r="P106" t="n">
-        <v>3.950356228083756</v>
+        <v>4.007318090085098</v>
       </c>
       <c r="Q106" t="n">
-        <v>-96.04964377191624</v>
+        <v>-95.99268190991491</v>
       </c>
       <c r="R106" t="n">
-        <v>-87.88769807445958</v>
+        <v>-87.84821042458671</v>
       </c>
       <c r="S106" t="n">
-        <v>-79.45280978534375</v>
+        <v>-79.39355234392021</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -31923,52 +31915,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>9.475000381469727</v>
+        <v>9.503000259399414</v>
       </c>
       <c r="E107" t="n">
-        <v>16.09677697541103</v>
+        <v>16.43985828965551</v>
       </c>
       <c r="F107" t="n">
-        <v>7.945905240624018</v>
+        <v>8.264899652028813</v>
       </c>
       <c r="G107" t="n">
-        <v>-50.19098391483787</v>
+        <v>-50.04379169172093</v>
       </c>
       <c r="H107" t="n">
-        <v>-51.40336682036206</v>
+        <v>-51.25975734890655</v>
       </c>
       <c r="I107" t="n">
-        <v>44.57864675021968</v>
+        <v>44.63363665776282</v>
       </c>
       <c r="J107" t="n">
         <v>20.38841217132817</v>
       </c>
       <c r="K107" t="n">
-        <v>0.3048827383479168</v>
+        <v>0.3061338747413573</v>
       </c>
       <c r="L107" t="n">
-        <v>11.82559783543909</v>
+        <v>11.82826449048002</v>
       </c>
       <c r="M107" t="n">
-        <v>12.491167543044</v>
+        <v>12.49228753816119</v>
       </c>
       <c r="N107" t="n">
-        <v>10.83412104987054</v>
+        <v>10.83469247595074</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.7808172434235302</v>
+        <v>-0.7790303566268775</v>
       </c>
       <c r="P107" t="n">
-        <v>11.84093799155546</v>
+        <v>11.97611915998993</v>
       </c>
       <c r="Q107" t="n">
-        <v>-88.15906200844454</v>
+        <v>-88.02388084001007</v>
       </c>
       <c r="R107" t="n">
-        <v>-75.34059094969489</v>
+        <v>-75.20733510010383</v>
       </c>
       <c r="S107" t="n">
-        <v>-52.62823278287196</v>
+        <v>-52.48824295216048</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -31981,7 +31973,7 @@
         <v>33.6</v>
       </c>
       <c r="X107" t="n">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -32073,7 +32065,7 @@
         <v>33.2</v>
       </c>
       <c r="X108" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -32169,7 +32161,7 @@
         <v>32.7</v>
       </c>
       <c r="X109" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -32199,52 +32191,52 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>2.70199990272522</v>
+        <v>2.703999996185303</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.638153499732198</v>
+        <v>-1.565343398699837</v>
       </c>
       <c r="F110" t="n">
-        <v>-6.310685029305896</v>
+        <v>-6.241333662578031</v>
       </c>
       <c r="G110" t="n">
-        <v>-19.65507076558526</v>
+        <v>-19.59559727435733</v>
       </c>
       <c r="H110" t="n">
-        <v>-25.97260733898091</v>
+        <v>-25.91781025931449</v>
       </c>
       <c r="I110" t="n">
-        <v>45.35346998367637</v>
+        <v>45.3675368392399</v>
       </c>
       <c r="J110" t="n">
         <v>48.09674867775514</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2007562253206951</v>
+        <v>0.2014973780735247</v>
       </c>
       <c r="L110" t="n">
-        <v>3.2303150436797</v>
+        <v>3.230505528771137</v>
       </c>
       <c r="M110" t="n">
-        <v>3.329987097078214</v>
+        <v>3.330065532115865</v>
       </c>
       <c r="N110" t="n">
-        <v>3.317390381743035</v>
+        <v>3.317424281632189</v>
       </c>
       <c r="O110" t="n">
-        <v>-0.09496984860511427</v>
+        <v>-0.0948422073130749</v>
       </c>
       <c r="P110" t="n">
-        <v>4.098051244913919</v>
+        <v>4.135478142785333</v>
       </c>
       <c r="Q110" t="n">
-        <v>-95.90194875508608</v>
+        <v>-95.86452185721467</v>
       </c>
       <c r="R110" t="n">
-        <v>-71.63717663354269</v>
+        <v>-71.582112262737</v>
       </c>
       <c r="S110" t="n">
-        <v>-25.62620480793096</v>
+        <v>-25.57115131173535</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -32254,10 +32246,10 @@
       <c r="U110" t="inlineStr"/>
       <c r="V110" t="inlineStr"/>
       <c r="W110" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="X110" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -32349,7 +32341,7 @@
         <v>30.8</v>
       </c>
       <c r="X111" t="n">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -32629,7 +32621,7 @@
         <v>22.3</v>
       </c>
       <c r="X114" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -32659,52 +32651,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.7588000297546387</v>
+        <v>0.7608000040054321</v>
       </c>
       <c r="E115" t="n">
-        <v>0.09867902206650569</v>
+        <v>0.3625097715820536</v>
       </c>
       <c r="F115" t="n">
-        <v>-39.37457080676423</v>
+        <v>-39.21477996256911</v>
       </c>
       <c r="G115" t="n">
-        <v>-91.5381136083886</v>
+        <v>-91.51581055852994</v>
       </c>
       <c r="H115" t="n">
-        <v>-95.37378972248767</v>
+        <v>-95.36159638950011</v>
       </c>
       <c r="I115" t="n">
-        <v>33.66835566385409</v>
+        <v>33.68339859437324</v>
       </c>
       <c r="J115" t="n">
         <v>37.34832998198571</v>
       </c>
       <c r="K115" t="n">
-        <v>0.1940790773330167</v>
+        <v>0.194353515016167</v>
       </c>
       <c r="L115" t="n">
-        <v>2.578459608005513</v>
+        <v>2.578650081743684</v>
       </c>
       <c r="M115" t="n">
-        <v>4.178250930518845</v>
+        <v>4.178359037235104</v>
       </c>
       <c r="N115" t="n">
-        <v>6.264559301165036</v>
+        <v>6.264614856005336</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.02475202453109659</v>
+        <v>-0.02462439084671542</v>
       </c>
       <c r="P115" t="n">
-        <v>0.2530614123537269</v>
+        <v>0.3015353185945826</v>
       </c>
       <c r="Q115" t="n">
-        <v>-99.74693858764627</v>
+        <v>-99.69846468140541</v>
       </c>
       <c r="R115" t="n">
-        <v>-63.6933384435202</v>
+        <v>-63.67464886011675</v>
       </c>
       <c r="S115" t="n">
-        <v>-83.89974760755312</v>
+        <v>-83.85731206596967</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -32725,7 +32717,7 @@
         <v>20.4</v>
       </c>
       <c r="X115" t="n">
-        <v>72.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -32734,7 +32726,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long; doji — indecisione del mercato; sul supporto dei 20g (0.7484)</t>
+          <t>EMA e SMA allineate al ribasso — struttura bearish solida; trend molto direzionale (ADX 37); RSI scarico (34) — zona di interesse long; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -32755,52 +32747,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6.328999996185303</v>
+        <v>6.330999851226807</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.7716751413622602</v>
+        <v>-0.7403206989782918</v>
       </c>
       <c r="F116" t="n">
-        <v>-28.96194619446959</v>
+        <v>-28.93949939242705</v>
       </c>
       <c r="G116" t="n">
-        <v>-85.90199229359719</v>
+        <v>-85.89753756586708</v>
       </c>
       <c r="H116" t="n">
-        <v>-47.06223128036184</v>
+        <v>-47.04550385679985</v>
       </c>
       <c r="I116" t="n">
-        <v>38.54452766067261</v>
+        <v>38.54607187418291</v>
       </c>
       <c r="J116" t="n">
         <v>17.78710309672154</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2016922257436261</v>
+        <v>0.2017459667812261</v>
       </c>
       <c r="L116" t="n">
-        <v>14.73818447400489</v>
+        <v>14.7383749363898</v>
       </c>
       <c r="M116" t="n">
-        <v>18.74807415774305</v>
+        <v>18.74818225801557</v>
       </c>
       <c r="N116" t="n">
-        <v>20.4549775181034</v>
+        <v>20.45503306963233</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.9848104609441286</v>
+        <v>-0.9846828348674048</v>
       </c>
       <c r="P116" t="n">
-        <v>2.102925503320956</v>
+        <v>2.109543885674372</v>
       </c>
       <c r="Q116" t="n">
-        <v>-97.89707449667904</v>
+        <v>-97.89045611432563</v>
       </c>
       <c r="R116" t="n">
-        <v>-68.6906122233155</v>
+        <v>-68.68661355669121</v>
       </c>
       <c r="S116" t="n">
-        <v>-71.70611816990387</v>
+        <v>-71.69717779034063</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -33180,7 +33172,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17/08/2026 20:27:23</t>
+          <t>17/08/2026 21:26:41</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33220,13 +33212,13 @@
         <v>15.1899995803833</v>
       </c>
       <c r="N2" t="n">
-        <v>99.59300231933594</v>
+        <v>99.56400299072266</v>
       </c>
       <c r="O2" t="n">
-        <v>4474.2001953125</v>
+        <v>4473.10009765625</v>
       </c>
       <c r="P2" t="n">
-        <v>84.72000122070312</v>
+        <v>84.94999694824219</v>
       </c>
       <c r="Q2" t="n">
         <v>4.619856179944848</v>
@@ -33243,7 +33235,7 @@
         <v>4.406072690546755</v>
       </c>
       <c r="U2" t="n">
-        <v>3.428037063075394</v>
+        <v>3.461413825165328</v>
       </c>
       <c r="V2" t="n">
         <v>0.06764446371292338</v>
@@ -33267,10 +33259,10 @@
         <v>0.2931891435008565</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5776843770692294</v>
+        <v>0.5775423384474593</v>
       </c>
       <c r="AD2" t="n">
-        <v>-6.059830536334355</v>
+        <v>-6.082928152834144</v>
       </c>
       <c r="AE2" t="n">
         <v>-3.358079834484684</v>
@@ -33294,7 +33286,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.635472647194829</v>
+        <v>2.641035440876484</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33393,13 +33385,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.06015650068387</v>
+        <v>75.629206071249</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08033729451011387</v>
+        <v>0.0803406566430634</v>
       </c>
       <c r="D2" t="n">
-        <v>68.10344827586206</v>
+        <v>67.24137931034483</v>
       </c>
       <c r="E2" t="n">
         <v>37.13048693837295</v>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -1169,7 +1169,7 @@
         <v>-13.89005352790985</v>
       </c>
       <c r="R8" t="n">
-        <v>109.2435801283177</v>
+        <v>109.3250964097663</v>
       </c>
       <c r="S8" t="n">
         <v>5.837879955976955</v>
@@ -1437,7 +1437,7 @@
         <v>-26.29427792915531</v>
       </c>
       <c r="R11" t="n">
-        <v>131.0489206959446</v>
+        <v>130.8751876643086</v>
       </c>
       <c r="S11" t="n">
         <v>4.935619379685119</v>
@@ -1813,7 +1813,7 @@
         <v>-17.37967000826688</v>
       </c>
       <c r="R15" t="n">
-        <v>123.6328516556867</v>
+        <v>123.6308850703517</v>
       </c>
       <c r="S15" t="n">
         <v>11.11555642224717</v>
@@ -2685,79 +2685,83 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>MSCIWORLD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ethereum</t>
+          <t>MSCI World ETF</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2326.2900390625</v>
+        <v>159.9299926757812</v>
       </c>
       <c r="E25" t="n">
-        <v>3.32371427716327</v>
+        <v>-0.4791563703071766</v>
       </c>
       <c r="F25" t="n">
-        <v>23.67907610919524</v>
+        <v>-1.514875745497413</v>
       </c>
       <c r="G25" t="n">
-        <v>21.32694735425382</v>
+        <v>2.506081461510679</v>
       </c>
       <c r="H25" t="n">
-        <v>35.96224071742409</v>
+        <v>3.041031993907106</v>
       </c>
       <c r="I25" t="n">
-        <v>84.38732037487213</v>
+        <v>54.39445660947897</v>
       </c>
       <c r="J25" t="n">
-        <v>24.74638979332766</v>
+        <v>41.1656325492966</v>
       </c>
       <c r="K25" t="n">
-        <v>1.29241027134186</v>
+        <v>0.5867775875649188</v>
       </c>
       <c r="L25" t="n">
-        <v>1960.646949614593</v>
+        <v>159.4622858504092</v>
       </c>
       <c r="M25" t="n">
-        <v>1901.136682945431</v>
+        <v>157.3285539387835</v>
       </c>
       <c r="N25" t="n">
-        <v>2125.878269031748</v>
+        <v>148.7078829737173</v>
       </c>
       <c r="O25" t="n">
-        <v>38.78562709749747</v>
+        <v>-0.01197899771999578</v>
       </c>
       <c r="P25" t="n">
-        <v>95.73002380847775</v>
+        <v>57.36177582232416</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.269976191522247</v>
+        <v>-42.63822417767584</v>
       </c>
       <c r="R25" t="n">
-        <v>544.0336163072053</v>
+        <v>29.4609916583787</v>
       </c>
       <c r="S25" t="n">
-        <v>25.04609922050946</v>
+        <v>3.642016205109133</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W25" t="n">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>73</v>
+        <v>69.3</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2766,90 +2770,94 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 25); RSI ipercomprato (84) — attenzione estensione; vicino alla resistenza dei 20g (2,347)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSCIWORLD</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MSCI World ETF</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>159.9299926757812</v>
+        <v>52.41999816894531</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4791563703071766</v>
+        <v>-0.1904080120844309</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.514875745497413</v>
+        <v>0.2102787091694758</v>
       </c>
       <c r="G26" t="n">
-        <v>2.506081461510679</v>
+        <v>3.148363801119913</v>
       </c>
       <c r="H26" t="n">
-        <v>3.041031993907106</v>
+        <v>4.798076147976382</v>
       </c>
       <c r="I26" t="n">
-        <v>54.39445660947897</v>
+        <v>54.0511460774312</v>
       </c>
       <c r="J26" t="n">
-        <v>41.1656325492966</v>
+        <v>19.872776634607</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5867775875649188</v>
+        <v>0.6063421594002183</v>
       </c>
       <c r="L26" t="n">
-        <v>159.4622858504092</v>
+        <v>52.07718884359414</v>
       </c>
       <c r="M26" t="n">
-        <v>157.3285539387835</v>
+        <v>51.62426364945335</v>
       </c>
       <c r="N26" t="n">
-        <v>148.7078829737173</v>
+        <v>49.76833475412095</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.01197899771999578</v>
+        <v>-0.02389940264892609</v>
       </c>
       <c r="P26" t="n">
-        <v>57.36177582232416</v>
+        <v>63.69229830228365</v>
       </c>
       <c r="Q26" t="n">
-        <v>-42.63822417767584</v>
+        <v>-36.30770169771635</v>
       </c>
       <c r="R26" t="n">
-        <v>29.4609916583787</v>
+        <v>29.90619502794331</v>
       </c>
       <c r="S26" t="n">
-        <v>3.642016205109133</v>
+        <v>4.235428941422659</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>Trend Bullish</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
           <t>Double Bottom</t>
         </is>
       </c>
       <c r="W26" t="n">
-        <v>67.40000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>69.3</v>
+        <v>84</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2858,90 +2866,86 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 41); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Bottom; morning star — inversione rialzista a 3 candele; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>Ethereum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>93.43000030517578</v>
+        <v>2316.320068359375</v>
       </c>
       <c r="E27" t="n">
-        <v>1.975548465764776</v>
+        <v>2.880891418885234</v>
       </c>
       <c r="F27" t="n">
-        <v>7.304468396282338</v>
+        <v>23.14901461871353</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6803437777449628</v>
+        <v>20.80696657356451</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.919868748831384</v>
+        <v>35.37953626788337</v>
       </c>
       <c r="I27" t="n">
-        <v>59.9686164777549</v>
+        <v>84.12751690417284</v>
       </c>
       <c r="J27" t="n">
-        <v>9.497398018094769</v>
+        <v>24.74638979332766</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8136305014504261</v>
+        <v>1.283891750787609</v>
       </c>
       <c r="L27" t="n">
-        <v>88.18294060628898</v>
+        <v>1959.697428595247</v>
       </c>
       <c r="M27" t="n">
-        <v>87.6914462234661</v>
+        <v>1900.745703702172</v>
       </c>
       <c r="N27" t="n">
-        <v>84.29389795468038</v>
+        <v>2125.779065343159</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6627817406235763</v>
+        <v>38.14936685889331</v>
       </c>
       <c r="P27" t="n">
-        <v>92.22422780566433</v>
+        <v>93.71412746593975</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.77577219433567</v>
+        <v>-6.285872534060242</v>
       </c>
       <c r="R27" t="n">
-        <v>87.77345086856491</v>
+        <v>541.3400011880428</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.210251226734476</v>
+        <v>24.5101789677318</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="n">
-        <v>67.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>81.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -2950,73 +2954,73 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 9); morning star — inversione rialzista a 3 candele; in zona Fib Fib 50.0 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend in sviluppo (ADX 25); RSI ipercomprato (84) — attenzione estensione; vicino alla resistenza dei 20g (2,347)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>52.41999816894531</v>
+        <v>93.15000152587891</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1904080120844309</v>
+        <v>1.669939678487897</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2102787091694758</v>
+        <v>6.982889459474872</v>
       </c>
       <c r="G28" t="n">
-        <v>3.148363801119913</v>
+        <v>-0.9779931667161845</v>
       </c>
       <c r="H28" t="n">
-        <v>4.798076147976382</v>
+        <v>-9.192825245515813</v>
       </c>
       <c r="I28" t="n">
-        <v>54.0511460774312</v>
+        <v>59.60578534885493</v>
       </c>
       <c r="J28" t="n">
-        <v>19.872776634607</v>
+        <v>9.497398018094769</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6063421594002183</v>
+        <v>0.8000362721295995</v>
       </c>
       <c r="L28" t="n">
-        <v>52.07718884359414</v>
+        <v>88.15627405587976</v>
       </c>
       <c r="M28" t="n">
-        <v>51.62426364945335</v>
+        <v>87.68046587917995</v>
       </c>
       <c r="N28" t="n">
-        <v>49.76833475412095</v>
+        <v>84.29111189717494</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.02389940264892609</v>
+        <v>0.644912872657052</v>
       </c>
       <c r="P28" t="n">
-        <v>63.69229830228365</v>
+        <v>90.53647185425514</v>
       </c>
       <c r="Q28" t="n">
-        <v>-36.30770169771635</v>
+        <v>-9.463528145744855</v>
       </c>
       <c r="R28" t="n">
-        <v>29.90619502794331</v>
+        <v>86.42432309422506</v>
       </c>
       <c r="S28" t="n">
-        <v>4.235428941422659</v>
+        <v>-7.488331247101754</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3028,16 +3032,12 @@
           <t>Morning Star</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Double Bottom</t>
-        </is>
-      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="n">
-        <v>67.09999999999999</v>
+        <v>67</v>
       </c>
       <c r="X28" t="n">
-        <v>84</v>
+        <v>81.7</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; pattern: Double Bottom; morning star — inversione rialzista a 3 candele; in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; mercato laterale — ATR basso (ADX 9); morning star — inversione rialzista a 3 candele; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -3067,52 +3067,52 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>86.52999877929688</v>
+        <v>86.20999908447266</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8155620800522012</v>
+        <v>0.4427324307483271</v>
       </c>
       <c r="F29" t="n">
-        <v>6.498460036057696</v>
+        <v>6.104614257812502</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3455062137871723</v>
+        <v>-0.7140420747524301</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.19200814773422</v>
+        <v>-10.52413030641819</v>
       </c>
       <c r="I29" t="n">
-        <v>58.92724214986504</v>
+        <v>58.42471369754137</v>
       </c>
       <c r="J29" t="n">
         <v>10.69494301366865</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7934521286552612</v>
+        <v>0.7741026018017819</v>
       </c>
       <c r="L29" t="n">
-        <v>82.50510564060168</v>
+        <v>82.47462947918986</v>
       </c>
       <c r="M29" t="n">
-        <v>82.47325855640801</v>
+        <v>82.46070954876785</v>
       </c>
       <c r="N29" t="n">
-        <v>79.45825176226452</v>
+        <v>79.45506768569911</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5762594922598852</v>
+        <v>0.5558378593138287</v>
       </c>
       <c r="P29" t="n">
-        <v>91.37544039175934</v>
+        <v>88.99626131433152</v>
       </c>
       <c r="Q29" t="n">
-        <v>-8.62455960824065</v>
+        <v>-11.00373868566849</v>
       </c>
       <c r="R29" t="n">
-        <v>76.81624146479311</v>
+        <v>74.95252492097954</v>
       </c>
       <c r="S29" t="n">
-        <v>-6.139498331944115</v>
+        <v>-6.486607222658813</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="W29" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="X29" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -3337,83 +3337,87 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>GBP/USD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.64200019836426</v>
+        <v>1.36297345161438</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9293522771622653</v>
+        <v>0.6869391732336361</v>
       </c>
       <c r="F32" t="n">
-        <v>12.44896365368695</v>
+        <v>0.9772496162167688</v>
       </c>
       <c r="G32" t="n">
-        <v>25.83928692454804</v>
+        <v>1.872725317374102</v>
       </c>
       <c r="H32" t="n">
-        <v>33.99892418480941</v>
+        <v>0.9881486464428546</v>
       </c>
       <c r="I32" t="n">
-        <v>81.42335151384894</v>
+        <v>67.8933817016884</v>
       </c>
       <c r="J32" t="n">
-        <v>53.86222535816791</v>
+        <v>49.40842046097136</v>
       </c>
       <c r="K32" t="n">
-        <v>1.073171189376103</v>
+        <v>0.9697554132700289</v>
       </c>
       <c r="L32" t="n">
-        <v>9.114011043962801</v>
+        <v>1.348388811281686</v>
       </c>
       <c r="M32" t="n">
-        <v>8.66230318763388</v>
+        <v>1.343379189366839</v>
       </c>
       <c r="N32" t="n">
-        <v>9.554260813655427</v>
+        <v>1.340046420846628</v>
       </c>
       <c r="O32" t="n">
-        <v>0.2100717736725994</v>
+        <v>0.001260284563544383</v>
       </c>
       <c r="P32" t="n">
-        <v>92.82741247189786</v>
+        <v>87.69976969781563</v>
       </c>
       <c r="Q32" t="n">
-        <v>-7.172587528102138</v>
+        <v>-12.30023030218438</v>
       </c>
       <c r="R32" t="n">
-        <v>233.4512504093123</v>
+        <v>143.703073527112</v>
       </c>
       <c r="S32" t="n">
-        <v>30.3959761329454</v>
+        <v>1.902715213219008</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr"/>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Morning Star</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Breakout 20d, Breakout 50d, Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W32" t="n">
         <v>66</v>
       </c>
       <c r="X32" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -3422,90 +3426,94 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 54); RSI ipercomprato (81) — attenzione estensione</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 49); RSI in forza (68) — momentum positivo; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3659)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EMERGING</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MSCI Emerging ETF</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>66.62000274658203</v>
+        <v>10.57199954986572</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7714447610375874</v>
+        <v>0.2654620328241375</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.08997834181037057</v>
+        <v>11.70930003481612</v>
       </c>
       <c r="G33" t="n">
-        <v>2.50808576148791</v>
+        <v>25.01154481525307</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8935392672915654</v>
+        <v>33.11750984387712</v>
       </c>
       <c r="I33" t="n">
-        <v>54.65504414521295</v>
+        <v>80.96765620756456</v>
       </c>
       <c r="J33" t="n">
-        <v>18.90463159391577</v>
+        <v>53.86222535816791</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7472529223630026</v>
+        <v>1.058103835331945</v>
       </c>
       <c r="L33" t="n">
-        <v>65.6738433245296</v>
+        <v>9.10734431553437</v>
       </c>
       <c r="M33" t="n">
-        <v>65.52460845710752</v>
+        <v>8.659558064163349</v>
       </c>
       <c r="N33" t="n">
-        <v>61.31804018297998</v>
+        <v>9.553564289789769</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2178178379649917</v>
+        <v>0.2056044958197017</v>
       </c>
       <c r="P33" t="n">
-        <v>71.30436873840561</v>
+        <v>90.2542329803498</v>
       </c>
       <c r="Q33" t="n">
-        <v>-28.69563126159439</v>
+        <v>-9.7457670196502</v>
       </c>
       <c r="R33" t="n">
-        <v>62.58575258687515</v>
+        <v>231.110110583078</v>
       </c>
       <c r="S33" t="n">
-        <v>3.126941672096417</v>
+        <v>29.53826116200333</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W33" t="n">
-        <v>65.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="X33" t="n">
-        <v>70.90000000000001</v>
+        <v>69</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
@@ -3514,90 +3522,90 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 54); RSI ipercomprato (81) — attenzione estensione; doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BTC</t>
+          <t>EMERGING</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bitcoin</t>
+          <t>MSCI Emerging ETF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>72825.9609375</v>
+        <v>66.62000274658203</v>
       </c>
       <c r="E34" t="n">
-        <v>5.139265731205422</v>
+        <v>0.7714447610375874</v>
       </c>
       <c r="F34" t="n">
-        <v>15.55215601913598</v>
+        <v>-0.08997834181037057</v>
       </c>
       <c r="G34" t="n">
-        <v>12.51543255605616</v>
+        <v>2.50808576148791</v>
       </c>
       <c r="H34" t="n">
-        <v>14.61284678270998</v>
+        <v>0.8935392672915654</v>
       </c>
       <c r="I34" t="n">
-        <v>80.14631030156411</v>
+        <v>54.65504414521295</v>
       </c>
       <c r="J34" t="n">
-        <v>17.54181990712204</v>
+        <v>18.90463159391577</v>
       </c>
       <c r="K34" t="n">
-        <v>1.361599678042105</v>
+        <v>0.7472529223630026</v>
       </c>
       <c r="L34" t="n">
-        <v>65203.44467606935</v>
+        <v>65.6738433245296</v>
       </c>
       <c r="M34" t="n">
-        <v>64839.07706202279</v>
+        <v>65.52460845710752</v>
       </c>
       <c r="N34" t="n">
-        <v>71509.8595819161</v>
+        <v>61.31804018297998</v>
       </c>
       <c r="O34" t="n">
-        <v>794.4307008230096</v>
+        <v>0.2178178379649917</v>
       </c>
       <c r="P34" t="n">
-        <v>99.55417580263966</v>
+        <v>71.30436873840561</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.4458241973603386</v>
+        <v>-28.69563126159439</v>
       </c>
       <c r="R34" t="n">
-        <v>432.2725828498512</v>
+        <v>62.58575258687515</v>
       </c>
       <c r="S34" t="n">
-        <v>15.93952831408383</v>
+        <v>3.126941672096417</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Trend Bullish</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Double Bottom</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W34" t="n">
-        <v>65.3</v>
+        <v>65.5</v>
       </c>
       <c r="X34" t="n">
-        <v>77.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -3606,94 +3614,90 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>RSI ipercomprato (80) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (72,872); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); pattern: Double Top; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>BTC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Bitcoin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1842.800048828125</v>
+        <v>72704.1484375</v>
       </c>
       <c r="E35" t="n">
-        <v>2.230116153702943</v>
+        <v>4.96340431252984</v>
       </c>
       <c r="F35" t="n">
-        <v>6.816606827305316</v>
+        <v>15.35887745715227</v>
       </c>
       <c r="G35" t="n">
-        <v>12.14703648901048</v>
+        <v>12.32723337609618</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.743948041539748</v>
+        <v>14.42113935833833</v>
       </c>
       <c r="I35" t="n">
-        <v>64.80039282186726</v>
+        <v>79.97377641515924</v>
       </c>
       <c r="J35" t="n">
-        <v>35.55262625541045</v>
+        <v>17.54181990712204</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9531142515391056</v>
+        <v>1.357406586738559</v>
       </c>
       <c r="L35" t="n">
-        <v>1728.297760469877</v>
+        <v>65191.84348559316</v>
       </c>
       <c r="M35" t="n">
-        <v>1727.889641216551</v>
+        <v>64834.30010123848</v>
       </c>
       <c r="N35" t="n">
-        <v>1783.029123008688</v>
+        <v>71508.64751723949</v>
       </c>
       <c r="O35" t="n">
-        <v>12.86711770739378</v>
+        <v>786.6569116492142</v>
       </c>
       <c r="P35" t="n">
-        <v>97.27393880426015</v>
+        <v>98.38116012845093</v>
       </c>
       <c r="Q35" t="n">
-        <v>-2.726061195739846</v>
+        <v>-1.618839871549066</v>
       </c>
       <c r="R35" t="n">
-        <v>121.8622004709555</v>
+        <v>430.6857161374078</v>
       </c>
       <c r="S35" t="n">
-        <v>15.23982721298534</v>
+        <v>15.74560181299887</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Hammer</t>
-        </is>
-      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
+          <t>Breakout 20d, Breakout 50d, Double Bottom</t>
         </is>
       </c>
       <c r="W35" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="X35" t="n">
-        <v>79.40000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -3702,7 +3706,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); RSI in forza (65) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; hammer — segnale di rimbalzo da supporto; vicino alla resistenza dei 20g (1,849); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>RSI ipercomprato (80) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (72,872); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -3815,52 +3819,52 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>4577.60009765625</v>
+        <v>4575.10009765625</v>
       </c>
       <c r="E37" t="n">
-        <v>1.964632183166715</v>
+        <v>1.90894545321656</v>
       </c>
       <c r="F37" t="n">
-        <v>4.904207425307883</v>
+        <v>4.846915282488862</v>
       </c>
       <c r="G37" t="n">
-        <v>10.38607647773404</v>
+        <v>10.32579047954567</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8326422880964968</v>
+        <v>0.7775737805068239</v>
       </c>
       <c r="I37" t="n">
-        <v>71.77948793877675</v>
+        <v>71.68443598176479</v>
       </c>
       <c r="J37" t="n">
         <v>54.59051061571555</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9601966111192854</v>
+        <v>0.9574524039350366</v>
       </c>
       <c r="L37" t="n">
-        <v>4307.820582293627</v>
+        <v>4307.582487055532</v>
       </c>
       <c r="M37" t="n">
-        <v>4268.517295097237</v>
+        <v>4268.419255881551</v>
       </c>
       <c r="N37" t="n">
-        <v>4289.802658125054</v>
+        <v>4289.777782503164</v>
       </c>
       <c r="O37" t="n">
-        <v>33.12570865166253</v>
+        <v>32.96616449211851</v>
       </c>
       <c r="P37" t="n">
-        <v>96.58254527468597</v>
+        <v>96.14441005349185</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.417454725314033</v>
+        <v>-3.855589946508139</v>
       </c>
       <c r="R37" t="n">
-        <v>143.7512190478628</v>
+        <v>143.4243869849529</v>
       </c>
       <c r="S37" t="n">
-        <v>13.12212690123618</v>
+        <v>13.06034664275577</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3897,87 +3901,83 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GBP/USD</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.36286199092865</v>
+        <v>1841.300048828125</v>
       </c>
       <c r="E38" t="n">
-        <v>0.67870523788367</v>
+        <v>2.146903015995427</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9689919399780811</v>
+        <v>6.729660383852143</v>
       </c>
       <c r="G38" t="n">
-        <v>1.864394411289627</v>
+        <v>12.05575118931641</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9798900789077525</v>
+        <v>-5.820670460788435</v>
       </c>
       <c r="I38" t="n">
-        <v>67.82137576000119</v>
+        <v>64.68433922103048</v>
       </c>
       <c r="J38" t="n">
-        <v>49.40842046097136</v>
+        <v>35.55262625541045</v>
       </c>
       <c r="K38" t="n">
-        <v>0.9674429509777429</v>
+        <v>0.9491549777251251</v>
       </c>
       <c r="L38" t="n">
-        <v>1.348378195978283</v>
+        <v>1728.154903327019</v>
       </c>
       <c r="M38" t="n">
-        <v>1.343374818359555</v>
+        <v>1727.830817687139</v>
       </c>
       <c r="N38" t="n">
-        <v>1.340045311785078</v>
+        <v>1783.014197635554</v>
       </c>
       <c r="O38" t="n">
-        <v>0.001253171402973601</v>
+        <v>12.77139121166722</v>
       </c>
       <c r="P38" t="n">
-        <v>87.23368194371056</v>
+        <v>96.62486906887968</v>
       </c>
       <c r="Q38" t="n">
-        <v>-12.76631805628944</v>
+        <v>-3.375130931120327</v>
       </c>
       <c r="R38" t="n">
-        <v>143.4332632100962</v>
+        <v>121.424687800933</v>
       </c>
       <c r="S38" t="n">
-        <v>1.894381854633065</v>
+        <v>15.14602444749842</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Morning Star</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Breakout 20d, Breakout 50d, Outside Bar</t>
         </is>
       </c>
       <c r="W38" t="n">
-        <v>64.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="X38" t="n">
-        <v>71</v>
+        <v>79.3</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 49); RSI in forza (68) — momentum positivo; pattern: Double Bottom; morning star — inversione rialzista a 3 candele; vicino alla resistenza dei 20g (1.3659); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 36); RSI in forza (65) — momentum positivo; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (1,849); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -4187,52 +4187,52 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>68.18000030517578</v>
+        <v>68.12999725341797</v>
       </c>
       <c r="E41" t="n">
-        <v>3.721056230194297</v>
+        <v>3.644987451669235</v>
       </c>
       <c r="F41" t="n">
-        <v>5.097651026680605</v>
+        <v>5.020572656771694</v>
       </c>
       <c r="G41" t="n">
-        <v>13.59735943811027</v>
+        <v>13.51404740205704</v>
       </c>
       <c r="H41" t="n">
-        <v>-10.77551365171766</v>
+        <v>-10.84095068000993</v>
       </c>
       <c r="I41" t="n">
-        <v>65.27426965982443</v>
+        <v>65.1806766508671</v>
       </c>
       <c r="J41" t="n">
         <v>52.74320980151838</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9285959459388643</v>
+        <v>0.9257743926726801</v>
       </c>
       <c r="L41" t="n">
-        <v>63.29075954035397</v>
+        <v>63.28599734494847</v>
       </c>
       <c r="M41" t="n">
-        <v>63.7619024313681</v>
+        <v>63.7599415273776</v>
       </c>
       <c r="N41" t="n">
-        <v>65.18174333158635</v>
+        <v>65.18124578878277</v>
       </c>
       <c r="O41" t="n">
-        <v>0.7001536588160528</v>
+        <v>0.6969625808691243</v>
       </c>
       <c r="P41" t="n">
-        <v>92.39762709568662</v>
+        <v>91.95815566837005</v>
       </c>
       <c r="Q41" t="n">
-        <v>-7.602372904313378</v>
+        <v>-8.041844331629941</v>
       </c>
       <c r="R41" t="n">
-        <v>122.038142807228</v>
+        <v>121.7227780656515</v>
       </c>
       <c r="S41" t="n">
-        <v>17.96255910097806</v>
+        <v>17.87604563776586</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4279,52 +4279,52 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>87.31999969482422</v>
+        <v>87.47000122070312</v>
       </c>
       <c r="E42" t="n">
-        <v>2.278805641076787</v>
+        <v>2.45450395721114</v>
       </c>
       <c r="F42" t="n">
-        <v>16.00548788775615</v>
+        <v>16.20476640647244</v>
       </c>
       <c r="G42" t="n">
-        <v>17.25841566203958</v>
+        <v>17.45984650643859</v>
       </c>
       <c r="H42" t="n">
-        <v>25.24274713164278</v>
+        <v>25.45789375602059</v>
       </c>
       <c r="I42" t="n">
-        <v>77.45959469805858</v>
+        <v>77.6222391039813</v>
       </c>
       <c r="J42" t="n">
         <v>20.14370064584781</v>
       </c>
       <c r="K42" t="n">
-        <v>1.242528648060224</v>
+        <v>1.24725393700721</v>
       </c>
       <c r="L42" t="n">
-        <v>77.31976551837626</v>
+        <v>77.33405137798377</v>
       </c>
       <c r="M42" t="n">
-        <v>76.33243062553315</v>
+        <v>76.33831303831271</v>
       </c>
       <c r="N42" t="n">
-        <v>89.03866984104704</v>
+        <v>89.04016239354335</v>
       </c>
       <c r="O42" t="n">
-        <v>1.234821225098613</v>
+        <v>1.244393972049277</v>
       </c>
       <c r="P42" t="n">
-        <v>96.55124701135351</v>
+        <v>97.52631075178748</v>
       </c>
       <c r="Q42" t="n">
-        <v>-3.448752988646491</v>
+        <v>-2.473689248212515</v>
       </c>
       <c r="R42" t="n">
-        <v>315.8066889341466</v>
+        <v>316.8771710938051</v>
       </c>
       <c r="S42" t="n">
-        <v>19.96205934393207</v>
+        <v>20.16813460746913</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="W42" t="n">
-        <v>62.6</v>
+        <v>62.7</v>
       </c>
       <c r="X42" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); RSI ipercomprato (77) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (87.85)</t>
+          <t>trend in sviluppo (ADX 20); RSI ipercomprato (78) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (87.85)</t>
         </is>
       </c>
     </row>
@@ -4927,52 +4927,52 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7.183000087738037</v>
+        <v>7.190999984741211</v>
       </c>
       <c r="E49" t="n">
-        <v>6.145189868975831</v>
+        <v>6.263406571740981</v>
       </c>
       <c r="F49" t="n">
-        <v>13.40911938075446</v>
+        <v>13.53542611376084</v>
       </c>
       <c r="G49" t="n">
-        <v>11.63980904828443</v>
+        <v>11.76414525362082</v>
       </c>
       <c r="H49" t="n">
-        <v>21.62735119528942</v>
+        <v>21.76281079022835</v>
       </c>
       <c r="I49" t="n">
-        <v>68.94511554224545</v>
+        <v>69.07681417754024</v>
       </c>
       <c r="J49" t="n">
         <v>17.71993701189335</v>
       </c>
       <c r="K49" t="n">
-        <v>1.305193666307023</v>
+        <v>1.30887243623956</v>
       </c>
       <c r="L49" t="n">
-        <v>6.522317726653551</v>
+        <v>6.523079621606234</v>
       </c>
       <c r="M49" t="n">
-        <v>6.639393671333411</v>
+        <v>6.639707392784516</v>
       </c>
       <c r="N49" t="n">
-        <v>8.940156409428457</v>
+        <v>8.940236010393662</v>
       </c>
       <c r="O49" t="n">
-        <v>0.06724019501733486</v>
+        <v>0.06775072975485905</v>
       </c>
       <c r="P49" t="n">
-        <v>90.44413129508777</v>
+        <v>91.15665933625361</v>
       </c>
       <c r="Q49" t="n">
-        <v>-9.555868704912227</v>
+        <v>-8.843340663746392</v>
       </c>
       <c r="R49" t="n">
-        <v>326.4857607502789</v>
+        <v>327.5674344753154</v>
       </c>
       <c r="S49" t="n">
-        <v>12.61764363964222</v>
+        <v>12.74306888520156</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="W49" t="n">
-        <v>57.4</v>
+        <v>57.5</v>
       </c>
       <c r="X49" t="n">
-        <v>67.3</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -5287,52 +5287,52 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.48199987411499</v>
+        <v>6.482500076293945</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.08478329800634121</v>
+        <v>-0.0770730527000052</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.676152175603374</v>
+        <v>-1.668564732857281</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4805403730491209</v>
+        <v>0.48829424318384</v>
       </c>
       <c r="H53" t="n">
-        <v>3.595971004154896</v>
+        <v>3.603965285462141</v>
       </c>
       <c r="I53" t="n">
-        <v>50.48034641865979</v>
+        <v>50.51694159742495</v>
       </c>
       <c r="J53" t="n">
         <v>27.16664755269229</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4364794654573853</v>
+        <v>0.4374201603466574</v>
       </c>
       <c r="L53" t="n">
-        <v>6.504408408278894</v>
+        <v>6.504456046581652</v>
       </c>
       <c r="M53" t="n">
-        <v>6.394589534874696</v>
+        <v>6.394609150646419</v>
       </c>
       <c r="N53" t="n">
-        <v>5.925006842433137</v>
+        <v>5.925011819569246</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.01986522776803676</v>
+        <v>-0.01983330603354014</v>
       </c>
       <c r="P53" t="n">
-        <v>24.42387672258333</v>
+        <v>24.5775486615599</v>
       </c>
       <c r="Q53" t="n">
-        <v>-75.57612327741667</v>
+        <v>-75.42245133844011</v>
       </c>
       <c r="R53" t="n">
-        <v>-21.11576768223572</v>
+        <v>-21.03895860101741</v>
       </c>
       <c r="S53" t="n">
-        <v>2.807296599451403</v>
+        <v>2.815230020427983</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5369,83 +5369,87 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NEXI</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nexi</t>
+          <t>EUR/USD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.130000114440918</v>
+        <v>1.168360829353333</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3645284120800341</v>
+        <v>0.8996416752131697</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.525368761010049</v>
+        <v>1.331934808332624</v>
       </c>
       <c r="G54" t="n">
-        <v>-1.900235700265374</v>
+        <v>2.453563627301425</v>
       </c>
       <c r="H54" t="n">
-        <v>14.65852628061788</v>
+        <v>0.3972489231614196</v>
       </c>
       <c r="I54" t="n">
-        <v>51.347272788003</v>
+        <v>72.19066870676421</v>
       </c>
       <c r="J54" t="n">
-        <v>22.40807421633575</v>
+        <v>58.21094877226511</v>
       </c>
       <c r="K54" t="n">
-        <v>0.3933734869550722</v>
+        <v>1.024726524969223</v>
       </c>
       <c r="L54" t="n">
-        <v>4.145223286767552</v>
+        <v>1.153522838110066</v>
       </c>
       <c r="M54" t="n">
-        <v>3.982606841556622</v>
+        <v>1.151552222455529</v>
       </c>
       <c r="N54" t="n">
-        <v>3.930103374402217</v>
+        <v>1.155980180678204</v>
       </c>
       <c r="O54" t="n">
-        <v>-0.03602437889207888</v>
+        <v>0.001350386978062624</v>
       </c>
       <c r="P54" t="n">
-        <v>18.46969317619942</v>
+        <v>85.72171563279082</v>
       </c>
       <c r="Q54" t="n">
-        <v>-81.53030682380057</v>
+        <v>-14.27828436720919</v>
       </c>
       <c r="R54" t="n">
-        <v>-34.77483329866339</v>
+        <v>142.7088964613431</v>
       </c>
       <c r="S54" t="n">
-        <v>-1.666659476264754</v>
+        <v>2.382295711410176</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>Piercing Pattern</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr"/>
+          <t>Doji, Morning Star</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Breakout 20d, Breakout 50d, Double Top, Double Bottom</t>
+        </is>
+      </c>
       <c r="W54" t="n">
         <v>56.7</v>
       </c>
       <c r="X54" t="n">
-        <v>64.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -5454,90 +5458,90 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); segnale candlestick: Piercing Pattern; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 58); RSI ipercomprato (72) — attenzione estensione; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; doji — indecisione del mercato; vicino alla resistenza dei 20g (1.1714); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SP500</t>
+          <t>NEXI</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Nexi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Indici</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7641.16015625</v>
+        <v>4.130000114440918</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.8668915122777232</v>
+        <v>0.3645284120800341</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.023724525635962</v>
+        <v>-2.525368761010049</v>
       </c>
       <c r="G55" t="n">
-        <v>1.896265562867772</v>
+        <v>-1.900235700265374</v>
       </c>
       <c r="H55" t="n">
-        <v>2.624862817389007</v>
+        <v>14.65852628061788</v>
       </c>
       <c r="I55" t="n">
-        <v>51.17080217160539</v>
+        <v>51.347272788003</v>
       </c>
       <c r="J55" t="n">
-        <v>38.06261383311766</v>
+        <v>22.40807421633575</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5160290649959052</v>
+        <v>0.3933734869550722</v>
       </c>
       <c r="L55" t="n">
-        <v>7656.296321568731</v>
+        <v>4.145223286767552</v>
       </c>
       <c r="M55" t="n">
-        <v>7546.525745701148</v>
+        <v>3.982606841556622</v>
       </c>
       <c r="N55" t="n">
-        <v>7121.120106453847</v>
+        <v>3.930103374402217</v>
       </c>
       <c r="O55" t="n">
-        <v>-6.482073694752756</v>
+        <v>-0.03602437889207888</v>
       </c>
       <c r="P55" t="n">
-        <v>43.72281090084266</v>
+        <v>18.46969317619942</v>
       </c>
       <c r="Q55" t="n">
-        <v>-56.27718909915734</v>
+        <v>-81.53030682380057</v>
       </c>
       <c r="R55" t="n">
-        <v>12.79367210249388</v>
+        <v>-34.77483329866339</v>
       </c>
       <c r="S55" t="n">
-        <v>3.143236069025734</v>
+        <v>-1.666659476264754</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Piercing Pattern</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="X55" t="n">
-        <v>69.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
@@ -5546,86 +5550,90 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 38); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 22); segnale candlestick: Piercing Pattern; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>SP500</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Indici</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.196710005402565</v>
+        <v>7641.16015625</v>
       </c>
       <c r="E56" t="n">
-        <v>5.262878809444471</v>
+        <v>-0.8668915122777232</v>
       </c>
       <c r="F56" t="n">
-        <v>11.68329016081024</v>
+        <v>-2.023724525635962</v>
       </c>
       <c r="G56" t="n">
-        <v>15.92656880852539</v>
+        <v>1.896265562867772</v>
       </c>
       <c r="H56" t="n">
-        <v>21.35551534370834</v>
+        <v>2.624862817389007</v>
       </c>
       <c r="I56" t="n">
-        <v>63.70212922207554</v>
+        <v>51.17080217160539</v>
       </c>
       <c r="J56" t="n">
-        <v>35.18622759702112</v>
+        <v>38.06261383311766</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7564111025874183</v>
+        <v>0.5160290649959052</v>
       </c>
       <c r="L56" t="n">
-        <v>0.1825314658165669</v>
+        <v>7656.296321568731</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1804114495449347</v>
+        <v>7546.525745701148</v>
       </c>
       <c r="N56" t="n">
-        <v>0.2487427546420465</v>
+        <v>7121.120106453847</v>
       </c>
       <c r="O56" t="n">
-        <v>-0.000461827650829257</v>
+        <v>-6.482073694752756</v>
       </c>
       <c r="P56" t="n">
-        <v>79.08112630559957</v>
+        <v>43.72281090084266</v>
       </c>
       <c r="Q56" t="n">
-        <v>-20.91887369440043</v>
+        <v>-56.27718909915734</v>
       </c>
       <c r="R56" t="n">
-        <v>36.02295429082385</v>
+        <v>12.79367210249388</v>
       </c>
       <c r="S56" t="n">
-        <v>17.11438728949484</v>
+        <v>3.143236069025734</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Double Bottom, Bull Flag / Consolidation, Volatility Squeeze</t>
+        </is>
+      </c>
       <c r="W56" t="n">
         <v>56.6</v>
       </c>
       <c r="X56" t="n">
-        <v>61.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -5634,7 +5642,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); RSI in forza (64) — momentum positivo; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 38); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -5655,52 +5663,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>183.1399993896484</v>
+        <v>183.1000061035156</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.2722718371061972</v>
+        <v>-0.2940499280807862</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.99958311680656</v>
+        <v>-4.020547254373852</v>
       </c>
       <c r="G57" t="n">
-        <v>1.592053613561673</v>
+        <v>1.569868399613172</v>
       </c>
       <c r="H57" t="n">
-        <v>2.541989435040359</v>
+        <v>2.519596778396416</v>
       </c>
       <c r="I57" t="n">
-        <v>49.22839515929226</v>
+        <v>49.17049314991791</v>
       </c>
       <c r="J57" t="n">
         <v>20.49915346610195</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5265034525083686</v>
+        <v>0.5251580197573106</v>
       </c>
       <c r="L57" t="n">
-        <v>184.2922702173335</v>
+        <v>184.2884613329399</v>
       </c>
       <c r="M57" t="n">
-        <v>181.2942996235948</v>
+        <v>181.2927312594328</v>
       </c>
       <c r="N57" t="n">
-        <v>162.0542646068567</v>
+        <v>162.0538666637111</v>
       </c>
       <c r="O57" t="n">
-        <v>0.01205764105411955</v>
+        <v>0.009505362964754349</v>
       </c>
       <c r="P57" t="n">
-        <v>53.98184115043561</v>
+        <v>53.76808769355861</v>
       </c>
       <c r="Q57" t="n">
-        <v>-46.01815884956438</v>
+        <v>-46.23191230644139</v>
       </c>
       <c r="R57" t="n">
-        <v>10.7740005353121</v>
+        <v>10.64496503799451</v>
       </c>
       <c r="S57" t="n">
-        <v>2.628188580337465</v>
+        <v>2.605777099913387</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5717,7 +5725,7 @@
         <v>56.6</v>
       </c>
       <c r="X57" t="n">
-        <v>59.9</v>
+        <v>59.8</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -5733,87 +5741,87 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>UCG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EUR/USD</t>
+          <t>UniCredit</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.167951464653015</v>
+        <v>82.81999969482422</v>
       </c>
       <c r="E58" t="n">
-        <v>0.864288939535296</v>
+        <v>0.5463116829395265</v>
       </c>
       <c r="F58" t="n">
-        <v>1.296430607846588</v>
+        <v>-3.032436314522913</v>
       </c>
       <c r="G58" t="n">
-        <v>2.417666435854215</v>
+        <v>0.2420684357220759</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3620722134621834</v>
+        <v>11.78297177546079</v>
       </c>
       <c r="I58" t="n">
-        <v>71.89850973030875</v>
+        <v>50.06936192125564</v>
       </c>
       <c r="J58" t="n">
-        <v>58.21094877226511</v>
+        <v>16.21799290893182</v>
       </c>
       <c r="K58" t="n">
-        <v>1.015455435274411</v>
+        <v>0.4404270554978781</v>
       </c>
       <c r="L58" t="n">
-        <v>1.153483850995751</v>
+        <v>83.32625444133527</v>
       </c>
       <c r="M58" t="n">
-        <v>1.151536168937869</v>
+        <v>80.75973397320639</v>
       </c>
       <c r="N58" t="n">
-        <v>1.155976107397604</v>
+        <v>72.35995539155856</v>
       </c>
       <c r="O58" t="n">
-        <v>0.001324262279238831</v>
+        <v>-0.3704278749282057</v>
       </c>
       <c r="P58" t="n">
-        <v>83.78040714338209</v>
+        <v>15.36387696724295</v>
       </c>
       <c r="Q58" t="n">
-        <v>-16.21959285661792</v>
+        <v>-84.63612303275706</v>
       </c>
       <c r="R58" t="n">
-        <v>141.7386941138039</v>
+        <v>-23.30073615346086</v>
       </c>
       <c r="S58" t="n">
-        <v>2.346423490475735</v>
+        <v>-0.468692938275983</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Bullish Harami</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Breakout 20d, Breakout 50d, Double Top, Double Bottom</t>
+          <t>Volatility Squeeze</t>
         </is>
       </c>
       <c r="W58" t="n">
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="X58" t="n">
-        <v>66.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
@@ -5822,94 +5830,86 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 58); RSI in forza (72) — momentum positivo; pattern: Double Bottom; breakout massimi 50g — rottura resistenza rilevante; doji — indecisione del mercato; vicino alla resistenza dei 20g (1.1714); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>segnale candlestick: Bullish Harami</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>UCG</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UniCredit</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>82.81999969482422</v>
+        <v>0.1970800012350082</v>
       </c>
       <c r="E59" t="n">
-        <v>0.5463116829395265</v>
+        <v>5.460869889719056</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.032436314522913</v>
+        <v>11.8933575228058</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2420684357220759</v>
+        <v>16.14461743925375</v>
       </c>
       <c r="H59" t="n">
-        <v>11.78297177546079</v>
+        <v>21.58377538990823</v>
       </c>
       <c r="I59" t="n">
-        <v>50.06936192125564</v>
+        <v>63.92193515677244</v>
       </c>
       <c r="J59" t="n">
-        <v>16.21799290893182</v>
+        <v>35.18622759702112</v>
       </c>
       <c r="K59" t="n">
-        <v>0.4404270554978781</v>
+        <v>0.7652283161431761</v>
       </c>
       <c r="L59" t="n">
-        <v>83.32625444133527</v>
+        <v>0.1825667035148948</v>
       </c>
       <c r="M59" t="n">
-        <v>80.75973397320639</v>
+        <v>0.1804259591854226</v>
       </c>
       <c r="N59" t="n">
-        <v>72.35995539155856</v>
+        <v>0.248746436192618</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.3704278749282057</v>
+        <v>-0.0004382153811804583</v>
       </c>
       <c r="P59" t="n">
-        <v>15.36387696724295</v>
+        <v>80.24624737636601</v>
       </c>
       <c r="Q59" t="n">
-        <v>-84.63612303275706</v>
+        <v>-19.75375262363399</v>
       </c>
       <c r="R59" t="n">
-        <v>-23.30073615346086</v>
+        <v>36.62332390027895</v>
       </c>
       <c r="S59" t="n">
-        <v>-0.468692938275983</v>
+        <v>17.33467011205681</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Volatility Squeeze</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
       <c r="W59" t="n">
         <v>56.1</v>
       </c>
       <c r="X59" t="n">
-        <v>64.5</v>
+        <v>61.4</v>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>segnale candlestick: Bullish Harami</t>
+          <t>trend molto direzionale (ADX 35); RSI in forza (64) — momentum positivo; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -6105,87 +6105,83 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BC</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Brunello Cucinelli</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>86.51999664306641</v>
+        <v>1.258700013160706</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.9161739058105245</v>
+        <v>13.97107682264289</v>
       </c>
       <c r="F62" t="n">
-        <v>-3.759738404275248</v>
+        <v>25.69403044062915</v>
       </c>
       <c r="G62" t="n">
-        <v>5.076512619727014</v>
+        <v>16.1349869437051</v>
       </c>
       <c r="H62" t="n">
-        <v>3.024521534414903</v>
+        <v>10.7636152687387</v>
       </c>
       <c r="I62" t="n">
-        <v>48.47539389180901</v>
+        <v>77.21408581890901</v>
       </c>
       <c r="J62" t="n">
-        <v>44.57261476289134</v>
+        <v>51.59083204131132</v>
       </c>
       <c r="K62" t="n">
-        <v>0.4084839113104383</v>
+        <v>1.389582477225412</v>
       </c>
       <c r="L62" t="n">
-        <v>87.57814864423703</v>
+        <v>1.057227825286267</v>
       </c>
       <c r="M62" t="n">
-        <v>85.73151825645063</v>
+        <v>1.081957685489382</v>
       </c>
       <c r="N62" t="n">
-        <v>86.37517968525142</v>
+        <v>1.34138169622753</v>
       </c>
       <c r="O62" t="n">
-        <v>-0.5221559583580868</v>
+        <v>0.02052994551119162</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>78.0067789752335</v>
       </c>
       <c r="Q62" t="n">
-        <v>-100</v>
+        <v>-21.9932210247665</v>
       </c>
       <c r="R62" t="n">
-        <v>-18.99178823921573</v>
+        <v>259.9283406102176</v>
       </c>
       <c r="S62" t="n">
-        <v>4.89814878965229</v>
+        <v>18.6853868728202</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Dark Cloud Cover, Evening Star</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Double Bottom</t>
+          <t>Breakout 20d, Breakout 50d</t>
         </is>
       </c>
       <c r="W62" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="X62" t="n">
-        <v>60.3</v>
+        <v>67.2</v>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
@@ -6194,86 +6190,94 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 45); pattern: Double Bottom; candela di inversione bearish (engulfing); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 52); RSI ipercomprato (77) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Brunello Cucinelli</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>351.5499877929688</v>
+        <v>86.51999664306641</v>
       </c>
       <c r="E63" t="n">
-        <v>-1.598281872186658</v>
+        <v>-0.9161739058105245</v>
       </c>
       <c r="F63" t="n">
-        <v>-3.183607729046989</v>
+        <v>-3.759738404275248</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9591902644532579</v>
+        <v>5.076512619727014</v>
       </c>
       <c r="H63" t="n">
-        <v>16.02309828150783</v>
+        <v>3.024521534414903</v>
       </c>
       <c r="I63" t="n">
-        <v>48.46226705865762</v>
+        <v>48.47539389180901</v>
       </c>
       <c r="J63" t="n">
-        <v>21.30046089592741</v>
+        <v>44.57261476289134</v>
       </c>
       <c r="K63" t="n">
-        <v>0.2295727928905255</v>
+        <v>0.4084839113104383</v>
       </c>
       <c r="L63" t="n">
-        <v>355.6416275361465</v>
+        <v>87.57814864423703</v>
       </c>
       <c r="M63" t="n">
-        <v>343.8177354162271</v>
+        <v>85.73151825645063</v>
       </c>
       <c r="N63" t="n">
-        <v>317.0639468252256</v>
+        <v>86.37517968525142</v>
       </c>
       <c r="O63" t="n">
-        <v>-1.475874800280415</v>
+        <v>-0.5221559583580868</v>
       </c>
       <c r="P63" t="n">
-        <v>4.533788563511041</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>-95.46621143648896</v>
+        <v>-100</v>
       </c>
       <c r="R63" t="n">
-        <v>-27.1434746331199</v>
+        <v>-18.99178823921573</v>
       </c>
       <c r="S63" t="n">
-        <v>0.4715615676668117</v>
+        <v>4.89814878965229</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bearish Engulfing, Dark Cloud Cover, Evening Star</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Double Bottom</t>
+        </is>
+      </c>
       <c r="W63" t="n">
-        <v>55.1</v>
+        <v>55.4</v>
       </c>
       <c r="X63" t="n">
-        <v>58.8</v>
+        <v>60.3</v>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
@@ -6282,90 +6286,86 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 21); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 45); pattern: Double Bottom; candela di inversione bearish (engulfing); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Generali</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>42.84000015258789</v>
+        <v>351.5499877929688</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.06997616058852518</v>
+        <v>-1.598281872186658</v>
       </c>
       <c r="F64" t="n">
-        <v>-2.370102302214949</v>
+        <v>-3.183607729046989</v>
       </c>
       <c r="G64" t="n">
-        <v>1.228734549890054</v>
+        <v>0.9591902644532579</v>
       </c>
       <c r="H64" t="n">
-        <v>9.509205834029654</v>
+        <v>16.02309828150783</v>
       </c>
       <c r="I64" t="n">
-        <v>43.11098788866273</v>
+        <v>48.46226705865762</v>
       </c>
       <c r="J64" t="n">
-        <v>54.95734313291454</v>
+        <v>21.30046089592741</v>
       </c>
       <c r="K64" t="n">
-        <v>0.120205083772139</v>
+        <v>0.2295727928905255</v>
       </c>
       <c r="L64" t="n">
-        <v>43.56016106692836</v>
+        <v>355.6416275361465</v>
       </c>
       <c r="M64" t="n">
-        <v>42.56200992124792</v>
+        <v>343.8177354162271</v>
       </c>
       <c r="N64" t="n">
-        <v>38.27531359178325</v>
+        <v>317.0639468252256</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.2518039219017114</v>
+        <v>-1.475874800280415</v>
       </c>
       <c r="P64" t="n">
-        <v>10.81080384459743</v>
+        <v>4.533788563511041</v>
       </c>
       <c r="Q64" t="n">
-        <v>-89.18919615540257</v>
+        <v>-95.46621143648896</v>
       </c>
       <c r="R64" t="n">
-        <v>-65.61210318464965</v>
+        <v>-27.1434746331199</v>
       </c>
       <c r="S64" t="n">
-        <v>0.1870950285196793</v>
+        <v>0.4715615676668117</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Doji</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="n">
         <v>55.1</v>
       </c>
       <c r="X64" t="n">
-        <v>57.1</v>
+        <v>58.8</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -6374,90 +6374,90 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 55); doji — indecisione del mercato; sul supporto dei 20g (42.38); in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 21); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>Generali</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.237100005149841</v>
+        <v>42.84000015258789</v>
       </c>
       <c r="E65" t="n">
-        <v>12.01526833242592</v>
+        <v>-0.06997616058852518</v>
       </c>
       <c r="F65" t="n">
-        <v>23.53704939983468</v>
+        <v>-2.370102302214949</v>
       </c>
       <c r="G65" t="n">
-        <v>14.14204452525978</v>
+        <v>1.228734549890054</v>
       </c>
       <c r="H65" t="n">
-        <v>8.862848642774113</v>
+        <v>9.509205834029654</v>
       </c>
       <c r="I65" t="n">
-        <v>75.89081647887514</v>
+        <v>43.11098788866273</v>
       </c>
       <c r="J65" t="n">
-        <v>51.59083204131132</v>
+        <v>54.95734313291454</v>
       </c>
       <c r="K65" t="n">
-        <v>1.36143143634402</v>
+        <v>0.120205083772139</v>
       </c>
       <c r="L65" t="n">
-        <v>1.055170681666185</v>
+        <v>43.56016106692836</v>
       </c>
       <c r="M65" t="n">
-        <v>1.081110626351701</v>
+        <v>42.56200992124792</v>
       </c>
       <c r="N65" t="n">
-        <v>1.341166770774685</v>
+        <v>38.27531359178325</v>
       </c>
       <c r="O65" t="n">
-        <v>0.01915148346149546</v>
+        <v>-0.2518039219017114</v>
       </c>
       <c r="P65" t="n">
-        <v>71.7726540274658</v>
+        <v>10.81080384459743</v>
       </c>
       <c r="Q65" t="n">
-        <v>-28.22734597253419</v>
+        <v>-89.18919615540257</v>
       </c>
       <c r="R65" t="n">
-        <v>252.1689785570284</v>
+        <v>-65.61210318464965</v>
       </c>
       <c r="S65" t="n">
-        <v>16.64867814125515</v>
+        <v>0.1870950285196793</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Breakout 20d, Breakout 50d</t>
-        </is>
-      </c>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="X65" t="n">
-        <v>67</v>
+        <v>57.1</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 52); RSI ipercomprato (76) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante</t>
+          <t>trend molto direzionale (ADX 55); doji — indecisione del mercato; sul supporto dei 20g (42.38); in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7211,66 +7211,66 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1338.5</v>
+        <v>68.62000274658203</v>
       </c>
       <c r="E74" t="n">
-        <v>0.4955308555415705</v>
+        <v>-0.7233796008851101</v>
       </c>
       <c r="F74" t="n">
-        <v>1.202179397214831</v>
+        <v>-3.907016905822869</v>
       </c>
       <c r="G74" t="n">
-        <v>2.732364334857351</v>
+        <v>-1.0240863489414</v>
       </c>
       <c r="H74" t="n">
-        <v>-3.245628424293245</v>
+        <v>8.131112096678116</v>
       </c>
       <c r="I74" t="n">
-        <v>53.73735176587082</v>
+        <v>42.11431805649795</v>
       </c>
       <c r="J74" t="n">
-        <v>23.17353422636409</v>
+        <v>17.3924398629683</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6010136386342469</v>
+        <v>0.02871535774900085</v>
       </c>
       <c r="L74" t="n">
-        <v>1320.938242814111</v>
+        <v>70.04104008507623</v>
       </c>
       <c r="M74" t="n">
-        <v>1318.873943670788</v>
+        <v>68.71656778580707</v>
       </c>
       <c r="N74" t="n">
-        <v>1391.374992636323</v>
+        <v>64.16965014910076</v>
       </c>
       <c r="O74" t="n">
-        <v>-2.598254524009725</v>
+        <v>-0.2872365392003461</v>
       </c>
       <c r="P74" t="n">
-        <v>68.92210260631212</v>
+        <v>1.197633514550688</v>
       </c>
       <c r="Q74" t="n">
-        <v>-31.07789739368788</v>
+        <v>-98.80236648544931</v>
       </c>
       <c r="R74" t="n">
-        <v>25.68605364988914</v>
+        <v>-121.6845925267145</v>
       </c>
       <c r="S74" t="n">
-        <v>6.627893566127518</v>
+        <v>-0.2181095009541445</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7280,14 +7280,14 @@
       <c r="U74" t="inlineStr"/>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W74" t="n">
-        <v>52.8</v>
+        <v>51.9</v>
       </c>
       <c r="X74" t="n">
-        <v>62.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
@@ -7296,73 +7296,73 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 23); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>pattern: Double Top; sul supporto dei 20g (68.58); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>CPR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Campari</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>68.62000274658203</v>
+        <v>5.834000110626221</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.7233796008851101</v>
+        <v>0.137313709403375</v>
       </c>
       <c r="F75" t="n">
-        <v>-3.907016905822869</v>
+        <v>-2.179746974094965</v>
       </c>
       <c r="G75" t="n">
-        <v>-1.0240863489414</v>
+        <v>3.770897989845623</v>
       </c>
       <c r="H75" t="n">
-        <v>8.131112096678116</v>
+        <v>2.530756624914776</v>
       </c>
       <c r="I75" t="n">
-        <v>42.11431805649795</v>
+        <v>51.35492018695155</v>
       </c>
       <c r="J75" t="n">
-        <v>17.3924398629683</v>
+        <v>47.44302177931041</v>
       </c>
       <c r="K75" t="n">
-        <v>0.02871535774900085</v>
+        <v>0.4504037774490752</v>
       </c>
       <c r="L75" t="n">
-        <v>70.04104008507623</v>
+        <v>5.84519952201526</v>
       </c>
       <c r="M75" t="n">
-        <v>68.71656778580707</v>
+        <v>5.761944560983284</v>
       </c>
       <c r="N75" t="n">
-        <v>64.16965014910076</v>
+        <v>5.871737211822508</v>
       </c>
       <c r="O75" t="n">
-        <v>-0.2872365392003461</v>
+        <v>-0.02109091131944965</v>
       </c>
       <c r="P75" t="n">
-        <v>1.197633514550688</v>
+        <v>25.50339866101717</v>
       </c>
       <c r="Q75" t="n">
-        <v>-98.80236648544931</v>
+        <v>-74.49660133898283</v>
       </c>
       <c r="R75" t="n">
-        <v>-121.6845925267145</v>
+        <v>-10.80830316546844</v>
       </c>
       <c r="S75" t="n">
-        <v>-0.2181095009541445</v>
+        <v>2.243257321009096</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7370,16 +7370,12 @@
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="n">
-        <v>51.9</v>
+        <v>51.6</v>
       </c>
       <c r="X75" t="n">
-        <v>68.09999999999999</v>
+        <v>53.8</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -7388,86 +7384,94 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>pattern: Double Top; sul supporto dei 20g (68.58); in zona Fib Fib 23.6 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 47); in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CPR</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Campari</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>5.834000110626221</v>
+        <v>1334</v>
       </c>
       <c r="E76" t="n">
-        <v>0.137313709403375</v>
+        <v>0.1576676587915271</v>
       </c>
       <c r="F76" t="n">
-        <v>-2.179746974094965</v>
+        <v>0.8619404676014852</v>
       </c>
       <c r="G76" t="n">
-        <v>3.770897989845623</v>
+        <v>2.386980965782359</v>
       </c>
       <c r="H76" t="n">
-        <v>2.530756624914776</v>
+        <v>-3.570913946960919</v>
       </c>
       <c r="I76" t="n">
-        <v>51.35492018695155</v>
+        <v>53.10963848993205</v>
       </c>
       <c r="J76" t="n">
-        <v>47.44302177931041</v>
+        <v>23.17353422636409</v>
       </c>
       <c r="K76" t="n">
-        <v>0.4504037774490752</v>
+        <v>0.577909219906026</v>
       </c>
       <c r="L76" t="n">
-        <v>5.84519952201526</v>
+        <v>1320.50967138554</v>
       </c>
       <c r="M76" t="n">
-        <v>5.761944560983284</v>
+        <v>1318.697473082553</v>
       </c>
       <c r="N76" t="n">
-        <v>5.871737211822508</v>
+        <v>1391.33021651692</v>
       </c>
       <c r="O76" t="n">
-        <v>-0.02109091131944965</v>
+        <v>-2.885434011189215</v>
       </c>
       <c r="P76" t="n">
-        <v>25.50339866101717</v>
+        <v>65.38158265006921</v>
       </c>
       <c r="Q76" t="n">
-        <v>-74.49660133898283</v>
+        <v>-34.6184173499308</v>
       </c>
       <c r="R76" t="n">
-        <v>-10.80830316546844</v>
+        <v>23.29754203715655</v>
       </c>
       <c r="S76" t="n">
-        <v>2.243257321009096</v>
+        <v>6.269413535460688</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W76" t="n">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="X76" t="n">
-        <v>53.8</v>
+        <v>61</v>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
@@ -7476,7 +7480,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 47); in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 23); doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -7855,83 +7859,87 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.8381999731063843</v>
+        <v>311.2999877929688</v>
       </c>
       <c r="E81" t="n">
-        <v>6.231560302117933</v>
+        <v>-1.745415211206824</v>
       </c>
       <c r="F81" t="n">
-        <v>10.37167020846095</v>
+        <v>1.978633897044424</v>
       </c>
       <c r="G81" t="n">
-        <v>9.135225154337734</v>
+        <v>-4.476978796422504</v>
       </c>
       <c r="H81" t="n">
-        <v>-12.74012941676453</v>
+        <v>2.068919558227056</v>
       </c>
       <c r="I81" t="n">
-        <v>59.83488181323854</v>
+        <v>48.9254164058298</v>
       </c>
       <c r="J81" t="n">
-        <v>15.13964090290866</v>
+        <v>34.84480275321701</v>
       </c>
       <c r="K81" t="n">
-        <v>0.8441579375714233</v>
+        <v>0.4180413534279388</v>
       </c>
       <c r="L81" t="n">
-        <v>0.7910563568430511</v>
+        <v>312.320891034991</v>
       </c>
       <c r="M81" t="n">
-        <v>0.8322071769018661</v>
+        <v>309.381239538945</v>
       </c>
       <c r="N81" t="n">
-        <v>1.267492445747978</v>
+        <v>282.9182776541044</v>
       </c>
       <c r="O81" t="n">
-        <v>0.00450859671783369</v>
+        <v>-0.4613958126797078</v>
       </c>
       <c r="P81" t="n">
-        <v>94.54048745428967</v>
+        <v>54.4392953858207</v>
       </c>
       <c r="Q81" t="n">
-        <v>-5.459512545710325</v>
+        <v>-45.5607046141793</v>
       </c>
       <c r="R81" t="n">
-        <v>81.69565187656846</v>
+        <v>-5.412493656321037</v>
       </c>
       <c r="S81" t="n">
-        <v>10.57288715633162</v>
+        <v>-3.22079703761472</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr"/>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Dark Cloud Cover</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W81" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="X81" t="n">
-        <v>56.4</v>
+        <v>65.5</v>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
@@ -7940,94 +7948,90 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom</t>
+          <t>trend molto direzionale (ADX 35); pattern: Double Top; segnale candlestick: Dark Cloud Cover; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>311.2999877929688</v>
+        <v>179.7700042724609</v>
       </c>
       <c r="E82" t="n">
-        <v>-1.745415211206824</v>
+        <v>-1.198127349461497</v>
       </c>
       <c r="F82" t="n">
-        <v>1.978633897044424</v>
+        <v>-3.240211653595659</v>
       </c>
       <c r="G82" t="n">
-        <v>-4.476978796422504</v>
+        <v>0.5143964984898108</v>
       </c>
       <c r="H82" t="n">
-        <v>2.068919558227056</v>
+        <v>5.418404714306391</v>
       </c>
       <c r="I82" t="n">
-        <v>48.9254164058298</v>
+        <v>41.48235932127205</v>
       </c>
       <c r="J82" t="n">
-        <v>34.84480275321701</v>
+        <v>19.69998171037362</v>
       </c>
       <c r="K82" t="n">
-        <v>0.4180413534279388</v>
+        <v>0.1816189409766972</v>
       </c>
       <c r="L82" t="n">
-        <v>312.320891034991</v>
+        <v>183.2766910113127</v>
       </c>
       <c r="M82" t="n">
-        <v>309.381239538945</v>
+        <v>181.0817951339118</v>
       </c>
       <c r="N82" t="n">
-        <v>282.9182776541044</v>
+        <v>170.3573657647942</v>
       </c>
       <c r="O82" t="n">
-        <v>-0.4613958126797078</v>
+        <v>-0.5443995521216567</v>
       </c>
       <c r="P82" t="n">
-        <v>54.4392953858207</v>
+        <v>2.546310604682541</v>
       </c>
       <c r="Q82" t="n">
-        <v>-45.5607046141793</v>
+        <v>-97.45368939531745</v>
       </c>
       <c r="R82" t="n">
-        <v>-5.412493656321037</v>
+        <v>-72.53929859733917</v>
       </c>
       <c r="S82" t="n">
-        <v>-3.22079703761472</v>
+        <v>-1.192699867993108</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Dark Cloud Cover</t>
-        </is>
-      </c>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
       <c r="V82" t="inlineStr">
         <is>
-          <t>Double Top</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W82" t="n">
         <v>49.7</v>
       </c>
       <c r="X82" t="n">
-        <v>65.5</v>
+        <v>60.2</v>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
@@ -8036,73 +8040,73 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 35); pattern: Double Top; segnale candlestick: Dark Cloud Cover; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>179.7700042724609</v>
+        <v>0.8407999873161316</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.198127349461497</v>
+        <v>6.561080196142188</v>
       </c>
       <c r="F83" t="n">
-        <v>-3.240211653595659</v>
+        <v>10.7140323178655</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5143964984898108</v>
+        <v>9.473751932301777</v>
       </c>
       <c r="H83" t="n">
-        <v>5.418404714306391</v>
+        <v>-12.46945784585489</v>
       </c>
       <c r="I83" t="n">
-        <v>41.48235932127205</v>
+        <v>60.29836485372865</v>
       </c>
       <c r="J83" t="n">
-        <v>19.69998171037362</v>
+        <v>15.13964090290866</v>
       </c>
       <c r="K83" t="n">
-        <v>0.1816189409766972</v>
+        <v>0.8618287746563874</v>
       </c>
       <c r="L83" t="n">
-        <v>183.2766910113127</v>
+        <v>0.7913039772439794</v>
       </c>
       <c r="M83" t="n">
-        <v>181.0817951339118</v>
+        <v>0.8323091382434248</v>
       </c>
       <c r="N83" t="n">
-        <v>170.3573657647942</v>
+        <v>1.267518316536135</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.5443995521216567</v>
+        <v>0.004674523550592381</v>
       </c>
       <c r="P83" t="n">
-        <v>2.546310604682541</v>
+        <v>96.76709836678108</v>
       </c>
       <c r="Q83" t="n">
-        <v>-97.45368939531745</v>
+        <v>-3.232901633218926</v>
       </c>
       <c r="R83" t="n">
-        <v>-72.53929859733917</v>
+        <v>84.03164132579357</v>
       </c>
       <c r="S83" t="n">
-        <v>-1.192699867993108</v>
+        <v>10.91587342099805</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8116,10 +8120,10 @@
         </is>
       </c>
       <c r="W83" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="X83" t="n">
-        <v>60.2</v>
+        <v>56.5</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -8128,7 +8132,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>pattern: Double Bottom; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>RSI in forza (60) — momentum positivo; pattern: Double Bottom</t>
         </is>
       </c>
     </row>
@@ -8241,52 +8245,52 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>159.1230010986328</v>
+        <v>159.0240020751953</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.2676289219414651</v>
+        <v>-0.3296778229404773</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.1286665415276445</v>
+        <v>-0.1908018985377846</v>
       </c>
       <c r="G85" t="n">
-        <v>-2.489799017406802</v>
+        <v>-2.550465386227274</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1063240643439212</v>
+        <v>0.04404250697092049</v>
       </c>
       <c r="I85" t="n">
-        <v>41.78864005767124</v>
+        <v>41.12770852375719</v>
       </c>
       <c r="J85" t="n">
         <v>65.23399688675336</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4070603315015116</v>
+        <v>0.3969962020207909</v>
       </c>
       <c r="L85" t="n">
-        <v>159.7935037345245</v>
+        <v>159.7840752561019</v>
       </c>
       <c r="M85" t="n">
-        <v>160.3295411698179</v>
+        <v>160.3256588551733</v>
       </c>
       <c r="N85" t="n">
-        <v>157.8952333050916</v>
+        <v>157.8942482401818</v>
       </c>
       <c r="O85" t="n">
-        <v>0.05362597954011239</v>
+        <v>0.04730809314410767</v>
       </c>
       <c r="P85" t="n">
-        <v>85.53434496165893</v>
+        <v>83.34458364834215</v>
       </c>
       <c r="Q85" t="n">
-        <v>-14.46565503834107</v>
+        <v>-16.65541635165784</v>
       </c>
       <c r="R85" t="n">
-        <v>-31.92005304262533</v>
+        <v>-32.87670490072239</v>
       </c>
       <c r="S85" t="n">
-        <v>-2.427010324789036</v>
+        <v>-2.487715757850439</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8300,10 +8304,10 @@
         </is>
       </c>
       <c r="W85" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="X85" t="n">
-        <v>57.9</v>
+        <v>58</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -8663,7 +8667,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>Bearish Harami</t>
+          <t>Doji, Bearish Harami</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -8684,7 +8688,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 49); segnale candlestick: Bearish Harami</t>
+          <t>trend molto direzionale (ADX 49); doji — indecisione del mercato</t>
         </is>
       </c>
     </row>
@@ -9257,52 +9261,52 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>98.88600158691406</v>
+        <v>98.87599945068359</v>
       </c>
       <c r="E96" t="n">
-        <v>0.05666270851143462</v>
+        <v>0.04654216207293782</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.074427278306589</v>
+        <v>-1.084433417084185</v>
       </c>
       <c r="G96" t="n">
-        <v>-2.228591869029684</v>
+        <v>-2.238481266192849</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.306483362243859</v>
+        <v>-0.3165671771287126</v>
       </c>
       <c r="I96" t="n">
-        <v>30.40576191919601</v>
+        <v>30.17930744427143</v>
       </c>
       <c r="J96" t="n">
         <v>62.3085577059136</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1162788155309843</v>
+        <v>0.113482360994029</v>
       </c>
       <c r="L96" t="n">
-        <v>99.8736426897165</v>
+        <v>99.87269010531361</v>
       </c>
       <c r="M96" t="n">
-        <v>100.0890617842539</v>
+        <v>100.0886695436174</v>
       </c>
       <c r="N96" t="n">
-        <v>99.61448400303014</v>
+        <v>99.61438447928656</v>
       </c>
       <c r="O96" t="n">
-        <v>-0.1109903477334368</v>
+        <v>-0.1116286607008445</v>
       </c>
       <c r="P96" t="n">
-        <v>21.60222018504882</v>
+        <v>20.94548223401111</v>
       </c>
       <c r="Q96" t="n">
-        <v>-78.39777981495118</v>
+        <v>-79.05451776598889</v>
       </c>
       <c r="R96" t="n">
-        <v>-112.3777483074165</v>
+        <v>-112.6401684378885</v>
       </c>
       <c r="S96" t="n">
-        <v>-2.508132417043785</v>
+        <v>-2.517993539197361</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9311,7 +9315,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>Hammer, Bullish Harami</t>
+          <t>Doji, Bullish Harami</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -9332,7 +9336,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 62); RSI scarico (30) — zona di interesse long; pattern: Double Bottom; hammer — segnale di rimbalzo da supporto; sul supporto dei 20g (98.56); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 62); RSI scarico (30) — zona di interesse long; pattern: Double Bottom; doji — indecisione del mercato; sul supporto dei 20g (98.56); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -12751,52 +12755,52 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6.48199987411499</v>
+        <v>6.482500076293945</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.780442487818956</v>
+        <v>-1.772863092935018</v>
       </c>
       <c r="F16" t="n">
-        <v>4.212220140850964</v>
+        <v>4.220261976796724</v>
       </c>
       <c r="G16" t="n">
-        <v>18.56593863305518</v>
+        <v>18.5750881150061</v>
       </c>
       <c r="H16" t="n">
-        <v>34.95731647204834</v>
+        <v>34.96773084185338</v>
       </c>
       <c r="I16" t="n">
-        <v>61.89715215601197</v>
+        <v>61.91657778290684</v>
       </c>
       <c r="J16" t="n">
         <v>36.46284296893615</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7754469623810508</v>
+        <v>0.7760117294856881</v>
       </c>
       <c r="L16" t="n">
-        <v>6.236068956735425</v>
+        <v>6.236116595038183</v>
       </c>
       <c r="M16" t="n">
-        <v>5.816064517892851</v>
+        <v>5.816084133664575</v>
       </c>
       <c r="N16" t="n">
-        <v>4.806325169979562</v>
+        <v>4.806330147115671</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0009547845790013887</v>
+        <v>0.0009867063134980092</v>
       </c>
       <c r="P16" t="n">
-        <v>69.23073252804809</v>
+        <v>69.29329690404748</v>
       </c>
       <c r="Q16" t="n">
-        <v>-30.7692674719519</v>
+        <v>-30.70670309595252</v>
       </c>
       <c r="R16" t="n">
-        <v>52.32488853464488</v>
+        <v>52.35810319078978</v>
       </c>
       <c r="S16" t="n">
-        <v>16.51985688542803</v>
+        <v>16.52884847559118</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -13479,52 +13483,52 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>183.1399993896484</v>
+        <v>183.1000061035156</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.615596713750935</v>
+        <v>-3.636644704535119</v>
       </c>
       <c r="F24" t="n">
-        <v>4.299791109528361</v>
+        <v>4.277014592091777</v>
       </c>
       <c r="G24" t="n">
-        <v>40.96367146764959</v>
+        <v>40.93288845756919</v>
       </c>
       <c r="H24" t="n">
-        <v>53.14629827465374</v>
+        <v>53.11285487753956</v>
       </c>
       <c r="I24" t="n">
-        <v>59.48752095348063</v>
+        <v>59.45489075978509</v>
       </c>
       <c r="J24" t="n">
         <v>46.55317943028517</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6251342644250009</v>
+        <v>0.6244049869154323</v>
       </c>
       <c r="L24" t="n">
-        <v>174.8747645356416</v>
+        <v>174.870955651248</v>
       </c>
       <c r="M24" t="n">
-        <v>158.4112941602181</v>
+        <v>158.4097257960561</v>
       </c>
       <c r="N24" t="n">
-        <v>119.9460682072096</v>
+        <v>119.945670264064</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5939753051745313</v>
+        <v>-0.5965275832638959</v>
       </c>
       <c r="P24" t="n">
-        <v>51.68887001701306</v>
+        <v>51.56493664314092</v>
       </c>
       <c r="Q24" t="n">
-        <v>-48.31112998298694</v>
+        <v>-48.43506335685908</v>
       </c>
       <c r="R24" t="n">
-        <v>33.03429122926237</v>
+        <v>32.99330288277433</v>
       </c>
       <c r="S24" t="n">
-        <v>34.6716611456086</v>
+        <v>34.64225215633194</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -16427,52 +16431,52 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4577.60009765625</v>
+        <v>4575.10009765625</v>
       </c>
       <c r="E56" t="n">
-        <v>4.501876534308824</v>
+        <v>4.444804119558232</v>
       </c>
       <c r="F56" t="n">
-        <v>14.07780679737593</v>
+        <v>14.01550460607279</v>
       </c>
       <c r="G56" t="n">
-        <v>1.905612147289637</v>
+        <v>1.849957650406275</v>
       </c>
       <c r="H56" t="n">
-        <v>33.41105627181066</v>
+        <v>33.33819546405896</v>
       </c>
       <c r="I56" t="n">
-        <v>57.40710794260052</v>
+        <v>57.33910645935386</v>
       </c>
       <c r="J56" t="n">
         <v>45.91953041093898</v>
       </c>
       <c r="K56" t="n">
-        <v>0.669952240700318</v>
+        <v>0.667838272976753</v>
       </c>
       <c r="L56" t="n">
-        <v>4353.456658978917</v>
+        <v>4353.218563740822</v>
       </c>
       <c r="M56" t="n">
-        <v>4235.962567225039</v>
+        <v>4235.864528009352</v>
       </c>
       <c r="N56" t="n">
-        <v>3189.252370023002</v>
+        <v>3189.227494401111</v>
       </c>
       <c r="O56" t="n">
-        <v>7.7335443920811</v>
+        <v>7.574000232537081</v>
       </c>
       <c r="P56" t="n">
-        <v>96.92719870797077</v>
+        <v>96.53324982437728</v>
       </c>
       <c r="Q56" t="n">
-        <v>-3.072801292029229</v>
+        <v>-3.46675017562272</v>
       </c>
       <c r="R56" t="n">
-        <v>28.61051269820188</v>
+        <v>28.42461717181072</v>
       </c>
       <c r="S56" t="n">
-        <v>-1.588732717268626</v>
+        <v>-1.64247882067613</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -16795,52 +16799,52 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.36286199092865</v>
+        <v>1.36297345161438</v>
       </c>
       <c r="E60" t="n">
-        <v>1.022140365849444</v>
+        <v>1.030402388793838</v>
       </c>
       <c r="F60" t="n">
-        <v>1.110735235265103</v>
+        <v>1.119004503877052</v>
       </c>
       <c r="G60" t="n">
-        <v>2.196929403088466</v>
+        <v>2.205287505307618</v>
       </c>
       <c r="H60" t="n">
-        <v>0.006814363102858323</v>
+        <v>0.01499334834185184</v>
       </c>
       <c r="I60" t="n">
-        <v>58.48088143114289</v>
+        <v>58.51675870743941</v>
       </c>
       <c r="J60" t="n">
         <v>10.09070046342652</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9368250893658145</v>
+        <v>0.9387877375095091</v>
       </c>
       <c r="L60" t="n">
-        <v>1.343304660890956</v>
+        <v>1.343315276194359</v>
       </c>
       <c r="M60" t="n">
-        <v>1.338421283005393</v>
+        <v>1.338425654012677</v>
       </c>
       <c r="N60" t="n">
-        <v>1.3089779543777</v>
+        <v>1.308979063439249</v>
       </c>
       <c r="O60" t="n">
-        <v>0.002072820859318264</v>
+        <v>0.002079934019889046</v>
       </c>
       <c r="P60" t="n">
-        <v>94.08489025519738</v>
+        <v>94.30084603853945</v>
       </c>
       <c r="Q60" t="n">
-        <v>-5.915109744802626</v>
+        <v>-5.699153961460554</v>
       </c>
       <c r="R60" t="n">
-        <v>153.0168244194316</v>
+        <v>153.291854925811</v>
       </c>
       <c r="S60" t="n">
-        <v>3.010562522080895</v>
+        <v>3.018987166698306</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -16987,52 +16991,52 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.167951464653015</v>
+        <v>1.168360829353333</v>
       </c>
       <c r="E62" t="n">
-        <v>1.249710899268108</v>
+        <v>1.28519872458781</v>
       </c>
       <c r="F62" t="n">
-        <v>2.052096166898387</v>
+        <v>2.087865226682517</v>
       </c>
       <c r="G62" t="n">
-        <v>1.25204429156287</v>
+        <v>1.287532934732005</v>
       </c>
       <c r="H62" t="n">
-        <v>0.6832597557558051</v>
+        <v>0.7185490410594131</v>
       </c>
       <c r="I62" t="n">
-        <v>56.28796473764891</v>
+        <v>56.47479626115906</v>
       </c>
       <c r="J62" t="n">
         <v>27.3538893007498</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7040776233955712</v>
+        <v>0.7113903265809164</v>
       </c>
       <c r="L62" t="n">
-        <v>1.155625183526701</v>
+        <v>1.155664170641017</v>
       </c>
       <c r="M62" t="n">
-        <v>1.154574581453105</v>
+        <v>1.154590634970764</v>
       </c>
       <c r="N62" t="n">
-        <v>1.124949698746352</v>
+        <v>1.124953772026952</v>
       </c>
       <c r="O62" t="n">
-        <v>0.001115216437331872</v>
+        <v>0.001141341136155665</v>
       </c>
       <c r="P62" t="n">
-        <v>91.19186573052163</v>
+        <v>92.24610340370795</v>
       </c>
       <c r="Q62" t="n">
-        <v>-8.808134269478376</v>
+        <v>-7.753896596292055</v>
       </c>
       <c r="R62" t="n">
-        <v>56.75353325596033</v>
+        <v>57.63406172570151</v>
       </c>
       <c r="S62" t="n">
-        <v>1.193647664269859</v>
+        <v>1.229115839535533</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -17157,83 +17161,83 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WTI Crude</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>86.52999877929688</v>
+        <v>481.1499938964844</v>
       </c>
       <c r="E64" t="n">
-        <v>5.012132496285071</v>
+        <v>-2.876463499306703</v>
       </c>
       <c r="F64" t="n">
-        <v>4.897564577707136</v>
+        <v>22.17510155606943</v>
       </c>
       <c r="G64" t="n">
-        <v>-13.15736721262321</v>
+        <v>34.862799201994</v>
       </c>
       <c r="H64" t="n">
-        <v>18.56672348464059</v>
+        <v>1.303268181061457</v>
       </c>
       <c r="I64" t="n">
-        <v>53.02756928813727</v>
+        <v>60.74047114091155</v>
       </c>
       <c r="J64" t="n">
-        <v>22.85872803239619</v>
+        <v>17.72677015289205</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5049796191177106</v>
+        <v>0.886329756567954</v>
       </c>
       <c r="L64" t="n">
-        <v>82.84499528267527</v>
+        <v>430.5567282243847</v>
       </c>
       <c r="M64" t="n">
-        <v>78.44016433708323</v>
+        <v>434.041001680574</v>
       </c>
       <c r="N64" t="n">
-        <v>73.97692469677601</v>
+        <v>394.5699317604564</v>
       </c>
       <c r="O64" t="n">
-        <v>-0.8630407014260884</v>
+        <v>13.44200318388416</v>
       </c>
       <c r="P64" t="n">
-        <v>45.93447495542927</v>
+        <v>80.19814449824699</v>
       </c>
       <c r="Q64" t="n">
-        <v>-54.06552504457073</v>
+        <v>-19.801855501753</v>
       </c>
       <c r="R64" t="n">
-        <v>-9.590687899593588</v>
+        <v>161.3800223976484</v>
       </c>
       <c r="S64" t="n">
-        <v>-22.42245107669607</v>
+        <v>28.83575346901914</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Double Top</t>
         </is>
       </c>
       <c r="W64" t="n">
         <v>61.1</v>
       </c>
       <c r="X64" t="n">
-        <v>82.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
@@ -17242,90 +17246,86 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 23); pattern: Bear Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>RSI in forza (61) — momentum positivo; pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SOYBEAN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Soybean</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>481.1499938964844</v>
+        <v>1236</v>
       </c>
       <c r="E65" t="n">
-        <v>-2.876463499306703</v>
+        <v>5.30351437699681</v>
       </c>
       <c r="F65" t="n">
-        <v>22.17510155606943</v>
+        <v>2.615193026151941</v>
       </c>
       <c r="G65" t="n">
-        <v>34.862799201994</v>
+        <v>6.620659909424198</v>
       </c>
       <c r="H65" t="n">
-        <v>1.303268181061457</v>
+        <v>15.54101425566721</v>
       </c>
       <c r="I65" t="n">
-        <v>60.74047114091155</v>
+        <v>60.96116489029419</v>
       </c>
       <c r="J65" t="n">
-        <v>17.72677015289205</v>
+        <v>21.73806173974758</v>
       </c>
       <c r="K65" t="n">
-        <v>0.886329756567954</v>
+        <v>0.9320868655848048</v>
       </c>
       <c r="L65" t="n">
-        <v>430.5567282243847</v>
+        <v>1170.452137739532</v>
       </c>
       <c r="M65" t="n">
-        <v>434.041001680574</v>
+        <v>1134.880670155577</v>
       </c>
       <c r="N65" t="n">
-        <v>394.5699317604564</v>
+        <v>1156.011523968149</v>
       </c>
       <c r="O65" t="n">
-        <v>13.44200318388416</v>
+        <v>1.685300603202293</v>
       </c>
       <c r="P65" t="n">
-        <v>80.19814449824699</v>
+        <v>90.44481054365733</v>
       </c>
       <c r="Q65" t="n">
-        <v>-19.801855501753</v>
+        <v>-9.555189456342669</v>
       </c>
       <c r="R65" t="n">
-        <v>161.3800223976484</v>
+        <v>77.06563384974183</v>
       </c>
       <c r="S65" t="n">
-        <v>28.83575346901914</v>
+        <v>6.231198968629137</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Double Top</t>
-        </is>
-      </c>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="n">
-        <v>61.1</v>
+        <v>61</v>
       </c>
       <c r="X65" t="n">
-        <v>68.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
@@ -17334,86 +17334,86 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>RSI in forza (61) — momentum positivo; pattern: Double Top; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 22); RSI in forza (61) — momentum positivo; vicino alla resistenza dei 20g (1,250); favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SOYBEAN</t>
+          <t>STM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Soybean</t>
+          <t>STMicroelectronics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1236</v>
+        <v>42.9900016784668</v>
       </c>
       <c r="E66" t="n">
-        <v>5.30351437699681</v>
+        <v>-7.855529303874764</v>
       </c>
       <c r="F66" t="n">
-        <v>2.615193026151941</v>
+        <v>-20.09293254998263</v>
       </c>
       <c r="G66" t="n">
-        <v>6.620659909424198</v>
+        <v>50.81565670640995</v>
       </c>
       <c r="H66" t="n">
-        <v>15.54101425566721</v>
+        <v>67.99531622558143</v>
       </c>
       <c r="I66" t="n">
-        <v>60.96116489029419</v>
+        <v>45.39342432429468</v>
       </c>
       <c r="J66" t="n">
-        <v>21.73806173974758</v>
+        <v>56.28777962905946</v>
       </c>
       <c r="K66" t="n">
-        <v>0.9320868655848048</v>
+        <v>0.262471917931579</v>
       </c>
       <c r="L66" t="n">
-        <v>1170.452137739532</v>
+        <v>48.73869317930035</v>
       </c>
       <c r="M66" t="n">
-        <v>1134.880670155577</v>
+        <v>40.2356107842097</v>
       </c>
       <c r="N66" t="n">
-        <v>1156.011523968149</v>
+        <v>33.3516180721731</v>
       </c>
       <c r="O66" t="n">
-        <v>1.685300603202293</v>
+        <v>-2.785803869127568</v>
       </c>
       <c r="P66" t="n">
-        <v>90.44481054365733</v>
+        <v>2.004936698568073</v>
       </c>
       <c r="Q66" t="n">
-        <v>-9.555189456342669</v>
+        <v>-97.99506330143193</v>
       </c>
       <c r="R66" t="n">
-        <v>77.06563384974183</v>
+        <v>-33.13004848961406</v>
       </c>
       <c r="S66" t="n">
-        <v>6.231198968629137</v>
+        <v>47.80815895372497</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Bullish</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="n">
-        <v>61</v>
+        <v>60.8</v>
       </c>
       <c r="X66" t="n">
-        <v>73.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
@@ -17422,86 +17422,94 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 22); RSI in forza (61) — momentum positivo; vicino alla resistenza dei 20g (1,250); favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 56); in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM</t>
+          <t>COFFEE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>STMicroelectronics</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>42.9900016784668</v>
+        <v>328.2999877929688</v>
       </c>
       <c r="E67" t="n">
-        <v>-7.855529303874764</v>
+        <v>-2.898556088031068</v>
       </c>
       <c r="F67" t="n">
-        <v>-20.09293254998263</v>
+        <v>-0.04567648302230554</v>
       </c>
       <c r="G67" t="n">
-        <v>50.81565670640995</v>
+        <v>8.816696887530838</v>
       </c>
       <c r="H67" t="n">
-        <v>67.99531622558143</v>
+        <v>-6.119537794409091</v>
       </c>
       <c r="I67" t="n">
-        <v>45.39342432429468</v>
+        <v>54.34481796922368</v>
       </c>
       <c r="J67" t="n">
-        <v>56.28777962905946</v>
+        <v>20.49409837241396</v>
       </c>
       <c r="K67" t="n">
-        <v>0.262471917931579</v>
+        <v>0.7406245939854794</v>
       </c>
       <c r="L67" t="n">
-        <v>48.73869317930035</v>
+        <v>312.955391197352</v>
       </c>
       <c r="M67" t="n">
-        <v>40.2356107842097</v>
+        <v>319.2809637491268</v>
       </c>
       <c r="N67" t="n">
-        <v>33.3516180721731</v>
+        <v>278.5354401885603</v>
       </c>
       <c r="O67" t="n">
-        <v>-2.785803869127568</v>
+        <v>7.677125268388624</v>
       </c>
       <c r="P67" t="n">
-        <v>2.004936698568073</v>
+        <v>67.66796879005055</v>
       </c>
       <c r="Q67" t="n">
-        <v>-97.99506330143193</v>
+        <v>-32.33203120994946</v>
       </c>
       <c r="R67" t="n">
-        <v>-33.13004848961406</v>
+        <v>85.18080067648512</v>
       </c>
       <c r="S67" t="n">
-        <v>47.80815895372497</v>
+        <v>11.13743892222738</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
           <t>Bullish</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Shooting Star, Bearish Engulfing, Dark Cloud Cover, Evening Star</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Outside Bar</t>
+        </is>
+      </c>
       <c r="W67" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="X67" t="n">
-        <v>62.9</v>
+        <v>74.5</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -17510,19 +17518,19 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 56); in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>trend in sviluppo (ADX 20); shooting star — rifiuto di resistenza; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>COFFEE</t>
+          <t>SILVER</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -17531,73 +17539,69 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>328.2999877929688</v>
+        <v>68.12999725341797</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.898556088031068</v>
+        <v>4.83473616849377</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.04567648302230554</v>
+        <v>21.57821378792752</v>
       </c>
       <c r="G68" t="n">
-        <v>8.816696887530838</v>
+        <v>-2.034655191290524</v>
       </c>
       <c r="H68" t="n">
-        <v>-6.119537794409091</v>
+        <v>87.78424127569724</v>
       </c>
       <c r="I68" t="n">
-        <v>54.34481796922368</v>
+        <v>51.66525686399288</v>
       </c>
       <c r="J68" t="n">
-        <v>20.49409837241396</v>
+        <v>16.39479696384767</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7406245939854794</v>
+        <v>0.4874975432326509</v>
       </c>
       <c r="L68" t="n">
-        <v>312.955391197352</v>
+        <v>66.29396451268944</v>
       </c>
       <c r="M68" t="n">
-        <v>319.2809637491268</v>
+        <v>63.45363258208902</v>
       </c>
       <c r="N68" t="n">
-        <v>278.5354401885603</v>
+        <v>43.33996307956686</v>
       </c>
       <c r="O68" t="n">
-        <v>7.677125268388624</v>
+        <v>-0.583617243088602</v>
       </c>
       <c r="P68" t="n">
-        <v>67.66796879005055</v>
+        <v>55.92750349911083</v>
       </c>
       <c r="Q68" t="n">
-        <v>-32.33203120994946</v>
+        <v>-44.07249650088917</v>
       </c>
       <c r="R68" t="n">
-        <v>85.18080067648512</v>
+        <v>-15.64966316879615</v>
       </c>
       <c r="S68" t="n">
-        <v>11.13743892222738</v>
+        <v>-6.331206871919948</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Shooting Star, Bearish Engulfing, Dark Cloud Cover, Evening Star</t>
-        </is>
-      </c>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
       <c r="V68" t="inlineStr">
         <is>
           <t>Outside Bar</t>
         </is>
       </c>
       <c r="W68" t="n">
-        <v>60.7</v>
+        <v>60.5</v>
       </c>
       <c r="X68" t="n">
-        <v>74.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -17606,90 +17610,94 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 20); shooting star — rifiuto di resistenza; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SILVER</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Reply</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>68.18000030517578</v>
+        <v>119.4000015258789</v>
       </c>
       <c r="E69" t="n">
-        <v>4.911678146329934</v>
+        <v>-0.9950223577321893</v>
       </c>
       <c r="F69" t="n">
-        <v>21.66744440530224</v>
+        <v>22.08588732117924</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.962754906475872</v>
+        <v>52.88092683566801</v>
       </c>
       <c r="H69" t="n">
-        <v>87.92206287432265</v>
+        <v>-17.71192522163101</v>
       </c>
       <c r="I69" t="n">
-        <v>51.71501514132292</v>
+        <v>63.89958015715951</v>
       </c>
       <c r="J69" t="n">
-        <v>16.39479696384767</v>
+        <v>28.67138143768508</v>
       </c>
       <c r="K69" t="n">
-        <v>0.4889246799420757</v>
+        <v>0.9803629934204511</v>
       </c>
       <c r="L69" t="n">
-        <v>66.29872670809495</v>
+        <v>104.0398880147917</v>
       </c>
       <c r="M69" t="n">
-        <v>63.45559348607952</v>
+        <v>107.9566336703007</v>
       </c>
       <c r="N69" t="n">
-        <v>43.34046062237041</v>
+        <v>117.6522035364615</v>
       </c>
       <c r="O69" t="n">
-        <v>-0.580426165141662</v>
+        <v>3.543878680003377</v>
       </c>
       <c r="P69" t="n">
-        <v>56.14073615695797</v>
+        <v>91.57303334667048</v>
       </c>
       <c r="Q69" t="n">
-        <v>-43.85926384304202</v>
+        <v>-8.426966653329513</v>
       </c>
       <c r="R69" t="n">
-        <v>-15.50417921809267</v>
+        <v>152.6958339154655</v>
       </c>
       <c r="S69" t="n">
-        <v>-6.262459980687096</v>
+        <v>45.52102021319904</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Doji, Bearish Harami</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Double Top, Inside Bar</t>
         </is>
       </c>
       <c r="W69" t="n">
-        <v>60.5</v>
+        <v>60.4</v>
       </c>
       <c r="X69" t="n">
-        <v>68.2</v>
+        <v>72.2</v>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
@@ -17698,19 +17706,19 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200)</t>
+          <t>trend in sviluppo (ADX 29); RSI in forza (64) — momentum positivo; pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>BRENT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Brent Crude</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -17719,52 +17727,52 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1842.800048828125</v>
+        <v>93.15000152587891</v>
       </c>
       <c r="E70" t="n">
-        <v>5.30285993303572</v>
+        <v>5.230462108445133</v>
       </c>
       <c r="F70" t="n">
-        <v>14.75899818118434</v>
+        <v>5.732126151218075</v>
       </c>
       <c r="G70" t="n">
-        <v>-1.486150279089182</v>
+        <v>-17.2514863832217</v>
       </c>
       <c r="H70" t="n">
-        <v>52.19689251017807</v>
+        <v>25.48834341010178</v>
       </c>
       <c r="I70" t="n">
-        <v>52.21730262405032</v>
+        <v>54.0075255102205</v>
       </c>
       <c r="J70" t="n">
-        <v>21.09923897482488</v>
+        <v>21.7182258999562</v>
       </c>
       <c r="K70" t="n">
-        <v>0.5370146299248095</v>
+        <v>0.5424083428996889</v>
       </c>
       <c r="L70" t="n">
-        <v>1787.50336580718</v>
+        <v>88.01241526584286</v>
       </c>
       <c r="M70" t="n">
-        <v>1755.312888671864</v>
+        <v>83.16898403534366</v>
       </c>
       <c r="N70" t="n">
-        <v>1349.114446366752</v>
+        <v>78.24663277020289</v>
       </c>
       <c r="O70" t="n">
-        <v>-0.4184303313275706</v>
+        <v>-0.6437445520321081</v>
       </c>
       <c r="P70" t="n">
-        <v>71.3534705614927</v>
+        <v>54.07755695867073</v>
       </c>
       <c r="Q70" t="n">
-        <v>-28.64652943850729</v>
+        <v>-45.92244304132926</v>
       </c>
       <c r="R70" t="n">
-        <v>-3.087543735443119</v>
+        <v>0.1187873658873832</v>
       </c>
       <c r="S70" t="n">
-        <v>-6.161523423538229</v>
+        <v>-14.56479632322378</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -17778,10 +17786,10 @@
         </is>
       </c>
       <c r="W70" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="X70" t="n">
-        <v>72.5</v>
+        <v>81.3</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
@@ -17790,91 +17798,87 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 21); pattern: Bear Flag / Consolidation</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 22); pattern: Bear Flag / Consolidation; in zona Fib Fib 38.2 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Reply</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>119.4000015258789</v>
+        <v>1841.300048828125</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9950223577321893</v>
+        <v>5.217145647321431</v>
       </c>
       <c r="F71" t="n">
-        <v>22.08588732117924</v>
+        <v>14.66558680029075</v>
       </c>
       <c r="G71" t="n">
-        <v>52.88092683566801</v>
+        <v>-1.566338455052885</v>
       </c>
       <c r="H71" t="n">
-        <v>-17.71192522163101</v>
+        <v>52.0730074804862</v>
       </c>
       <c r="I71" t="n">
-        <v>63.89958015715951</v>
+        <v>52.14236497758628</v>
       </c>
       <c r="J71" t="n">
-        <v>28.67138143768508</v>
+        <v>21.09923897482488</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9803629934204511</v>
+        <v>0.5350040663673733</v>
       </c>
       <c r="L71" t="n">
-        <v>104.0398880147917</v>
+        <v>1787.360508664322</v>
       </c>
       <c r="M71" t="n">
-        <v>107.9566336703007</v>
+        <v>1755.254065142452</v>
       </c>
       <c r="N71" t="n">
-        <v>117.6522035364615</v>
+        <v>1349.099520993618</v>
       </c>
       <c r="O71" t="n">
-        <v>3.543878680003377</v>
+        <v>-0.5141568270537675</v>
       </c>
       <c r="P71" t="n">
-        <v>91.57303334667048</v>
+        <v>71.01053505251339</v>
       </c>
       <c r="Q71" t="n">
-        <v>-8.426966653329513</v>
+        <v>-28.98946494748661</v>
       </c>
       <c r="R71" t="n">
-        <v>152.6958339154655</v>
+        <v>-3.257891510073232</v>
       </c>
       <c r="S71" t="n">
-        <v>45.52102021319904</v>
+        <v>-6.237905945317623</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Doji, Bearish Harami</t>
-        </is>
-      </c>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Double Top, Inside Bar</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W71" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="X71" t="n">
         <v>72.2</v>
@@ -17886,186 +17890,186 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 29); RSI in forza (64) — momentum positivo; pattern: Double Top; doji — indecisione del mercato; in zona Fib Fib 50.0 — livello strutturale</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 21); pattern: Bear Flag / Consolidation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BRENT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Brent Crude</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>93.43000030517578</v>
+        <v>815.3900146484375</v>
       </c>
       <c r="E72" t="n">
-        <v>5.546773439122088</v>
+        <v>-4.807545480657282</v>
       </c>
       <c r="F72" t="n">
-        <v>6.049945429477321</v>
+        <v>-7.371519572046692</v>
       </c>
       <c r="G72" t="n">
-        <v>-17.00275334595072</v>
+        <v>17.2548153611984</v>
       </c>
       <c r="H72" t="n">
-        <v>25.86554772996488</v>
+        <v>128.3685877399419</v>
       </c>
       <c r="I72" t="n">
-        <v>54.16195903069605</v>
+        <v>48.84208934480618</v>
       </c>
       <c r="J72" t="n">
-        <v>21.7182258999562</v>
+        <v>34.00957552927402</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5484145189102775</v>
+        <v>0.2159613610717264</v>
       </c>
       <c r="L72" t="n">
-        <v>88.03908181625209</v>
+        <v>850.1506443934657</v>
       </c>
       <c r="M72" t="n">
-        <v>83.17996437962981</v>
+        <v>736.0039326680494</v>
       </c>
       <c r="N72" t="n">
-        <v>78.24941882770833</v>
+        <v>471.2414223395907</v>
       </c>
       <c r="O72" t="n">
-        <v>-0.6258756840655839</v>
+        <v>-23.31416498016245</v>
       </c>
       <c r="P72" t="n">
-        <v>54.73560339630856</v>
+        <v>13.24212325056878</v>
       </c>
       <c r="Q72" t="n">
-        <v>-45.26439660369144</v>
+        <v>-86.75787674943122</v>
       </c>
       <c r="R72" t="n">
-        <v>0.5605147260334731</v>
+        <v>-29.92985962795138</v>
       </c>
       <c r="S72" t="n">
-        <v>-14.30798738767233</v>
+        <v>13.68757814273796</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr"/>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bearish Engulfing, Dark Cloud Cover</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Outside Bar</t>
         </is>
       </c>
       <c r="W72" t="n">
-        <v>60.3</v>
+        <v>58.9</v>
       </c>
       <c r="X72" t="n">
-        <v>81.2</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend in sviluppo (ADX 22); pattern: Bear Flag / Consolidation; in zona Fib Fib 38.2 — livello strutturale; favorito dal quadrante macro (Surriscaldamento)</t>
+          <t>trend molto direzionale (ADX 34); candela di inversione bearish (engulfing)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>WTI Crude</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Azioni USA</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>815.3900146484375</v>
+        <v>86.20999908447266</v>
       </c>
       <c r="E73" t="n">
-        <v>-4.807545480657282</v>
+        <v>4.623783359272338</v>
       </c>
       <c r="F73" t="n">
-        <v>-7.371519572046692</v>
+        <v>4.509639128426968</v>
       </c>
       <c r="G73" t="n">
-        <v>17.2548153611984</v>
+        <v>-13.47852307049594</v>
       </c>
       <c r="H73" t="n">
-        <v>128.3685877399419</v>
+        <v>18.12824762809788</v>
       </c>
       <c r="I73" t="n">
-        <v>48.84208934480618</v>
+        <v>52.84356557563387</v>
       </c>
       <c r="J73" t="n">
-        <v>34.00957552927402</v>
+        <v>22.85872803239619</v>
       </c>
       <c r="K73" t="n">
-        <v>0.2159613610717264</v>
+        <v>0.497613122155318</v>
       </c>
       <c r="L73" t="n">
-        <v>850.1506443934657</v>
+        <v>82.81451912126344</v>
       </c>
       <c r="M73" t="n">
-        <v>736.0039326680494</v>
+        <v>78.42761532944307</v>
       </c>
       <c r="N73" t="n">
-        <v>471.2414223395907</v>
+        <v>73.97374062021059</v>
       </c>
       <c r="O73" t="n">
-        <v>-23.31416498016245</v>
+        <v>-0.8834623343721448</v>
       </c>
       <c r="P73" t="n">
-        <v>13.24212325056878</v>
+        <v>45.18029231926939</v>
       </c>
       <c r="Q73" t="n">
-        <v>-86.75787674943122</v>
+        <v>-54.81970768073061</v>
       </c>
       <c r="R73" t="n">
-        <v>-29.92985962795138</v>
+        <v>-10.10046255998016</v>
       </c>
       <c r="S73" t="n">
-        <v>13.68757814273796</v>
+        <v>-22.70934339532404</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>Bullish</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Bearish Engulfing, Dark Cloud Cover</t>
-        </is>
-      </c>
+          <t>Trend Bullish</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Outside Bar</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W73" t="n">
-        <v>58.9</v>
+        <v>58.8</v>
       </c>
       <c r="X73" t="n">
-        <v>67.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
@@ -18074,7 +18078,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 34); candela di inversione bearish (engulfing)</t>
+          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend in sviluppo (ADX 23); pattern: Bear Flag / Consolidation; favorito dal quadrante macro (Surriscaldamento)</t>
         </is>
       </c>
     </row>
@@ -18919,52 +18923,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>159.1230010986328</v>
+        <v>159.0240020751953</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.1900529299850628</v>
+        <v>-0.2521500952035294</v>
       </c>
       <c r="F83" t="n">
-        <v>-2.003378479334728</v>
+        <v>-2.064347476674755</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.3637940636673997</v>
+        <v>-0.4257831351316854</v>
       </c>
       <c r="H83" t="n">
-        <v>11.12407002202174</v>
+        <v>11.05493372911233</v>
       </c>
       <c r="I83" t="n">
-        <v>50.06029865222524</v>
+        <v>49.7564844278406</v>
       </c>
       <c r="J83" t="n">
         <v>10.57169220539061</v>
       </c>
       <c r="K83" t="n">
-        <v>0.3856025226736057</v>
+        <v>0.3726969553302708</v>
       </c>
       <c r="L83" t="n">
-        <v>159.7135192546677</v>
+        <v>159.7040907762451</v>
       </c>
       <c r="M83" t="n">
-        <v>157.0964148044471</v>
+        <v>157.0925324898025</v>
       </c>
       <c r="N83" t="n">
-        <v>147.2435733198651</v>
+        <v>147.2425882549553</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.4339666899460894</v>
+        <v>-0.4402845763420942</v>
       </c>
       <c r="P83" t="n">
-        <v>44.33109253399245</v>
+        <v>43.19617402317067</v>
       </c>
       <c r="Q83" t="n">
-        <v>-55.66890746600755</v>
+        <v>-56.80382597682933</v>
       </c>
       <c r="R83" t="n">
-        <v>-27.71680740058899</v>
+        <v>-28.76404317749271</v>
       </c>
       <c r="S83" t="n">
-        <v>-0.2307316538342041</v>
+        <v>-0.2928035106188998</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -19283,52 +19287,52 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>72825.9609375</v>
+        <v>72704.1484375</v>
       </c>
       <c r="E87" t="n">
-        <v>15.93047322790211</v>
+        <v>15.7365618728265</v>
       </c>
       <c r="F87" t="n">
-        <v>12.57544451533454</v>
+        <v>12.38714495624198</v>
       </c>
       <c r="G87" t="n">
-        <v>10.41778061009946</v>
+        <v>10.23309007217288</v>
       </c>
       <c r="H87" t="n">
-        <v>-31.00467564165449</v>
+        <v>-31.12008081915175</v>
       </c>
       <c r="I87" t="n">
-        <v>52.0301237516278</v>
+        <v>51.90359210315623</v>
       </c>
       <c r="J87" t="n">
         <v>31.87275619729787</v>
       </c>
       <c r="K87" t="n">
-        <v>0.6303522479478757</v>
+        <v>0.6261965846880391</v>
       </c>
       <c r="L87" t="n">
-        <v>68802.66856550926</v>
+        <v>68791.06737503306</v>
       </c>
       <c r="M87" t="n">
-        <v>77053.87240973505</v>
+        <v>77049.09544895074</v>
       </c>
       <c r="N87" t="n">
-        <v>68479.44541969948</v>
+        <v>68478.23335502286</v>
       </c>
       <c r="O87" t="n">
-        <v>1076.497562487451</v>
+        <v>1068.723773313667</v>
       </c>
       <c r="P87" t="n">
-        <v>74.08414384079583</v>
+        <v>73.48563887487822</v>
       </c>
       <c r="Q87" t="n">
-        <v>-25.91585615920416</v>
+        <v>-26.51436112512178</v>
       </c>
       <c r="R87" t="n">
-        <v>5.713514881443356</v>
+        <v>5.179863228724813</v>
       </c>
       <c r="S87" t="n">
-        <v>5.572566987965488</v>
+        <v>5.39598080701198</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -19338,7 +19342,7 @@
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
       <c r="W87" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="X87" t="n">
         <v>62.7</v>
@@ -19555,52 +19559,52 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2326.2900390625</v>
+        <v>2316.320068359375</v>
       </c>
       <c r="E90" t="n">
-        <v>24.13878370625733</v>
+        <v>23.60675200948243</v>
       </c>
       <c r="F90" t="n">
-        <v>24.3002627679485</v>
+        <v>23.76753900720601</v>
       </c>
       <c r="G90" t="n">
-        <v>17.33770478640986</v>
+        <v>16.83482102752831</v>
       </c>
       <c r="H90" t="n">
-        <v>-8.659647454501096</v>
+        <v>-9.051112243327996</v>
       </c>
       <c r="I90" t="n">
-        <v>56.20765829040298</v>
+        <v>55.9689777070021</v>
       </c>
       <c r="J90" t="n">
         <v>33.22528043012893</v>
       </c>
       <c r="K90" t="n">
-        <v>0.8323220874230867</v>
+        <v>0.8237947395833145</v>
       </c>
       <c r="L90" t="n">
-        <v>2025.987384176167</v>
+        <v>2025.037863156821</v>
       </c>
       <c r="M90" t="n">
-        <v>2363.350853691208</v>
+        <v>2362.959874447949</v>
       </c>
       <c r="N90" t="n">
-        <v>2465.957179388456</v>
+        <v>2465.857975699867</v>
       </c>
       <c r="O90" t="n">
-        <v>74.15393434929138</v>
+        <v>73.51767411068724</v>
       </c>
       <c r="P90" t="n">
-        <v>97.48865927840072</v>
+        <v>96.30303145555943</v>
       </c>
       <c r="Q90" t="n">
-        <v>-2.511340721599275</v>
+        <v>-3.696968544440575</v>
       </c>
       <c r="R90" t="n">
-        <v>59.94838722057673</v>
+        <v>59.01737405034579</v>
       </c>
       <c r="S90" t="n">
-        <v>10.30321888913817</v>
+        <v>9.830483399444766</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -19610,10 +19614,10 @@
       <c r="U90" t="inlineStr"/>
       <c r="V90" t="inlineStr"/>
       <c r="W90" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="X90" t="n">
-        <v>69.3</v>
+        <v>69.2</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -19831,52 +19835,52 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.64200019836426</v>
+        <v>10.57199954986572</v>
       </c>
       <c r="E93" t="n">
-        <v>13.39954351356349</v>
+        <v>12.65362719732368</v>
       </c>
       <c r="F93" t="n">
-        <v>27.12775107766896</v>
+        <v>26.29153374523881</v>
       </c>
       <c r="G93" t="n">
-        <v>26.61116579959326</v>
+        <v>25.7783464472229</v>
       </c>
       <c r="H93" t="n">
-        <v>-19.96636835544257</v>
+        <v>-20.49281131845557</v>
       </c>
       <c r="I93" t="n">
-        <v>56.5993065048926</v>
+        <v>56.26727366451279</v>
       </c>
       <c r="J93" t="n">
         <v>18.24429951698081</v>
       </c>
       <c r="K93" t="n">
-        <v>1.003883765789847</v>
+        <v>0.9895512449574152</v>
       </c>
       <c r="L93" t="n">
-        <v>9.099840043216233</v>
+        <v>9.093173314787801</v>
       </c>
       <c r="M93" t="n">
-        <v>10.98507607530285</v>
+        <v>10.98233095183232</v>
       </c>
       <c r="N93" t="n">
-        <v>12.88699678063615</v>
+        <v>12.8863002567705</v>
       </c>
       <c r="O93" t="n">
-        <v>0.4105999530796667</v>
+        <v>0.406132675226769</v>
       </c>
       <c r="P93" t="n">
-        <v>94.88500377185377</v>
+        <v>93.04998909381135</v>
       </c>
       <c r="Q93" t="n">
-        <v>-5.114996228146216</v>
+        <v>-6.950010906188653</v>
       </c>
       <c r="R93" t="n">
-        <v>123.4419745236974</v>
+        <v>121.7817059975746</v>
       </c>
       <c r="S93" t="n">
-        <v>20.77224478257374</v>
+        <v>19.97783252004592</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -19886,7 +19890,7 @@
       <c r="U93" t="inlineStr"/>
       <c r="V93" t="inlineStr"/>
       <c r="W93" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="X93" t="n">
         <v>65</v>
@@ -19901,66 +19905,66 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>IG_IT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Palladium</t>
+          <t>Italgas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Commodities</t>
+          <t>Azioni IT</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1338.5</v>
+        <v>8.789999961853027</v>
       </c>
       <c r="E94" t="n">
-        <v>1.209829867674861</v>
+        <v>2.209297348319761</v>
       </c>
       <c r="F94" t="n">
-        <v>7.596463022508049</v>
+        <v>-13.22803689486282</v>
       </c>
       <c r="G94" t="n">
-        <v>-3.767346573750818</v>
+        <v>-10.12269732258366</v>
       </c>
       <c r="H94" t="n">
-        <v>28.75144588625034</v>
+        <v>26.20243746279096</v>
       </c>
       <c r="I94" t="n">
-        <v>47.28624254188866</v>
+        <v>35.01204718477037</v>
       </c>
       <c r="J94" t="n">
-        <v>41.25296563457131</v>
+        <v>31.52026952893062</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4622923448666842</v>
+        <v>0.01690113952033673</v>
       </c>
       <c r="L94" t="n">
-        <v>1355.881498072733</v>
+        <v>9.737560836986031</v>
       </c>
       <c r="M94" t="n">
-        <v>1379.028189131795</v>
+        <v>9.393417503348731</v>
       </c>
       <c r="N94" t="n">
-        <v>1362.20536604941</v>
+        <v>7.311845515913642</v>
       </c>
       <c r="O94" t="n">
-        <v>6.556604852543671</v>
+        <v>-0.2417040957597307</v>
       </c>
       <c r="P94" t="n">
-        <v>69.08380162646199</v>
+        <v>8.616761313259317</v>
       </c>
       <c r="Q94" t="n">
-        <v>-30.91619837353801</v>
+        <v>-91.38323868674068</v>
       </c>
       <c r="R94" t="n">
-        <v>-13.29834295070255</v>
+        <v>-222.1416907997849</v>
       </c>
       <c r="S94" t="n">
-        <v>-10.25211357859093</v>
+        <v>-15.23625787022728</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -19969,19 +19973,19 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>Doji, Bullish Harami</t>
+          <t>Bullish Harami</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>Bear Flag / Consolidation</t>
+          <t>Inside Bar</t>
         </is>
       </c>
       <c r="W94" t="n">
-        <v>46.2</v>
+        <v>46.1</v>
       </c>
       <c r="X94" t="n">
-        <v>69.8</v>
+        <v>63.6</v>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
@@ -19990,94 +19994,90 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 41); pattern: Bear Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 32); RSI scarico (35) — zona di interesse long; segnale candlestick: Bullish Harami; in zona Fib Fib 38.2 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IG_IT</t>
+          <t>DXY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Italgas</t>
+          <t>US Dollar Index</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Azioni IT</t>
+          <t>FX/Macro</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>8.789999961853027</v>
+        <v>98.87599945068359</v>
       </c>
       <c r="E95" t="n">
-        <v>2.209297348319761</v>
+        <v>-0.7966276039414133</v>
       </c>
       <c r="F95" t="n">
-        <v>-13.22803689486282</v>
+        <v>-1.860050173018768</v>
       </c>
       <c r="G95" t="n">
-        <v>-10.12269732258366</v>
+        <v>-1.272093914912331</v>
       </c>
       <c r="H95" t="n">
-        <v>26.20243746279096</v>
+        <v>0.7089011441682835</v>
       </c>
       <c r="I95" t="n">
-        <v>35.01204718477037</v>
+        <v>45.18793553057339</v>
       </c>
       <c r="J95" t="n">
-        <v>31.52026952893062</v>
+        <v>32.30282727268204</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01690113952033673</v>
+        <v>0.3287807323430511</v>
       </c>
       <c r="L95" t="n">
-        <v>9.737560836986031</v>
+        <v>99.76011183288868</v>
       </c>
       <c r="M95" t="n">
-        <v>9.393417503348731</v>
+        <v>99.65077276541491</v>
       </c>
       <c r="N95" t="n">
-        <v>7.311845515913642</v>
+        <v>100.8050019990842</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.2417040957597307</v>
+        <v>-0.1364193036195633</v>
       </c>
       <c r="P95" t="n">
-        <v>8.616761313259317</v>
+        <v>9.83656694121162</v>
       </c>
       <c r="Q95" t="n">
-        <v>-91.38323868674068</v>
+        <v>-90.16343305878839</v>
       </c>
       <c r="R95" t="n">
-        <v>-222.1416907997849</v>
+        <v>-52.51075851232633</v>
       </c>
       <c r="S95" t="n">
-        <v>-15.23625787022728</v>
+        <v>-1.153653246721942</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Bullish Harami</t>
-        </is>
-      </c>
+          <t>Bearish</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
       <c r="V95" t="inlineStr">
         <is>
-          <t>Inside Bar</t>
+          <t>Double Top, Double Bottom</t>
         </is>
       </c>
       <c r="W95" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="X95" t="n">
-        <v>63.6</v>
+        <v>56.5</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -20086,90 +20086,94 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); RSI scarico (35) — zona di interesse long; segnale candlestick: Bullish Harami; in zona Fib Fib 38.2 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 32); pattern: Double Bottom; sul supporto dei 20g (97.63); in zona Fib Fib 78.6 — livello strutturale</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DXY</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>US Dollar Index</t>
+          <t>Palladium</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FX/Macro</t>
+          <t>Commodities</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>98.88600158691406</v>
+        <v>1334</v>
       </c>
       <c r="E96" t="n">
-        <v>-0.7865923511931272</v>
+        <v>0.8695652173912993</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.850122494378104</v>
+        <v>7.234726688102899</v>
       </c>
       <c r="G96" t="n">
-        <v>-1.262106759567272</v>
+        <v>-4.090878094421813</v>
       </c>
       <c r="H96" t="n">
-        <v>0.71908869377042</v>
+        <v>28.31858708424202</v>
       </c>
       <c r="I96" t="n">
-        <v>45.24079364825529</v>
+        <v>46.97533807677089</v>
       </c>
       <c r="J96" t="n">
-        <v>32.30282727268204</v>
+        <v>41.25296563457131</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3308510051935452</v>
+        <v>0.4530997267573053</v>
       </c>
       <c r="L96" t="n">
-        <v>99.76106441729158</v>
+        <v>1355.452926644162</v>
       </c>
       <c r="M96" t="n">
-        <v>99.6511650060514</v>
+        <v>1378.851718543559</v>
       </c>
       <c r="N96" t="n">
-        <v>100.8051015228278</v>
+        <v>1362.160589930007</v>
       </c>
       <c r="O96" t="n">
-        <v>-0.1357809906521556</v>
+        <v>6.269425365364178</v>
       </c>
       <c r="P96" t="n">
-        <v>10.14498890763103</v>
+        <v>67.3294156615497</v>
       </c>
       <c r="Q96" t="n">
-        <v>-89.85501109236897</v>
+        <v>-32.67058433845029</v>
       </c>
       <c r="R96" t="n">
-        <v>-52.26141412151684</v>
+        <v>-13.87461762613037</v>
       </c>
       <c r="S96" t="n">
-        <v>-1.143654110110404</v>
+        <v>-10.5538434918493</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>Bearish</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr"/>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Doji</t>
+        </is>
+      </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom</t>
+          <t>Bear Flag / Consolidation</t>
         </is>
       </c>
       <c r="W96" t="n">
-        <v>46</v>
+        <v>45.7</v>
       </c>
       <c r="X96" t="n">
-        <v>56.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -20178,7 +20182,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 32); pattern: Double Bottom; sul supporto dei 20g (97.63); in zona Fib Fib 78.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 41); pattern: Bear Flag / Consolidation; doji — indecisione del mercato; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -20295,52 +20299,52 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>87.31999969482422</v>
+        <v>87.47000122070312</v>
       </c>
       <c r="E98" t="n">
-        <v>17.14670186565414</v>
+        <v>17.34794080396087</v>
       </c>
       <c r="F98" t="n">
-        <v>14.36015874042031</v>
+        <v>14.55661085185835</v>
       </c>
       <c r="G98" t="n">
-        <v>7.24321337021796</v>
+        <v>7.427439729607688</v>
       </c>
       <c r="H98" t="n">
-        <v>-42.85878541892415</v>
+        <v>-42.76062612657771</v>
       </c>
       <c r="I98" t="n">
-        <v>49.73031246011598</v>
+        <v>49.82811995517083</v>
       </c>
       <c r="J98" t="n">
         <v>16.31758573403537</v>
       </c>
       <c r="K98" t="n">
-        <v>0.7740068055336097</v>
+        <v>0.778633035024723</v>
       </c>
       <c r="L98" t="n">
-        <v>82.47012732038912</v>
+        <v>82.48441317999664</v>
       </c>
       <c r="M98" t="n">
-        <v>104.7270855618203</v>
+        <v>104.7329679745998</v>
       </c>
       <c r="N98" t="n">
-        <v>111.4014337734536</v>
+        <v>111.4029263259499</v>
       </c>
       <c r="O98" t="n">
-        <v>3.109409935266193</v>
+        <v>3.118982682216856</v>
       </c>
       <c r="P98" t="n">
-        <v>98.06622175492183</v>
+        <v>98.61295764903288</v>
       </c>
       <c r="Q98" t="n">
-        <v>-1.933778245078167</v>
+        <v>-1.387042350967125</v>
       </c>
       <c r="R98" t="n">
-        <v>25.74698986438266</v>
+        <v>26.05246865416865</v>
       </c>
       <c r="S98" t="n">
-        <v>6.677101477588621</v>
+        <v>6.860355349025871</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -20350,7 +20354,7 @@
       <c r="U98" t="inlineStr"/>
       <c r="V98" t="inlineStr"/>
       <c r="W98" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="X98" t="n">
         <v>66.40000000000001</v>
@@ -20735,52 +20739,52 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.237100005149841</v>
+        <v>1.258700013160706</v>
       </c>
       <c r="E103" t="n">
-        <v>24.71105831469886</v>
+        <v>26.88853778073006</v>
       </c>
       <c r="F103" t="n">
-        <v>12.8822205678687</v>
+        <v>14.85316621365322</v>
       </c>
       <c r="G103" t="n">
-        <v>-6.794064450164261</v>
+        <v>-5.166670588588218</v>
       </c>
       <c r="H103" t="n">
-        <v>-42.91652103638375</v>
+        <v>-41.9198323307259</v>
       </c>
       <c r="I103" t="n">
-        <v>46.07863078627032</v>
+        <v>47.11231503273751</v>
       </c>
       <c r="J103" t="n">
         <v>19.02129507564944</v>
       </c>
       <c r="K103" t="n">
-        <v>0.5282072207917921</v>
+        <v>0.5617954588466221</v>
       </c>
       <c r="L103" t="n">
-        <v>1.230652313892453</v>
+        <v>1.232709457512535</v>
       </c>
       <c r="M103" t="n">
-        <v>1.534953096888722</v>
+        <v>1.535800156026403</v>
       </c>
       <c r="N103" t="n">
-        <v>1.378024606691233</v>
+        <v>1.378239532144077</v>
       </c>
       <c r="O103" t="n">
-        <v>0.02645507698550911</v>
+        <v>0.02783353903520527</v>
       </c>
       <c r="P103" t="n">
-        <v>60.26016242313701</v>
+        <v>65.49432001433952</v>
       </c>
       <c r="Q103" t="n">
-        <v>-39.73983757686299</v>
+        <v>-34.50567998566048</v>
       </c>
       <c r="R103" t="n">
-        <v>-12.70569335788443</v>
+        <v>-10.38950649671268</v>
       </c>
       <c r="S103" t="n">
-        <v>-6.668896470261076</v>
+        <v>-5.039317151278711</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -20798,10 +20802,10 @@
         </is>
       </c>
       <c r="W103" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="X103" t="n">
-        <v>64.40000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
@@ -21575,52 +21579,52 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7.183000087738037</v>
+        <v>7.190999984741211</v>
       </c>
       <c r="E112" t="n">
-        <v>13.62346237318772</v>
+        <v>13.75000782564861</v>
       </c>
       <c r="F112" t="n">
-        <v>11.26438026224366</v>
+        <v>11.38829834262061</v>
       </c>
       <c r="G112" t="n">
-        <v>-16.4350002978948</v>
+        <v>-16.34193174958331</v>
       </c>
       <c r="H112" t="n">
-        <v>-62.42207563419395</v>
+        <v>-62.38022410685893</v>
       </c>
       <c r="I112" t="n">
-        <v>40.56479067451131</v>
+        <v>40.62326381450632</v>
       </c>
       <c r="J112" t="n">
         <v>37.99811787268366</v>
       </c>
       <c r="K112" t="n">
-        <v>0.4135991562785948</v>
+        <v>0.4149576221430091</v>
       </c>
       <c r="L112" t="n">
-        <v>7.75477650078065</v>
+        <v>7.755538395733334</v>
       </c>
       <c r="M112" t="n">
-        <v>11.67405361025379</v>
+        <v>11.67436733170489</v>
       </c>
       <c r="N112" t="n">
-        <v>20.51519862924658</v>
+        <v>20.51527823021179</v>
       </c>
       <c r="O112" t="n">
-        <v>0.2811766275539582</v>
+        <v>0.2816871622914825</v>
       </c>
       <c r="P112" t="n">
-        <v>38.31139752945778</v>
+        <v>38.51717179299332</v>
       </c>
       <c r="Q112" t="n">
-        <v>-61.68860247054222</v>
+        <v>-61.48282820700668</v>
       </c>
       <c r="R112" t="n">
-        <v>-35.53424713759338</v>
+        <v>-35.42465837100379</v>
       </c>
       <c r="S112" t="n">
-        <v>-20.67393001370843</v>
+        <v>-20.58558247343202</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -21637,7 +21641,7 @@
         <v>26</v>
       </c>
       <c r="X112" t="n">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -21667,52 +21671,52 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.196710005402565</v>
+        <v>0.1970800012350082</v>
       </c>
       <c r="E113" t="n">
-        <v>12.50407370716897</v>
+        <v>12.71568489755735</v>
       </c>
       <c r="F113" t="n">
-        <v>18.51213550025581</v>
+        <v>18.73504737573113</v>
       </c>
       <c r="G113" t="n">
-        <v>-17.88764434368324</v>
+        <v>-17.73319755119417</v>
       </c>
       <c r="H113" t="n">
-        <v>-68.96579505299025</v>
+        <v>-68.90742218847792</v>
       </c>
       <c r="I113" t="n">
-        <v>42.38908637148239</v>
+        <v>42.45928163646894</v>
       </c>
       <c r="J113" t="n">
         <v>23.55414755572129</v>
       </c>
       <c r="K113" t="n">
-        <v>0.4557345697244793</v>
+        <v>0.4578801700580207</v>
       </c>
       <c r="L113" t="n">
-        <v>0.2122965137879935</v>
+        <v>0.2123317514863215</v>
       </c>
       <c r="M113" t="n">
-        <v>0.3292928479672604</v>
+        <v>0.3293073576077484</v>
       </c>
       <c r="N113" t="n">
-        <v>0.4973458198122536</v>
+        <v>0.4973495013628252</v>
       </c>
       <c r="O113" t="n">
-        <v>0.01188036957923662</v>
+        <v>0.01190398184888541</v>
       </c>
       <c r="P113" t="n">
-        <v>50.30043407517234</v>
+        <v>50.62122955494052</v>
       </c>
       <c r="Q113" t="n">
-        <v>-49.69956592482766</v>
+        <v>-49.37877044505948</v>
       </c>
       <c r="R113" t="n">
-        <v>-19.92442821411126</v>
+        <v>-19.77313896296495</v>
       </c>
       <c r="S113" t="n">
-        <v>-21.45016337146921</v>
+        <v>-21.30241739315877</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -21943,52 +21947,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.8381999731063843</v>
+        <v>0.8407999873161316</v>
       </c>
       <c r="E116" t="n">
-        <v>10.59345277000279</v>
+        <v>10.93650282718828</v>
       </c>
       <c r="F116" t="n">
-        <v>2.442760926082088</v>
+        <v>2.760528335578005</v>
       </c>
       <c r="G116" t="n">
-        <v>-33.37096261112885</v>
+        <v>-33.16428586387147</v>
       </c>
       <c r="H116" t="n">
-        <v>-78.06844941723337</v>
+        <v>-78.00041989565553</v>
       </c>
       <c r="I116" t="n">
-        <v>32.68678034258198</v>
+        <v>32.84191234220177</v>
       </c>
       <c r="J116" t="n">
         <v>42.24686780573031</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2899233132122236</v>
+        <v>0.2927670166453117</v>
       </c>
       <c r="L116" t="n">
-        <v>1.039619614188397</v>
+        <v>1.039867234589325</v>
       </c>
       <c r="M116" t="n">
-        <v>1.809316526985627</v>
+        <v>1.809418488327186</v>
       </c>
       <c r="N116" t="n">
-        <v>5.07108350270416</v>
+        <v>5.071109373492317</v>
       </c>
       <c r="O116" t="n">
-        <v>0.04123893896404163</v>
+        <v>0.04140486579680047</v>
       </c>
       <c r="P116" t="n">
-        <v>17.9681336587308</v>
+        <v>18.39131787915253</v>
       </c>
       <c r="Q116" t="n">
-        <v>-82.03186634126919</v>
+        <v>-81.60868212084746</v>
       </c>
       <c r="R116" t="n">
-        <v>-48.51445635898155</v>
+        <v>-48.34064737233575</v>
       </c>
       <c r="S116" t="n">
-        <v>-32.56713215308833</v>
+        <v>-32.35796200249023</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -24033,52 +24037,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>183.1399993896484</v>
+        <v>183.1000061035156</v>
       </c>
       <c r="E21" t="n">
-        <v>4.442539500987586</v>
+        <v>4.419731810801819</v>
       </c>
       <c r="F21" t="n">
-        <v>37.80286516212781</v>
+        <v>37.77277239465637</v>
       </c>
       <c r="G21" t="n">
-        <v>56.71073695062761</v>
+        <v>56.6765151674899</v>
       </c>
       <c r="H21" t="n">
-        <v>148.0563386802129</v>
+        <v>148.0021692570232</v>
       </c>
       <c r="I21" t="n">
-        <v>70.94326020845172</v>
+        <v>70.93299633809406</v>
       </c>
       <c r="J21" t="n">
         <v>26.10445601962337</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8863778772581846</v>
+        <v>0.8860702767263391</v>
       </c>
       <c r="L21" t="n">
-        <v>147.6508686568963</v>
+        <v>147.6470597725028</v>
       </c>
       <c r="M21" t="n">
-        <v>118.8014509102924</v>
+        <v>118.7998825461303</v>
       </c>
       <c r="N21" t="n">
-        <v>78.93966992640752</v>
+        <v>78.93911057974832</v>
       </c>
       <c r="O21" t="n">
-        <v>3.76067358938387</v>
+        <v>3.758121311294481</v>
       </c>
       <c r="P21" t="n">
-        <v>78.96228697561743</v>
+        <v>78.90831856803551</v>
       </c>
       <c r="Q21" t="n">
-        <v>-21.03771302438256</v>
+        <v>-21.09168143196449</v>
       </c>
       <c r="R21" t="n">
-        <v>121.849711008996</v>
+        <v>121.8167766604592</v>
       </c>
       <c r="S21" t="n">
-        <v>57.52623088295638</v>
+        <v>57.49183101593596</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -24669,52 +24673,52 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.48199987411499</v>
+        <v>6.482500076293945</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7147297194173285</v>
+        <v>0.7225016614470947</v>
       </c>
       <c r="F28" t="n">
-        <v>16.00894431284545</v>
+        <v>16.01789647696925</v>
       </c>
       <c r="G28" t="n">
-        <v>58.85307374446227</v>
+        <v>58.86533209916202</v>
       </c>
       <c r="H28" t="n">
-        <v>50.8669745918445</v>
+        <v>50.87861667621488</v>
       </c>
       <c r="I28" t="n">
-        <v>68.44323106501353</v>
+        <v>68.44763898638423</v>
       </c>
       <c r="J28" t="n">
         <v>65.50118230776258</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8859664106338683</v>
+        <v>0.8861037438192692</v>
       </c>
       <c r="L28" t="n">
-        <v>5.486418258745403</v>
+        <v>5.486465897048161</v>
       </c>
       <c r="M28" t="n">
-        <v>4.758407073163925</v>
+        <v>4.758426688935648</v>
       </c>
       <c r="N28" t="n">
-        <v>3.976579648131761</v>
+        <v>3.976588126134795</v>
       </c>
       <c r="O28" t="n">
-        <v>0.1091779747085548</v>
+        <v>0.1092098964430515</v>
       </c>
       <c r="P28" t="n">
-        <v>89.76917075747799</v>
+        <v>89.78997350970789</v>
       </c>
       <c r="Q28" t="n">
-        <v>-10.23082924252201</v>
+        <v>-10.21002649029212</v>
       </c>
       <c r="R28" t="n">
-        <v>111.3530799218737</v>
+        <v>111.3662930417925</v>
       </c>
       <c r="S28" t="n">
-        <v>62.61916143653112</v>
+        <v>62.63171041222846</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -25401,52 +25405,52 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>68.18000030517578</v>
+        <v>68.12999725341797</v>
       </c>
       <c r="E36" t="n">
-        <v>18.386554799967</v>
+        <v>18.29973037930708</v>
       </c>
       <c r="F36" t="n">
-        <v>-8.7160288170261</v>
+        <v>-8.782976266649012</v>
       </c>
       <c r="G36" t="n">
-        <v>122.1932588946254</v>
+        <v>122.0303028814982</v>
       </c>
       <c r="H36" t="n">
-        <v>160.5770988707097</v>
+        <v>160.3859922396828</v>
       </c>
       <c r="I36" t="n">
-        <v>60.64063403643365</v>
+        <v>60.61632488552284</v>
       </c>
       <c r="J36" t="n">
         <v>66.73999449958801</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6857824283204349</v>
+        <v>0.6851859116708761</v>
       </c>
       <c r="L36" t="n">
-        <v>56.78443080757321</v>
+        <v>56.7796686121677</v>
       </c>
       <c r="M36" t="n">
-        <v>42.51244292132753</v>
+        <v>42.51048201733703</v>
       </c>
       <c r="N36" t="n">
-        <v>31.48973215415934</v>
+        <v>31.48888464480752</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.09660718927418621</v>
+        <v>-0.09979826722112506</v>
       </c>
       <c r="P36" t="n">
-        <v>37.83862663580447</v>
+        <v>37.78011273879857</v>
       </c>
       <c r="Q36" t="n">
-        <v>-62.16137336419553</v>
+        <v>-62.21988726120143</v>
       </c>
       <c r="R36" t="n">
-        <v>42.56881735783952</v>
+        <v>42.50848527055592</v>
       </c>
       <c r="S36" t="n">
-        <v>135.5908743848817</v>
+        <v>135.4180925920861</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -26321,52 +26325,52 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>93.43000030517578</v>
+        <v>93.15000152587891</v>
       </c>
       <c r="E46" t="n">
-        <v>3.672877782639983</v>
+        <v>3.362182297993543</v>
       </c>
       <c r="F46" t="n">
-        <v>-21.05618799344084</v>
+        <v>-21.29277336133851</v>
       </c>
       <c r="G46" t="n">
-        <v>28.09157825327664</v>
+        <v>27.70770278038808</v>
       </c>
       <c r="H46" t="n">
-        <v>24.35778480069792</v>
+        <v>23.98509906992061</v>
       </c>
       <c r="I46" t="n">
-        <v>55.51659160657612</v>
+        <v>55.4151313962665</v>
       </c>
       <c r="J46" t="n">
         <v>23.79402312962622</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7508586207212857</v>
+        <v>0.7470168868007939</v>
       </c>
       <c r="L46" t="n">
-        <v>81.90838826222918</v>
+        <v>81.88172171181996</v>
       </c>
       <c r="M46" t="n">
-        <v>78.92159210755568</v>
+        <v>78.91061176326953</v>
       </c>
       <c r="N46" t="n">
-        <v>72.45124431983044</v>
+        <v>72.44649857780846</v>
       </c>
       <c r="O46" t="n">
-        <v>2.486590238524141</v>
+        <v>2.468721370557617</v>
       </c>
       <c r="P46" t="n">
-        <v>51.51380305630976</v>
+        <v>51.09825127431162</v>
       </c>
       <c r="Q46" t="n">
-        <v>-48.48619694369025</v>
+        <v>-48.90174872568838</v>
       </c>
       <c r="R46" t="n">
-        <v>70.80850452664829</v>
+        <v>70.32796393289985</v>
       </c>
       <c r="S46" t="n">
-        <v>25.17417077864186</v>
+        <v>24.79903843460851</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -26501,52 +26505,52 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4577.60009765625</v>
+        <v>4575.10009765625</v>
       </c>
       <c r="E48" t="n">
-        <v>13.05228290863722</v>
+        <v>12.99054079459447</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.506153682097144</v>
+        <v>-1.559944885029185</v>
       </c>
       <c r="G48" t="n">
-        <v>72.28453510185359</v>
+        <v>72.19044402168799</v>
       </c>
       <c r="H48" t="n">
-        <v>158.5046290621915</v>
+        <v>158.3634499380067</v>
       </c>
       <c r="I48" t="n">
-        <v>66.14482847211085</v>
+        <v>66.11604509043721</v>
       </c>
       <c r="J48" t="n">
         <v>81.39230805339344</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7385290948091101</v>
+        <v>0.7377224387018722</v>
       </c>
       <c r="L48" t="n">
-        <v>3933.89400862615</v>
+        <v>3933.655913388055</v>
       </c>
       <c r="M48" t="n">
-        <v>3135.615635547652</v>
+        <v>3135.517596331966</v>
       </c>
       <c r="N48" t="n">
-        <v>2393.445682627743</v>
+        <v>2393.403309746387</v>
       </c>
       <c r="O48" t="n">
-        <v>-31.38232209452315</v>
+        <v>-31.54186625406783</v>
       </c>
       <c r="P48" t="n">
-        <v>56.56892001822514</v>
+        <v>56.46126813497948</v>
       </c>
       <c r="Q48" t="n">
-        <v>-43.43107998177487</v>
+        <v>-43.53873186502052</v>
       </c>
       <c r="R48" t="n">
-        <v>37.65202223709861</v>
+        <v>37.59439117018062</v>
       </c>
       <c r="S48" t="n">
-        <v>74.10619894527014</v>
+        <v>74.01111298579848</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -26685,52 +26689,52 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1842.800048828125</v>
+        <v>1841.300048828125</v>
       </c>
       <c r="E50" t="n">
-        <v>11.66454549502642</v>
+        <v>11.57365293272752</v>
       </c>
       <c r="F50" t="n">
-        <v>-5.497433393429485</v>
+        <v>-5.574356470352559</v>
       </c>
       <c r="G50" t="n">
-        <v>94.08110045583203</v>
+        <v>93.92312257273565</v>
       </c>
       <c r="H50" t="n">
-        <v>72.14386257152032</v>
+        <v>72.00374113294021</v>
       </c>
       <c r="I50" t="n">
-        <v>58.90908966032697</v>
+        <v>58.87752010377861</v>
       </c>
       <c r="J50" t="n">
         <v>70.1998447981956</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6649609978678361</v>
+        <v>0.6641487743868981</v>
       </c>
       <c r="L50" t="n">
-        <v>1613.870601833272</v>
+        <v>1613.727744690415</v>
       </c>
       <c r="M50" t="n">
-        <v>1330.048258485632</v>
+        <v>1329.98943495622</v>
       </c>
       <c r="N50" t="n">
-        <v>1140.846539844372</v>
+        <v>1140.821116115558</v>
       </c>
       <c r="O50" t="n">
-        <v>-10.57483440966459</v>
+        <v>-10.67056090539097</v>
       </c>
       <c r="P50" t="n">
-        <v>35.94722212971733</v>
+        <v>35.85205653864592</v>
       </c>
       <c r="Q50" t="n">
-        <v>-64.05277787028267</v>
+        <v>-64.14794346135407</v>
       </c>
       <c r="R50" t="n">
-        <v>34.17195433569696</v>
+        <v>34.09334805036499</v>
       </c>
       <c r="S50" t="n">
-        <v>106.1297593767478</v>
+        <v>105.9619741418484</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -27325,52 +27329,52 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>159.1230010986328</v>
+        <v>159.0240020751953</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.6617416127051134</v>
+        <v>-0.7235453148878634</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.449197830332948</v>
+        <v>-0.5111337674958527</v>
       </c>
       <c r="G57" t="n">
-        <v>5.258182848088677</v>
+        <v>5.192696040783495</v>
       </c>
       <c r="H57" t="n">
-        <v>43.95711387955477</v>
+        <v>43.86755037463994</v>
       </c>
       <c r="I57" t="n">
-        <v>58.67002895239581</v>
+        <v>58.51899579654904</v>
       </c>
       <c r="J57" t="n">
         <v>26.49181088905198</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7414205964843912</v>
+        <v>0.7377474242769043</v>
       </c>
       <c r="L57" t="n">
-        <v>154.8563315677536</v>
+        <v>154.846903089331</v>
       </c>
       <c r="M57" t="n">
-        <v>146.5128026895881</v>
+        <v>146.5089203749436</v>
       </c>
       <c r="N57" t="n">
-        <v>132.467636461557</v>
+        <v>132.4662016931014</v>
       </c>
       <c r="O57" t="n">
-        <v>0.3617370766029997</v>
+        <v>0.355419190206995</v>
       </c>
       <c r="P57" t="n">
-        <v>77.18472285549601</v>
+        <v>76.71958923711777</v>
       </c>
       <c r="Q57" t="n">
-        <v>-22.81527714450399</v>
+        <v>-23.28041076288222</v>
       </c>
       <c r="R57" t="n">
-        <v>68.15075083268809</v>
+        <v>67.73678165967902</v>
       </c>
       <c r="S57" t="n">
-        <v>1.355461032281235</v>
+        <v>1.29240231925436</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -27384,10 +27388,10 @@
         </is>
       </c>
       <c r="W57" t="n">
-        <v>73.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="X57" t="n">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
@@ -27881,52 +27885,52 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>86.52999877929688</v>
+        <v>86.20999908447266</v>
       </c>
       <c r="E63" t="n">
-        <v>2.196764675298835</v>
+        <v>1.818827151093738</v>
       </c>
       <c r="F63" t="n">
-        <v>-14.64785843010115</v>
+        <v>-14.96350224889542</v>
       </c>
       <c r="G63" t="n">
-        <v>27.24999820484835</v>
+        <v>26.77941041834213</v>
       </c>
       <c r="H63" t="n">
-        <v>17.77595935974148</v>
+        <v>17.34040785639666</v>
       </c>
       <c r="I63" t="n">
-        <v>55.64167164242384</v>
+        <v>55.5079871443588</v>
       </c>
       <c r="J63" t="n">
         <v>21.8831417623618</v>
       </c>
       <c r="K63" t="n">
-        <v>0.7631941174765847</v>
+        <v>0.7580650661978647</v>
       </c>
       <c r="L63" t="n">
-        <v>76.25727749969627</v>
+        <v>76.22680133828445</v>
       </c>
       <c r="M63" t="n">
-        <v>73.75935144564741</v>
+        <v>73.74680243800725</v>
       </c>
       <c r="N63" t="n">
-        <v>67.84379129842638</v>
+        <v>67.83836757478529</v>
       </c>
       <c r="O63" t="n">
-        <v>2.396602733259948</v>
+        <v>2.376181100313891</v>
       </c>
       <c r="P63" t="n">
-        <v>48.91472460637502</v>
+        <v>48.41860107785004</v>
       </c>
       <c r="Q63" t="n">
-        <v>-51.08527539362498</v>
+        <v>-51.58139892214996</v>
       </c>
       <c r="R63" t="n">
-        <v>65.14032944252639</v>
+        <v>64.5538953009824</v>
       </c>
       <c r="S63" t="n">
-        <v>20.6497452684351</v>
+        <v>20.2035661142554</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -28349,52 +28353,52 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.167951464653015</v>
+        <v>1.168360829353333</v>
       </c>
       <c r="E68" t="n">
-        <v>1.353656298562655</v>
+        <v>1.389180556541181</v>
       </c>
       <c r="F68" t="n">
-        <v>1.915451307910621</v>
+        <v>1.951172473939367</v>
       </c>
       <c r="G68" t="n">
-        <v>10.56996054799888</v>
+        <v>10.6087151025619</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.868718550497639</v>
+        <v>-1.834323728591003</v>
       </c>
       <c r="I68" t="n">
-        <v>56.3576844832204</v>
+        <v>56.42821013987012</v>
       </c>
       <c r="J68" t="n">
         <v>39.40466120531415</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6317369222655904</v>
+        <v>0.6339653370139384</v>
       </c>
       <c r="L68" t="n">
-        <v>1.145993483043537</v>
+        <v>1.146032470157853</v>
       </c>
       <c r="M68" t="n">
-        <v>1.12529089131203</v>
+        <v>1.12530694482969</v>
       </c>
       <c r="N68" t="n">
-        <v>1.120960508425972</v>
+        <v>1.120966441247716</v>
       </c>
       <c r="O68" t="n">
-        <v>-0.001903765157464737</v>
+        <v>-0.001877640458640945</v>
       </c>
       <c r="P68" t="n">
-        <v>50.71979482731241</v>
+        <v>51.30614886289322</v>
       </c>
       <c r="Q68" t="n">
-        <v>-49.28020517268758</v>
+        <v>-48.69385113710678</v>
       </c>
       <c r="R68" t="n">
-        <v>28.98161927167009</v>
+        <v>29.16365765705177</v>
       </c>
       <c r="S68" t="n">
-        <v>12.2366330546287</v>
+        <v>12.27597177464024</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -29733,52 +29737,52 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.36286199092865</v>
+        <v>1.36297345161438</v>
       </c>
       <c r="E83" t="n">
-        <v>1.245658707863551</v>
+        <v>1.253939011094451</v>
       </c>
       <c r="F83" t="n">
-        <v>3.460307221280146</v>
+        <v>3.468768647943654</v>
       </c>
       <c r="G83" t="n">
-        <v>7.339011879617474</v>
+        <v>7.347790523346132</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.546847061828494</v>
+        <v>-1.538795141669447</v>
       </c>
       <c r="I83" t="n">
-        <v>56.79589157581602</v>
+        <v>56.81119253470492</v>
       </c>
       <c r="J83" t="n">
         <v>19.49328859849469</v>
       </c>
       <c r="K83" t="n">
-        <v>0.7249100110316649</v>
+        <v>0.7256482713829524</v>
       </c>
       <c r="L83" t="n">
-        <v>1.330828613461921</v>
+        <v>1.330839228765324</v>
       </c>
       <c r="M83" t="n">
-        <v>1.310141555366721</v>
+        <v>1.310145926374005</v>
       </c>
       <c r="N83" t="n">
-        <v>1.337785487737853</v>
+        <v>1.337787103110109</v>
       </c>
       <c r="O83" t="n">
-        <v>-0.0007813957286861087</v>
+        <v>-0.0007742825681153268</v>
       </c>
       <c r="P83" t="n">
-        <v>73.87676618293216</v>
+        <v>74.0102380796035</v>
       </c>
       <c r="Q83" t="n">
-        <v>-26.12323381706785</v>
+        <v>-25.9897619203965</v>
       </c>
       <c r="R83" t="n">
-        <v>53.02215003996975</v>
+        <v>53.08598827258721</v>
       </c>
       <c r="S83" t="n">
-        <v>8.602380158273814</v>
+        <v>8.611262125666631</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -30193,52 +30197,52 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>72825.9609375</v>
+        <v>72704.1484375</v>
       </c>
       <c r="E88" t="n">
-        <v>15.93952831408383</v>
+        <v>15.74560181299887</v>
       </c>
       <c r="F88" t="n">
-        <v>6.730800937591885</v>
+        <v>6.552277434134535</v>
       </c>
       <c r="G88" t="n">
-        <v>-24.49282040818343</v>
+        <v>-24.61911765432512</v>
       </c>
       <c r="H88" t="n">
-        <v>107.8316883404117</v>
+        <v>107.4840582204646</v>
       </c>
       <c r="I88" t="n">
-        <v>48.44182332093317</v>
+        <v>48.38333943570272</v>
       </c>
       <c r="J88" t="n">
         <v>29.75698791974825</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2918242801352876</v>
+        <v>0.2902920248438608</v>
       </c>
       <c r="L88" t="n">
-        <v>77671.55582054159</v>
+        <v>77659.95463006539</v>
       </c>
       <c r="M88" t="n">
-        <v>66596.00966495494</v>
+        <v>66591.13716495493</v>
       </c>
       <c r="N88" t="n">
-        <v>50188.58431582878</v>
+        <v>50186.09834644102</v>
       </c>
       <c r="O88" t="n">
-        <v>-5140.234958566933</v>
+        <v>-5148.008747740717</v>
       </c>
       <c r="P88" t="n">
-        <v>22.02794477152049</v>
+        <v>21.84998719988349</v>
       </c>
       <c r="Q88" t="n">
-        <v>-77.9720552284795</v>
+        <v>-78.15001280011651</v>
       </c>
       <c r="R88" t="n">
-        <v>-54.20960060675701</v>
+        <v>-54.31269435333853</v>
       </c>
       <c r="S88" t="n">
-        <v>-22.05225079350691</v>
+        <v>-22.18263026365719</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -30463,52 +30467,52 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1338.5</v>
+        <v>1334</v>
       </c>
       <c r="E91" t="n">
-        <v>4.931014864998717</v>
+        <v>4.578239693618436</v>
       </c>
       <c r="F91" t="n">
-        <v>-9.019844723769443</v>
+        <v>-9.325717490854268</v>
       </c>
       <c r="G91" t="n">
-        <v>35.17471051294494</v>
+        <v>34.72025687281923</v>
       </c>
       <c r="H91" t="n">
-        <v>-51.80744411813052</v>
+        <v>-51.96946615882414</v>
       </c>
       <c r="I91" t="n">
-        <v>50.73680494312109</v>
+        <v>50.59766259518243</v>
       </c>
       <c r="J91" t="n">
         <v>56.77545406727184</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5506883788017355</v>
+        <v>0.5466007245716895</v>
       </c>
       <c r="L91" t="n">
-        <v>1325.77244623414</v>
+        <v>1325.343874805569</v>
       </c>
       <c r="M91" t="n">
-        <v>1360.495810028874</v>
+        <v>1360.319339440638</v>
       </c>
       <c r="N91" t="n">
-        <v>1348.537751557063</v>
+        <v>1348.461480370622</v>
       </c>
       <c r="O91" t="n">
-        <v>-1.392265198105918</v>
+        <v>-1.679444685285404</v>
       </c>
       <c r="P91" t="n">
-        <v>23.57753681633774</v>
+        <v>23.16389581955989</v>
       </c>
       <c r="Q91" t="n">
-        <v>-76.42246318366226</v>
+        <v>-76.83610418044012</v>
       </c>
       <c r="R91" t="n">
-        <v>7.586793083354031</v>
+        <v>7.154765683689224</v>
       </c>
       <c r="S91" t="n">
-        <v>48.24454134538543</v>
+        <v>47.74614729528888</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -30525,7 +30529,7 @@
         <v>45.4</v>
       </c>
       <c r="X91" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -30831,52 +30835,52 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.237100005149841</v>
+        <v>1.258700013160706</v>
       </c>
       <c r="E95" t="n">
-        <v>16.64867814125515</v>
+        <v>18.6853868728202</v>
       </c>
       <c r="F95" t="n">
-        <v>-7.696941725125006</v>
+        <v>-6.085312277331834</v>
       </c>
       <c r="G95" t="n">
-        <v>-36.36712925045263</v>
+        <v>-35.25608688344688</v>
       </c>
       <c r="H95" t="n">
-        <v>75.13385591700406</v>
+        <v>78.19172728959583</v>
       </c>
       <c r="I95" t="n">
-        <v>44.63754180982547</v>
+        <v>45.04939111142782</v>
       </c>
       <c r="J95" t="n">
         <v>35.50075396679262</v>
       </c>
       <c r="K95" t="n">
-        <v>0.21835230083568</v>
+        <v>0.2256887070949296</v>
       </c>
       <c r="L95" t="n">
-        <v>1.561036153886141</v>
+        <v>1.563093297506223</v>
       </c>
       <c r="M95" t="n">
-        <v>1.321659147469955</v>
+        <v>1.32252314779039</v>
       </c>
       <c r="N95" t="n">
-        <v>1.026359342891489</v>
+        <v>1.026800159381506</v>
       </c>
       <c r="O95" t="n">
-        <v>-0.1746160612609043</v>
+        <v>-0.1732375992112081</v>
       </c>
       <c r="P95" t="n">
-        <v>9.342518464636683</v>
+        <v>10.15400339889986</v>
       </c>
       <c r="Q95" t="n">
-        <v>-90.65748153536332</v>
+        <v>-89.84599660110014</v>
       </c>
       <c r="R95" t="n">
-        <v>-58.51333480481743</v>
+        <v>-58.04978204248278</v>
       </c>
       <c r="S95" t="n">
-        <v>-40.52769674655452</v>
+        <v>-39.48929870165</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -30906,7 +30910,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>trend molto direzionale (ADX 36); morning star — inversione rialzista a 3 candele</t>
+          <t>trend molto direzionale (ADX 36); morning star — inversione rialzista a 3 candele; in zona Fib Fib 61.8 — livello strutturale</t>
         </is>
       </c>
     </row>
@@ -31019,52 +31023,52 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>98.88600158691406</v>
+        <v>98.87599945068359</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.9158331031009381</v>
+        <v>-0.9258552833861344</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.074427278306589</v>
+        <v>-1.084433417084185</v>
       </c>
       <c r="G97" t="n">
-        <v>-6.481933436092779</v>
+        <v>-6.491392615620429</v>
       </c>
       <c r="H97" t="n">
-        <v>6.973170678563823</v>
+        <v>6.962350540132056</v>
       </c>
       <c r="I97" t="n">
-        <v>46.2774706778711</v>
+        <v>46.25682562819426</v>
       </c>
       <c r="J97" t="n">
         <v>27.6570566169491</v>
       </c>
       <c r="K97" t="n">
-        <v>0.4107315899119435</v>
+        <v>0.4099891361285347</v>
       </c>
       <c r="L97" t="n">
-        <v>100.039549713905</v>
+        <v>100.0385971295021</v>
       </c>
       <c r="M97" t="n">
-        <v>100.7351153372828</v>
+        <v>100.7347230966463</v>
       </c>
       <c r="N97" t="n">
-        <v>99.83354045278961</v>
+        <v>99.83337092505688</v>
       </c>
       <c r="O97" t="n">
-        <v>0.1388646085982932</v>
+        <v>0.1382262956308855</v>
       </c>
       <c r="P97" t="n">
-        <v>53.37597656250001</v>
+        <v>53.2159423828125</v>
       </c>
       <c r="Q97" t="n">
-        <v>-46.6240234375</v>
+        <v>-46.7840576171875</v>
       </c>
       <c r="R97" t="n">
-        <v>-20.57010581927006</v>
+        <v>-20.63426837188837</v>
       </c>
       <c r="S97" t="n">
-        <v>-8.852425537804109</v>
+        <v>-8.861644946438474</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -31391,52 +31395,52 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>2326.2900390625</v>
+        <v>2316.320068359375</v>
       </c>
       <c r="E101" t="n">
-        <v>25.04609922050946</v>
+        <v>24.5101789677318</v>
       </c>
       <c r="F101" t="n">
-        <v>10.52790983756309</v>
+        <v>10.05421137157032</v>
       </c>
       <c r="G101" t="n">
-        <v>-37.22409536761997</v>
+        <v>-37.49313917537286</v>
       </c>
       <c r="H101" t="n">
-        <v>2.274844961335987</v>
+        <v>1.836517327718101</v>
       </c>
       <c r="I101" t="n">
-        <v>48.03920165784557</v>
+        <v>47.94453959354863</v>
       </c>
       <c r="J101" t="n">
         <v>13.49900468124963</v>
       </c>
       <c r="K101" t="n">
-        <v>0.4072759197533346</v>
+        <v>0.4044717100236812</v>
       </c>
       <c r="L101" t="n">
-        <v>2491.056406105295</v>
+        <v>2490.10688508595</v>
       </c>
       <c r="M101" t="n">
-        <v>2417.498992252722</v>
+        <v>2417.100193424597</v>
       </c>
       <c r="N101" t="n">
-        <v>1999.753603746323</v>
+        <v>1999.550134956464</v>
       </c>
       <c r="O101" t="n">
-        <v>-137.3695707662439</v>
+        <v>-138.005831004848</v>
       </c>
       <c r="P101" t="n">
-        <v>23.78097701868842</v>
+        <v>23.49175991162791</v>
       </c>
       <c r="Q101" t="n">
-        <v>-76.21902298131158</v>
+        <v>-76.50824008837209</v>
       </c>
       <c r="R101" t="n">
-        <v>-51.84562523849643</v>
+        <v>-52.15516611549119</v>
       </c>
       <c r="S101" t="n">
-        <v>-30.19451210801426</v>
+        <v>-30.49368317332171</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -31449,7 +31453,7 @@
         <v>40.1</v>
       </c>
       <c r="X101" t="n">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
@@ -31663,52 +31667,52 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>87.31999969482422</v>
+        <v>87.47000122070312</v>
       </c>
       <c r="E104" t="n">
-        <v>19.96205934393207</v>
+        <v>20.16813460746913</v>
       </c>
       <c r="F104" t="n">
-        <v>5.070050023271966</v>
+        <v>5.250543242268146</v>
       </c>
       <c r="G104" t="n">
-        <v>-63.27137855924231</v>
+        <v>-63.20828477455613</v>
       </c>
       <c r="H104" t="n">
-        <v>145.5816381640481</v>
+        <v>146.0035073873784</v>
       </c>
       <c r="I104" t="n">
-        <v>43.69431848254091</v>
+        <v>43.72769903485793</v>
       </c>
       <c r="J104" t="n">
         <v>25.06630027881427</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2675380487813038</v>
+        <v>0.2682267311507446</v>
       </c>
       <c r="L104" t="n">
-        <v>114.6673336221705</v>
+        <v>114.681619481778</v>
       </c>
       <c r="M104" t="n">
-        <v>113.9044149705152</v>
+        <v>113.9121073564577</v>
       </c>
       <c r="N104" t="n">
-        <v>92.78821311895358</v>
+        <v>92.79216052752935</v>
       </c>
       <c r="O104" t="n">
-        <v>-10.79409347010607</v>
+        <v>-10.7845207231554</v>
       </c>
       <c r="P104" t="n">
-        <v>13.95537009226337</v>
+        <v>14.03317365814472</v>
       </c>
       <c r="Q104" t="n">
-        <v>-86.04462990773663</v>
+        <v>-85.96682634185528</v>
       </c>
       <c r="R104" t="n">
-        <v>-80.10445174266141</v>
+        <v>-80.03936781886533</v>
       </c>
       <c r="S104" t="n">
-        <v>-62.30323434705113</v>
+        <v>-62.23847744842075</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -31855,52 +31859,52 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.196710005402565</v>
+        <v>0.1970800012350082</v>
       </c>
       <c r="E106" t="n">
-        <v>17.11438728949484</v>
+        <v>17.33467011205681</v>
       </c>
       <c r="F106" t="n">
-        <v>-18.56782722912113</v>
+        <v>-18.41465980639465</v>
       </c>
       <c r="G106" t="n">
-        <v>-81.76824925606196</v>
+        <v>-81.73395678690363</v>
       </c>
       <c r="H106" t="n">
-        <v>-85.78142454153254</v>
+        <v>-85.7546805350335</v>
       </c>
       <c r="I106" t="n">
-        <v>39.10262589122793</v>
+        <v>39.12251433661381</v>
       </c>
       <c r="J106" t="n">
         <v>31.07283787478976</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2160397173775746</v>
+        <v>0.216361211799816</v>
       </c>
       <c r="L106" t="n">
-        <v>0.3873402019057559</v>
+        <v>0.3873754396040838</v>
       </c>
       <c r="M106" t="n">
-        <v>0.4781447491439705</v>
+        <v>0.4781595489772683</v>
       </c>
       <c r="N106" t="n">
-        <v>0.4612707697807179</v>
+        <v>0.4612783207160739</v>
       </c>
       <c r="O106" t="n">
-        <v>-0.0415087889485059</v>
+        <v>-0.04148517667885708</v>
       </c>
       <c r="P106" t="n">
-        <v>6.609370373991955</v>
+        <v>6.651522219777653</v>
       </c>
       <c r="Q106" t="n">
-        <v>-93.39062962600805</v>
+        <v>-93.34847778022235</v>
       </c>
       <c r="R106" t="n">
-        <v>-86.0417171174137</v>
+        <v>-86.01240976422498</v>
       </c>
       <c r="S106" t="n">
-        <v>-76.68663660456167</v>
+        <v>-76.64278602726698</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -31943,52 +31947,52 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.64200019836426</v>
+        <v>10.57199954986572</v>
       </c>
       <c r="E107" t="n">
-        <v>30.3959761329454</v>
+        <v>29.53826116200333</v>
       </c>
       <c r="F107" t="n">
-        <v>21.24119247846814</v>
+        <v>20.4436955850239</v>
       </c>
       <c r="G107" t="n">
-        <v>-44.05619654693863</v>
+        <v>-44.42418211809007</v>
       </c>
       <c r="H107" t="n">
-        <v>-45.41790405106862</v>
+        <v>-45.77693262103818</v>
       </c>
       <c r="I107" t="n">
-        <v>46.78163981274054</v>
+        <v>46.65444614006415</v>
       </c>
       <c r="J107" t="n">
         <v>20.11319030263622</v>
       </c>
       <c r="K107" t="n">
-        <v>0.3576826767371864</v>
+        <v>0.3544808600061304</v>
       </c>
       <c r="L107" t="n">
-        <v>11.93674067514333</v>
+        <v>11.9300739467149</v>
       </c>
       <c r="M107" t="n">
-        <v>12.53784753571978</v>
+        <v>12.53504750977984</v>
       </c>
       <c r="N107" t="n">
-        <v>10.85793737266431</v>
+        <v>10.85650878800107</v>
       </c>
       <c r="O107" t="n">
-        <v>-0.7063420414336788</v>
+        <v>-0.7108093192865765</v>
       </c>
       <c r="P107" t="n">
-        <v>17.47511965501729</v>
+        <v>17.13716212966789</v>
       </c>
       <c r="Q107" t="n">
-        <v>-82.52488034498271</v>
+        <v>-82.86283787033211</v>
       </c>
       <c r="R107" t="n">
-        <v>-64.36387582868655</v>
+        <v>-64.70273269300662</v>
       </c>
       <c r="S107" t="n">
-        <v>-46.79363210291045</v>
+        <v>-47.14361144773515</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -32687,52 +32691,52 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.8381999731063843</v>
+        <v>0.8407999873161316</v>
       </c>
       <c r="E115" t="n">
-        <v>10.57288715633162</v>
+        <v>10.91587342099805</v>
       </c>
       <c r="F115" t="n">
-        <v>-33.03079714458514</v>
+        <v>-32.82306523737184</v>
       </c>
       <c r="G115" t="n">
-        <v>-90.65267176100214</v>
+        <v>-90.62367726443289</v>
       </c>
       <c r="H115" t="n">
-        <v>-94.88970851589295</v>
+        <v>-94.87385689229365</v>
       </c>
       <c r="I115" t="n">
-        <v>34.26037136217104</v>
+        <v>34.27957875094344</v>
       </c>
       <c r="J115" t="n">
         <v>37.36065781323977</v>
       </c>
       <c r="K115" t="n">
-        <v>0.2050252961732513</v>
+        <v>0.2053854909277746</v>
       </c>
       <c r="L115" t="n">
-        <v>2.586021507372346</v>
+        <v>2.586269127773274</v>
       </c>
       <c r="M115" t="n">
-        <v>4.18254281934867</v>
+        <v>4.182683360657304</v>
       </c>
       <c r="N115" t="n">
-        <v>6.266764855147029</v>
+        <v>6.266837077763967</v>
       </c>
       <c r="O115" t="n">
-        <v>-0.01968490563913328</v>
+        <v>-0.01951897880637432</v>
       </c>
       <c r="P115" t="n">
-        <v>2.66240839256353</v>
+        <v>2.725113247806178</v>
       </c>
       <c r="Q115" t="n">
-        <v>-97.33759160743647</v>
+        <v>-97.27488675219382</v>
       </c>
       <c r="R115" t="n">
-        <v>-63.17882202541978</v>
+        <v>-63.1545053173805</v>
       </c>
       <c r="S115" t="n">
-        <v>-82.21503611864811</v>
+        <v>-82.15986890283448</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -32779,52 +32783,52 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>7.183000087738037</v>
+        <v>7.190999984741211</v>
       </c>
       <c r="E116" t="n">
-        <v>12.61764363964222</v>
+        <v>12.74306888520156</v>
       </c>
       <c r="F116" t="n">
-        <v>-19.37646594637088</v>
+        <v>-19.28667338607815</v>
       </c>
       <c r="G116" t="n">
-        <v>-83.99968547115512</v>
+        <v>-83.98186549806788</v>
       </c>
       <c r="H116" t="n">
-        <v>-39.9191029251055</v>
+        <v>-39.85218924243995</v>
       </c>
       <c r="I116" t="n">
-        <v>39.55794916951663</v>
+        <v>39.56748941811238</v>
       </c>
       <c r="J116" t="n">
         <v>17.72278053337836</v>
       </c>
       <c r="K116" t="n">
-        <v>0.2248636073933953</v>
+        <v>0.2250827346426703</v>
       </c>
       <c r="L116" t="n">
-        <v>14.81951781605754</v>
+        <v>14.82027971101022</v>
       </c>
       <c r="M116" t="n">
-        <v>18.79423632485402</v>
+        <v>18.79466875171905</v>
       </c>
       <c r="N116" t="n">
-        <v>20.47869974286875</v>
+        <v>20.47892196222995</v>
       </c>
       <c r="O116" t="n">
-        <v>-0.9303101702011629</v>
+        <v>-0.9297996354636382</v>
       </c>
       <c r="P116" t="n">
-        <v>4.929179915990098</v>
+        <v>4.95565502346346</v>
       </c>
       <c r="Q116" t="n">
-        <v>-95.0708200840099</v>
+        <v>-95.04434497653654</v>
       </c>
       <c r="R116" t="n">
-        <v>-66.30641949538693</v>
+        <v>-66.29036335379531</v>
       </c>
       <c r="S116" t="n">
-        <v>-67.88829897447835</v>
+        <v>-67.8525353245183</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -33200,7 +33204,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20/08/2026 20:28:23</t>
+          <t>20/08/2026 21:28:12</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -33237,16 +33241,16 @@
         <v>0.03000000000000025</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>16.01000022888184</v>
       </c>
       <c r="N2" t="n">
-        <v>98.88600158691406</v>
+        <v>98.87599945068359</v>
       </c>
       <c r="O2" t="n">
-        <v>4577.60009765625</v>
+        <v>4575.10009765625</v>
       </c>
       <c r="P2" t="n">
-        <v>86.52999877929688</v>
+        <v>86.20999908447266</v>
       </c>
       <c r="Q2" t="n">
         <v>2.624862817389007</v>
@@ -33263,10 +33267,10 @@
         <v>3.801336709606194</v>
       </c>
       <c r="U2" t="n">
-        <v>2.860031810887501</v>
+        <v>2.827293146246747</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.724799286861746</v>
+        <v>-1.723132582048106</v>
       </c>
       <c r="W2" t="n">
         <v>-1.30266571520422</v>
@@ -33287,10 +33291,10 @@
         <v>0.2931891435008565</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5990713457186281</v>
+        <v>0.5987441702702827</v>
       </c>
       <c r="AD2" t="n">
-        <v>-1.746380438511852</v>
+        <v>-1.800040444555084</v>
       </c>
       <c r="AE2" t="n">
         <v>-2.582228896070116</v>
@@ -33314,7 +33318,7 @@
         <v>95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.714726764050075</v>
+        <v>2.708992535807676</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -33413,10 +33417,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.15812680157038</v>
+        <v>74.15561924199463</v>
       </c>
       <c r="C2" t="n">
-        <v>0.07322162378695296</v>
+        <v>0.07312132140392316</v>
       </c>
       <c r="D2" t="n">
         <v>64.65517241379311</v>
@@ -33425,7 +33429,7 @@
         <v>38.06261383311766</v>
       </c>
       <c r="F2" t="n">
-        <v>13.14249274926803</v>
+        <v>13.14249274926798</v>
       </c>
     </row>
   </sheetData>
@@ -33682,43 +33686,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLATINUM</t>
+          <t>EMERGING</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PALLADIUM</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="D12" t="n">
         <v>0.912</v>
       </c>
       <c r="E12" t="n">
-        <v>0.881</v>
+        <v>0.914</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EMERGING</t>
+          <t>PLATINUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>PALLADIUM</t>
         </is>
       </c>
       <c r="C13" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.91</v>
       </c>
-      <c r="D13" t="n">
-        <v>0.912</v>
-      </c>
       <c r="E13" t="n">
-        <v>0.914</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="14">
@@ -33775,7 +33779,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.892</v>
+        <v>0.891</v>
       </c>
       <c r="D16" t="n">
         <v>0.903</v>
@@ -33829,43 +33833,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ASIA_EX_JP</t>
+          <t>FTSEMIB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>UCG</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.908</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="D19" t="n">
         <v>0.893</v>
       </c>
       <c r="E19" t="n">
-        <v>0.87</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FTSEMIB</t>
+          <t>ASIA_EX_JP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UCG</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.908</v>
       </c>
       <c r="D20" t="n">
         <v>0.893</v>
       </c>
       <c r="E20" t="n">
-        <v>0.864</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="21">
@@ -33942,13 +33946,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.849</v>
+        <v>-0.843</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.724</v>
+        <v>-0.72</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.638</v>
+        <v>-0.635</v>
       </c>
     </row>
     <row r="3">
@@ -33975,85 +33979,85 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.792</v>
+        <v>-0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.704</v>
+        <v>-0.698</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.624</v>
+        <v>-0.601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.5</v>
+        <v>-0.786</v>
       </c>
       <c r="D5" t="n">
         <v>-0.698</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.601</v>
+        <v>-0.619</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.823</v>
+        <v>-0.52</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.694</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.612</v>
+        <v>-0.656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.52</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.6870000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.656</v>
+        <v>-0.608</v>
       </c>
     </row>
     <row r="8">
@@ -34068,13 +34072,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.869</v>
+        <v>-0.863</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6889999999999999</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.632</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="9">
@@ -34164,43 +34168,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ENI</t>
+          <t>REY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.831</v>
+        <v>-0.739</v>
       </c>
       <c r="D13" t="n">
         <v>-0.66</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.519</v>
+        <v>-0.535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REY</t>
+          <t>ENI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.739</v>
+        <v>-0.831</v>
       </c>
       <c r="D14" t="n">
         <v>-0.66</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.535</v>
+        <v>-0.519</v>
       </c>
     </row>
     <row r="15">
@@ -34227,64 +34231,64 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>EMERGING</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WTI</t>
+          <t>KIE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.842</v>
+        <v>-0.529</v>
       </c>
       <c r="D16" t="n">
         <v>-0.653</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.614</v>
+        <v>-0.607</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EMERGING</t>
+          <t>ICLN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KIE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.529</v>
+        <v>-0.504</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.653</v>
+        <v>-0.65</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.607</v>
+        <v>-0.581</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>WTI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.504</v>
+        <v>-0.833</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.65</v>
+        <v>-0.649</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.581</v>
+        <v>-0.612</v>
       </c>
     </row>
     <row r="19">
@@ -34341,13 +34345,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.649</v>
+        <v>-0.646</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.634</v>
+        <v>-0.633</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.538</v>
+        <v>-0.537</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sarada_dati.xlsx
+++ b/docs/sarada_dati.xlsx
@@ -953,7 +953,7 @@
         <v>77.57073350421426</v>
       </c>
       <c r="J6" t="n">
-        <v>50.04189554231717</v>
+        <v>50.54184892520264</v>
       </c>
       <c r="K6" t="n">
         <v>1.046235870325406</v>
@@ -977,7 +977,7 @@
         <v>17.14677425262816</v>
       </c>
       <c r="R6" t="n">
-        <v>60.08440736149066</v>
+        <v>69.81403616291877</v>
       </c>
       <c r="S6" t="n">
         <v>12.79439214756133</v>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 50); RSI ipercomprato (78) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (87.35)</t>
+          <t>EMA e SMA allineate al rialzo — struttura bullish solida; trend molto direzionale (ADX 51); RSI ipercomprato (78) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (87.35)</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         <v>67.867028752685</v>
       </c>
       <c r="J15" t="n">
-        <v>19.97568501248483</v>
+        <v>19.97983365715019</v>
       </c>
       <c r="K15" t="n">
         <v>0.8749002646490039</v>
@@ -1801,7 +1801,7 @@
         <v>-18.05625692206467</v>
       </c>
       <c r="R15" t="n">
-        <v>83.00444873842726</v>
+        <v>83.03632192877889</v>
       </c>
       <c r="S15" t="n">
         <v>5.20580989030861</v>
@@ -1939,52 +1939,52 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6.58050012588501</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="E17" t="n">
-        <v>1.865326424558389</v>
+        <v>1.857583356818426</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2879013999481983</v>
+        <v>-0.295480794832137</v>
       </c>
       <c r="G17" t="n">
-        <v>4.369552815974953</v>
+        <v>4.361619394998373</v>
       </c>
       <c r="H17" t="n">
-        <v>3.760645190298018</v>
+        <v>3.752758054089367</v>
       </c>
       <c r="I17" t="n">
-        <v>56.79141938110121</v>
+        <v>56.76376708173776</v>
       </c>
       <c r="J17" t="n">
         <v>26.02354401785365</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6152009118553925</v>
+        <v>0.6142099451308163</v>
       </c>
       <c r="L17" t="n">
-        <v>6.509759561051393</v>
+        <v>6.509711922748636</v>
       </c>
       <c r="M17" t="n">
-        <v>6.401051240510292</v>
+        <v>6.401031624738567</v>
       </c>
       <c r="N17" t="n">
-        <v>5.931312437968564</v>
+        <v>5.931307460832455</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0167837307212637</v>
+        <v>-0.01681565245576103</v>
       </c>
       <c r="P17" t="n">
-        <v>54.1925385356954</v>
+        <v>54.03719625697671</v>
       </c>
       <c r="Q17" t="n">
-        <v>-45.80746146430459</v>
+        <v>-45.96280374302329</v>
       </c>
       <c r="R17" t="n">
-        <v>18.97221828631143</v>
+        <v>18.89483333868553</v>
       </c>
       <c r="S17" t="n">
-        <v>4.121834606772712</v>
+        <v>4.113920015548511</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2407,52 +2407,52 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>93.88999938964844</v>
+        <v>93.87000274658203</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1172964510379737</v>
+        <v>0.09597352149361971</v>
       </c>
       <c r="F22" t="n">
-        <v>6.066428999353857</v>
+        <v>6.043839026664366</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.753404396543628</v>
+        <v>-6.773264007807455</v>
       </c>
       <c r="H22" t="n">
-        <v>-9.320070929641789</v>
+        <v>-9.339383893607012</v>
       </c>
       <c r="I22" t="n">
-        <v>60.56130283166888</v>
+        <v>60.5344425097672</v>
       </c>
       <c r="J22" t="n">
         <v>12.38703016093908</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8658204156834951</v>
+        <v>0.86483562255297</v>
       </c>
       <c r="L22" t="n">
-        <v>88.75662861290509</v>
+        <v>88.75472417070829</v>
       </c>
       <c r="M22" t="n">
-        <v>87.94771391797379</v>
+        <v>87.94692973589275</v>
       </c>
       <c r="N22" t="n">
-        <v>84.39282947048417</v>
+        <v>84.39263049891137</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7433540745519336</v>
+        <v>0.7420779355072282</v>
       </c>
       <c r="P22" t="n">
-        <v>94.48442354848257</v>
+        <v>94.3645395994385</v>
       </c>
       <c r="Q22" t="n">
-        <v>-5.51557645151744</v>
+        <v>-5.635460400561501</v>
       </c>
       <c r="R22" t="n">
-        <v>115.2060395151271</v>
+        <v>115.0992049275595</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.986153571089589</v>
+        <v>-3.00681552946801</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
-        <v>69.40000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="X22" t="n">
         <v>76.2</v>
@@ -2513,7 +2513,7 @@
         <v>69.06885848949715</v>
       </c>
       <c r="J23" t="n">
-        <v>37.73493847278824</v>
+        <v>37.74111804385331</v>
       </c>
       <c r="K23" t="n">
         <v>1.031868685591115</v>
@@ -2531,13 +2531,13 @@
         <v>7.325665615974905</v>
       </c>
       <c r="P23" t="n">
-        <v>100</v>
+        <v>99.73684210526315</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0</v>
+        <v>-0.2631578947368421</v>
       </c>
       <c r="R23" t="n">
-        <v>116.8862032287912</v>
+        <v>117.0461623641771</v>
       </c>
       <c r="S23" t="n">
         <v>-0.6209935897435903</v>
@@ -2679,52 +2679,52 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2439.72998046875</v>
+        <v>2466.969970703125</v>
       </c>
       <c r="E25" t="n">
-        <v>4.872161154016963</v>
+        <v>6.043076242392598</v>
       </c>
       <c r="F25" t="n">
-        <v>30.19232652053003</v>
+        <v>31.64594545844561</v>
       </c>
       <c r="G25" t="n">
-        <v>31.14388665477599</v>
+        <v>32.60812991955224</v>
       </c>
       <c r="H25" t="n">
-        <v>40.27068524462154</v>
+        <v>41.83683073072917</v>
       </c>
       <c r="I25" t="n">
-        <v>86.99543560415702</v>
+        <v>87.49700412693521</v>
       </c>
       <c r="J25" t="n">
-        <v>28.41948207656204</v>
+        <v>28.44719344158946</v>
       </c>
       <c r="K25" t="n">
-        <v>1.216549926960047</v>
+        <v>1.236754846023511</v>
       </c>
       <c r="L25" t="n">
-        <v>2006.282067313571</v>
+        <v>2008.876352097798</v>
       </c>
       <c r="M25" t="n">
-        <v>1922.261557820673</v>
+        <v>1923.329792731825</v>
       </c>
       <c r="N25" t="n">
-        <v>2129.002104807339</v>
+        <v>2129.273149486288</v>
       </c>
       <c r="O25" t="n">
-        <v>54.80235400320829</v>
+        <v>56.54074654238205</v>
       </c>
       <c r="P25" t="n">
-        <v>99.37018836477155</v>
+        <v>101.9043398190051</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.6298116352284452</v>
+        <v>1.904339819005075</v>
       </c>
       <c r="R25" t="n">
-        <v>449.0344027749263</v>
+        <v>457.1297578345116</v>
       </c>
       <c r="S25" t="n">
-        <v>32.34818933867716</v>
+        <v>33.82587884283701</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>68.8</v>
       </c>
       <c r="X25" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>trend in sviluppo (ADX 28); RSI ipercomprato (87) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (2,443)</t>
+          <t>trend in sviluppo (ADX 28); RSI ipercomprato (87) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (2,455)</t>
         </is>
       </c>
     </row>
@@ -2867,52 +2867,52 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>86.68000030517578</v>
+        <v>86.63999938964844</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.309349313337138</v>
+        <v>-1.354892880106362</v>
       </c>
       <c r="F27" t="n">
-        <v>5.194173179660289</v>
+        <v>5.145628380161993</v>
       </c>
       <c r="G27" t="n">
-        <v>-5.976789229105939</v>
+        <v>-6.020178874911364</v>
       </c>
       <c r="H27" t="n">
-        <v>-10.26914940542453</v>
+        <v>-10.31055822132432</v>
       </c>
       <c r="I27" t="n">
-        <v>58.25221093667407</v>
+        <v>58.16584672151309</v>
       </c>
       <c r="J27" t="n">
         <v>13.23431822388321</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8194653060240282</v>
+        <v>0.8170136980712632</v>
       </c>
       <c r="L27" t="n">
-        <v>83.01473305982823</v>
+        <v>83.01092344882564</v>
       </c>
       <c r="M27" t="n">
-        <v>82.68721009714103</v>
+        <v>82.68564143378703</v>
       </c>
       <c r="N27" t="n">
-        <v>79.54291660049277</v>
+        <v>79.5425185814328</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6468685953746718</v>
+        <v>0.6443158303951624</v>
       </c>
       <c r="P27" t="n">
-        <v>84.28184716091972</v>
+        <v>84.01083828735625</v>
       </c>
       <c r="Q27" t="n">
-        <v>-15.71815283908028</v>
+        <v>-15.98916171264375</v>
       </c>
       <c r="R27" t="n">
-        <v>99.35578838380258</v>
+        <v>99.09989563841545</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.944796019832496</v>
+        <v>-2.989584863882233</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2945,83 +2945,83 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Consumer Discr.</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Settoriali</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>118.0199966430664</v>
+        <v>11.97900009155273</v>
       </c>
       <c r="E28" t="n">
-        <v>1.148437036669425</v>
+        <v>12.09035268652392</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1522845260771066</v>
+        <v>27.64641202880376</v>
       </c>
       <c r="G28" t="n">
-        <v>8.514154399553121</v>
+        <v>46.77817900010493</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.9733207410127842</v>
+        <v>50.17125301060921</v>
       </c>
       <c r="I28" t="n">
-        <v>53.73029422929575</v>
+        <v>87.54337711781854</v>
       </c>
       <c r="J28" t="n">
-        <v>33.93303183889963</v>
+        <v>60.02769318110039</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6088981011141292</v>
+        <v>1.207878273004857</v>
       </c>
       <c r="L28" t="n">
-        <v>117.0979731369855</v>
+        <v>9.390737305486125</v>
       </c>
       <c r="M28" t="n">
-        <v>116.5533882308409</v>
+        <v>8.794062003577386</v>
       </c>
       <c r="N28" t="n">
-        <v>115.8345123462193</v>
+        <v>9.578830033711011</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.0269388460976745</v>
+        <v>0.3015425459489734</v>
       </c>
       <c r="P28" t="n">
-        <v>44.62232774950461</v>
+        <v>100.9095511446577</v>
       </c>
       <c r="Q28" t="n">
-        <v>-55.37767225049539</v>
+        <v>0.9095511446576798</v>
       </c>
       <c r="R28" t="n">
-        <v>21.67265689900711</v>
+        <v>269.9013309862351</v>
       </c>
       <c r="S28" t="n">
-        <v>7.86947508707454</v>
+        <v>48.69659407173628</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Trend Bullish</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Double Top, Double Bottom, Bear Flag / Consolidation</t>
+          <t>Breakout 20d, Breakout 50d</t>
         </is>
       </c>
       <c r="W28" t="n">
         <v>68</v>
       </c>
       <c r="X28" t="n">
-        <v>77.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -3030,90 +3030,90 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>EMA allineate al rialzo (EMA20&gt;EMA50&gt;EMA200); trend molto direzionale (ADX 34); pattern: Double Bottom; in zona Fib Fib 23.6 — livello strutturale</t>
+          <t>trend molto direzionale (ADX 60); RSI ipercomprato (88) — attenzione estensione; breakout massimi 50g — rottura resistenza rilevante; vicino alla resistenza dei 20g (11.94)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Consumer Discr.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Settoriali</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.75599956512451</v>
+        <v>118.0199966430664</v>
       </c>
       <c r="E29" t="n">
-        <v>10.00368372704654</v>
+        <v>1.148437036669425</v>
       </c>
       <c r="F29" t="n">
-        <v>25.2701521